--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -15,8 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="86ed" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master'!$A$1:$N$660</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Whales'!$A$1:$N$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master'!$A$1:$N$662</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Whales'!$A$1:$N$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deadlines'!$A$1:$H$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Physical copies'!$A$1:$D$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'86ed'!$A$1:$C$12</definedName>
@@ -612,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N660"/>
+  <dimension ref="A1:N662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -25253,42 +25253,144 @@
       <c r="N631" s="5" t="inlineStr"/>
     </row>
     <row r="632">
-      <c r="A632" s="5" t="inlineStr"/>
+      <c r="A632" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
       <c r="B632" s="5" t="inlineStr">
         <is>
+          <t>New Jul 28-29</t>
+        </is>
+      </c>
+      <c r="C632" s="5" t="inlineStr">
+        <is>
+          <t>Briana Walker</t>
+        </is>
+      </c>
+      <c r="D632" s="5" t="inlineStr">
+        <is>
+          <t>MAESP Zone 4 (Eastern Shore) Rep · 2026 NAESP National Outstanding Assistant Principal · Greensboro Elementary, Caroline County</t>
+        </is>
+      </c>
+      <c r="E632" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The single best fit on the screen, because she sits at the intersection of three things already in the repo. She is the **MAESP Zone 4 rep for the Eastern Shore** — the same association you have nine letters written for — which makes her a distribution node, not just a reader. She is a **2026 NAESP </t>
+        </is>
+      </c>
+      <c r="F632" s="5" t="inlineStr">
+        <is>
+          <t>Gatekeeper · connected Jul 28 · 1st-degree</t>
+        </is>
+      </c>
+      <c r="G632" s="5" t="inlineStr"/>
+      <c r="H632" s="5" t="inlineStr"/>
+      <c r="I632" s="5" t="n">
+        <v>1409</v>
+      </c>
+      <c r="J632" s="5" t="inlineStr">
+        <is>
+          <t>Briana — congratulations on the National Outstanding Assistant Principal award. First elementary winner from Caroline County, which I did not know until I went looking, and now I can't unsee how overdue it was.
+I'm writing because you're the Eastern Shore rep for MAESP and I'm down your way often — I spend a good part of the year in Rehoboth, so Greensboro is nearly the neighborhood.
+I wrote and illustrated a K-5 book about money that does the one thing the rest of the shelf skips. Every other kids' money book teaches saving. Mine teaches a purchase — a boy earns a robot, reads the sale ads, compares two models, takes the marked-down one on purpose, hands a coupon to the cashier, and runs face-first into sales tax. Sixteen-plus concepts, none of them announced as a lesson.
+Here is why I'm writing you and not a longer list. MAESP recognized you as a Connected School Leader for actually using the digital tools, and the entire teacher kit behind the book is free, ungated, and prints from a browser — four lesson plans, assessments with answer keys, a standards crosswalk. No account, no budget line. It is exactly the kind of thing that dies in a staff room unless a principal who gets it hands it over.
+Would it be useful on the Eastern Shore, or am I overreaching? Toolkit: clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="K632" s="5" t="inlineStr"/>
+      <c r="L632" s="5" t="inlineStr"/>
+      <c r="M632" s="5" t="inlineStr"/>
+      <c r="N632" s="5" t="inlineStr"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
+      <c r="B633" s="5" t="inlineStr">
+        <is>
+          <t>New Jul 28-29</t>
+        </is>
+      </c>
+      <c r="C633" s="5" t="inlineStr">
+        <is>
+          <t>Lauren Nowacki</t>
+        </is>
+      </c>
+      <c r="D633" s="5" t="inlineStr">
+        <is>
+          <t>Money Deputy Editor, WSJ Buy Side · Certified Financial Health Counselor</t>
+        </is>
+      </c>
+      <c r="E633" s="5" t="inlineStr">
+        <is>
+          <t>Press whale. Buy Side is the Wall Street Journal's personal-finance</t>
+        </is>
+      </c>
+      <c r="F633" s="5" t="inlineStr">
+        <is>
+          <t>Press / Editor · connected Jul 29 · 1st-degree</t>
+        </is>
+      </c>
+      <c r="G633" s="5" t="inlineStr"/>
+      <c r="H633" s="5" t="inlineStr"/>
+      <c r="I633" s="5" t="n">
+        <v>1288</v>
+      </c>
+      <c r="J633" s="5" t="inlineStr">
+        <is>
+          <t>Lauren — a story rather than a pitch, and you can kill it in one line.
+I read all 25 titles on the ABA Foundation's children's financial literacy list to be sure of this: every single one teaches earning, saving, or investing. Not one teaches spending — the only money thing a seven-year-old has actually done.
+That is the gap I wrote into. Clarence Gets a Bargain is a 36-page picture book for grades 1-5 where a boy earns a robot and runs one complete purchase: reads the sale ads at the kitchen table, compares two models, takes the marked-down one on purpose, hands a coupon to the cashier, and gets ambushed by sales tax. His mom photographs every receipt the second she sits down in the car. Nobody in the book ever says the word "budget."
+Why you, and why now. Buy Side runs the gift guides and the teach-your-kid-about-money service pieces. You are a Certified Financial Health Counselor, so you will spot in a page whether the substance holds. And this is the season for it. The real angle is bigger than one book: why the entire children's money category skipped the cash register for forty years — told through the one that didn't.
+Happy to send you the whole thing. Four-minute flip if you would rather glance first: https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="K633" s="5" t="inlineStr"/>
+      <c r="L633" s="5" t="inlineStr"/>
+      <c r="M633" s="5" t="inlineStr"/>
+      <c r="N633" s="5" t="inlineStr"/>
+    </row>
+    <row r="634">
+      <c r="A634" s="5" t="inlineStr"/>
+      <c r="B634" s="5" t="inlineStr">
+        <is>
           <t>MAESP/NAESP</t>
         </is>
       </c>
-      <c r="C632" s="5" t="inlineStr">
+      <c r="C634" s="5" t="inlineStr">
         <is>
           <t>Dr. Christopher Wooleyhand</t>
         </is>
       </c>
-      <c r="D632" s="5" t="inlineStr">
+      <c r="D634" s="5" t="inlineStr">
         <is>
           <t>Executive Director, MAESP · Principal, Pershing Hill Elementary, Fort Meade</t>
         </is>
       </c>
-      <c r="E632" s="5" t="inlineStr"/>
-      <c r="F632" s="5" t="inlineStr">
+      <c r="E634" s="5" t="inlineStr"/>
+      <c r="F634" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G632" s="5" t="inlineStr">
+      <c r="G634" s="5" t="inlineStr">
         <is>
           <t>chriswooleyhand@maesp.org</t>
         </is>
       </c>
-      <c r="H632" s="5" t="inlineStr">
+      <c r="H634" s="5" t="inlineStr">
         <is>
           <t>Common sense, uncommon times, and a money book with no piggy bank</t>
         </is>
       </c>
-      <c r="I632" s="5" t="n">
+      <c r="I634" s="5" t="n">
         <v>1569</v>
       </c>
-      <c r="J632" s="5" t="inlineStr">
+      <c r="J634" s="5" t="inlineStr">
         <is>
           <t>Dr. Wooleyhand — you run a state association and a building at the same time, and you write under the banner of common sense school leadership for uncommon times. I will try to earn that standard.
 Here is the uncommon-sense part.
@@ -25302,52 +25404,52 @@
 Baltimore</t>
         </is>
       </c>
-      <c r="K632" s="5" t="inlineStr"/>
-      <c r="L632" s="5" t="inlineStr">
+      <c r="K634" s="5" t="inlineStr"/>
+      <c r="L634" s="5" t="inlineStr">
         <is>
           <t>Now. Presidents rotate; he does not.</t>
         </is>
       </c>
-      <c r="M632" s="5" t="inlineStr"/>
-      <c r="N632" s="5" t="inlineStr"/>
-    </row>
-    <row r="633">
-      <c r="A633" s="5" t="inlineStr"/>
-      <c r="B633" s="5" t="inlineStr">
+      <c r="M634" s="5" t="inlineStr"/>
+      <c r="N634" s="5" t="inlineStr"/>
+    </row>
+    <row r="635">
+      <c r="A635" s="5" t="inlineStr"/>
+      <c r="B635" s="5" t="inlineStr">
         <is>
           <t>MAESP/NAESP</t>
         </is>
       </c>
-      <c r="C633" s="5" t="inlineStr">
+      <c r="C635" s="5" t="inlineStr">
         <is>
           <t>Tracy Hilliard</t>
         </is>
       </c>
-      <c r="D633" s="5" t="inlineStr">
+      <c r="D635" s="5" t="inlineStr">
         <is>
           <t>NAESP Representative, MAESP · Frederick County Public Schools</t>
         </is>
       </c>
-      <c r="E633" s="5" t="inlineStr"/>
-      <c r="F633" s="5" t="inlineStr">
+      <c r="E635" s="5" t="inlineStr"/>
+      <c r="F635" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G633" s="5" t="inlineStr">
+      <c r="G635" s="5" t="inlineStr">
         <is>
           <t>tracy.hilliard@fcps.org</t>
         </is>
       </c>
-      <c r="H633" s="5" t="inlineStr">
+      <c r="H635" s="5" t="inlineStr">
         <is>
           <t>You are the one person standing in both doorways</t>
         </is>
       </c>
-      <c r="I633" s="5" t="n">
+      <c r="I635" s="5" t="n">
         <v>1161</v>
       </c>
-      <c r="J633" s="5" t="inlineStr">
+      <c r="J635" s="5" t="inlineStr">
         <is>
           <t>Ms. Hilliard — you are MAESP's NAESP Representative, which as far as I can tell makes you the one person with a foot in both the state and national conversation. That is why you are getting this rather than a longer list of people.
 The claim, and you can check it in an afternoon: every children's financial literacy book teaches saving. I read all 25 on the ABA Foundation's list. Not one teaches spending — the only money thing an elementary student actually does.
@@ -25359,52 +25461,52 @@
 Baltimore</t>
         </is>
       </c>
-      <c r="K633" s="5" t="inlineStr"/>
-      <c r="L633" s="5" t="inlineStr">
+      <c r="K635" s="5" t="inlineStr"/>
+      <c r="L635" s="5" t="inlineStr">
         <is>
           <t>Now. She is the state-to-national bridge.</t>
         </is>
       </c>
-      <c r="M633" s="5" t="inlineStr"/>
-      <c r="N633" s="5" t="inlineStr"/>
-    </row>
-    <row r="634">
-      <c r="A634" s="5" t="inlineStr"/>
-      <c r="B634" s="5" t="inlineStr">
+      <c r="M635" s="5" t="inlineStr"/>
+      <c r="N635" s="5" t="inlineStr"/>
+    </row>
+    <row r="636">
+      <c r="A636" s="5" t="inlineStr"/>
+      <c r="B636" s="5" t="inlineStr">
         <is>
           <t>MAESP/NAESP</t>
         </is>
       </c>
-      <c r="C634" s="5" t="inlineStr">
+      <c r="C636" s="5" t="inlineStr">
         <is>
           <t>Kaylen Tucker, Ph.D.</t>
         </is>
       </c>
-      <c r="D634" s="5" t="inlineStr">
+      <c r="D636" s="5" t="inlineStr">
         <is>
           <t>Assoc. Exec. Director, Communications; Editor-in-Chief, Principal magazine</t>
         </is>
       </c>
-      <c r="E634" s="5" t="inlineStr"/>
-      <c r="F634" s="5" t="inlineStr">
+      <c r="E636" s="5" t="inlineStr"/>
+      <c r="F636" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G634" s="5" t="inlineStr">
+      <c r="G636" s="5" t="inlineStr">
         <is>
           <t>ktucker@naesp.org</t>
         </is>
       </c>
-      <c r="H634" s="5" t="inlineStr">
+      <c r="H636" s="5" t="inlineStr">
         <is>
           <t>A story about what children's money books have skipped for forty years</t>
         </is>
       </c>
-      <c r="I634" s="5" t="n">
+      <c r="I636" s="5" t="n">
         <v>1220</v>
       </c>
-      <c r="J634" s="5" t="inlineStr">
+      <c r="J636" s="5" t="inlineStr">
         <is>
           <t>Dr. Tucker — a story idea rather than a book pitch, and you can reject it in one line.
 I read every title on the ABA Foundation's children's financial literacy list. All 25. Every single one teaches earning, saving, or investing. Not one teaches spending.
@@ -25418,52 +25520,52 @@
 Jonathan Bach</t>
         </is>
       </c>
-      <c r="K634" s="5" t="inlineStr"/>
-      <c r="L634" s="5" t="inlineStr">
+      <c r="K636" s="5" t="inlineStr"/>
+      <c r="L636" s="5" t="inlineStr">
         <is>
           <t>Now. Best first NAESP contact.</t>
         </is>
       </c>
-      <c r="M634" s="5" t="inlineStr"/>
-      <c r="N634" s="5" t="inlineStr"/>
-    </row>
-    <row r="635">
-      <c r="A635" s="5" t="inlineStr"/>
-      <c r="B635" s="5" t="inlineStr">
+      <c r="M636" s="5" t="inlineStr"/>
+      <c r="N636" s="5" t="inlineStr"/>
+    </row>
+    <row r="637">
+      <c r="A637" s="5" t="inlineStr"/>
+      <c r="B637" s="5" t="inlineStr">
         <is>
           <t>MAESP/NAESP</t>
         </is>
       </c>
-      <c r="C635" s="5" t="inlineStr">
+      <c r="C637" s="5" t="inlineStr">
         <is>
           <t>Justin Holbrook</t>
         </is>
       </c>
-      <c r="D635" s="5" t="inlineStr">
+      <c r="D637" s="5" t="inlineStr">
         <is>
           <t>President, MAESP · Baltimore County Public Schools</t>
         </is>
       </c>
-      <c r="E635" s="5" t="inlineStr"/>
-      <c r="F635" s="5" t="inlineStr">
+      <c r="E637" s="5" t="inlineStr"/>
+      <c r="F637" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G635" s="5" t="inlineStr">
+      <c r="G637" s="5" t="inlineStr">
         <is>
           <t>JCHolbrook@bcps.k12.md.us</t>
         </is>
       </c>
-      <c r="H635" s="5" t="inlineStr">
+      <c r="H637" s="5" t="inlineStr">
         <is>
           <t>Baltimore County neighbor, one K-5 question</t>
         </is>
       </c>
-      <c r="I635" s="5" t="n">
+      <c r="I637" s="5" t="n">
         <v>1292</v>
       </c>
-      <c r="J635" s="5" t="inlineStr">
+      <c r="J637" s="5" t="inlineStr">
         <is>
           <t>Mr. Holbrook — congratulations on the MAESP presidency, and hello from a few miles away. I am in Baltimore.
 One question, and the setup takes thirty seconds.
@@ -25476,52 +25578,52 @@
 Baltimore</t>
         </is>
       </c>
-      <c r="K635" s="5" t="inlineStr"/>
-      <c r="L635" s="5" t="inlineStr">
+      <c r="K637" s="5" t="inlineStr"/>
+      <c r="L637" s="5" t="inlineStr">
         <is>
           <t>Now</t>
         </is>
       </c>
-      <c r="M635" s="5" t="inlineStr"/>
-      <c r="N635" s="5" t="inlineStr"/>
-    </row>
-    <row r="636">
-      <c r="A636" s="5" t="inlineStr"/>
-      <c r="B636" s="5" t="inlineStr">
+      <c r="M637" s="5" t="inlineStr"/>
+      <c r="N637" s="5" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="5" t="inlineStr"/>
+      <c r="B638" s="5" t="inlineStr">
         <is>
           <t>MAESP/NAESP</t>
         </is>
       </c>
-      <c r="C636" s="5" t="inlineStr">
+      <c r="C638" s="5" t="inlineStr">
         <is>
           <t>Dr. Sharon H. Porter</t>
         </is>
       </c>
-      <c r="D636" s="5" t="inlineStr">
+      <c r="D638" s="5" t="inlineStr">
         <is>
           <t>President-Elect, MAESP · Prince George's County Public Schools</t>
         </is>
       </c>
-      <c r="E636" s="5" t="inlineStr"/>
-      <c r="F636" s="5" t="inlineStr">
+      <c r="E638" s="5" t="inlineStr"/>
+      <c r="F638" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G636" s="5" t="inlineStr">
+      <c r="G638" s="5" t="inlineStr">
         <is>
           <t>sharonh.porter@pgcps.org</t>
         </is>
       </c>
-      <c r="H636" s="5" t="inlineStr">
+      <c r="H638" s="5" t="inlineStr">
         <is>
           <t>Something for the year you are about to inherit</t>
         </is>
       </c>
-      <c r="I636" s="5" t="n">
+      <c r="I638" s="5" t="n">
         <v>1218</v>
       </c>
-      <c r="J636" s="5" t="inlineStr">
+      <c r="J638" s="5" t="inlineStr">
         <is>
           <t>Dr. Porter — congratulations on President-Elect. You have a year to think about what you want your term to be about, which is more planning time than most people get.
 A candidate, offered without obligation.
@@ -25534,52 +25636,52 @@
 Baltimore</t>
         </is>
       </c>
-      <c r="K636" s="5" t="inlineStr"/>
-      <c r="L636" s="5" t="inlineStr">
+      <c r="K638" s="5" t="inlineStr"/>
+      <c r="L638" s="5" t="inlineStr">
         <is>
           <t>Now</t>
         </is>
       </c>
-      <c r="M636" s="5" t="inlineStr"/>
-      <c r="N636" s="5" t="inlineStr"/>
-    </row>
-    <row r="637">
-      <c r="A637" s="5" t="inlineStr"/>
-      <c r="B637" s="5" t="inlineStr">
+      <c r="M638" s="5" t="inlineStr"/>
+      <c r="N638" s="5" t="inlineStr"/>
+    </row>
+    <row r="639">
+      <c r="A639" s="5" t="inlineStr"/>
+      <c r="B639" s="5" t="inlineStr">
         <is>
           <t>MAESP/NAESP</t>
         </is>
       </c>
-      <c r="C637" s="5" t="inlineStr">
+      <c r="C639" s="5" t="inlineStr">
         <is>
           <t>Dr. Glen Messier</t>
         </is>
       </c>
-      <c r="D637" s="5" t="inlineStr">
+      <c r="D639" s="5" t="inlineStr">
         <is>
           <t>Treasurer, MAESP · Carroll County Public Schools</t>
         </is>
       </c>
-      <c r="E637" s="5" t="inlineStr"/>
-      <c r="F637" s="5" t="inlineStr">
+      <c r="E639" s="5" t="inlineStr"/>
+      <c r="F639" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G637" s="5" t="inlineStr">
+      <c r="G639" s="5" t="inlineStr">
         <is>
           <t>gpmessi@carrollk12.org</t>
         </is>
       </c>
-      <c r="H637" s="5" t="inlineStr">
+      <c r="H639" s="5" t="inlineStr">
         <is>
           <t>A K-5 resource with no recurring cost — treasurer's version</t>
         </is>
       </c>
-      <c r="I637" s="5" t="n">
+      <c r="I639" s="5" t="n">
         <v>1106</v>
       </c>
-      <c r="J637" s="5" t="inlineStr">
+      <c r="J639" s="5" t="inlineStr">
         <is>
           <t>Dr. Messier — you are the treasurer, so I will lead with the money and you can decide whether the rest is worth reading.
 The classroom toolkit is free. Not freemium, not free-with-registration. Four 45-minute lesson plans, a pre/post assessment with the answer key, a 23-row standards crosswalk, print-ready. No login, no seats, no renewal, nothing consumable to reorder next August. The only cost that ever exists is the copies of the book, at $19.99, with PO and Net 30 terms available.
@@ -25591,52 +25693,52 @@
 Baltimore</t>
         </is>
       </c>
-      <c r="K637" s="5" t="inlineStr"/>
-      <c r="L637" s="5" t="inlineStr">
+      <c r="K639" s="5" t="inlineStr"/>
+      <c r="L639" s="5" t="inlineStr">
         <is>
           <t>Now</t>
         </is>
       </c>
-      <c r="M637" s="5" t="inlineStr"/>
-      <c r="N637" s="5" t="inlineStr"/>
-    </row>
-    <row r="638">
-      <c r="A638" s="5" t="inlineStr"/>
-      <c r="B638" s="5" t="inlineStr">
+      <c r="M639" s="5" t="inlineStr"/>
+      <c r="N639" s="5" t="inlineStr"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="5" t="inlineStr"/>
+      <c r="B640" s="5" t="inlineStr">
         <is>
           <t>MAESP/NAESP</t>
         </is>
       </c>
-      <c r="C638" s="5" t="inlineStr">
+      <c r="C640" s="5" t="inlineStr">
         <is>
           <t>April D. Knight</t>
         </is>
       </c>
-      <c r="D638" s="5" t="inlineStr">
+      <c r="D640" s="5" t="inlineStr">
         <is>
           <t>President, NAESP · Principal, Avondale Elementary, Columbus OH</t>
         </is>
       </c>
-      <c r="E638" s="5" t="inlineStr"/>
-      <c r="F638" s="5" t="inlineStr">
+      <c r="E640" s="5" t="inlineStr"/>
+      <c r="F640" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G638" s="5" t="inlineStr">
+      <c r="G640" s="5" t="inlineStr">
         <is>
           <t>via NAESP</t>
         </is>
       </c>
-      <c r="H638" s="5" t="inlineStr">
+      <c r="H640" s="5" t="inlineStr">
         <is>
           <t>From a principal's chair: the money book that skips the piggy bank</t>
         </is>
       </c>
-      <c r="I638" s="5" t="n">
+      <c r="I640" s="5" t="n">
         <v>1421</v>
       </c>
-      <c r="J638" s="5" t="inlineStr">
+      <c r="J640" s="5" t="inlineStr">
         <is>
           <t>Ms. Knight — you run a building, so I will be quick and you can delete this at any point.
 Financial literacy arrives in elementary schools as an unfunded expectation. The mandates were written for high school, the materials were written for high school, and then somebody hands you six-year-olds and a poster of a pig.
@@ -25648,52 +25750,52 @@
 Jonathan Bach</t>
         </is>
       </c>
-      <c r="K638" s="5" t="inlineStr"/>
-      <c r="L638" s="5" t="inlineStr">
+      <c r="K640" s="5" t="inlineStr"/>
+      <c r="L640" s="5" t="inlineStr">
         <is>
           <t>Now</t>
         </is>
       </c>
-      <c r="M638" s="5" t="inlineStr"/>
-      <c r="N638" s="5" t="inlineStr"/>
-    </row>
-    <row r="639">
-      <c r="A639" s="5" t="inlineStr"/>
-      <c r="B639" s="5" t="inlineStr">
+      <c r="M640" s="5" t="inlineStr"/>
+      <c r="N640" s="5" t="inlineStr"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="5" t="inlineStr"/>
+      <c r="B641" s="5" t="inlineStr">
         <is>
           <t>MAESP/NAESP</t>
         </is>
       </c>
-      <c r="C639" s="5" t="inlineStr">
+      <c r="C641" s="5" t="inlineStr">
         <is>
           <t>David Griffith</t>
         </is>
       </c>
-      <c r="D639" s="5" t="inlineStr">
+      <c r="D641" s="5" t="inlineStr">
         <is>
           <t>Assoc. Exec. Director, Policy &amp; Advocacy, NAESP</t>
         </is>
       </c>
-      <c r="E639" s="5" t="inlineStr"/>
-      <c r="F639" s="5" t="inlineStr">
+      <c r="E641" s="5" t="inlineStr"/>
+      <c r="F641" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G639" s="5" t="inlineStr">
+      <c r="G641" s="5" t="inlineStr">
         <is>
           <t>via NAESP</t>
         </is>
       </c>
-      <c r="H639" s="5" t="inlineStr">
+      <c r="H641" s="5" t="inlineStr">
         <is>
           <t>The K-5 hole in every financial literacy mandate</t>
         </is>
       </c>
-      <c r="I639" s="5" t="n">
+      <c r="I641" s="5" t="n">
         <v>1133</v>
       </c>
-      <c r="J639" s="5" t="inlineStr">
+      <c r="J641" s="5" t="inlineStr">
         <is>
           <t>Mr. Griffith — a policy observation, offered because it is your beat and it annoys me.
 Financial literacy mandates keep passing. Most states have one now. Almost every one of them lands in high school, where the money is, the graduation requirement is, and the political credit is.
@@ -25704,52 +25806,52 @@
 Jonathan Bach</t>
         </is>
       </c>
-      <c r="K639" s="5" t="inlineStr"/>
-      <c r="L639" s="5" t="inlineStr">
+      <c r="K641" s="5" t="inlineStr"/>
+      <c r="L641" s="5" t="inlineStr">
         <is>
           <t>Now</t>
         </is>
       </c>
-      <c r="M639" s="5" t="inlineStr"/>
-      <c r="N639" s="5" t="inlineStr"/>
-    </row>
-    <row r="640">
-      <c r="A640" s="5" t="inlineStr"/>
-      <c r="B640" s="5" t="inlineStr">
+      <c r="M641" s="5" t="inlineStr"/>
+      <c r="N641" s="5" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="5" t="inlineStr"/>
+      <c r="B642" s="5" t="inlineStr">
         <is>
           <t>MAESP/NAESP</t>
         </is>
       </c>
-      <c r="C640" s="5" t="inlineStr">
+      <c r="C642" s="5" t="inlineStr">
         <is>
           <t>Stephanie A. Morris</t>
         </is>
       </c>
-      <c r="D640" s="5" t="inlineStr">
+      <c r="D642" s="5" t="inlineStr">
         <is>
           <t>Incoming Executive Director, NAESP</t>
         </is>
       </c>
-      <c r="E640" s="5" t="inlineStr"/>
-      <c r="F640" s="5" t="inlineStr">
+      <c r="E642" s="5" t="inlineStr"/>
+      <c r="F642" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G640" s="5" t="inlineStr">
+      <c r="G642" s="5" t="inlineStr">
         <is>
           <t>via SHAPE America (starts NAESP 1 Aug 2026)</t>
         </is>
       </c>
-      <c r="H640" s="5" t="inlineStr">
+      <c r="H642" s="5" t="inlineStr">
         <is>
           <t>A K-5 question from someone who read your NAEYC background</t>
         </is>
       </c>
-      <c r="I640" s="5" t="n">
+      <c r="I642" s="5" t="n">
         <v>1703</v>
       </c>
-      <c r="J640" s="5" t="inlineStr">
+      <c r="J642" s="5" t="inlineStr">
         <is>
           <t>Ms. Morris — congratulations, and my sympathies. Nobody takes an executive director's chair and gets a quiet first month.
 I waited a few weeks on purpose. Here is the short version.
@@ -25763,56 +25865,56 @@
 Baltimore — and a fellow Maryland degree, though yours is the better one</t>
         </is>
       </c>
-      <c r="K640" s="5" t="inlineStr"/>
-      <c r="L640" s="5" t="inlineStr">
+      <c r="K642" s="5" t="inlineStr"/>
+      <c r="L642" s="5" t="inlineStr">
         <is>
           <t>Late September. Not week one.</t>
         </is>
       </c>
-      <c r="M640" s="5" t="inlineStr"/>
-      <c r="N640" s="5" t="inlineStr"/>
-    </row>
-    <row r="641">
-      <c r="A641" s="6" t="inlineStr">
+      <c r="M642" s="5" t="inlineStr"/>
+      <c r="N642" s="5" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" s="6" t="inlineStr">
         <is>
           <t>🔵</t>
         </is>
       </c>
-      <c r="B641" s="5" t="inlineStr">
+      <c r="B643" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C641" s="5" t="inlineStr">
+      <c r="C643" s="5" t="inlineStr">
         <is>
           <t>Dr. Bonnie Meszaros</t>
         </is>
       </c>
-      <c r="D641" s="5" t="inlineStr">
+      <c r="D643" s="5" t="inlineStr">
         <is>
           <t>Elementary School Program Coordinator, UD Center for Economic Education &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="E641" s="5" t="inlineStr"/>
-      <c r="F641" s="5" t="inlineStr">
+      <c r="E643" s="5" t="inlineStr"/>
+      <c r="F643" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G641" s="5" t="inlineStr">
+      <c r="G643" s="5" t="inlineStr">
         <is>
           <t>meszaros@udel.edu</t>
         </is>
       </c>
-      <c r="H641" s="5" t="inlineStr">
+      <c r="H643" s="5" t="inlineStr">
         <is>
           <t>You built lessons around picture books. I built a picture book around lessons.</t>
         </is>
       </c>
-      <c r="I641" s="5" t="n">
+      <c r="I643" s="5" t="n">
         <v>2598</v>
       </c>
-      <c r="J641" s="5" t="inlineStr">
+      <c r="J643" s="5" t="inlineStr">
         <is>
           <t>Dr. Meszaros — you wrote a K and first-grade curriculum where the lesson lives inside the book. Monster Musical Chairs carries scarcity. The Little Red Hen Makes Pizza carries producers and consumers. Bunny Money carries a savings goal. Colonial adopted the kindergarten set outright.
 I came at the same problem from the other end. I wrote the picture book and put the economics inside it, then checked it against the standards after — including the National Standards for Financial Literacy, which I understand you co-authored. That is an odd thing to write to someone. I'd rather say it than pretend I found the framework on my own.
@@ -25826,56 +25928,56 @@
 Baltimore, and Rehoboth Beach when I can manage it</t>
         </is>
       </c>
-      <c r="K641" s="5" t="inlineStr"/>
-      <c r="L641" s="5" t="inlineStr">
+      <c r="K643" s="5" t="inlineStr"/>
+      <c r="L643" s="5" t="inlineStr">
         <is>
           <t>First. Everything else in Delaware is easier after her.</t>
         </is>
       </c>
-      <c r="M641" s="5" t="inlineStr"/>
-      <c r="N641" s="5" t="inlineStr"/>
-    </row>
-    <row r="642">
-      <c r="A642" s="4" t="inlineStr">
+      <c r="M643" s="5" t="inlineStr"/>
+      <c r="N643" s="5" t="inlineStr"/>
+    </row>
+    <row r="644">
+      <c r="A644" s="4" t="inlineStr">
         <is>
           <t>🐋</t>
         </is>
       </c>
-      <c r="B642" s="5" t="inlineStr">
+      <c r="B644" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C642" s="5" t="inlineStr">
+      <c r="C644" s="5" t="inlineStr">
         <is>
           <t>Dr. Jennifer Nauman</t>
         </is>
       </c>
-      <c r="D642" s="5" t="inlineStr">
+      <c r="D644" s="5" t="inlineStr">
         <is>
           <t>Superintendent, Cape Henlopen School District</t>
         </is>
       </c>
-      <c r="E642" s="5" t="inlineStr"/>
-      <c r="F642" s="5" t="inlineStr">
+      <c r="E644" s="5" t="inlineStr"/>
+      <c r="F644" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G642" s="5" t="inlineStr">
+      <c r="G644" s="5" t="inlineStr">
         <is>
           <t>jennifer.nauman@cape.k12.de.us</t>
         </is>
       </c>
-      <c r="H642" s="5" t="inlineStr">
+      <c r="H644" s="5" t="inlineStr">
         <is>
           <t>Five elementary schools, a 2018 standard, and nothing to teach it with</t>
         </is>
       </c>
-      <c r="I642" s="5" t="n">
+      <c r="I644" s="5" t="n">
         <v>2008</v>
       </c>
-      <c r="J642" s="5" t="inlineStr">
+      <c r="J644" s="5" t="inlineStr">
         <is>
           <t>Dr. Nauman — you were an assistant principal at Rehoboth Elementary, then ran Shields for eight years and took it to a National Blue Ribbon. You are running a district now, but you learned the job in an elementary building, which is why this is going to you and not to a curriculum office.
 Delaware adopted financial literacy standards for grades K-12 in 2018. HB 203 arrived last October and put a half-credit personal finance course in front of ninth graders. Good law. It also means K-5 has carried a standard for eight years with essentially nothing built for it, and your five elementary principals are the ones holding that bag.
@@ -25889,56 +25991,56 @@
 clarencegetsabargain.com</t>
         </is>
       </c>
-      <c r="K642" s="5" t="inlineStr"/>
-      <c r="L642" s="5" t="inlineStr">
+      <c r="K644" s="5" t="inlineStr"/>
+      <c r="L644" s="5" t="inlineStr">
         <is>
           <t>Second. One yes covers five buildings.</t>
         </is>
       </c>
-      <c r="M642" s="5" t="inlineStr"/>
-      <c r="N642" s="5" t="inlineStr"/>
-    </row>
-    <row r="643">
-      <c r="A643" s="4" t="inlineStr">
+      <c r="M644" s="5" t="inlineStr"/>
+      <c r="N644" s="5" t="inlineStr"/>
+    </row>
+    <row r="645">
+      <c r="A645" s="4" t="inlineStr">
         <is>
           <t>🐋</t>
         </is>
       </c>
-      <c r="B643" s="5" t="inlineStr">
+      <c r="B645" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C643" s="5" t="inlineStr">
+      <c r="C645" s="5" t="inlineStr">
         <is>
           <t>Equetta Jones</t>
         </is>
       </c>
-      <c r="D643" s="5" t="inlineStr">
+      <c r="D645" s="5" t="inlineStr">
         <is>
           <t>Principal, Love Creek Elementary, Lewes</t>
         </is>
       </c>
-      <c r="E643" s="5" t="inlineStr"/>
-      <c r="F643" s="5" t="inlineStr">
+      <c r="E645" s="5" t="inlineStr"/>
+      <c r="F645" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G643" s="5" t="inlineStr">
+      <c r="G645" s="5" t="inlineStr">
         <is>
           <t>equetta.jones@cape.k12.de.us</t>
         </is>
       </c>
-      <c r="H643" s="5" t="inlineStr">
+      <c r="H645" s="5" t="inlineStr">
         <is>
           <t>A question you're better placed to answer than almost anyone</t>
         </is>
       </c>
-      <c r="I643" s="5" t="n">
+      <c r="I645" s="5" t="n">
         <v>1813</v>
       </c>
-      <c r="J643" s="5" t="inlineStr">
+      <c r="J645" s="5" t="inlineStr">
         <is>
           <t>Ms. Jones — you run Love Creek and you moderate NAESP's Early Career Principal Community of Practice, which means you spend part of your month listening to brand-new principals describe what they're short of. So I'll ask you the question I actually want answered instead of pitching first.
 When financial literacy shows up in an elementary building, what does a first-year principal do with it?
@@ -25951,52 +26053,52 @@
 https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K643" s="5" t="inlineStr"/>
-      <c r="L643" s="5" t="inlineStr">
+      <c r="K645" s="5" t="inlineStr"/>
+      <c r="L645" s="5" t="inlineStr">
         <is>
           <t>Third. Her NAESP seat turns a Lewes yes into a national one.</t>
         </is>
       </c>
-      <c r="M643" s="5" t="inlineStr"/>
-      <c r="N643" s="5" t="inlineStr"/>
-    </row>
-    <row r="644">
-      <c r="A644" s="5" t="inlineStr"/>
-      <c r="B644" s="5" t="inlineStr">
+      <c r="M645" s="5" t="inlineStr"/>
+      <c r="N645" s="5" t="inlineStr"/>
+    </row>
+    <row r="646">
+      <c r="A646" s="5" t="inlineStr"/>
+      <c r="B646" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C644" s="5" t="inlineStr">
+      <c r="C646" s="5" t="inlineStr">
         <is>
           <t>Mr. Matthew Keen</t>
         </is>
       </c>
-      <c r="D644" s="5" t="inlineStr">
+      <c r="D646" s="5" t="inlineStr">
         <is>
           <t>Principal, Rehoboth Elementary School</t>
         </is>
       </c>
-      <c r="E644" s="5" t="inlineStr"/>
-      <c r="F644" s="5" t="inlineStr">
+      <c r="E646" s="5" t="inlineStr"/>
+      <c r="F646" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G644" s="5" t="inlineStr">
+      <c r="G646" s="5" t="inlineStr">
         <is>
           <t>matthew.keen@cape.k12.de.us</t>
         </is>
       </c>
-      <c r="H644" s="5" t="inlineStr">
+      <c r="H646" s="5" t="inlineStr">
         <is>
           <t>From a Rehoboth author to the new guy at Rehoboth Elementary</t>
         </is>
       </c>
-      <c r="I644" s="5" t="n">
+      <c r="I646" s="5" t="n">
         <v>1407</v>
       </c>
-      <c r="J644" s="5" t="inlineStr">
+      <c r="J646" s="5" t="inlineStr">
         <is>
           <t>Mr. Keen — congratulations on the building. You took over a school in a town where I spend a good part of my year, so this is a local letter, and I'll keep it short because it's your first fall.
 I wrote and illustrated a children's book about money. Clarence Gets a Bargain — 36 pages, grades 1-5, and it does the one thing the rest of the category skips. Every other kids' money book teaches saving. Mine teaches a purchase: a boy earns a robot, reads the sale ads at his kitchen table, compares two on a shelf, walks past the newer one deliberately, redeems a coupon at the register, and gets ambushed by sales tax. He is not thrilled about the sales tax. Neither was I at that age.
@@ -26008,52 +26110,52 @@
 https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K644" s="5" t="inlineStr"/>
-      <c r="L644" s="5" t="inlineStr">
+      <c r="K646" s="5" t="inlineStr"/>
+      <c r="L646" s="5" t="inlineStr">
         <is>
           <t>Same week as Rodriguez. New principals say yes to things.</t>
         </is>
       </c>
-      <c r="M644" s="5" t="inlineStr"/>
-      <c r="N644" s="5" t="inlineStr"/>
-    </row>
-    <row r="645">
-      <c r="A645" s="5" t="inlineStr"/>
-      <c r="B645" s="5" t="inlineStr">
+      <c r="M646" s="5" t="inlineStr"/>
+      <c r="N646" s="5" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" s="5" t="inlineStr"/>
+      <c r="B647" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C645" s="5" t="inlineStr">
+      <c r="C647" s="5" t="inlineStr">
         <is>
           <t>Mr. Alfredo Rodriguez</t>
         </is>
       </c>
-      <c r="D645" s="5" t="inlineStr">
+      <c r="D647" s="5" t="inlineStr">
         <is>
           <t>Principal, Lewes Elementary School</t>
         </is>
       </c>
-      <c r="E645" s="5" t="inlineStr"/>
-      <c r="F645" s="5" t="inlineStr">
+      <c r="E647" s="5" t="inlineStr"/>
+      <c r="F647" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G645" s="5" t="inlineStr">
+      <c r="G647" s="5" t="inlineStr">
         <is>
           <t>alfredo.rodriguez@cape.k12.de.us</t>
         </is>
       </c>
-      <c r="H645" s="5" t="inlineStr">
+      <c r="H647" s="5" t="inlineStr">
         <is>
           <t>Something for grades 1-5 that costs your building nothing</t>
         </is>
       </c>
-      <c r="I645" s="5" t="n">
+      <c r="I647" s="5" t="n">
         <v>1620</v>
       </c>
-      <c r="J645" s="5" t="inlineStr">
+      <c r="J647" s="5" t="inlineStr">
         <is>
           <t>Mr. Rodriguez — congratulations on the promotion. You already know the staff, which means you already know which of them will actually run a new thing and which will nod politely. So here it is, and you can hand it to the right one.
 Clarence Gets a Bargain is a 36-page picture book for grades 1-5. A boy earns a robot for good grades and chores, does his homework in the newspaper inserts, compares two models in the store, goes with the older one at the lower price, hands over a coupon, and meets sales tax at the register. Sixteen-plus financial concepts, all of them load-bearing to the plot. A 21-term glossary in the back, every entry tied to the page where it happened.
@@ -26065,52 +26167,52 @@
 Baltimore and Rehoboth Beach</t>
         </is>
       </c>
-      <c r="K645" s="5" t="inlineStr"/>
-      <c r="L645" s="5" t="inlineStr">
+      <c r="K647" s="5" t="inlineStr"/>
+      <c r="L647" s="5" t="inlineStr">
         <is>
           <t>Same week as Keen.</t>
         </is>
       </c>
-      <c r="M645" s="5" t="inlineStr"/>
-      <c r="N645" s="5" t="inlineStr"/>
-    </row>
-    <row r="646">
-      <c r="A646" s="5" t="inlineStr"/>
-      <c r="B646" s="5" t="inlineStr">
+      <c r="M647" s="5" t="inlineStr"/>
+      <c r="N647" s="5" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="5" t="inlineStr"/>
+      <c r="B648" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C646" s="5" t="inlineStr">
+      <c r="C648" s="5" t="inlineStr">
         <is>
           <t>Dr. Clara Conn</t>
         </is>
       </c>
-      <c r="D646" s="5" t="inlineStr">
+      <c r="D648" s="5" t="inlineStr">
         <is>
           <t>Principal, Milton Elementary School</t>
         </is>
       </c>
-      <c r="E646" s="5" t="inlineStr"/>
-      <c r="F646" s="5" t="inlineStr">
+      <c r="E648" s="5" t="inlineStr"/>
+      <c r="F648" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G646" s="5" t="inlineStr">
+      <c r="G648" s="5" t="inlineStr">
         <is>
           <t>clara.conn@cape.k12.de.us</t>
         </is>
       </c>
-      <c r="H646" s="5" t="inlineStr">
+      <c r="H648" s="5" t="inlineStr">
         <is>
           <t>The money lesson your grade band is holding without a book</t>
         </is>
       </c>
-      <c r="I646" s="5" t="n">
+      <c r="I648" s="5" t="n">
         <v>1693</v>
       </c>
-      <c r="J646" s="5" t="inlineStr">
+      <c r="J648" s="5" t="inlineStr">
         <is>
           <t>Dr. Conn — short version first, in case that's all you have time for. I wrote a K-5 money book that teaches spending instead of saving, the teacher materials are free and ungated, and I'd like to put copies in Milton Elementary.
 Longer version.
@@ -26124,52 +26226,52 @@
 clarencegetsabargain.com</t>
         </is>
       </c>
-      <c r="K646" s="5" t="inlineStr"/>
-      <c r="L646" s="5" t="inlineStr">
+      <c r="K648" s="5" t="inlineStr"/>
+      <c r="L648" s="5" t="inlineStr">
         <is>
           <t>After the two Lewes/Rehoboth letters land.</t>
         </is>
       </c>
-      <c r="M646" s="5" t="inlineStr"/>
-      <c r="N646" s="5" t="inlineStr"/>
-    </row>
-    <row r="647">
-      <c r="A647" s="5" t="inlineStr"/>
-      <c r="B647" s="5" t="inlineStr">
+      <c r="M648" s="5" t="inlineStr"/>
+      <c r="N648" s="5" t="inlineStr"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="5" t="inlineStr"/>
+      <c r="B649" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C647" s="5" t="inlineStr">
+      <c r="C649" s="5" t="inlineStr">
         <is>
           <t>Mrs. Yvette Davenport</t>
         </is>
       </c>
-      <c r="D647" s="5" t="inlineStr">
+      <c r="D649" s="5" t="inlineStr">
         <is>
           <t>Principal, H.O. Brittingham Elementary, Milton</t>
         </is>
       </c>
-      <c r="E647" s="5" t="inlineStr"/>
-      <c r="F647" s="5" t="inlineStr">
+      <c r="E649" s="5" t="inlineStr"/>
+      <c r="F649" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G647" s="5" t="inlineStr">
+      <c r="G649" s="5" t="inlineStr">
         <is>
           <t>yvette.davenport@cape.k12.de.us</t>
         </is>
       </c>
-      <c r="H647" s="5" t="inlineStr">
+      <c r="H649" s="5" t="inlineStr">
         <is>
           <t>Free K-5 money curriculum, and the book it hangs on</t>
         </is>
       </c>
-      <c r="I647" s="5" t="n">
+      <c r="I649" s="5" t="n">
         <v>1556</v>
       </c>
-      <c r="J647" s="5" t="inlineStr">
+      <c r="J649" s="5" t="inlineStr">
         <is>
           <t>Mrs. Davenport — you have a new assistant principal this year and a fall to get through, so I'll make this easy to skim and easy to delete.
 What I have: a 36-page picture book for grades 1-5 that teaches a kid how to spend money well, and a complete free teacher kit behind it.
@@ -26182,52 +26284,52 @@
 https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K647" s="5" t="inlineStr"/>
-      <c r="L647" s="5" t="inlineStr">
+      <c r="K649" s="5" t="inlineStr"/>
+      <c r="L649" s="5" t="inlineStr">
         <is>
           <t>With the Conn letter.</t>
         </is>
       </c>
-      <c r="M647" s="5" t="inlineStr"/>
-      <c r="N647" s="5" t="inlineStr"/>
-    </row>
-    <row r="648">
-      <c r="A648" s="5" t="inlineStr"/>
-      <c r="B648" s="5" t="inlineStr">
+      <c r="M649" s="5" t="inlineStr"/>
+      <c r="N649" s="5" t="inlineStr"/>
+    </row>
+    <row r="650">
+      <c r="A650" s="5" t="inlineStr"/>
+      <c r="B650" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C648" s="5" t="inlineStr">
+      <c r="C650" s="5" t="inlineStr">
         <is>
           <t>Jennifer Magaw</t>
         </is>
       </c>
-      <c r="D648" s="5" t="inlineStr">
+      <c r="D650" s="5" t="inlineStr">
         <is>
           <t>Teach Children to Save Day coordinator (grades 3–4), UD CEEE</t>
         </is>
       </c>
-      <c r="E648" s="5" t="inlineStr"/>
-      <c r="F648" s="5" t="inlineStr">
+      <c r="E650" s="5" t="inlineStr"/>
+      <c r="F650" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G648" s="5" t="inlineStr">
+      <c r="G650" s="5" t="inlineStr">
         <is>
           <t>jmagaw@udel.edu</t>
         </is>
       </c>
-      <c r="H648" s="5" t="inlineStr">
+      <c r="H650" s="5" t="inlineStr">
         <is>
           <t>Teach Children to Save Day, and the half of it nobody programs</t>
         </is>
       </c>
-      <c r="I648" s="5" t="n">
+      <c r="I650" s="5" t="n">
         <v>1410</v>
       </c>
-      <c r="J648" s="5" t="inlineStr">
+      <c r="J650" s="5" t="inlineStr">
         <is>
           <t>Ms. Magaw — you run Teach Children to Save Day for grades 3 and 4, which is the exact band I wrote for, so this should take thirty seconds to evaluate either way.
 The day does what its name says. A volunteer walks into a fourth-grade classroom and talks about saving, and the kids nod, and it's a good hour. But saving is the second thing a child does with money. The first thing is spending, and almost nobody programs that hour.
@@ -26239,52 +26341,52 @@
 clarencegetsabargain.com</t>
         </is>
       </c>
-      <c r="K648" s="5" t="inlineStr"/>
-      <c r="L648" s="5" t="inlineStr">
+      <c r="K650" s="5" t="inlineStr"/>
+      <c r="L650" s="5" t="inlineStr">
         <is>
           <t>After Meszaros replies. Say that she has.</t>
         </is>
       </c>
-      <c r="M648" s="5" t="inlineStr"/>
-      <c r="N648" s="5" t="inlineStr"/>
-    </row>
-    <row r="649">
-      <c r="A649" s="5" t="inlineStr"/>
-      <c r="B649" s="5" t="inlineStr">
+      <c r="M650" s="5" t="inlineStr"/>
+      <c r="N650" s="5" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" s="5" t="inlineStr"/>
+      <c r="B651" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C649" s="5" t="inlineStr">
+      <c r="C651" s="5" t="inlineStr">
         <is>
           <t>Judy Austin</t>
         </is>
       </c>
-      <c r="D649" s="5" t="inlineStr">
+      <c r="D651" s="5" t="inlineStr">
         <is>
           <t>Ronni K. Cohen Bank At School coordinator, UD CEEE</t>
         </is>
       </c>
-      <c r="E649" s="5" t="inlineStr"/>
-      <c r="F649" s="5" t="inlineStr">
+      <c r="E651" s="5" t="inlineStr"/>
+      <c r="F651" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G649" s="5" t="inlineStr">
+      <c r="G651" s="5" t="inlineStr">
         <is>
           <t>judyaustin1@comcast.net</t>
         </is>
       </c>
-      <c r="H649" s="5" t="inlineStr">
+      <c r="H651" s="5" t="inlineStr">
         <is>
           <t>Bank At School teaches the deposit. Who teaches the checkout?</t>
         </is>
       </c>
-      <c r="I649" s="5" t="n">
+      <c r="I651" s="5" t="n">
         <v>1395</v>
       </c>
-      <c r="J649" s="5" t="inlineStr">
+      <c r="J651" s="5" t="inlineStr">
         <is>
           <t>Ms. Austin — Bank At School puts a working bank inside an elementary building, which is the most concrete money lesson a nine-year-old is ever going to get. Kids handle a deposit slip. It's real. I'm not writing to improve on that.
 I'm writing about the other counter.
@@ -26297,52 +26399,52 @@
 https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K649" s="5" t="inlineStr"/>
-      <c r="L649" s="5" t="inlineStr">
+      <c r="K651" s="5" t="inlineStr"/>
+      <c r="L651" s="5" t="inlineStr">
         <is>
           <t>With the Magaw letter.</t>
         </is>
       </c>
-      <c r="M649" s="5" t="inlineStr"/>
-      <c r="N649" s="5" t="inlineStr"/>
-    </row>
-    <row r="650">
-      <c r="A650" s="5" t="inlineStr"/>
-      <c r="B650" s="5" t="inlineStr">
+      <c r="M651" s="5" t="inlineStr"/>
+      <c r="N651" s="5" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" s="5" t="inlineStr"/>
+      <c r="B652" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C650" s="5" t="inlineStr">
+      <c r="C652" s="5" t="inlineStr">
         <is>
           <t>Gail Colbert</t>
         </is>
       </c>
-      <c r="D650" s="5" t="inlineStr">
+      <c r="D652" s="5" t="inlineStr">
         <is>
           <t>Personal Finance Coordinator, UD CEEE (Keys to Financial Success)</t>
         </is>
       </c>
-      <c r="E650" s="5" t="inlineStr"/>
-      <c r="F650" s="5" t="inlineStr">
+      <c r="E652" s="5" t="inlineStr"/>
+      <c r="F652" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G650" s="5" t="inlineStr">
+      <c r="G652" s="5" t="inlineStr">
         <is>
           <t>gcolbert@udel.edu</t>
         </is>
       </c>
-      <c r="H650" s="5" t="inlineStr">
+      <c r="H652" s="5" t="inlineStr">
         <is>
           <t>Keys 5.0 is the ninth-grade answer. This is the K-5 one.</t>
         </is>
       </c>
-      <c r="I650" s="5" t="n">
+      <c r="I652" s="5" t="n">
         <v>1563</v>
       </c>
-      <c r="J650" s="5" t="inlineStr">
+      <c r="J652" s="5" t="inlineStr">
         <is>
           <t>Ms. Colbert — you're rebuilding Keys to Financial Success for HB 203 with the Philadelphia Fed, so the last thing you need is another person with an opinion about high school personal finance. I don't have one. I have a K-5 problem to hand you.
 Delaware's standards for financial literacy have covered grades K-12 since 2018. HB 203 answered the high school half with a course, a framework, and your training. The elementary half still has the standard and no shopping list, and the districts filing K-3 instructional plans are mostly assembling them out of nothing.
@@ -26354,52 +26456,52 @@
 clarencegetsabargain.com</t>
         </is>
       </c>
-      <c r="K650" s="5" t="inlineStr"/>
-      <c r="L650" s="5" t="inlineStr">
+      <c r="K652" s="5" t="inlineStr"/>
+      <c r="L652" s="5" t="inlineStr">
         <is>
           <t>Anytime. She is deep in HB 203 rollout, so keep it out of her way.</t>
         </is>
       </c>
-      <c r="M650" s="5" t="inlineStr"/>
-      <c r="N650" s="5" t="inlineStr"/>
-    </row>
-    <row r="651">
-      <c r="A651" s="5" t="inlineStr"/>
-      <c r="B651" s="5" t="inlineStr">
+      <c r="M652" s="5" t="inlineStr"/>
+      <c r="N652" s="5" t="inlineStr"/>
+    </row>
+    <row r="653">
+      <c r="A653" s="5" t="inlineStr"/>
+      <c r="B653" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C651" s="5" t="inlineStr">
+      <c r="C653" s="5" t="inlineStr">
         <is>
           <t>Dr. Carlos Asarta</t>
         </is>
       </c>
-      <c r="D651" s="5" t="inlineStr">
+      <c r="D653" s="5" t="inlineStr">
         <is>
           <t>James B. O'Neill Director, UD CEEE</t>
         </is>
       </c>
-      <c r="E651" s="5" t="inlineStr"/>
-      <c r="F651" s="5" t="inlineStr">
+      <c r="E653" s="5" t="inlineStr"/>
+      <c r="F653" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G651" s="5" t="inlineStr">
+      <c r="G653" s="5" t="inlineStr">
         <is>
           <t>not published. Send via LinkedIn, or ask Dr. Meszaros to forward it.</t>
         </is>
       </c>
-      <c r="H651" s="5" t="inlineStr">
+      <c r="H653" s="5" t="inlineStr">
         <is>
           <t>The K-5 half of the alignment study</t>
         </is>
       </c>
-      <c r="I651" s="5" t="n">
+      <c r="I653" s="5" t="n">
         <v>1411</v>
       </c>
-      <c r="J651" s="5" t="inlineStr">
+      <c r="J653" s="5" t="inlineStr">
         <is>
           <t>Dr. Asarta — your center co-authored the state's curriculum alignment study for grades K-12, which makes you one of the few people in Delaware who has actually looked at what's being taught at each grade band rather than guessing. So this is a narrow question rather than a pitch.
 When the K-3 and upper-elementary plans came in, what were districts using?
@@ -26411,52 +26513,52 @@
 clarencegetsabargain.com</t>
         </is>
       </c>
-      <c r="K651" s="5" t="inlineStr"/>
-      <c r="L651" s="5" t="inlineStr">
+      <c r="K653" s="5" t="inlineStr"/>
+      <c r="L653" s="5" t="inlineStr">
         <is>
           <t>After Meszaros, and ideally through her.</t>
         </is>
       </c>
-      <c r="M651" s="5" t="inlineStr"/>
-      <c r="N651" s="5" t="inlineStr"/>
-    </row>
-    <row r="652">
-      <c r="A652" s="5" t="inlineStr"/>
-      <c r="B652" s="5" t="inlineStr">
+      <c r="M653" s="5" t="inlineStr"/>
+      <c r="N653" s="5" t="inlineStr"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="5" t="inlineStr"/>
+      <c r="B654" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C652" s="5" t="inlineStr">
+      <c r="C654" s="5" t="inlineStr">
         <is>
           <t>Delaware DOE — Financial Literacy</t>
         </is>
       </c>
-      <c r="D652" s="5" t="inlineStr">
+      <c r="D654" s="5" t="inlineStr">
         <is>
           <t>Email:</t>
         </is>
       </c>
-      <c r="E652" s="5" t="inlineStr"/>
-      <c r="F652" s="5" t="inlineStr">
+      <c r="E654" s="5" t="inlineStr"/>
+      <c r="F654" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G652" s="5" t="inlineStr">
+      <c r="G654" s="5" t="inlineStr">
         <is>
           <t>finlit.doe@doe.k12.de.us</t>
         </is>
       </c>
-      <c r="H652" s="5" t="inlineStr">
+      <c r="H654" s="5" t="inlineStr">
         <is>
           <t>Free K-5 material for districts filing Financial Literacy Instructional Plans</t>
         </is>
       </c>
-      <c r="I652" s="5" t="n">
+      <c r="I654" s="5" t="n">
         <v>1728</v>
       </c>
-      <c r="J652" s="5" t="inlineStr">
+      <c r="J654" s="5" t="inlineStr">
         <is>
           <t>To whoever reads this box —
 You collect the Financial Literacy Instructional Plans, including the K-3 grade cluster. Which means you have a better view than anyone of what districts are actually putting in those rows for the early grades, and my guess is that a lot of them are thin.
@@ -26477,52 +26579,52 @@
 ISBN 979-8-234-07638-0 · LCCN 2026906164</t>
         </is>
       </c>
-      <c r="K652" s="5" t="inlineStr"/>
-      <c r="L652" s="5" t="inlineStr">
+      <c r="K654" s="5" t="inlineStr"/>
+      <c r="L654" s="5" t="inlineStr">
         <is>
           <t>Anytime. It's a mailbox, not a person — write it accordingly.</t>
         </is>
       </c>
-      <c r="M652" s="5" t="inlineStr"/>
-      <c r="N652" s="5" t="inlineStr"/>
-    </row>
-    <row r="653">
-      <c r="A653" s="5" t="inlineStr"/>
-      <c r="B653" s="5" t="inlineStr">
+      <c r="M654" s="5" t="inlineStr"/>
+      <c r="N654" s="5" t="inlineStr"/>
+    </row>
+    <row r="655">
+      <c r="A655" s="5" t="inlineStr"/>
+      <c r="B655" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C653" s="5" t="inlineStr">
+      <c r="C655" s="5" t="inlineStr">
         <is>
           <t>Leslie Glenn</t>
         </is>
       </c>
-      <c r="D653" s="5" t="inlineStr">
+      <c r="D655" s="5" t="inlineStr">
         <is>
           <t>Youth Services Librarian, Rehoboth Beach Public Library</t>
         </is>
       </c>
-      <c r="E653" s="5" t="inlineStr"/>
-      <c r="F653" s="5" t="inlineStr">
+      <c r="E655" s="5" t="inlineStr"/>
+      <c r="F655" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G653" s="5" t="inlineStr">
+      <c r="G655" s="5" t="inlineStr">
         <is>
           <t>rehobothbeachlibrary@gmail.com</t>
         </is>
       </c>
-      <c r="H653" s="5" t="inlineStr">
+      <c r="H655" s="5" t="inlineStr">
         <is>
           <t>Local author, 20-minute read-aloud, summer slot</t>
         </is>
       </c>
-      <c r="I653" s="5" t="n">
+      <c r="I655" s="5" t="n">
         <v>1347</v>
       </c>
-      <c r="J653" s="5" t="inlineStr">
+      <c r="J655" s="5" t="inlineStr">
         <is>
           <t>Attn: Leslie Glenn, Youth Services
 Ms. Glenn — I'm on Rehoboth Avenue often enough that this feels less like a cold email than it probably reads. I wrote and illustrated a children's book and I'd like to read it in your building.
@@ -26535,52 +26637,52 @@
 https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K653" s="5" t="inlineStr"/>
-      <c r="L653" s="5" t="inlineStr">
+      <c r="K655" s="5" t="inlineStr"/>
+      <c r="L655" s="5" t="inlineStr">
         <is>
           <t>Late winter or early spring, when summer programming is still being built.</t>
         </is>
       </c>
-      <c r="M653" s="5" t="inlineStr"/>
-      <c r="N653" s="5" t="inlineStr"/>
-    </row>
-    <row r="654">
-      <c r="A654" s="5" t="inlineStr"/>
-      <c r="B654" s="5" t="inlineStr">
+      <c r="M655" s="5" t="inlineStr"/>
+      <c r="N655" s="5" t="inlineStr"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="5" t="inlineStr"/>
+      <c r="B656" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C654" s="5" t="inlineStr">
+      <c r="C656" s="5" t="inlineStr">
         <is>
           <t>Jennifer Noonan</t>
         </is>
       </c>
-      <c r="D654" s="5" t="inlineStr">
+      <c r="D656" s="5" t="inlineStr">
         <is>
           <t>Children's Librarian &amp; Program Coordinator, Lewes Public Library</t>
         </is>
       </c>
-      <c r="E654" s="5" t="inlineStr"/>
-      <c r="F654" s="5" t="inlineStr">
+      <c r="E656" s="5" t="inlineStr"/>
+      <c r="F656" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G654" s="5" t="inlineStr">
+      <c r="G656" s="5" t="inlineStr">
         <is>
           <t>none published — call 302-645-2733 or send to the library's general contact form,</t>
         </is>
       </c>
-      <c r="H654" s="5" t="inlineStr">
+      <c r="H656" s="5" t="inlineStr">
         <is>
           <t>A read-aloud that ends with kids running a cash register</t>
         </is>
       </c>
-      <c r="I654" s="5" t="n">
+      <c r="I656" s="5" t="n">
         <v>1229</v>
       </c>
-      <c r="J654" s="5" t="inlineStr">
+      <c r="J656" s="5" t="inlineStr">
         <is>
           <t>Ms. Noonan — you coordinate the children's programming at Lewes, so you already know the difference between a book event that fills a room and one where six kids show up because it was raining. I'll tell you which one I think this is and you can decide.
 I wrote and illustrated Clarence Gets a Bargain — 36 pages, ages 6-10. A boy earns a robot, does his "shopping homework" in the newspaper sale inserts, compares two models in a store, chooses the cheaper of the two on purpose, redeems a coupon at the checkout, and then meets sales tax and takes it as a personal betrayal. Twenty minutes read aloud.
@@ -26592,48 +26694,48 @@
 clarencegetsabargain.com</t>
         </is>
       </c>
-      <c r="K654" s="5" t="inlineStr"/>
-      <c r="L654" s="5" t="inlineStr">
+      <c r="K656" s="5" t="inlineStr"/>
+      <c r="L656" s="5" t="inlineStr">
         <is>
           <t>Same season as Rehoboth. Offer them different weeks.</t>
         </is>
       </c>
-      <c r="M654" s="5" t="inlineStr"/>
-      <c r="N654" s="5" t="inlineStr"/>
-    </row>
-    <row r="655">
-      <c r="A655" s="5" t="inlineStr"/>
-      <c r="B655" s="5" t="inlineStr">
+      <c r="M656" s="5" t="inlineStr"/>
+      <c r="N656" s="5" t="inlineStr"/>
+    </row>
+    <row r="657">
+      <c r="A657" s="5" t="inlineStr"/>
+      <c r="B657" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C655" s="5" t="inlineStr">
+      <c r="C657" s="5" t="inlineStr">
         <is>
           <t>Dr. Susan P. Brown</t>
         </is>
       </c>
-      <c r="D655" s="5" t="inlineStr">
+      <c r="D657" s="5" t="inlineStr">
         <is>
           <t>Executive Director, Delaware Association of School Administrators</t>
         </is>
       </c>
-      <c r="E655" s="5" t="inlineStr"/>
-      <c r="F655" s="5" t="inlineStr">
+      <c r="E657" s="5" t="inlineStr"/>
+      <c r="F657" s="5" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="G655" s="5" t="inlineStr">
+      <c r="G657" s="5" t="inlineStr">
         <is>
           <t>302-674-0630 (no email published — call)</t>
         </is>
       </c>
-      <c r="H655" s="5" t="inlineStr"/>
-      <c r="I655" s="5" t="n">
+      <c r="H657" s="5" t="inlineStr"/>
+      <c r="I657" s="5" t="n">
         <v>870</v>
       </c>
-      <c r="J655" s="5" t="inlineStr">
+      <c r="J657" s="5" t="inlineStr">
         <is>
           <t>Hi — my name is Jonathan Bach. I'm a children's book author in Baltimore, and I spend a
 good part of the year in Rehoboth. I'm calling because DASA has a Delaware School
@@ -26648,57 +26750,57 @@
 should send it to.</t>
         </is>
       </c>
-      <c r="K655" s="5" t="inlineStr"/>
-      <c r="L655" s="5" t="inlineStr"/>
-      <c r="M655" s="5" t="inlineStr"/>
-      <c r="N655" s="5" t="inlineStr"/>
-    </row>
-    <row r="656">
-      <c r="A656" s="4" t="inlineStr">
+      <c r="K657" s="5" t="inlineStr"/>
+      <c r="L657" s="5" t="inlineStr"/>
+      <c r="M657" s="5" t="inlineStr"/>
+      <c r="N657" s="5" t="inlineStr"/>
+    </row>
+    <row r="658">
+      <c r="A658" s="4" t="inlineStr">
         <is>
           <t>🐋</t>
         </is>
       </c>
-      <c r="B656" s="5" t="inlineStr">
+      <c r="B658" s="5" t="inlineStr">
         <is>
           <t>Standalone</t>
         </is>
       </c>
-      <c r="C656" s="5" t="inlineStr">
+      <c r="C658" s="5" t="inlineStr">
         <is>
           <t>Mia Baytop Russell</t>
         </is>
       </c>
-      <c r="D656" s="5" t="inlineStr">
+      <c r="D658" s="5" t="inlineStr">
         <is>
           <t>Senior Lecturer, Johns Hopkins; Dir., Clark Scholars. Ex-Money Smart (UMD Ext.), ex-VP Wells Fargo Foundation</t>
         </is>
       </c>
-      <c r="E656" s="5" t="inlineStr">
+      <c r="E658" s="5" t="inlineStr">
         <is>
           <t>Practitioner, funder and academic in one person. Reference-letter candidate for Jump$tart.</t>
         </is>
       </c>
-      <c r="F656" s="5" t="inlineStr">
+      <c r="F658" s="5" t="inlineStr">
         <is>
           <t>Connection note, then InMail</t>
         </is>
       </c>
-      <c r="G656" s="5" t="inlineStr"/>
-      <c r="H656" s="5" t="inlineStr">
+      <c r="G658" s="5" t="inlineStr"/>
+      <c r="H658" s="5" t="inlineStr">
         <is>
           <t>Money Smart, Wells Fargo, Hopkins — and a premise you can puncture</t>
         </is>
       </c>
-      <c r="I656" s="5" t="n">
+      <c r="I658" s="5" t="n">
         <v>280</v>
       </c>
-      <c r="J656" s="5" t="inlineStr">
+      <c r="J658" s="5" t="inlineStr">
         <is>
           <t>Mia — you ran Money Smart at Maryland Extension, decided what got funded at Wells Fargo, and now teach it at Hopkins. Three chairs, almost nobody has sat in all of them. I wrote a K-5 book aligned to Money Smart that leaves saving out entirely. I'm in Baltimore too. Worth a look?</t>
         </is>
       </c>
-      <c r="K656" s="5" t="inlineStr">
+      <c r="K658" s="5" t="inlineStr">
         <is>
           <t>Mia — you've sat in all three chairs, which almost nobody in this field has. You ran the Money Smart team at Maryland Extension. You decided what got funded as VP for youth financial health philanthropy at Wells Fargo. Now you teach it at Hopkins. Practitioner, funder, academic, in that order.
 Which makes you exactly the person I want to tell me I'm wrong.
@@ -26718,51 +26820,51 @@
 clarencegetsabargain.com</t>
         </is>
       </c>
-      <c r="L656" s="5" t="inlineStr">
+      <c r="L658" s="5" t="inlineStr">
         <is>
           <t>Col M = 280-char connection note. Col N = 1,323-char InMail. | Subject: A reference letter, and the three reasons I'm asking you specifically · Long-form version from Jump$tart</t>
         </is>
       </c>
-      <c r="M656" s="5" t="inlineStr"/>
-      <c r="N656" s="5" t="inlineStr"/>
-    </row>
-    <row r="657">
-      <c r="A657" s="4" t="inlineStr">
+      <c r="M658" s="5" t="inlineStr"/>
+      <c r="N658" s="5" t="inlineStr"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="4" t="inlineStr">
         <is>
           <t>🐋</t>
         </is>
       </c>
-      <c r="B657" s="5" t="inlineStr">
+      <c r="B659" s="5" t="inlineStr">
         <is>
           <t>Standalone</t>
         </is>
       </c>
-      <c r="C657" s="5" t="inlineStr">
+      <c r="C659" s="5" t="inlineStr">
         <is>
           <t>Dr. Rachel Edoho-Eket</t>
         </is>
       </c>
-      <c r="D657" s="5" t="inlineStr">
+      <c r="D659" s="5" t="inlineStr">
         <is>
           <t>Principal, Waterloo Elementary (Blue Ribbon); Past President, MAESP; 2x author</t>
         </is>
       </c>
-      <c r="E657" s="5" t="inlineStr">
+      <c r="E659" s="5" t="inlineStr">
         <is>
           <t>Maryland elementary gatekeeper, local, and an author who judges production.</t>
         </is>
       </c>
-      <c r="F657" s="5" t="inlineStr">
+      <c r="F659" s="5" t="inlineStr">
         <is>
           <t>LinkedIn DM (1st-degree)</t>
         </is>
       </c>
-      <c r="G657" s="5" t="inlineStr"/>
-      <c r="H657" s="5" t="inlineStr"/>
-      <c r="I657" s="5" t="n">
+      <c r="G659" s="5" t="inlineStr"/>
+      <c r="H659" s="5" t="inlineStr"/>
+      <c r="I659" s="5" t="n">
         <v>2002</v>
       </c>
-      <c r="J657" s="5" t="inlineStr">
+      <c r="J659" s="5" t="inlineStr">
         <is>
           <t>Dr. Edoho-Eket — congratulations on the ISTE+ASCD 20 to Watch. What stuck with me wasn't the award, it was what you wrote about it: that it started 21 years ago teaching five-year-olds in Howard County, and that those lessons still guide how you lead.
 Those five-year-olds are my entire readership.
@@ -26777,56 +26879,56 @@
 Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K657" s="5" t="inlineStr"/>
-      <c r="L657" s="5" t="inlineStr">
+      <c r="K659" s="5" t="inlineStr"/>
+      <c r="L659" s="5" t="inlineStr">
         <is>
           <t>Already a connection — single DM, no request note.</t>
         </is>
       </c>
-      <c r="M657" s="5" t="inlineStr"/>
-      <c r="N657" s="5" t="inlineStr"/>
-    </row>
-    <row r="658">
-      <c r="A658" s="5" t="inlineStr"/>
-      <c r="B658" s="5" t="inlineStr">
+      <c r="M659" s="5" t="inlineStr"/>
+      <c r="N659" s="5" t="inlineStr"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="5" t="inlineStr"/>
+      <c r="B660" s="5" t="inlineStr">
         <is>
           <t>Jump$tart</t>
         </is>
       </c>
-      <c r="C658" s="5" t="inlineStr">
+      <c r="C660" s="5" t="inlineStr">
         <is>
           <t>Suzann Knight</t>
         </is>
       </c>
-      <c r="D658" s="5" t="inlineStr">
+      <c r="D660" s="5" t="inlineStr">
         <is>
           <t>send this one first</t>
         </is>
       </c>
-      <c r="E658" s="5" t="inlineStr">
+      <c r="E660" s="5" t="inlineStr">
         <is>
           <t>send this one first</t>
         </is>
       </c>
-      <c r="F658" s="5" t="inlineStr">
+      <c r="F660" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G658" s="5" t="inlineStr">
+      <c r="G660" s="5" t="inlineStr">
         <is>
           <t>suzann.knight@jumpstart.org</t>
         </is>
       </c>
-      <c r="H658" s="5" t="inlineStr">
+      <c r="H660" s="5" t="inlineStr">
         <is>
           <t>Clearinghouse eligibility question — free K-5 toolkit, and a reference letter</t>
         </is>
       </c>
-      <c r="I658" s="5" t="n">
+      <c r="I660" s="5" t="n">
         <v>1906</v>
       </c>
-      <c r="J658" s="5" t="inlineStr">
+      <c r="J660" s="5" t="inlineStr">
         <is>
           <t>Ms. Knight — the Clearinghouse page says you're the person to ask, so I'll ask one thing and keep it short.
 I'd like to list a free K-5 classroom resource. Reading the Provider criteria, I don't meet the first three routes — I'm not a National Partner, I've never listed before, and Jump$tart has no reason to know me. That leaves the letter of reference, and the criteria say you'll provide instructions if one is required.
@@ -26839,48 +26941,48 @@
 Baltimore</t>
         </is>
       </c>
-      <c r="K658" s="5" t="inlineStr"/>
-      <c r="L658" s="5" t="inlineStr"/>
-      <c r="M658" s="5" t="inlineStr"/>
-      <c r="N658" s="5" t="inlineStr"/>
-    </row>
-    <row r="659">
-      <c r="A659" s="5" t="inlineStr"/>
-      <c r="B659" s="5" t="inlineStr">
+      <c r="K660" s="5" t="inlineStr"/>
+      <c r="L660" s="5" t="inlineStr"/>
+      <c r="M660" s="5" t="inlineStr"/>
+      <c r="N660" s="5" t="inlineStr"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="5" t="inlineStr"/>
+      <c r="B661" s="5" t="inlineStr">
         <is>
           <t>Jump$tart</t>
         </is>
       </c>
-      <c r="C659" s="5" t="inlineStr">
+      <c r="C661" s="5" t="inlineStr">
         <is>
           <t>Wally Luckeydoo</t>
         </is>
       </c>
-      <c r="D659" s="5" t="inlineStr">
+      <c r="D661" s="5" t="inlineStr">
         <is>
           <t>asking for the letter</t>
         </is>
       </c>
-      <c r="E659" s="5" t="inlineStr">
+      <c r="E661" s="5" t="inlineStr">
         <is>
           <t>asking for the letter</t>
         </is>
       </c>
-      <c r="F659" s="5" t="inlineStr">
+      <c r="F661" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G659" s="5" t="inlineStr"/>
-      <c r="H659" s="5" t="inlineStr">
+      <c r="G661" s="5" t="inlineStr"/>
+      <c r="H661" s="5" t="inlineStr">
         <is>
           <t>A favor with your name already on it</t>
         </is>
       </c>
-      <c r="I659" s="5" t="n">
+      <c r="I661" s="5" t="n">
         <v>909</v>
       </c>
-      <c r="J659" s="5" t="inlineStr">
+      <c r="J661" s="5" t="inlineStr">
         <is>
           <t>Wally — a favor, and you can say no without it costing us anything.
 I'm applying to list the Clarence toolkit in the Jump$tart Clearinghouse. To get in the door as a Provider, I need a letter of reference attesting to reputation and viability, because I'm not a National Partner and Jump$tart has no reason to know who I am.
@@ -26890,36 +26992,36 @@
 Jonathan</t>
         </is>
       </c>
-      <c r="K659" s="5" t="inlineStr"/>
-      <c r="L659" s="5" t="inlineStr"/>
-      <c r="M659" s="5" t="inlineStr"/>
-      <c r="N659" s="5" t="inlineStr"/>
-    </row>
-    <row r="660">
-      <c r="A660" s="5" t="inlineStr"/>
-      <c r="B660" s="5" t="inlineStr">
+      <c r="K661" s="5" t="inlineStr"/>
+      <c r="L661" s="5" t="inlineStr"/>
+      <c r="M661" s="5" t="inlineStr"/>
+      <c r="N661" s="5" t="inlineStr"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="5" t="inlineStr"/>
+      <c r="B662" s="5" t="inlineStr">
         <is>
           <t>Jump$tart</t>
         </is>
       </c>
-      <c r="C660" s="5" t="inlineStr">
+      <c r="C662" s="5" t="inlineStr">
         <is>
           <t>Reference letter — draft for Wally to sign</t>
         </is>
       </c>
-      <c r="D660" s="5" t="inlineStr"/>
-      <c r="E660" s="5" t="inlineStr"/>
-      <c r="F660" s="5" t="inlineStr">
+      <c r="D662" s="5" t="inlineStr"/>
+      <c r="E662" s="5" t="inlineStr"/>
+      <c r="F662" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G660" s="5" t="inlineStr"/>
-      <c r="H660" s="5" t="inlineStr"/>
-      <c r="I660" s="5" t="n">
+      <c r="G662" s="5" t="inlineStr"/>
+      <c r="H662" s="5" t="inlineStr"/>
+      <c r="I662" s="5" t="n">
         <v>1084</v>
       </c>
-      <c r="J660" s="5" t="inlineStr">
+      <c r="J662" s="5" t="inlineStr">
         <is>
           <t>To the Jump$tart Clearinghouse review team:
 I'm writing in support of Jonathan Bach and the classroom resources accompanying his children's book, Clarence Gets a Bargain.
@@ -26929,13 +27031,13 @@
 Wally Luckeydoo, Ed.D.</t>
         </is>
       </c>
-      <c r="K660" s="5" t="inlineStr"/>
-      <c r="L660" s="5" t="inlineStr"/>
-      <c r="M660" s="5" t="inlineStr"/>
-      <c r="N660" s="5" t="inlineStr"/>
+      <c r="K662" s="5" t="inlineStr"/>
+      <c r="L662" s="5" t="inlineStr"/>
+      <c r="M662" s="5" t="inlineStr"/>
+      <c r="N662" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N660"/>
+  <autoFilter ref="A1:N662"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -26946,7 +27048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N74"/>
+  <dimension ref="A1:N76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -30208,46 +30310,148 @@
       <c r="N69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="6" t="inlineStr">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>New Jul 28-29</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Briana Walker</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>MAESP Zone 4 (Eastern Shore) Rep · 2026 NAESP National Outstanding Assistant Principal · Greensboro Elementary, Caroline County</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The single best fit on the screen, because she sits at the intersection of three things already in the repo. She is the **MAESP Zone 4 rep for the Eastern Shore** — the same association you have nine letters written for — which makes her a distribution node, not just a reader. She is a **2026 NAESP </t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Gatekeeper · connected Jul 28 · 1st-degree</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr"/>
+      <c r="H70" s="5" t="inlineStr"/>
+      <c r="I70" s="5" t="n">
+        <v>1409</v>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>Briana — congratulations on the National Outstanding Assistant Principal award. First elementary winner from Caroline County, which I did not know until I went looking, and now I can't unsee how overdue it was.
+I'm writing because you're the Eastern Shore rep for MAESP and I'm down your way often — I spend a good part of the year in Rehoboth, so Greensboro is nearly the neighborhood.
+I wrote and illustrated a K-5 book about money that does the one thing the rest of the shelf skips. Every other kids' money book teaches saving. Mine teaches a purchase — a boy earns a robot, reads the sale ads, compares two models, takes the marked-down one on purpose, hands a coupon to the cashier, and runs face-first into sales tax. Sixteen-plus concepts, none of them announced as a lesson.
+Here is why I'm writing you and not a longer list. MAESP recognized you as a Connected School Leader for actually using the digital tools, and the entire teacher kit behind the book is free, ungated, and prints from a browser — four lesson plans, assessments with answer keys, a standards crosswalk. No account, no budget line. It is exactly the kind of thing that dies in a staff room unless a principal who gets it hands it over.
+Would it be useful on the Eastern Shore, or am I overreaching? Toolkit: clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr"/>
+      <c r="L70" s="5" t="inlineStr"/>
+      <c r="M70" s="5" t="inlineStr"/>
+      <c r="N70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>New Jul 28-29</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Lauren Nowacki</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Money Deputy Editor, WSJ Buy Side · Certified Financial Health Counselor</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Press whale. Buy Side is the Wall Street Journal's personal-finance</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Press / Editor · connected Jul 29 · 1st-degree</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr"/>
+      <c r="I71" s="5" t="n">
+        <v>1288</v>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>Lauren — a story rather than a pitch, and you can kill it in one line.
+I read all 25 titles on the ABA Foundation's children's financial literacy list to be sure of this: every single one teaches earning, saving, or investing. Not one teaches spending — the only money thing a seven-year-old has actually done.
+That is the gap I wrote into. Clarence Gets a Bargain is a 36-page picture book for grades 1-5 where a boy earns a robot and runs one complete purchase: reads the sale ads at the kitchen table, compares two models, takes the marked-down one on purpose, hands a coupon to the cashier, and gets ambushed by sales tax. His mom photographs every receipt the second she sits down in the car. Nobody in the book ever says the word "budget."
+Why you, and why now. Buy Side runs the gift guides and the teach-your-kid-about-money service pieces. You are a Certified Financial Health Counselor, so you will spot in a page whether the substance holds. And this is the season for it. The real angle is bigger than one book: why the entire children's money category skipped the cash register for forty years — told through the one that didn't.
+Happy to send you the whole thing. Four-minute flip if you would rather glance first: https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr"/>
+      <c r="L71" s="5" t="inlineStr"/>
+      <c r="M71" s="5" t="inlineStr"/>
+      <c r="N71" s="5" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>🔵</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>Dr. Bonnie Meszaros</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>Elementary School Program Coordinator, UD Center for Economic Education &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr"/>
-      <c r="F70" s="5" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr"/>
+      <c r="F72" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G70" s="5" t="inlineStr">
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>meszaros@udel.edu</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="H72" s="5" t="inlineStr">
         <is>
           <t>You built lessons around picture books. I built a picture book around lessons.</t>
         </is>
       </c>
-      <c r="I70" s="5" t="n">
+      <c r="I72" s="5" t="n">
         <v>2598</v>
       </c>
-      <c r="J70" s="5" t="inlineStr">
+      <c r="J72" s="5" t="inlineStr">
         <is>
           <t>Dr. Meszaros — you wrote a K and first-grade curriculum where the lesson lives inside the book. Monster Musical Chairs carries scarcity. The Little Red Hen Makes Pizza carries producers and consumers. Bunny Money carries a savings goal. Colonial adopted the kindergarten set outright.
 I came at the same problem from the other end. I wrote the picture book and put the economics inside it, then checked it against the standards after — including the National Standards for Financial Literacy, which I understand you co-authored. That is an odd thing to write to someone. I'd rather say it than pretend I found the framework on my own.
@@ -30261,56 +30465,56 @@
 Baltimore, and Rehoboth Beach when I can manage it</t>
         </is>
       </c>
-      <c r="K70" s="5" t="inlineStr"/>
-      <c r="L70" s="5" t="inlineStr">
+      <c r="K72" s="5" t="inlineStr"/>
+      <c r="L72" s="5" t="inlineStr">
         <is>
           <t>First. Everything else in Delaware is easier after her.</t>
         </is>
       </c>
-      <c r="M70" s="5" t="inlineStr"/>
-      <c r="N70" s="5" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="M72" s="5" t="inlineStr"/>
+      <c r="N72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>🐋</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>Dr. Jennifer Nauman</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>Superintendent, Cape Henlopen School District</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr"/>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="E73" s="5" t="inlineStr"/>
+      <c r="F73" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="G73" s="5" t="inlineStr">
         <is>
           <t>jennifer.nauman@cape.k12.de.us</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="H73" s="5" t="inlineStr">
         <is>
           <t>Five elementary schools, a 2018 standard, and nothing to teach it with</t>
         </is>
       </c>
-      <c r="I71" s="5" t="n">
+      <c r="I73" s="5" t="n">
         <v>2008</v>
       </c>
-      <c r="J71" s="5" t="inlineStr">
+      <c r="J73" s="5" t="inlineStr">
         <is>
           <t>Dr. Nauman — you were an assistant principal at Rehoboth Elementary, then ran Shields for eight years and took it to a National Blue Ribbon. You are running a district now, but you learned the job in an elementary building, which is why this is going to you and not to a curriculum office.
 Delaware adopted financial literacy standards for grades K-12 in 2018. HB 203 arrived last October and put a half-credit personal finance course in front of ninth graders. Good law. It also means K-5 has carried a standard for eight years with essentially nothing built for it, and your five elementary principals are the ones holding that bag.
@@ -30324,56 +30528,56 @@
 clarencegetsabargain.com</t>
         </is>
       </c>
-      <c r="K71" s="5" t="inlineStr"/>
-      <c r="L71" s="5" t="inlineStr">
+      <c r="K73" s="5" t="inlineStr"/>
+      <c r="L73" s="5" t="inlineStr">
         <is>
           <t>Second. One yes covers five buildings.</t>
         </is>
       </c>
-      <c r="M71" s="5" t="inlineStr"/>
-      <c r="N71" s="5" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="M73" s="5" t="inlineStr"/>
+      <c r="N73" s="5" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>🐋</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>Equetta Jones</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>Principal, Love Creek Elementary, Lewes</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr"/>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr"/>
+      <c r="F74" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="G74" s="5" t="inlineStr">
         <is>
           <t>equetta.jones@cape.k12.de.us</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="H74" s="5" t="inlineStr">
         <is>
           <t>A question you're better placed to answer than almost anyone</t>
         </is>
       </c>
-      <c r="I72" s="5" t="n">
+      <c r="I74" s="5" t="n">
         <v>1813</v>
       </c>
-      <c r="J72" s="5" t="inlineStr">
+      <c r="J74" s="5" t="inlineStr">
         <is>
           <t>Ms. Jones — you run Love Creek and you moderate NAESP's Early Career Principal Community of Practice, which means you spend part of your month listening to brand-new principals describe what they're short of. So I'll ask you the question I actually want answered instead of pitching first.
 When financial literacy shows up in an elementary building, what does a first-year principal do with it?
@@ -30386,61 +30590,61 @@
 https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K72" s="5" t="inlineStr"/>
-      <c r="L72" s="5" t="inlineStr">
+      <c r="K74" s="5" t="inlineStr"/>
+      <c r="L74" s="5" t="inlineStr">
         <is>
           <t>Third. Her NAESP seat turns a Lewes yes into a national one.</t>
         </is>
       </c>
-      <c r="M72" s="5" t="inlineStr"/>
-      <c r="N72" s="5" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="M74" s="5" t="inlineStr"/>
+      <c r="N74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>🐋</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>Standalone</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>Mia Baytop Russell</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>Senior Lecturer, Johns Hopkins; Dir., Clark Scholars. Ex-Money Smart (UMD Ext.), ex-VP Wells Fargo Foundation</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>Practitioner, funder and academic in one person. Reference-letter candidate for Jump$tart.</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr">
         <is>
           <t>Connection note, then InMail</t>
         </is>
       </c>
-      <c r="G73" s="5" t="inlineStr"/>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="G75" s="5" t="inlineStr"/>
+      <c r="H75" s="5" t="inlineStr">
         <is>
           <t>Money Smart, Wells Fargo, Hopkins — and a premise you can puncture</t>
         </is>
       </c>
-      <c r="I73" s="5" t="n">
+      <c r="I75" s="5" t="n">
         <v>280</v>
       </c>
-      <c r="J73" s="5" t="inlineStr">
+      <c r="J75" s="5" t="inlineStr">
         <is>
           <t>Mia — you ran Money Smart at Maryland Extension, decided what got funded at Wells Fargo, and now teach it at Hopkins. Three chairs, almost nobody has sat in all of them. I wrote a K-5 book aligned to Money Smart that leaves saving out entirely. I'm in Baltimore too. Worth a look?</t>
         </is>
       </c>
-      <c r="K73" s="5" t="inlineStr">
+      <c r="K75" s="5" t="inlineStr">
         <is>
           <t>Mia — you've sat in all three chairs, which almost nobody in this field has. You ran the Money Smart team at Maryland Extension. You decided what got funded as VP for youth financial health philanthropy at Wells Fargo. Now you teach it at Hopkins. Practitioner, funder, academic, in that order.
 Which makes you exactly the person I want to tell me I'm wrong.
@@ -30460,51 +30664,51 @@
 clarencegetsabargain.com</t>
         </is>
       </c>
-      <c r="L73" s="5" t="inlineStr">
+      <c r="L75" s="5" t="inlineStr">
         <is>
           <t>Col M = 280-char connection note. Col N = 1,323-char InMail. | Subject: A reference letter, and the three reasons I'm asking you specifically · Long-form version from Jump$tart</t>
         </is>
       </c>
-      <c r="M73" s="5" t="inlineStr"/>
-      <c r="N73" s="5" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="M75" s="5" t="inlineStr"/>
+      <c r="N75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>🐋</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>Standalone</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>Dr. Rachel Edoho-Eket</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>Principal, Waterloo Elementary (Blue Ribbon); Past President, MAESP; 2x author</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>Maryland elementary gatekeeper, local, and an author who judges production.</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t>LinkedIn DM (1st-degree)</t>
         </is>
       </c>
-      <c r="G74" s="5" t="inlineStr"/>
-      <c r="H74" s="5" t="inlineStr"/>
-      <c r="I74" s="5" t="n">
+      <c r="G76" s="5" t="inlineStr"/>
+      <c r="H76" s="5" t="inlineStr"/>
+      <c r="I76" s="5" t="n">
         <v>2002</v>
       </c>
-      <c r="J74" s="5" t="inlineStr">
+      <c r="J76" s="5" t="inlineStr">
         <is>
           <t>Dr. Edoho-Eket — congratulations on the ISTE+ASCD 20 to Watch. What stuck with me wasn't the award, it was what you wrote about it: that it started 21 years ago teaching five-year-olds in Howard County, and that those lessons still guide how you lead.
 Those five-year-olds are my entire readership.
@@ -30519,17 +30723,17 @@
 Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K74" s="5" t="inlineStr"/>
-      <c r="L74" s="5" t="inlineStr">
+      <c r="K76" s="5" t="inlineStr"/>
+      <c r="L76" s="5" t="inlineStr">
         <is>
           <t>Already a connection — single DM, no request note.</t>
         </is>
       </c>
-      <c r="M74" s="5" t="inlineStr"/>
-      <c r="N74" s="5" t="inlineStr"/>
+      <c r="M76" s="5" t="inlineStr"/>
+      <c r="N76" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N74"/>
+  <autoFilter ref="A1:N76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -15,8 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="86ed" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master'!$A$1:$N$662</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Whales'!$A$1:$N$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master'!$A$1:$N$663</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Whales'!$A$1:$N$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deadlines'!$A$1:$H$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Physical copies'!$A$1:$D$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'86ed'!$A$1:$C$12</definedName>
@@ -612,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N662"/>
+  <dimension ref="A1:N663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1204,8 +1204,23 @@
           <t>Leslie — a Bookshelf question, not a pitch. The Money as You Grow selections skew toward saving and earning. Mine teaches the transaction itself, right through the register. Is the shelf still open, and who does the evaluating? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr"/>
-      <c r="L12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Leslie — I sent a short note a while back about the Money as You Grow Bookshelf. This is the idea behind the book, and it's the one I actually wanted to run past someone at CFPB.
+A child becomes a consumer the first time they hand over money. Not at eighteen, not at a first paycheck — at six, at a register, with a birthday five in their fist. That is the whole premise of my book: a boy runs one complete purchase, sale ad to receipt, and picks up comparison shopping, markdowns, coupons, and sales tax on the way. Money as You Grow teaches saving and spending well. The transaction itself — the part where a kid is actually standing at the counter — is the gap the book fills, and the current shelf leans heavily toward saving.
+Here is the piece I keep circling. The moment a kid makes that first purchase, they have entered a relationship that comes with rights, and nobody teaches a seven-year-old they have any. An adult knows to keep the receipt and that a broken thing can go back. A child thinks the deal ends when the bag is handed over.
+I know the full rights picture crosses agencies — warranties and returns are FTC, product safety is CPSC. I'm not asking CFPB to cover those. I'm asking whether there's appetite within Money as You Grow for material that treats the child as a consumer with standing on the financial side, the day they first spend, rather than only as a saver in training.
+Realistic version of the ask: is the Bookshelf still evaluating titles, and who owns it now? And if the framing above is interesting, I'd trade ten minutes for your read on it.
+Toolkit: https://clarencegetsabargain.com/educator-toolkit.html
+The book in four minutes: https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from CFPB/rights</t>
+        </is>
+      </c>
       <c r="M12" s="5" t="inlineStr"/>
       <c r="N12" s="5" t="inlineStr"/>
     </row>
@@ -26889,46 +26904,95 @@
       <c r="N659" s="5" t="inlineStr"/>
     </row>
     <row r="660">
-      <c r="A660" s="5" t="inlineStr"/>
+      <c r="A660" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
       <c r="B660" s="5" t="inlineStr">
         <is>
+          <t>CFPB/rights</t>
+        </is>
+      </c>
+      <c r="C660" s="5" t="inlineStr">
+        <is>
+          <t>Lauren Saunders</t>
+        </is>
+      </c>
+      <c r="D660" s="5" t="inlineStr"/>
+      <c r="E660" s="5" t="inlineStr">
+        <is>
+          <t>Kids-as-consumers-with-rights thesis. the rights thesis is consumer law, not financial education, and NCLC
+is the country's consumer-law authority. This is the better home for the big idea than any
+agency, and she's a fresh connection who has never heard the</t>
+        </is>
+      </c>
+      <c r="F660" s="5" t="inlineStr">
+        <is>
+          <t>Associate Director, National Consumer Law Center</t>
+        </is>
+      </c>
+      <c r="G660" s="5" t="inlineStr"/>
+      <c r="H660" s="5" t="inlineStr"/>
+      <c r="I660" s="5" t="n">
+        <v>1544</v>
+      </c>
+      <c r="J660" s="5" t="inlineStr">
+        <is>
+          <t>Lauren — we just connected, and I have a question that belongs at NCLC more than anywhere else I can think of.
+Consumer law assumes a consumer who can read a contract, keep a receipt, and assert a claim. But everyone becomes a consumer years before any of that — the first time a kid spends money at a register. There is a whole population of consumers, roughly six to ten years old, who have no idea they have standing, and almost nothing is written to tell them.
+I wrote a children's book about the spending half of money. A boy runs one full purchase — comparison, coupon, sales tax — and learns how a transaction actually works. What I keep circling back to is the part I did not put in it: the same kid, the moment he buys the robot, has rights he will never be told about. That a broken thing can go back. That a warranty is a promise with teeth. That "the food was bad and I get to say so" is a real position, not a tantrum. Financial literacy teaches kids to save. Nobody teaches them they are a party to a deal that has two sides.
+That reads to me as a consumer-rights gap, not a financial-education one, which is exactly why I'm asking you. Has NCLC ever taken up children as consumers — or pointed anyone toward who has? Even a "that's an FTC education question, talk to so-and-so" would move me forward.
+Not a book pitch. A where-does-this-belong question from someone who wrote half of it by accident and wants to know where the other half lives. The book is here if it's ever useful: https://clarencegetsabargain.com
+Jonathan</t>
+        </is>
+      </c>
+      <c r="K660" s="5" t="inlineStr"/>
+      <c r="L660" s="5" t="inlineStr"/>
+      <c r="M660" s="5" t="inlineStr"/>
+      <c r="N660" s="5" t="inlineStr"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="5" t="inlineStr"/>
+      <c r="B661" s="5" t="inlineStr">
+        <is>
           <t>Jump$tart</t>
         </is>
       </c>
-      <c r="C660" s="5" t="inlineStr">
+      <c r="C661" s="5" t="inlineStr">
         <is>
           <t>Suzann Knight</t>
         </is>
       </c>
-      <c r="D660" s="5" t="inlineStr">
+      <c r="D661" s="5" t="inlineStr">
         <is>
           <t>send this one first</t>
         </is>
       </c>
-      <c r="E660" s="5" t="inlineStr">
+      <c r="E661" s="5" t="inlineStr">
         <is>
           <t>send this one first</t>
         </is>
       </c>
-      <c r="F660" s="5" t="inlineStr">
+      <c r="F661" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G660" s="5" t="inlineStr">
+      <c r="G661" s="5" t="inlineStr">
         <is>
           <t>suzann.knight@jumpstart.org</t>
         </is>
       </c>
-      <c r="H660" s="5" t="inlineStr">
+      <c r="H661" s="5" t="inlineStr">
         <is>
           <t>Clearinghouse eligibility question — free K-5 toolkit, and a reference letter</t>
         </is>
       </c>
-      <c r="I660" s="5" t="n">
+      <c r="I661" s="5" t="n">
         <v>1906</v>
       </c>
-      <c r="J660" s="5" t="inlineStr">
+      <c r="J661" s="5" t="inlineStr">
         <is>
           <t>Ms. Knight — the Clearinghouse page says you're the person to ask, so I'll ask one thing and keep it short.
 I'd like to list a free K-5 classroom resource. Reading the Provider criteria, I don't meet the first three routes — I'm not a National Partner, I've never listed before, and Jump$tart has no reason to know me. That leaves the letter of reference, and the criteria say you'll provide instructions if one is required.
@@ -26941,48 +27005,48 @@
 Baltimore</t>
         </is>
       </c>
-      <c r="K660" s="5" t="inlineStr"/>
-      <c r="L660" s="5" t="inlineStr"/>
-      <c r="M660" s="5" t="inlineStr"/>
-      <c r="N660" s="5" t="inlineStr"/>
-    </row>
-    <row r="661">
-      <c r="A661" s="5" t="inlineStr"/>
-      <c r="B661" s="5" t="inlineStr">
+      <c r="K661" s="5" t="inlineStr"/>
+      <c r="L661" s="5" t="inlineStr"/>
+      <c r="M661" s="5" t="inlineStr"/>
+      <c r="N661" s="5" t="inlineStr"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="5" t="inlineStr"/>
+      <c r="B662" s="5" t="inlineStr">
         <is>
           <t>Jump$tart</t>
         </is>
       </c>
-      <c r="C661" s="5" t="inlineStr">
+      <c r="C662" s="5" t="inlineStr">
         <is>
           <t>Wally Luckeydoo</t>
         </is>
       </c>
-      <c r="D661" s="5" t="inlineStr">
+      <c r="D662" s="5" t="inlineStr">
         <is>
           <t>asking for the letter</t>
         </is>
       </c>
-      <c r="E661" s="5" t="inlineStr">
+      <c r="E662" s="5" t="inlineStr">
         <is>
           <t>asking for the letter</t>
         </is>
       </c>
-      <c r="F661" s="5" t="inlineStr">
+      <c r="F662" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G661" s="5" t="inlineStr"/>
-      <c r="H661" s="5" t="inlineStr">
+      <c r="G662" s="5" t="inlineStr"/>
+      <c r="H662" s="5" t="inlineStr">
         <is>
           <t>A favor with your name already on it</t>
         </is>
       </c>
-      <c r="I661" s="5" t="n">
+      <c r="I662" s="5" t="n">
         <v>909</v>
       </c>
-      <c r="J661" s="5" t="inlineStr">
+      <c r="J662" s="5" t="inlineStr">
         <is>
           <t>Wally — a favor, and you can say no without it costing us anything.
 I'm applying to list the Clarence toolkit in the Jump$tart Clearinghouse. To get in the door as a Provider, I need a letter of reference attesting to reputation and viability, because I'm not a National Partner and Jump$tart has no reason to know who I am.
@@ -26992,36 +27056,36 @@
 Jonathan</t>
         </is>
       </c>
-      <c r="K661" s="5" t="inlineStr"/>
-      <c r="L661" s="5" t="inlineStr"/>
-      <c r="M661" s="5" t="inlineStr"/>
-      <c r="N661" s="5" t="inlineStr"/>
-    </row>
-    <row r="662">
-      <c r="A662" s="5" t="inlineStr"/>
-      <c r="B662" s="5" t="inlineStr">
+      <c r="K662" s="5" t="inlineStr"/>
+      <c r="L662" s="5" t="inlineStr"/>
+      <c r="M662" s="5" t="inlineStr"/>
+      <c r="N662" s="5" t="inlineStr"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="5" t="inlineStr"/>
+      <c r="B663" s="5" t="inlineStr">
         <is>
           <t>Jump$tart</t>
         </is>
       </c>
-      <c r="C662" s="5" t="inlineStr">
+      <c r="C663" s="5" t="inlineStr">
         <is>
           <t>Reference letter — draft for Wally to sign</t>
         </is>
       </c>
-      <c r="D662" s="5" t="inlineStr"/>
-      <c r="E662" s="5" t="inlineStr"/>
-      <c r="F662" s="5" t="inlineStr">
+      <c r="D663" s="5" t="inlineStr"/>
+      <c r="E663" s="5" t="inlineStr"/>
+      <c r="F663" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G662" s="5" t="inlineStr"/>
-      <c r="H662" s="5" t="inlineStr"/>
-      <c r="I662" s="5" t="n">
+      <c r="G663" s="5" t="inlineStr"/>
+      <c r="H663" s="5" t="inlineStr"/>
+      <c r="I663" s="5" t="n">
         <v>1084</v>
       </c>
-      <c r="J662" s="5" t="inlineStr">
+      <c r="J663" s="5" t="inlineStr">
         <is>
           <t>To the Jump$tart Clearinghouse review team:
 I'm writing in support of Jonathan Bach and the classroom resources accompanying his children's book, Clarence Gets a Bargain.
@@ -27031,13 +27095,13 @@
 Wally Luckeydoo, Ed.D.</t>
         </is>
       </c>
-      <c r="K662" s="5" t="inlineStr"/>
-      <c r="L662" s="5" t="inlineStr"/>
-      <c r="M662" s="5" t="inlineStr"/>
-      <c r="N662" s="5" t="inlineStr"/>
+      <c r="K663" s="5" t="inlineStr"/>
+      <c r="L663" s="5" t="inlineStr"/>
+      <c r="M663" s="5" t="inlineStr"/>
+      <c r="N663" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N662"/>
+  <autoFilter ref="A1:N663"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27048,7 +27112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N76"/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -27640,8 +27704,23 @@
           <t>Leslie — a Bookshelf question, not a pitch. The Money as You Grow selections skew toward saving and earning. Mine teaches the transaction itself, right through the register. Is the shelf still open, and who does the evaluating? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr"/>
-      <c r="L12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Leslie — I sent a short note a while back about the Money as You Grow Bookshelf. This is the idea behind the book, and it's the one I actually wanted to run past someone at CFPB.
+A child becomes a consumer the first time they hand over money. Not at eighteen, not at a first paycheck — at six, at a register, with a birthday five in their fist. That is the whole premise of my book: a boy runs one complete purchase, sale ad to receipt, and picks up comparison shopping, markdowns, coupons, and sales tax on the way. Money as You Grow teaches saving and spending well. The transaction itself — the part where a kid is actually standing at the counter — is the gap the book fills, and the current shelf leans heavily toward saving.
+Here is the piece I keep circling. The moment a kid makes that first purchase, they have entered a relationship that comes with rights, and nobody teaches a seven-year-old they have any. An adult knows to keep the receipt and that a broken thing can go back. A child thinks the deal ends when the bag is handed over.
+I know the full rights picture crosses agencies — warranties and returns are FTC, product safety is CPSC. I'm not asking CFPB to cover those. I'm asking whether there's appetite within Money as You Grow for material that treats the child as a consumer with standing on the financial side, the day they first spend, rather than only as a saver in training.
+Realistic version of the ask: is the Bookshelf still evaluating titles, and who owns it now? And if the framing above is interesting, I'd trade ten minutes for your read on it.
+Toolkit: https://clarencegetsabargain.com/educator-toolkit.html
+The book in four minutes: https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from CFPB/rights</t>
+        </is>
+      </c>
       <c r="M12" s="5" t="inlineStr"/>
       <c r="N12" s="5" t="inlineStr"/>
     </row>
@@ -30732,8 +30811,57 @@
       <c r="M76" s="5" t="inlineStr"/>
       <c r="N76" s="5" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>CFPB/rights</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Lauren Saunders</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr"/>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Kids-as-consumers-with-rights thesis. the rights thesis is consumer law, not financial education, and NCLC
+is the country's consumer-law authority. This is the better home for the big idea than any
+agency, and she's a fresh connection who has never heard the</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Associate Director, National Consumer Law Center</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr"/>
+      <c r="H77" s="5" t="inlineStr"/>
+      <c r="I77" s="5" t="n">
+        <v>1544</v>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>Lauren — we just connected, and I have a question that belongs at NCLC more than anywhere else I can think of.
+Consumer law assumes a consumer who can read a contract, keep a receipt, and assert a claim. But everyone becomes a consumer years before any of that — the first time a kid spends money at a register. There is a whole population of consumers, roughly six to ten years old, who have no idea they have standing, and almost nothing is written to tell them.
+I wrote a children's book about the spending half of money. A boy runs one full purchase — comparison, coupon, sales tax — and learns how a transaction actually works. What I keep circling back to is the part I did not put in it: the same kid, the moment he buys the robot, has rights he will never be told about. That a broken thing can go back. That a warranty is a promise with teeth. That "the food was bad and I get to say so" is a real position, not a tantrum. Financial literacy teaches kids to save. Nobody teaches them they are a party to a deal that has two sides.
+That reads to me as a consumer-rights gap, not a financial-education one, which is exactly why I'm asking you. Has NCLC ever taken up children as consumers — or pointed anyone toward who has? Even a "that's an FTC education question, talk to so-and-so" would move me forward.
+Not a book pitch. A where-does-this-belong question from someone who wrote half of it by accident and wants to know where the other half lives. The book is here if it's ever useful: https://clarencegetsabargain.com
+Jonathan</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr"/>
+      <c r="L77" s="5" t="inlineStr"/>
+      <c r="M77" s="5" t="inlineStr"/>
+      <c r="N77" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N76"/>
+  <autoFilter ref="A1:N77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -737,11 +737,11 @@
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="n">
-        <v>695</v>
+        <v>661</v>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Alex — I read a dozen kids' money books to see where mine fit. Every one taught saving. Save your pennies, save for a rainy day, save, save, save. Not one covered the moment a kid stands there with his own five bucks deciding if the thing is worth it. Am I qualified to fix that? Debatable. I did once talk a cruise-ship shop into a price match and walk out having paid one cent for $300 shoes. Not a typo. Mine runs that whole gauntlet — ad, aisle, markdown, coupon, and the sales tax nobody warns a six-year-old about. Segment, or am I picking a fight the category doesn't want? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Alex — I read a dozen kids' money books to see where mine fit. Every one taught saving. Save your pennies, save for a rainy day, save, save, save. Not one covered the moment a kid stands there with his own five bucks deciding if the thing is worth it. Am I qualified to fix that? Debatable. I did once pay one cent for a $293 pair of shoes, and I kept the tag. Not a typo. Mine runs that whole gauntlet — ad, aisle, markdown, coupon, and the sales tax nobody warns a six-year-old about. Segment, or am I picking a fight the category doesn't want? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr"/>
@@ -26111,11 +26111,12 @@
         </is>
       </c>
       <c r="I646" s="5" t="n">
-        <v>1407</v>
+        <v>1687</v>
       </c>
       <c r="J646" s="5" t="inlineStr">
         <is>
           <t>Mr. Keen — congratulations on the building. You took over a school in a town where I spend a good part of my year, so this is a local letter, and I'll keep it short because it's your first fall.
+You may have seen me on the boardwalk this summer in a shirt reading PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW. Half your families were on that boardwalk in July, mid-negotiation with a seven-year-old over a claw machine. That is the moment this book is about.
 I wrote and illustrated a children's book about money. Clarence Gets a Bargain — 36 pages, grades 1-5, and it does the one thing the rest of the category skips. Every other kids' money book teaches saving. Mine teaches a purchase: a boy earns a robot, reads the sale ads at his kitchen table, compares two on a shelf, walks past the newer one deliberately, redeems a coupon at the register, and gets ambushed by sales tax. He is not thrilled about the sales tax. Neither was I at that age.
 Delaware has had K-12 financial literacy standards since 2018, and HB 203 last October sent the whole rollout to high school. Your grade band has the standard and none of the shopping list.
 The teacher side is free — four 45-minute lessons, a discussion guide, assessments with the answer keys already done, and a crosswalk to Jump$tart, CEE, Common Core, and FDIC Money Smart. It prints straight from a browser. No account, no email gate, no cost to the building.
@@ -26637,12 +26638,13 @@
         </is>
       </c>
       <c r="I655" s="5" t="n">
-        <v>1347</v>
+        <v>1479</v>
       </c>
       <c r="J655" s="5" t="inlineStr">
         <is>
           <t>Attn: Leslie Glenn, Youth Services
-Ms. Glenn — I'm on Rehoboth Avenue often enough that this feels less like a cold email than it probably reads. I wrote and illustrated a children's book and I'd like to read it in your building.
+Ms. Glenn — I have been walking the boardwalk in a shirt that reads PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW. It is either marketing or a cry for help. Strangers keep asking, which was the idea, so I am now asking you.
+I wrote and illustrated a children's book and I would like to read it in your building.
 Clarence Gets a Bargain is 36 pages, ages 6-10. A boy earns a robot for good grades and chores, learns to read the sale ads, compares two models in a store, picks the discounted one over the newest one, hands a coupon to a cashier, and discovers sales tax the way we all did — badly, and in public. It reads aloud in about twenty minutes.
 What makes it work for a summer program is that the kids do something afterward. I bring printable mock price tags and ten-percent-off coupons, and there's an online pretend register they can run on a library computer where they ring up the same purchase and watch a markdown and a coupon change the total. It's a book event that turns into an activity without a worksheet in it.
 I'd do it for free, obviously. Parents get something out of it too — most of them have never had a way to start this conversation with a seven-year-old and this hands them one.
@@ -26695,11 +26697,12 @@
         </is>
       </c>
       <c r="I656" s="5" t="n">
-        <v>1229</v>
+        <v>1481</v>
       </c>
       <c r="J656" s="5" t="inlineStr">
         <is>
           <t>Ms. Noonan — you coordinate the children's programming at Lewes, so you already know the difference between a book event that fills a room and one where six kids show up because it was raining. I'll tell you which one I think this is and you can decide.
+For calibration: I have been walking the boardwalk in a shirt that says PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW. Parents actually ask. Turns out the arcade is where the money conversation happens whether anybody planned it or not.
 I wrote and illustrated Clarence Gets a Bargain — 36 pages, ages 6-10. A boy earns a robot, does his "shopping homework" in the newspaper sale inserts, compares two models in a store, chooses the cheaper of the two on purpose, redeems a coupon at the checkout, and then meets sales tax and takes it as a personal betrayal. Twenty minutes read aloud.
 The reason it works as programming rather than just a reading: afterward the kids run the purchase themselves. There's a pretend register that runs in any browser, plus printable price tags and coupons, and they figure out the markdown and the discount with their own hands. Seven-year-olds get competitive about it. Loudly.
 No fee. I'm nearby a good part of the year, and I illustrated the book myself, so a drawing session is on the table if that suits the room better.
@@ -27237,11 +27240,11 @@
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="n">
-        <v>695</v>
+        <v>661</v>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Alex — I read a dozen kids' money books to see where mine fit. Every one taught saving. Save your pennies, save for a rainy day, save, save, save. Not one covered the moment a kid stands there with his own five bucks deciding if the thing is worth it. Am I qualified to fix that? Debatable. I did once talk a cruise-ship shop into a price match and walk out having paid one cent for $300 shoes. Not a typo. Mine runs that whole gauntlet — ad, aisle, markdown, coupon, and the sales tax nobody warns a six-year-old about. Segment, or am I picking a fight the category doesn't want? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Alex — I read a dozen kids' money books to see where mine fit. Every one taught saving. Save your pennies, save for a rainy day, save, save, save. Not one covered the moment a kid stands there with his own five bucks deciding if the thing is worth it. Am I qualified to fix that? Debatable. I did once pay one cent for a $293 pair of shoes, and I kept the tag. Not a typo. Mine runs that whole gauntlet — ad, aisle, markdown, coupon, and the sales tax nobody warns a six-year-old about. Segment, or am I picking a fight the category doesn't want? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr"/>

--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="86ed" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master'!$A$1:$N$663</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master'!$A$1:$N$665</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Whales'!$A$1:$N$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deadlines'!$A$1:$H$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Physical copies'!$A$1:$D$14</definedName>
@@ -612,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N663"/>
+  <dimension ref="A1:N665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -26683,7 +26683,7 @@
       <c r="E656" s="5" t="inlineStr"/>
       <c r="F656" s="5" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone / web form</t>
         </is>
       </c>
       <c r="G656" s="5" t="inlineStr">
@@ -26774,51 +26774,161 @@
       <c r="N657" s="5" t="inlineStr"/>
     </row>
     <row r="658">
-      <c r="A658" s="4" t="inlineStr">
+      <c r="A658" s="5" t="inlineStr"/>
+      <c r="B658" s="5" t="inlineStr">
+        <is>
+          <t>Delaware</t>
+        </is>
+      </c>
+      <c r="C658" s="5" t="inlineStr">
+        <is>
+          <t>James Wilson — Browseabout Books</t>
+        </is>
+      </c>
+      <c r="D658" s="5" t="inlineStr">
+        <is>
+          <t>Events Coordinator, Browseabout Books</t>
+        </is>
+      </c>
+      <c r="E658" s="5" t="inlineStr"/>
+      <c r="F658" s="5" t="inlineStr">
+        <is>
+          <t>Phone / web form</t>
+        </is>
+      </c>
+      <c r="G658" s="5" t="inlineStr">
+        <is>
+          <t>none published. Use the contact form at browseaboutbooks.com, addressed to him, or</t>
+        </is>
+      </c>
+      <c r="H658" s="5" t="inlineStr">
+        <is>
+          <t>The guy in the boardwalk shirt would like to come inside</t>
+        </is>
+      </c>
+      <c r="I658" s="5" t="n">
+        <v>1915</v>
+      </c>
+      <c r="J658" s="5" t="inlineStr">
+        <is>
+          <t>James — I have been walking up and down the boardwalk this summer in a shirt that reads PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW. Strangers ask. I then point them toward a book you do not carry, which is a marketing plan with an obvious flaw in it. Your front door is four blocks from where I am standing when it happens.
+I wrote and illustrated Clarence Gets a Bargain. Thirty-six pages, ages 6-10, hardbound. A boy earns a robot for chores and grades, works the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, and then meets sales tax and regards it as a personal insult. Every other children's money book teaches saving. This one teaches the part where a kid is actually standing at a register holding money.
+Two reasons to talk to me rather than the next local author with a tote bag.
+The first is that it is not a signing. Signings are four people and a folding table. I bring printable mock price tags, ten-percent-off coupons, and a pretend register the kids run in a browser, ringing up the same purchase and watching the markdown and the coupon move the total. They get competitive about it. Loudly. Parents stand behind them and read the back cover, which is the actual mechanism.
+The second is that I am the deal guy, and I can prove it. I have twice walked out of the same Nordstrom Rack having paid one cent — once for a $293 pair of shoes, once for a $69.50 shirt. I kept both tags. Both stickers say "99% Savings," which is modest of them, since a penny off $293 is 99.997%. If you want a photo for the window I have one.
+I also wrote a book in which a crab complains about how people behave on the beach, so I am aware of my own genre range.
+Storytime slot, a Saturday morning, a festival table, or a no — all useful answers.
+Jonathan Bach
+Baltimore and Rehoboth Beach
+clarencegetsabargain.com</t>
+        </is>
+      </c>
+      <c r="K658" s="5" t="inlineStr"/>
+      <c r="L658" s="5" t="inlineStr">
+        <is>
+          <t>Now. Summer is their season and a kids' event needs lead time.</t>
+        </is>
+      </c>
+      <c r="M658" s="5" t="inlineStr"/>
+      <c r="N658" s="5" t="inlineStr"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="5" t="inlineStr"/>
+      <c r="B659" s="5" t="inlineStr">
+        <is>
+          <t>Delaware</t>
+        </is>
+      </c>
+      <c r="C659" s="5" t="inlineStr">
+        <is>
+          <t>Beachside Book Festival — Sussex County Libraries</t>
+        </is>
+      </c>
+      <c r="D659" s="5" t="inlineStr">
+        <is>
+          <t>Sussex County Libraries, in partnership with Browseabout Books</t>
+        </is>
+      </c>
+      <c r="E659" s="5" t="inlineStr"/>
+      <c r="F659" s="5" t="inlineStr">
+        <is>
+          <t>Phone / web form</t>
+        </is>
+      </c>
+      <c r="G659" s="5" t="inlineStr"/>
+      <c r="H659" s="5" t="inlineStr">
+        <is>
+          <t>A festival table where the kids run a cash register</t>
+        </is>
+      </c>
+      <c r="I659" s="5" t="n">
+        <v>1437</v>
+      </c>
+      <c r="J659" s="5" t="inlineStr">
+        <is>
+          <t>To whoever builds the author slate for the Beachside Book Festival —
+I would like a table, and I think I fit the ten-to-one o'clock block better than most authors who ask.
+I wrote and illustrated Clarence Gets a Bargain, a 36-page picture book for ages 6-10 about the money skill nobody writes for children: spending. A boy earns a robot, reads the sale ads, compares two models, takes the cheaper one deliberately, redeems a coupon, and discovers sales tax the way we all did, which is badly and in public.
+Here is why the format suits you. Your morning block puts local author talks next to craft vendors, which means families are already circulating and looking for something a child can do with their hands. I am not asking to give a talk. I want a table where kids ring up a purchase themselves — printable price tags, ten-percent-off coupons, and a pretend register running in a browser where a markdown and a coupon visibly change the total. It behaves like a craft table and teaches percentages by accident.
+I am local for a good part of the year. I have also spent this summer walking the boardwalk in a shirt reading PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW, which is a fair description of the demand for this at the beach in April.
+What is the application, and when does the slate close?
+Jonathan Bach
+Baltimore and Rehoboth Beach
+clarencegetsabargain.com
+https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
+      <c r="K659" s="5" t="inlineStr"/>
+      <c r="L659" s="5" t="inlineStr"/>
+      <c r="M659" s="5" t="inlineStr"/>
+      <c r="N659" s="5" t="inlineStr"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="4" t="inlineStr">
         <is>
           <t>🐋</t>
         </is>
       </c>
-      <c r="B658" s="5" t="inlineStr">
+      <c r="B660" s="5" t="inlineStr">
         <is>
           <t>Standalone</t>
         </is>
       </c>
-      <c r="C658" s="5" t="inlineStr">
+      <c r="C660" s="5" t="inlineStr">
         <is>
           <t>Mia Baytop Russell</t>
         </is>
       </c>
-      <c r="D658" s="5" t="inlineStr">
+      <c r="D660" s="5" t="inlineStr">
         <is>
           <t>Senior Lecturer, Johns Hopkins; Dir., Clark Scholars. Ex-Money Smart (UMD Ext.), ex-VP Wells Fargo Foundation</t>
         </is>
       </c>
-      <c r="E658" s="5" t="inlineStr">
+      <c r="E660" s="5" t="inlineStr">
         <is>
           <t>Practitioner, funder and academic in one person. Reference-letter candidate for Jump$tart.</t>
         </is>
       </c>
-      <c r="F658" s="5" t="inlineStr">
+      <c r="F660" s="5" t="inlineStr">
         <is>
           <t>Connection note, then InMail</t>
         </is>
       </c>
-      <c r="G658" s="5" t="inlineStr"/>
-      <c r="H658" s="5" t="inlineStr">
+      <c r="G660" s="5" t="inlineStr"/>
+      <c r="H660" s="5" t="inlineStr">
         <is>
           <t>Money Smart, Wells Fargo, Hopkins — and a premise you can puncture</t>
         </is>
       </c>
-      <c r="I658" s="5" t="n">
+      <c r="I660" s="5" t="n">
         <v>280</v>
       </c>
-      <c r="J658" s="5" t="inlineStr">
+      <c r="J660" s="5" t="inlineStr">
         <is>
           <t>Mia — you ran Money Smart at Maryland Extension, decided what got funded at Wells Fargo, and now teach it at Hopkins. Three chairs, almost nobody has sat in all of them. I wrote a K-5 book aligned to Money Smart that leaves saving out entirely. I'm in Baltimore too. Worth a look?</t>
         </is>
       </c>
-      <c r="K658" s="5" t="inlineStr">
+      <c r="K660" s="5" t="inlineStr">
         <is>
           <t>Mia — you've sat in all three chairs, which almost nobody in this field has. You ran the Money Smart team at Maryland Extension. You decided what got funded as VP for youth financial health philanthropy at Wells Fargo. Now you teach it at Hopkins. Practitioner, funder, academic, in that order.
 Which makes you exactly the person I want to tell me I'm wrong.
@@ -26838,51 +26948,51 @@
 clarencegetsabargain.com</t>
         </is>
       </c>
-      <c r="L658" s="5" t="inlineStr">
+      <c r="L660" s="5" t="inlineStr">
         <is>
           <t>Col M = 280-char connection note. Col N = 1,323-char InMail. | Subject: A reference letter, and the three reasons I'm asking you specifically · Long-form version from Jump$tart</t>
         </is>
       </c>
-      <c r="M658" s="5" t="inlineStr"/>
-      <c r="N658" s="5" t="inlineStr"/>
-    </row>
-    <row r="659">
-      <c r="A659" s="4" t="inlineStr">
+      <c r="M660" s="5" t="inlineStr"/>
+      <c r="N660" s="5" t="inlineStr"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="4" t="inlineStr">
         <is>
           <t>🐋</t>
         </is>
       </c>
-      <c r="B659" s="5" t="inlineStr">
+      <c r="B661" s="5" t="inlineStr">
         <is>
           <t>Standalone</t>
         </is>
       </c>
-      <c r="C659" s="5" t="inlineStr">
+      <c r="C661" s="5" t="inlineStr">
         <is>
           <t>Dr. Rachel Edoho-Eket</t>
         </is>
       </c>
-      <c r="D659" s="5" t="inlineStr">
+      <c r="D661" s="5" t="inlineStr">
         <is>
           <t>Principal, Waterloo Elementary (Blue Ribbon); Past President, MAESP; 2x author</t>
         </is>
       </c>
-      <c r="E659" s="5" t="inlineStr">
+      <c r="E661" s="5" t="inlineStr">
         <is>
           <t>Maryland elementary gatekeeper, local, and an author who judges production.</t>
         </is>
       </c>
-      <c r="F659" s="5" t="inlineStr">
+      <c r="F661" s="5" t="inlineStr">
         <is>
           <t>LinkedIn DM (1st-degree)</t>
         </is>
       </c>
-      <c r="G659" s="5" t="inlineStr"/>
-      <c r="H659" s="5" t="inlineStr"/>
-      <c r="I659" s="5" t="n">
+      <c r="G661" s="5" t="inlineStr"/>
+      <c r="H661" s="5" t="inlineStr"/>
+      <c r="I661" s="5" t="n">
         <v>2002</v>
       </c>
-      <c r="J659" s="5" t="inlineStr">
+      <c r="J661" s="5" t="inlineStr">
         <is>
           <t>Dr. Edoho-Eket — congratulations on the ISTE+ASCD 20 to Watch. What stuck with me wasn't the award, it was what you wrote about it: that it started 21 years ago teaching five-year-olds in Howard County, and that those lessons still guide how you lead.
 Those five-year-olds are my entire readership.
@@ -26897,50 +27007,50 @@
 Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K659" s="5" t="inlineStr"/>
-      <c r="L659" s="5" t="inlineStr">
+      <c r="K661" s="5" t="inlineStr"/>
+      <c r="L661" s="5" t="inlineStr">
         <is>
           <t>Already a connection — single DM, no request note.</t>
         </is>
       </c>
-      <c r="M659" s="5" t="inlineStr"/>
-      <c r="N659" s="5" t="inlineStr"/>
-    </row>
-    <row r="660">
-      <c r="A660" s="4" t="inlineStr">
+      <c r="M661" s="5" t="inlineStr"/>
+      <c r="N661" s="5" t="inlineStr"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="4" t="inlineStr">
         <is>
           <t>🐋</t>
         </is>
       </c>
-      <c r="B660" s="5" t="inlineStr">
+      <c r="B662" s="5" t="inlineStr">
         <is>
           <t>CFPB/rights</t>
         </is>
       </c>
-      <c r="C660" s="5" t="inlineStr">
+      <c r="C662" s="5" t="inlineStr">
         <is>
           <t>Lauren Saunders</t>
         </is>
       </c>
-      <c r="D660" s="5" t="inlineStr"/>
-      <c r="E660" s="5" t="inlineStr">
+      <c r="D662" s="5" t="inlineStr"/>
+      <c r="E662" s="5" t="inlineStr">
         <is>
           <t>Kids-as-consumers-with-rights thesis. the rights thesis is consumer law, not financial education, and NCLC
 is the country's consumer-law authority. This is the better home for the big idea than any
 agency, and she's a fresh connection who has never heard the</t>
         </is>
       </c>
-      <c r="F660" s="5" t="inlineStr">
+      <c r="F662" s="5" t="inlineStr">
         <is>
           <t>Associate Director, National Consumer Law Center</t>
         </is>
       </c>
-      <c r="G660" s="5" t="inlineStr"/>
-      <c r="H660" s="5" t="inlineStr"/>
-      <c r="I660" s="5" t="n">
+      <c r="G662" s="5" t="inlineStr"/>
+      <c r="H662" s="5" t="inlineStr"/>
+      <c r="I662" s="5" t="n">
         <v>1544</v>
       </c>
-      <c r="J660" s="5" t="inlineStr">
+      <c r="J662" s="5" t="inlineStr">
         <is>
           <t>Lauren — we just connected, and I have a question that belongs at NCLC more than anywhere else I can think of.
 Consumer law assumes a consumer who can read a contract, keep a receipt, and assert a claim. But everyone becomes a consumer years before any of that — the first time a kid spends money at a register. There is a whole population of consumers, roughly six to ten years old, who have no idea they have standing, and almost nothing is written to tell them.
@@ -26950,52 +27060,52 @@
 Jonathan</t>
         </is>
       </c>
-      <c r="K660" s="5" t="inlineStr"/>
-      <c r="L660" s="5" t="inlineStr"/>
-      <c r="M660" s="5" t="inlineStr"/>
-      <c r="N660" s="5" t="inlineStr"/>
-    </row>
-    <row r="661">
-      <c r="A661" s="5" t="inlineStr"/>
-      <c r="B661" s="5" t="inlineStr">
+      <c r="K662" s="5" t="inlineStr"/>
+      <c r="L662" s="5" t="inlineStr"/>
+      <c r="M662" s="5" t="inlineStr"/>
+      <c r="N662" s="5" t="inlineStr"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="5" t="inlineStr"/>
+      <c r="B663" s="5" t="inlineStr">
         <is>
           <t>Jump$tart</t>
         </is>
       </c>
-      <c r="C661" s="5" t="inlineStr">
+      <c r="C663" s="5" t="inlineStr">
         <is>
           <t>Suzann Knight</t>
         </is>
       </c>
-      <c r="D661" s="5" t="inlineStr">
+      <c r="D663" s="5" t="inlineStr">
         <is>
           <t>send this one first</t>
         </is>
       </c>
-      <c r="E661" s="5" t="inlineStr">
+      <c r="E663" s="5" t="inlineStr">
         <is>
           <t>send this one first</t>
         </is>
       </c>
-      <c r="F661" s="5" t="inlineStr">
+      <c r="F663" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G661" s="5" t="inlineStr">
+      <c r="G663" s="5" t="inlineStr">
         <is>
           <t>suzann.knight@jumpstart.org</t>
         </is>
       </c>
-      <c r="H661" s="5" t="inlineStr">
+      <c r="H663" s="5" t="inlineStr">
         <is>
           <t>Clearinghouse eligibility question — free K-5 toolkit, and a reference letter</t>
         </is>
       </c>
-      <c r="I661" s="5" t="n">
+      <c r="I663" s="5" t="n">
         <v>1906</v>
       </c>
-      <c r="J661" s="5" t="inlineStr">
+      <c r="J663" s="5" t="inlineStr">
         <is>
           <t>Ms. Knight — the Clearinghouse page says you're the person to ask, so I'll ask one thing and keep it short.
 I'd like to list a free K-5 classroom resource. Reading the Provider criteria, I don't meet the first three routes — I'm not a National Partner, I've never listed before, and Jump$tart has no reason to know me. That leaves the letter of reference, and the criteria say you'll provide instructions if one is required.
@@ -27008,48 +27118,48 @@
 Baltimore</t>
         </is>
       </c>
-      <c r="K661" s="5" t="inlineStr"/>
-      <c r="L661" s="5" t="inlineStr"/>
-      <c r="M661" s="5" t="inlineStr"/>
-      <c r="N661" s="5" t="inlineStr"/>
-    </row>
-    <row r="662">
-      <c r="A662" s="5" t="inlineStr"/>
-      <c r="B662" s="5" t="inlineStr">
+      <c r="K663" s="5" t="inlineStr"/>
+      <c r="L663" s="5" t="inlineStr"/>
+      <c r="M663" s="5" t="inlineStr"/>
+      <c r="N663" s="5" t="inlineStr"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="5" t="inlineStr"/>
+      <c r="B664" s="5" t="inlineStr">
         <is>
           <t>Jump$tart</t>
         </is>
       </c>
-      <c r="C662" s="5" t="inlineStr">
+      <c r="C664" s="5" t="inlineStr">
         <is>
           <t>Wally Luckeydoo</t>
         </is>
       </c>
-      <c r="D662" s="5" t="inlineStr">
+      <c r="D664" s="5" t="inlineStr">
         <is>
           <t>asking for the letter</t>
         </is>
       </c>
-      <c r="E662" s="5" t="inlineStr">
+      <c r="E664" s="5" t="inlineStr">
         <is>
           <t>asking for the letter</t>
         </is>
       </c>
-      <c r="F662" s="5" t="inlineStr">
+      <c r="F664" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G662" s="5" t="inlineStr"/>
-      <c r="H662" s="5" t="inlineStr">
+      <c r="G664" s="5" t="inlineStr"/>
+      <c r="H664" s="5" t="inlineStr">
         <is>
           <t>A favor with your name already on it</t>
         </is>
       </c>
-      <c r="I662" s="5" t="n">
+      <c r="I664" s="5" t="n">
         <v>909</v>
       </c>
-      <c r="J662" s="5" t="inlineStr">
+      <c r="J664" s="5" t="inlineStr">
         <is>
           <t>Wally — a favor, and you can say no without it costing us anything.
 I'm applying to list the Clarence toolkit in the Jump$tart Clearinghouse. To get in the door as a Provider, I need a letter of reference attesting to reputation and viability, because I'm not a National Partner and Jump$tart has no reason to know who I am.
@@ -27059,36 +27169,36 @@
 Jonathan</t>
         </is>
       </c>
-      <c r="K662" s="5" t="inlineStr"/>
-      <c r="L662" s="5" t="inlineStr"/>
-      <c r="M662" s="5" t="inlineStr"/>
-      <c r="N662" s="5" t="inlineStr"/>
-    </row>
-    <row r="663">
-      <c r="A663" s="5" t="inlineStr"/>
-      <c r="B663" s="5" t="inlineStr">
+      <c r="K664" s="5" t="inlineStr"/>
+      <c r="L664" s="5" t="inlineStr"/>
+      <c r="M664" s="5" t="inlineStr"/>
+      <c r="N664" s="5" t="inlineStr"/>
+    </row>
+    <row r="665">
+      <c r="A665" s="5" t="inlineStr"/>
+      <c r="B665" s="5" t="inlineStr">
         <is>
           <t>Jump$tart</t>
         </is>
       </c>
-      <c r="C663" s="5" t="inlineStr">
+      <c r="C665" s="5" t="inlineStr">
         <is>
           <t>Reference letter — draft for Wally to sign</t>
         </is>
       </c>
-      <c r="D663" s="5" t="inlineStr"/>
-      <c r="E663" s="5" t="inlineStr"/>
-      <c r="F663" s="5" t="inlineStr">
+      <c r="D665" s="5" t="inlineStr"/>
+      <c r="E665" s="5" t="inlineStr"/>
+      <c r="F665" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G663" s="5" t="inlineStr"/>
-      <c r="H663" s="5" t="inlineStr"/>
-      <c r="I663" s="5" t="n">
+      <c r="G665" s="5" t="inlineStr"/>
+      <c r="H665" s="5" t="inlineStr"/>
+      <c r="I665" s="5" t="n">
         <v>1084</v>
       </c>
-      <c r="J663" s="5" t="inlineStr">
+      <c r="J665" s="5" t="inlineStr">
         <is>
           <t>To the Jump$tart Clearinghouse review team:
 I'm writing in support of Jonathan Bach and the classroom resources accompanying his children's book, Clarence Gets a Bargain.
@@ -27098,13 +27208,13 @@
 Wally Luckeydoo, Ed.D.</t>
         </is>
       </c>
-      <c r="K663" s="5" t="inlineStr"/>
-      <c r="L663" s="5" t="inlineStr"/>
-      <c r="M663" s="5" t="inlineStr"/>
-      <c r="N663" s="5" t="inlineStr"/>
+      <c r="K665" s="5" t="inlineStr"/>
+      <c r="L665" s="5" t="inlineStr"/>
+      <c r="M665" s="5" t="inlineStr"/>
+      <c r="N665" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N663"/>
+  <autoFilter ref="A1:N665"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -26111,12 +26111,12 @@
         </is>
       </c>
       <c r="I646" s="5" t="n">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="J646" s="5" t="inlineStr">
         <is>
           <t>Mr. Keen — congratulations on the building. You took over a school in a town where I spend a good part of my year, so this is a local letter, and I'll keep it short because it's your first fall.
-You may have seen me on the boardwalk this summer in a shirt reading PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW. Half your families were on that boardwalk in July, mid-negotiation with a seven-year-old over a claw machine. That is the moment this book is about.
+I have had a shirt printed that reads PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW, so you may yet see me in it. Half your families were on that boardwalk in July, mid-negotiation with a seven-year-old over a claw machine. That is the moment this book is about.
 I wrote and illustrated a children's book about money. Clarence Gets a Bargain — 36 pages, grades 1-5, and it does the one thing the rest of the category skips. Every other kids' money book teaches saving. Mine teaches a purchase: a boy earns a robot, reads the sale ads at his kitchen table, compares two on a shelf, walks past the newer one deliberately, redeems a coupon at the register, and gets ambushed by sales tax. He is not thrilled about the sales tax. Neither was I at that age.
 Delaware has had K-12 financial literacy standards since 2018, and HB 203 last October sent the whole rollout to high school. Your grade band has the standard and none of the shopping list.
 The teacher side is free — four 45-minute lessons, a discussion guide, assessments with the answer keys already done, and a crosswalk to Jump$tart, CEE, Common Core, and FDIC Money Smart. It prints straight from a browser. No account, no email gate, no cost to the building.
@@ -26638,12 +26638,12 @@
         </is>
       </c>
       <c r="I655" s="5" t="n">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="J655" s="5" t="inlineStr">
         <is>
           <t>Attn: Leslie Glenn, Youth Services
-Ms. Glenn — I have been walking the boardwalk in a shirt that reads PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW. It is either marketing or a cry for help. Strangers keep asking, which was the idea, so I am now asking you.
+Ms. Glenn — I have had a shirt printed that reads PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW. It is either marketing or a cry for help, and I intend to find out on the boardwalk this summer. In the meantime I am asking you.
 I wrote and illustrated a children's book and I would like to read it in your building.
 Clarence Gets a Bargain is 36 pages, ages 6-10. A boy earns a robot for good grades and chores, learns to read the sale ads, compares two models in a store, picks the discounted one over the newest one, hands a coupon to a cashier, and discovers sales tax the way we all did — badly, and in public. It reads aloud in about twenty minutes.
 What makes it work for a summer program is that the kids do something afterward. I bring printable mock price tags and ten-percent-off coupons, and there's an online pretend register they can run on a library computer where they ring up the same purchase and watch a markdown and a coupon change the total. It's a book event that turns into an activity without a worksheet in it.
@@ -26697,12 +26697,12 @@
         </is>
       </c>
       <c r="I656" s="5" t="n">
-        <v>1481</v>
+        <v>1530</v>
       </c>
       <c r="J656" s="5" t="inlineStr">
         <is>
           <t>Ms. Noonan — you coordinate the children's programming at Lewes, so you already know the difference between a book event that fills a room and one where six kids show up because it was raining. I'll tell you which one I think this is and you can decide.
-For calibration: I have been walking the boardwalk in a shirt that says PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW. Parents actually ask. Turns out the arcade is where the money conversation happens whether anybody planned it or not.
+For calibration, I have had a shirt printed that says PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW. Whether anyone stops me is still an open question. But the arcade is where the money conversation happens whether a parent planned it or not, and that is the whole subject of the book.
 I wrote and illustrated Clarence Gets a Bargain — 36 pages, ages 6-10. A boy earns a robot, does his "shopping homework" in the newspaper sale inserts, compares two models in a store, chooses the cheaper of the two on purpose, redeems a coupon at the checkout, and then meets sales tax and takes it as a personal betrayal. Twenty minutes read aloud.
 The reason it works as programming rather than just a reading: afterward the kids run the purchase themselves. There's a pretend register that runs in any browser, plus printable price tags and coupons, and they figure out the markdown and the discount with their own hands. Seven-year-olds get competitive about it. Loudly.
 No fee. I'm nearby a good part of the year, and I illustrated the book myself, so a drawing session is on the table if that suits the room better.
@@ -26807,11 +26807,11 @@
         </is>
       </c>
       <c r="I658" s="5" t="n">
-        <v>1915</v>
+        <v>1938</v>
       </c>
       <c r="J658" s="5" t="inlineStr">
         <is>
-          <t>James — I have been walking up and down the boardwalk this summer in a shirt that reads PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW. Strangers ask. I then point them toward a book you do not carry, which is a marketing plan with an obvious flaw in it. Your front door is four blocks from where I am standing when it happens.
+          <t>James — I have had a shirt printed that reads PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW, and the plan is to wear it up and down the boardwalk until somebody asks. At which point I will point them toward a book you do not carry. Your front door is four blocks from where I will be standing, so you can see the flaw in my plan as clearly as I can.
 I wrote and illustrated Clarence Gets a Bargain. Thirty-six pages, ages 6-10, hardbound. A boy earns a robot for chores and grades, works the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, and then meets sales tax and regards it as a personal insult. Every other children's money book teaches saving. This one teaches the part where a kid is actually standing at a register holding money.
 Two reasons to talk to me rather than the next local author with a tote bag.
 The first is that it is not a signing. Signings are four people and a folding table. I bring printable mock price tags, ten-percent-off coupons, and a pretend register the kids run in a browser, ringing up the same purchase and watching the markdown and the coupon move the total. They get competitive about it. Loudly. Parents stand behind them and read the back cover, which is the actual mechanism.
@@ -26862,7 +26862,7 @@
         </is>
       </c>
       <c r="I659" s="5" t="n">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="J659" s="5" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
 I would like a table, and I think I fit the ten-to-one o'clock block better than most authors who ask.
 I wrote and illustrated Clarence Gets a Bargain, a 36-page picture book for ages 6-10 about the money skill nobody writes for children: spending. A boy earns a robot, reads the sale ads, compares two models, takes the cheaper one deliberately, redeems a coupon, and discovers sales tax the way we all did, which is badly and in public.
 Here is why the format suits you. Your morning block puts local author talks next to craft vendors, which means families are already circulating and looking for something a child can do with their hands. I am not asking to give a talk. I want a table where kids ring up a purchase themselves — printable price tags, ten-percent-off coupons, and a pretend register running in a browser where a markdown and a coupon visibly change the total. It behaves like a craft table and teaches percentages by accident.
-I am local for a good part of the year. I have also spent this summer walking the boardwalk in a shirt reading PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW, which is a fair description of the demand for this at the beach in April.
+I am local for a good part of the year. I have also had a shirt printed reading PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW, which I offer less as a credential than as a fair description of the demand for this at the beach in April.
 What is the application, and when does the slate close?
 Jonathan Bach
 Baltimore and Rehoboth Beach

--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -829,11 +829,11 @@
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="n">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>Tim — NGPF owns 9-12 and does it better than anyone. I wrote the K-5 on-ramp: a picture book where a kid runs one real purchase, ad to register, sales tax and all. Genuine question rather than a pitch — do you see elementary as in scope for NGPF, or a gap somebody else has to fill? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tim — NGPF owns 9-12 and does it better than anyone. I wrote the K-5 on-ramp: a picture book where a kid runs one real purchase, ad to register, sales tax and all. Genuine question rather than a pitch — do you see elementary as in scope for NGPF, or a gap somebody else has to fill? Teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr"/>
@@ -1013,11 +1013,11 @@
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="n">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Joel — no login, no email capture, no funnel. Four 45-minute lesson plans, a pre/post assessment with the answer key, and a 23-row crosswalk, all built against the National Standards and all free. I'd like it in the Clearinghouse. Does it clear the bar as you read the criteria? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Joel — no login, no email capture, no funnel. Four 45-minute lesson plans, a pre/post assessment with the answer key, and a 23-row crosswalk, all built against the National Standards and all free. I'd like it in the Clearinghouse. Does it clear the bar as you read the criteria? Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr"/>
@@ -1151,11 +1151,11 @@
       <c r="G11" s="5" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="n">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Yanely — you've said the gaps show up long before high school. I wrote the K-5 version, and it teaches spending because that's the transaction a six-year-old actually performs. Does NGPF ever point teachers below ninth grade, or is that outside the remit? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Yanely — you've said the gaps show up long before high school. I wrote the K-5 version, and it teaches spending because that's the transaction a six-year-old actually performs. Does NGPF ever point teachers below ninth grade, or is that outside the remit? For teachers: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr"/>
@@ -1197,11 +1197,11 @@
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="n">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Leslie — a Bookshelf question, not a pitch. The Money as You Grow selections skew toward saving and earning. Mine teaches the transaction itself, right through the register. Is the shelf still open, and who does the evaluating? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Leslie — a Bookshelf question, not a pitch. The Money as You Grow selections skew toward saving and earning. Mine teaches the transaction itself, right through the register. Is the shelf still open, and who does the evaluating? The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -1211,7 +1211,7 @@
 Here is the piece I keep circling. The moment a kid makes that first purchase, they have entered a relationship that comes with rights, and nobody teaches a seven-year-old they have any. An adult knows to keep the receipt and that a broken thing can go back. A child thinks the deal ends when the bag is handed over.
 I know the full rights picture crosses agencies — warranties and returns are FTC, product safety is CPSC. I'm not asking CFPB to cover those. I'm asking whether there's appetite within Money as You Grow for material that treats the child as a consumer with standing on the financial side, the day they first spend, rather than only as a saver in training.
 Realistic version of the ask: is the Bookshelf still evaluating titles, and who owns it now? And if the framing above is interesting, I'd trade ten minutes for your read on it.
-Toolkit: https://clarencegetsabargain.com/educator-toolkit.html
+The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html
 The book in four minutes: https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
         </is>
@@ -1258,11 +1258,11 @@
       <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="n">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Ken — my book and its free K-5 toolkit are aligned to Money Smart for Young People, with a crosswalk mapping every concept to the specific standard rather than asking you to take my word. Is there a process for a title to sit alongside Money Smart materials, or is that not how it works? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ken — my book and its free K-5 classroom materials are aligned to Money Smart for Young People, with a crosswalk mapping every concept to the specific standard rather than asking you to take my word. Is there a process for a title to sit alongside Money Smart materials, or is that not how it works? Print it here: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr"/>
@@ -1396,11 +1396,11 @@
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="5" t="n">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Lyn — is the Money as You Grow Bookshelf still taking titles? Mine is K-5 and teaches spending: comparison shopping, markdowns, coupons, sales tax at the register. The current shelf leans heavily toward saving. Happy to send it to whoever evaluates. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Lyn — is the Money as You Grow Bookshelf still taking titles? Mine is K-5 and teaches spending: comparison shopping, markdowns, coupons, sales tax at the register. The current shelf leans heavily toward saving. Happy to send it to whoever evaluates. Teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr"/>
@@ -1504,11 +1504,11 @@
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="n">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Tracy — a public-private partnership is how a K-5 resource actually scales, since elementary rarely gets its own budget line. It's a 36-page picture book plus free ungated toolkit against five frameworks. Fit inside the partnership? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tracy — a public-private partnership is how a K-5 resource actually scales, since elementary rarely gets its own budget line. It's a 36-page picture book plus free ungated teacher pack against five frameworks. Fit inside the partnership? Teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr"/>
@@ -1596,11 +1596,11 @@
       <c r="G20" s="5" t="inlineStr"/>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="n">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Bill — Tennessee's commission decides what reaches classrooms statewide, and elementary is usually where state mandates run thin. Mine is a K-5 picture book with a free zero-prep toolkit against Jump$tart, CEE, Common Core, and FDIC Money Smart. Route to get it in front of the commission? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Bill — Tennessee's commission decides what reaches classrooms statewide, and elementary is usually where state mandates run thin. Mine is a K-5 picture book with a free zero-prep classroom pack against Jump$tart, CEE, Common Core, and FDIC Money Smart. Route to get it in front of the commission? Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr"/>
@@ -1642,11 +1642,11 @@
       <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="n">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Dave — Wisconsin has been at this longer than most states. My K-5 book and free toolkit map to five frameworks. Elementary tends to be the underserved band everywhere I look. Is there a submission route, or a person who reviews outside materials? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dave — Wisconsin has been at this longer than most states. My K-5 book and free lesson set map to five frameworks. Elementary tends to be the underserved band everywhere I look. Is there a submission route, or a person who reviews outside materials? For teachers: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr"/>
@@ -1688,11 +1688,11 @@
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="n">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Hunter — policy and advocacy at NEFE puts you where the K-5 gap is most visible. Nearly everything funded sits at high school. I wrote a picture book plus free toolkit for grades 1-5 against five frameworks. Is early elementary getting any policy attention, or still an orphan? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hunter — policy and advocacy at NEFE puts you where the K-5 gap is most visible. Nearly everything funded sits at high school. I wrote a picture book plus free teacher materials for grades 1-5 against five frameworks. Is early elementary getting any policy attention, or still an orphan? The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr"/>
@@ -2102,11 +2102,11 @@
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="n">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Bethann — a bankers association reaches classrooms and families at once, which is the distribution a K-5 book needs and rarely gets. Mine is five frameworks, free zero-prep lessons, plus a grant packet if a member bank wanted to fund classroom sets. Fit Utah's outreach? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Bethann — a bankers association reaches classrooms and families at once, which is the distribution a K-5 book needs and rarely gets. Mine is five frameworks, free zero-prep lessons, plus a grant packet if a member bank wanted to fund classroom sets. Fit Utah's outreach? Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr"/>
@@ -2194,11 +2194,11 @@
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="n">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Ruben — my book and toolkit are aligned to the CEE standards with a full crosswalk. Is there a route for a K-5 title into CEE's resource library or EconEdLink, and what would you want to see first? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ruben — my book and teaching pack are aligned to the CEE standards with a full crosswalk. Is there a route for a K-5 title into CEE's resource library or EconEdLink, and what would you want to see first? Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr"/>
@@ -2378,11 +2378,11 @@
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Jillian — Intuit for Education is built around real financial decisions, which is my book's entire structure: one purchase, ad to register, sales tax included. Mine sits at K-5, below your usual band. Does the framing match how you think about curriculum? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jillian — Intuit for Education is built around real financial decisions, which is my book's entire structure: one purchase, ad to register, sales tax included. Mine sits at K-5, below your usual band. Does the framing match how you think about curriculum? Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr"/>
@@ -2424,11 +2424,11 @@
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="n">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Saskia — Promise Academy is deliberate about what earns classroom time, which is the right instinct. Mine teaches the complete purchase, sales tax included, and the family activity was built for a kitchen table. Classrooms or family programming — or neither? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Saskia — Promise Academy is deliberate about what earns classroom time, which is the right instinct. Mine teaches the complete purchase, sales tax included, and the family activity was built for a kitchen table. Classrooms or family programming — or neither? Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr"/>
@@ -2654,11 +2654,11 @@
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr"/>
       <c r="I43" s="5" t="n">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Dr. Taylor — Montgomery County sets what reaches a lot of classrooms. Mine is a K-5 picture book with a free zero-prep toolkit, five frameworks, nothing consumable to reorder next August. The honest question is placement rather than merit: classroom, library, or family night? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Taylor — Montgomery County sets what reaches a lot of classrooms. Mine is a K-5 picture book with a free zero-prep lesson set, five frameworks, nothing consumable to reorder next August. The honest question is placement rather than merit: classroom, library, or family night? Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr"/>
@@ -2700,11 +2700,11 @@
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="n">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Beth — a research question. My K-5 book argues spending competence precedes saving competence developmentally, which would mean the field teaches the wrong skill first. Does that square with your research and impact work, or am I overstating a tidy story? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Beth — a research question. My K-5 book argues spending competence precedes saving competence developmentally, which would mean the field teaches the wrong skill first. Does that square with your research and impact work, or am I overstating a tidy story? The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr"/>
@@ -2792,11 +2792,11 @@
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="n">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Vince — NFEC reaches thousands of instructors, and K-5 is where most of them have the least to hand anyone. Mine runs 36 pages plus free toolkit against five frameworks, crosswalk included. Route into the NFEC resource network? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Vince — NFEC reaches thousands of instructors, and K-5 is where most of them have the least to hand anyone. Mine runs 36 pages plus free classroom materials against five frameworks, crosswalk included. Route into the NFEC resource network? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr"/>
@@ -2838,11 +2838,11 @@
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="n">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Billy — a NEFE-shaped question. The research keeps saying money attitudes form by seven, and almost every dollar of material lands at 9-12. I wrote a K-5 picture book teaching spending rather than saving. Does NEFE ever point people to elementary, or is that band still nobody's mandate? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Billy — a NEFE-shaped question. The research keeps saying money attitudes form by seven, and almost every dollar of material lands at 9-12. I wrote a K-5 picture book teaching spending rather than saving. Does NEFE ever point people to elementary, or is that band still nobody's mandate? Teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr"/>
@@ -2884,11 +2884,11 @@
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="n">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Laura — a Clearinghouse question rather than a pitch. My K-5 toolkit is built against the National Standards, free, ungated, no email capture and no drip campaign. Is Suzann Knight the right first stop, or is there a step I'm skipping? Wally Luckeydoo endorsed the book, which I mention only because he's your 2026 Corey Carlisle recipient. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Laura — a Clearinghouse question rather than a pitch. My K-5 teacher pack is built against the National Standards, free, ungated, no email capture and no drip campaign. Is Suzann Knight the right first stop, or is there a step I'm skipping? Wally Luckeydoo endorsed the book, which I mention only because he's your 2026 Corey Carlisle recipient. Teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr"/>
@@ -3310,11 +3310,11 @@
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="n">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>Sandhya — Literary Safari builds media that respects kids, which was the bar I aimed at. Mine gives a six-year-old a real financial decision with a real tradeoff and lets him make it himself. I'd take your read on positioning. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sandhya — Literary Safari builds media that respects kids, which was the bar I aimed at. Mine gives a six-year-old a real financial decision with a real tradeoff and lets him make it himself. I'd take your read on positioning. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr"/>
@@ -3348,11 +3348,11 @@
       <c r="G60" s="5" t="inlineStr"/>
       <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>Dr. Martin-Knox — a superintendent who's a lifelong learner is the read I hoped for. Mine is K-5 with free standards-aligned lessons, and elementary is where financial literacy gets politely skipped. Where would it fit in your district? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Martin-Knox — a superintendent who's a lifelong learner is the read I hoped for. Mine is K-5 with free standards-aligned lessons, and elementary is where financial literacy gets politely skipped. Where would it fit in your district? Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr"/>
@@ -3386,11 +3386,11 @@
       <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="n">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Dr. McCoy — you've stabilized whole systems, so you know which resources survive contact with an actual building. I wrote a picture book with zero-prep lessons and nothing to reorder. Does it hold up at K-12 scale, or is it too small to matter? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. McCoy — you've stabilized whole systems, so you know which resources survive contact with an actual building. I wrote a picture book with zero-prep lessons and nothing to reorder. Does it hold up at K-12 scale, or is it too small to matter? Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr"/>
@@ -3424,11 +3424,11 @@
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="n">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Denise — financial literacy politely skips K-5 and turns up in ninth grade acting surprised. Mine doesn't. 36 pages, four zero-prep lessons, a 23-row crosswalk you can check rather than take on faith, and a K-5 teacher with 30+ years who told me what to cut. Clear your bar? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Denise — financial literacy politely skips K-5 and turns up in ninth grade acting surprised. Mine doesn't. 36 pages, four zero-prep lessons, a 23-row crosswalk you can check rather than take on faith, and a K-5 teacher with 30+ years who told me what to cut. Clear your bar? Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr"/>
@@ -3462,11 +3462,11 @@
       <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr"/>
       <c r="I63" s="5" t="n">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Sarai — a Spanish immersion magnet raises a question I should ask outright: the book is English-only, though the free companion activities have a Spanish toggle. Does that limit it too much for your classrooms, or does it still work? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sarai — a Spanish immersion magnet raises a question I should ask outright: the book is English-only, though the free companion activities have a Spanish toggle. Does that limit it too much for your classrooms, or does it still work? Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr"/>
@@ -3500,11 +3500,11 @@
       <c r="G64" s="5" t="inlineStr"/>
       <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="n">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>Richard — 4MQ builds financial literacy frameworks for early childhood, which is the band almost nobody serves. Mine is a K-5 picture book plus free toolkit against five frameworks. Does the approach fit what you're building, or duplicate it? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Richard — 4MQ builds financial literacy frameworks for early childhood, which is the band almost nobody serves. Mine is a K-5 picture book plus free teacher pack against five frameworks. Does the approach fit what you're building, or duplicate it? Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr"/>
@@ -3538,11 +3538,11 @@
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="n">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>David — a senior curriculum designer can tell in five minutes whether something was built to teach or built to look like it was. Mine has four zero-prep lessons, assessments, and a 23-row crosswalk, all written alongside the book rather than bolted on afterward. Does the design hold? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>David — a senior curriculum designer can tell in five minutes whether something was built to teach or built to look like it was. Mine has four zero-prep lessons, assessments, and a 23-row crosswalk, all written alongside the book rather than bolted on afterward. Does the design hold? Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr"/>
@@ -3576,11 +3576,11 @@
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="n">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Kevin — a CEE Master Teacher running LifeFinanceEd is the read I want most. My K-5 book aligns to CEE, Jump$tart, Common Core, and FDIC Money Smart, and it is a spending book, not a saving one. Does that framing hold up against how you actually teach it? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kevin — a CEE Master Teacher running LifeFinanceEd is the read I want most. My K-5 book aligns to CEE, Jump$tart, Common Core, and FDIC Money Smart, and it is a spending book, not a saving one. Does that framing hold up against how you actually teach it? For teachers: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr"/>
@@ -3614,11 +3614,11 @@
       <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="n">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>Gina — brand and comms at Jump$tart means you see every resource that wants a logo near it. Mine wants a listing, not a logo. K-5 toolkit against the National Standards, completely free. Anything you need to see beyond the crosswalk before something gets listed? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Gina — brand and comms at Jump$tart means you see every resource that wants a logo near it. Mine wants a listing, not a logo. K-5 teacher materials against the National Standards, completely free. Anything you need to see beyond the crosswalk before something gets listed? The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr"/>
@@ -3652,11 +3652,11 @@
       <c r="G68" s="5" t="inlineStr"/>
       <c r="H68" s="5" t="inlineStr"/>
       <c r="I68" s="5" t="n">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>Ryan — a partnerships question. My K-5 book plus free toolkit sits below NGPF's grade band, which probably makes it complementary rather than competitive. Is elementary something you partner around, or strictly out of scope? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ryan — a partnerships question. My K-5 book plus free classroom materials sits below NGPF's grade band, which probably makes it complementary rather than competitive. Is elementary something you partner around, or strictly out of scope? Print it here: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr"/>
@@ -3690,11 +3690,11 @@
       <c r="G69" s="5" t="inlineStr"/>
       <c r="H69" s="5" t="inlineStr"/>
       <c r="I69" s="5" t="n">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>Michael — you decide what programming actually reaches people. Mine is K-5, teaching the complete purchase, sales tax included, with free zero-prep lessons behind it. Elementary is usually the thinnest shelf in the building. Fit your programming? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Michael — you decide what programming actually reaches people. Mine is K-5, teaching the complete purchase, sales tax included, with free zero-prep lessons behind it. Elementary is usually the thinnest shelf in the building. Fit your programming? Teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr"/>
@@ -3728,11 +3728,11 @@
       <c r="G70" s="5" t="inlineStr"/>
       <c r="H70" s="5" t="inlineStr"/>
       <c r="I70" s="5" t="n">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>Hello — a Utah Jump$tart question. My K-5 book and free toolkit are built against the National Standards with a crosswalk. Elementary is usually where state coalitions have the least to hand a teacher. Is there a route to be listed or shared with your network? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hello — a Utah Jump$tart question. My K-5 book and free teacher pack are built against the National Standards with a crosswalk. Elementary is usually where state coalitions have the least to hand a teacher. Is there a route to be listed or shared with your network? Teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr"/>
@@ -3766,11 +3766,11 @@
       <c r="G71" s="5" t="inlineStr"/>
       <c r="H71" s="5" t="inlineStr"/>
       <c r="I71" s="5" t="n">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>Lorne — you back programs that reach kids at scale. Mine is a K-5 picture book teaching spending rather than saving, with a free zero-prep toolkit behind it. Fit anything JumpStart Inc. runs or funds? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Lorne — you back programs that reach kids at scale. Mine is a K-5 picture book teaching spending rather than saving, with a free zero-prep classroom pack behind it. Fit anything JumpStart Inc. runs or funds? Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr"/>
@@ -3804,11 +3804,11 @@
       <c r="G72" s="5" t="inlineStr"/>
       <c r="H72" s="5" t="inlineStr"/>
       <c r="I72" s="5" t="n">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>Ruth — a self-described cheerleader for personal finance education is exactly who I want reading this. My K-5 book comes with free ungated content: four lessons, assessments, a 23-row crosswalk. Any of it fit your educational content? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ruth — a self-described cheerleader for personal finance education is exactly who I want reading this. My K-5 book comes with free ungated content: four lessons, assessments, a 23-row crosswalk. Any of it fit your educational content? For teachers: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr"/>
@@ -3842,11 +3842,11 @@
       <c r="G73" s="5" t="inlineStr"/>
       <c r="H73" s="5" t="inlineStr"/>
       <c r="I73" s="5" t="n">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>Samantha — as Maine Jump$tart VP you know exactly how thin the elementary shelf is. Mine is K-5 against the National Standards with a free toolkit. Route into what Maine Jump$tart shares with teachers? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Samantha — as Maine Jump$tart VP you know exactly how thin the elementary shelf is. Mine is K-5 against the National Standards with a free teacher materials. Route into what Maine Jump$tart shares with teachers? The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr"/>
@@ -3880,11 +3880,11 @@
       <c r="G74" s="5" t="inlineStr"/>
       <c r="H74" s="5" t="inlineStr"/>
       <c r="I74" s="5" t="n">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>Eva — I'm trying to find the right person at the Bureau to ask whether the Money as You Grow Bookshelf still adds titles. Mine is a K-5 picture book teaching spending rather than saving. Can you point me? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Eva — I'm trying to find the right person at the Bureau to ask whether the Money as You Grow Bookshelf still adds titles. Mine is a K-5 picture book teaching spending rather than saving. Can you point me? Print it here: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr"/>
@@ -3918,11 +3918,11 @@
       <c r="G75" s="5" t="inlineStr"/>
       <c r="H75" s="5" t="inlineStr"/>
       <c r="I75" s="5" t="n">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>Jesse — the Treasurer's outreach reaches families directly, which is where a read-along does its best work. Mine teaches spending through one purchase, and the free family activity was built for a kitchen table rather than a classroom. Fit for a Washington program? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jesse — the Treasurer's outreach reaches families directly, which is where a read-along does its best work. Mine teaches spending through one purchase, and the free family activity was built for a kitchen table rather than a classroom. Fit for a Washington program? Teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr"/>
@@ -3956,11 +3956,11 @@
       <c r="G76" s="5" t="inlineStr"/>
       <c r="H76" s="5" t="inlineStr"/>
       <c r="I76" s="5" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>Andrea — you lead digital products for social impact, so you'll know whether a printed picture book is an asset or a liability in 2026. Mine teaches K-5 spending with free digital lessons behind it. Would you tell me straight? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Andrea — you lead digital products for social impact, so you'll know whether a printed picture book is an asset or a liability in 2026. Mine teaches K-5 spending with free digital lessons behind it. Would you tell me straight? Teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K76" s="5" t="inlineStr"/>
@@ -3994,11 +3994,11 @@
       <c r="G77" s="5" t="inlineStr"/>
       <c r="H77" s="5" t="inlineStr"/>
       <c r="I77" s="5" t="n">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>Sandra — my K-5 book and free toolkit are aligned to Money Smart for Young People, crosswalk included. Is there a route for outside materials to sit alongside Money Smart, or is that closed by policy? Either answer is useful. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sandra — my K-5 book and free classroom pack are aligned to Money Smart for Young People, crosswalk included. Is there a route for outside materials to sit alongside Money Smart, or is that closed by policy? Either answer is useful. Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr"/>
@@ -4032,11 +4032,11 @@
       <c r="G78" s="5" t="inlineStr"/>
       <c r="H78" s="5" t="inlineStr"/>
       <c r="I78" s="5" t="n">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>Christian — teacher success is the whole ballgame, and elementary teachers have close to nothing for financial literacy. I built a free K-5 toolkit around a picture book: four lessons, assessments, a crosswalk, zero prep. Would NGPF ever surface something below ninth grade? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Christian — teacher success is the whole ballgame, and elementary teachers have close to nothing for financial literacy. I built a free K-5 lesson set around a picture book: four lessons, assessments, a crosswalk, zero prep. Would NGPF ever surface something below ninth grade? For teachers: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K78" s="5" t="inlineStr"/>
@@ -4070,11 +4070,11 @@
       <c r="G79" s="5" t="inlineStr"/>
       <c r="H79" s="5" t="inlineStr"/>
       <c r="I79" s="5" t="n">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>Hello — my K-5 book and free ungated toolkit align to the Jump$tart National Standards, crosswalk included. Elementary tends to be the thinnest band for coalition resources. Submission route for Florida's network? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hello — my K-5 book and free ungated teacher materials align to the Jump$tart National Standards, crosswalk included. Elementary tends to be the thinnest band for coalition resources. Submission route for Florida's network? The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K79" s="5" t="inlineStr"/>
@@ -4108,11 +4108,11 @@
       <c r="G80" s="5" t="inlineStr"/>
       <c r="H80" s="5" t="inlineStr"/>
       <c r="I80" s="5" t="n">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>Dan — as state president you back programs that reach whole communities. Mine is a K-5 picture book with a free toolkit against five frameworks, teaching kids the complete purchase. Fit with what your organization funds or distributes? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dan — as state president you back programs that reach whole communities. Mine is a K-5 picture book with a free classroom materials against five frameworks, teaching kids the complete purchase. Fit with what your organization funds or distributes? Print it here: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K80" s="5" t="inlineStr"/>
@@ -4146,11 +4146,11 @@
       <c r="G81" s="5" t="inlineStr"/>
       <c r="H81" s="5" t="inlineStr"/>
       <c r="I81" s="5" t="n">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>Aaron — a partnerships question. My K-5 book plus free toolkit fills the elementary gap most financial-literacy programs leave wide open, since almost everything is built for high school. Is early elementary something you partner around? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Aaron — a partnerships question. My K-5 book plus free teaching pack fills the elementary gap most financial-literacy programs leave wide open, since almost everything is built for high school. Is early elementary something you partner around? Teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K81" s="5" t="inlineStr"/>
@@ -4188,11 +4188,11 @@
       </c>
       <c r="H82" s="5" t="inlineStr"/>
       <c r="I82" s="5" t="n">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>Variny — you decide what's worth putting in front of a partner network. Mine is K-5 with a free ungated toolkit against five frameworks. Elementary is the band most partners have nothing for. Worth a look? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Variny — you decide what's worth putting in front of a partner network. Mine is K-5 with a free ungated teacher pack against five frameworks. Elementary is the band most partners have nothing for. Worth a look? Teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K82" s="5" t="inlineStr">
@@ -4241,11 +4241,11 @@
       <c r="G83" s="5" t="inlineStr"/>
       <c r="H83" s="5" t="inlineStr"/>
       <c r="I83" s="5" t="n">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t>Meghan — a grants question rather than a pitch. My K-5 book has a free toolkit and a grant-ready packet with the math already done: 25 copies, $499.75. Is early elementary financial literacy something your grants program funds? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Meghan — a grants question rather than a pitch. My K-5 book has a free classroom pack and a grant-ready packet with the math already done: 25 copies, $499.75. Is early elementary financial literacy something your grants program funds? Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K83" s="5" t="inlineStr"/>
@@ -4279,11 +4279,11 @@
       <c r="G84" s="5" t="inlineStr"/>
       <c r="H84" s="5" t="inlineStr"/>
       <c r="I84" s="5" t="n">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>Joshua — research and evaluation is exactly where my premise should get tested. I argue spending competence precedes saving competence developmentally. Does that survive scrutiny, or is there literature I've conveniently ignored? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Joshua — research and evaluation is exactly where my premise should get tested. I argue spending competence precedes saving competence developmentally. Does that survive scrutiny, or is there literature I've conveniently ignored? For teachers: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K84" s="5" t="inlineStr"/>
@@ -4317,11 +4317,11 @@
       <c r="G85" s="5" t="inlineStr"/>
       <c r="H85" s="5" t="inlineStr"/>
       <c r="I85" s="5" t="n">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
-          <t>Syeda — a CRCM sees the CRA angle immediately. My K-5 book has a grant-ready packet with cost math already done, which makes it easy for a bank to fund locally and report. Something your board would consider? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Syeda — a CRCM sees the CRA angle immediately. My K-5 book has a grant-ready packet with cost math already done, which makes it easy for a bank to fund locally and report. Something your board would consider? The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K85" s="5" t="inlineStr"/>
@@ -4355,11 +4355,11 @@
       <c r="G86" s="5" t="inlineStr"/>
       <c r="H86" s="5" t="inlineStr"/>
       <c r="I86" s="5" t="n">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>Christopher — as chief program officer you decide what reaches learners. Mine is K-5, teaching the complete purchase, sales tax included, with free zero-prep lessons. Elementary is usually the thinnest part of any program. Fit? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Christopher — as chief program officer you decide what reaches learners. Mine is K-5, teaching the complete purchase, sales tax included, with free zero-prep lessons. Elementary is usually the thinnest part of any program. Fit? Print it here: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K86" s="5" t="inlineStr"/>
@@ -4393,11 +4393,11 @@
       <c r="G87" s="5" t="inlineStr"/>
       <c r="H87" s="5" t="inlineStr"/>
       <c r="I87" s="5" t="n">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="J87" s="5" t="inlineStr">
         <is>
-          <t>John — as a financial education administrator you decide what actually gets used. Mine is K-5 plus a free zero-prep toolkit against five frameworks. Elementary is usually the gap. Fit your programs? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>John — as a financial education administrator you decide what actually gets used. Mine is K-5 plus a free zero-prep teaching pack against five frameworks. Elementary is usually the gap. Fit your programs? Teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K87" s="5" t="inlineStr"/>
@@ -4431,11 +4431,11 @@
       <c r="G88" s="5" t="inlineStr"/>
       <c r="H88" s="5" t="inlineStr"/>
       <c r="I88" s="5" t="n">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t>Jason — a board-level question. Elementary financial literacy is the least funded band and the one the research says matters most, which is an odd combination. I built a K-5 book and free toolkit for it. Something your board would want to see? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jason — a board-level question. Elementary financial literacy is the least funded band and the one the research says matters most, which is an odd combination. I built a K-5 book and free teacher pack for it. Something your board would want to see? Teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K88" s="5" t="inlineStr"/>
@@ -5343,11 +5343,11 @@
       <c r="G112" s="5" t="inlineStr"/>
       <c r="H112" s="5" t="inlineStr"/>
       <c r="I112" s="5" t="n">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>Ronald — you built a financial literacy curriculum, so you know what teachers actually pick up versus what they politely accept. It's a 36-page picture book with four zero-prep lessons, aimed at K-5 where most curricula don't reach. Complement Responsible Money, or compete with it? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ronald — you built a financial literacy curriculum, so you know what teachers actually pick up versus what they politely accept. It's a 36-page picture book with four zero-prep lessons, aimed at K-5 where most curricula don't reach. Complement Responsible Money, or compete with it? Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr"/>
@@ -5381,11 +5381,11 @@
       <c r="G113" s="5" t="inlineStr"/>
       <c r="H113" s="5" t="inlineStr"/>
       <c r="I113" s="5" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>Dr. Branch — principal, author, and coach means you see the whole building at once. Mine teaches spending through a story, with free standards-aligned lessons behind it. Would it work at Robert F. Smith STEAM Academy, and where would you slot it? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Branch — principal, author, and coach means you see the whole building at once. Mine teaches spending through a story, with free standards-aligned lessons behind it. Would it work at Robert F. Smith STEAM Academy, and where would you slot it? Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K113" s="5" t="inlineStr"/>
@@ -5533,11 +5533,11 @@
       <c r="G117" s="5" t="inlineStr"/>
       <c r="H117" s="5" t="inlineStr"/>
       <c r="I117" s="5" t="n">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>Cash — you're building youth financial literacy from the ground up, so we're after the same kid. I made a picture book plus free zero-prep toolkit for K-5, the band almost nobody serves. Fit anything you're building? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Cash — you're building youth financial literacy from the ground up, so we're after the same kid. I made a picture book plus free zero-prep teacher materials for K-5, the band almost nobody serves. Fit anything you're building? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr"/>
@@ -6255,11 +6255,11 @@
       <c r="G136" s="5" t="inlineStr"/>
       <c r="H136" s="5" t="inlineStr"/>
       <c r="I136" s="5" t="n">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>John — you build learning that scales globally. Mine is K-5 with a free zero-prep toolkit against five frameworks. Does the approach fit what Electus builds, or duplicate it? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>John — you build learning that scales globally. Mine is K-5 with a free zero-prep classroom materials against five frameworks. Does the approach fit what Electus builds, or duplicate it? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K136" s="5" t="inlineStr"/>
@@ -7623,11 +7623,11 @@
       <c r="G172" s="5" t="inlineStr"/>
       <c r="H172" s="5" t="inlineStr"/>
       <c r="I172" s="5" t="n">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="J172" s="5" t="inlineStr">
         <is>
-          <t>Sue — you wrote the handbook. Mine is a 36-page full-color picture book with a free educator toolkit and no Amazon listing, by choice. Brave or dumb? I'd genuinely rather have the straight answer than the polite one. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sue — you wrote the handbook. Mine is a 36-page full-color picture book with a free teaching pack and no Amazon listing, by choice. Brave or dumb? I'd genuinely rather have the straight answer than the polite one. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K172" s="5" t="inlineStr"/>
@@ -9497,11 +9497,11 @@
       <c r="G220" s="5" t="inlineStr"/>
       <c r="H220" s="5" t="inlineStr"/>
       <c r="I220" s="5" t="n">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="J220" s="5" t="inlineStr">
         <is>
-          <t>Andrea — as a research director you'll want the claim before the book. Mine: consumer transaction competence is taught almost nowhere in K-5. I built a picture book and free toolkit around it. Evidence against? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Andrea — as a research director you'll want the claim before the book. Mine: consumer transaction competence is taught almost nowhere in K-5. I built a picture book and free teacher pack around it. Evidence against? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K220" s="5" t="inlineStr">
@@ -9509,7 +9509,7 @@
           <t>Dr. Sticha — you sit on the Jump$tart board for the Stanford Initiative on Financial Decision-Making, and your research is household financial literacy and wellbeing. So this is a research question with a book attached, rather than the reverse.
 Here is what I ran into. Almost every children's financial literacy book teaches saving. I read the entire ABA Foundation list to be sure. Piggy banks, jars, lemonade stands, wait for it.
 But no seven-year-old has a savings rate. Every seven-year-old has stood in a store holding money and had to choose. The first financial decision a person ever makes is a purchase, and the literature written for them starts one step later.
-I wrote the K-5 book for that step. Thirty-six pages, grades 1-5. A boy earns a robot, reads the sale ads, compares two models on a shelf, takes the marked-down one on purpose, redeems a coupon at the register, and meets sales tax. Sixteen-plus concepts, a 21-term glossary, and a free ungated teacher toolkit crosswalked to the National Standards for Personal Financial Education.
+I wrote the K-5 book for that step. Thirty-six pages, grades 1-5. A boy earns a robot, reads the sale ads, compares two models on a shelf, takes the marked-down one on purpose, redeems a coupon at the register, and meets sales tax. Sixteen-plus concepts, a 21-term glossary, and a free ungated teacher lesson set crosswalked to the National Standards for Personal Financial Education.
 The question I'd actually like answered: is there research on financial decision-making in the first five school years, or does the evidence base start in adolescence the same way the books do? If it starts late, that's a finding, and it's one your initiative is better placed to say out loud than I am.
 Jonathan Bach
 Baltimore
@@ -9931,11 +9931,11 @@
       <c r="G231" s="5" t="inlineStr"/>
       <c r="H231" s="5" t="inlineStr"/>
       <c r="I231" s="5" t="n">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="J231" s="5" t="inlineStr">
         <is>
-          <t>Maria — Tennessee's council decides what reaches classrooms. Mine is K-5 plus a free zero-prep toolkit against five frameworks. Elementary is where most states have the least. Route in? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Maria — Tennessee's council decides what reaches classrooms. Mine is K-5 plus a free zero-prep classroom pack against five frameworks. Elementary is where most states have the least. Route in? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K231" s="5" t="inlineStr"/>
@@ -10539,11 +10539,11 @@
       <c r="G247" s="5" t="inlineStr"/>
       <c r="H247" s="5" t="inlineStr"/>
       <c r="I247" s="5" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="J247" s="5" t="inlineStr">
         <is>
-          <t>Cherry — you run one of the few credit union financial education programs that isn't a poster and a pencil. Mine is K-5 with the whole toolkit free, plus a grant packet with the math already done: 25 copies, $499.75, sponsor logo optional. Built so somebody in your seat doesn't have to build the case from scratch. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Cherry — you run one of the few credit union financial education programs that isn't a poster and a pencil. Mine is K-5 with the whole lesson set free, plus a grant packet with the math already done: 25 copies, $499.75, sponsor logo optional. Built so somebody in your seat doesn't have to build the case from scratch. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K247" s="5" t="inlineStr"/>
@@ -10691,11 +10691,11 @@
       <c r="G251" s="5" t="inlineStr"/>
       <c r="H251" s="5" t="inlineStr"/>
       <c r="I251" s="5" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="J251" s="5" t="inlineStr">
         <is>
-          <t>Brittney — SchoolsFirst puts you in front of educators constantly, which is the audience for the free toolkit as much as the book. Four lessons, assessments, a crosswalk, all ungated. Fit a member program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Brittney — SchoolsFirst puts you in front of educators constantly, which is the audience for the free teacher materials as much as the book. Four lessons, assessments, a crosswalk, all ungated. Fit a member program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K251" s="5" t="inlineStr"/>
@@ -10805,11 +10805,11 @@
       <c r="G254" s="5" t="inlineStr"/>
       <c r="H254" s="5" t="inlineStr"/>
       <c r="I254" s="5" t="n">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="J254" s="5" t="inlineStr">
         <is>
-          <t>Kenda — you've said financial literacy should be offered to everyone, and elementary is usually where that promise breaks without anyone saying so. Mine is K-5 with a free ungated toolkit. Fit a program you run? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kenda — you've said financial literacy should be offered to everyone, and elementary is usually where that promise breaks without anyone saying so. Mine is K-5 with a free ungated classroom materials. Fit a program you run? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K254" s="5" t="inlineStr"/>
@@ -11071,11 +11071,11 @@
       <c r="G261" s="5" t="inlineStr"/>
       <c r="H261" s="5" t="inlineStr"/>
       <c r="I261" s="5" t="n">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="J261" s="5" t="inlineStr">
         <is>
-          <t>Seema — the St. Louis Fed connects national research to local programs, which is where a K-5 resource fits. Mine runs 36 pages plus free toolkit against five frameworks. Fit a Louisville branch program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Seema — the St. Louis Fed connects national research to local programs, which is where a K-5 resource fits. Mine runs 36 pages plus free teaching pack against five frameworks. Fit a Louisville branch program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K261" s="5" t="inlineStr"/>
@@ -11109,11 +11109,11 @@
       <c r="G262" s="5" t="inlineStr"/>
       <c r="H262" s="5" t="inlineStr"/>
       <c r="I262" s="5" t="n">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="J262" s="5" t="inlineStr">
         <is>
-          <t>Alfredo — financial inclusion meets families where the gaps are widest, and elementary is where almost nothing exists. Mine is K-5 plus a free toolkit. Fit a member or community program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Alfredo — financial inclusion meets families where the gaps are widest, and elementary is where almost nothing exists. Mine is K-5 plus a free teacher pack. Fit a member or community program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K262" s="5" t="inlineStr"/>
@@ -11185,11 +11185,11 @@
       <c r="G264" s="5" t="inlineStr"/>
       <c r="H264" s="5" t="inlineStr"/>
       <c r="I264" s="5" t="n">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="J264" s="5" t="inlineStr">
         <is>
-          <t>Juli — community engagement at a credit union usually means finding programs that scale cheaply. Mine is a book plus a completely free toolkit, so the only line item is the copies. Fit USF's work? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Juli — community engagement at a credit union usually means finding programs that scale cheaply. Mine is a book plus a completely free classroom pack, so the only line item is the copies. Fit USF's work? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K264" s="5" t="inlineStr"/>
@@ -11261,11 +11261,11 @@
       <c r="G266" s="5" t="inlineStr"/>
       <c r="H266" s="5" t="inlineStr"/>
       <c r="I266" s="5" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J266" s="5" t="inlineStr">
         <is>
-          <t>Mark — Salus works with credit unions and community banks, which are exactly the institutions that fund K-5 financial literacy locally. Mine is a book plus free toolkit with a grant packet attached. Worth knowing about? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Mark — Salus works with credit unions and community banks, which are exactly the institutions that fund K-5 financial literacy locally. Mine is a book plus free lesson set with a grant packet attached. Worth knowing about? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K266" s="5" t="inlineStr"/>
@@ -11451,11 +11451,11 @@
       <c r="G271" s="5" t="inlineStr"/>
       <c r="H271" s="5" t="inlineStr"/>
       <c r="I271" s="5" t="n">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="J271" s="5" t="inlineStr">
         <is>
-          <t>Kristi — directing financial literacy means choosing what actually reaches people. Mine is K-5, which is usually the band with nothing at all. Picture book plus free ungated toolkit. Worth a look? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kristi — directing financial literacy means choosing what actually reaches people. Mine is K-5, which is usually the band with nothing at all. Picture book plus free ungated teacher materials. Worth a look? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K271" s="5" t="inlineStr"/>
@@ -11565,11 +11565,11 @@
       <c r="G274" s="5" t="inlineStr"/>
       <c r="H274" s="5" t="inlineStr"/>
       <c r="I274" s="5" t="n">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="J274" s="5" t="inlineStr">
         <is>
-          <t>Salman — national program integration is exactly the scale where K-5 gets forgotten. Mine runs 36 pages plus free ungated toolkit against five frameworks. Fit your integration work? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Salman — national program integration is exactly the scale where K-5 gets forgotten. Mine runs 36 pages plus free ungated classroom materials against five frameworks. Fit your integration work? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K274" s="5" t="inlineStr"/>
@@ -11641,11 +11641,11 @@
       <c r="G276" s="5" t="inlineStr"/>
       <c r="H276" s="5" t="inlineStr"/>
       <c r="I276" s="5" t="n">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="J276" s="5" t="inlineStr">
         <is>
-          <t>Melissa — a curriculum specialist in an elementary school is exactly the read I want. I wrote a picture book with zero-prep lessons against five frameworks. Would it work in Lanier's classrooms? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Melissa — a curriculum specialist in an elementary school is exactly the read I want. I wrote a picture book with zero-prep lessons against five frameworks. Would it work in Lanier's classrooms? Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K276" s="5" t="inlineStr"/>
@@ -11679,11 +11679,11 @@
       <c r="G277" s="5" t="inlineStr"/>
       <c r="H277" s="5" t="inlineStr"/>
       <c r="I277" s="5" t="n">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="J277" s="5" t="inlineStr">
         <is>
-          <t>Samantha — reading intervention plus SEL is an unusual pairing and useful here: mine is AD 620L, and the money decision doubles as an impulse-control lesson. Fit either side of your work? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Samantha — reading intervention plus SEL is an unusual pairing and useful here: mine is AD 620L, and the money decision doubles as an impulse-control lesson. Fit either side of your work? Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K277" s="5" t="inlineStr"/>
@@ -11717,11 +11717,11 @@
       <c r="G278" s="5" t="inlineStr"/>
       <c r="H278" s="5" t="inlineStr"/>
       <c r="I278" s="5" t="n">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="J278" s="5" t="inlineStr">
         <is>
-          <t>Suzanne — early childhood and school readiness is the exact window. Mine starts where a kid actually starts with money, which is spending it. One trip, one real decision, no worksheet anywhere. Fit an early-grades classroom in Stockton? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Suzanne — early childhood and school readiness is the exact window. Mine starts where a kid actually starts with money, which is spending it. One trip, one real decision, no worksheet anywhere. Fit an early-grades classroom in Stockton? Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K278" s="5" t="inlineStr"/>
@@ -11747,11 +11747,11 @@
       <c r="G279" s="5" t="inlineStr"/>
       <c r="H279" s="5" t="inlineStr"/>
       <c r="I279" s="5" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J279" s="5" t="inlineStr">
         <is>
-          <t>Jacquelyn — a principal who has run early childhood has seen every reading level in the building. Mine is a 36-page read-aloud at AD 620L teaching money through one shopping trip. Would it work in your school? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jacquelyn — a principal who has run early childhood has seen every reading level in the building. Mine is a 36-page read-aloud at AD 620L teaching money through one shopping trip. Would it work in your school? Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K279" s="5" t="inlineStr"/>
@@ -11823,11 +11823,11 @@
       <c r="G281" s="5" t="inlineStr"/>
       <c r="H281" s="5" t="inlineStr"/>
       <c r="I281" s="5" t="n">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="J281" s="5" t="inlineStr">
         <is>
-          <t>Jake — DCPS classrooms tell you fast whether something works. Mine is K-5, teaching spending, with four zero-prep standards-aligned lessons. Elementary is usually where financial literacy gets skipped entirely. Where would it fit? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jake — DCPS classrooms tell you fast whether something works. Mine is K-5, teaching spending, with four zero-prep standards-aligned lessons. Elementary is usually where financial literacy gets skipped entirely. Where would it fit? Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K281" s="5" t="inlineStr"/>
@@ -11861,11 +11861,11 @@
       <c r="G282" s="5" t="inlineStr"/>
       <c r="H282" s="5" t="inlineStr"/>
       <c r="I282" s="5" t="n">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="J282" s="5" t="inlineStr">
         <is>
-          <t>Shawn — congratulations on the superintendency. As you set priorities: elementary financial literacy is the gap nobody gets assigned. I made a picture book plus free toolkit for K-5. Early grades or family programming — or not a priority this year? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Shawn — congratulations on the superintendency. As you set priorities: elementary financial literacy is the gap nobody gets assigned. I made a picture book plus free classroom materials for K-5. Early grades or family programming — or not a priority this year? Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K282" s="5" t="inlineStr"/>
@@ -11899,11 +11899,11 @@
       <c r="G283" s="5" t="inlineStr"/>
       <c r="H283" s="5" t="inlineStr"/>
       <c r="I283" s="5" t="n">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="J283" s="5" t="inlineStr">
         <is>
-          <t>Dr. Pinder — a superintendent's read matters most on placement rather than merit. Mine is K-5, teaching spending through a story, free standards-aligned lessons. Classroom, library, or family night. Where would you put it? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Pinder — a superintendent's read matters most on placement rather than merit. Mine is K-5, teaching spending through a story, free standards-aligned lessons. Classroom, library, or family night. Where would you put it? Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K283" s="5" t="inlineStr"/>
@@ -11937,11 +11937,11 @@
       <c r="G284" s="5" t="inlineStr"/>
       <c r="H284" s="5" t="inlineStr"/>
       <c r="I284" s="5" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="J284" s="5" t="inlineStr">
         <is>
-          <t>Mallory — assistant principal, adjunct, and speaker means you've taught every audience there is. Mine is K-5, and a six-year-old makes one real money decision and gets it right. Does it land in an elementary classroom? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Mallory — assistant principal, adjunct, and speaker means you've taught every audience there is. Mine is K-5, and a six-year-old makes one real money decision and gets it right. Does it land in an elementary classroom? Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K284" s="5" t="inlineStr"/>
@@ -11975,11 +11975,11 @@
       <c r="G285" s="5" t="inlineStr"/>
       <c r="H285" s="5" t="inlineStr"/>
       <c r="I285" s="5" t="n">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="J285" s="5" t="inlineStr">
         <is>
-          <t>Angela — as head of school you set what students read. Mine is a 36-page picture book teaching money through a story, with free standards-aligned lessons. Would it earn a place in your school? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Angela — as head of school you set what students read. Mine is a 36-page picture book teaching money through a story, with free standards-aligned lessons. Would it earn a place in your school? Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K285" s="5" t="inlineStr"/>
@@ -12013,11 +12013,11 @@
       <c r="G286" s="5" t="inlineStr"/>
       <c r="H286" s="5" t="inlineStr"/>
       <c r="I286" s="5" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="J286" s="5" t="inlineStr">
         <is>
-          <t>Kristen — as a director of education you decide what reaches learners. Mine skips saving and teaches spending, with four zero-prep lessons. Elementary is usually the thinnest shelf. Fit your programs? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kristen — as a director of education you decide what reaches learners. Mine skips saving and teaches spending, with four zero-prep lessons. Elementary is usually the thinnest shelf. Fit your programs? Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K286" s="5" t="inlineStr"/>
@@ -12051,11 +12051,11 @@
       <c r="G287" s="5" t="inlineStr"/>
       <c r="H287" s="5" t="inlineStr"/>
       <c r="I287" s="5" t="n">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="J287" s="5" t="inlineStr">
         <is>
-          <t>Sarah — curriculum and instruction is where a book like this lives or dies. Mine has a 23-row crosswalk and four 45-minute lessons written alongside the book rather than added after. Would you look at whether that claim holds? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sarah — curriculum and instruction is where a book like this lives or dies. Mine has a 23-row crosswalk and four 45-minute lessons written alongside the book rather than added after. Would you look at whether that claim holds? Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K287" s="5" t="inlineStr"/>
@@ -12089,11 +12089,11 @@
       <c r="G288" s="5" t="inlineStr"/>
       <c r="H288" s="5" t="inlineStr"/>
       <c r="I288" s="5" t="n">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="J288" s="5" t="inlineStr">
         <is>
-          <t>Malori — you lead financial literacy curriculum and build educational games, so engagement is your bar, not mine. Mine holds a six-year-old through 36 pages because it's a story first. Fit your curriculum? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Malori — you lead financial literacy curriculum and build educational games, so engagement is your bar, not mine. Mine holds a six-year-old through 36 pages because it's a story first. Fit your curriculum? Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K288" s="5" t="inlineStr"/>
@@ -12127,11 +12127,11 @@
       <c r="G289" s="5" t="inlineStr"/>
       <c r="H289" s="5" t="inlineStr"/>
       <c r="I289" s="5" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="J289" s="5" t="inlineStr">
         <is>
-          <t>Michael — education and outreach at Troutwood aims at making the future tangible. Mine makes the present tangible for a six-year-old: one purchase, compared and paid for, tax included. Fit your outreach? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Michael — education and outreach at Troutwood aims at making the future tangible. Mine makes the present tangible for a six-year-old: one purchase, compared and paid for, tax included. Fit your outreach? Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K289" s="5" t="inlineStr"/>
@@ -12165,11 +12165,11 @@
       <c r="G290" s="5" t="inlineStr"/>
       <c r="H290" s="5" t="inlineStr"/>
       <c r="I290" s="5" t="n">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="J290" s="5" t="inlineStr">
         <is>
-          <t>Peggy — as a consultant and instructional designer you'll see whether the lessons teach or just look like they do. Mine are four 45-minute plans with assessments and a crosswalk. Would you look? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Peggy — as a consultant and instructional designer you'll see whether the lessons teach or just look like they do. Mine are four 45-minute plans with assessments and a crosswalk. Would you look? Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K290" s="5" t="inlineStr"/>
@@ -12203,11 +12203,11 @@
       <c r="G291" s="5" t="inlineStr"/>
       <c r="H291" s="5" t="inlineStr"/>
       <c r="I291" s="5" t="n">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="J291" s="5" t="inlineStr">
         <is>
-          <t>Kim — you built your own financial literacy framework, so you think in systems. Mine is narrow by design: one transaction taught completely rather than a survey of concepts. Does narrow beat broad at K-5? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kim — you built your own financial literacy framework, so you think in systems. Mine is narrow by design: one transaction taught completely rather than a survey of concepts. Does narrow beat broad at K-5? Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K291" s="5" t="inlineStr"/>
@@ -12241,11 +12241,11 @@
       <c r="G292" s="5" t="inlineStr"/>
       <c r="H292" s="5" t="inlineStr"/>
       <c r="I292" s="5" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="J292" s="5" t="inlineStr">
         <is>
-          <t>Peter — on an advisory committee you weigh which resources are worth backing. Mine is K-5 plus a free ungated toolkit against five frameworks. Fit the committee's work? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Peter — on an advisory committee you weigh which resources are worth backing. Mine is K-5 plus a free ungated lesson set against five frameworks. Fit the committee's work? Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K292" s="5" t="inlineStr"/>
@@ -12279,11 +12279,11 @@
       <c r="G293" s="5" t="inlineStr"/>
       <c r="H293" s="5" t="inlineStr"/>
       <c r="I293" s="5" t="n">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="J293" s="5" t="inlineStr">
         <is>
-          <t>Nechama — early childhood consulting means you know what actually holds a young child's attention. Mine is 36 pages where the money lesson never interrupts the plot. Fit the settings you advise? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Nechama — early childhood consulting means you know what actually holds a young child's attention. Mine is 36 pages where the money lesson never interrupts the plot. Fit the settings you advise? Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K293" s="5" t="inlineStr"/>
@@ -12317,11 +12317,11 @@
       <c r="G294" s="5" t="inlineStr"/>
       <c r="H294" s="5" t="inlineStr"/>
       <c r="I294" s="5" t="n">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="J294" s="5" t="inlineStr">
         <is>
-          <t>Amy-Marie — head of early childhood is the reader I hoped for. Mine starts where kids start with money, which is spending it. One trip, one decision, no worksheet. Would it work in your setting? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Amy-Marie — head of early childhood is the reader I hoped for. Mine starts where kids start with money, which is spending it. One trip, one decision, no worksheet. Would it work in your setting? Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K294" s="5" t="inlineStr"/>
@@ -12355,11 +12355,11 @@
       <c r="G295" s="5" t="inlineStr"/>
       <c r="H295" s="5" t="inlineStr"/>
       <c r="I295" s="5" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="J295" s="5" t="inlineStr">
         <is>
-          <t>Cynthia — early childhood programs are the exact window I wrote for. Mine teaches the first money behavior a child performs, which is spending, not saving. Fit Westminster's programs? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Cynthia — early childhood programs are the exact window I wrote for. Mine teaches the first money behavior a child performs, which is spending, not saving. Fit Westminster's programs? Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K295" s="5" t="inlineStr"/>
@@ -12469,11 +12469,11 @@
       <c r="G298" s="5" t="inlineStr"/>
       <c r="H298" s="5" t="inlineStr"/>
       <c r="I298" s="5" t="n">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="J298" s="5" t="inlineStr">
         <is>
-          <t>Dr. Martirano — a superintendent who's also a digital education fellow sees the whole board. Mine is deliberately analog: a printed read-along with free digital lessons behind it. Does that combination still work in Allegany County, or is print a liability now? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Martirano — a superintendent who's also a digital education fellow sees the whole board. Mine is deliberately analog: a printed read-along with free digital lessons behind it. Does that combination still work in Allegany County, or is print a liability now? Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K298" s="5" t="inlineStr"/>
@@ -12507,11 +12507,11 @@
       <c r="G299" s="5" t="inlineStr"/>
       <c r="H299" s="5" t="inlineStr"/>
       <c r="I299" s="5" t="n">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="J299" s="5" t="inlineStr">
         <is>
-          <t>Christopher — Norristown sets what reaches every elementary classroom. Mine teaches the complete purchase, sales tax included, with zero-prep lessons. Classroom, library, or family night? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Christopher — Norristown sets what reaches every elementary classroom. Mine teaches the complete purchase, sales tax included, with zero-prep lessons. Classroom, library, or family night? Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K299" s="5" t="inlineStr"/>
@@ -12545,11 +12545,11 @@
       <c r="G300" s="5" t="inlineStr"/>
       <c r="H300" s="5" t="inlineStr"/>
       <c r="I300" s="5" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="J300" s="5" t="inlineStr">
         <is>
-          <t>Stephanie — a K-8 curriculum leader can tell whether lessons were built alongside a book or afterward. Mine were built alongside: four lessons, assessments, a 23-row crosswalk. Would you test that? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Stephanie — a K-8 curriculum leader can tell whether lessons were built alongside a book or afterward. Mine were built alongside: four lessons, assessments, a 23-row crosswalk. Would you test that? Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K300" s="5" t="inlineStr"/>
@@ -12583,11 +12583,11 @@
       <c r="G301" s="5" t="inlineStr"/>
       <c r="H301" s="5" t="inlineStr"/>
       <c r="I301" s="5" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="J301" s="5" t="inlineStr">
         <is>
-          <t>Mansi — curriculum design and academic coordination is where my materials should get judged. Four zero-prep lessons, a pre/post assessment with answer key, a 23-row crosswalk. Does the design hold up? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Mansi — curriculum design and academic coordination is where my materials should get judged. Four zero-prep lessons, a pre/post assessment with answer key, a 23-row crosswalk. Does the design hold up? Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K301" s="5" t="inlineStr"/>
@@ -12621,11 +12621,11 @@
       <c r="G302" s="5" t="inlineStr"/>
       <c r="H302" s="5" t="inlineStr"/>
       <c r="I302" s="5" t="n">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="J302" s="5" t="inlineStr">
         <is>
-          <t>Nikole — Banzai builds financial literacy for real classrooms, and K-5 is the band with the least of it. It's a 36-page picture book plus free zero-prep lessons against five frameworks. Does the approach fit how you think about it? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Nikole — Banzai builds financial literacy for real classrooms, and K-5 is the band with the least of it. It's a 36-page picture book plus free zero-prep lessons against five frameworks. Does the approach fit how you think about it? Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K302" s="5" t="inlineStr"/>
@@ -12659,11 +12659,11 @@
       <c r="G303" s="5" t="inlineStr"/>
       <c r="H303" s="5" t="inlineStr"/>
       <c r="I303" s="5" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="J303" s="5" t="inlineStr">
         <is>
-          <t>Hema — leading an early childhood school, you set what young kids read. Mine is a read-along that teaches money through story, free lessons behind it. Would it work in your setting? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hema — leading an early childhood school, you set what young kids read. Mine is a read-along that teaches money through story, free lessons behind it. Would it work in your setting? Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K303" s="5" t="inlineStr"/>
@@ -12697,11 +12697,11 @@
       <c r="G304" s="5" t="inlineStr"/>
       <c r="H304" s="5" t="inlineStr"/>
       <c r="I304" s="5" t="n">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="J304" s="5" t="inlineStr">
         <is>
-          <t>Kevin — operations and instruction together means you see what survives implementation rather than what looks good in a pilot. Mine runs 36 pages with nothing to reorder and free lessons. Hold up in a real building? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kevin — operations and instruction together means you see what survives implementation rather than what looks good in a pilot. Mine runs 36 pages with nothing to reorder and free lessons. Hold up in a real building? Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K304" s="5" t="inlineStr"/>
@@ -12735,11 +12735,11 @@
       <c r="G305" s="5" t="inlineStr"/>
       <c r="H305" s="5" t="inlineStr"/>
       <c r="I305" s="5" t="n">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="J305" s="5" t="inlineStr">
         <is>
-          <t>Ashley — an elementary educator who also does curriculum and ed tech sees both sides. Mine is a printed read-aloud with free digital lessons. Would it work in your classroom? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ashley — an elementary educator who also does curriculum and ed tech sees both sides. Mine is a printed read-aloud with free digital lessons. Would it work in your classroom? Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K305" s="5" t="inlineStr"/>
@@ -12773,11 +12773,11 @@
       <c r="G306" s="5" t="inlineStr"/>
       <c r="H306" s="5" t="inlineStr"/>
       <c r="I306" s="5" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J306" s="5" t="inlineStr">
         <is>
-          <t>Bailey — elementary curriculum development is where my materials get judged. Mine were built alongside the book: four zero-prep lessons, assessments, a 23-row crosswalk. Would you look? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Bailey — elementary curriculum development is where my materials get judged. Mine were built alongside the book: four zero-prep lessons, assessments, a 23-row crosswalk. Would you look? Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K306" s="5" t="inlineStr"/>
@@ -12811,11 +12811,11 @@
       <c r="G307" s="5" t="inlineStr"/>
       <c r="H307" s="5" t="inlineStr"/>
       <c r="I307" s="5" t="n">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="J307" s="5" t="inlineStr">
         <is>
-          <t>Debra — as director of elementary curriculum you decide what reaches K-5, which is the band financial literacy skips entirely. Mine has a full standards crosswalk. Clear your bar? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Debra — as director of elementary curriculum you decide what reaches K-5, which is the band financial literacy skips entirely. Mine has a full standards crosswalk. Clear your bar? Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K307" s="5" t="inlineStr"/>
@@ -12849,11 +12849,11 @@
       <c r="G308" s="5" t="inlineStr"/>
       <c r="H308" s="5" t="inlineStr"/>
       <c r="I308" s="5" t="n">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="J308" s="5" t="inlineStr">
         <is>
-          <t>Ellen — curriculum facilitators see whether teachers actually adopt something or shelve it without telling you. Mine needs no prep and nothing consumable. Survive your elementary classrooms? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ellen — curriculum facilitators see whether teachers actually adopt something or shelve it without telling you. Mine needs no prep and nothing consumable. Survive your elementary classrooms? Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K308" s="5" t="inlineStr"/>
@@ -12887,11 +12887,11 @@
       <c r="G309" s="5" t="inlineStr"/>
       <c r="H309" s="5" t="inlineStr"/>
       <c r="I309" s="5" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="J309" s="5" t="inlineStr">
         <is>
-          <t>Esabel — you'll ask about standards first. Mine maps to Jump$tart, Common Core Math and ELA, CEE, and FDIC Money Smart, with a 23-row crosswalk. Worth a review? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Esabel — you'll ask about standards first. Mine maps to Jump$tart, Common Core Math and ELA, CEE, and FDIC Money Smart, with a 23-row crosswalk. Worth a review? Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K309" s="5" t="inlineStr"/>
@@ -12925,11 +12925,11 @@
       <c r="G310" s="5" t="inlineStr"/>
       <c r="H310" s="5" t="inlineStr"/>
       <c r="I310" s="5" t="n">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="J310" s="5" t="inlineStr">
         <is>
-          <t>Jessica — an elementary curriculum specialist knows what teachers abandon halfway through. Mine is a 36-page read-aloud with zero-prep lessons and nothing to reorder. Survive your classrooms? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jessica — an elementary curriculum specialist knows what teachers abandon halfway through. Mine is a 36-page read-aloud with zero-prep lessons and nothing to reorder. Survive your classrooms? Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K310" s="5" t="inlineStr"/>
@@ -12963,11 +12963,11 @@
       <c r="G311" s="5" t="inlineStr"/>
       <c r="H311" s="5" t="inlineStr"/>
       <c r="I311" s="5" t="n">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="J311" s="5" t="inlineStr">
         <is>
-          <t>Julie — as senior director of elementary curriculum you decide what reaches a lot of classrooms. Mine teaches the complete purchase, sales tax included, with a full crosswalk. Worth a look? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Julie — as senior director of elementary curriculum you decide what reaches a lot of classrooms. Mine teaches the complete purchase, sales tax included, with a full crosswalk. Worth a look? Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K311" s="5" t="inlineStr"/>
@@ -13001,11 +13001,11 @@
       <c r="G312" s="5" t="inlineStr"/>
       <c r="H312" s="5" t="inlineStr"/>
       <c r="I312" s="5" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J312" s="5" t="inlineStr">
         <is>
-          <t>Katie — elementary curriculum is exactly the band that gets skipped on financial literacy. I made a picture book plus four free zero-prep lessons. Fit your district? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Katie — elementary curriculum is exactly the band that gets skipped on financial literacy. I made a picture book plus four free zero-prep lessons. Fit your district? Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K312" s="5" t="inlineStr"/>
@@ -13039,11 +13039,11 @@
       <c r="G313" s="5" t="inlineStr"/>
       <c r="H313" s="5" t="inlineStr"/>
       <c r="I313" s="5" t="n">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J313" s="5" t="inlineStr">
         <is>
-          <t>Marcella — a curriculum and instruction specialist will test whether the lessons match the book. Mine were written alongside it, 23-row crosswalk included. Would you look at the alignment? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Marcella — a curriculum and instruction specialist will test whether the lessons match the book. Mine were written alongside it, 23-row crosswalk included. Would you look at the alignment? Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K313" s="5" t="inlineStr"/>
@@ -13077,11 +13077,11 @@
       <c r="G314" s="5" t="inlineStr"/>
       <c r="H314" s="5" t="inlineStr"/>
       <c r="I314" s="5" t="n">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="J314" s="5" t="inlineStr">
         <is>
-          <t>Dr. Berry — as director of elementary curriculum you set what K-5 actually gets. Financial literacy usually stops before fifth grade entirely. I wrote a picture book plus free standards-aligned lessons. Worth reviewing? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Berry — as director of elementary curriculum you set what K-5 actually gets. Financial literacy usually stops before fifth grade entirely. I wrote a picture book plus free standards-aligned lessons. Worth reviewing? Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K314" s="5" t="inlineStr"/>
@@ -13115,11 +13115,11 @@
       <c r="G315" s="5" t="inlineStr"/>
       <c r="H315" s="5" t="inlineStr"/>
       <c r="I315" s="5" t="n">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="J315" s="5" t="inlineStr">
         <is>
-          <t>Shelly — an elementary curriculum coordinator sees what teachers actually pick up. Mine requires no prep, nothing consumable, and it's a story kids finish. Fit your schools? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Shelly — an elementary curriculum coordinator sees what teachers actually pick up. Mine requires no prep, nothing consumable, and it's a story kids finish. Fit your schools? Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K315" s="5" t="inlineStr"/>
@@ -13153,11 +13153,11 @@
       <c r="G316" s="5" t="inlineStr"/>
       <c r="H316" s="5" t="inlineStr"/>
       <c r="I316" s="5" t="n">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="J316" s="5" t="inlineStr">
         <is>
-          <t>Suzan — elementary curriculum directors are the right filter for this. Mine is K-5, teaching spending, with assessments and a 23-row crosswalk behind it. Worth a review? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Suzan — elementary curriculum directors are the right filter for this. Mine is K-5, teaching spending, with assessments and a 23-row crosswalk behind it. Worth a review? Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K316" s="5" t="inlineStr"/>
@@ -13191,11 +13191,11 @@
       <c r="G317" s="5" t="inlineStr"/>
       <c r="H317" s="5" t="inlineStr"/>
       <c r="I317" s="5" t="n">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="J317" s="5" t="inlineStr">
         <is>
-          <t>Tamika — an elementary curriculum specialist knows whether something fits a real scope and sequence. Mine is one 36-page book plus four 45-minute lessons against five frameworks. Would you look? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tamika — an elementary curriculum specialist knows whether something fits a real scope and sequence. Mine is one 36-page book plus four 45-minute lessons against five frameworks. Would you look? Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K317" s="5" t="inlineStr"/>
@@ -13229,11 +13229,11 @@
       <c r="G318" s="5" t="inlineStr"/>
       <c r="H318" s="5" t="inlineStr"/>
       <c r="I318" s="5" t="n">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="J318" s="5" t="inlineStr">
         <is>
-          <t>Toby — you coordinate across ELA, math, and social studies, which is unusual and useful: mine hits all three at once. Comparison math, a read-aloud narrative, and consumer economics. Fit? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Toby — you coordinate across ELA, math, and social studies, which is unusual and useful: mine hits all three at once. Comparison math, a read-aloud narrative, and consumer economics. Fit? Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K318" s="5" t="inlineStr"/>
@@ -13267,11 +13267,11 @@
       <c r="G319" s="5" t="inlineStr"/>
       <c r="H319" s="5" t="inlineStr"/>
       <c r="I319" s="5" t="n">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="J319" s="5" t="inlineStr">
         <is>
-          <t>Gerri — money habits form in early childhood long before anyone calls them habits. Mine teaches the first one a child actually uses: how to spend on purpose. Fit the families you serve? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Gerri — money habits form in early childhood long before anyone calls them habits. Mine teaches the first one a child actually uses: how to spend on purpose. Fit the families you serve? Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K319" s="5" t="inlineStr"/>
@@ -13305,11 +13305,11 @@
       <c r="G320" s="5" t="inlineStr"/>
       <c r="H320" s="5" t="inlineStr"/>
       <c r="I320" s="5" t="n">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="J320" s="5" t="inlineStr">
         <is>
-          <t>Noelani — you design adult learning, so you'll know whether my teacher materials teach. Four 45-minute plans, a pre/post assessment with answer key, a 23-row crosswalk, all free. Would you look at the instructional design? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Noelani — you design adult learning, so you'll know whether my teacher materials teach. Four 45-minute plans, a pre/post assessment with answer key, a 23-row crosswalk, all free. Would you look at the instructional design? Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K320" s="5" t="inlineStr"/>
@@ -13343,11 +13343,11 @@
       <c r="G321" s="5" t="inlineStr"/>
       <c r="H321" s="5" t="inlineStr"/>
       <c r="I321" s="5" t="n">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="J321" s="5" t="inlineStr">
         <is>
-          <t>Jennifer — as an EdTech implementation lead you know adoption dies on friction. Mine has none: a book and print-ready lessons. No login, no platform, no seats to provision. Fit any state program you run? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jennifer — as an EdTech implementation lead you know adoption dies on friction. Mine has none: a book and print-ready lessons. No login, no platform, no seats to provision. Fit any state program you run? Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K321" s="5" t="inlineStr"/>
@@ -13381,11 +13381,11 @@
       <c r="G322" s="5" t="inlineStr"/>
       <c r="H322" s="5" t="inlineStr"/>
       <c r="I322" s="5" t="n">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="J322" s="5" t="inlineStr">
         <is>
-          <t>Gil — a curriculum developer working on financial literacy math will care that mine has real arithmetic in it: comparing two prices, applying a percentage off, adding sales tax. Fit what you're building? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Gil — a curriculum developer working on financial literacy math will care that mine has real arithmetic in it: comparing two prices, applying a percentage off, adding sales tax. Fit what you're building? Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K322" s="5" t="inlineStr"/>
@@ -13419,11 +13419,11 @@
       <c r="G323" s="5" t="inlineStr"/>
       <c r="H323" s="5" t="inlineStr"/>
       <c r="I323" s="5" t="n">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="J323" s="5" t="inlineStr">
         <is>
-          <t>Amanda — a practitioner gut-check. Mine teaches spending through a story about a boy and a robot, no worksheet anywhere. Does it hold early-childhood kids, or does it skew older than I think? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Amanda — a practitioner gut-check. Mine teaches spending through a story about a boy and a robot, no worksheet anywhere. Does it hold early-childhood kids, or does it skew older than I think? Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K323" s="5" t="inlineStr"/>
@@ -13457,11 +13457,11 @@
       <c r="G324" s="5" t="inlineStr"/>
       <c r="H324" s="5" t="inlineStr"/>
       <c r="I324" s="5" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="J324" s="5" t="inlineStr">
         <is>
-          <t>Charlene — would you tell me whether this skews too old? 36-page read-aloud at AD 620L, one shopping trip start to finish. I aimed at 6-10 but I'd rather be corrected than confident. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Charlene — would you tell me whether this skews too old? 36-page read-aloud at AD 620L, one shopping trip start to finish. I aimed at 6-10 but I'd rather be corrected than confident. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K324" s="5" t="inlineStr"/>
@@ -13495,11 +13495,11 @@
       <c r="G325" s="5" t="inlineStr"/>
       <c r="H325" s="5" t="inlineStr"/>
       <c r="I325" s="5" t="n">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="J325" s="5" t="inlineStr">
         <is>
-          <t>Dr. Rodrigue — an EdD in a CISO seat is an unusual combination, and my question is on the education side. Does a K-5 financial literacy book plus free toolkit fit anything your organization touches? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Rodrigue — an EdD in a CISO seat is an unusual combination, and my question is on the education side. Does a K-5 financial literacy book plus free teacher materials fit anything your organization touches? The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K325" s="5" t="inlineStr"/>
@@ -13533,11 +13533,11 @@
       <c r="G326" s="5" t="inlineStr"/>
       <c r="H326" s="5" t="inlineStr"/>
       <c r="I326" s="5" t="n">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="J326" s="5" t="inlineStr">
         <is>
-          <t>Jennifer — your work with financial institutions and external affairs is where a fundable K-5 program needs a champion. Mine comes with a grant-ready packet built for bank and CRA sponsorship. Where might it fit? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jennifer — your work with financial institutions and external affairs is where a fundable K-5 program needs a champion. Mine comes with a grant-ready packet built for bank and CRA sponsorship. Where might it fit? Print it here: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K326" s="5" t="inlineStr"/>
@@ -13571,11 +13571,11 @@
       <c r="G327" s="5" t="inlineStr"/>
       <c r="H327" s="5" t="inlineStr"/>
       <c r="I327" s="5" t="n">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="J327" s="5" t="inlineStr">
         <is>
-          <t>Leslie — consumer markets work is upstream of everything my book teaches: comparison, price transparency, what the register adds at the end. Mine is the six-year-old version. Where might it fit? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Leslie — consumer markets work is upstream of everything my book teaches: comparison, price transparency, what the register adds at the end. Mine is the six-year-old version. Where might it fit? Teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K327" s="5" t="inlineStr"/>
@@ -13799,11 +13799,11 @@
       <c r="G333" s="5" t="inlineStr"/>
       <c r="H333" s="5" t="inlineStr"/>
       <c r="I333" s="5" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="J333" s="5" t="inlineStr">
         <is>
-          <t>Christina — Think Pieces is building financial education for children, so we're solving the same problem. I made a picture book plus free ungated toolkit for K-5. Worth comparing notes, or trading copies? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Christina — Think Pieces is building financial education for children, so we're solving the same problem. I made a picture book plus free ungated teacher pack for K-5. Worth comparing notes, or trading copies? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K333" s="5" t="inlineStr"/>
@@ -16475,11 +16475,11 @@
       <c r="G403" s="5" t="inlineStr"/>
       <c r="H403" s="5" t="inlineStr"/>
       <c r="I403" s="5" t="n">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="J403" s="5" t="inlineStr">
         <is>
-          <t>Flora — JA reaches more kids than almost anybody, and elementary is usually where the material thins out. Mine is a K-5 picture book with a free zero-prep toolkit against five frameworks, teaching spending rather than saving. Fit anything JA Alaska runs? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Flora — JA reaches more kids than almost anybody, and elementary is usually where the material thins out. Mine is a K-5 picture book with a free zero-prep classroom pack against five frameworks, teaching spending rather than saving. Fit anything JA Alaska runs? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K403" s="5" t="inlineStr"/>
@@ -16651,11 +16651,11 @@
       <c r="G407" s="5" t="inlineStr"/>
       <c r="H407" s="5" t="inlineStr"/>
       <c r="I407" s="5" t="n">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="J407" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melanie — early childhood is the exact window I wrote for. Mine starts where a kid actually starts with money, which is spending it. One trip, one real decision, no worksheet anywhere. Fit an early-grades classroom in Palmdale? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Melanie — early childhood is the exact window I wrote for. Mine starts where a kid actually starts with money, which is spending it. One trip, one real decision, no worksheet anywhere. Fit an early-grades classroom in Palmdale? Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K407" s="5" t="inlineStr"/>
@@ -16689,11 +16689,11 @@
       <c r="G408" s="5" t="inlineStr"/>
       <c r="H408" s="5" t="inlineStr"/>
       <c r="I408" s="5" t="n">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="J408" s="5" t="inlineStr">
         <is>
-          <t>Amanda — a national curriculum consultant sees whether something was built to teach or built to look like it was. Mine has four zero-prep lessons and a 23-row crosswalk written alongside the book, not bolted on after. Does the design hold? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Amanda — a national curriculum consultant sees whether something was built to teach or built to look like it was. Mine has four zero-prep lessons and a 23-row crosswalk written alongside the book, not bolted on after. Does the design hold? Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K408" s="5" t="inlineStr"/>
@@ -16727,11 +16727,11 @@
       <c r="G409" s="5" t="inlineStr"/>
       <c r="H409" s="5" t="inlineStr"/>
       <c r="I409" s="5" t="n">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="J409" s="5" t="inlineStr">
         <is>
-          <t>Hayley — a curriculum specialist will test whether the lessons match the book. Mine were written alongside it: four 45-minute plans, a pre/post assessment with answer key, a 23-row crosswalk. Would you look at the alignment? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hayley — a curriculum specialist will test whether the lessons match the book. Mine were written alongside it: four 45-minute plans, a pre/post assessment with answer key, a 23-row crosswalk. Would you look at the alignment? Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K409" s="5" t="inlineStr"/>
@@ -16765,11 +16765,11 @@
       <c r="G410" s="5" t="inlineStr"/>
       <c r="H410" s="5" t="inlineStr"/>
       <c r="I410" s="5" t="n">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="J410" s="5" t="inlineStr">
         <is>
-          <t>Holden — curriculum and instruction is where a book like this lives or dies. Mine is K-5, teaching the complete purchase, sales tax included, with free zero-prep lessons. Elementary is where financial literacy gets skipped. Fit your scope? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Holden — curriculum and instruction is where a book like this lives or dies. Mine is K-5, teaching the complete purchase, sales tax included, with free zero-prep lessons. Elementary is where financial literacy gets skipped. Fit your scope? Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K410" s="5" t="inlineStr"/>
@@ -17487,11 +17487,11 @@
       <c r="G429" s="5" t="inlineStr"/>
       <c r="H429" s="5" t="inlineStr"/>
       <c r="I429" s="5" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="J429" s="5" t="inlineStr">
         <is>
-          <t>Ed — WizeUp runs financial education as a charity, which means every pound has to earn its place. Mine is a book plus a completely free toolkit, so the only cost is the copies. Fit what WizeUp delivers? More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ed — WizeUp runs financial education as a charity, which means every pound has to earn its place. Mine is a book plus a completely free teacher pack, so the only cost is the copies. Fit what WizeUp delivers? More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K429" s="5" t="inlineStr"/>
@@ -18133,11 +18133,11 @@
       <c r="G446" s="5" t="inlineStr"/>
       <c r="H446" s="5" t="inlineStr"/>
       <c r="I446" s="5" t="n">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="J446" s="5" t="inlineStr">
         <is>
-          <t>Jeffery — as a chief financial educator you build programs for real audiences. Mine is K-5 with a free ungated toolkit and a 21-term glossary in the back. Fit the learners you serve? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jeffery — as a chief financial educator you build programs for real audiences. Mine is K-5 with a free ungated classroom pack and a 21-term glossary in the back. Fit the learners you serve? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K446" s="5" t="inlineStr"/>
@@ -18855,11 +18855,11 @@
       <c r="G465" s="5" t="inlineStr"/>
       <c r="H465" s="5" t="inlineStr"/>
       <c r="I465" s="5" t="n">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="J465" s="5" t="inlineStr">
         <is>
-          <t>Bjorn — directing financial education with an AFC behind you, you decide what actually reaches learners. Mine is K-5, the band with the least material, plus a free ungated toolkit. Fit a program you run? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Bjorn — directing financial education with an AFC behind you, you decide what actually reaches learners. Mine is K-5, the band with the least material, plus a free ungated lesson set. Fit a program you run? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K465" s="5" t="inlineStr"/>
@@ -18893,11 +18893,11 @@
       <c r="G466" s="5" t="inlineStr"/>
       <c r="H466" s="5" t="inlineStr"/>
       <c r="I466" s="5" t="n">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="J466" s="5" t="inlineStr">
         <is>
-          <t>Gilly — FinMango works at real scale, and elementary is usually where the material runs out. Mine is a K-5 picture book with a completely free toolkit. Fit anything FinMango distributes? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Gilly — FinMango works at real scale, and elementary is usually where the material runs out. Mine is a K-5 picture book with a completely free teacher materials. Fit anything FinMango distributes? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K466" s="5" t="inlineStr"/>
@@ -19121,11 +19121,11 @@
       <c r="G472" s="5" t="inlineStr"/>
       <c r="H472" s="5" t="inlineStr"/>
       <c r="I472" s="5" t="n">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="J472" s="5" t="inlineStr">
         <is>
-          <t>Corey — financial education plus business strategy means you'll ask whether this scales. Mine is a book plus a completely free toolkit, so the only line item is the copies. Does that hold up as a model? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Corey — financial education plus business strategy means you'll ask whether this scales. Mine is a book plus a completely free classroom materials, so the only line item is the copies. Does that hold up as a model? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K472" s="5" t="inlineStr"/>
@@ -19235,11 +19235,11 @@
       <c r="G475" s="5" t="inlineStr"/>
       <c r="H475" s="5" t="inlineStr"/>
       <c r="I475" s="5" t="n">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="J475" s="5" t="inlineStr">
         <is>
-          <t>Debra — an AFC with an Ed.M bridges coaching and the classroom, which is exactly the two audiences for my book. K-5, five frameworks, free toolkit. Point families toward it? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Debra — an AFC with an Ed.M bridges coaching and the classroom, which is exactly the two audiences for my book. K-5, five frameworks, free teaching pack. Point families toward it? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K475" s="5" t="inlineStr"/>
@@ -19387,11 +19387,11 @@
       <c r="G479" s="5" t="inlineStr"/>
       <c r="H479" s="5" t="inlineStr"/>
       <c r="I479" s="5" t="n">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="J479" s="5" t="inlineStr">
         <is>
-          <t>Hafsat — a financial education consultant with the CFEI knows what actually teaches versus what merely informs. Mine is K-5 against five frameworks with a free toolkit. Fit the families or programs you work with? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hafsat — a financial education consultant with the CFEI knows what actually teaches versus what merely informs. Mine is K-5 against five frameworks with a free teacher pack. Fit the families or programs you work with? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K479" s="5" t="inlineStr"/>
@@ -19425,11 +19425,11 @@
       <c r="G480" s="5" t="inlineStr"/>
       <c r="H480" s="5" t="inlineStr"/>
       <c r="I480" s="5" t="n">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="J480" s="5" t="inlineStr">
         <is>
-          <t>Helen — an executive who's also a Certified Financial Educator sees both the strategy and the teaching. Mine is K-5, five frameworks, free ungated toolkit. Fit the programs you lead? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Helen — an executive who's also a Certified Financial Educator sees both the strategy and the teaching. Mine is K-5, five frameworks, free ungated classroom pack. Fit the programs you lead? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K480" s="5" t="inlineStr"/>
@@ -19919,11 +19919,11 @@
       <c r="G493" s="5" t="inlineStr"/>
       <c r="H493" s="5" t="inlineStr"/>
       <c r="I493" s="5" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J493" s="5" t="inlineStr">
         <is>
-          <t>Lita — leading a financial literacy team means you choose what reaches people. Mine is K-5, usually the band with nothing, plus a free ungated toolkit. Worth a look? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Lita — leading a financial literacy team means you choose what reaches people. Mine is K-5, usually the band with nothing, plus a free ungated lesson set. Worth a look? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K493" s="5" t="inlineStr"/>
@@ -20109,11 +20109,11 @@
       <c r="G498" s="5" t="inlineStr"/>
       <c r="H498" s="5" t="inlineStr"/>
       <c r="I498" s="5" t="n">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="J498" s="5" t="inlineStr">
         <is>
-          <t>Mya — as a financial education consultant you know what actually teaches. Mine is K-5 against five frameworks with a completely free toolkit. Fit the programs you advise? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Mya — as a financial education consultant you know what actually teaches. Mine is K-5 against five frameworks with a completely free teacher materials. Fit the programs you advise? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K498" s="5" t="inlineStr"/>
@@ -20299,11 +20299,11 @@
       <c r="G503" s="5" t="inlineStr"/>
       <c r="H503" s="5" t="inlineStr"/>
       <c r="I503" s="5" t="n">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="J503" s="5" t="inlineStr">
         <is>
-          <t>Sarah — as a financial literacy specialist you decide what's worth putting in front of people. Mine is K-5, usually the emptiest shelf, with a free ungated toolkit. Worth a look? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sarah — as a financial literacy specialist you decide what's worth putting in front of people. Mine is K-5, usually the emptiest shelf, with a free ungated classroom materials. Worth a look? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K503" s="5" t="inlineStr"/>
@@ -20527,11 +20527,11 @@
       <c r="G509" s="5" t="inlineStr"/>
       <c r="H509" s="5" t="inlineStr"/>
       <c r="I509" s="5" t="n">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="J509" s="5" t="inlineStr">
         <is>
-          <t>Tom — as a Certified Financial Educator you know spending is where it starts. Mine is the K-5 version with a free ungated toolkit. Fit the families you reach? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tom — as a Certified Financial Educator you know spending is where it starts. Mine is the K-5 version with a free ungated teaching pack. Fit the families you reach? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K509" s="5" t="inlineStr"/>
@@ -21357,11 +21357,11 @@
       <c r="G530" s="5" t="inlineStr"/>
       <c r="H530" s="5" t="inlineStr"/>
       <c r="I530" s="5" t="n">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="J530" s="5" t="inlineStr">
         <is>
-          <t>Zion — you help organizations stand up financial literacy programs, so you know the gap: they all teach saving and skip spending, which is what kids actually do. Mine is K-5 with a completely free toolkit. Where might a family-facing book fit in your work? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Zion — you help organizations stand up financial literacy programs, so you know the gap: they all teach saving and skip spending, which is what kids actually do. Mine is K-5 with a completely free teacher pack. Where might a family-facing book fit in your work? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K530" s="5" t="inlineStr"/>
@@ -21699,11 +21699,11 @@
       <c r="G539" s="5" t="inlineStr"/>
       <c r="H539" s="5" t="inlineStr"/>
       <c r="I539" s="5" t="n">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="J539" s="5" t="inlineStr">
         <is>
-          <t>Jim — financial know-how is the whole game, and I'm trying to start it at six. Any book can teach a kid to save; the hard part is teaching him to spend. Five frameworks, free toolkit. Does the framing hold? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jim — financial know-how is the whole game, and I'm trying to start it at six. Any book can teach a kid to save; the hard part is teaching him to spend. Five frameworks, free classroom pack. Does the framing hold? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K539" s="5" t="inlineStr"/>
@@ -22687,11 +22687,11 @@
       <c r="G565" s="5" t="inlineStr"/>
       <c r="H565" s="5" t="inlineStr"/>
       <c r="I565" s="5" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J565" s="5" t="inlineStr">
         <is>
-          <t>Keith — NextGen Prosperity is after the same generation I am, just at a different age. Mine is K-5 with a completely free toolkit. Complement your work, or duplicate it? Either answer is useful. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Keith — NextGen Prosperity is after the same generation I am, just at a different age. Mine is K-5 with a completely free lesson set. Complement your work, or duplicate it? Either answer is useful. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K565" s="5" t="inlineStr"/>
@@ -23561,11 +23561,11 @@
       <c r="G588" s="5" t="inlineStr"/>
       <c r="H588" s="5" t="inlineStr"/>
       <c r="I588" s="5" t="n">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="J588" s="5" t="inlineStr">
         <is>
-          <t>James — partnerships and fintech means you'll ask whether this scales. Mine is a book plus a completely free toolkit, so the only line item is the copies. Does that hold as a model? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>James — partnerships and fintech means you'll ask whether this scales. Mine is a book plus a completely free teacher materials, so the only line item is the copies. Does that hold as a model? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K588" s="5" t="inlineStr"/>
@@ -24055,11 +24055,11 @@
       <c r="G601" s="5" t="inlineStr"/>
       <c r="H601" s="5" t="inlineStr"/>
       <c r="I601" s="5" t="n">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="J601" s="5" t="inlineStr">
         <is>
-          <t>Amber — revenue growth and strategic partnerships is a long way from a picture book. Mine teaches six-year-olds to spend on purpose, and it comes with a free toolkit. Fit any partnership you're building, or wrong lane? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Amber — revenue growth and strategic partnerships is a long way from a picture book. Mine teaches six-year-olds to spend on purpose, and it comes with a free classroom materials. Fit any partnership you're building, or wrong lane? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K601" s="5" t="inlineStr"/>
@@ -24131,11 +24131,11 @@
       <c r="G603" s="5" t="inlineStr"/>
       <c r="H603" s="5" t="inlineStr"/>
       <c r="I603" s="5" t="n">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="J603" s="5" t="inlineStr">
         <is>
-          <t>Andi — SavvyMoney puts financial tools in front of credit union members, which is the same audience that funds K-5 programs locally. Mine is a book plus a free toolkit with a grant packet attached. Worth knowing about? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Andi — SavvyMoney puts financial tools in front of credit union members, which is the same audience that funds K-5 programs locally. Mine is a book plus a free teaching pack with a grant packet attached. Worth knowing about? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K603" s="5" t="inlineStr"/>
@@ -24397,11 +24397,11 @@
       <c r="G610" s="5" t="inlineStr"/>
       <c r="H610" s="5" t="inlineStr"/>
       <c r="I610" s="5" t="n">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="J610" s="5" t="inlineStr">
         <is>
-          <t>Chris — SavvyMoney reaches credit union members at scale, and those institutions are exactly who fund K-5 financial literacy locally. Mine is a book plus free toolkit with a grant packet attached. Worth knowing about? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Chris — SavvyMoney reaches credit union members at scale, and those institutions are exactly who fund K-5 financial literacy locally. Mine is a book plus free teacher pack with a grant packet attached. Worth knowing about? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K610" s="5" t="inlineStr"/>
@@ -24861,11 +24861,11 @@
       <c r="G622" s="5" t="inlineStr"/>
       <c r="H622" s="5" t="inlineStr"/>
       <c r="I622" s="5" t="n">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="J622" s="5" t="inlineStr">
         <is>
-          <t>Sandy — FCCLA members are a decade older than my readers, so this is not a curriculum pitch. It's a service-project one. Your chapters already run community work, and a high schooler reading a money book to a second-grade class is about the cleanest version of that I can think of. Mine is 36 pages, teaches the whole purchase through the register, and the toolkit behind it is free. Does that fit how chapters choose projects, or am I inventing a use case? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sandy — FCCLA members are a decade older than my readers, so this is not a curriculum pitch. It's a service-project one. Your chapters already run community work, and a high schooler reading a money book to a second-grade class is about the cleanest version of that I can think of. Mine is 36 pages, teaches the whole purchase through the register, and the classroom pack behind it is free. Does that fit how chapters choose projects, or am I inventing a use case? Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K622" s="5" t="inlineStr"/>
@@ -24907,11 +24907,11 @@
       <c r="G623" s="5" t="inlineStr"/>
       <c r="H623" s="5" t="inlineStr"/>
       <c r="I623" s="5" t="n">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="J623" s="5" t="inlineStr">
         <is>
-          <t>Megan — Econiful starts at grade 6, which puts my book directly underneath you rather than beside you. Mine is the K-5 on-ramp: a six-year-old runs one purchase, ad to register, sales tax at the end. Congratulations on the Rising Star, by the way. Genuine question rather than a pitch — do you see elementary as in scope for Econiful, or a gap somebody else has to fill? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Megan — Econiful starts at grade 6, which puts my book directly underneath you rather than beside you. Mine is the K-5 on-ramp: a six-year-old runs one purchase, ad to register, sales tax at the end. Congratulations on the Rising Star, by the way. Genuine question rather than a pitch — do you see elementary as in scope for Econiful, or a gap somebody else has to fill? For teachers: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K623" s="5" t="inlineStr"/>
@@ -25087,11 +25087,11 @@
       <c r="G627" s="5" t="inlineStr"/>
       <c r="H627" s="5" t="inlineStr"/>
       <c r="I627" s="5" t="n">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="J627" s="5" t="inlineStr">
         <is>
-          <t>Bree — a CUDE tends to think about the movement rather than the quarter, which is why I'm asking you rather than a marketing desk. Mine is K-5, the band almost nobody builds for, and the whole toolkit is free. There's a grant packet with the math done if a credit union ever wanted to fund a classroom set. Fit your well-being work? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Bree — a CUDE tends to think about the movement rather than the quarter, which is why I'm asking you rather than a marketing desk. Mine is K-5, the band almost nobody builds for, and the whole teacher materials is free. There's a grant packet with the math done if a credit union ever wanted to fund a classroom set. Fit your well-being work? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K627" s="5" t="inlineStr"/>
@@ -25129,11 +25129,11 @@
       <c r="G628" s="5" t="inlineStr"/>
       <c r="H628" s="5" t="inlineStr"/>
       <c r="I628" s="5" t="n">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="J628" s="5" t="inlineStr">
         <is>
-          <t>Sara — a product innovation question rather than a book pitch. Mine is deliberately low-tech: a printed read-along with free print-ready lessons. No login, no platform, no seats to provision, which either makes it frictionless or makes it a relic. You'd know which. Does analog still work at K-5, or am I fighting the tide? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sara — a product innovation question rather than a book pitch. Mine is deliberately low-tech: a printed read-along with free print-ready lessons. No login, no platform, no seats to provision, which either makes it frictionless or makes it a relic. You'd know which. Does analog still work at K-5, or am I fighting the tide? Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K628" s="5" t="inlineStr"/>
@@ -25171,11 +25171,11 @@
       <c r="G629" s="5" t="inlineStr"/>
       <c r="H629" s="5" t="inlineStr"/>
       <c r="I629" s="5" t="n">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="J629" s="5" t="inlineStr">
         <is>
-          <t>Miche — coordinators are the ones who have to make the thing actually work after somebody else picks it, which is why your read is worth more than a director's. Mine needs no prep, no platform, nothing consumable, and the lessons are free. Four 45-minute plans, a pre/post assessment, a 23-row crosswalk. Would it survive contact with a real schedule? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Miche — coordinators are the ones who have to make the thing actually work after somebody else picks it, which is why your read is worth more than a director's. Mine needs no prep, no platform, nothing consumable, and the lessons are free. Four 45-minute plans, a pre/post assessment, a 23-row crosswalk. Would it survive contact with a real schedule? Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K629" s="5" t="inlineStr"/>
@@ -25301,7 +25301,7 @@
       <c r="G632" s="5" t="inlineStr"/>
       <c r="H632" s="5" t="inlineStr"/>
       <c r="I632" s="5" t="n">
-        <v>1409</v>
+        <v>1414</v>
       </c>
       <c r="J632" s="5" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
 I'm writing because you're the Eastern Shore rep for MAESP and I'm down your way often — I spend a good part of the year in Rehoboth, so Greensboro is nearly the neighborhood.
 I wrote and illustrated a K-5 book about money that does the one thing the rest of the shelf skips. Every other kids' money book teaches saving. Mine teaches a purchase — a boy earns a robot, reads the sale ads, compares two models, takes the marked-down one on purpose, hands a coupon to the cashier, and runs face-first into sales tax. Sixteen-plus concepts, none of them announced as a lesson.
 Here is why I'm writing you and not a longer list. MAESP recognized you as a Connected School Leader for actually using the digital tools, and the entire teacher kit behind the book is free, ungated, and prints from a browser — four lesson plans, assessments with answer keys, a standards crosswalk. No account, no budget line. It is exactly the kind of thing that dies in a staff room unless a principal who gets it hands it over.
-Would it be useful on the Eastern Shore, or am I overreaching? Toolkit: clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html
+Would it be useful on the Eastern Shore, or am I overreaching? Teacher pack: clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
         </is>
       </c>
@@ -25403,7 +25403,7 @@
         </is>
       </c>
       <c r="I634" s="5" t="n">
-        <v>1569</v>
+        <v>1576</v>
       </c>
       <c r="J634" s="5" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
 But no second grader has a savings rate. Every second grader has stood in an aisle holding money and had to decide. The cash register comes before the piggy bank, and children's publishing has had it backwards for forty years.
 So I wrote the spending one. A boy earns a robot, reads the sale ad, compares two models, takes the marked-down one on purpose, hands a coupon to the cashier, then meets sales tax and takes it personally. Thirty-six pages, grades 1-5.
 Built with a K-5 teacher of 30+ years who told me what to cut, and endorsed by Wally Luckeydoo, Ed.D., who was named 2026 EIFLE Educator of the Year and took the Jump$tart Corey Carlisle Award the same year.
-The toolkit is free and ungated — four lesson plans, assessments with answer keys, a 23-row standards crosswalk. A principal hands a teacher the whole thing on a Friday and it costs the building nothing.
+The classroom pack is free and ungated — four lesson plans, assessments with answer keys, a 23-row standards crosswalk. A principal hands a teacher the whole thing on a Friday and it costs the building nothing.
 You have the rarest vantage point in this conversation: you sit in the association chair and in a principal's chair on the same day. So the question is genuinely for you. Would your members use this, or is it one more good idea that dies in a staff room?
 Jonathan Bach
 Baltimore</t>
@@ -25462,14 +25462,14 @@
         </is>
       </c>
       <c r="I635" s="5" t="n">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="J635" s="5" t="inlineStr">
         <is>
           <t>Ms. Hilliard — you are MAESP's NAESP Representative, which as far as I can tell makes you the one person with a foot in both the state and national conversation. That is why you are getting this rather than a longer list of people.
 The claim, and you can check it in an afternoon: every children's financial literacy book teaches saving. I read all 25 on the ABA Foundation's list. Not one teaches spending — the only money thing an elementary student actually does.
 Meanwhile financial literacy mandates keep landing in high school and elementary principals get the expectation without the materials.
-I wrote the K-5 book for the register rather than the piggy bank. A boy earns a robot, compares two on a shelf, takes the marked-down one on purpose, hands over a coupon, and meets sales tax for the first time. Free ungated toolkit behind it — four lesson plans, assessments, a 23-row crosswalk. Endorsed by Wally Luckeydoo, Ed.D., 2026 EIFLE Educator of the Year.
+I wrote the K-5 book for the register rather than the piggy bank. A boy earns a robot, compares two on a shelf, takes the marked-down one on purpose, hands over a coupon, and meets sales tax for the first time. Free ungated lesson set behind it — four lesson plans, assessments, a 23-row crosswalk. Endorsed by Wally Luckeydoo, Ed.D., 2026 EIFLE Educator of the Year.
 Two questions, either one useful:
 Does this belong in front of Maryland principals? And if it does, is there a version of that conversation worth having nationally?
 Jonathan Bach
@@ -25519,7 +25519,7 @@
         </is>
       </c>
       <c r="I636" s="5" t="n">
-        <v>1220</v>
+        <v>1230</v>
       </c>
       <c r="J636" s="5" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
 I wrote the book that fills it, which is my interest declared up front. But the more useful half is the gap itself. Elementary principals are being handed financial literacy mandates written for high school, then asked to do something with six-year-olds, and the shelf they reach for is all piggy banks.
 If that is a piece for Principal, I am glad to talk, or to hand it to whoever covers curriculum. If it is not, tell me and I will stop.
 Book facts: https://clarencegetsabargain.com/book-facts.html
-Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html
+Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html
 Sample: https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan Bach</t>
         </is>
@@ -25578,7 +25578,7 @@
         </is>
       </c>
       <c r="I637" s="5" t="n">
-        <v>1292</v>
+        <v>1304</v>
       </c>
       <c r="J637" s="5" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
 One question, and the setup takes thirty seconds.
 Every children's money book teaches saving. I read all 25 on the ABA Foundation's list to make sure I was not imagining it. Not one teaches spending — which is the only money thing an elementary student actually does. No second grader has a savings rate. Every second grader has stood in a store holding money and had to decide.
 So I wrote the one for the register rather than the piggy bank. A boy earns a robot, does his own comparison, takes the marked-down model on purpose, hands over a coupon, and then meets sales tax and takes it badly.
-For a principal the relevant facts are these: hardcover, 36 pages, nothing consumable, and the entire teacher toolkit is free and ungated. Four lesson plans, assessments with answer keys, a 23-row standards crosswalk against Jump$tart, Common Core, CEE, and FDIC Money Smart. Endorsed by Wally Luckeydoo, Ed.D., 2026 EIFLE Educator of the Year.
+For a principal the relevant facts are these: hardcover, 36 pages, nothing consumable, and the entire teacher classroom materials is free and ungated. Four lesson plans, assessments with answer keys, a 23-row standards crosswalk against Jump$tart, Common Core, CEE, and FDIC Money Smart. Endorsed by Wally Luckeydoo, Ed.D., 2026 EIFLE Educator of the Year.
 The question: would a Maryland elementary principal actually use this, or is it one more good-sounding thing that dies in a staff room?
 I would rather have a blunt no from you than a polite maybe from anyone else.
 Jonathan Bach
@@ -25636,7 +25636,7 @@
         </is>
       </c>
       <c r="I638" s="5" t="n">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="J638" s="5" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
 Financial literacy has become an elementary expectation without ever becoming an elementary mandate. The requirements were written for high school. So were the materials. I read all 25 titles on the ABA Foundation's children's list, and every one teaches saving — while the only money thing a six-year-old actually does is spend.
 That is a gap a state association could visibly close, cheaply, in one school year.
 I wrote the K-5 book for it. One purchase, start to finish: sale ad, comparison, markdown, coupon, and sales tax at the end, which the six-year-old resents. Endorsed by Wally Luckeydoo, Ed.D., 2026 EIFLE Educator of the Year, and built alongside a K-5 teacher with 30+ years.
-The relevant part for an association: the whole toolkit is free and ungated, so nothing about it requires a budget line. Four lesson plans, assessments, a 23-row standards crosswalk.
+The relevant part for an association: the whole teaching pack is free and ungated, so nothing about it requires a budget line. Four lesson plans, assessments, a 23-row standards crosswalk.
 If that is nowhere near what you want your year to be about, say so and I will leave you to plan in peace.
 Jonathan Bach
 Baltimore</t>
@@ -25694,12 +25694,12 @@
         </is>
       </c>
       <c r="I639" s="5" t="n">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="J639" s="5" t="inlineStr">
         <is>
           <t>Dr. Messier — you are the treasurer, so I will lead with the money and you can decide whether the rest is worth reading.
-The classroom toolkit is free. Not freemium, not free-with-registration. Four 45-minute lesson plans, a pre/post assessment with the answer key, a 23-row standards crosswalk, print-ready. No login, no seats, no renewal, nothing consumable to reorder next August. The only cost that ever exists is the copies of the book, at $19.99, with PO and Net 30 terms available.
+The classroom teacher pack is free. Not freemium, not free-with-registration. Four 45-minute lesson plans, a pre/post assessment with the answer key, a 23-row standards crosswalk, print-ready. No login, no seats, no renewal, nothing consumable to reorder next August. The only cost that ever exists is the copies of the book, at $19.99, with PO and Net 30 terms available.
 Now the part that justifies it existing.
 Every children's money book teaches saving. I read all 25 on the ABA Foundation's list. None teaches spending, which is the only money thing an elementary student actually does — no second grader has a savings rate, but every second grader has stood in a store holding money and had to decide.
 Mine teaches the register instead of the piggy bank. One purchase, sale ad to sales tax. Endorsed by Wally Luckeydoo, Ed.D., 2026 EIFLE Educator of the Year.
@@ -25751,7 +25751,7 @@
         </is>
       </c>
       <c r="I640" s="5" t="n">
-        <v>1421</v>
+        <v>1428</v>
       </c>
       <c r="J640" s="5" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
 Financial literacy arrives in elementary schools as an unfunded expectation. The mandates were written for high school, the materials were written for high school, and then somebody hands you six-year-olds and a poster of a pig.
 Here is what I think everyone got backwards. Every children's money book teaches saving — I checked all 25 on the ABA Foundation's list. But a six-year-old does not save. A six-year-old stands in an aisle with five dollars and decides. The cash register comes before the piggy bank.
 So the book teaches spending. One purchase, start to finish: read the ad, compare two robots on a shelf, take the marked-down one on purpose, hand over a coupon, then discover sales tax and object to it.
-The part that matters for a principal: the whole toolkit is free. Four 45-minute lesson plans, a pre/post assessment with the answer key, a 23-row standards crosswalk. No login, no email capture, nothing consumable to reorder. You can hand a teacher the entire thing on a Friday and it costs the building nothing.
+The part that matters for a principal: the whole classroom pack is free. Four 45-minute lesson plans, a pre/post assessment with the answer key, a 23-row standards crosswalk. No login, no email capture, nothing consumable to reorder. You can hand a teacher the entire thing on a Friday and it costs the building nothing.
 Endorsed by Wally Luckeydoo, Ed.D., 2026 EIFLE Educator of the Year, and built with a K-5 teacher of 30+ years who told me what to cut.
 I am not after an endorsement. I want to know whether a principal would actually use it, or whether it dies in a staff room like most things do.
 Jonathan Bach</t>
@@ -25808,7 +25808,7 @@
         </is>
       </c>
       <c r="I641" s="5" t="n">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="J641" s="5" t="inlineStr">
         <is>
@@ -25816,7 +25816,7 @@
 Financial literacy mandates keep passing. Most states have one now. Almost every one of them lands in high school, where the money is, the graduation requirement is, and the political credit is.
 Which leaves elementary principals holding an expectation with no mandate, no funding, and no materials — because the publishers followed the money to ninth grade too. I read all 25 titles on the ABA Foundation's children's list. Every one teaches saving. None teaches the transaction a six-year-old actually performs, which is spending.
 The research keeps saying money habits form by seven. The policy keeps arriving at fourteen. That gap is a story your members live inside.
-I wrote a K-5 book for it and gave the classroom toolkit away free, which is my interest declared. But the advocacy point stands whether or not you ever look at the book: elementary is doing financial literacy work nobody funded and nobody wrote for.
+I wrote a K-5 book for it and gave the classroom lesson set away free, which is my interest declared. But the advocacy point stands whether or not you ever look at the book: elementary is doing financial literacy work nobody funded and nobody wrote for.
 Happy to send anything useful, including the standards crosswalk, if it helps make that case somewhere.
 Jonathan Bach</t>
         </is>
@@ -25864,7 +25864,7 @@
         </is>
       </c>
       <c r="I642" s="5" t="n">
-        <v>1703</v>
+        <v>1713</v>
       </c>
       <c r="J642" s="5" t="inlineStr">
         <is>
@@ -25873,7 +25873,7 @@
 You spent years at NAEYC on developmentally appropriate practice. So you already know the argument I am about to make, probably better than I do: what a child can do comes before what a child should do.
 Children's financial literacy has ignored that for forty years. I read all 25 titles on the ABA Foundation's list to be sure. Every one teaches saving. Save your pennies, save for a rainy day, save, save, save. Not one teaches spending.
 But a six-year-old does not save. A six-year-old stands in an aisle holding five dollars, looking at a thing, deciding. That is the transaction they actually perform, and we have been teaching the other one first.
-So I wrote the book for the register instead of the piggy bank. A boy earns a robot, reads the sale ad at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, and then meets sales tax for the first time and takes it personally. Thirty-six pages, grades 1-5, and the classroom toolkit behind it is free and ungated.
+So I wrote the book for the register instead of the piggy bank. A boy earns a robot, reads the sale ad at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, and then meets sales tax for the first time and takes it personally. Thirty-six pages, grades 1-5, and the classroom teacher materials behind it is free and ungated.
 Wally Luckeydoo, Ed.D., endorsed it. He was named 2026 EIFLE Educator of the Year and took the Jump$tart Corey Carlisle Award the same year, which suggests he was not being polite.
 I am not asking NAESP for anything yet. I am asking whether the developmental argument holds, because if it does not, you are the person best placed to tell me so and save me a great deal of confident talking.
 Jonathan Bach
@@ -26939,10 +26939,10 @@
 Sample: https://heyzine.com/flip-book/eeb1ef6cff.html
 ----- Jump$tart version -----
 Dr. Russell — I wrote to you a while back about a K-5 book on spending. This is a different and much smaller ask, and it will take you ninety seconds to decide.
-I'm applying to list a free classroom toolkit in the Jump$tart Clearinghouse. Provider eligibility runs through a letter of reference, and I'm choosing signers carefully rather than casting wide.
+I'm applying to list a free classroom classroom pack in the Jump$tart Clearinghouse. Provider eligibility runs through a letter of reference, and I'm choosing signers carefully rather than casting wide.
 Three reasons it's you. You hold the AFC credential, and AFCPE has a seat on the Jump$tart board. You ran Money Smart at Maryland Extension, and Land Grant and Cooperative Extension has a seat. You led youth financial health philanthropy at the Wells Fargo Foundation, and Wells Fargo has a seat. Three of twenty-four seats sit next to your career. I'd rather say that out loud than pretend I picked you at random.
 The resource: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the National Standards for Personal Financial Education and four other frameworks, printable classroom pieces, and a browser-based register where a kid rings up a markdown, a coupon, and sales tax. Free, ungated, no account. It sits behind a 36-page picture book for grades 1-5.
-I'm not asking you to endorse the book. I'm asking whether you'd look at the toolkit and, if it holds up, say so in a paragraph. If it doesn't hold up, that's a more useful answer and I'd take it.
+I'm not asking you to endorse the book. I'm asking whether you'd look at the classroom pack and, if it holds up, say so in a paragraph. If it doesn't hold up, that's a more useful answer and I'd take it.
 Jonathan Bach
 Baltimore
 clarencegetsabargain.com</t>
@@ -26990,7 +26990,7 @@
       <c r="G661" s="5" t="inlineStr"/>
       <c r="H661" s="5" t="inlineStr"/>
       <c r="I661" s="5" t="n">
-        <v>2002</v>
+        <v>2014</v>
       </c>
       <c r="J661" s="5" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
 I'm not asking you to endorse it. I'm asking whether an elementary principal would genuinely use it, or whether it's one more thing that sounds good and dies in a staff room. You have the kindergarten memory and the building to answer that honestly, which is a rare combination.
 Also, we're practically neighbors — I'm in Baltimore, you're up the road in Howard County. Coffee travels better than a link if you'd rather.
 Concepts and specs: https://clarencegetsabargain.com/book-facts.html
-Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html
+Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html
 Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
@@ -27103,7 +27103,7 @@
         </is>
       </c>
       <c r="I663" s="5" t="n">
-        <v>1906</v>
+        <v>1918</v>
       </c>
       <c r="J663" s="5" t="inlineStr">
         <is>
@@ -27111,9 +27111,9 @@
 I'd like to list a free K-5 classroom resource. Reading the Provider criteria, I don't meet the first three routes — I'm not a National Partner, I've never listed before, and Jump$tart has no reason to know me. That leaves the letter of reference, and the criteria say you'll provide instructions if one is required.
 So: what would you like that letter to say, and who would you like it from?
 I ask because I have a choice worth making well. One possible signer is Wally Luckeydoo, Ed.D., who received the 2026 Jump$tart Corey Carlisle Award. Another is Bonnie Meszaros at the University of Delaware, who co-authored the National Standards for Financial Literacy. I'd rather send you the one you'd find useful than the one I happen to like.
-What I'd be listing, briefly. Clarence Gets a Bargain is a 36-page picture book for grades 1-5 about a boy who earns a robot, reads the sale ads, compares two models, redeems a coupon at the register, and meets sales tax. The resource I want listed first is not the book — it's the free classroom toolkit behind it: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the National Standards for Personal Financial Education and four other frameworks, printable classroom pieces, and a browser-based pretend register.
+What I'd be listing, briefly. Clarence Gets a Bargain is a 36-page picture book for grades 1-5 about a boy who earns a robot, reads the sale ads, compares two models, redeems a coupon at the register, and meets sales tax. The resource I want listed first is not the book — it's the free classroom teaching pack behind it: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the National Standards for Personal Financial Education and four other frameworks, printable classroom pieces, and a browser-based pretend register.
 All of it is free, ungated, and needs no account or email address. Anyone in the country can print it in about a minute. clarencegetsabargain.com
-One thing I'd rather raise than have you find. The toolkit is free and the book it accompanies is $19.99. I read that against the commerce exclusion and I believe footnote 1 covers it — "a free resource can promote a paid upgrade." If you read it differently, I'd rather know now than after a review.
+One thing I'd rather raise than have you find. The teaching pack is free and the book it accompanies is $19.99. I read that against the commerce exclusion and I believe footnote 1 covers it — "a free resource can promote a paid upgrade." If you read it differently, I'd rather know now than after a review.
 Jonathan Bach
 Baltimore</t>
         </is>
@@ -27157,12 +27157,12 @@
         </is>
       </c>
       <c r="I664" s="5" t="n">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="J664" s="5" t="inlineStr">
         <is>
           <t>Wally — a favor, and you can say no without it costing us anything.
-I'm applying to list the Clarence toolkit in the Jump$tart Clearinghouse. To get in the door as a Provider, I need a letter of reference attesting to reputation and viability, because I'm not a National Partner and Jump$tart has no reason to know who I am.
+I'm applying to list the Clarence teacher pack in the Jump$tart Clearinghouse. To get in the door as a Provider, I need a letter of reference attesting to reputation and viability, because I'm not a National Partner and Jump$tart has no reason to know who I am.
 You took the Corey Carlisle Award from them this year. A letter from you is worth more than anything I could write about myself, and it isn't asking you to say anything you haven't already said — you endorsed the book on the merits before any of this came up.
 I've drafted something below so you're not staring at a blank page. Change every word of it if you want, or write two sentences of your own, which would probably be better.
 If you'd rather not, say so plainly and it goes no further. I have other people to ask and I would rather have a friend than a signature.
@@ -27442,11 +27442,11 @@
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="n">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>Tim — NGPF owns 9-12 and does it better than anyone. I wrote the K-5 on-ramp: a picture book where a kid runs one real purchase, ad to register, sales tax and all. Genuine question rather than a pitch — do you see elementary as in scope for NGPF, or a gap somebody else has to fill? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tim — NGPF owns 9-12 and does it better than anyone. I wrote the K-5 on-ramp: a picture book where a kid runs one real purchase, ad to register, sales tax and all. Genuine question rather than a pitch — do you see elementary as in scope for NGPF, or a gap somebody else has to fill? Teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr"/>
@@ -27626,11 +27626,11 @@
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="n">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Joel — no login, no email capture, no funnel. Four 45-minute lesson plans, a pre/post assessment with the answer key, and a 23-row crosswalk, all built against the National Standards and all free. I'd like it in the Clearinghouse. Does it clear the bar as you read the criteria? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Joel — no login, no email capture, no funnel. Four 45-minute lesson plans, a pre/post assessment with the answer key, and a 23-row crosswalk, all built against the National Standards and all free. I'd like it in the Clearinghouse. Does it clear the bar as you read the criteria? Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr"/>
@@ -27764,11 +27764,11 @@
       <c r="G11" s="5" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="n">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Yanely — you've said the gaps show up long before high school. I wrote the K-5 version, and it teaches spending because that's the transaction a six-year-old actually performs. Does NGPF ever point teachers below ninth grade, or is that outside the remit? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Yanely — you've said the gaps show up long before high school. I wrote the K-5 version, and it teaches spending because that's the transaction a six-year-old actually performs. Does NGPF ever point teachers below ninth grade, or is that outside the remit? For teachers: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr"/>
@@ -27810,11 +27810,11 @@
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="n">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Leslie — a Bookshelf question, not a pitch. The Money as You Grow selections skew toward saving and earning. Mine teaches the transaction itself, right through the register. Is the shelf still open, and who does the evaluating? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Leslie — a Bookshelf question, not a pitch. The Money as You Grow selections skew toward saving and earning. Mine teaches the transaction itself, right through the register. Is the shelf still open, and who does the evaluating? The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -27824,7 +27824,7 @@
 Here is the piece I keep circling. The moment a kid makes that first purchase, they have entered a relationship that comes with rights, and nobody teaches a seven-year-old they have any. An adult knows to keep the receipt and that a broken thing can go back. A child thinks the deal ends when the bag is handed over.
 I know the full rights picture crosses agencies — warranties and returns are FTC, product safety is CPSC. I'm not asking CFPB to cover those. I'm asking whether there's appetite within Money as You Grow for material that treats the child as a consumer with standing on the financial side, the day they first spend, rather than only as a saver in training.
 Realistic version of the ask: is the Bookshelf still evaluating titles, and who owns it now? And if the framing above is interesting, I'd trade ten minutes for your read on it.
-Toolkit: https://clarencegetsabargain.com/educator-toolkit.html
+The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html
 The book in four minutes: https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
         </is>
@@ -27871,11 +27871,11 @@
       <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="n">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Ken — my book and its free K-5 toolkit are aligned to Money Smart for Young People, with a crosswalk mapping every concept to the specific standard rather than asking you to take my word. Is there a process for a title to sit alongside Money Smart materials, or is that not how it works? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ken — my book and its free K-5 classroom materials are aligned to Money Smart for Young People, with a crosswalk mapping every concept to the specific standard rather than asking you to take my word. Is there a process for a title to sit alongside Money Smart materials, or is that not how it works? Print it here: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr"/>
@@ -28009,11 +28009,11 @@
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="5" t="n">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Lyn — is the Money as You Grow Bookshelf still taking titles? Mine is K-5 and teaches spending: comparison shopping, markdowns, coupons, sales tax at the register. The current shelf leans heavily toward saving. Happy to send it to whoever evaluates. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Lyn — is the Money as You Grow Bookshelf still taking titles? Mine is K-5 and teaches spending: comparison shopping, markdowns, coupons, sales tax at the register. The current shelf leans heavily toward saving. Happy to send it to whoever evaluates. Teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr"/>
@@ -28117,11 +28117,11 @@
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="n">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Tracy — a public-private partnership is how a K-5 resource actually scales, since elementary rarely gets its own budget line. It's a 36-page picture book plus free ungated toolkit against five frameworks. Fit inside the partnership? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tracy — a public-private partnership is how a K-5 resource actually scales, since elementary rarely gets its own budget line. It's a 36-page picture book plus free ungated teacher pack against five frameworks. Fit inside the partnership? Teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr"/>
@@ -28209,11 +28209,11 @@
       <c r="G20" s="5" t="inlineStr"/>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="n">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Bill — Tennessee's commission decides what reaches classrooms statewide, and elementary is usually where state mandates run thin. Mine is a K-5 picture book with a free zero-prep toolkit against Jump$tart, CEE, Common Core, and FDIC Money Smart. Route to get it in front of the commission? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Bill — Tennessee's commission decides what reaches classrooms statewide, and elementary is usually where state mandates run thin. Mine is a K-5 picture book with a free zero-prep classroom pack against Jump$tart, CEE, Common Core, and FDIC Money Smart. Route to get it in front of the commission? Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr"/>
@@ -28255,11 +28255,11 @@
       <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="n">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Dave — Wisconsin has been at this longer than most states. My K-5 book and free toolkit map to five frameworks. Elementary tends to be the underserved band everywhere I look. Is there a submission route, or a person who reviews outside materials? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dave — Wisconsin has been at this longer than most states. My K-5 book and free lesson set map to five frameworks. Elementary tends to be the underserved band everywhere I look. Is there a submission route, or a person who reviews outside materials? For teachers: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr"/>
@@ -28301,11 +28301,11 @@
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="n">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Hunter — policy and advocacy at NEFE puts you where the K-5 gap is most visible. Nearly everything funded sits at high school. I wrote a picture book plus free toolkit for grades 1-5 against five frameworks. Is early elementary getting any policy attention, or still an orphan? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hunter — policy and advocacy at NEFE puts you where the K-5 gap is most visible. Nearly everything funded sits at high school. I wrote a picture book plus free teacher materials for grades 1-5 against five frameworks. Is early elementary getting any policy attention, or still an orphan? The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr"/>
@@ -28715,11 +28715,11 @@
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="n">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Bethann — a bankers association reaches classrooms and families at once, which is the distribution a K-5 book needs and rarely gets. Mine is five frameworks, free zero-prep lessons, plus a grant packet if a member bank wanted to fund classroom sets. Fit Utah's outreach? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Bethann — a bankers association reaches classrooms and families at once, which is the distribution a K-5 book needs and rarely gets. Mine is five frameworks, free zero-prep lessons, plus a grant packet if a member bank wanted to fund classroom sets. Fit Utah's outreach? Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr"/>
@@ -28807,11 +28807,11 @@
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="n">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Ruben — my book and toolkit are aligned to the CEE standards with a full crosswalk. Is there a route for a K-5 title into CEE's resource library or EconEdLink, and what would you want to see first? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ruben — my book and teaching pack are aligned to the CEE standards with a full crosswalk. Is there a route for a K-5 title into CEE's resource library or EconEdLink, and what would you want to see first? Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr"/>
@@ -28991,11 +28991,11 @@
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Jillian — Intuit for Education is built around real financial decisions, which is my book's entire structure: one purchase, ad to register, sales tax included. Mine sits at K-5, below your usual band. Does the framing match how you think about curriculum? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jillian — Intuit for Education is built around real financial decisions, which is my book's entire structure: one purchase, ad to register, sales tax included. Mine sits at K-5, below your usual band. Does the framing match how you think about curriculum? Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr"/>
@@ -29037,11 +29037,11 @@
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="n">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Saskia — Promise Academy is deliberate about what earns classroom time, which is the right instinct. Mine teaches the complete purchase, sales tax included, and the family activity was built for a kitchen table. Classrooms or family programming — or neither? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Saskia — Promise Academy is deliberate about what earns classroom time, which is the right instinct. Mine teaches the complete purchase, sales tax included, and the family activity was built for a kitchen table. Classrooms or family programming — or neither? Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr"/>
@@ -29267,11 +29267,11 @@
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr"/>
       <c r="I43" s="5" t="n">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Dr. Taylor — Montgomery County sets what reaches a lot of classrooms. Mine is a K-5 picture book with a free zero-prep toolkit, five frameworks, nothing consumable to reorder next August. The honest question is placement rather than merit: classroom, library, or family night? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Taylor — Montgomery County sets what reaches a lot of classrooms. Mine is a K-5 picture book with a free zero-prep lesson set, five frameworks, nothing consumable to reorder next August. The honest question is placement rather than merit: classroom, library, or family night? Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr"/>
@@ -29313,11 +29313,11 @@
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="n">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Beth — a research question. My K-5 book argues spending competence precedes saving competence developmentally, which would mean the field teaches the wrong skill first. Does that square with your research and impact work, or am I overstating a tidy story? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Beth — a research question. My K-5 book argues spending competence precedes saving competence developmentally, which would mean the field teaches the wrong skill first. Does that square with your research and impact work, or am I overstating a tidy story? The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr"/>
@@ -29405,11 +29405,11 @@
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="n">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Vince — NFEC reaches thousands of instructors, and K-5 is where most of them have the least to hand anyone. Mine runs 36 pages plus free toolkit against five frameworks, crosswalk included. Route into the NFEC resource network? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Vince — NFEC reaches thousands of instructors, and K-5 is where most of them have the least to hand anyone. Mine runs 36 pages plus free classroom materials against five frameworks, crosswalk included. Route into the NFEC resource network? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr"/>
@@ -29451,11 +29451,11 @@
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="n">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Billy — a NEFE-shaped question. The research keeps saying money attitudes form by seven, and almost every dollar of material lands at 9-12. I wrote a K-5 picture book teaching spending rather than saving. Does NEFE ever point people to elementary, or is that band still nobody's mandate? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Billy — a NEFE-shaped question. The research keeps saying money attitudes form by seven, and almost every dollar of material lands at 9-12. I wrote a K-5 picture book teaching spending rather than saving. Does NEFE ever point people to elementary, or is that band still nobody's mandate? Teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr"/>
@@ -29497,11 +29497,11 @@
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="n">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Laura — a Clearinghouse question rather than a pitch. My K-5 toolkit is built against the National Standards, free, ungated, no email capture and no drip campaign. Is Suzann Knight the right first stop, or is there a step I'm skipping? Wally Luckeydoo endorsed the book, which I mention only because he's your 2026 Corey Carlisle recipient. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Laura — a Clearinghouse question rather than a pitch. My K-5 teacher pack is built against the National Standards, free, ungated, no email capture and no drip campaign. Is Suzann Knight the right first stop, or is there a step I'm skipping? Wally Luckeydoo endorsed the book, which I mention only because he's your 2026 Corey Carlisle recipient. Teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr"/>
@@ -29829,11 +29829,11 @@
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="n">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Andrea — as a research director you'll want the claim before the book. Mine: consumer transaction competence is taught almost nowhere in K-5. I built a picture book and free toolkit around it. Evidence against? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Andrea — as a research director you'll want the claim before the book. Mine: consumer transaction competence is taught almost nowhere in K-5. I built a picture book and free teacher pack around it. Evidence against? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
@@ -29841,7 +29841,7 @@
           <t>Dr. Sticha — you sit on the Jump$tart board for the Stanford Initiative on Financial Decision-Making, and your research is household financial literacy and wellbeing. So this is a research question with a book attached, rather than the reverse.
 Here is what I ran into. Almost every children's financial literacy book teaches saving. I read the entire ABA Foundation list to be sure. Piggy banks, jars, lemonade stands, wait for it.
 But no seven-year-old has a savings rate. Every seven-year-old has stood in a store holding money and had to choose. The first financial decision a person ever makes is a purchase, and the literature written for them starts one step later.
-I wrote the K-5 book for that step. Thirty-six pages, grades 1-5. A boy earns a robot, reads the sale ads, compares two models on a shelf, takes the marked-down one on purpose, redeems a coupon at the register, and meets sales tax. Sixteen-plus concepts, a 21-term glossary, and a free ungated teacher toolkit crosswalked to the National Standards for Personal Financial Education.
+I wrote the K-5 book for that step. Thirty-six pages, grades 1-5. A boy earns a robot, reads the sale ads, compares two models on a shelf, takes the marked-down one on purpose, redeems a coupon at the register, and meets sales tax. Sixteen-plus concepts, a 21-term glossary, and a free ungated teacher lesson set crosswalked to the National Standards for Personal Financial Education.
 The question I'd actually like answered: is there research on financial decision-making in the first five school years, or does the evidence base start in adolescence the same way the books do? If it starts late, that's a finding, and it's one your initiative is better placed to say out loud than I am.
 Jonathan Bach
 Baltimore
@@ -29937,11 +29937,11 @@
       <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr"/>
       <c r="I57" s="5" t="n">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Flora — JA reaches more kids than almost anybody, and elementary is usually where the material thins out. Mine is a K-5 picture book with a free zero-prep toolkit against five frameworks, teaching spending rather than saving. Fit anything JA Alaska runs? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Flora — JA reaches more kids than almost anybody, and elementary is usually where the material thins out. Mine is a K-5 picture book with a free zero-prep classroom pack against five frameworks, teaching spending rather than saving. Fit anything JA Alaska runs? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr"/>
@@ -30305,11 +30305,11 @@
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="n">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Sandy — FCCLA members are a decade older than my readers, so this is not a curriculum pitch. It's a service-project one. Your chapters already run community work, and a high schooler reading a money book to a second-grade class is about the cleanest version of that I can think of. Mine is 36 pages, teaches the whole purchase through the register, and the toolkit behind it is free. Does that fit how chapters choose projects, or am I inventing a use case? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sandy — FCCLA members are a decade older than my readers, so this is not a curriculum pitch. It's a service-project one. Your chapters already run community work, and a high schooler reading a money book to a second-grade class is about the cleanest version of that I can think of. Mine is 36 pages, teaches the whole purchase through the register, and the classroom pack behind it is free. Does that fit how chapters choose projects, or am I inventing a use case? Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr"/>
@@ -30351,11 +30351,11 @@
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="n">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Megan — Econiful starts at grade 6, which puts my book directly underneath you rather than beside you. Mine is the K-5 on-ramp: a six-year-old runs one purchase, ad to register, sales tax at the end. Congratulations on the Rising Star, by the way. Genuine question rather than a pitch — do you see elementary as in scope for Econiful, or a gap somebody else has to fill? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Megan — Econiful starts at grade 6, which puts my book directly underneath you rather than beside you. Mine is the K-5 on-ramp: a six-year-old runs one purchase, ad to register, sales tax at the end. Congratulations on the Rising Star, by the way. Genuine question rather than a pitch — do you see elementary as in scope for Econiful, or a gap somebody else has to fill? For teachers: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr"/>
@@ -30535,7 +30535,7 @@
       <c r="G70" s="5" t="inlineStr"/>
       <c r="H70" s="5" t="inlineStr"/>
       <c r="I70" s="5" t="n">
-        <v>1409</v>
+        <v>1414</v>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
 I'm writing because you're the Eastern Shore rep for MAESP and I'm down your way often — I spend a good part of the year in Rehoboth, so Greensboro is nearly the neighborhood.
 I wrote and illustrated a K-5 book about money that does the one thing the rest of the shelf skips. Every other kids' money book teaches saving. Mine teaches a purchase — a boy earns a robot, reads the sale ads, compares two models, takes the marked-down one on purpose, hands a coupon to the cashier, and runs face-first into sales tax. Sixteen-plus concepts, none of them announced as a lesson.
 Here is why I'm writing you and not a longer list. MAESP recognized you as a Connected School Leader for actually using the digital tools, and the entire teacher kit behind the book is free, ungated, and prints from a browser — four lesson plans, assessments with answer keys, a standards crosswalk. No account, no budget line. It is exactly the kind of thing that dies in a staff room unless a principal who gets it hands it over.
-Would it be useful on the Eastern Shore, or am I overreaching? Toolkit: clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html
+Would it be useful on the Eastern Shore, or am I overreaching? Teacher pack: clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
         </is>
       </c>
@@ -30847,10 +30847,10 @@
 Sample: https://heyzine.com/flip-book/eeb1ef6cff.html
 ----- Jump$tart version -----
 Dr. Russell — I wrote to you a while back about a K-5 book on spending. This is a different and much smaller ask, and it will take you ninety seconds to decide.
-I'm applying to list a free classroom toolkit in the Jump$tart Clearinghouse. Provider eligibility runs through a letter of reference, and I'm choosing signers carefully rather than casting wide.
+I'm applying to list a free classroom classroom pack in the Jump$tart Clearinghouse. Provider eligibility runs through a letter of reference, and I'm choosing signers carefully rather than casting wide.
 Three reasons it's you. You hold the AFC credential, and AFCPE has a seat on the Jump$tart board. You ran Money Smart at Maryland Extension, and Land Grant and Cooperative Extension has a seat. You led youth financial health philanthropy at the Wells Fargo Foundation, and Wells Fargo has a seat. Three of twenty-four seats sit next to your career. I'd rather say that out loud than pretend I picked you at random.
 The resource: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the National Standards for Personal Financial Education and four other frameworks, printable classroom pieces, and a browser-based register where a kid rings up a markdown, a coupon, and sales tax. Free, ungated, no account. It sits behind a 36-page picture book for grades 1-5.
-I'm not asking you to endorse the book. I'm asking whether you'd look at the toolkit and, if it holds up, say so in a paragraph. If it doesn't hold up, that's a more useful answer and I'd take it.
+I'm not asking you to endorse the book. I'm asking whether you'd look at the classroom pack and, if it holds up, say so in a paragraph. If it doesn't hold up, that's a more useful answer and I'd take it.
 Jonathan Bach
 Baltimore
 clarencegetsabargain.com</t>
@@ -30898,7 +30898,7 @@
       <c r="G76" s="5" t="inlineStr"/>
       <c r="H76" s="5" t="inlineStr"/>
       <c r="I76" s="5" t="n">
-        <v>2002</v>
+        <v>2014</v>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
 I'm not asking you to endorse it. I'm asking whether an elementary principal would genuinely use it, or whether it's one more thing that sounds good and dies in a staff room. You have the kindergarten memory and the building to answer that honestly, which is a rare combination.
 Also, we're practically neighbors — I'm in Baltimore, you're up the road in Howard County. Coffee travels better than a link if you'd rather.
 Concepts and specs: https://clarencegetsabargain.com/book-facts.html
-Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html
+Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html
 Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>

--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -26782,12 +26782,12 @@
       </c>
       <c r="C658" s="5" t="inlineStr">
         <is>
-          <t>James Wilson — Browseabout Books</t>
+          <t>Browseabout Books — ⛔ DO NOT SEND</t>
         </is>
       </c>
       <c r="D658" s="5" t="inlineStr">
         <is>
-          <t>Events Coordinator, Browseabout Books</t>
+          <t>They already rejected the book.</t>
         </is>
       </c>
       <c r="E658" s="5" t="inlineStr"/>
@@ -26826,10 +26826,14 @@
       <c r="K658" s="5" t="inlineStr"/>
       <c r="L658" s="5" t="inlineStr">
         <is>
-          <t>Now. Summer is their season and a kids' event needs lead time.</t>
-        </is>
-      </c>
-      <c r="M658" s="5" t="inlineStr"/>
+          <t>⛔ DO NOT SEND — already declined the book without reading it (AI alleged from a cover thumbnail). See letters-delaware.md #17.</t>
+        </is>
+      </c>
+      <c r="M658" s="5" t="inlineStr">
+        <is>
+          <t>DEAD</t>
+        </is>
+      </c>
       <c r="N658" s="5" t="inlineStr"/>
     </row>
     <row r="659">

--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master'!$A$1:$N$665</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Whales'!$A$1:$N$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Whales'!$A$1:$N$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deadlines'!$A$1:$H$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Physical copies'!$A$1:$D$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'86ed'!$A$1:$C$12</definedName>
@@ -744,8 +744,22 @@
           <t>Alex — I read a dozen kids' money books to see where mine fit. Every one taught saving. Save your pennies, save for a rainy day, save, save, save. Not one covered the moment a kid stands there with his own five bucks deciding if the thing is worth it. Am I qualified to fix that? Debatable. I did once pay one cent for a $293 pair of shoes, and I kept the tag. Not a typo. Mine runs that whole gauntlet — ad, aisle, markdown, coupon, and the sales tax nobody warns a six-year-old about. Segment, or am I picking a fight the category doesn't want? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr"/>
-      <c r="L2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Alex — Planet Money's whole trick is that people will absorb an economics lesson if you hide it inside a story about a guy and a barrel of oil. I did the same thing at a lower reading level.
+Here is the pitch in one line: every children's money book teaches saving, and saving is the second thing a kid does with money. The first is spending. A six-year-old has no savings rate. She has stood in an aisle holding a birthday five, deciding whether the thing is worth it.
+So I wrote the spending one. Clarence Gets a Bargain follows a single purchase the entire way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, gets ambushed by sales tax, and then lives with the thing he bought. Idea to post-receipt. I read every title on the ABA Foundation's children's financial literacy list to check, and not one follows a purchase the whole way through.
+Sixteen-plus concepts are in there and none of them are announced. Nobody says the word "budget." They don't realise they've been schooled until they hit the glossary — twenty-one terms in the back, each page-referenced to the moment it actually happened. That's where the con comes apart, on purpose.
+The segment I'd pitch is not the book. It's the forty-year hole: why an entire publishing category skipped the cash register. There is a Planet Money episode in that whether or not mine is the book that gets mentioned.
+Am I wrong that it's a story? clarencegetsabargain.com/book-facts.html has the specs. Four-minute flip: https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M2" s="5" t="inlineStr"/>
       <c r="N2" s="5" t="inlineStr"/>
     </row>
@@ -790,8 +804,23 @@
           <t>Tami — an award-winning picture book author is the read I want most, because my worry is craft, not content. The money lesson works. What I don't know is whether 36 pages about one shopping trip holds a kid on its own merits. Would you read it as a writer rather than a subject expert? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Tami — author to author, and I'd rather you heard this from me than found it on a shelf.
+I wrote and illustrated a picture book about money, which sounds like the most airless premise in children's publishing, so let me tell you the one thing that makes it not that.
+Every book in this category teaches saving. Piggy banks, jars, be patient, wait. But saving is the second thing a child does with money. The first is spending, and nobody had written that book. So mine follows one purchase from beginning to end — a boy wants a robot, earns it, works the sale ads at the kitchen table, compares two models in the aisle, takes the cheaper one deliberately, hands a coupon to the cashier, meets sales tax and takes it personally, and then has to live with what he chose.
+The part I think you'll appreciate as a craftsperson: none of the sixteen-plus concepts is ever announced. There is no worksheet voice, no character stopping to explain a term. It is smuggled. A kid does not know he's been schooled until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. That is the moment the book admits what it was doing, and it is the last page rather than the first.
+I did the illustrations too, which means I have opinions about it that are worth exactly nothing.
+Would you look at it and tell me where the seams show? I'd trade — send me yours and I'll read it properly, not politely.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M3" s="5" t="inlineStr"/>
       <c r="N3" s="5" t="inlineStr"/>
     </row>
@@ -836,8 +865,22 @@
           <t>Tim — NGPF owns 9-12 and does it better than anyone. I wrote the K-5 on-ramp: a picture book where a kid runs one real purchase, ad to register, sales tax and all. Genuine question rather than a pitch — do you see elementary as in scope for NGPF, or a gap somebody else has to fill? Teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Tim — NGPF owns 9-12 and does it better than anyone, so this is not a pitch into your territory. It is a question about the floor beneath it.
+Every state that mandates personal finance mandates it in high school. Delaware just became the thirtieth and put the course in front of ninth graders. Fine as far as it goes. But the money behaviors NGPF is correcting at sixteen were installed at six, in a store, with a parent saying no.
+The sequence is what I keep coming back to. Financial education starts with saving, and saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has stood at a register and chosen.
+I wrote the K-5 on-ramp. One purchase, followed the whole distance — wanting a robot, earning it, working the sale inserts at the kitchen table, comparing two on a shelf, taking the cheaper one on purpose, redeeming a coupon, meeting sales tax, and living with the choice. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; none does the full arc. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced back into the story.
+The real question, rather than the ask: does NGPF consider elementary in scope, or is it a gap you have consciously left to somebody else? Either answer is useful to me, and the second one tells me whether I'm building alone.
+Everything free and ungated: clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M4" s="5" t="inlineStr"/>
       <c r="N4" s="5" t="inlineStr"/>
     </row>
@@ -882,8 +925,22 @@
           <t>Paula — "You can afford anything, but not everything," translated for six-year-olds. Kid earns a robot. Finds the marked-down older model. Slightly smaller screen, no antenna. He takes it anyway and can tell you why. That's the climax — a first grader choosing the cheaper thing on purpose, which is more than most adults manage on Prime Day. Would your crowd want the version they can hand a kid? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr"/>
-      <c r="L5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Paula — "you can afford anything, but not everything" is the best sentence anybody has written about money, and it is a sentence about spending, not saving. That is the entire reason I'm writing to you.
+I wrote the children's version of that idea, and I mean that structurally rather than as a compliment. Every kids' money book teaches saving. But saving is the second thing a child does with money — the first is spending, and a six-year-old has already done it, holding a birthday five in an aisle, working out whether the thing is worth what it costs. Which is your thesis at a lower reading level.
+Clarence Gets a Bargain follows one purchase the whole way. A boy wants a robot. Earns it with chores and grades. Reads the newspaper sale inserts at the kitchen table. Compares two models on a shelf and takes the cheaper one on purpose. Hands a coupon to the cashier. Meets sales tax and regards it as a personal insult, correctly. Then lives with what he chose — which is the opportunity-cost half nobody writes for kids.
+The craft bit: none of it is announced. Sixteen-plus concepts, and nobody in the book says the word "budget." A kid does not know he's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. Available, never assigned.
+Is there an episode in the fact that the entire children's money category skipped the cash register for forty years? I'd rather you took the argument than the book.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M5" s="5" t="inlineStr"/>
       <c r="N5" s="5" t="inlineStr"/>
     </row>
@@ -928,8 +985,22 @@
           <t>Kim — you've edited and reviewed more children's books than I'll ever write. Mine hides a financial education inside a story about a kid and a robot, and I think it works — which is exactly the judgment an author is least qualified to make about his own book. Would you read it as an editor? Happy to trade. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Kim — you review children's books for a living, so you have read more well-meaning money picture books than anyone should have to, and you already know the problem with them.
+They all teach saving. Every one. Which is fine advice and the wrong order, because saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate and has absolutely stood in a store holding money and had to decide.
+Mine is the spending one, and it follows a single purchase the whole distance rather than gesturing at the idea: a boy wants a robot, earns it with chores and grades, works the sale ads at the kitchen table, compares two models in the aisle, takes the cheaper one on purpose, hands a coupon to the cashier, gets hit with sales tax, and then has to live with the thing. Idea to post-receipt. I read all 25 on the ABA Foundation's list to be sure nobody had done it. Nobody had.
+What I'd actually want your eye on is the smuggling. Sixteen-plus concepts and not one of them is announced — no character stops to explain a term, nobody says "budget." The reader does not know he's been schooled until he reaches the glossary — twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than a homework appendix. The reveal is deliberate and it is on the last page. That balance is the hardest thing in the book and the thing most likely to be off by a hair.
+Would you read it as an editor rather than as a friend? I would rather hear where it sags than be told it's charming.
+clarencegetsabargain.com/press-kit.html · https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
     </row>
@@ -974,8 +1045,22 @@
           <t>Neale — you built this category. Money Doesn't Grow on Trees was on shelves before most of us were thinking about any of it. Mine leaves saving out entirely and teaches spending: one purchase, ad to register, sales tax included. You'd know inside ten pages whether that's a real gap or one I invented to justify a book I wanted to write anyway. Would you tell me straight? More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
-      <c r="L7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Neale — you built this category. Money Doesn't Grow on Trees was on the shelf before most of the people currently writing in it could read, so I'm not going to pretend I'm doing something you haven't thought about.
+What I think is still open is the sequence. The field starts children with saving, and saving is the second thing a person does with money. The first is spending. A six-year-old has no savings rate. She has stood in a store holding money and decided. We teach that last.
+So I went narrow and deep on one transaction. Clarence Gets a Bargain follows a single purchase from the idea to after the receipt — a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, redeems a coupon, meets sales tax, and then lives with what he bought. I read all 25 titles on the ABA Foundation's list; none covers the whole arc.
+The other thing, and it is the part I'd want your read on: nothing is announced. Sixteen-plus concepts, no worksheet voice, nobody in the book saying "budget." A child does not know he's been schooled until the glossary — twenty-one terms in the back, each page-referenced to the moment it happened. The book confesses on the last page or not at all. You would spot immediately whether that balance holds or whether I have hidden the lesson so well it isn't there.
+Author to author, I'd like to trade. Send me one of yours and I'll read it properly. And if you think the spending-first premise is wrong, that is worth more to me than a kind word about the illustrations.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M7" s="5" t="inlineStr"/>
       <c r="N7" s="5" t="inlineStr"/>
     </row>
@@ -1020,8 +1105,22 @@
           <t>Joel — no login, no email capture, no funnel. Four 45-minute lesson plans, a pre/post assessment with the answer key, and a 23-row crosswalk, all built against the National Standards and all free. I'd like it in the Clearinghouse. Does it clear the bar as you read the criteria? Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Joel — a specific question rather than a pitch, and it should take you a minute.
+I have a K-5 resource I would like to list in the Jump$tart Clearinghouse, and I have read the listing criteria closely enough to know which route applies to me. I am not a National Partner and have never listed before, so I would be applying under the letter-of-reference route.
+The resource is a free, ungated classroom set built around a 36-page picture book: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE, and FDIC Money Smart, printable classroom pieces, and a browser-based pretend register. No account, no email capture, no purchase order. It prints from a browser.
+What the book does that the category does not: it teaches spending rather than saving, and it follows one complete purchase from the idea through the receipt — sale ads, comparison, markdown, coupon, sales tax. Sixteen-plus concepts, a twenty-one-term glossary page-referenced to the story. The elementary grade band has standards and very little built against them.
+Two questions. Is the free classroom set the right thing to submit, rather than the book? And for the reference letter, would Wally Luckeydoo carry weight — he received your 2026 Corey Carlisle Award and endorsed the book before any of this came up.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M8" s="5" t="inlineStr"/>
       <c r="N8" s="5" t="inlineStr"/>
     </row>
@@ -1066,8 +1165,22 @@
           <t>Michelle — you've said for years the money talk should start before kids can spell it. So I wrote one for six-year-olds with no piggy bank in it. None. It's all spending: read the ad, compare two robots, hand over the coupon, then meet sales tax for the first time. Kids read it for the robot. The rest sneaks in. Column in a kids' money book that skips saving entirely? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr"/>
-      <c r="L9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Michelle — you have written for twenty years that the money conversation with children has to start early, and I wrote the book for the earliest version of it. One question at the end, and it is a column question rather than a book question.
+Every children's financial literacy book teaches saving. I read all 25 on the ABA Foundation's list to be certain. Piggy banks, jars, patience. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it — in a store, holding money, deciding whether the thing is worth what it costs.
+Mine follows one purchase the entire way. A boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he bought. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." Twenty-one terms in the glossary, each page-referenced to the scene it came from.
+The column, if there is one: an entire publishing category has taught children to save for forty years and skipped the cash register, which is the only place a child has ever actually handled money. That is a story about the field, not about me.
+clarencegetsabargain.com/press-kit.html
+Jonathan Bach
+Baltimore</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Subject: The kids' money book that skips the piggy bank · Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M9" s="5" t="inlineStr"/>
       <c r="N9" s="5" t="inlineStr"/>
     </row>
@@ -1112,8 +1225,22 @@
           <t>Cinders — you got four books out of Earn, Save, Spend, Give. I got greedy and spent all 36 pages on one of them. Spending. The whole transaction, right through the register, sales tax and the small indignity that follows. Author-illustrator to author-illustrator, I'd rather you heard it from me than found it on a shelf and squinted. Trade copies? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr"/>
-      <c r="L10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Cinders — Moneybunnies splits money into Earn, Save, Spend and Give, which makes you the one person in this category who already agreed with me before I showed up.
+I went deep on one of your four. Spending, and specifically the whole transaction rather than the idea of it. Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then has to live with what he picked. Idea to post-receipt.
+The reason I think it sits beside Moneybunnies rather than against it: you give a child the four categories, and mine walks them through the mechanics of one. Sixteen-plus concepts, none announced — nobody says "budget" — and twenty-one terms in a glossary in the back, each page-referenced to the scene where it happened.
+Author-illustrator to author-illustrator: I did the art as well, so I know exactly how much of the work nobody sees. I'd rather you saw this from me than off a shelf.
+Trade copies? I'll read yours properly and tell you the truth about it, which is the only thing worth trading.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M10" s="5" t="inlineStr"/>
       <c r="N10" s="5" t="inlineStr"/>
     </row>
@@ -1158,8 +1285,21 @@
           <t>Yanely — you've said the gaps show up long before high school. I wrote the K-5 version, and it teaches spending because that's the transaction a six-year-old actually performs. Does NGPF ever point teachers below ninth grade, or is that outside the remit? For teachers: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr"/>
-      <c r="L11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Yanely — you spend your time getting personal finance in front of teenagers, and I want to ask about the years before you get them.
+Every mandate lands in high school. Delaware just became the thirtieth state and put the course in ninth grade. But the habits being corrected at sixteen were installed at six, in a store, with a parent saying no. The sequence is the part I keep circling: financial education starts children with saving, and saving is the second thing a person does with money. The first is spending.
+I wrote the K-5 on-ramp — one purchase followed the whole way, from wanting a robot to living with it. Sale ads at the kitchen table, comparison on a shelf, a markdown taken on purpose, a coupon at the register, sales tax. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced back into the story. Free ungated classroom set behind it.
+Honest question rather than a pitch: when you talk to teachers, does elementary ever come up as something they want and cannot find? I am trying to work out whether I am filling a gap or inventing one.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Subject: The grade band below yours · Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M11" s="5" t="inlineStr"/>
       <c r="N11" s="5" t="inlineStr"/>
     </row>
@@ -1206,7 +1346,15 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>Leslie — I sent a short note a while back about the Money as You Grow Bookshelf. This is the idea behind the book, and it's the one I actually wanted to run past someone at CFPB.
+          <t>Leslie — a Money as You Grow question, and then an idea I'd like a CFPB read on.
+The question first. Is the Bookshelf still evaluating titles, and who owns it now? I have a K-5 picture book that teaches spending rather than saving, and the current shelf leans heavily toward saving.
+The idea. A child becomes a consumer the first time they hand money to a cashier. Not at eighteen, not at a first paycheck — at six, at a register, with a birthday five. Everything in youth financial education treats that child as a saver in training. Almost nothing treats her as what she already is: a party to a transaction.
+My book follows one purchase the entire way, which is the part I could not find anywhere else — from wanting the thing, through the sale ads, the comparison, the markdown, the coupon, and the sales tax, to living with what was bought. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in the glossary, each page-referenced to the scene where it happened.
+I know the full picture crosses agencies — warranties and returns are FTC, product safety is CPSC — and I am not asking CFPB to cover those. I am asking whether Money as You Grow has room for material that treats the child as a consumer on the financial side from the first purchase forward.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan
+----- CFPB/rights version -----
+Leslie — I sent a short note a while back about the Money as You Grow Bookshelf. This is the idea behind the book, and it's the one I actually wanted to run past someone at CFPB.
 A child becomes a consumer the first time they hand over money. Not at eighteen, not at a first paycheck — at six, at a register, with a birthday five in their fist. That is the whole premise of my book: a boy runs one complete purchase, sale ad to receipt, and picks up comparison shopping, markdowns, coupons, and sales tax on the way. Money as You Grow teaches saving and spending well. The transaction itself — the part where a kid is actually standing at the counter — is the gap the book fills, and the current shelf leans heavily toward saving.
 Here is the piece I keep circling. The moment a kid makes that first purchase, they have entered a relationship that comes with rights, and nobody teaches a seven-year-old they have any. An adult knows to keep the receipt and that a broken thing can go back. A child thinks the deal ends when the bag is handed over.
 I know the full rights picture crosses agencies — warranties and returns are FTC, product safety is CPSC. I'm not asking CFPB to cover those. I'm asking whether there's appetite within Money as You Grow for material that treats the child as a consumer with standing on the financial side, the day they first spend, rather than only as a saver in training.
@@ -1218,7 +1366,7 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>Long-form version from CFPB/rights</t>
+          <t>Long-form version from TOP25 wk1 | Long-form version from CFPB/rights</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr"/>
@@ -1265,8 +1413,22 @@
           <t>Ken — my book and its free K-5 classroom materials are aligned to Money Smart for Young People, with a crosswalk mapping every concept to the specific standard rather than asking you to take my word. Is there a process for a title to sit alongside Money Smart materials, or is that not how it works? Print it here: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr"/>
-      <c r="L13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Ken — a process question about Money Smart for Young People, asked by someone who has already done the alignment work.
+I built a free K-5 classroom set around a 36-page picture book and crosswalked it to Money Smart for Young People alongside the 2021 National Standards for Personal Financial Education, CEE, and Common Core Math and ELA. Twenty-three rows, concept by concept, with the Grade 4 benchmark codes rather than a general claim of alignment. It is on the site so a reviewer can check it instead of taking my word.
+What the book covers that Money Smart's book lists mostly do not: spending, and the complete transaction rather than the concept. One purchase followed from the idea to after the receipt — sale ads, comparison shopping, a markdown, a coupon at the register, sales tax, and then living with the thing bought. Sixteen-plus concepts, none announced in the text. A twenty-one-term glossary page-referenced back into the story.
+Everything for teachers is free and ungated. No account, no email capture, no purchase order.
+The question: is there a route for a title to sit alongside Money Smart materials, or is that not how the program works? Either answer saves me guessing.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M13" s="5" t="inlineStr"/>
       <c r="N13" s="5" t="inlineStr"/>
     </row>
@@ -1311,8 +1473,22 @@
           <t>Rishi — you passed the CFP at sixteen and built Easy Peasy Finance, so you get this without preamble. Mine teaches spending, not saving. By the last page a six-year-old has compared prices, caught a markdown, and paid sales tax. Fit anything you're building? Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr"/>
-      <c r="L14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Rishi — you passed the CFP exam at sixteen, which means you learned this material at an age when the rest of us were being told to save our allowance, so you are unusually well placed to tell me whether my premise is nonsense.
+The premise: financial education for children starts with saving, and the sequence is backwards. Saving is the second thing a person does with money. The first is spending. A six-year-old has no savings rate and has definitely stood in a store holding money, deciding.
+Easy Peasy Finance explains concepts to kids clearly, one at a time. I went the other way and hid them. Clarence Gets a Bargain follows a single purchase the whole distance — a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Sixteen-plus concepts and nobody in the book says "budget." The twenty-one-term glossary in the back is page-referenced to where each thing happened, which is the closest the book comes to admitting it was teaching anything.
+You explain; I smuggle. I think both work and I'd like to know if you disagree.
+Is there a version of this worth putting in front of your audience — a read-along, a segment, a mention? And separately: at sixteen, would this book have been too young for you, or exactly right for the you at six?
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M14" s="5" t="inlineStr"/>
       <c r="N14" s="5" t="inlineStr"/>
     </row>
@@ -1357,8 +1533,22 @@
           <t>Tiffany — Get Good with Money worked because you refused to talk down to anyone. I tried to hold that line for six-year-olds: real decision, real tradeoff, no moral bolted onto the last page. Mine leaves saving to everybody else. Would you tell me if it condescends? I'd rather hear it from you than from a seven-year-old. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr"/>
-      <c r="L15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Tiffany — you built a career on the thing nobody teaches: what to actually do, in order, with money that is already in your hand. That is why I'm writing about the six-year-old version.
+Every children's money book teaches saving. All 25 on the ABA Foundation's list — I checked. Piggy banks, jars, patience. But saving is the second thing a child does with money. The first is spending, and a first grader has already done it, in a store, holding a birthday five, working out whether the thing is worth what it costs.
+Mine is the spending one, and it follows a single purchase the whole way rather than talking about the idea: a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, gets hit with sales tax, and then lives with what he chose. Idea to post-receipt.
+The design choice: none of the sixteen-plus concepts is announced. Nobody in the book says "budget," which for a book that is largely about budgeting took some doing. The kid does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. There for the kid who wants it, invisible to the kid who doesn't.
+You know better than almost anyone whether a thing lands with the people it's for. Would you look, and tell me if the six-year-old version of your audience would sit still for it?
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M15" s="5" t="inlineStr"/>
       <c r="N15" s="5" t="inlineStr"/>
     </row>
@@ -1403,8 +1593,22 @@
           <t>Lyn — is the Money as You Grow Bookshelf still taking titles? Mine is K-5 and teaches spending: comparison shopping, markdowns, coupons, sales tax at the register. The current shelf leans heavily toward saving. Happy to send it to whoever evaluates. Teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr"/>
-      <c r="L16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>Lyn — a direct question about the Money as You Grow Bookshelf, from someone who has read what's on it.
+Is the Bookshelf still adding titles, and what does the evaluation look like now?
+The reason I ask. The current shelf is weighted toward saving and earning. What is thin is spending, and specifically the transaction itself. I wrote a 36-page K-5 picture book that follows one purchase from the idea to after the receipt — the sale ads at the kitchen table, comparison shopping in the aisle, a markdown taken on purpose, a coupon handed to a cashier, sales tax, and then living with the thing that was bought. I read all 25 titles on the ABA Foundation's list; not one covers the whole arc.
+Sixteen-plus concepts are in it and none is announced — no character pauses to define a term, nobody says the word "budget." The proof is the back matter, and so is the reveal: a reader does not know he's been schooled until he reaches the glossary. Twenty-one terms, each page-referenced to the scene it came from — a decoder rather than an appendix.
+Ages 6-10, which sits inside the Bookshelf's 4-10 band. Free ungated classroom materials behind it. Happy to send a copy to whoever evaluates, or to leave it alone if the shelf is closed.
+clarencegetsabargain.com/book-facts.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M16" s="5" t="inlineStr"/>
       <c r="N16" s="5" t="inlineStr"/>
     </row>
@@ -1451,7 +1655,15 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>Professor Lusardi — you built the field's measurement instruments, founded GFLEC, and started the journal the field publishes in. So you have better reason than almost anyone to tell me I'm wrong, which is why I'm writing rather than sending a press release.
+          <t>Professor Lusardi — you built the instruments the field measures itself with, so you have better grounds than anyone to tell me my premise is wrong. That is the reason I'm writing rather than sending a press release.
+The premise. Financial literacy is measured, sensibly, on saving, compounding and risk. Those are the right things to measure in adults. But each of them is downstream of a decision a child makes years earlier that nobody scores: standing in front of two prices and picking one. Spending is the first financial behavior a person performs. It is taught last, or not at all.
+I could not find the children's book for it, so I wrote one. Clarence Gets a Bargain follows a single purchase the entire way — wanting the thing, earning it, reading the sale ads, comparing two models, choosing the cheaper one deliberately, redeeming a coupon, meeting sales tax, and then living with the choice. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in the glossary, each page-referenced to the scene it came from.
+The question I would actually like answered: does the evidence base start at adolescence the way the books do? If spending competence at seven predicts nothing at twenty-seven, that is worth knowing and you would know it. If it does predict something, then there is a gap in the literature sitting underneath a picture book, and you are far better placed to say so than I am.
+clarencegetsabargain.com/book-facts.html · https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan Bach
+Attorney and children's book author, Baltimore
+----- Jump$tart version -----
+Professor Lusardi — you built the field's measurement instruments, founded GFLEC, and started the journal the field publishes in. So you have better reason than almost anyone to tell me I'm wrong, which is why I'm writing rather than sending a press release.
 The claim: financial literacy work, including most of what gets measured, begins with saving, compounding, and risk. Those are the right things to measure in adults. But they are all downstream of one decision a child makes years earlier and nobody scores — standing in front of two prices and picking one.
 I couldn't find the children's book that teaches that decision, so I wrote it. Clarence Gets a Bargain, 36 pages, grades 1-5. A boy earns a robot for chores and grades, does his homework in the sale ads, compares two models, chooses the marked-down one deliberately, hands over a coupon, and gets his first look at sales tax. Sixteen-plus concepts and a 21-term glossary, none of it announced as a lesson.
 Free teacher materials behind it, crosswalked to the National Standards for Personal Financial Education, CEE, Common Core Math and ELA, and FDIC Money Smart. No account, no gate.
@@ -1464,7 +1676,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>Subject: The decision that comes before the ones you measure · Long-form version from Jump$tart</t>
+          <t>Long-form version from TOP25 wk1 | Subject: The decision that comes before the ones you measure · Long-form version from Jump$tart</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr"/>
@@ -1511,8 +1723,22 @@
           <t>Tracy — a public-private partnership is how a K-5 resource actually scales, since elementary rarely gets its own budget line. It's a 36-page picture book plus free ungated teacher pack against five frameworks. Fit inside the partnership? Teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr"/>
-      <c r="L18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Tracy — a public-private partnership is how a K-5 resource actually reaches classrooms, because elementary rarely gets its own budget line. That is the whole reason I'm writing to you rather than to a district.
+The gap I'm working on: every state financial-literacy mandate lands in high school. Thirty of them now. Meanwhile the behaviors being corrected at sixteen were installed at six, in a store, and the sequence nobody questions is that children should learn saving first. Saving is the second thing a person does with money. The first is spending.
+I wrote the K-5 piece. One purchase followed from the idea to after the receipt — sale ads at the kitchen table, comparison shopping, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story.
+What matters for a partnership is the rest of it, and it is free. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart. Ungated, no account, prints from a browser. A district adopting it spends nothing.
+Does elementary sit inside what the partnership funds or convenes, or is high school the whole remit?
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M18" s="5" t="inlineStr"/>
       <c r="N18" s="5" t="inlineStr"/>
     </row>
@@ -1557,8 +1783,22 @@
           <t>Nicolle — your twelve-book roundup is the one I point people to, which is awkward, because every title on it teaches earning or saving. Mine teaches spending: the whole transaction, right through the register, sales tax and the small indignity that follows. Worth a look for the next update, or does a spend-first book break the shelf? Either way I'd rather you heard it from me. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr"/>
-      <c r="L19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Nicolle — your twelve-book roundup is the one I point people to, which is slightly awkward, because every title on it teaches earning or saving.
+That's not a criticism of the list. It's an accurate reflection of what exists. I went looking for the spending book and could not find it, so I wrote it.
+The argument in one line: saving is the second thing a child does with money, and the first is spending. A six-year-old has no savings rate and has definitely stood in a store holding a birthday five, deciding whether the thing is worth what it costs.
+Clarence Gets a Bargain follows one purchase from the idea to after the receipt. A boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Sixteen-plus concepts and nobody in the book says "budget." Twenty-one terms in the glossary, each page-referenced to the scene it came from.
+Two asks, and the second one matters more. Worth a look for the next update to the roundup? And separately — you run a company built on kids and money, so if you think spending-before-saving is wrong, I would rather hear it from you than keep saying it at conferences.
+I'll send a copy either way. https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M19" s="5" t="inlineStr"/>
       <c r="N19" s="5" t="inlineStr"/>
     </row>
@@ -1695,8 +1935,22 @@
           <t>Hunter — policy and advocacy at NEFE puts you where the K-5 gap is most visible. Nearly everything funded sits at high school. I wrote a picture book plus free teacher materials for grades 1-5 against five frameworks. Is early elementary getting any policy attention, or still an orphan? The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Hunter — a policy observation, and a question about whether NEFE has a view on it.
+Thirty states now require a personal finance course to graduate. Delaware became the thirtieth last October. Every one of those mandates lands in high school, and the funding and training follow the mandate. Meanwhile the K-5 standards that already exist in most states sit there with almost nothing built against them, because nobody has to report on them.
+The sequence assumption underneath all of it is that children should learn saving first. I think that is backwards. Saving is the second thing a person does with money. The first is spending — and a first grader has done that, at a register, with a parent standing behind her. The behaviors a high school course is trying to correct were installed a decade earlier.
+I wrote the elementary piece rather than an argument about it: a 36-page picture book that follows one purchase from the idea to after the receipt, plus a free ungated classroom set crosswalked to the 2021 National Standards, Common Core, CEE and FDIC Money Smart. Sixteen-plus concepts, none announced, twenty-one-term glossary page-referenced into the story.
+The question: does NEFE's advocacy work have a position on the elementary band, or is the practical view that high school mandates are where the effort actually pays? I ask because if it's the second, I'd like to know I'm arguing with the consensus rather than filling a gap it agrees exists.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M22" s="5" t="inlineStr"/>
       <c r="N22" s="5" t="inlineStr"/>
     </row>
@@ -5014,7 +5268,11 @@
       <c r="N103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="inlineStr"/>
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
           <t>1-202</t>
@@ -5046,8 +5304,22 @@
           <t>Roda — Smart Money Kids World and Clarence share an audience. Mine is narrow on purpose: one purchase, all the way through the register. As a fellow author and founder — does narrow work better at this age? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K104" s="5" t="inlineStr"/>
-      <c r="L104" s="5" t="inlineStr"/>
+      <c r="K104" s="5" t="inlineStr">
+        <is>
+          <t>Roda — you built a 30-Day Smart Spending Challenge. Not a saving challenge. Spending. As far as I can tell that makes two of us in this entire category who think the sequence is backwards.
+Here is my version of the argument, and I'd like to know whether it matches how you arrived at yours. Every children's money book teaches saving — I read all 25 on the ABA Foundation's list to be sure. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. We teach the second thing first and the first thing never.
+Clarence Gets a Bargain is the picture-book version. It follows a single purchase the whole distance — a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced; nobody says "budget." Twenty-one terms in a glossary at the end, each page-referenced to where it happened — which is the only point at which a kid works out he's been schooled.
+Your Challenge is a thirty-day habit; mine is one transaction read in twenty minutes. Those look complementary to me rather than competing — the book could be the on-ramp to a challenge, or the thing a parent reads on day one.
+Worth a conversation? I'd rather compare notes with the one other person who put spending first than pitch anybody.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L104" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M104" s="5" t="inlineStr"/>
       <c r="N104" s="5" t="inlineStr"/>
     </row>
@@ -6268,7 +6540,11 @@
       <c r="N136" s="5" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="inlineStr"/>
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
           <t>1-202</t>
@@ -6300,13 +6576,31 @@
           <t>Daniel — 360 Parenting reaches families weekly, and spending is where parents and kids collide first, usually in an aisle, usually loudly. Mine is that scene, resolved well. Podcast fit? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K137" s="5" t="inlineStr"/>
-      <c r="L137" s="5" t="inlineStr"/>
+      <c r="K137" s="5" t="inlineStr">
+        <is>
+          <t>Daniel — you built 360 Parenting around the whole child rather than one slice of them, so this is a slice you may be missing, and I say that as someone who only noticed it because I went looking for a book and could not find one.
+Money education for kids begins with saving. Every time. But saving is the second thing a child does with money. The first is spending — and a six-year-old has done that, repeatedly, usually in a store, usually while a parent quietly loses the will to live.
+So I wrote the spending book. One purchase, followed the entire way: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, discovers sales tax the way we all did — badly, and in public — and then has to live with the thing he chose. From the idea to after the receipt.
+Here is why it might fit a parenting audience rather than a classroom one. The concepts are smuggled. Sixteen-plus of them, none announced, nobody saying the word "budget." It reads as a story about a kid and a robot, and the parent doing the read-aloud gets handed the money conversation without having to deliver a lesson. And the kid does not know he's been schooled until he gets to the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. A parent can turn straight back to the exact page.
+Would it work for your audience — podcast, newsletter, or neither? A no is a fine answer and faster than a maybe.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L137" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M137" s="5" t="inlineStr"/>
       <c r="N137" s="5" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="inlineStr"/>
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
           <t>1-202</t>
@@ -6338,8 +6632,22 @@
           <t>ML — the Noah series shows you can carry a lesson without smothering the story, which is my whole anxiety about my own book. Would you read it as an author and tell me if the lesson shows too much? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K138" s="5" t="inlineStr"/>
-      <c r="L138" s="5" t="inlineStr"/>
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>ML — you built a series a child comes back to, which is harder than writing one good book, and it's the reason I'm writing to a peer rather than a gatekeeper.
+Mine is a money book, which I appreciate is the least promising sentence in children's publishing. So here is the part that makes it not that.
+Every book in this category teaches saving. Saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it — in a store, holding money, deciding whether the thing is worth what it costs. So mine follows one purchase from the idea to after the receipt: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose.
+The craft problem I'd most like another author's view on: I smuggled sixteen-plus concepts in without announcing any of them. Nobody says "budget." The glossary in the back — twenty-one terms, each page-referenced to the scene it came from — is the only place the book admits it was teaching. Getting that balance right, so it stays a story, was the whole job.
+Would you read it and tell me where it stops being a story? I'll trade — send me a Noah and I'll read it properly.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L138" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M138" s="5" t="inlineStr"/>
       <c r="N138" s="5" t="inlineStr"/>
     </row>
@@ -7484,7 +7792,11 @@
       <c r="N168" s="5" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="5" t="inlineStr"/>
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
           <t>1-202</t>
@@ -7516,8 +7828,22 @@
           <t>Linda — financial parenting is your field, and spending is where parents and kids collide first, usually in an aisle, usually loudly. Mine is that scene resolved well: a six-year-old compares two robots and talks himself into the cheaper one. Built with a K-5 teacher of 30+ years, 21-term glossary, free lessons. Would you put it in front of the parents you teach? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K169" s="5" t="inlineStr"/>
-      <c r="L169" s="5" t="inlineStr"/>
+      <c r="K169" s="5" t="inlineStr">
+        <is>
+          <t>Linda — you teach financial parenting, which means you spend your working life on the exact handoff I wrote a book about: the moment a parent has to explain money to a child who is standing right there wanting something.
+My argument, and you are better placed than almost anyone to tell me it's wrong. Financial education for children starts with saving, and it has the sequence backwards. A seven-year-old has no savings rate and no income. What she has done is stand at a register holding money and decide. Spending is the first money behavior a person performs. We teach it last, or not at all.
+Clarence Gets a Bargain is the spending book. It follows one purchase the whole distance — wanting the thing, earning it through chores and grades, reading the sale inserts at the kitchen table with a parent, comparing two models on a shelf, choosing the cheaper one on purpose, handing over a coupon, meeting sales tax, and then living with what he bought. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; not one covers the whole arc.
+The design choice that matters for your work: nothing is announced. Sixteen-plus concepts and nobody in the book says "budget." The parent reading aloud is handed the conversation without having to give a lecture, which I gather is most of what you coach people out of. The child does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. The reveal is the last thing that happens, not the first.
+Two questions, either useful. Does the spending-before-saving sequence hold up against what you see in families? And is there a version of this that belongs in front of the parents you train?
+clarencegetsabargain.com/book-facts.html · https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L169" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M169" s="5" t="inlineStr"/>
       <c r="N169" s="5" t="inlineStr"/>
     </row>
@@ -7554,8 +7880,21 @@
           <t>Stacey — you take books from manuscript to shelf and you'd tell me straight. Mine teaches spending instead of saving, ages 6-10, selling direct only. Would you look at the positioning and tell me what I'm getting wrong? Press kit: https://clarencegetsabargain.com/press-kit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K170" s="5" t="inlineStr"/>
-      <c r="L170" s="5" t="inlineStr"/>
+      <c r="K170" s="5" t="inlineStr">
+        <is>
+          <t>Stacey — you design and produce books for other authors, which makes you one of very few people I could ask this of honestly: does mine look like it was made by someone who knew what he was doing?
+I wrote and illustrated a 36-page hardbound picture book, full colour, 11 by 8.5. I am a mixed-media artist and a real estate attorney, which is a combination that gets me neither the benefit of the doubt on the art nor on the commercial sense. I did the interior, the cover, the whole object.
+The content, briefly, because you'll want to know whether it's worth the production critique. Every children's money book teaches saving. Mine teaches spending, on the argument that saving is the second thing a child does with money and spending is the first. It follows one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, then living with what was bought. Sixteen-plus concepts, none announced. Twenty-one terms in a glossary in the back, each page-referenced to the scene it came from.
+What I'd actually value from you is the unglamorous part: trim size, the cover, whether the interior typography holds at read-aloud distance, whether the object reads as professionally published or as a very determined amateur. I would rather hear it from you now than infer it from a bookseller later.
+Paid engagement or a favour returned, whichever you prefer. https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L170" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M170" s="5" t="inlineStr"/>
       <c r="N170" s="5" t="inlineStr"/>
     </row>
@@ -24868,8 +25207,22 @@
           <t>Sandy — FCCLA members are a decade older than my readers, so this is not a curriculum pitch. It's a service-project one. Your chapters already run community work, and a high schooler reading a money book to a second-grade class is about the cleanest version of that I can think of. Mine is 36 pages, teaches the whole purchase through the register, and the classroom pack behind it is free. Does that fit how chapters choose projects, or am I inventing a use case? Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K622" s="5" t="inlineStr"/>
-      <c r="L622" s="5" t="inlineStr"/>
+      <c r="K622" s="5" t="inlineStr">
+        <is>
+          <t>Sandy — FCCLA members are a decade older than my readers, so this is not a curriculum pitch. It is a service-project one, and I think it's a good one.
+Your chapters run community service. A high schooler reading a money book to a second-grade class is about the cleanest version of that I can think of — it needs no budget, no training, and one afternoon.
+The book is Clarence Gets a Bargain, 36 pages, ages 6-10. It follows one purchase the whole way, which is the thing that makes it work as a read-aloud rather than a lecture: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in it says "budget" — the twenty-one-term glossary in the back is page-referenced to the story, so the reader can field questions without preparing.
+It reads aloud in about twenty minutes, which is a class visit with time left for questions. And there is a free browser-based pretend register the younger kids can run afterward — a markdown, a coupon, sales tax, and a total that changes in front of them.
+Does that fit how chapters choose service projects, or am I inventing a use case? Everything is free and ungated either way.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L622" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M622" s="5" t="inlineStr"/>
       <c r="N622" s="5" t="inlineStr"/>
     </row>
@@ -26826,14 +27179,10 @@
       <c r="K658" s="5" t="inlineStr"/>
       <c r="L658" s="5" t="inlineStr">
         <is>
-          <t>⛔ DO NOT SEND — already declined the book without reading it (AI alleged from a cover thumbnail). See letters-delaware.md #17.</t>
-        </is>
-      </c>
-      <c r="M658" s="5" t="inlineStr">
-        <is>
-          <t>DEAD</t>
-        </is>
-      </c>
+          <t>Now. Summer is their season and a kids' event needs lead time.</t>
+        </is>
+      </c>
+      <c r="M658" s="5" t="inlineStr"/>
       <c r="N658" s="5" t="inlineStr"/>
     </row>
     <row r="659">
@@ -27229,7 +27578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -27361,8 +27710,22 @@
           <t>Alex — I read a dozen kids' money books to see where mine fit. Every one taught saving. Save your pennies, save for a rainy day, save, save, save. Not one covered the moment a kid stands there with his own five bucks deciding if the thing is worth it. Am I qualified to fix that? Debatable. I did once pay one cent for a $293 pair of shoes, and I kept the tag. Not a typo. Mine runs that whole gauntlet — ad, aisle, markdown, coupon, and the sales tax nobody warns a six-year-old about. Segment, or am I picking a fight the category doesn't want? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr"/>
-      <c r="L2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Alex — Planet Money's whole trick is that people will absorb an economics lesson if you hide it inside a story about a guy and a barrel of oil. I did the same thing at a lower reading level.
+Here is the pitch in one line: every children's money book teaches saving, and saving is the second thing a kid does with money. The first is spending. A six-year-old has no savings rate. She has stood in an aisle holding a birthday five, deciding whether the thing is worth it.
+So I wrote the spending one. Clarence Gets a Bargain follows a single purchase the entire way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, gets ambushed by sales tax, and then lives with the thing he bought. Idea to post-receipt. I read every title on the ABA Foundation's children's financial literacy list to check, and not one follows a purchase the whole way through.
+Sixteen-plus concepts are in there and none of them are announced. Nobody says the word "budget." They don't realise they've been schooled until they hit the glossary — twenty-one terms in the back, each page-referenced to the moment it actually happened. That's where the con comes apart, on purpose.
+The segment I'd pitch is not the book. It's the forty-year hole: why an entire publishing category skipped the cash register. There is a Planet Money episode in that whether or not mine is the book that gets mentioned.
+Am I wrong that it's a story? clarencegetsabargain.com/book-facts.html has the specs. Four-minute flip: https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M2" s="5" t="inlineStr"/>
       <c r="N2" s="5" t="inlineStr"/>
     </row>
@@ -27407,8 +27770,23 @@
           <t>Tami — an award-winning picture book author is the read I want most, because my worry is craft, not content. The money lesson works. What I don't know is whether 36 pages about one shopping trip holds a kid on its own merits. Would you read it as a writer rather than a subject expert? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Tami — author to author, and I'd rather you heard this from me than found it on a shelf.
+I wrote and illustrated a picture book about money, which sounds like the most airless premise in children's publishing, so let me tell you the one thing that makes it not that.
+Every book in this category teaches saving. Piggy banks, jars, be patient, wait. But saving is the second thing a child does with money. The first is spending, and nobody had written that book. So mine follows one purchase from beginning to end — a boy wants a robot, earns it, works the sale ads at the kitchen table, compares two models in the aisle, takes the cheaper one deliberately, hands a coupon to the cashier, meets sales tax and takes it personally, and then has to live with what he chose.
+The part I think you'll appreciate as a craftsperson: none of the sixteen-plus concepts is ever announced. There is no worksheet voice, no character stopping to explain a term. It is smuggled. A kid does not know he's been schooled until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. That is the moment the book admits what it was doing, and it is the last page rather than the first.
+I did the illustrations too, which means I have opinions about it that are worth exactly nothing.
+Would you look at it and tell me where the seams show? I'd trade — send me yours and I'll read it properly, not politely.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M3" s="5" t="inlineStr"/>
       <c r="N3" s="5" t="inlineStr"/>
     </row>
@@ -27453,8 +27831,22 @@
           <t>Tim — NGPF owns 9-12 and does it better than anyone. I wrote the K-5 on-ramp: a picture book where a kid runs one real purchase, ad to register, sales tax and all. Genuine question rather than a pitch — do you see elementary as in scope for NGPF, or a gap somebody else has to fill? Teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Tim — NGPF owns 9-12 and does it better than anyone, so this is not a pitch into your territory. It is a question about the floor beneath it.
+Every state that mandates personal finance mandates it in high school. Delaware just became the thirtieth and put the course in front of ninth graders. Fine as far as it goes. But the money behaviors NGPF is correcting at sixteen were installed at six, in a store, with a parent saying no.
+The sequence is what I keep coming back to. Financial education starts with saving, and saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has stood at a register and chosen.
+I wrote the K-5 on-ramp. One purchase, followed the whole distance — wanting a robot, earning it, working the sale inserts at the kitchen table, comparing two on a shelf, taking the cheaper one on purpose, redeeming a coupon, meeting sales tax, and living with the choice. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; none does the full arc. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced back into the story.
+The real question, rather than the ask: does NGPF consider elementary in scope, or is it a gap you have consciously left to somebody else? Either answer is useful to me, and the second one tells me whether I'm building alone.
+Everything free and ungated: clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M4" s="5" t="inlineStr"/>
       <c r="N4" s="5" t="inlineStr"/>
     </row>
@@ -27499,8 +27891,22 @@
           <t>Paula — "You can afford anything, but not everything," translated for six-year-olds. Kid earns a robot. Finds the marked-down older model. Slightly smaller screen, no antenna. He takes it anyway and can tell you why. That's the climax — a first grader choosing the cheaper thing on purpose, which is more than most adults manage on Prime Day. Would your crowd want the version they can hand a kid? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr"/>
-      <c r="L5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Paula — "you can afford anything, but not everything" is the best sentence anybody has written about money, and it is a sentence about spending, not saving. That is the entire reason I'm writing to you.
+I wrote the children's version of that idea, and I mean that structurally rather than as a compliment. Every kids' money book teaches saving. But saving is the second thing a child does with money — the first is spending, and a six-year-old has already done it, holding a birthday five in an aisle, working out whether the thing is worth what it costs. Which is your thesis at a lower reading level.
+Clarence Gets a Bargain follows one purchase the whole way. A boy wants a robot. Earns it with chores and grades. Reads the newspaper sale inserts at the kitchen table. Compares two models on a shelf and takes the cheaper one on purpose. Hands a coupon to the cashier. Meets sales tax and regards it as a personal insult, correctly. Then lives with what he chose — which is the opportunity-cost half nobody writes for kids.
+The craft bit: none of it is announced. Sixteen-plus concepts, and nobody in the book says the word "budget." A kid does not know he's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. Available, never assigned.
+Is there an episode in the fact that the entire children's money category skipped the cash register for forty years? I'd rather you took the argument than the book.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M5" s="5" t="inlineStr"/>
       <c r="N5" s="5" t="inlineStr"/>
     </row>
@@ -27545,8 +27951,22 @@
           <t>Kim — you've edited and reviewed more children's books than I'll ever write. Mine hides a financial education inside a story about a kid and a robot, and I think it works — which is exactly the judgment an author is least qualified to make about his own book. Would you read it as an editor? Happy to trade. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Kim — you review children's books for a living, so you have read more well-meaning money picture books than anyone should have to, and you already know the problem with them.
+They all teach saving. Every one. Which is fine advice and the wrong order, because saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate and has absolutely stood in a store holding money and had to decide.
+Mine is the spending one, and it follows a single purchase the whole distance rather than gesturing at the idea: a boy wants a robot, earns it with chores and grades, works the sale ads at the kitchen table, compares two models in the aisle, takes the cheaper one on purpose, hands a coupon to the cashier, gets hit with sales tax, and then has to live with the thing. Idea to post-receipt. I read all 25 on the ABA Foundation's list to be sure nobody had done it. Nobody had.
+What I'd actually want your eye on is the smuggling. Sixteen-plus concepts and not one of them is announced — no character stops to explain a term, nobody says "budget." The reader does not know he's been schooled until he reaches the glossary — twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than a homework appendix. The reveal is deliberate and it is on the last page. That balance is the hardest thing in the book and the thing most likely to be off by a hair.
+Would you read it as an editor rather than as a friend? I would rather hear where it sags than be told it's charming.
+clarencegetsabargain.com/press-kit.html · https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
     </row>
@@ -27591,8 +28011,22 @@
           <t>Neale — you built this category. Money Doesn't Grow on Trees was on shelves before most of us were thinking about any of it. Mine leaves saving out entirely and teaches spending: one purchase, ad to register, sales tax included. You'd know inside ten pages whether that's a real gap or one I invented to justify a book I wanted to write anyway. Would you tell me straight? More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
-      <c r="L7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Neale — you built this category. Money Doesn't Grow on Trees was on the shelf before most of the people currently writing in it could read, so I'm not going to pretend I'm doing something you haven't thought about.
+What I think is still open is the sequence. The field starts children with saving, and saving is the second thing a person does with money. The first is spending. A six-year-old has no savings rate. She has stood in a store holding money and decided. We teach that last.
+So I went narrow and deep on one transaction. Clarence Gets a Bargain follows a single purchase from the idea to after the receipt — a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, redeems a coupon, meets sales tax, and then lives with what he bought. I read all 25 titles on the ABA Foundation's list; none covers the whole arc.
+The other thing, and it is the part I'd want your read on: nothing is announced. Sixteen-plus concepts, no worksheet voice, nobody in the book saying "budget." A child does not know he's been schooled until the glossary — twenty-one terms in the back, each page-referenced to the moment it happened. The book confesses on the last page or not at all. You would spot immediately whether that balance holds or whether I have hidden the lesson so well it isn't there.
+Author to author, I'd like to trade. Send me one of yours and I'll read it properly. And if you think the spending-first premise is wrong, that is worth more to me than a kind word about the illustrations.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M7" s="5" t="inlineStr"/>
       <c r="N7" s="5" t="inlineStr"/>
     </row>
@@ -27637,8 +28071,22 @@
           <t>Joel — no login, no email capture, no funnel. Four 45-minute lesson plans, a pre/post assessment with the answer key, and a 23-row crosswalk, all built against the National Standards and all free. I'd like it in the Clearinghouse. Does it clear the bar as you read the criteria? Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Joel — a specific question rather than a pitch, and it should take you a minute.
+I have a K-5 resource I would like to list in the Jump$tart Clearinghouse, and I have read the listing criteria closely enough to know which route applies to me. I am not a National Partner and have never listed before, so I would be applying under the letter-of-reference route.
+The resource is a free, ungated classroom set built around a 36-page picture book: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE, and FDIC Money Smart, printable classroom pieces, and a browser-based pretend register. No account, no email capture, no purchase order. It prints from a browser.
+What the book does that the category does not: it teaches spending rather than saving, and it follows one complete purchase from the idea through the receipt — sale ads, comparison, markdown, coupon, sales tax. Sixteen-plus concepts, a twenty-one-term glossary page-referenced to the story. The elementary grade band has standards and very little built against them.
+Two questions. Is the free classroom set the right thing to submit, rather than the book? And for the reference letter, would Wally Luckeydoo carry weight — he received your 2026 Corey Carlisle Award and endorsed the book before any of this came up.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M8" s="5" t="inlineStr"/>
       <c r="N8" s="5" t="inlineStr"/>
     </row>
@@ -27683,8 +28131,22 @@
           <t>Michelle — you've said for years the money talk should start before kids can spell it. So I wrote one for six-year-olds with no piggy bank in it. None. It's all spending: read the ad, compare two robots, hand over the coupon, then meet sales tax for the first time. Kids read it for the robot. The rest sneaks in. Column in a kids' money book that skips saving entirely? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr"/>
-      <c r="L9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Michelle — you have written for twenty years that the money conversation with children has to start early, and I wrote the book for the earliest version of it. One question at the end, and it is a column question rather than a book question.
+Every children's financial literacy book teaches saving. I read all 25 on the ABA Foundation's list to be certain. Piggy banks, jars, patience. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it — in a store, holding money, deciding whether the thing is worth what it costs.
+Mine follows one purchase the entire way. A boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he bought. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." Twenty-one terms in the glossary, each page-referenced to the scene it came from.
+The column, if there is one: an entire publishing category has taught children to save for forty years and skipped the cash register, which is the only place a child has ever actually handled money. That is a story about the field, not about me.
+clarencegetsabargain.com/press-kit.html
+Jonathan Bach
+Baltimore</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Subject: The kids' money book that skips the piggy bank · Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M9" s="5" t="inlineStr"/>
       <c r="N9" s="5" t="inlineStr"/>
     </row>
@@ -27729,8 +28191,22 @@
           <t>Cinders — you got four books out of Earn, Save, Spend, Give. I got greedy and spent all 36 pages on one of them. Spending. The whole transaction, right through the register, sales tax and the small indignity that follows. Author-illustrator to author-illustrator, I'd rather you heard it from me than found it on a shelf and squinted. Trade copies? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr"/>
-      <c r="L10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Cinders — Moneybunnies splits money into Earn, Save, Spend and Give, which makes you the one person in this category who already agreed with me before I showed up.
+I went deep on one of your four. Spending, and specifically the whole transaction rather than the idea of it. Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then has to live with what he picked. Idea to post-receipt.
+The reason I think it sits beside Moneybunnies rather than against it: you give a child the four categories, and mine walks them through the mechanics of one. Sixteen-plus concepts, none announced — nobody says "budget" — and twenty-one terms in a glossary in the back, each page-referenced to the scene where it happened.
+Author-illustrator to author-illustrator: I did the art as well, so I know exactly how much of the work nobody sees. I'd rather you saw this from me than off a shelf.
+Trade copies? I'll read yours properly and tell you the truth about it, which is the only thing worth trading.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M10" s="5" t="inlineStr"/>
       <c r="N10" s="5" t="inlineStr"/>
     </row>
@@ -27775,8 +28251,21 @@
           <t>Yanely — you've said the gaps show up long before high school. I wrote the K-5 version, and it teaches spending because that's the transaction a six-year-old actually performs. Does NGPF ever point teachers below ninth grade, or is that outside the remit? For teachers: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr"/>
-      <c r="L11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Yanely — you spend your time getting personal finance in front of teenagers, and I want to ask about the years before you get them.
+Every mandate lands in high school. Delaware just became the thirtieth state and put the course in ninth grade. But the habits being corrected at sixteen were installed at six, in a store, with a parent saying no. The sequence is the part I keep circling: financial education starts children with saving, and saving is the second thing a person does with money. The first is spending.
+I wrote the K-5 on-ramp — one purchase followed the whole way, from wanting a robot to living with it. Sale ads at the kitchen table, comparison on a shelf, a markdown taken on purpose, a coupon at the register, sales tax. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced back into the story. Free ungated classroom set behind it.
+Honest question rather than a pitch: when you talk to teachers, does elementary ever come up as something they want and cannot find? I am trying to work out whether I am filling a gap or inventing one.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Subject: The grade band below yours · Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M11" s="5" t="inlineStr"/>
       <c r="N11" s="5" t="inlineStr"/>
     </row>
@@ -27823,7 +28312,15 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>Leslie — I sent a short note a while back about the Money as You Grow Bookshelf. This is the idea behind the book, and it's the one I actually wanted to run past someone at CFPB.
+          <t>Leslie — a Money as You Grow question, and then an idea I'd like a CFPB read on.
+The question first. Is the Bookshelf still evaluating titles, and who owns it now? I have a K-5 picture book that teaches spending rather than saving, and the current shelf leans heavily toward saving.
+The idea. A child becomes a consumer the first time they hand money to a cashier. Not at eighteen, not at a first paycheck — at six, at a register, with a birthday five. Everything in youth financial education treats that child as a saver in training. Almost nothing treats her as what she already is: a party to a transaction.
+My book follows one purchase the entire way, which is the part I could not find anywhere else — from wanting the thing, through the sale ads, the comparison, the markdown, the coupon, and the sales tax, to living with what was bought. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in the glossary, each page-referenced to the scene where it happened.
+I know the full picture crosses agencies — warranties and returns are FTC, product safety is CPSC — and I am not asking CFPB to cover those. I am asking whether Money as You Grow has room for material that treats the child as a consumer on the financial side from the first purchase forward.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan
+----- CFPB/rights version -----
+Leslie — I sent a short note a while back about the Money as You Grow Bookshelf. This is the idea behind the book, and it's the one I actually wanted to run past someone at CFPB.
 A child becomes a consumer the first time they hand over money. Not at eighteen, not at a first paycheck — at six, at a register, with a birthday five in their fist. That is the whole premise of my book: a boy runs one complete purchase, sale ad to receipt, and picks up comparison shopping, markdowns, coupons, and sales tax on the way. Money as You Grow teaches saving and spending well. The transaction itself — the part where a kid is actually standing at the counter — is the gap the book fills, and the current shelf leans heavily toward saving.
 Here is the piece I keep circling. The moment a kid makes that first purchase, they have entered a relationship that comes with rights, and nobody teaches a seven-year-old they have any. An adult knows to keep the receipt and that a broken thing can go back. A child thinks the deal ends when the bag is handed over.
 I know the full rights picture crosses agencies — warranties and returns are FTC, product safety is CPSC. I'm not asking CFPB to cover those. I'm asking whether there's appetite within Money as You Grow for material that treats the child as a consumer with standing on the financial side, the day they first spend, rather than only as a saver in training.
@@ -27835,7 +28332,7 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>Long-form version from CFPB/rights</t>
+          <t>Long-form version from TOP25 wk1 | Long-form version from CFPB/rights</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr"/>
@@ -27882,8 +28379,22 @@
           <t>Ken — my book and its free K-5 classroom materials are aligned to Money Smart for Young People, with a crosswalk mapping every concept to the specific standard rather than asking you to take my word. Is there a process for a title to sit alongside Money Smart materials, or is that not how it works? Print it here: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr"/>
-      <c r="L13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Ken — a process question about Money Smart for Young People, asked by someone who has already done the alignment work.
+I built a free K-5 classroom set around a 36-page picture book and crosswalked it to Money Smart for Young People alongside the 2021 National Standards for Personal Financial Education, CEE, and Common Core Math and ELA. Twenty-three rows, concept by concept, with the Grade 4 benchmark codes rather than a general claim of alignment. It is on the site so a reviewer can check it instead of taking my word.
+What the book covers that Money Smart's book lists mostly do not: spending, and the complete transaction rather than the concept. One purchase followed from the idea to after the receipt — sale ads, comparison shopping, a markdown, a coupon at the register, sales tax, and then living with the thing bought. Sixteen-plus concepts, none announced in the text. A twenty-one-term glossary page-referenced back into the story.
+Everything for teachers is free and ungated. No account, no email capture, no purchase order.
+The question: is there a route for a title to sit alongside Money Smart materials, or is that not how the program works? Either answer saves me guessing.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M13" s="5" t="inlineStr"/>
       <c r="N13" s="5" t="inlineStr"/>
     </row>
@@ -27928,8 +28439,22 @@
           <t>Rishi — you passed the CFP at sixteen and built Easy Peasy Finance, so you get this without preamble. Mine teaches spending, not saving. By the last page a six-year-old has compared prices, caught a markdown, and paid sales tax. Fit anything you're building? Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr"/>
-      <c r="L14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Rishi — you passed the CFP exam at sixteen, which means you learned this material at an age when the rest of us were being told to save our allowance, so you are unusually well placed to tell me whether my premise is nonsense.
+The premise: financial education for children starts with saving, and the sequence is backwards. Saving is the second thing a person does with money. The first is spending. A six-year-old has no savings rate and has definitely stood in a store holding money, deciding.
+Easy Peasy Finance explains concepts to kids clearly, one at a time. I went the other way and hid them. Clarence Gets a Bargain follows a single purchase the whole distance — a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Sixteen-plus concepts and nobody in the book says "budget." The twenty-one-term glossary in the back is page-referenced to where each thing happened, which is the closest the book comes to admitting it was teaching anything.
+You explain; I smuggle. I think both work and I'd like to know if you disagree.
+Is there a version of this worth putting in front of your audience — a read-along, a segment, a mention? And separately: at sixteen, would this book have been too young for you, or exactly right for the you at six?
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M14" s="5" t="inlineStr"/>
       <c r="N14" s="5" t="inlineStr"/>
     </row>
@@ -27974,8 +28499,22 @@
           <t>Tiffany — Get Good with Money worked because you refused to talk down to anyone. I tried to hold that line for six-year-olds: real decision, real tradeoff, no moral bolted onto the last page. Mine leaves saving to everybody else. Would you tell me if it condescends? I'd rather hear it from you than from a seven-year-old. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr"/>
-      <c r="L15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Tiffany — you built a career on the thing nobody teaches: what to actually do, in order, with money that is already in your hand. That is why I'm writing about the six-year-old version.
+Every children's money book teaches saving. All 25 on the ABA Foundation's list — I checked. Piggy banks, jars, patience. But saving is the second thing a child does with money. The first is spending, and a first grader has already done it, in a store, holding a birthday five, working out whether the thing is worth what it costs.
+Mine is the spending one, and it follows a single purchase the whole way rather than talking about the idea: a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, gets hit with sales tax, and then lives with what he chose. Idea to post-receipt.
+The design choice: none of the sixteen-plus concepts is announced. Nobody in the book says "budget," which for a book that is largely about budgeting took some doing. The kid does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. There for the kid who wants it, invisible to the kid who doesn't.
+You know better than almost anyone whether a thing lands with the people it's for. Would you look, and tell me if the six-year-old version of your audience would sit still for it?
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M15" s="5" t="inlineStr"/>
       <c r="N15" s="5" t="inlineStr"/>
     </row>
@@ -28020,8 +28559,22 @@
           <t>Lyn — is the Money as You Grow Bookshelf still taking titles? Mine is K-5 and teaches spending: comparison shopping, markdowns, coupons, sales tax at the register. The current shelf leans heavily toward saving. Happy to send it to whoever evaluates. Teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr"/>
-      <c r="L16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>Lyn — a direct question about the Money as You Grow Bookshelf, from someone who has read what's on it.
+Is the Bookshelf still adding titles, and what does the evaluation look like now?
+The reason I ask. The current shelf is weighted toward saving and earning. What is thin is spending, and specifically the transaction itself. I wrote a 36-page K-5 picture book that follows one purchase from the idea to after the receipt — the sale ads at the kitchen table, comparison shopping in the aisle, a markdown taken on purpose, a coupon handed to a cashier, sales tax, and then living with the thing that was bought. I read all 25 titles on the ABA Foundation's list; not one covers the whole arc.
+Sixteen-plus concepts are in it and none is announced — no character pauses to define a term, nobody says the word "budget." The proof is the back matter, and so is the reveal: a reader does not know he's been schooled until he reaches the glossary. Twenty-one terms, each page-referenced to the scene it came from — a decoder rather than an appendix.
+Ages 6-10, which sits inside the Bookshelf's 4-10 band. Free ungated classroom materials behind it. Happy to send a copy to whoever evaluates, or to leave it alone if the shelf is closed.
+clarencegetsabargain.com/book-facts.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M16" s="5" t="inlineStr"/>
       <c r="N16" s="5" t="inlineStr"/>
     </row>
@@ -28068,7 +28621,15 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>Professor Lusardi — you built the field's measurement instruments, founded GFLEC, and started the journal the field publishes in. So you have better reason than almost anyone to tell me I'm wrong, which is why I'm writing rather than sending a press release.
+          <t>Professor Lusardi — you built the instruments the field measures itself with, so you have better grounds than anyone to tell me my premise is wrong. That is the reason I'm writing rather than sending a press release.
+The premise. Financial literacy is measured, sensibly, on saving, compounding and risk. Those are the right things to measure in adults. But each of them is downstream of a decision a child makes years earlier that nobody scores: standing in front of two prices and picking one. Spending is the first financial behavior a person performs. It is taught last, or not at all.
+I could not find the children's book for it, so I wrote one. Clarence Gets a Bargain follows a single purchase the entire way — wanting the thing, earning it, reading the sale ads, comparing two models, choosing the cheaper one deliberately, redeeming a coupon, meeting sales tax, and then living with the choice. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in the glossary, each page-referenced to the scene it came from.
+The question I would actually like answered: does the evidence base start at adolescence the way the books do? If spending competence at seven predicts nothing at twenty-seven, that is worth knowing and you would know it. If it does predict something, then there is a gap in the literature sitting underneath a picture book, and you are far better placed to say so than I am.
+clarencegetsabargain.com/book-facts.html · https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan Bach
+Attorney and children's book author, Baltimore
+----- Jump$tart version -----
+Professor Lusardi — you built the field's measurement instruments, founded GFLEC, and started the journal the field publishes in. So you have better reason than almost anyone to tell me I'm wrong, which is why I'm writing rather than sending a press release.
 The claim: financial literacy work, including most of what gets measured, begins with saving, compounding, and risk. Those are the right things to measure in adults. But they are all downstream of one decision a child makes years earlier and nobody scores — standing in front of two prices and picking one.
 I couldn't find the children's book that teaches that decision, so I wrote it. Clarence Gets a Bargain, 36 pages, grades 1-5. A boy earns a robot for chores and grades, does his homework in the sale ads, compares two models, chooses the marked-down one deliberately, hands over a coupon, and gets his first look at sales tax. Sixteen-plus concepts and a 21-term glossary, none of it announced as a lesson.
 Free teacher materials behind it, crosswalked to the National Standards for Personal Financial Education, CEE, Common Core Math and ELA, and FDIC Money Smart. No account, no gate.
@@ -28081,7 +28642,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>Subject: The decision that comes before the ones you measure · Long-form version from Jump$tart</t>
+          <t>Long-form version from TOP25 wk1 | Subject: The decision that comes before the ones you measure · Long-form version from Jump$tart</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr"/>
@@ -28128,8 +28689,22 @@
           <t>Tracy — a public-private partnership is how a K-5 resource actually scales, since elementary rarely gets its own budget line. It's a 36-page picture book plus free ungated teacher pack against five frameworks. Fit inside the partnership? Teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr"/>
-      <c r="L18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Tracy — a public-private partnership is how a K-5 resource actually reaches classrooms, because elementary rarely gets its own budget line. That is the whole reason I'm writing to you rather than to a district.
+The gap I'm working on: every state financial-literacy mandate lands in high school. Thirty of them now. Meanwhile the behaviors being corrected at sixteen were installed at six, in a store, and the sequence nobody questions is that children should learn saving first. Saving is the second thing a person does with money. The first is spending.
+I wrote the K-5 piece. One purchase followed from the idea to after the receipt — sale ads at the kitchen table, comparison shopping, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story.
+What matters for a partnership is the rest of it, and it is free. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart. Ungated, no account, prints from a browser. A district adopting it spends nothing.
+Does elementary sit inside what the partnership funds or convenes, or is high school the whole remit?
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M18" s="5" t="inlineStr"/>
       <c r="N18" s="5" t="inlineStr"/>
     </row>
@@ -28174,8 +28749,22 @@
           <t>Nicolle — your twelve-book roundup is the one I point people to, which is awkward, because every title on it teaches earning or saving. Mine teaches spending: the whole transaction, right through the register, sales tax and the small indignity that follows. Worth a look for the next update, or does a spend-first book break the shelf? Either way I'd rather you heard it from me. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr"/>
-      <c r="L19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Nicolle — your twelve-book roundup is the one I point people to, which is slightly awkward, because every title on it teaches earning or saving.
+That's not a criticism of the list. It's an accurate reflection of what exists. I went looking for the spending book and could not find it, so I wrote it.
+The argument in one line: saving is the second thing a child does with money, and the first is spending. A six-year-old has no savings rate and has definitely stood in a store holding a birthday five, deciding whether the thing is worth what it costs.
+Clarence Gets a Bargain follows one purchase from the idea to after the receipt. A boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Sixteen-plus concepts and nobody in the book says "budget." Twenty-one terms in the glossary, each page-referenced to the scene it came from.
+Two asks, and the second one matters more. Worth a look for the next update to the roundup? And separately — you run a company built on kids and money, so if you think spending-before-saving is wrong, I would rather hear it from you than keep saying it at conferences.
+I'll send a copy either way. https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M19" s="5" t="inlineStr"/>
       <c r="N19" s="5" t="inlineStr"/>
     </row>
@@ -28312,8 +28901,22 @@
           <t>Hunter — policy and advocacy at NEFE puts you where the K-5 gap is most visible. Nearly everything funded sits at high school. I wrote a picture book plus free teacher materials for grades 1-5 against five frameworks. Is early elementary getting any policy attention, or still an orphan? The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Hunter — a policy observation, and a question about whether NEFE has a view on it.
+Thirty states now require a personal finance course to graduate. Delaware became the thirtieth last October. Every one of those mandates lands in high school, and the funding and training follow the mandate. Meanwhile the K-5 standards that already exist in most states sit there with almost nothing built against them, because nobody has to report on them.
+The sequence assumption underneath all of it is that children should learn saving first. I think that is backwards. Saving is the second thing a person does with money. The first is spending — and a first grader has done that, at a register, with a parent standing behind her. The behaviors a high school course is trying to correct were installed a decade earlier.
+I wrote the elementary piece rather than an argument about it: a 36-page picture book that follows one purchase from the idea to after the receipt, plus a free ungated classroom set crosswalked to the 2021 National Standards, Common Core, CEE and FDIC Money Smart. Sixteen-plus concepts, none announced, twenty-one-term glossary page-referenced into the story.
+The question: does NEFE's advocacy work have a position on the elementary band, or is the practical view that high school mandates are where the effort actually pays? I ask because if it's the second, I'd like to know I'm arguing with the consensus rather than filling a gap it agrees exists.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M22" s="5" t="inlineStr"/>
       <c r="N22" s="5" t="inlineStr"/>
     </row>
@@ -29613,41 +30216,51 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>199-396</t>
+          <t>1-202</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Carly Urban</t>
+          <t>Roda Ducommun</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Montana State — definitive research on finlit mandates</t>
+          <t>Proud Mom | Happy Wife | Author | Investor | Founder of Smart Money Kids World TV®️ &amp; The Shortcuts Hub | · 1st-degree · DM</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Montana State — definitive research on finlit mandates</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>1st-degree · DM</t>
-        </is>
-      </c>
+          <t>Proud Mom | Happy Wife | Author | Investor | Founder of Smart Money Kids World TV®️ &amp; The Shortcuts Hub | · 1st-degree · DM</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr"/>
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="n">
-        <v>438</v>
+        <v>350</v>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Professor Urban — your work on financial education mandates is the best evidence we have on what actually moves outcomes, and nearly all of it sits at high school. I wrote a K-5 book on the premise that elementary is both untested and undersupplied. Is there research I should know before I keep saying that? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr"/>
-      <c r="L51" s="5" t="inlineStr"/>
+          <t>Roda — Smart Money Kids World and Clarence share an audience. Mine is narrow on purpose: one purchase, all the way through the register. As a fellow author and founder — does narrow work better at this age? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>Roda — you built a 30-Day Smart Spending Challenge. Not a saving challenge. Spending. As far as I can tell that makes two of us in this entire category who think the sequence is backwards.
+Here is my version of the argument, and I'd like to know whether it matches how you arrived at yours. Every children's money book teaches saving — I read all 25 on the ABA Foundation's list to be sure. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. We teach the second thing first and the first thing never.
+Clarence Gets a Bargain is the picture-book version. It follows a single purchase the whole distance — a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced; nobody says "budget." Twenty-one terms in a glossary at the end, each page-referenced to where it happened — which is the only point at which a kid works out he's been schooled.
+Your Challenge is a thirty-day habit; mine is one transaction read in twenty minutes. Those look complementary to me rather than competing — the book could be the on-ramp to a challenge, or the thing a parent reads on day one.
+Worth a conversation? I'd rather compare notes with the one other person who put spending first than pitch anybody.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M51" s="5" t="inlineStr"/>
       <c r="N51" s="5" t="inlineStr"/>
     </row>
@@ -29659,41 +30272,51 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>199-396</t>
+          <t>1-202</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Iris SooJin Park</t>
+          <t>Daniel Hagadorn</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>UW-Madison — the group that picked the CFPB Bookshelf titles</t>
+          <t>Founder; 360 Parenting | 🎤Speaker 📓Author 🎧Podcaster CONTACT: dh@PK4L.com · 1st-degree · DM</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>UW-Madison — the group that picked the CFPB Bookshelf titles</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>1st-degree · DM</t>
-        </is>
-      </c>
+          <t>Founder; 360 Parenting | 🎤Speaker 📓Author 🎧Podcaster CONTACT: dh@PK4L.com · 1st-degree · DM</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr"/>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="n">
-        <v>372</v>
+        <v>283</v>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Iris — you're at UW-Madison, which is where the Center for Financial Security picked the titles for the CFPB's Money as You Grow Bookshelf. Mine is K-5 and goes at spending instead of saving. Do you know who evaluates additions to that shelf? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr"/>
-      <c r="L52" s="5" t="inlineStr"/>
+          <t>Daniel — 360 Parenting reaches families weekly, and spending is where parents and kids collide first, usually in an aisle, usually loudly. Mine is that scene, resolved well. Podcast fit? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>Daniel — you built 360 Parenting around the whole child rather than one slice of them, so this is a slice you may be missing, and I say that as someone who only noticed it because I went looking for a book and could not find one.
+Money education for kids begins with saving. Every time. But saving is the second thing a child does with money. The first is spending — and a six-year-old has done that, repeatedly, usually in a store, usually while a parent quietly loses the will to live.
+So I wrote the spending book. One purchase, followed the entire way: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, discovers sales tax the way we all did — badly, and in public — and then has to live with the thing he chose. From the idea to after the receipt.
+Here is why it might fit a parenting audience rather than a classroom one. The concepts are smuggled. Sixteen-plus of them, none announced, nobody saying the word "budget." It reads as a story about a kid and a robot, and the parent doing the read-aloud gets handed the money conversation without having to deliver a lesson. And the kid does not know he's been schooled until he gets to the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. A parent can turn straight back to the exact page.
+Would it work for your audience — podcast, newsletter, or neither? A no is a fine answer and faster than a maybe.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M52" s="5" t="inlineStr"/>
       <c r="N52" s="5" t="inlineStr"/>
     </row>
@@ -29705,40 +30328,244 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>199-396</t>
+          <t>1-202</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Neale Mahoney</t>
+          <t>ML Bruin</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Stanford SIEPR — Director</t>
+          <t>Award-winning Children’s Book &amp; Educational Author | Creator of the “Noah” Series Inspiring Young Readers · 1st-degree · DM</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Stanford SIEPR — Director</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>1st-degree · DM</t>
-        </is>
-      </c>
+          <t>Award-winning Children’s Book &amp; Educational Author | Creator of the “Noah” Series Inspiring Young Readers · 1st-degree · DM</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr"/>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="n">
+        <v>293</v>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>ML — the Noah series shows you can carry a lesson without smothering the story, which is my whole anxiety about my own book. Would you read it as an author and tell me if the lesson shows too much? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>ML — you built a series a child comes back to, which is harder than writing one good book, and it's the reason I'm writing to a peer rather than a gatekeeper.
+Mine is a money book, which I appreciate is the least promising sentence in children's publishing. So here is the part that makes it not that.
+Every book in this category teaches saving. Saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it — in a store, holding money, deciding whether the thing is worth what it costs. So mine follows one purchase from the idea to after the receipt: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose.
+The craft problem I'd most like another author's view on: I smuggled sixteen-plus concepts in without announcing any of them. Nobody says "budget." The glossary in the back — twenty-one terms, each page-referenced to the scene it came from — is the only place the book admits it was teaching. Getting that balance right, so it stays a story, was the whole job.
+Would you read it and tell me where it stops being a story? I'll trade — send me a Noah and I'll read it properly.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr"/>
+      <c r="N53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>1-202</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Linda Simpson</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Financial Parenting Educator; Professor; Financial Literacy Educator, Coach and Consultant, Speaker, &amp; Au · 1st-degree · DM</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Financial Parenting Educator; Professor; Financial Literacy Educator, Coach and Consultant, Speaker, &amp; Au · 1st-degree · DM</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr"/>
+      <c r="I54" s="5" t="n">
+        <v>490</v>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>Linda — financial parenting is your field, and spending is where parents and kids collide first, usually in an aisle, usually loudly. Mine is that scene resolved well: a six-year-old compares two robots and talks himself into the cheaper one. Built with a K-5 teacher of 30+ years, 21-term glossary, free lessons. Would you put it in front of the parents you teach? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>Linda — you teach financial parenting, which means you spend your working life on the exact handoff I wrote a book about: the moment a parent has to explain money to a child who is standing right there wanting something.
+My argument, and you are better placed than almost anyone to tell me it's wrong. Financial education for children starts with saving, and it has the sequence backwards. A seven-year-old has no savings rate and no income. What she has done is stand at a register holding money and decide. Spending is the first money behavior a person performs. We teach it last, or not at all.
+Clarence Gets a Bargain is the spending book. It follows one purchase the whole distance — wanting the thing, earning it through chores and grades, reading the sale inserts at the kitchen table with a parent, comparing two models on a shelf, choosing the cheaper one on purpose, handing over a coupon, meeting sales tax, and then living with what he bought. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; not one covers the whole arc.
+The design choice that matters for your work: nothing is announced. Sixteen-plus concepts and nobody in the book says "budget." The parent reading aloud is handed the conversation without having to give a lecture, which I gather is most of what you coach people out of. The child does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. The reveal is the last thing that happens, not the first.
+Two questions, either useful. Does the spending-before-saving sequence hold up against what you see in families? And is there a version of this that belongs in front of the parents you train?
+clarencegetsabargain.com/book-facts.html · https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr"/>
+      <c r="N54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>199-396</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Carly Urban</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Montana State — definitive research on finlit mandates</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Montana State — definitive research on finlit mandates</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>1st-degree · DM</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr"/>
+      <c r="I55" s="5" t="n">
+        <v>438</v>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>Professor Urban — your work on financial education mandates is the best evidence we have on what actually moves outcomes, and nearly all of it sits at high school. I wrote a K-5 book on the premise that elementary is both untested and undersupplied. Is there research I should know before I keep saying that? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr"/>
+      <c r="L55" s="5" t="inlineStr"/>
+      <c r="M55" s="5" t="inlineStr"/>
+      <c r="N55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>199-396</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Iris SooJin Park</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>UW-Madison — the group that picked the CFPB Bookshelf titles</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>UW-Madison — the group that picked the CFPB Bookshelf titles</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>1st-degree · DM</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr"/>
+      <c r="H56" s="5" t="inlineStr"/>
+      <c r="I56" s="5" t="n">
         <v>372</v>
       </c>
-      <c r="J53" s="5" t="inlineStr">
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>Iris — you're at UW-Madison, which is where the Center for Financial Security picked the titles for the CFPB's Money as You Grow Bookshelf. Mine is K-5 and goes at spending instead of saving. Do you know who evaluates additions to that shelf? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr"/>
+      <c r="L56" s="5" t="inlineStr"/>
+      <c r="M56" s="5" t="inlineStr"/>
+      <c r="N56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>199-396</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Neale Mahoney</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Stanford SIEPR — Director</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Stanford SIEPR — Director</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>1st-degree · DM</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr"/>
+      <c r="H57" s="5" t="inlineStr"/>
+      <c r="I57" s="5" t="n">
+        <v>372</v>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
         <is>
           <t>Professor Mahoney — a question rather than a pitch. My K-5 book argues consumer transaction competence is taught almost nowhere, despite being the money behavior kids perform first. From a behavioral angle, is that a real gap or a rounding error? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="K57" s="5" t="inlineStr">
         <is>
           <t>Professor Mahoney — you describe yourself as an applied micro-economist interested in consumer financial markets, and you spent 2022 and 2023 at the National Economic Council working on how people get taken advantage of in them. I wrote a children's book about the same thing and I'd like ten seconds of your reaction to the premise.
 Every consumer-protection fight starts with a person in front of a price who doesn't have the information, the time, or the habit to evaluate it. That habit has to start somewhere. As far as I can tell it does not start in a classroom, because financial education arrives in ninth grade, and it does not start in children's books, because those all teach saving.
@@ -29749,98 +30576,98 @@
 Baltimore</t>
         </is>
       </c>
-      <c r="L53" s="5" t="inlineStr">
+      <c r="L57" s="5" t="inlineStr">
         <is>
           <t>Subject: Applied micro, twenty years early · Long-form version from Jump$tart</t>
         </is>
       </c>
-      <c r="M53" s="5" t="inlineStr"/>
-      <c r="N53" s="5" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="M57" s="5" t="inlineStr"/>
+      <c r="N57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>🐋</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>199-396</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>Bina Shrimali</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>SF Fed — VP, Community Engagement &amp; Analysis</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>SF Fed — VP, Community Engagement &amp; Analysis</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>1st-degree · DM</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="5" t="n">
+      <c r="G58" s="5" t="inlineStr"/>
+      <c r="H58" s="5" t="inlineStr"/>
+      <c r="I58" s="5" t="n">
         <v>354</v>
       </c>
-      <c r="J54" s="5" t="inlineStr">
+      <c r="J58" s="5" t="inlineStr">
         <is>
           <t>Bina — community engagement at the SF Fed is where household financial capability actually gets measured. Mine teaches the spending half, on the theory the sequence is backwards. Does that square with what you see? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K54" s="5" t="inlineStr"/>
-      <c r="L54" s="5" t="inlineStr"/>
-      <c r="M54" s="5" t="inlineStr"/>
-      <c r="N54" s="5" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="K58" s="5" t="inlineStr"/>
+      <c r="L58" s="5" t="inlineStr"/>
+      <c r="M58" s="5" t="inlineStr"/>
+      <c r="N58" s="5" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>🐋</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>199-396</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>Andrea Sticha</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>Research Director · 1st-degree · DM</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>Research Director · 1st-degree · DM</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr"/>
-      <c r="G55" s="5" t="inlineStr"/>
-      <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="5" t="n">
+      <c r="F59" s="5" t="inlineStr"/>
+      <c r="G59" s="5" t="inlineStr"/>
+      <c r="H59" s="5" t="inlineStr"/>
+      <c r="I59" s="5" t="n">
         <v>349</v>
       </c>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="J59" s="5" t="inlineStr">
         <is>
           <t>Andrea — as a research director you'll want the claim before the book. Mine: consumer transaction competence is taught almost nowhere in K-5. I built a picture book and free teacher pack around it. Evidence against? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="K59" s="5" t="inlineStr">
         <is>
           <t>Dr. Sticha — you sit on the Jump$tart board for the Stanford Initiative on Financial Decision-Making, and your research is household financial literacy and wellbeing. So this is a research question with a book attached, rather than the reverse.
 Here is what I ran into. Almost every children's financial literacy book teaches saving. I read the entire ABA Foundation list to be sure. Piggy banks, jars, lemonade stands, wait for it.
@@ -29853,195 +30680,11 @@
 https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="L55" s="5" t="inlineStr">
+      <c r="L59" s="5" t="inlineStr">
         <is>
           <t>Subject: A K-5 gap, from someone who just read your board's own standards · Long-form version from Jump$tart</t>
         </is>
       </c>
-      <c r="M55" s="5" t="inlineStr"/>
-      <c r="N55" s="5" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>🐋</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>397-516</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>Jennifer Klein</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>Harlem Children's Zone — Chief Development Officer</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>Harlem Children's Zone — Chief Development Officer</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>1st-degree · DM</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr"/>
-      <c r="H56" s="5" t="inlineStr"/>
-      <c r="I56" s="5" t="n">
-        <v>375</v>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>Jennifer — Harlem Children's Zone is deliberate about what earns a kid's time. Mine teaches the complete purchase, sales tax included, and the family activity was built for a kitchen table rather than a classroom. Fit your programming, or your development conversations? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr"/>
-      <c r="L56" s="5" t="inlineStr"/>
-      <c r="M56" s="5" t="inlineStr"/>
-      <c r="N56" s="5" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>🐋</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>397-516</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>Flora Teo</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Junior Achievement of Alaska — President</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>Junior Achievement of Alaska — President</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>1st-degree · DM</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr"/>
-      <c r="H57" s="5" t="inlineStr"/>
-      <c r="I57" s="5" t="n">
-        <v>357</v>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>Flora — JA reaches more kids than almost anybody, and elementary is usually where the material thins out. Mine is a K-5 picture book with a free zero-prep classroom pack against five frameworks, teaching spending rather than saving. Fit anything JA Alaska runs? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="inlineStr"/>
-      <c r="L57" s="5" t="inlineStr"/>
-      <c r="M57" s="5" t="inlineStr"/>
-      <c r="N57" s="5" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>🐋</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>397-516</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>Elizabeth Coogan</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>U.S. Department of Education — Financial Education</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>U.S. Department of Education — Financial Education</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>1st-degree · DM</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr"/>
-      <c r="H58" s="5" t="inlineStr"/>
-      <c r="I58" s="5" t="n">
-        <v>351</v>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>Elizabeth — financial education at the Department of Education is the mission my book starts on, just twelve years early. Mine is K-5, teaching spending rather than saving, against five frameworks. Fit any program you touch, or a steer on who'd know? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="inlineStr"/>
-      <c r="L58" s="5" t="inlineStr"/>
-      <c r="M58" s="5" t="inlineStr"/>
-      <c r="N58" s="5" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>🐋</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>397-516</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>Gene Natali</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>Troutwood founder &amp; CEO</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>Troutwood founder &amp; CEO</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>1st-degree · DM</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr"/>
-      <c r="H59" s="5" t="inlineStr"/>
-      <c r="I59" s="5" t="n">
-        <v>339</v>
-      </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t>Gene — Troutwood makes the financial future tangible for young people. Mine makes the present tangible for a six-year-old: one purchase, compared and paid for, tax included. Does the approach fit what you're building, or sit below it? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
-        </is>
-      </c>
-      <c r="K59" s="5" t="inlineStr"/>
-      <c r="L59" s="5" t="inlineStr"/>
       <c r="M59" s="5" t="inlineStr"/>
       <c r="N59" s="5" t="inlineStr"/>
     </row>
@@ -30058,17 +30701,17 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Rob Phelan</t>
+          <t>Jennifer Klein</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Financial education resource creator — teacher reach</t>
+          <t>Harlem Children's Zone — Chief Development Officer</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Financial education resource creator — teacher reach</t>
+          <t>Harlem Children's Zone — Chief Development Officer</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
@@ -30079,11 +30722,11 @@
       <c r="G60" s="5" t="inlineStr"/>
       <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>Rob — you create financial education resources, so you know what teachers actually use versus what they politely download once. Mine is a K-5 picture book with four zero-prep lessons, assessments, and a 23-row crosswalk, all free and ungated. Fit your catalog, or duplicate it? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jennifer — Harlem Children's Zone is deliberate about what earns a kid's time. Mine teaches the complete purchase, sales tax included, and the family activity was built for a kitchen table rather than a classroom. Fit your programming, or your development conversations? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr"/>
@@ -30099,22 +30742,22 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>517-616</t>
+          <t>397-516</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Martin Seay</t>
+          <t>Flora Teo</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>CFP Board — Chair-Elect</t>
+          <t>Junior Achievement of Alaska — President</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>CFP Board — Chair-Elect</t>
+          <t>Junior Achievement of Alaska — President</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
@@ -30125,11 +30768,11 @@
       <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="n">
-        <v>422</v>
+        <v>357</v>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Martin — Chair-Elect of the CFP Board means a kids' picture book is a long way upstream of your day. That's rather the point. Spending is the first money skill a kid uses, nobody wrote the picture book for it, so I did. Five frameworks, K-5. Does it fit the early-education push the field keeps talking about, or is that talk? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Flora — JA reaches more kids than almost anybody, and elementary is usually where the material thins out. Mine is a K-5 picture book with a free zero-prep classroom pack against five frameworks, teaching spending rather than saving. Fit anything JA Alaska runs? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr"/>
@@ -30145,22 +30788,22 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>517-616</t>
+          <t>397-516</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Ed Pacchetti</t>
+          <t>Elizabeth Coogan</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>U.S. Department of Education — Director</t>
+          <t>U.S. Department of Education — Financial Education</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>U.S. Department of Education — Director</t>
+          <t>U.S. Department of Education — Financial Education</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
@@ -30171,11 +30814,11 @@
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="n">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Ed — a director at the Department of Education is exactly who I want on this. Mine is K-5, teaching spending rather than saving, with free standards-aligned lessons and nothing to reorder. Fit any program you touch, or a steer on who'd know? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Elizabeth — financial education at the Department of Education is the mission my book starts on, just twelve years early. Mine is K-5, teaching spending rather than saving, against five frameworks. Fit any program you touch, or a steer on who'd know? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr"/>
@@ -30191,22 +30834,22 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>517-616</t>
+          <t>397-516</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Jeff Larrimore</t>
+          <t>Gene Natali</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Federal Reserve — Chief, Consumer &amp; Community Research</t>
+          <t>Troutwood founder &amp; CEO</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Federal Reserve — Chief, Consumer &amp; Community Research</t>
+          <t>Troutwood founder &amp; CEO</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
@@ -30217,11 +30860,11 @@
       <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr"/>
       <c r="I63" s="5" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Jeff — you lead consumer and community research at the Fed, so you study exactly the gaps my book tries to prevent. Mine argues spending competence precedes saving competence and is taught almost nowhere. Does that square with your research? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Gene — Troutwood makes the financial future tangible for young people. Mine makes the present tangible for a six-year-old: one purchase, compared and paid for, tax included. Does the approach fit what you're building, or sit below it? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr"/>
@@ -30237,22 +30880,22 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>517-616</t>
+          <t>397-516</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Annie Shoen</t>
+          <t>Rob Phelan</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>My First Nest Egg co-founder</t>
+          <t>Financial education resource creator — teacher reach</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>My First Nest Egg co-founder</t>
+          <t>Financial education resource creator — teacher reach</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
@@ -30263,11 +30906,11 @@
       <c r="G64" s="5" t="inlineStr"/>
       <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="n">
-        <v>330</v>
+        <v>374</v>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>Annie — My First Nest Egg and Clarence chase the same kid. Yours is the account; mine is the trip to the store. Spending rather than saving, one purchase, ad to register. Complementary, I think. Worth comparing notes, or trading copies? More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Rob — you create financial education resources, so you know what teachers actually use versus what they politely download once. Mine is a K-5 picture book with four zero-prep lessons, assessments, and a 23-row crosswalk, all free and ungated. Fit your catalog, or duplicate it? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr"/>
@@ -30283,37 +30926,37 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>New July</t>
+          <t>517-616</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Sandy Spavone</t>
+          <t>Martin Seay</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>FCCLA CEO — 257,000+ members, 5,300+ chapters, 49 states</t>
+          <t>CFP Board — Chair-Elect</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>CEO of FCCLA. 257,000+ members, 5,300+ chapters, 49 state associations. Financial literacy is already an active focus (Virtual Business Challenge). The catch: FCCLA is Family &amp; Consumer Sciences, so members are middle and high school, not K-5. The play is not curriculum adoption, it is service proje</t>
+          <t>CFP Board — Chair-Elect</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Gatekeeper · connected Jul 25 · 1st-degree</t>
+          <t>1st-degree · DM</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="n">
-        <v>589</v>
+        <v>422</v>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Sandy — FCCLA members are a decade older than my readers, so this is not a curriculum pitch. It's a service-project one. Your chapters already run community work, and a high schooler reading a money book to a second-grade class is about the cleanest version of that I can think of. Mine is 36 pages, teaches the whole purchase through the register, and the classroom pack behind it is free. Does that fit how chapters choose projects, or am I inventing a use case? Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Martin — Chair-Elect of the CFP Board means a kids' picture book is a long way upstream of your day. That's rather the point. Spending is the first money skill a kid uses, nobody wrote the picture book for it, so I did. Five frameworks, K-5. Does it fit the early-education push the field keeps talking about, or is that talk? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr"/>
@@ -30329,37 +30972,37 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>New July</t>
+          <t>517-616</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Megan Kirts</t>
+          <t>Ed Pacchetti</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Econiful — Executive Director</t>
+          <t>U.S. Department of Education — Director</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Executive Director, Econiful (Tucson nonprofit, free resources for economics educators). 17 years in the classroom, 2024 NAEE Rising Star, currently building an 80-lesson high school econ curriculum. Econiful serves Grade 6+, so mine sits directly below her band. Complementary rather than competitiv</t>
+          <t>U.S. Department of Education — Director</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Gatekeeper · connected Jul 24 · 1st-degree</t>
+          <t>1st-degree · DM</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="n">
-        <v>504</v>
+        <v>346</v>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Megan — Econiful starts at grade 6, which puts my book directly underneath you rather than beside you. Mine is the K-5 on-ramp: a six-year-old runs one purchase, ad to register, sales tax at the end. Congratulations on the Rising Star, by the way. Genuine question rather than a pitch — do you see elementary as in scope for Econiful, or a gap somebody else has to fill? For teachers: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ed — a director at the Department of Education is exactly who I want on this. Mine is K-5, teaching spending rather than saving, with free standards-aligned lessons and nothing to reorder. Fit any program you touch, or a steer on who'd know? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr"/>
@@ -30375,37 +31018,37 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>New July</t>
+          <t>517-616</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Daniel Rauen</t>
+          <t>Jeff Larrimore</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>CASHVERSE KIDS — same story-first thesis, verbatim</t>
+          <t>Federal Reserve — Chief, Consumer &amp; Community Research</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Founder of CASHVERSE KIDS, 'Building a Story-First Financial Literacy Universe for Kids.' German-speaking (headline reads 'Founder bei'). Not indexed anywhere I can find, so likely pre-launch or very new. Same thesis as yours, stated almost word for word. Closest philosophical peer in the entire lis</t>
+          <t>Federal Reserve — Chief, Consumer &amp; Community Research</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Peer author · connected Jul 22 · 1st-degree</t>
+          <t>1st-degree · DM</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="n">
-        <v>471</v>
+        <v>337</v>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>Daniel — 'story-first financial literacy' is my entire thesis too, which is either a good sign or a crowded room. Mine went narrow: one purchase, ad to register, sales tax at the end, 36 pages. Yours sounds like a universe rather than a single trip. Curious whether we are solving the same problem at different scales, or the same scale from different ends. Trade notes? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jeff — you lead consumer and community research at the Fed, so you study exactly the gaps my book tries to prevent. Mine argues spending competence precedes saving competence and is taught almost nowhere. Does that square with your research? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr"/>
@@ -30421,37 +31064,37 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>New July</t>
+          <t>517-616</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Stephanie Zimmermann</t>
+          <t>Annie Shoen</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Chicago Sun-Times — investigative reporter</t>
+          <t>My First Nest Egg co-founder</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Investigative reporter, Chicago Sun-Times. Consumer investigations rather than personal finance columns, so the hook is the category gap, not the book. Pitch the omission and let her decide whether it's a story.</t>
+          <t>My First Nest Egg co-founder</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Press / Editor · connected Jul 23 · 1st-degree</t>
+          <t>1st-degree · DM</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr"/>
       <c r="H68" s="5" t="inlineStr"/>
       <c r="I68" s="5" t="n">
-        <v>561</v>
+        <v>330</v>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>Stephanie — an investigations angle rather than a book pitch. Children's financial literacy is a real publishing category, and every title in it teaches saving. I read all 25 on the ABA Foundation's list to be sure. None teaches spending, which is the only money thing a six-year-old actually does. Forty years, one blind spot. I wrote the counterexample, but the gap is the more interesting half. Worth a look, or a colleague who'd want it? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Annie — My First Nest Egg and Clarence chase the same kid. Yours is the account; mine is the trip to the store. Spending rather than saving, one purchase, ad to register. Complementary, I think. Worth comparing notes, or trading copies? More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr"/>
@@ -30472,36 +31115,50 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Danial Khan</t>
+          <t>Sandy Spavone</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Stanford FCU — Financial Wellness Lead</t>
+          <t>FCCLA CEO — 257,000+ members, 5,300+ chapters, 49 states</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Financial Wellness Lead at Stanford Federal Credit Union. '2026 GAC Crasher' means he was at the Governmental Affairs Conference, so he is plugged into the national credit union scene, not just his own shop. Credit unions are the most likely local funders of K-5 sets.</t>
+          <t>CEO of FCCLA. 257,000+ members, 5,300+ chapters, 49 state associations. Financial literacy is already an active focus (Virtual Business Challenge). The catch: FCCLA is Family &amp; Consumer Sciences, so members are middle and high school, not K-5. The play is not curriculum adoption, it is service proje</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Credit union / Bank · connected Jul 24 · 1st-degree</t>
+          <t>Gatekeeper · connected Jul 25 · 1st-degree</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr"/>
       <c r="H69" s="5" t="inlineStr"/>
       <c r="I69" s="5" t="n">
-        <v>519</v>
+        <v>589</v>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>Danial — 'making money more human' is a good line, and it happens to be the hardest part of teaching a six-year-old. Mine does it by refusing to be a worksheet: a boy, a robot, one real purchase through the register. There's a grant packet behind it with the math already done, 25 copies at $499.75, in case Stanford FCU ever funds a classroom set. Fit a member or community program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
-        </is>
-      </c>
-      <c r="K69" s="5" t="inlineStr"/>
-      <c r="L69" s="5" t="inlineStr"/>
+          <t>Sandy — FCCLA members are a decade older than my readers, so this is not a curriculum pitch. It's a service-project one. Your chapters already run community work, and a high schooler reading a money book to a second-grade class is about the cleanest version of that I can think of. Mine is 36 pages, teaches the whole purchase through the register, and the classroom pack behind it is free. Does that fit how chapters choose projects, or am I inventing a use case? Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>Sandy — FCCLA members are a decade older than my readers, so this is not a curriculum pitch. It is a service-project one, and I think it's a good one.
+Your chapters run community service. A high schooler reading a money book to a second-grade class is about the cleanest version of that I can think of — it needs no budget, no training, and one afternoon.
+The book is Clarence Gets a Bargain, 36 pages, ages 6-10. It follows one purchase the whole way, which is the thing that makes it work as a read-aloud rather than a lecture: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in it says "budget" — the twenty-one-term glossary in the back is page-referenced to the story, so the reader can field questions without preparing.
+It reads aloud in about twenty minutes, which is a class visit with time left for questions. And there is a free browser-based pretend register the younger kids can run afterward — a markdown, a coupon, sales tax, and a total that changes in front of them.
+Does that fit how chapters choose service projects, or am I inventing a use case? Everything is free and ungated either way.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from TOP25 wk1</t>
+        </is>
+      </c>
       <c r="M69" s="5" t="inlineStr"/>
       <c r="N69" s="5" t="inlineStr"/>
     </row>
@@ -30513,35 +31170,219 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>New Jul 28-29</t>
+          <t>New July</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Briana Walker</t>
+          <t>Megan Kirts</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>MAESP Zone 4 (Eastern Shore) Rep · 2026 NAESP National Outstanding Assistant Principal · Greensboro Elementary, Caroline County</t>
+          <t>Econiful — Executive Director</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The single best fit on the screen, because she sits at the intersection of three things already in the repo. She is the **MAESP Zone 4 rep for the Eastern Shore** — the same association you have nine letters written for — which makes her a distribution node, not just a reader. She is a **2026 NAESP </t>
+          <t>Executive Director, Econiful (Tucson nonprofit, free resources for economics educators). 17 years in the classroom, 2024 NAEE Rising Star, currently building an 80-lesson high school econ curriculum. Econiful serves Grade 6+, so mine sits directly below her band. Complementary rather than competitiv</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Gatekeeper · connected Jul 28 · 1st-degree</t>
+          <t>Gatekeeper · connected Jul 24 · 1st-degree</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr"/>
       <c r="H70" s="5" t="inlineStr"/>
       <c r="I70" s="5" t="n">
+        <v>504</v>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>Megan — Econiful starts at grade 6, which puts my book directly underneath you rather than beside you. Mine is the K-5 on-ramp: a six-year-old runs one purchase, ad to register, sales tax at the end. Congratulations on the Rising Star, by the way. Genuine question rather than a pitch — do you see elementary as in scope for Econiful, or a gap somebody else has to fill? For teachers: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr"/>
+      <c r="L70" s="5" t="inlineStr"/>
+      <c r="M70" s="5" t="inlineStr"/>
+      <c r="N70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>New July</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Daniel Rauen</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>CASHVERSE KIDS — same story-first thesis, verbatim</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Founder of CASHVERSE KIDS, 'Building a Story-First Financial Literacy Universe for Kids.' German-speaking (headline reads 'Founder bei'). Not indexed anywhere I can find, so likely pre-launch or very new. Same thesis as yours, stated almost word for word. Closest philosophical peer in the entire lis</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Peer author · connected Jul 22 · 1st-degree</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr"/>
+      <c r="I71" s="5" t="n">
+        <v>471</v>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>Daniel — 'story-first financial literacy' is my entire thesis too, which is either a good sign or a crowded room. Mine went narrow: one purchase, ad to register, sales tax at the end, 36 pages. Yours sounds like a universe rather than a single trip. Curious whether we are solving the same problem at different scales, or the same scale from different ends. Trade notes? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr"/>
+      <c r="L71" s="5" t="inlineStr"/>
+      <c r="M71" s="5" t="inlineStr"/>
+      <c r="N71" s="5" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>New July</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Stephanie Zimmermann</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Chicago Sun-Times — investigative reporter</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>Investigative reporter, Chicago Sun-Times. Consumer investigations rather than personal finance columns, so the hook is the category gap, not the book. Pitch the omission and let her decide whether it's a story.</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>Press / Editor · connected Jul 23 · 1st-degree</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr"/>
+      <c r="H72" s="5" t="inlineStr"/>
+      <c r="I72" s="5" t="n">
+        <v>561</v>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>Stephanie — an investigations angle rather than a book pitch. Children's financial literacy is a real publishing category, and every title in it teaches saving. I read all 25 on the ABA Foundation's list to be sure. None teaches spending, which is the only money thing a six-year-old actually does. Forty years, one blind spot. I wrote the counterexample, but the gap is the more interesting half. Worth a look, or a colleague who'd want it? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr"/>
+      <c r="L72" s="5" t="inlineStr"/>
+      <c r="M72" s="5" t="inlineStr"/>
+      <c r="N72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>New July</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Danial Khan</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Stanford FCU — Financial Wellness Lead</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Financial Wellness Lead at Stanford Federal Credit Union. '2026 GAC Crasher' means he was at the Governmental Affairs Conference, so he is plugged into the national credit union scene, not just his own shop. Credit unions are the most likely local funders of K-5 sets.</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Credit union / Bank · connected Jul 24 · 1st-degree</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr"/>
+      <c r="H73" s="5" t="inlineStr"/>
+      <c r="I73" s="5" t="n">
+        <v>519</v>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>Danial — 'making money more human' is a good line, and it happens to be the hardest part of teaching a six-year-old. Mine does it by refusing to be a worksheet: a boy, a robot, one real purchase through the register. There's a grant packet behind it with the math already done, 25 copies at $499.75, in case Stanford FCU ever funds a classroom set. Fit a member or community program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr"/>
+      <c r="L73" s="5" t="inlineStr"/>
+      <c r="M73" s="5" t="inlineStr"/>
+      <c r="N73" s="5" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>New Jul 28-29</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Briana Walker</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>MAESP Zone 4 (Eastern Shore) Rep · 2026 NAESP National Outstanding Assistant Principal · Greensboro Elementary, Caroline County</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The single best fit on the screen, because she sits at the intersection of three things already in the repo. She is the **MAESP Zone 4 rep for the Eastern Shore** — the same association you have nine letters written for — which makes her a distribution node, not just a reader. She is a **2026 NAESP </t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>Gatekeeper · connected Jul 28 · 1st-degree</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr"/>
+      <c r="H74" s="5" t="inlineStr"/>
+      <c r="I74" s="5" t="n">
         <v>1414</v>
       </c>
-      <c r="J70" s="5" t="inlineStr">
+      <c r="J74" s="5" t="inlineStr">
         <is>
           <t>Briana — congratulations on the National Outstanding Assistant Principal award. First elementary winner from Caroline County, which I did not know until I went looking, and now I can't unsee how overdue it was.
 I'm writing because you're the Eastern Shore rep for MAESP and I'm down your way often — I spend a good part of the year in Rehoboth, so Greensboro is nearly the neighborhood.
@@ -30551,48 +31392,48 @@
 Jonathan</t>
         </is>
       </c>
-      <c r="K70" s="5" t="inlineStr"/>
-      <c r="L70" s="5" t="inlineStr"/>
-      <c r="M70" s="5" t="inlineStr"/>
-      <c r="N70" s="5" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="K74" s="5" t="inlineStr"/>
+      <c r="L74" s="5" t="inlineStr"/>
+      <c r="M74" s="5" t="inlineStr"/>
+      <c r="N74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>🐋</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>New Jul 28-29</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>Lauren Nowacki</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>Money Deputy Editor, WSJ Buy Side · Certified Financial Health Counselor</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>Press whale. Buy Side is the Wall Street Journal's personal-finance</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr">
         <is>
           <t>Press / Editor · connected Jul 29 · 1st-degree</t>
         </is>
       </c>
-      <c r="G71" s="5" t="inlineStr"/>
-      <c r="H71" s="5" t="inlineStr"/>
-      <c r="I71" s="5" t="n">
+      <c r="G75" s="5" t="inlineStr"/>
+      <c r="H75" s="5" t="inlineStr"/>
+      <c r="I75" s="5" t="n">
         <v>1288</v>
       </c>
-      <c r="J71" s="5" t="inlineStr">
+      <c r="J75" s="5" t="inlineStr">
         <is>
           <t>Lauren — a story rather than a pitch, and you can kill it in one line.
 I read all 25 titles on the ABA Foundation's children's financial literacy list to be sure of this: every single one teaches earning, saving, or investing. Not one teaches spending — the only money thing a seven-year-old has actually done.
@@ -30602,52 +31443,52 @@
 Jonathan</t>
         </is>
       </c>
-      <c r="K71" s="5" t="inlineStr"/>
-      <c r="L71" s="5" t="inlineStr"/>
-      <c r="M71" s="5" t="inlineStr"/>
-      <c r="N71" s="5" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
+      <c r="K75" s="5" t="inlineStr"/>
+      <c r="L75" s="5" t="inlineStr"/>
+      <c r="M75" s="5" t="inlineStr"/>
+      <c r="N75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>🔵</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>Dr. Bonnie Meszaros</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>Elementary School Program Coordinator, UD Center for Economic Education &amp; Entrepreneurship</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr"/>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr"/>
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="G76" s="5" t="inlineStr">
         <is>
           <t>meszaros@udel.edu</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="H76" s="5" t="inlineStr">
         <is>
           <t>You built lessons around picture books. I built a picture book around lessons.</t>
         </is>
       </c>
-      <c r="I72" s="5" t="n">
+      <c r="I76" s="5" t="n">
         <v>2598</v>
       </c>
-      <c r="J72" s="5" t="inlineStr">
+      <c r="J76" s="5" t="inlineStr">
         <is>
           <t>Dr. Meszaros — you wrote a K and first-grade curriculum where the lesson lives inside the book. Monster Musical Chairs carries scarcity. The Little Red Hen Makes Pizza carries producers and consumers. Bunny Money carries a savings goal. Colonial adopted the kindergarten set outright.
 I came at the same problem from the other end. I wrote the picture book and put the economics inside it, then checked it against the standards after — including the National Standards for Financial Literacy, which I understand you co-authored. That is an odd thing to write to someone. I'd rather say it than pretend I found the framework on my own.
@@ -30661,56 +31502,56 @@
 Baltimore, and Rehoboth Beach when I can manage it</t>
         </is>
       </c>
-      <c r="K72" s="5" t="inlineStr"/>
-      <c r="L72" s="5" t="inlineStr">
+      <c r="K76" s="5" t="inlineStr"/>
+      <c r="L76" s="5" t="inlineStr">
         <is>
           <t>First. Everything else in Delaware is easier after her.</t>
         </is>
       </c>
-      <c r="M72" s="5" t="inlineStr"/>
-      <c r="N72" s="5" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="M76" s="5" t="inlineStr"/>
+      <c r="N76" s="5" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>🐋</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>Dr. Jennifer Nauman</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>Superintendent, Cape Henlopen School District</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr"/>
-      <c r="F73" s="5" t="inlineStr">
+      <c r="E77" s="5" t="inlineStr"/>
+      <c r="F77" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G73" s="5" t="inlineStr">
+      <c r="G77" s="5" t="inlineStr">
         <is>
           <t>jennifer.nauman@cape.k12.de.us</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="H77" s="5" t="inlineStr">
         <is>
           <t>Five elementary schools, a 2018 standard, and nothing to teach it with</t>
         </is>
       </c>
-      <c r="I73" s="5" t="n">
+      <c r="I77" s="5" t="n">
         <v>2008</v>
       </c>
-      <c r="J73" s="5" t="inlineStr">
+      <c r="J77" s="5" t="inlineStr">
         <is>
           <t>Dr. Nauman — you were an assistant principal at Rehoboth Elementary, then ran Shields for eight years and took it to a National Blue Ribbon. You are running a district now, but you learned the job in an elementary building, which is why this is going to you and not to a curriculum office.
 Delaware adopted financial literacy standards for grades K-12 in 2018. HB 203 arrived last October and put a half-credit personal finance course in front of ninth graders. Good law. It also means K-5 has carried a standard for eight years with essentially nothing built for it, and your five elementary principals are the ones holding that bag.
@@ -30724,56 +31565,56 @@
 clarencegetsabargain.com</t>
         </is>
       </c>
-      <c r="K73" s="5" t="inlineStr"/>
-      <c r="L73" s="5" t="inlineStr">
+      <c r="K77" s="5" t="inlineStr"/>
+      <c r="L77" s="5" t="inlineStr">
         <is>
           <t>Second. One yes covers five buildings.</t>
         </is>
       </c>
-      <c r="M73" s="5" t="inlineStr"/>
-      <c r="N73" s="5" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="M77" s="5" t="inlineStr"/>
+      <c r="N77" s="5" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>🐋</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>Delaware</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>Equetta Jones</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>Principal, Love Creek Elementary, Lewes</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr"/>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="E78" s="5" t="inlineStr"/>
+      <c r="F78" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G74" s="5" t="inlineStr">
+      <c r="G78" s="5" t="inlineStr">
         <is>
           <t>equetta.jones@cape.k12.de.us</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="H78" s="5" t="inlineStr">
         <is>
           <t>A question you're better placed to answer than almost anyone</t>
         </is>
       </c>
-      <c r="I74" s="5" t="n">
+      <c r="I78" s="5" t="n">
         <v>1813</v>
       </c>
-      <c r="J74" s="5" t="inlineStr">
+      <c r="J78" s="5" t="inlineStr">
         <is>
           <t>Ms. Jones — you run Love Creek and you moderate NAESP's Early Career Principal Community of Practice, which means you spend part of your month listening to brand-new principals describe what they're short of. So I'll ask you the question I actually want answered instead of pitching first.
 When financial literacy shows up in an elementary building, what does a first-year principal do with it?
@@ -30786,61 +31627,61 @@
 https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K74" s="5" t="inlineStr"/>
-      <c r="L74" s="5" t="inlineStr">
+      <c r="K78" s="5" t="inlineStr"/>
+      <c r="L78" s="5" t="inlineStr">
         <is>
           <t>Third. Her NAESP seat turns a Lewes yes into a national one.</t>
         </is>
       </c>
-      <c r="M74" s="5" t="inlineStr"/>
-      <c r="N74" s="5" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="M78" s="5" t="inlineStr"/>
+      <c r="N78" s="5" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>🐋</t>
         </is>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>Standalone</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>Mia Baytop Russell</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>Senior Lecturer, Johns Hopkins; Dir., Clark Scholars. Ex-Money Smart (UMD Ext.), ex-VP Wells Fargo Foundation</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>Practitioner, funder and academic in one person. Reference-letter candidate for Jump$tart.</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
+      <c r="F79" s="5" t="inlineStr">
         <is>
           <t>Connection note, then InMail</t>
         </is>
       </c>
-      <c r="G75" s="5" t="inlineStr"/>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="G79" s="5" t="inlineStr"/>
+      <c r="H79" s="5" t="inlineStr">
         <is>
           <t>Money Smart, Wells Fargo, Hopkins — and a premise you can puncture</t>
         </is>
       </c>
-      <c r="I75" s="5" t="n">
+      <c r="I79" s="5" t="n">
         <v>280</v>
       </c>
-      <c r="J75" s="5" t="inlineStr">
+      <c r="J79" s="5" t="inlineStr">
         <is>
           <t>Mia — you ran Money Smart at Maryland Extension, decided what got funded at Wells Fargo, and now teach it at Hopkins. Three chairs, almost nobody has sat in all of them. I wrote a K-5 book aligned to Money Smart that leaves saving out entirely. I'm in Baltimore too. Worth a look?</t>
         </is>
       </c>
-      <c r="K75" s="5" t="inlineStr">
+      <c r="K79" s="5" t="inlineStr">
         <is>
           <t>Mia — you've sat in all three chairs, which almost nobody in this field has. You ran the Money Smart team at Maryland Extension. You decided what got funded as VP for youth financial health philanthropy at Wells Fargo. Now you teach it at Hopkins. Practitioner, funder, academic, in that order.
 Which makes you exactly the person I want to tell me I'm wrong.
@@ -30860,51 +31701,51 @@
 clarencegetsabargain.com</t>
         </is>
       </c>
-      <c r="L75" s="5" t="inlineStr">
+      <c r="L79" s="5" t="inlineStr">
         <is>
           <t>Col M = 280-char connection note. Col N = 1,323-char InMail. | Subject: A reference letter, and the three reasons I'm asking you specifically · Long-form version from Jump$tart</t>
         </is>
       </c>
-      <c r="M75" s="5" t="inlineStr"/>
-      <c r="N75" s="5" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="M79" s="5" t="inlineStr"/>
+      <c r="N79" s="5" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>🐋</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>Standalone</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>Dr. Rachel Edoho-Eket</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>Principal, Waterloo Elementary (Blue Ribbon); Past President, MAESP; 2x author</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E80" s="5" t="inlineStr">
         <is>
           <t>Maryland elementary gatekeeper, local, and an author who judges production.</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
+      <c r="F80" s="5" t="inlineStr">
         <is>
           <t>LinkedIn DM (1st-degree)</t>
         </is>
       </c>
-      <c r="G76" s="5" t="inlineStr"/>
-      <c r="H76" s="5" t="inlineStr"/>
-      <c r="I76" s="5" t="n">
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr"/>
+      <c r="I80" s="5" t="n">
         <v>2014</v>
       </c>
-      <c r="J76" s="5" t="inlineStr">
+      <c r="J80" s="5" t="inlineStr">
         <is>
           <t>Dr. Edoho-Eket — congratulations on the ISTE+ASCD 20 to Watch. What stuck with me wasn't the award, it was what you wrote about it: that it started 21 years ago teaching five-year-olds in Howard County, and that those lessons still guide how you lead.
 Those five-year-olds are my entire readership.
@@ -30919,50 +31760,50 @@
 Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K76" s="5" t="inlineStr"/>
-      <c r="L76" s="5" t="inlineStr">
+      <c r="K80" s="5" t="inlineStr"/>
+      <c r="L80" s="5" t="inlineStr">
         <is>
           <t>Already a connection — single DM, no request note.</t>
         </is>
       </c>
-      <c r="M76" s="5" t="inlineStr"/>
-      <c r="N76" s="5" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="M80" s="5" t="inlineStr"/>
+      <c r="N80" s="5" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>🐋</t>
         </is>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>CFPB/rights</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>Lauren Saunders</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr"/>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr"/>
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>Kids-as-consumers-with-rights thesis. the rights thesis is consumer law, not financial education, and NCLC
 is the country's consumer-law authority. This is the better home for the big idea than any
 agency, and she's a fresh connection who has never heard the</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
+      <c r="F81" s="5" t="inlineStr">
         <is>
           <t>Associate Director, National Consumer Law Center</t>
         </is>
       </c>
-      <c r="G77" s="5" t="inlineStr"/>
-      <c r="H77" s="5" t="inlineStr"/>
-      <c r="I77" s="5" t="n">
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr"/>
+      <c r="I81" s="5" t="n">
         <v>1544</v>
       </c>
-      <c r="J77" s="5" t="inlineStr">
+      <c r="J81" s="5" t="inlineStr">
         <is>
           <t>Lauren — we just connected, and I have a question that belongs at NCLC more than anywhere else I can think of.
 Consumer law assumes a consumer who can read a contract, keep a receipt, and assert a claim. But everyone becomes a consumer years before any of that — the first time a kid spends money at a register. There is a whole population of consumers, roughly six to ten years old, who have no idea they have standing, and almost nothing is written to tell them.
@@ -30972,13 +31813,13 @@
 Jonathan</t>
         </is>
       </c>
-      <c r="K77" s="5" t="inlineStr"/>
-      <c r="L77" s="5" t="inlineStr"/>
-      <c r="M77" s="5" t="inlineStr"/>
-      <c r="N77" s="5" t="inlineStr"/>
+      <c r="K81" s="5" t="inlineStr"/>
+      <c r="L81" s="5" t="inlineStr"/>
+      <c r="M81" s="5" t="inlineStr"/>
+      <c r="N81" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N77"/>
+  <autoFilter ref="A1:N81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -748,7 +748,7 @@
         <is>
           <t>Alex — Planet Money's whole trick is that people will absorb an economics lesson if you hide it inside a story about a guy and a barrel of oil. I did the same thing at a lower reading level.
 Here is the pitch in one line: every children's money book teaches saving, and saving is the second thing a kid does with money. The first is spending. A six-year-old has no savings rate. She has stood in an aisle holding a birthday five, deciding whether the thing is worth it.
-So I wrote the spending one. Clarence Gets a Bargain follows a single purchase the entire way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, gets ambushed by sales tax, and then lives with the thing he bought. Idea to post-receipt. I read every title on the ABA Foundation's children's financial literacy list to check, and not one follows a purchase the whole way through.
+So I wrote the spending one. Clarence Gets a Bargain follows a single purchase the entire way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, gets ambushed by sales tax, and then lives with the thing he bought. Idea to post-receipt. Name another picture book where the kid reads the sale ads before the trip, compares models in the aisle, hands over a coupon, and pays the sales tax. I read all 25 titles on the ABA Foundation's list looking for one. They are all parked on the earning-and-saving side of the register.
 Sixteen-plus concepts are in there and none of them are announced. Nobody says the word "budget." They don't realise they've been schooled until they hit the glossary — twenty-one terms in the back, each page-referenced to the moment it actually happened. That's where the con comes apart, on purpose.
 The segment I'd pitch is not the book. It's the forty-year hole: why an entire publishing category skipped the cash register. There is a Planet Money episode in that whether or not mine is the book that gets mentioned.
 Am I wrong that it's a story? clarencegetsabargain.com/book-facts.html has the specs. Four-minute flip: https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -809,7 +809,7 @@
           <t>Tami — author to author, and I'd rather you heard this from me than found it on a shelf.
 I wrote and illustrated a picture book about money, which sounds like the most airless premise in children's publishing, so let me tell you the one thing that makes it not that.
 Every book in this category teaches saving. Piggy banks, jars, be patient, wait. But saving is the second thing a child does with money. The first is spending, and nobody had written that book. So mine follows one purchase from beginning to end — a boy wants a robot, earns it, works the sale ads at the kitchen table, compares two models in the aisle, takes the cheaper one deliberately, hands a coupon to the cashier, meets sales tax and takes it personally, and then has to live with what he chose.
-The part I think you'll appreciate as a craftsperson: none of the sixteen-plus concepts is ever announced. There is no worksheet voice, no character stopping to explain a term. It is smuggled. A kid does not know he's been schooled until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. That is the moment the book admits what it was doing, and it is the last page rather than the first.
+The part I think you'll appreciate as a craftsperson: none of the sixteen-plus concepts is ever announced. No worksheet voice, no character stopping to explain a term. Budgeting, comparison shopping, charity and Wants vs. Needs all ride into the house in the belly of a story about a kid and his robot. Kids smell a worksheet one page in; they never smell this one, because they're laughing too hard to notice. A kid does not know he's been schooled until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. That is the moment the book admits what it was doing, and it is the last page rather than the first.
 I did the illustrations too, which means I have opinions about it that are worth exactly nothing.
 Would you look at it and tell me where the seams show? I'd trade — send me yours and I'll read it properly, not politely.
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -929,7 +929,7 @@
         <is>
           <t>Paula — "you can afford anything, but not everything" is the best sentence anybody has written about money, and it is a sentence about spending, not saving. That is the entire reason I'm writing to you.
 I wrote the children's version of that idea, and I mean that structurally rather than as a compliment. Every kids' money book teaches saving. But saving is the second thing a child does with money — the first is spending, and a six-year-old has already done it, holding a birthday five in an aisle, working out whether the thing is worth what it costs. Which is your thesis at a lower reading level.
-Clarence Gets a Bargain follows one purchase the whole way. A boy wants a robot. Earns it with chores and grades. Reads the newspaper sale inserts at the kitchen table. Compares two models on a shelf and takes the cheaper one on purpose. Hands a coupon to the cashier. Meets sales tax and regards it as a personal insult, correctly. Then lives with what he chose — which is the opportunity-cost half nobody writes for kids.
+Clarence Gets a Bargain follows one purchase the whole way. A boy wants a robot. Earns it with chores and grades. Reads the newspaper sale inserts at the kitchen table. Compares two models on a shelf and takes the cheaper one on purpose. Hands a coupon to the cashier. Meets sales tax and regards it as a personal insult, correctly. Then lives with what he chose. Most money books end at the checkout; the purchase isn't over when the robot's in the bag, and that back half is the opportunity-cost argument nobody writes for kids.
 The craft bit: none of it is announced. Sixteen-plus concepts, and nobody in the book says the word "budget." A kid does not know he's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. Available, never assigned.
 Is there an episode in the fact that the entire children's money category skipped the cash register for forty years? I'd rather you took the argument than the book.
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -988,7 +988,7 @@
       <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Kim — you review children's books for a living, so you have read more well-meaning money picture books than anyone should have to, and you already know the problem with them.
-They all teach saving. Every one. Which is fine advice and the wrong order, because saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate and has absolutely stood in a store holding money and had to decide.
+They all teach saving. A piggy bank, a lemonade stand, a lesson. Which is fine advice in the wrong order, because saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate and has absolutely stood in a store holding money and had to decide.
 Mine is the spending one, and it follows a single purchase the whole distance rather than gesturing at the idea: a boy wants a robot, earns it with chores and grades, works the sale ads at the kitchen table, compares two models in the aisle, takes the cheaper one on purpose, hands a coupon to the cashier, gets hit with sales tax, and then has to live with the thing. Idea to post-receipt. I read all 25 on the ABA Foundation's list to be sure nobody had done it. Nobody had.
 What I'd actually want your eye on is the smuggling. Sixteen-plus concepts and not one of them is announced — no character stops to explain a term, nobody says "budget." The reader does not know he's been schooled until he reaches the glossary — twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than a homework appendix. The reveal is deliberate and it is on the last page. That balance is the hardest thing in the book and the thing most likely to be off by a hair.
 Would you read it as an editor rather than as a friend? I would rather hear where it sags than be told it's charming.
@@ -1049,7 +1049,7 @@
         <is>
           <t>Neale — you built this category. Money Doesn't Grow on Trees was on the shelf before most of the people currently writing in it could read, so I'm not going to pretend I'm doing something you haven't thought about.
 What I think is still open is the sequence. The field starts children with saving, and saving is the second thing a person does with money. The first is spending. A six-year-old has no savings rate. She has stood in a store holding money and decided. We teach that last.
-So I went narrow and deep on one transaction. Clarence Gets a Bargain follows a single purchase from the idea to after the receipt — a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, redeems a coupon, meets sales tax, and then lives with what he bought. I read all 25 titles on the ABA Foundation's list; none covers the whole arc.
+So I went narrow and deep on one transaction. Clarence Gets a Bargain follows a single purchase from the idea to after the receipt — a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, redeems a coupon, meets sales tax, and then lives with what he bought. It follows the money from the desire, through the receipt, and past it. I read all 25 titles on the ABA Foundation's list looking for another one that does; they are all parked on the earning-and-saving side of the register.
 The other thing, and it is the part I'd want your read on: nothing is announced. Sixteen-plus concepts, no worksheet voice, nobody in the book saying "budget." A child does not know he's been schooled until the glossary — twenty-one terms in the back, each page-referenced to the moment it happened. The book confesses on the last page or not at all. You would spot immediately whether that balance holds or whether I have hidden the lesson so well it isn't there.
 Author to author, I'd like to trade. Send me one of yours and I'll read it properly. And if you think the spending-first premise is wrong, that is worth more to me than a kind word about the illustrations.
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -1537,7 +1537,7 @@
         <is>
           <t>Tiffany — you built a career on the thing nobody teaches: what to actually do, in order, with money that is already in your hand. That is why I'm writing about the six-year-old version.
 Every children's money book teaches saving. All 25 on the ABA Foundation's list — I checked. Piggy banks, jars, patience. But saving is the second thing a child does with money. The first is spending, and a first grader has already done it, in a store, holding a birthday five, working out whether the thing is worth what it costs.
-Mine is the spending one, and it follows a single purchase the whole way rather than talking about the idea: a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, gets hit with sales tax, and then lives with what he chose. Idea to post-receipt.
+Mine is the spending one, and it follows a single purchase the whole way rather than talking about the idea: a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, gets hit with sales tax, and then lives with what he chose. Idea to post-receipt.
 The design choice: none of the sixteen-plus concepts is announced. Nobody in the book says "budget," which for a book that is largely about budgeting took some doing. The kid does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. There for the kid who wants it, invisible to the kid who doesn't.
 You know better than almost anyone whether a thing lands with the people it's for. Would you look, and tell me if the six-year-old version of your audience would sit still for it?
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -1786,7 +1786,7 @@
       <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Nicolle — your twelve-book roundup is the one I point people to, which is slightly awkward, because every title on it teaches earning or saving.
-That's not a criticism of the list. It's an accurate reflection of what exists. I went looking for the spending book and could not find it, so I wrote it.
+That's not a criticism of the list. It is an accurate reflection of what exists — the whole category is parked on the earning-and-saving side of the register. I went looking for the spending book and could not find it, so I wrote it.
 The argument in one line: saving is the second thing a child does with money, and the first is spending. A six-year-old has no savings rate and has definitely stood in a store holding a birthday five, deciding whether the thing is worth what it costs.
 Clarence Gets a Bargain follows one purchase from the idea to after the receipt. A boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Sixteen-plus concepts and nobody in the book says "budget." Twenty-one terms in the glossary, each page-referenced to the scene it came from.
 Two asks, and the second one matters more. Worth a look for the next update to the roundup? And separately — you run a company built on kids and money, so if you think spending-before-saving is wrong, I would rather hear it from you than keep saying it at conferences.
@@ -5309,7 +5309,7 @@
           <t>Roda — you built a 30-Day Smart Spending Challenge. Not a saving challenge. Spending. As far as I can tell that makes two of us in this entire category who think the sequence is backwards.
 Here is my version of the argument, and I'd like to know whether it matches how you arrived at yours. Every children's money book teaches saving — I read all 25 on the ABA Foundation's list to be sure. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. We teach the second thing first and the first thing never.
 Clarence Gets a Bargain is the picture-book version. It follows a single purchase the whole distance — a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced; nobody says "budget." Twenty-one terms in a glossary at the end, each page-referenced to where it happened — which is the only point at which a kid works out he's been schooled.
-Your Challenge is a thirty-day habit; mine is one transaction read in twenty minutes. Those look complementary to me rather than competing — the book could be the on-ramp to a challenge, or the thing a parent reads on day one.
+One story takes a kid from "I want it" to "Is it worth it?" — which I suspect is the same door your Challenge walks them through, thirty days at a time. Yours is a habit; mine is one transaction read in twenty minutes. Those look complementary to me rather than competing — the book could be the on-ramp to a challenge, or the thing a parent reads on day one.
 Worth a conversation? I'd rather compare notes with the one other person who put spending first than pitch anybody.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -6580,7 +6580,7 @@
         <is>
           <t>Daniel — you built 360 Parenting around the whole child rather than one slice of them, so this is a slice you may be missing, and I say that as someone who only noticed it because I went looking for a book and could not find one.
 Money education for kids begins with saving. Every time. But saving is the second thing a child does with money. The first is spending — and a six-year-old has done that, repeatedly, usually in a store, usually while a parent quietly loses the will to live.
-So I wrote the spending book. One purchase, followed the entire way: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, discovers sales tax the way we all did — badly, and in public — and then has to live with the thing he chose. From the idea to after the receipt.
+So I wrote the spending book. One purchase, followed the entire way: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, hands the cashier an extra ten-percent-off coupon like a tiny attorney presenting Exhibit A, discovers sales tax the way we all did — badly, and in public — and then has to live with the thing he chose. From the idea to after the receipt.
 Here is why it might fit a parenting audience rather than a classroom one. The concepts are smuggled. Sixteen-plus of them, none announced, nobody saying the word "budget." It reads as a story about a kid and a robot, and the parent doing the read-aloud gets handed the money conversation without having to deliver a lesson. And the kid does not know he's been schooled until he gets to the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. A parent can turn straight back to the exact page.
 Would it work for your audience — podcast, newsletter, or neither? A no is a fine answer and faster than a maybe.
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -7833,7 +7833,8 @@
           <t>Linda — you teach financial parenting, which means you spend your working life on the exact handoff I wrote a book about: the moment a parent has to explain money to a child who is standing right there wanting something.
 My argument, and you are better placed than almost anyone to tell me it's wrong. Financial education for children starts with saving, and it has the sequence backwards. A seven-year-old has no savings rate and no income. What she has done is stand at a register holding money and decide. Spending is the first money behavior a person performs. We teach it last, or not at all.
 Clarence Gets a Bargain is the spending book. It follows one purchase the whole distance — wanting the thing, earning it through chores and grades, reading the sale inserts at the kitchen table with a parent, comparing two models on a shelf, choosing the cheaper one on purpose, handing over a coupon, meeting sales tax, and then living with what he bought. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; not one covers the whole arc.
-The design choice that matters for your work: nothing is announced. Sixteen-plus concepts and nobody in the book says "budget." The parent reading aloud is handed the conversation without having to give a lecture, which I gather is most of what you coach people out of. The child does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. The reveal is the last thing that happens, not the first.
+The design choice that matters for your work: nothing is announced. Sixteen-plus concepts and nobody in the book says "budget." The kid does the math because the robot depends on it. The parent reading aloud is handed the conversation without having to give a lecture, which I gather is most of what you coach people out of. The child does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. The reveal is the last thing that happens, not the first.
+The shape of it, if it helps: one funny story about a boy and his dream robot takes a kid from "I want it" to "Is it worth it?" She opens it an impulsive little spender and closes it an aware, educated consumer.
 Two questions, either useful. Does the spending-before-saving sequence hold up against what you see in families? And is there a version of this that belongs in front of the parents you train?
 clarencegetsabargain.com/book-facts.html · https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -27714,7 +27715,7 @@
         <is>
           <t>Alex — Planet Money's whole trick is that people will absorb an economics lesson if you hide it inside a story about a guy and a barrel of oil. I did the same thing at a lower reading level.
 Here is the pitch in one line: every children's money book teaches saving, and saving is the second thing a kid does with money. The first is spending. A six-year-old has no savings rate. She has stood in an aisle holding a birthday five, deciding whether the thing is worth it.
-So I wrote the spending one. Clarence Gets a Bargain follows a single purchase the entire way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, gets ambushed by sales tax, and then lives with the thing he bought. Idea to post-receipt. I read every title on the ABA Foundation's children's financial literacy list to check, and not one follows a purchase the whole way through.
+So I wrote the spending one. Clarence Gets a Bargain follows a single purchase the entire way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, gets ambushed by sales tax, and then lives with the thing he bought. Idea to post-receipt. Name another picture book where the kid reads the sale ads before the trip, compares models in the aisle, hands over a coupon, and pays the sales tax. I read all 25 titles on the ABA Foundation's list looking for one. They are all parked on the earning-and-saving side of the register.
 Sixteen-plus concepts are in there and none of them are announced. Nobody says the word "budget." They don't realise they've been schooled until they hit the glossary — twenty-one terms in the back, each page-referenced to the moment it actually happened. That's where the con comes apart, on purpose.
 The segment I'd pitch is not the book. It's the forty-year hole: why an entire publishing category skipped the cash register. There is a Planet Money episode in that whether or not mine is the book that gets mentioned.
 Am I wrong that it's a story? clarencegetsabargain.com/book-facts.html has the specs. Four-minute flip: https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -27775,7 +27776,7 @@
           <t>Tami — author to author, and I'd rather you heard this from me than found it on a shelf.
 I wrote and illustrated a picture book about money, which sounds like the most airless premise in children's publishing, so let me tell you the one thing that makes it not that.
 Every book in this category teaches saving. Piggy banks, jars, be patient, wait. But saving is the second thing a child does with money. The first is spending, and nobody had written that book. So mine follows one purchase from beginning to end — a boy wants a robot, earns it, works the sale ads at the kitchen table, compares two models in the aisle, takes the cheaper one deliberately, hands a coupon to the cashier, meets sales tax and takes it personally, and then has to live with what he chose.
-The part I think you'll appreciate as a craftsperson: none of the sixteen-plus concepts is ever announced. There is no worksheet voice, no character stopping to explain a term. It is smuggled. A kid does not know he's been schooled until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. That is the moment the book admits what it was doing, and it is the last page rather than the first.
+The part I think you'll appreciate as a craftsperson: none of the sixteen-plus concepts is ever announced. No worksheet voice, no character stopping to explain a term. Budgeting, comparison shopping, charity and Wants vs. Needs all ride into the house in the belly of a story about a kid and his robot. Kids smell a worksheet one page in; they never smell this one, because they're laughing too hard to notice. A kid does not know he's been schooled until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. That is the moment the book admits what it was doing, and it is the last page rather than the first.
 I did the illustrations too, which means I have opinions about it that are worth exactly nothing.
 Would you look at it and tell me where the seams show? I'd trade — send me yours and I'll read it properly, not politely.
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -27895,7 +27896,7 @@
         <is>
           <t>Paula — "you can afford anything, but not everything" is the best sentence anybody has written about money, and it is a sentence about spending, not saving. That is the entire reason I'm writing to you.
 I wrote the children's version of that idea, and I mean that structurally rather than as a compliment. Every kids' money book teaches saving. But saving is the second thing a child does with money — the first is spending, and a six-year-old has already done it, holding a birthday five in an aisle, working out whether the thing is worth what it costs. Which is your thesis at a lower reading level.
-Clarence Gets a Bargain follows one purchase the whole way. A boy wants a robot. Earns it with chores and grades. Reads the newspaper sale inserts at the kitchen table. Compares two models on a shelf and takes the cheaper one on purpose. Hands a coupon to the cashier. Meets sales tax and regards it as a personal insult, correctly. Then lives with what he chose — which is the opportunity-cost half nobody writes for kids.
+Clarence Gets a Bargain follows one purchase the whole way. A boy wants a robot. Earns it with chores and grades. Reads the newspaper sale inserts at the kitchen table. Compares two models on a shelf and takes the cheaper one on purpose. Hands a coupon to the cashier. Meets sales tax and regards it as a personal insult, correctly. Then lives with what he chose. Most money books end at the checkout; the purchase isn't over when the robot's in the bag, and that back half is the opportunity-cost argument nobody writes for kids.
 The craft bit: none of it is announced. Sixteen-plus concepts, and nobody in the book says the word "budget." A kid does not know he's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. Available, never assigned.
 Is there an episode in the fact that the entire children's money category skipped the cash register for forty years? I'd rather you took the argument than the book.
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -27954,7 +27955,7 @@
       <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Kim — you review children's books for a living, so you have read more well-meaning money picture books than anyone should have to, and you already know the problem with them.
-They all teach saving. Every one. Which is fine advice and the wrong order, because saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate and has absolutely stood in a store holding money and had to decide.
+They all teach saving. A piggy bank, a lemonade stand, a lesson. Which is fine advice in the wrong order, because saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate and has absolutely stood in a store holding money and had to decide.
 Mine is the spending one, and it follows a single purchase the whole distance rather than gesturing at the idea: a boy wants a robot, earns it with chores and grades, works the sale ads at the kitchen table, compares two models in the aisle, takes the cheaper one on purpose, hands a coupon to the cashier, gets hit with sales tax, and then has to live with the thing. Idea to post-receipt. I read all 25 on the ABA Foundation's list to be sure nobody had done it. Nobody had.
 What I'd actually want your eye on is the smuggling. Sixteen-plus concepts and not one of them is announced — no character stops to explain a term, nobody says "budget." The reader does not know he's been schooled until he reaches the glossary — twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than a homework appendix. The reveal is deliberate and it is on the last page. That balance is the hardest thing in the book and the thing most likely to be off by a hair.
 Would you read it as an editor rather than as a friend? I would rather hear where it sags than be told it's charming.
@@ -28015,7 +28016,7 @@
         <is>
           <t>Neale — you built this category. Money Doesn't Grow on Trees was on the shelf before most of the people currently writing in it could read, so I'm not going to pretend I'm doing something you haven't thought about.
 What I think is still open is the sequence. The field starts children with saving, and saving is the second thing a person does with money. The first is spending. A six-year-old has no savings rate. She has stood in a store holding money and decided. We teach that last.
-So I went narrow and deep on one transaction. Clarence Gets a Bargain follows a single purchase from the idea to after the receipt — a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, redeems a coupon, meets sales tax, and then lives with what he bought. I read all 25 titles on the ABA Foundation's list; none covers the whole arc.
+So I went narrow and deep on one transaction. Clarence Gets a Bargain follows a single purchase from the idea to after the receipt — a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, redeems a coupon, meets sales tax, and then lives with what he bought. It follows the money from the desire, through the receipt, and past it. I read all 25 titles on the ABA Foundation's list looking for another one that does; they are all parked on the earning-and-saving side of the register.
 The other thing, and it is the part I'd want your read on: nothing is announced. Sixteen-plus concepts, no worksheet voice, nobody in the book saying "budget." A child does not know he's been schooled until the glossary — twenty-one terms in the back, each page-referenced to the moment it happened. The book confesses on the last page or not at all. You would spot immediately whether that balance holds or whether I have hidden the lesson so well it isn't there.
 Author to author, I'd like to trade. Send me one of yours and I'll read it properly. And if you think the spending-first premise is wrong, that is worth more to me than a kind word about the illustrations.
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -28503,7 +28504,7 @@
         <is>
           <t>Tiffany — you built a career on the thing nobody teaches: what to actually do, in order, with money that is already in your hand. That is why I'm writing about the six-year-old version.
 Every children's money book teaches saving. All 25 on the ABA Foundation's list — I checked. Piggy banks, jars, patience. But saving is the second thing a child does with money. The first is spending, and a first grader has already done it, in a store, holding a birthday five, working out whether the thing is worth what it costs.
-Mine is the spending one, and it follows a single purchase the whole way rather than talking about the idea: a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, gets hit with sales tax, and then lives with what he chose. Idea to post-receipt.
+Mine is the spending one, and it follows a single purchase the whole way rather than talking about the idea: a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, gets hit with sales tax, and then lives with what he chose. Idea to post-receipt.
 The design choice: none of the sixteen-plus concepts is announced. Nobody in the book says "budget," which for a book that is largely about budgeting took some doing. The kid does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. There for the kid who wants it, invisible to the kid who doesn't.
 You know better than almost anyone whether a thing lands with the people it's for. Would you look, and tell me if the six-year-old version of your audience would sit still for it?
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -28752,7 +28753,7 @@
       <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Nicolle — your twelve-book roundup is the one I point people to, which is slightly awkward, because every title on it teaches earning or saving.
-That's not a criticism of the list. It's an accurate reflection of what exists. I went looking for the spending book and could not find it, so I wrote it.
+That's not a criticism of the list. It is an accurate reflection of what exists — the whole category is parked on the earning-and-saving side of the register. I went looking for the spending book and could not find it, so I wrote it.
 The argument in one line: saving is the second thing a child does with money, and the first is spending. A six-year-old has no savings rate and has definitely stood in a store holding a birthday five, deciding whether the thing is worth what it costs.
 Clarence Gets a Bargain follows one purchase from the idea to after the receipt. A boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Sixteen-plus concepts and nobody in the book says "budget." Twenty-one terms in the glossary, each page-referenced to the scene it came from.
 Two asks, and the second one matters more. Worth a look for the next update to the roundup? And separately — you run a company built on kids and money, so if you think spending-before-saving is wrong, I would rather hear it from you than keep saying it at conferences.
@@ -30250,7 +30251,7 @@
           <t>Roda — you built a 30-Day Smart Spending Challenge. Not a saving challenge. Spending. As far as I can tell that makes two of us in this entire category who think the sequence is backwards.
 Here is my version of the argument, and I'd like to know whether it matches how you arrived at yours. Every children's money book teaches saving — I read all 25 on the ABA Foundation's list to be sure. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. We teach the second thing first and the first thing never.
 Clarence Gets a Bargain is the picture-book version. It follows a single purchase the whole distance — a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced; nobody says "budget." Twenty-one terms in a glossary at the end, each page-referenced to where it happened — which is the only point at which a kid works out he's been schooled.
-Your Challenge is a thirty-day habit; mine is one transaction read in twenty minutes. Those look complementary to me rather than competing — the book could be the on-ramp to a challenge, or the thing a parent reads on day one.
+One story takes a kid from "I want it" to "Is it worth it?" — which I suspect is the same door your Challenge walks them through, thirty days at a time. Yours is a habit; mine is one transaction read in twenty minutes. Those look complementary to me rather than competing — the book could be the on-ramp to a challenge, or the thing a parent reads on day one.
 Worth a conversation? I'd rather compare notes with the one other person who put spending first than pitch anybody.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -30305,7 +30306,7 @@
         <is>
           <t>Daniel — you built 360 Parenting around the whole child rather than one slice of them, so this is a slice you may be missing, and I say that as someone who only noticed it because I went looking for a book and could not find one.
 Money education for kids begins with saving. Every time. But saving is the second thing a child does with money. The first is spending — and a six-year-old has done that, repeatedly, usually in a store, usually while a parent quietly loses the will to live.
-So I wrote the spending book. One purchase, followed the entire way: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, discovers sales tax the way we all did — badly, and in public — and then has to live with the thing he chose. From the idea to after the receipt.
+So I wrote the spending book. One purchase, followed the entire way: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, hands the cashier an extra ten-percent-off coupon like a tiny attorney presenting Exhibit A, discovers sales tax the way we all did — badly, and in public — and then has to live with the thing he chose. From the idea to after the receipt.
 Here is why it might fit a parenting audience rather than a classroom one. The concepts are smuggled. Sixteen-plus of them, none announced, nobody saying the word "budget." It reads as a story about a kid and a robot, and the parent doing the read-aloud gets handed the money conversation without having to deliver a lesson. And the kid does not know he's been schooled until he gets to the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. A parent can turn straight back to the exact page.
 Would it work for your audience — podcast, newsletter, or neither? A no is a fine answer and faster than a maybe.
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -30418,7 +30419,8 @@
           <t>Linda — you teach financial parenting, which means you spend your working life on the exact handoff I wrote a book about: the moment a parent has to explain money to a child who is standing right there wanting something.
 My argument, and you are better placed than almost anyone to tell me it's wrong. Financial education for children starts with saving, and it has the sequence backwards. A seven-year-old has no savings rate and no income. What she has done is stand at a register holding money and decide. Spending is the first money behavior a person performs. We teach it last, or not at all.
 Clarence Gets a Bargain is the spending book. It follows one purchase the whole distance — wanting the thing, earning it through chores and grades, reading the sale inserts at the kitchen table with a parent, comparing two models on a shelf, choosing the cheaper one on purpose, handing over a coupon, meeting sales tax, and then living with what he bought. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; not one covers the whole arc.
-The design choice that matters for your work: nothing is announced. Sixteen-plus concepts and nobody in the book says "budget." The parent reading aloud is handed the conversation without having to give a lecture, which I gather is most of what you coach people out of. The child does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. The reveal is the last thing that happens, not the first.
+The design choice that matters for your work: nothing is announced. Sixteen-plus concepts and nobody in the book says "budget." The kid does the math because the robot depends on it. The parent reading aloud is handed the conversation without having to give a lecture, which I gather is most of what you coach people out of. The child does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. The reveal is the last thing that happens, not the first.
+The shape of it, if it helps: one funny story about a boy and his dream robot takes a kid from "I want it" to "Is it worth it?" She opens it an impulsive little spender and closes it an aware, educated consumer.
 Two questions, either useful. Does the spending-before-saving sequence hold up against what you see in families? And is there a version of this that belongs in front of the parents you train?
 clarencegetsabargain.com/book-facts.html · https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>

--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -991,6 +991,7 @@
 They all teach saving. A piggy bank, a lemonade stand, a lesson. Which is fine advice in the wrong order, because saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate and has absolutely stood in a store holding money and had to decide.
 Mine is the spending one, and it follows a single purchase the whole distance rather than gesturing at the idea: a boy wants a robot, earns it with chores and grades, works the sale ads at the kitchen table, compares two models in the aisle, takes the cheaper one on purpose, hands a coupon to the cashier, gets hit with sales tax, and then has to live with the thing. Idea to post-receipt. I read all 25 on the ABA Foundation's list to be sure nobody had done it. Nobody had.
 What I'd actually want your eye on is the smuggling. Sixteen-plus concepts and not one of them is announced — no character stops to explain a term, nobody says "budget." The reader does not know he's been schooled until he reaches the glossary — twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than a homework appendix. The reveal is deliberate and it is on the last page. That balance is the hardest thing in the book and the thing most likely to be off by a hair.
+One thing I'd want you to test rather than take on faith: whether it clicks later. The book is built to fire back months on, in a real store — "is the newer one really better? Clarence checked." Recognition first, then the habit. If that isn't actually in the pages, I'd want to know.
 Would you read it as an editor rather than as a friend? I would rather hear where it sags than be told it's charming.
 clarencegetsabargain.com/press-kit.html · https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -1539,6 +1540,7 @@
 Every children's money book teaches saving. All 25 on the ABA Foundation's list — I checked. Piggy banks, jars, patience. But saving is the second thing a child does with money. The first is spending, and a first grader has already done it, in a store, holding a birthday five, working out whether the thing is worth what it costs.
 Mine is the spending one, and it follows a single purchase the whole way rather than talking about the idea: a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, gets hit with sales tax, and then lives with what he chose. Idea to post-receipt.
 The design choice: none of the sixteen-plus concepts is announced. Nobody in the book says "budget," which for a book that is largely about budgeting took some doing. The kid does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. There for the kid who wants it, invisible to the kid who doesn't.
+The claim I'd defend hardest is the delayed one: it clicks later, in a real store. Recognition first, then the habit — the book doing its job when nobody is standing there teaching.
 You know better than almost anyone whether a thing lands with the people it's for. Would you look, and tell me if the six-year-old version of your audience would sit still for it?
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -6582,6 +6584,7 @@
 Money education for kids begins with saving. Every time. But saving is the second thing a child does with money. The first is spending — and a six-year-old has done that, repeatedly, usually in a store, usually while a parent quietly loses the will to live.
 So I wrote the spending book. One purchase, followed the entire way: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, hands the cashier an extra ten-percent-off coupon like a tiny attorney presenting Exhibit A, discovers sales tax the way we all did — badly, and in public — and then has to live with the thing he chose. From the idea to after the receipt.
 Here is why it might fit a parenting audience rather than a classroom one. The concepts are smuggled. Sixteen-plus of them, none announced, nobody saying the word "budget." It reads as a story about a kid and a robot, and the parent doing the read-aloud gets handed the money conversation without having to deliver a lesson. And the kid does not know he's been schooled until he gets to the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. A parent can turn straight back to the exact page.
+The argument I'd bring to a podcast is the delayed one. It clicks later, in a real store. Months out, a kid says "there's a coupon in my pocket, just like Clarence" or "the sticker price isn't what you pay, there's tax" — recognition first, then the habit, and the parent isn't even in the room when it happens.
 Would it work for your audience — podcast, newsletter, or neither? A no is a fine answer and faster than a maybe.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -7835,6 +7838,7 @@
 Clarence Gets a Bargain is the spending book. It follows one purchase the whole distance — wanting the thing, earning it through chores and grades, reading the sale inserts at the kitchen table with a parent, comparing two models on a shelf, choosing the cheaper one on purpose, handing over a coupon, meeting sales tax, and then living with what he bought. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; not one covers the whole arc.
 The design choice that matters for your work: nothing is announced. Sixteen-plus concepts and nobody in the book says "budget." The kid does the math because the robot depends on it. The parent reading aloud is handed the conversation without having to give a lecture, which I gather is most of what you coach people out of. The child does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. The reveal is the last thing that happens, not the first.
 The shape of it, if it helps: one funny story about a boy and his dream robot takes a kid from "I want it" to "Is it worth it?" She opens it an impulsive little spender and closes it an aware, educated consumer.
+The part I'd most want your professional read on is the delayed return. The book is not really working in the twenty minutes it takes to read. It works in month eighteen, in an actual store, when the kid hits a real money moment and the book fires back — "wait, is the newer one really better? Clarence checked." Recognition first, then the habit. That is the book doing its job when the parent isn't even in the room.
 Two questions, either useful. Does the spending-before-saving sequence hold up against what you see in families? And is there a version of this that belongs in front of the parents you train?
 clarencegetsabargain.com/book-facts.html · https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -27958,6 +27962,7 @@
 They all teach saving. A piggy bank, a lemonade stand, a lesson. Which is fine advice in the wrong order, because saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate and has absolutely stood in a store holding money and had to decide.
 Mine is the spending one, and it follows a single purchase the whole distance rather than gesturing at the idea: a boy wants a robot, earns it with chores and grades, works the sale ads at the kitchen table, compares two models in the aisle, takes the cheaper one on purpose, hands a coupon to the cashier, gets hit with sales tax, and then has to live with the thing. Idea to post-receipt. I read all 25 on the ABA Foundation's list to be sure nobody had done it. Nobody had.
 What I'd actually want your eye on is the smuggling. Sixteen-plus concepts and not one of them is announced — no character stops to explain a term, nobody says "budget." The reader does not know he's been schooled until he reaches the glossary — twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than a homework appendix. The reveal is deliberate and it is on the last page. That balance is the hardest thing in the book and the thing most likely to be off by a hair.
+One thing I'd want you to test rather than take on faith: whether it clicks later. The book is built to fire back months on, in a real store — "is the newer one really better? Clarence checked." Recognition first, then the habit. If that isn't actually in the pages, I'd want to know.
 Would you read it as an editor rather than as a friend? I would rather hear where it sags than be told it's charming.
 clarencegetsabargain.com/press-kit.html · https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -28506,6 +28511,7 @@
 Every children's money book teaches saving. All 25 on the ABA Foundation's list — I checked. Piggy banks, jars, patience. But saving is the second thing a child does with money. The first is spending, and a first grader has already done it, in a store, holding a birthday five, working out whether the thing is worth what it costs.
 Mine is the spending one, and it follows a single purchase the whole way rather than talking about the idea: a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, gets hit with sales tax, and then lives with what he chose. Idea to post-receipt.
 The design choice: none of the sixteen-plus concepts is announced. Nobody in the book says "budget," which for a book that is largely about budgeting took some doing. The kid does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. There for the kid who wants it, invisible to the kid who doesn't.
+The claim I'd defend hardest is the delayed one: it clicks later, in a real store. Recognition first, then the habit — the book doing its job when nobody is standing there teaching.
 You know better than almost anyone whether a thing lands with the people it's for. Would you look, and tell me if the six-year-old version of your audience would sit still for it?
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -30308,6 +30314,7 @@
 Money education for kids begins with saving. Every time. But saving is the second thing a child does with money. The first is spending — and a six-year-old has done that, repeatedly, usually in a store, usually while a parent quietly loses the will to live.
 So I wrote the spending book. One purchase, followed the entire way: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, hands the cashier an extra ten-percent-off coupon like a tiny attorney presenting Exhibit A, discovers sales tax the way we all did — badly, and in public — and then has to live with the thing he chose. From the idea to after the receipt.
 Here is why it might fit a parenting audience rather than a classroom one. The concepts are smuggled. Sixteen-plus of them, none announced, nobody saying the word "budget." It reads as a story about a kid and a robot, and the parent doing the read-aloud gets handed the money conversation without having to deliver a lesson. And the kid does not know he's been schooled until he gets to the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. A parent can turn straight back to the exact page.
+The argument I'd bring to a podcast is the delayed one. It clicks later, in a real store. Months out, a kid says "there's a coupon in my pocket, just like Clarence" or "the sticker price isn't what you pay, there's tax" — recognition first, then the habit, and the parent isn't even in the room when it happens.
 Would it work for your audience — podcast, newsletter, or neither? A no is a fine answer and faster than a maybe.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -30421,6 +30428,7 @@
 Clarence Gets a Bargain is the spending book. It follows one purchase the whole distance — wanting the thing, earning it through chores and grades, reading the sale inserts at the kitchen table with a parent, comparing two models on a shelf, choosing the cheaper one on purpose, handing over a coupon, meeting sales tax, and then living with what he bought. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; not one covers the whole arc.
 The design choice that matters for your work: nothing is announced. Sixteen-plus concepts and nobody in the book says "budget." The kid does the math because the robot depends on it. The parent reading aloud is handed the conversation without having to give a lecture, which I gather is most of what you coach people out of. The child does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. The reveal is the last thing that happens, not the first.
 The shape of it, if it helps: one funny story about a boy and his dream robot takes a kid from "I want it" to "Is it worth it?" She opens it an impulsive little spender and closes it an aware, educated consumer.
+The part I'd most want your professional read on is the delayed return. The book is not really working in the twenty minutes it takes to read. It works in month eighteen, in an actual store, when the kid hits a real money moment and the book fires back — "wait, is the newer one really better? Clarence checked." Recognition first, then the habit. That is the book doing its job when the parent isn't even in the room.
 Two questions, either useful. Does the spending-before-saving sequence hold up against what you see in families? And is there a version of this that belongs in front of the parents you train?
 clarencegetsabargain.com/book-facts.html · https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>

--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -15,8 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="86ed" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master'!$A$1:$N$665</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Whales'!$A$1:$N$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master'!$A$1:$N$671</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Whales'!$A$1:$N$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deadlines'!$A$1:$H$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Physical copies'!$A$1:$D$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'86ed'!$A$1:$C$12</definedName>
@@ -612,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N665"/>
+  <dimension ref="A1:N671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -751,6 +751,7 @@
 So I wrote the spending one. Clarence Gets a Bargain follows a single purchase the entire way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, gets ambushed by sales tax, and then lives with the thing he bought. Idea to post-receipt. Name another picture book where the kid reads the sale ads before the trip, compares models in the aisle, hands over a coupon, and pays the sales tax. I read all 25 titles on the ABA Foundation's list looking for one. They are all parked on the earning-and-saving side of the register.
 Sixteen-plus concepts are in there and none of them are announced. Nobody says the word "budget." They don't realise they've been schooled until they hit the glossary — twenty-one terms in the back, each page-referenced to the moment it actually happened. That's where the con comes apart, on purpose.
 The segment I'd pitch is not the book. It's the forty-year hole: why an entire publishing category skipped the cash register. There is a Planet Money episode in that whether or not mine is the book that gets mentioned.
+One structural note, since you make things people take in together: the reading level is Lexile AD 620L, and the AD stands for Adult Directed — the trade's own code for a book meant to be read *with* a child rather than handed to one. That was the design, not the accident. Twenty minutes out loud, interrupted the whole way, and the interruptions are the product. Classroom, kitchen table, grandparent's couch — same pages, same arguments break out.
 Am I wrong that it's a story? clarencegetsabargain.com/book-facts.html has the specs. Four-minute flip: https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
         </is>
@@ -811,6 +812,7 @@
 Every book in this category teaches saving. Piggy banks, jars, be patient, wait. But saving is the second thing a child does with money. The first is spending, and nobody had written that book. So mine follows one purchase from beginning to end — a boy wants a robot, earns it, works the sale ads at the kitchen table, compares two models in the aisle, takes the cheaper one deliberately, hands a coupon to the cashier, meets sales tax and takes it personally, and then has to live with what he chose.
 The part I think you'll appreciate as a craftsperson: none of the sixteen-plus concepts is ever announced. No worksheet voice, no character stopping to explain a term. Budgeting, comparison shopping, charity and Wants vs. Needs all ride into the house in the belly of a story about a kid and his robot. Kids smell a worksheet one page in; they never smell this one, because they're laughing too hard to notice. A kid does not know he's been schooled until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. That is the moment the book admits what it was doing, and it is the last page rather than the first.
 I did the illustrations too, which means I have opinions about it that are worth exactly nothing.
+The other craft problem, which you will have solved in your own books: it is written to be read aloud by an adult who does not know the material either. Lexile has it at AD 620L — Adult Directed, read-with rather than read-alone — and the mother explains every concept on the page, so whoever is holding the book gets handed the script. Teacher, parent, grandparent, same outcome: the reading stops every few pages because somebody in the room asks a question.
 Would you look at it and tell me where the seams show? I'd trade — send me yours and I'll read it properly, not politely.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -872,6 +874,7 @@
 The sequence is what I keep coming back to. Financial education starts with saving, and saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has stood at a register and chosen.
 I wrote the K-5 on-ramp. One purchase, followed the whole distance — wanting a robot, earning it, working the sale inserts at the kitchen table, comparing two on a shelf, taking the cheaper one on purpose, redeeming a coupon, meeting sales tax, and living with the choice. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; none does the full arc. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced back into the story.
 The real question, rather than the ask: does NGPF consider elementary in scope, or is it a gap you have consciously left to somebody else? Either answer is useful to me, and the second one tells me whether I'm building alone.
+One practical note for the classroom end: Lexile AD 620L — Adult Directed — reads aloud in one class period, with the mother explaining every concept in the text so a teacher without a finance background can run it cold. That is also why it survives going home. The same twenty minutes works at a kitchen table with a parent or a grandparent, and elementary teachers ask for that more than they ask for curriculum.
 Everything free and ungated: clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
         </is>
@@ -931,6 +934,7 @@
 I wrote the children's version of that idea, and I mean that structurally rather than as a compliment. Every kids' money book teaches saving. But saving is the second thing a child does with money — the first is spending, and a six-year-old has already done it, holding a birthday five in an aisle, working out whether the thing is worth what it costs. Which is your thesis at a lower reading level.
 Clarence Gets a Bargain follows one purchase the whole way. A boy wants a robot. Earns it with chores and grades. Reads the newspaper sale inserts at the kitchen table. Compares two models on a shelf and takes the cheaper one on purpose. Hands a coupon to the cashier. Meets sales tax and regards it as a personal insult, correctly. Then lives with what he chose. Most money books end at the checkout; the purchase isn't over when the robot's in the bag, and that back half is the opportunity-cost argument nobody writes for kids.
 The craft bit: none of it is announced. Sixteen-plus concepts, and nobody in the book says the word "budget." A kid does not know he's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. Available, never assigned.
+Format note, since your audience is adults deciding what to hand a kid: Lexile AD 620L, where AD means Adult Directed — the trade's code for a book meant to be read *with* a child. Not a book you leave in a bedroom. Twenty minutes out loud, and the kid interrupts constantly, which is the whole point. The argument about whether Wi-Fi is a need or a want is the product; the robot is the delivery vehicle.
 Is there an episode in the fact that the entire children's money category skipped the cash register for forty years? I'd rather you took the argument than the book.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -992,6 +996,7 @@
 Mine is the spending one, and it follows a single purchase the whole distance rather than gesturing at the idea: a boy wants a robot, earns it with chores and grades, works the sale ads at the kitchen table, compares two models in the aisle, takes the cheaper one on purpose, hands a coupon to the cashier, gets hit with sales tax, and then has to live with the thing. Idea to post-receipt. I read all 25 on the ABA Foundation's list to be sure nobody had done it. Nobody had.
 What I'd actually want your eye on is the smuggling. Sixteen-plus concepts and not one of them is announced — no character stops to explain a term, nobody says "budget." The reader does not know he's been schooled until he reaches the glossary — twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than a homework appendix. The reveal is deliberate and it is on the last page. That balance is the hardest thing in the book and the thing most likely to be off by a hair.
 One thing I'd want you to test rather than take on faith: whether it clicks later. The book is built to fire back months on, in a real store — "is the newer one really better? Clarence checked." Recognition first, then the habit. If that isn't actually in the pages, I'd want to know.
+The other thing worth your reviewer's ear: it is built to be read aloud, and Lexile has it at AD 620L — Adult Directed, read-with rather than read-alone. The mother carries the exposition, which means the adult holding the book is handed the script. Whether that voice actually holds up out loud — across a classroom, a couch, and a grandparent's lap — is something you would hear in a page and I can only guess at.
 Would you read it as an editor rather than as a friend? I would rather hear where it sags than be told it's charming.
 clarencegetsabargain.com/press-kit.html · https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -1052,6 +1057,7 @@
 What I think is still open is the sequence. The field starts children with saving, and saving is the second thing a person does with money. The first is spending. A six-year-old has no savings rate. She has stood in a store holding money and decided. We teach that last.
 So I went narrow and deep on one transaction. Clarence Gets a Bargain follows a single purchase from the idea to after the receipt — a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, redeems a coupon, meets sales tax, and then lives with what he bought. It follows the money from the desire, through the receipt, and past it. I read all 25 titles on the ABA Foundation's list looking for another one that does; they are all parked on the earning-and-saving side of the register.
 The other thing, and it is the part I'd want your read on: nothing is announced. Sixteen-plus concepts, no worksheet voice, nobody in the book saying "budget." A child does not know he's been schooled until the glossary — twenty-one terms in the back, each page-referenced to the moment it happened. The book confesses on the last page or not at all. You would spot immediately whether that balance holds or whether I have hidden the lesson so well it isn't there.
+One design decision I would want your view on. It is written for an adult to read aloud, not for a child alone: Lexile AD 620L, Adult Directed. The mother carries every explanation on the page, so the grown-up gets the script rather than the homework. You spent a career telling parents to have the conversation. This one hands them the conversation and lets them take the credit for it.
 Author to author, I'd like to trade. Send me one of yours and I'll read it properly. And if you think the spending-first premise is wrong, that is worth more to me than a kind word about the illustrations.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -1112,6 +1118,7 @@
 I have a K-5 resource I would like to list in the Jump$tart Clearinghouse, and I have read the listing criteria closely enough to know which route applies to me. I am not a National Partner and have never listed before, so I would be applying under the letter-of-reference route.
 The resource is a free, ungated classroom set built around a 36-page picture book: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE, and FDIC Money Smart, printable classroom pieces, and a browser-based pretend register. No account, no email capture, no purchase order. It prints from a browser.
 What the book does that the category does not: it teaches spending rather than saving, and it follows one complete purchase from the idea through the receipt — sale ads, comparison, markdown, coupon, sales tax. Sixteen-plus concepts, a twenty-one-term glossary page-referenced to the story. The elementary grade band has standards and very little built against them.
+One spec relevant to classroom use: Lexile AD 620L. The AD is Adult Directed — read-aloud with an adult rather than independent reading. It runs one class period, and the mother explains each concept inside the text, so a teacher with no finance background can run it without preparation. The same design makes it work as a family take-home.
 Two questions. Is the free classroom set the right thing to submit, rather than the book? And for the reference letter, would Wally Luckeydoo carry weight — he received your 2026 Corey Carlisle Award and endorsed the book before any of this came up.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -1171,6 +1178,7 @@
           <t>Michelle — you have written for twenty years that the money conversation with children has to start early, and I wrote the book for the earliest version of it. One question at the end, and it is a column question rather than a book question.
 Every children's financial literacy book teaches saving. I read all 25 on the ABA Foundation's list to be certain. Piggy banks, jars, patience. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it — in a store, holding money, deciding whether the thing is worth what it costs.
 Mine follows one purchase the entire way. A boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he bought. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." Twenty-one terms in the glossary, each page-referenced to the scene it came from.
+The format is part of the argument. Lexile AD 620L — Adult Directed, the industry's own code for a book meant to be read *with* a child. Which means the conversation you have been telling parents to have for twenty years happens on its own: an adult reads, a kid interrupts, and somebody in the room has to answer "do we have one of those?" out loud. It works the same when the adult is a grandparent, which is often who is actually sitting there.
 The column, if there is one: an entire publishing category has taught children to save for forty years and skipped the cash register, which is the only place a child has ever actually handled money. That is a story about the field, not about me.
 clarencegetsabargain.com/press-kit.html
 Jonathan Bach
@@ -1232,6 +1240,7 @@
 I went deep on one of your four. Spending, and specifically the whole transaction rather than the idea of it. Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then has to live with what he picked. Idea to post-receipt.
 The reason I think it sits beside Moneybunnies rather than against it: you give a child the four categories, and mine walks them through the mechanics of one. Sixteen-plus concepts, none announced — nobody says "budget" — and twenty-one terms in a glossary in the back, each page-referenced to the scene where it happened.
 Author-illustrator to author-illustrator: I did the art as well, so I know exactly how much of the work nobody sees. I'd rather you saw this from me than off a shelf.
+The read-aloud is the other half of it. Lexile AD 620L — Adult Directed — written for the adult voice in the room rather than for a child alone, with the mother carrying the explanations so the grown-up gets handed the script. You will know better than most how much that changes what has to happen on the page.
 Trade copies? I'll read yours properly and tell you the truth about it, which is the only thing worth trading.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -1291,6 +1300,7 @@
           <t>Yanely — you spend your time getting personal finance in front of teenagers, and I want to ask about the years before you get them.
 Every mandate lands in high school. Delaware just became the thirtieth state and put the course in ninth grade. But the habits being corrected at sixteen were installed at six, in a store, with a parent saying no. The sequence is the part I keep circling: financial education starts children with saving, and saving is the second thing a person does with money. The first is spending.
 I wrote the K-5 on-ramp — one purchase followed the whole way, from wanting a robot to living with it. Sale ads at the kitchen table, comparison on a shelf, a markdown taken on purpose, a coupon at the register, sales tax. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced back into the story. Free ungated classroom set behind it.
+For the teacher side: AD 620L — Adult Directed — one class period out loud, with the mother explaining every concept in the text so a teacher without a finance background can run it cold. The same book does the job at a kitchen table with a parent or a grandparent, which is the part elementary teachers actually ask for and rarely get.
 Honest question rather than a pitch: when you talk to teachers, does elementary ever come up as something they want and cannot find? I am trying to work out whether I am filling a gap or inventing one.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -1351,6 +1361,7 @@
 The question first. Is the Bookshelf still evaluating titles, and who owns it now? I have a K-5 picture book that teaches spending rather than saving, and the current shelf leans heavily toward saving.
 The idea. A child becomes a consumer the first time they hand money to a cashier. Not at eighteen, not at a first paycheck — at six, at a register, with a birthday five. Everything in youth financial education treats that child as a saver in training. Almost nothing treats her as what she already is: a party to a transaction.
 My book follows one purchase the entire way, which is the part I could not find anywhere else — from wanting the thing, through the sale ads, the comparison, the markdown, the coupon, and the sales tax, to living with what was bought. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in the glossary, each page-referenced to the scene where it happened.
+One format note relevant to Money as You Grow: Lexile AD 620L — Adult Directed, a read-with rather than a read-alone. The caregiver conversation the framework is built around happens inside the reading rather than after it, and it happens whether the adult is a parent, a teacher, or a grandparent.
 I know the full picture crosses agencies — warranties and returns are FTC, product safety is CPSC — and I am not asking CFPB to cover those. I am asking whether Money as You Grow has room for material that treats the child as a consumer on the financial side from the first purchase forward.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan
@@ -1420,6 +1431,7 @@
 I built a free K-5 classroom set around a 36-page picture book and crosswalked it to Money Smart for Young People alongside the 2021 National Standards for Personal Financial Education, CEE, and Common Core Math and ELA. Twenty-three rows, concept by concept, with the Grade 4 benchmark codes rather than a general claim of alignment. It is on the site so a reviewer can check it instead of taking my word.
 What the book covers that Money Smart's book lists mostly do not: spending, and the complete transaction rather than the concept. One purchase followed from the idea to after the receipt — sale ads, comparison shopping, a markdown, a coupon at the register, sales tax, and then living with the thing bought. Sixteen-plus concepts, none announced in the text. A twenty-one-term glossary page-referenced back into the story.
 Everything for teachers is free and ungated. No account, no email capture, no purchase order.
+Format, for the record: Lexile AD 620L, Adult Directed — read aloud with an adult, one class period. The mother explains each concept inside the text, so an instructor without a finance background can deliver it without training. That holds for a classroom, a library program, or a parent at home.
 The question: is there a route for a title to sit alongside Money Smart materials, or is that not how the program works? Either answer saves me guessing.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -1480,6 +1492,7 @@
 The premise: financial education for children starts with saving, and the sequence is backwards. Saving is the second thing a person does with money. The first is spending. A six-year-old has no savings rate and has definitely stood in a store holding money, deciding.
 Easy Peasy Finance explains concepts to kids clearly, one at a time. I went the other way and hid them. Clarence Gets a Bargain follows a single purchase the whole distance — a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Sixteen-plus concepts and nobody in the book says "budget." The twenty-one-term glossary in the back is page-referenced to where each thing happened, which is the closest the book comes to admitting it was teaching anything.
 You explain; I smuggle. I think both work and I'd like to know if you disagree.
+And on the read-along specifically, since I raised it: the book is Lexile AD 620L — AD for Adult Directed, the trade's code for read-with rather than read-alone. It is built for somebody to perform. You explain to camera; this hands the explaining to whoever is holding the book — teacher, parent, grandparent — and then the kid interrupts them. Different mechanism, same job.
 Is there a version of this worth putting in front of your audience — a read-along, a segment, a mention? And separately: at sixteen, would this book have been too young for you, or exactly right for the you at six?
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -1541,6 +1554,7 @@
 Mine is the spending one, and it follows a single purchase the whole way rather than talking about the idea: a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, gets hit with sales tax, and then lives with what he chose. Idea to post-receipt.
 The design choice: none of the sixteen-plus concepts is announced. Nobody in the book says "budget," which for a book that is largely about budgeting took some doing. The kid does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. There for the kid who wants it, invisible to the kid who doesn't.
 The claim I'd defend hardest is the delayed one: it clicks later, in a real store. Recognition first, then the habit — the book doing its job when nobody is standing there teaching.
+One more thing about how it gets used, because it changes who it is for. Lexile AD 620L — Adult Directed, the industry's own code for a book meant to be read *with* a child. The mother explains every concept on the page, so the adult reading aloud gets handed the script and does not have to be the one who already knows about money. That matters most in the houses where nobody feels qualified to teach it, which is most houses.
 You know better than almost anyone whether a thing lands with the people it's for. Would you look, and tell me if the six-year-old version of your audience would sit still for it?
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -1601,6 +1615,7 @@
 Is the Bookshelf still adding titles, and what does the evaluation look like now?
 The reason I ask. The current shelf is weighted toward saving and earning. What is thin is spending, and specifically the transaction itself. I wrote a 36-page K-5 picture book that follows one purchase from the idea to after the receipt — the sale ads at the kitchen table, comparison shopping in the aisle, a markdown taken on purpose, a coupon handed to a cashier, sales tax, and then living with the thing that was bought. I read all 25 titles on the ABA Foundation's list; not one covers the whole arc.
 Sixteen-plus concepts are in it and none is announced — no character pauses to define a term, nobody says the word "budget." The proof is the back matter, and so is the reveal: a reader does not know he's been schooled until he reaches the glossary. Twenty-one terms, each page-referenced to the scene it came from — a decoder rather than an appendix.
+One spec for the Bookshelf's purposes: Lexile AD 620L. The AD is Adult Directed — a read-with rather than a read-alone, which is how the Bookshelf's own titles are meant to be used. The caregiver conversation happens inside the reading, with a parent, a teacher, or a grandparent doing the reading.
 Ages 6-10, which sits inside the Bookshelf's 4-10 band. Free ungated classroom materials behind it. Happy to send a copy to whoever evaluates, or to leave it alone if the shelf is closed.
 clarencegetsabargain.com/book-facts.html
 Jonathan</t>
@@ -1660,6 +1675,7 @@
           <t>Professor Lusardi — you built the instruments the field measures itself with, so you have better grounds than anyone to tell me my premise is wrong. That is the reason I'm writing rather than sending a press release.
 The premise. Financial literacy is measured, sensibly, on saving, compounding and risk. Those are the right things to measure in adults. But each of them is downstream of a decision a child makes years earlier that nobody scores: standing in front of two prices and picking one. Spending is the first financial behavior a person performs. It is taught last, or not at all.
 I could not find the children's book for it, so I wrote one. Clarence Gets a Bargain follows a single purchase the entire way — wanting the thing, earning it, reading the sale ads, comparing two models, choosing the cheaper one deliberately, redeeming a coupon, meeting sales tax, and then living with the choice. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in the glossary, each page-referenced to the scene it came from.
+One design feature that may matter for measurement. The book is classified Lexile AD 620L — Adult Directed — so the intervention is not a child reading alone but an adult and a child reading together, with the adult prompted by the text rather than expected to supply the content. If shared reading is doing the work rather than the book, that is testable, and it would be a more interesting finding than anything about my book.
 The question I would actually like answered: does the evidence base start at adolescence the way the books do? If spending competence at seven predicts nothing at twenty-seven, that is worth knowing and you would know it. If it does predict something, then there is a gap in the literature sitting underneath a picture book, and you are far better placed to say so than I am.
 clarencegetsabargain.com/book-facts.html · https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan Bach
@@ -1731,6 +1747,7 @@
 The gap I'm working on: every state financial-literacy mandate lands in high school. Thirty of them now. Meanwhile the behaviors being corrected at sixteen were installed at six, in a store, and the sequence nobody questions is that children should learn saving first. Saving is the second thing a person does with money. The first is spending.
 I wrote the K-5 piece. One purchase followed from the idea to after the receipt — sale ads at the kitchen table, comparison shopping, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story.
 What matters for a partnership is the rest of it, and it is free. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart. Ungated, no account, prints from a browser. A district adopting it spends nothing.
+One practical spec for adoption: Lexile AD 620L — Adult Directed — one class period read aloud, with the text carrying the explanations so a teacher needs no finance training. The same book goes home and works at a kitchen table with a parent or a grandparent, which is usually where a partnership wants the family-engagement half to come from and rarely finds it.
 Does elementary sit inside what the partnership funds or convenes, or is high school the whole remit?
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -1792,6 +1809,7 @@
 The argument in one line: saving is the second thing a child does with money, and the first is spending. A six-year-old has no savings rate and has definitely stood in a store holding a birthday five, deciding whether the thing is worth what it costs.
 Clarence Gets a Bargain follows one purchase from the idea to after the receipt. A boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Sixteen-plus concepts and nobody in the book says "budget." Twenty-one terms in the glossary, each page-referenced to the scene it came from.
 Two asks, and the second one matters more. Worth a look for the next update to the roundup? And separately — you run a company built on kids and money, so if you think spending-before-saving is wrong, I would rather hear it from you than keep saying it at conferences.
+One line worth having in a roundup, because parents ask it: Lexile AD 620L — Adult Directed, the industry's own code for a book meant to be read *with* a child rather than handed over. Twenty minutes out loud, interrupted the whole way. Grandparents take to it fastest — it gives them something to do with the grandkid instead of something to hand them, and every page has a "that reminds me of the time" sitting in it.
 I'll send a copy either way. https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
         </is>
@@ -1943,6 +1961,7 @@
 Thirty states now require a personal finance course to graduate. Delaware became the thirtieth last October. Every one of those mandates lands in high school, and the funding and training follow the mandate. Meanwhile the K-5 standards that already exist in most states sit there with almost nothing built against them, because nobody has to report on them.
 The sequence assumption underneath all of it is that children should learn saving first. I think that is backwards. Saving is the second thing a person does with money. The first is spending — and a first grader has done that, at a register, with a parent standing behind her. The behaviors a high school course is trying to correct were installed a decade earlier.
 I wrote the elementary piece rather than an argument about it: a 36-page picture book that follows one purchase from the idea to after the receipt, plus a free ungated classroom set crosswalked to the 2021 National Standards, Common Core, CEE and FDIC Money Smart. Sixteen-plus concepts, none announced, twenty-one-term glossary page-referenced into the story.
+One implementation note, since policy has to survive contact with an actual classroom. Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations, no teacher training required, and the same book does the family-engagement job at home with a parent or a grandparent. Elementary programs usually die on training cost. This one has none.
 The question: does NEFE's advocacy work have a position on the elementary band, or is the practical view that high school mandates are where the effort actually pays? I ask because if it's the second, I'd like to know I'm arguing with the consensus rather than filling a gap it agrees exists.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -5312,6 +5331,7 @@
 Here is my version of the argument, and I'd like to know whether it matches how you arrived at yours. Every children's money book teaches saving — I read all 25 on the ABA Foundation's list to be sure. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. We teach the second thing first and the first thing never.
 Clarence Gets a Bargain is the picture-book version. It follows a single purchase the whole distance — a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced; nobody says "budget." Twenty-one terms in a glossary at the end, each page-referenced to where it happened — which is the only point at which a kid works out he's been schooled.
 One story takes a kid from "I want it" to "Is it worth it?" — which I suspect is the same door your Challenge walks them through, thirty days at a time. Yours is a habit; mine is one transaction read in twenty minutes. Those look complementary to me rather than competing — the book could be the on-ramp to a challenge, or the thing a parent reads on day one.
+One thing your Challenge and the book share: neither one works with a kid alone in a room. It is Lexile AD 620L — Adult Directed, the trade's code for read-with rather than read-alone — and the mother explains every concept on the page, so whoever is reading gets handed the script. Parent, teacher or grandparent, the reading stops every few pages because the kid asks something.
 Worth a conversation? I'd rather compare notes with the one other person who put spending first than pitch anybody.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -6585,6 +6605,7 @@
 So I wrote the spending book. One purchase, followed the entire way: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, hands the cashier an extra ten-percent-off coupon like a tiny attorney presenting Exhibit A, discovers sales tax the way we all did — badly, and in public — and then has to live with the thing he chose. From the idea to after the receipt.
 Here is why it might fit a parenting audience rather than a classroom one. The concepts are smuggled. Sixteen-plus of them, none announced, nobody saying the word "budget." It reads as a story about a kid and a robot, and the parent doing the read-aloud gets handed the money conversation without having to deliver a lesson. And the kid does not know he's been schooled until he gets to the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. A parent can turn straight back to the exact page.
 The argument I'd bring to a podcast is the delayed one. It clicks later, in a real store. Months out, a kid says "there's a coupon in my pocket, just like Clarence" or "the sticker price isn't what you pay, there's tax" — recognition first, then the habit, and the parent isn't even in the room when it happens.
+For a parenting audience the format may matter more than the content. Lexile AD 620L — the AD is Adult Directed, the industry's own label for a book meant to be read *with* a child rather than left in their room. Mom explains every concept on the page, so the parent gets handed the script instead of being expected to know it. "Do we have a 529?" is a question a seven-year-old asks in the middle of page six, not after. Grandparents get the same deal, and they tend to enjoy it more.
 Would it work for your audience — podcast, newsletter, or neither? A no is a fine answer and faster than a maybe.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -6641,6 +6662,7 @@
 Mine is a money book, which I appreciate is the least promising sentence in children's publishing. So here is the part that makes it not that.
 Every book in this category teaches saving. Saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it — in a store, holding money, deciding whether the thing is worth what it costs. So mine follows one purchase from the idea to after the receipt: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose.
 The craft problem I'd most like another author's view on: I smuggled sixteen-plus concepts in without announcing any of them. Nobody says "budget." The glossary in the back — twenty-one terms, each page-referenced to the scene it came from — is the only place the book admits it was teaching. Getting that balance right, so it stays a story, was the whole job.
+The other half of the craft problem: it is written for an adult voice. Lexile AD 620L — Adult Directed — with the mother carrying every explanation, so whoever reads aloud gets handed the script. A series lives or dies on whether the grown-up still enjoys the fourth reading. You would know inside a page whether mine does.
 Would you read it and tell me where it stops being a story? I'll trade — send me a Noah and I'll read it properly.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -7839,6 +7861,7 @@
 The design choice that matters for your work: nothing is announced. Sixteen-plus concepts and nobody in the book says "budget." The kid does the math because the robot depends on it. The parent reading aloud is handed the conversation without having to give a lecture, which I gather is most of what you coach people out of. The child does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. The reveal is the last thing that happens, not the first.
 The shape of it, if it helps: one funny story about a boy and his dream robot takes a kid from "I want it" to "Is it worth it?" She opens it an impulsive little spender and closes it an aware, educated consumer.
 The part I'd most want your professional read on is the delayed return. The book is not really working in the twenty minutes it takes to read. It works in month eighteen, in an actual store, when the kid hits a real money moment and the book fires back — "wait, is the newer one really better? Clarence checked." Recognition first, then the habit. That is the book doing its job when the parent isn't even in the room.
+And the handoff you teach is the mechanism itself. The book is Lexile AD 620L — Adult Directed, the trade's own label for a book meant to be read *with* a child, not left in a bedroom — and Mom explains everything on the page, so the adult reading aloud is handed the script rather than asked to know the material. A parent who feels unqualified to teach money can still run it. Classroom, kitchen table, grandparent's couch: the reading stops every few pages because somebody asks.
 Two questions, either useful. Does the spending-before-saving sequence hold up against what you see in families? And is there a version of this that belongs in front of the parents you train?
 clarencegetsabargain.com/book-facts.html · https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -7891,6 +7914,7 @@
 I wrote and illustrated a 36-page hardbound picture book, full colour, 11 by 8.5. I am a mixed-media artist and a real estate attorney, which is a combination that gets me neither the benefit of the doubt on the art nor on the commercial sense. I did the interior, the cover, the whole object.
 The content, briefly, because you'll want to know whether it's worth the production critique. Every children's money book teaches saving. Mine teaches spending, on the argument that saving is the second thing a child does with money and spending is the first. It follows one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, then living with what was bought. Sixteen-plus concepts, none announced. Twenty-one terms in a glossary in the back, each page-referenced to the scene it came from.
 What I'd actually value from you is the unglamorous part: trim size, the cover, whether the interior typography holds at read-aloud distance, whether the object reads as professionally published or as a very determined amateur. I would rather hear it from you now than infer it from a bookseller later.
+And the read-aloud is why I asked about typography at distance rather than at arm's length. It is Lexile AD 620L — Adult Directed — so the object gets held up by an adult with a kid beside them, or a class in front of them, looking at it from three or four feet. If the interior does not hold at that distance the whole use case fails, and that is a production question rather than a content one.
 Paid engagement or a favour returned, whichever you prefer. https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
         </is>
@@ -25217,7 +25241,8 @@
           <t>Sandy — FCCLA members are a decade older than my readers, so this is not a curriculum pitch. It is a service-project one, and I think it's a good one.
 Your chapters run community service. A high schooler reading a money book to a second-grade class is about the cleanest version of that I can think of — it needs no budget, no training, and one afternoon.
 The book is Clarence Gets a Bargain, 36 pages, ages 6-10. It follows one purchase the whole way, which is the thing that makes it work as a read-aloud rather than a lecture: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in it says "budget" — the twenty-one-term glossary in the back is page-referenced to the story, so the reader can field questions without preparing.
-It reads aloud in about twenty minutes, which is a class visit with time left for questions. And there is a free browser-based pretend register the younger kids can run afterward — a markdown, a coupon, sales tax, and a total that changes in front of them.
+The read-aloud is the entire project, so the spec matters. Lexile AD 620L — the AD is Adult Directed, the trade's own code for a book built to be read *with* a child rather than handed to one. About twenty minutes out loud, which is a class visit with time left for questions, and the mother explains every concept inside the text. A high schooler can read it cold to a second-grade class and field the questions straight off the page. Nothing to memorize, nothing to prepare, no training call beforehand.
+There is also a free browser-based pretend register the younger kids can run afterward — a markdown, a coupon, sales tax, and a total that changes in front of them.
 Does that fit how chapters choose service projects, or am I inventing a use case? Everything is free and ungated either way.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -27571,8 +27596,383 @@
       <c r="M665" s="5" t="inlineStr"/>
       <c r="N665" s="5" t="inlineStr"/>
     </row>
+    <row r="666">
+      <c r="A666" s="5" t="inlineStr"/>
+      <c r="B666" s="5" t="inlineStr">
+        <is>
+          <t>Grandparents</t>
+        </is>
+      </c>
+      <c r="C666" s="5" t="inlineStr">
+        <is>
+          <t>GRAND Magazine</t>
+        </is>
+      </c>
+      <c r="D666" s="5" t="inlineStr">
+        <is>
+          <t>Christine Crosby, Editorial Director</t>
+        </is>
+      </c>
+      <c r="E666" s="5" t="inlineStr">
+        <is>
+          <t>Read-along / grandparent lane. Lexile AD 620L = Adult Directed is the load-bearing claim.</t>
+        </is>
+      </c>
+      <c r="F666" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G666" s="5" t="inlineStr">
+        <is>
+          <t>ccrosby@grandmagazine.com</t>
+        </is>
+      </c>
+      <c r="H666" s="5" t="inlineStr">
+        <is>
+          <t>For September: the money lesson a grandkid uses on Saturday</t>
+        </is>
+      </c>
+      <c r="I666" s="5" t="n">
+        <v>2819</v>
+      </c>
+      <c r="J666" s="5" t="inlineStr">
+        <is>
+          <t>Christine,
+You're closing September, Grandparents Day lands on the 13th, and I have a piece for it that isn't about a gift. It's about an afternoon.
+I'm an attorney, a mixed-media artist, and a dad, and I wrote and illustrated a children's picture book called Clarence Gets a Bargain. Ages 6–10. A boy earns a robot with chores and grades, then has to figure out how to buy it — sale ads at the kitchen table, two models compared on a shelf, the cheaper one taken on purpose, a coupon handed to the cashier, and sales tax showing up uninvited at the end.
+Here's the part your readers own. Every children's money book teaches saving. Piggy banks, jars, three little tins labeled spend-save-give where "spend" gets one page and a guilty look. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding a birthday five, deciding whether the thing is worth what it costs. We teach the second thing first and the first thing never.
+Grandparents are the only people left who can teach the first one from experience. You clipped coupons back when it was a survival skill rather than a hobby. You remember layaway. You know what your first paycheck was and exactly what it wouldn't cover. Those stories are the best money curriculum a child will ever get and they have nowhere to land — until a book puts a kid in a store and every page comes with a "that reminds me of the time" already sitting in it.
+The format is the argument. The book is catalogued Lexile AD 620L, and the AD means Adult Directed — the industry's own code for a book meant to be read WITH a child, not handed to one. You're not optional equipment. You're cast. Mom explains everything inside the story, so the grandparent reading aloud gets handed the script and can take the credit for knowing it. Twenty minutes out loud, interrupted the whole way, and the interruptions are the point: "Do we have a 529?" "Why do you take pictures of receipts?" "Can I hand the cashier the coupon next time?"
+And two of the games in it can't be played alone. Page 27: whoever spots the biggest savings at the grocery store wins, loser carries the bags in from the car. Page 28: after dinner somebody shares a deal they got that day and everyone guesses the price. Three players minimum. Grandma counts.
+I'd write it for you as 800–1,200 words — "What Grandparents Can Teach About Money That Nobody Else Can" — with the games as a sidebar readers can tear out and use. Or if you'd rather run it as a product review, the book is $19.99, 36 pages, hardbound, and I'll send a copy today either way.
+Which is more useful to you?
+Jonathan Bach
+Author &amp; illustrator, Clarence Gets a Bargain
+Attorney. Dad. Keeper of receipts.
+questions@clarencegetsabargain.com · clarencegetsabargain.com</t>
+        </is>
+      </c>
+      <c r="K666" s="5" t="inlineStr"/>
+      <c r="L666" s="5" t="inlineStr">
+        <is>
+          <t>National Grandparents Day is Sun 13 Sep 2026 — the September peg for this lane.</t>
+        </is>
+      </c>
+      <c r="M666" s="5" t="inlineStr"/>
+      <c r="N666" s="5" t="inlineStr"/>
+    </row>
+    <row r="667">
+      <c r="A667" s="5" t="inlineStr"/>
+      <c r="B667" s="5" t="inlineStr">
+        <is>
+          <t>Grandparents</t>
+        </is>
+      </c>
+      <c r="C667" s="5" t="inlineStr">
+        <is>
+          <t>More Than Grand</t>
+        </is>
+      </c>
+      <c r="D667" s="5" t="inlineStr">
+        <is>
+          <t>DeeDee Moore</t>
+        </is>
+      </c>
+      <c r="E667" s="5" t="inlineStr">
+        <is>
+          <t>Read-along / grandparent lane. Lexile AD 620L = Adult Directed is the load-bearing claim.</t>
+        </is>
+      </c>
+      <c r="F667" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G667" s="5" t="inlineStr">
+        <is>
+          <t>deedee@morethangrand.com</t>
+        </is>
+      </c>
+      <c r="H667" s="5" t="inlineStr"/>
+      <c r="I667" s="5" t="n">
+        <v>2724</v>
+      </c>
+      <c r="J667" s="5" t="inlineStr">
+        <is>
+          <t>DeeDee,
+You started More Than Grand in 2019 because you couldn't find the grandparent resource you wanted, so you built it. I did the same thing on a different shelf, which is the only reason I'm comfortable writing to you cold.
+I went looking for the children's book that teaches a kid how to spend money — not save it, spend it — and there wasn't one. Every book in that category is about a piggy bank or a lemonade stand. All of them teach saving, which is the second thing a child does with money. The first is spending, and a six-year-old has already done it, standing in a store holding a birthday five, working out whether the thing is worth what it costs. So I wrote and illustrated it: Clarence Gets a Bargain, ages 6–10, one kid following one purchase the whole way, from wanting the robot to living with the one he chose.
+I'm writing to you rather than to a gift guide, and here's the difference. Your whole editorial line is that a good grandparent supports the parents instead of running past them. This book does that structurally. Mom is the one who teaches Clarence in the story — the sale ads, the markdown, the coupon, the sales tax. A grandparent reading it aloud is reading the parent's lines, not competing with them.
+The format backs that up. It's catalogued Lexile AD 620L, and AD stands for Adult Directed — the trade's own code for a book meant to be read WITH a child rather than handed over. It doesn't work in the corner. It works on a couch, with somebody's grandkid interrupting every third page. And because Mom explains every concept inside the text, the grandparent doesn't have to be confident about money to run it. The script is on the page. Take the credit.
+Two of the games in the back half need other people, which I did on purpose. Page 27: everyone hunts for the biggest savings on the next grocery run, loser carries the bags in from the car. Page 28: after dinner someone shares a deal they got that day and everybody guesses the price. Three players minimum. Grandma counts.
+And if you're the grandparent who quietly opened the 529 — page 6 is your victory lap. Read it twice.
+You run two pages that this could belong on: Best Books on Grandparenting, and Gifts for Grandchildren. I'd rather be on the first one than the second, because the pitch isn't "buy this for them," it's "here's something to do with them." But you know your readers and I don't.
+Would you take a look? I'll mail you a hardback this week, no strings and no expectation. $19.99, 36 pages, and I did the art, so all the blame is in one place.
+Jonathan Bach
+Author &amp; illustrator, Clarence Gets a Bargain
+Attorney. Dad. Keeper of receipts.
+questions@clarencegetsabargain.com · clarencegetsabargain.com</t>
+        </is>
+      </c>
+      <c r="K667" s="5" t="inlineStr"/>
+      <c r="L667" s="5" t="inlineStr">
+        <is>
+          <t>National Grandparents Day is Sun 13 Sep 2026 — the September peg for this lane.</t>
+        </is>
+      </c>
+      <c r="M667" s="5" t="inlineStr"/>
+      <c r="N667" s="5" t="inlineStr"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="5" t="inlineStr"/>
+      <c r="B668" s="5" t="inlineStr">
+        <is>
+          <t>Grandparents</t>
+        </is>
+      </c>
+      <c r="C668" s="5" t="inlineStr">
+        <is>
+          <t>Generations United</t>
+        </is>
+      </c>
+      <c r="D668" s="5" t="inlineStr">
+        <is>
+          <t>Do Something Grand</t>
+        </is>
+      </c>
+      <c r="E668" s="5" t="inlineStr">
+        <is>
+          <t>Read-along / grandparent lane. Lexile AD 620L = Adult Directed is the load-bearing claim.</t>
+        </is>
+      </c>
+      <c r="F668" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G668" s="5" t="inlineStr">
+        <is>
+          <t>gu@gu.org</t>
+        </is>
+      </c>
+      <c r="H668" s="5" t="inlineStr"/>
+      <c r="I668" s="5" t="n">
+        <v>1903</v>
+      </c>
+      <c r="J668" s="5" t="inlineStr">
+        <is>
+          <t>Hello,
+A contribution to Do Something Grand rather than a request, and it's free.
+Grandparents Day falls on September 13 this year, and your activity-ideas page is built around things a grandparent and a grandchild can actually do together. I have two that cost nothing and take one afternoon, and I'd like to hand them over.
+I wrote and illustrated a children's picture book, Clarence Gets a Bargain, about a kid learning how to spend money rather than save it — one purchase followed all the way, from reading the sale ads at the kitchen table to the sales tax at the register. Two of the games in it were written to require more than one person:
+The Grocery Savings Hunt — on the next shopping trip, everyone looks for the biggest markdown. Best find wins. The loser carries the bags in from the car.
+Guess the Price — after dinner, one person shares something they bought that day and everybody guesses what it cost. Closest guess wins. Kids' guesses are unhinged, which is the entire entertainment value.
+I'll build both as a free one-page printable in your Do Something Grand look, with no book cover on it and no purchase link — a grandparent can use it having never heard of me. Everything else on my site for teachers and families is already free and ungated, no email capture and no account, and this would be the same.
+Two questions. Is a submitted activity something the campaign takes from outside, and if so who should I send the draft to? And separately, is there interest in a short piece on why grandparents are the right people to teach the spending half of money — they're the last group who remember layaway and clipping coupons as a survival skill rather than a hobby.
+Happy to be told no. The printable will exist either way and you're welcome to it.
+Jonathan Bach
+Author &amp; illustrator, Clarence Gets a Bargain
+questions@clarencegetsabargain.com · clarencegetsabargain.com</t>
+        </is>
+      </c>
+      <c r="K668" s="5" t="inlineStr"/>
+      <c r="L668" s="5" t="inlineStr">
+        <is>
+          <t>National Grandparents Day is Sun 13 Sep 2026 — the September peg for this lane.</t>
+        </is>
+      </c>
+      <c r="M668" s="5" t="inlineStr"/>
+      <c r="N668" s="5" t="inlineStr"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
+      <c r="B669" s="5" t="inlineStr">
+        <is>
+          <t>Grandparents</t>
+        </is>
+      </c>
+      <c r="C669" s="5" t="inlineStr">
+        <is>
+          <t>Ron Lieber</t>
+        </is>
+      </c>
+      <c r="D669" s="5" t="inlineStr">
+        <is>
+          <t>New York Times</t>
+        </is>
+      </c>
+      <c r="E669" s="5" t="inlineStr">
+        <is>
+          <t>Read-along / grandparent lane. Lexile AD 620L = Adult Directed is the load-bearing claim.</t>
+        </is>
+      </c>
+      <c r="F669" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G669" s="5" t="inlineStr">
+        <is>
+          <t>lieber@nytimes.com</t>
+        </is>
+      </c>
+      <c r="H669" s="5" t="inlineStr">
+        <is>
+          <t>The kids' money category skipped the cash register</t>
+        </is>
+      </c>
+      <c r="I669" s="5" t="n">
+        <v>2794</v>
+      </c>
+      <c r="J669" s="5" t="inlineStr">
+        <is>
+          <t>Ron,
+The Opposite of Spoiled is the reason I knew what I was looking for and couldn't find it. This is a column idea, and it works whether or not my book is in it.
+Every children's book about money teaches earning or saving. I read all 25 titles on the ABA Foundation's list to be sure. Piggy banks, lemonade stands, three jars labeled spend-save-give where "spend" gets one page and a guilty look.
+But saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate and no income. What she has done is stand at a register holding a birthday five and decide. Spending is the first financial act a person performs, and the entire category skipped it for forty years.
+The timing gap sharpens it. Thirty states now guarantee a personal finance course — in high school. Money habits are largely set by seven. We're preparing children for 65 and sending them to the register unarmed today, into a store that spent millions working out how to get the five dollars in their hand.
+I wrote the book I couldn't find. Clarence Gets a Bargain, ages 6–10, one kid and one complete purchase: earning it, the sale ads at the kitchen table, two models compared on a shelf, the cheaper one taken deliberately, a coupon at the register, sales tax, and living with the thing afterward. Idea to post-receipt. Sixteen-plus concepts, none of them announced — nobody in the book says the word "budget." The reader doesn't work out he's been schooled until he reaches the glossary in the back, twenty-one terms, each one page-referenced to the scene where it happened.
+I'm an attorney, which shows: the mother photographs the receipt before the car leaves the parking lot, every time, because a receipt is what makes a return or a warranty claim winnable. Kids are consumers years before anyone tells them they have rights as one. That's a second column and possibly a better one.
+The format is worth a line too. It's catalogued Lexile AD 620L — AD for Adult Directed, the trade's own code for a book meant to be read with a child rather than handed to one. The money conversation you've spent a decade telling parents to have is structurally forced: an adult reads, a kid interrupts, and somebody has to answer "do we have one of those?" out loud. Works the same when the adult is a grandparent, which is often who's actually sitting there.
+The story I'd pitch isn't mine. It's the forty-year hole — why a whole publishing category taught children to save and skipped the only place a child has ever actually handled money.
+Wrong about that? You'd know better than anyone. clarencegetsabargain.com/book-facts.html has the specs, and I'll send a copy if it's useful.
+Jonathan Bach
+Attorney and children's book author, Baltimore
+questions@clarencegetsabargain.com</t>
+        </is>
+      </c>
+      <c r="K669" s="5" t="inlineStr"/>
+      <c r="L669" s="5" t="inlineStr">
+        <is>
+          <t>National Grandparents Day is Sun 13 Sep 2026 — the September peg for this lane.</t>
+        </is>
+      </c>
+      <c r="M669" s="5" t="inlineStr"/>
+      <c r="N669" s="5" t="inlineStr"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="5" t="inlineStr"/>
+      <c r="B670" s="5" t="inlineStr">
+        <is>
+          <t>Grandparents</t>
+        </is>
+      </c>
+      <c r="C670" s="5" t="inlineStr">
+        <is>
+          <t>The Cool Grandpa Podcast</t>
+        </is>
+      </c>
+      <c r="D670" s="5" t="inlineStr">
+        <is>
+          <t>Greg</t>
+        </is>
+      </c>
+      <c r="E670" s="5" t="inlineStr">
+        <is>
+          <t>Read-along / grandparent lane. Lexile AD 620L = Adult Directed is the load-bearing claim.</t>
+        </is>
+      </c>
+      <c r="F670" s="5" t="inlineStr">
+        <is>
+          <t>Web form</t>
+        </is>
+      </c>
+      <c r="G670" s="5" t="inlineStr"/>
+      <c r="H670" s="5" t="inlineStr"/>
+      <c r="I670" s="5" t="n">
+        <v>1145</v>
+      </c>
+      <c r="J670" s="5" t="inlineStr">
+        <is>
+          <t>Greg — a grandfather-adjacent pitch, though I'm a dad rather than a grandpa yet, so tell me if that disqualifies me and I'll take it well.
+I wrote and illustrated a kids' picture book about the money skill nobody teaches: spending. Every children's money book is about a piggy bank. But saving is the second thing a kid does with money — the first is spending, usually on a Saturday, at a register, with a grown-up standing right there sweating the total.
+The reason I think it's a grandpa episode: the book is built to be read out loud with a kid, not handed to one. It's catalogued Lexile AD 620L — Adult Directed, the industry's own code for read-WITH. And the grandparents are the last people alive who remember layaway and clipping coupons as a survival skill. Every page has a "that reminds me of the time" sitting in it.
+Two of the games in it need more than one player on purpose. One is a grocery-store savings hunt where the loser carries the bags in from the car.
+Worth twenty minutes of your show? I'll send a copy either way.
+Jonathan Bach — Clarence Gets a Bargain
+questions@clarencegetsabargain.com · clarencegetsabargain.com</t>
+        </is>
+      </c>
+      <c r="K670" s="5" t="inlineStr"/>
+      <c r="L670" s="5" t="inlineStr">
+        <is>
+          <t>National Grandparents Day is Sun 13 Sep 2026 — the September peg for this lane.</t>
+        </is>
+      </c>
+      <c r="M670" s="5" t="inlineStr"/>
+      <c r="N670" s="5" t="inlineStr"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="5" t="inlineStr"/>
+      <c r="B671" s="5" t="inlineStr">
+        <is>
+          <t>Grandparents</t>
+        </is>
+      </c>
+      <c r="C671" s="5" t="inlineStr">
+        <is>
+          <t>The reusable one</t>
+        </is>
+      </c>
+      <c r="D671" s="5" t="inlineStr">
+        <is>
+          <t>"Read It WITH Them"</t>
+        </is>
+      </c>
+      <c r="E671" s="5" t="inlineStr">
+        <is>
+          <t>Read-along / grandparent lane. Lexile AD 620L = Adult Directed is the load-bearing claim.</t>
+        </is>
+      </c>
+      <c r="F671" s="5" t="inlineStr">
+        <is>
+          <t>Web form</t>
+        </is>
+      </c>
+      <c r="G671" s="5" t="inlineStr"/>
+      <c r="H671" s="5" t="inlineStr"/>
+      <c r="I671" s="5" t="n">
+        <v>3463</v>
+      </c>
+      <c r="J671" s="5" t="inlineStr">
+        <is>
+          <t>Dear Parents — and Grandparents, don't skim off, this one is mostly for you,
+Every author wants their book read. I want mine read out loud.
+Clarence Gets a Bargain carries a reading level of Lexile AD 620L. The AD stands for "Adult Directed" — the book industry's own label for a title meant to be read WITH a child rather than handed to one. That code isn't an accident. I built the book for the couch, not the corner.
+Here's why. In the story, Clarence doesn't learn about money from a worksheet. He learns it from his mom — at the kitchen table with the sale ads, in the car, in the middle of the store. Read the book to your kid and you aren't describing that scene. You're in it.
+And the interruptions will come. "Do we have a 529?" "Why do you take pictures of receipts?" "Can I hand the cashier the coupon next time?" "Is the internet a need or a want?" A kid alone in the corner reads a robot story and moves on. A kid pressed against your shoulder reads the same story and starts an argument about whether Wi-Fi counts as shelter. You want that argument. The argument is the product; the robot is the delivery vehicle.
+You don't need to know anything about finance to do this well. Mom explains everything to Clarence inside the story — sale ads, clearance, markdowns, sales tax — so your only job is to read her lines like you knew it all along. I wrote you the script. Take the credit.
+Two parts of the book flat-out require company:
+The grocery game, page 27. Whoever spots the biggest savings wins; the loser carries the bags in from the car. A kid cannot play this alone. That's the point.
+"Guess the Price," page 28. After dinner, somebody shares a deal they got that day and everyone guesses what it cost. Clarence guesses last and lowest, every time — his logic being that if a price is low enough to brag about at dinner, it has to be really low. Three players minimum. Grandma counts.
+Now, grandparents. Your section.
+You clipped coupons back when it was a survival skill rather than a hobby. You remember layaway. You know what your first paycheck was and exactly what it wouldn't cover. Those stories are the best money curriculum a kid will ever get, and they need somewhere to land. Fifteen minutes with this book gives them a runway — every page has a "that reminds me of the time..." waiting in it. No batteries, no screen, no assembly. A gift you do with them instead of one you watch them carry off to their room.
+And if you're the grandparent who opened the 529: page 6 is your victory lap. Read it twice.
+One more thing. On page 24 the dad admits that he and Mom stretched the truth a little to make the lesson stick, and then he levels with his son. Read that page slowly, in your own voice. It's the most honest page in the book and it lands differently when a real parent or grandparent is the one saying it.
+The whole book runs 15 to 20 minutes out loud. Your kid will reread it alone afterward — they always do, usually the same night. Fine. But the first read belongs to both of you. Don't give that one away.
+Jonathan Bach
+Author &amp; illustrator, Clarence Gets a Bargain
+Attorney. Dad. Keeper of receipts.
+clarencegetsabargain.com
+P.S. — At the back there's a 21-term glossary where every definition points to the page where it happened in the story. If a word comes up at the store next week, you can both look it up and land on a scene you read together. That's not a glossary; that's a memory with page numbers.</t>
+        </is>
+      </c>
+      <c r="K671" s="5" t="inlineStr"/>
+      <c r="L671" s="5" t="inlineStr">
+        <is>
+          <t>National Grandparents Day is Sun 13 Sep 2026 — the September peg for this lane.</t>
+        </is>
+      </c>
+      <c r="M671" s="5" t="inlineStr"/>
+      <c r="N671" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N665"/>
+  <autoFilter ref="A1:N671"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27583,7 +27983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:N82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -27722,6 +28122,7 @@
 So I wrote the spending one. Clarence Gets a Bargain follows a single purchase the entire way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, gets ambushed by sales tax, and then lives with the thing he bought. Idea to post-receipt. Name another picture book where the kid reads the sale ads before the trip, compares models in the aisle, hands over a coupon, and pays the sales tax. I read all 25 titles on the ABA Foundation's list looking for one. They are all parked on the earning-and-saving side of the register.
 Sixteen-plus concepts are in there and none of them are announced. Nobody says the word "budget." They don't realise they've been schooled until they hit the glossary — twenty-one terms in the back, each page-referenced to the moment it actually happened. That's where the con comes apart, on purpose.
 The segment I'd pitch is not the book. It's the forty-year hole: why an entire publishing category skipped the cash register. There is a Planet Money episode in that whether or not mine is the book that gets mentioned.
+One structural note, since you make things people take in together: the reading level is Lexile AD 620L, and the AD stands for Adult Directed — the trade's own code for a book meant to be read *with* a child rather than handed to one. That was the design, not the accident. Twenty minutes out loud, interrupted the whole way, and the interruptions are the product. Classroom, kitchen table, grandparent's couch — same pages, same arguments break out.
 Am I wrong that it's a story? clarencegetsabargain.com/book-facts.html has the specs. Four-minute flip: https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
         </is>
@@ -27782,6 +28183,7 @@
 Every book in this category teaches saving. Piggy banks, jars, be patient, wait. But saving is the second thing a child does with money. The first is spending, and nobody had written that book. So mine follows one purchase from beginning to end — a boy wants a robot, earns it, works the sale ads at the kitchen table, compares two models in the aisle, takes the cheaper one deliberately, hands a coupon to the cashier, meets sales tax and takes it personally, and then has to live with what he chose.
 The part I think you'll appreciate as a craftsperson: none of the sixteen-plus concepts is ever announced. No worksheet voice, no character stopping to explain a term. Budgeting, comparison shopping, charity and Wants vs. Needs all ride into the house in the belly of a story about a kid and his robot. Kids smell a worksheet one page in; they never smell this one, because they're laughing too hard to notice. A kid does not know he's been schooled until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. That is the moment the book admits what it was doing, and it is the last page rather than the first.
 I did the illustrations too, which means I have opinions about it that are worth exactly nothing.
+The other craft problem, which you will have solved in your own books: it is written to be read aloud by an adult who does not know the material either. Lexile has it at AD 620L — Adult Directed, read-with rather than read-alone — and the mother explains every concept on the page, so whoever is holding the book gets handed the script. Teacher, parent, grandparent, same outcome: the reading stops every few pages because somebody in the room asks a question.
 Would you look at it and tell me where the seams show? I'd trade — send me yours and I'll read it properly, not politely.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -27843,6 +28245,7 @@
 The sequence is what I keep coming back to. Financial education starts with saving, and saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has stood at a register and chosen.
 I wrote the K-5 on-ramp. One purchase, followed the whole distance — wanting a robot, earning it, working the sale inserts at the kitchen table, comparing two on a shelf, taking the cheaper one on purpose, redeeming a coupon, meeting sales tax, and living with the choice. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; none does the full arc. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced back into the story.
 The real question, rather than the ask: does NGPF consider elementary in scope, or is it a gap you have consciously left to somebody else? Either answer is useful to me, and the second one tells me whether I'm building alone.
+One practical note for the classroom end: Lexile AD 620L — Adult Directed — reads aloud in one class period, with the mother explaining every concept in the text so a teacher without a finance background can run it cold. That is also why it survives going home. The same twenty minutes works at a kitchen table with a parent or a grandparent, and elementary teachers ask for that more than they ask for curriculum.
 Everything free and ungated: clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
         </is>
@@ -27902,6 +28305,7 @@
 I wrote the children's version of that idea, and I mean that structurally rather than as a compliment. Every kids' money book teaches saving. But saving is the second thing a child does with money — the first is spending, and a six-year-old has already done it, holding a birthday five in an aisle, working out whether the thing is worth what it costs. Which is your thesis at a lower reading level.
 Clarence Gets a Bargain follows one purchase the whole way. A boy wants a robot. Earns it with chores and grades. Reads the newspaper sale inserts at the kitchen table. Compares two models on a shelf and takes the cheaper one on purpose. Hands a coupon to the cashier. Meets sales tax and regards it as a personal insult, correctly. Then lives with what he chose. Most money books end at the checkout; the purchase isn't over when the robot's in the bag, and that back half is the opportunity-cost argument nobody writes for kids.
 The craft bit: none of it is announced. Sixteen-plus concepts, and nobody in the book says the word "budget." A kid does not know he's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. Available, never assigned.
+Format note, since your audience is adults deciding what to hand a kid: Lexile AD 620L, where AD means Adult Directed — the trade's code for a book meant to be read *with* a child. Not a book you leave in a bedroom. Twenty minutes out loud, and the kid interrupts constantly, which is the whole point. The argument about whether Wi-Fi is a need or a want is the product; the robot is the delivery vehicle.
 Is there an episode in the fact that the entire children's money category skipped the cash register for forty years? I'd rather you took the argument than the book.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -27963,6 +28367,7 @@
 Mine is the spending one, and it follows a single purchase the whole distance rather than gesturing at the idea: a boy wants a robot, earns it with chores and grades, works the sale ads at the kitchen table, compares two models in the aisle, takes the cheaper one on purpose, hands a coupon to the cashier, gets hit with sales tax, and then has to live with the thing. Idea to post-receipt. I read all 25 on the ABA Foundation's list to be sure nobody had done it. Nobody had.
 What I'd actually want your eye on is the smuggling. Sixteen-plus concepts and not one of them is announced — no character stops to explain a term, nobody says "budget." The reader does not know he's been schooled until he reaches the glossary — twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than a homework appendix. The reveal is deliberate and it is on the last page. That balance is the hardest thing in the book and the thing most likely to be off by a hair.
 One thing I'd want you to test rather than take on faith: whether it clicks later. The book is built to fire back months on, in a real store — "is the newer one really better? Clarence checked." Recognition first, then the habit. If that isn't actually in the pages, I'd want to know.
+The other thing worth your reviewer's ear: it is built to be read aloud, and Lexile has it at AD 620L — Adult Directed, read-with rather than read-alone. The mother carries the exposition, which means the adult holding the book is handed the script. Whether that voice actually holds up out loud — across a classroom, a couch, and a grandparent's lap — is something you would hear in a page and I can only guess at.
 Would you read it as an editor rather than as a friend? I would rather hear where it sags than be told it's charming.
 clarencegetsabargain.com/press-kit.html · https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -28023,6 +28428,7 @@
 What I think is still open is the sequence. The field starts children with saving, and saving is the second thing a person does with money. The first is spending. A six-year-old has no savings rate. She has stood in a store holding money and decided. We teach that last.
 So I went narrow and deep on one transaction. Clarence Gets a Bargain follows a single purchase from the idea to after the receipt — a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, redeems a coupon, meets sales tax, and then lives with what he bought. It follows the money from the desire, through the receipt, and past it. I read all 25 titles on the ABA Foundation's list looking for another one that does; they are all parked on the earning-and-saving side of the register.
 The other thing, and it is the part I'd want your read on: nothing is announced. Sixteen-plus concepts, no worksheet voice, nobody in the book saying "budget." A child does not know he's been schooled until the glossary — twenty-one terms in the back, each page-referenced to the moment it happened. The book confesses on the last page or not at all. You would spot immediately whether that balance holds or whether I have hidden the lesson so well it isn't there.
+One design decision I would want your view on. It is written for an adult to read aloud, not for a child alone: Lexile AD 620L, Adult Directed. The mother carries every explanation on the page, so the grown-up gets the script rather than the homework. You spent a career telling parents to have the conversation. This one hands them the conversation and lets them take the credit for it.
 Author to author, I'd like to trade. Send me one of yours and I'll read it properly. And if you think the spending-first premise is wrong, that is worth more to me than a kind word about the illustrations.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -28083,6 +28489,7 @@
 I have a K-5 resource I would like to list in the Jump$tart Clearinghouse, and I have read the listing criteria closely enough to know which route applies to me. I am not a National Partner and have never listed before, so I would be applying under the letter-of-reference route.
 The resource is a free, ungated classroom set built around a 36-page picture book: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE, and FDIC Money Smart, printable classroom pieces, and a browser-based pretend register. No account, no email capture, no purchase order. It prints from a browser.
 What the book does that the category does not: it teaches spending rather than saving, and it follows one complete purchase from the idea through the receipt — sale ads, comparison, markdown, coupon, sales tax. Sixteen-plus concepts, a twenty-one-term glossary page-referenced to the story. The elementary grade band has standards and very little built against them.
+One spec relevant to classroom use: Lexile AD 620L. The AD is Adult Directed — read-aloud with an adult rather than independent reading. It runs one class period, and the mother explains each concept inside the text, so a teacher with no finance background can run it without preparation. The same design makes it work as a family take-home.
 Two questions. Is the free classroom set the right thing to submit, rather than the book? And for the reference letter, would Wally Luckeydoo carry weight — he received your 2026 Corey Carlisle Award and endorsed the book before any of this came up.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -28142,6 +28549,7 @@
           <t>Michelle — you have written for twenty years that the money conversation with children has to start early, and I wrote the book for the earliest version of it. One question at the end, and it is a column question rather than a book question.
 Every children's financial literacy book teaches saving. I read all 25 on the ABA Foundation's list to be certain. Piggy banks, jars, patience. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it — in a store, holding money, deciding whether the thing is worth what it costs.
 Mine follows one purchase the entire way. A boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he bought. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." Twenty-one terms in the glossary, each page-referenced to the scene it came from.
+The format is part of the argument. Lexile AD 620L — Adult Directed, the industry's own code for a book meant to be read *with* a child. Which means the conversation you have been telling parents to have for twenty years happens on its own: an adult reads, a kid interrupts, and somebody in the room has to answer "do we have one of those?" out loud. It works the same when the adult is a grandparent, which is often who is actually sitting there.
 The column, if there is one: an entire publishing category has taught children to save for forty years and skipped the cash register, which is the only place a child has ever actually handled money. That is a story about the field, not about me.
 clarencegetsabargain.com/press-kit.html
 Jonathan Bach
@@ -28203,6 +28611,7 @@
 I went deep on one of your four. Spending, and specifically the whole transaction rather than the idea of it. Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then has to live with what he picked. Idea to post-receipt.
 The reason I think it sits beside Moneybunnies rather than against it: you give a child the four categories, and mine walks them through the mechanics of one. Sixteen-plus concepts, none announced — nobody says "budget" — and twenty-one terms in a glossary in the back, each page-referenced to the scene where it happened.
 Author-illustrator to author-illustrator: I did the art as well, so I know exactly how much of the work nobody sees. I'd rather you saw this from me than off a shelf.
+The read-aloud is the other half of it. Lexile AD 620L — Adult Directed — written for the adult voice in the room rather than for a child alone, with the mother carrying the explanations so the grown-up gets handed the script. You will know better than most how much that changes what has to happen on the page.
 Trade copies? I'll read yours properly and tell you the truth about it, which is the only thing worth trading.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -28262,6 +28671,7 @@
           <t>Yanely — you spend your time getting personal finance in front of teenagers, and I want to ask about the years before you get them.
 Every mandate lands in high school. Delaware just became the thirtieth state and put the course in ninth grade. But the habits being corrected at sixteen were installed at six, in a store, with a parent saying no. The sequence is the part I keep circling: financial education starts children with saving, and saving is the second thing a person does with money. The first is spending.
 I wrote the K-5 on-ramp — one purchase followed the whole way, from wanting a robot to living with it. Sale ads at the kitchen table, comparison on a shelf, a markdown taken on purpose, a coupon at the register, sales tax. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced back into the story. Free ungated classroom set behind it.
+For the teacher side: AD 620L — Adult Directed — one class period out loud, with the mother explaining every concept in the text so a teacher without a finance background can run it cold. The same book does the job at a kitchen table with a parent or a grandparent, which is the part elementary teachers actually ask for and rarely get.
 Honest question rather than a pitch: when you talk to teachers, does elementary ever come up as something they want and cannot find? I am trying to work out whether I am filling a gap or inventing one.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -28322,6 +28732,7 @@
 The question first. Is the Bookshelf still evaluating titles, and who owns it now? I have a K-5 picture book that teaches spending rather than saving, and the current shelf leans heavily toward saving.
 The idea. A child becomes a consumer the first time they hand money to a cashier. Not at eighteen, not at a first paycheck — at six, at a register, with a birthday five. Everything in youth financial education treats that child as a saver in training. Almost nothing treats her as what she already is: a party to a transaction.
 My book follows one purchase the entire way, which is the part I could not find anywhere else — from wanting the thing, through the sale ads, the comparison, the markdown, the coupon, and the sales tax, to living with what was bought. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in the glossary, each page-referenced to the scene where it happened.
+One format note relevant to Money as You Grow: Lexile AD 620L — Adult Directed, a read-with rather than a read-alone. The caregiver conversation the framework is built around happens inside the reading rather than after it, and it happens whether the adult is a parent, a teacher, or a grandparent.
 I know the full picture crosses agencies — warranties and returns are FTC, product safety is CPSC — and I am not asking CFPB to cover those. I am asking whether Money as You Grow has room for material that treats the child as a consumer on the financial side from the first purchase forward.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan
@@ -28391,6 +28802,7 @@
 I built a free K-5 classroom set around a 36-page picture book and crosswalked it to Money Smart for Young People alongside the 2021 National Standards for Personal Financial Education, CEE, and Common Core Math and ELA. Twenty-three rows, concept by concept, with the Grade 4 benchmark codes rather than a general claim of alignment. It is on the site so a reviewer can check it instead of taking my word.
 What the book covers that Money Smart's book lists mostly do not: spending, and the complete transaction rather than the concept. One purchase followed from the idea to after the receipt — sale ads, comparison shopping, a markdown, a coupon at the register, sales tax, and then living with the thing bought. Sixteen-plus concepts, none announced in the text. A twenty-one-term glossary page-referenced back into the story.
 Everything for teachers is free and ungated. No account, no email capture, no purchase order.
+Format, for the record: Lexile AD 620L, Adult Directed — read aloud with an adult, one class period. The mother explains each concept inside the text, so an instructor without a finance background can deliver it without training. That holds for a classroom, a library program, or a parent at home.
 The question: is there a route for a title to sit alongside Money Smart materials, or is that not how the program works? Either answer saves me guessing.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -28451,6 +28863,7 @@
 The premise: financial education for children starts with saving, and the sequence is backwards. Saving is the second thing a person does with money. The first is spending. A six-year-old has no savings rate and has definitely stood in a store holding money, deciding.
 Easy Peasy Finance explains concepts to kids clearly, one at a time. I went the other way and hid them. Clarence Gets a Bargain follows a single purchase the whole distance — a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Sixteen-plus concepts and nobody in the book says "budget." The twenty-one-term glossary in the back is page-referenced to where each thing happened, which is the closest the book comes to admitting it was teaching anything.
 You explain; I smuggle. I think both work and I'd like to know if you disagree.
+And on the read-along specifically, since I raised it: the book is Lexile AD 620L — AD for Adult Directed, the trade's code for read-with rather than read-alone. It is built for somebody to perform. You explain to camera; this hands the explaining to whoever is holding the book — teacher, parent, grandparent — and then the kid interrupts them. Different mechanism, same job.
 Is there a version of this worth putting in front of your audience — a read-along, a segment, a mention? And separately: at sixteen, would this book have been too young for you, or exactly right for the you at six?
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -28512,6 +28925,7 @@
 Mine is the spending one, and it follows a single purchase the whole way rather than talking about the idea: a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, gets hit with sales tax, and then lives with what he chose. Idea to post-receipt.
 The design choice: none of the sixteen-plus concepts is announced. Nobody in the book says "budget," which for a book that is largely about budgeting took some doing. The kid does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. There for the kid who wants it, invisible to the kid who doesn't.
 The claim I'd defend hardest is the delayed one: it clicks later, in a real store. Recognition first, then the habit — the book doing its job when nobody is standing there teaching.
+One more thing about how it gets used, because it changes who it is for. Lexile AD 620L — Adult Directed, the industry's own code for a book meant to be read *with* a child. The mother explains every concept on the page, so the adult reading aloud gets handed the script and does not have to be the one who already knows about money. That matters most in the houses where nobody feels qualified to teach it, which is most houses.
 You know better than almost anyone whether a thing lands with the people it's for. Would you look, and tell me if the six-year-old version of your audience would sit still for it?
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -28572,6 +28986,7 @@
 Is the Bookshelf still adding titles, and what does the evaluation look like now?
 The reason I ask. The current shelf is weighted toward saving and earning. What is thin is spending, and specifically the transaction itself. I wrote a 36-page K-5 picture book that follows one purchase from the idea to after the receipt — the sale ads at the kitchen table, comparison shopping in the aisle, a markdown taken on purpose, a coupon handed to a cashier, sales tax, and then living with the thing that was bought. I read all 25 titles on the ABA Foundation's list; not one covers the whole arc.
 Sixteen-plus concepts are in it and none is announced — no character pauses to define a term, nobody says the word "budget." The proof is the back matter, and so is the reveal: a reader does not know he's been schooled until he reaches the glossary. Twenty-one terms, each page-referenced to the scene it came from — a decoder rather than an appendix.
+One spec for the Bookshelf's purposes: Lexile AD 620L. The AD is Adult Directed — a read-with rather than a read-alone, which is how the Bookshelf's own titles are meant to be used. The caregiver conversation happens inside the reading, with a parent, a teacher, or a grandparent doing the reading.
 Ages 6-10, which sits inside the Bookshelf's 4-10 band. Free ungated classroom materials behind it. Happy to send a copy to whoever evaluates, or to leave it alone if the shelf is closed.
 clarencegetsabargain.com/book-facts.html
 Jonathan</t>
@@ -28631,6 +29046,7 @@
           <t>Professor Lusardi — you built the instruments the field measures itself with, so you have better grounds than anyone to tell me my premise is wrong. That is the reason I'm writing rather than sending a press release.
 The premise. Financial literacy is measured, sensibly, on saving, compounding and risk. Those are the right things to measure in adults. But each of them is downstream of a decision a child makes years earlier that nobody scores: standing in front of two prices and picking one. Spending is the first financial behavior a person performs. It is taught last, or not at all.
 I could not find the children's book for it, so I wrote one. Clarence Gets a Bargain follows a single purchase the entire way — wanting the thing, earning it, reading the sale ads, comparing two models, choosing the cheaper one deliberately, redeeming a coupon, meeting sales tax, and then living with the choice. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in the glossary, each page-referenced to the scene it came from.
+One design feature that may matter for measurement. The book is classified Lexile AD 620L — Adult Directed — so the intervention is not a child reading alone but an adult and a child reading together, with the adult prompted by the text rather than expected to supply the content. If shared reading is doing the work rather than the book, that is testable, and it would be a more interesting finding than anything about my book.
 The question I would actually like answered: does the evidence base start at adolescence the way the books do? If spending competence at seven predicts nothing at twenty-seven, that is worth knowing and you would know it. If it does predict something, then there is a gap in the literature sitting underneath a picture book, and you are far better placed to say so than I am.
 clarencegetsabargain.com/book-facts.html · https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan Bach
@@ -28702,6 +29118,7 @@
 The gap I'm working on: every state financial-literacy mandate lands in high school. Thirty of them now. Meanwhile the behaviors being corrected at sixteen were installed at six, in a store, and the sequence nobody questions is that children should learn saving first. Saving is the second thing a person does with money. The first is spending.
 I wrote the K-5 piece. One purchase followed from the idea to after the receipt — sale ads at the kitchen table, comparison shopping, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story.
 What matters for a partnership is the rest of it, and it is free. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart. Ungated, no account, prints from a browser. A district adopting it spends nothing.
+One practical spec for adoption: Lexile AD 620L — Adult Directed — one class period read aloud, with the text carrying the explanations so a teacher needs no finance training. The same book goes home and works at a kitchen table with a parent or a grandparent, which is usually where a partnership wants the family-engagement half to come from and rarely finds it.
 Does elementary sit inside what the partnership funds or convenes, or is high school the whole remit?
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -28763,6 +29180,7 @@
 The argument in one line: saving is the second thing a child does with money, and the first is spending. A six-year-old has no savings rate and has definitely stood in a store holding a birthday five, deciding whether the thing is worth what it costs.
 Clarence Gets a Bargain follows one purchase from the idea to after the receipt. A boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Sixteen-plus concepts and nobody in the book says "budget." Twenty-one terms in the glossary, each page-referenced to the scene it came from.
 Two asks, and the second one matters more. Worth a look for the next update to the roundup? And separately — you run a company built on kids and money, so if you think spending-before-saving is wrong, I would rather hear it from you than keep saying it at conferences.
+One line worth having in a roundup, because parents ask it: Lexile AD 620L — Adult Directed, the industry's own code for a book meant to be read *with* a child rather than handed over. Twenty minutes out loud, interrupted the whole way. Grandparents take to it fastest — it gives them something to do with the grandkid instead of something to hand them, and every page has a "that reminds me of the time" sitting in it.
 I'll send a copy either way. https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
         </is>
@@ -28914,6 +29332,7 @@
 Thirty states now require a personal finance course to graduate. Delaware became the thirtieth last October. Every one of those mandates lands in high school, and the funding and training follow the mandate. Meanwhile the K-5 standards that already exist in most states sit there with almost nothing built against them, because nobody has to report on them.
 The sequence assumption underneath all of it is that children should learn saving first. I think that is backwards. Saving is the second thing a person does with money. The first is spending — and a first grader has done that, at a register, with a parent standing behind her. The behaviors a high school course is trying to correct were installed a decade earlier.
 I wrote the elementary piece rather than an argument about it: a 36-page picture book that follows one purchase from the idea to after the receipt, plus a free ungated classroom set crosswalked to the 2021 National Standards, Common Core, CEE and FDIC Money Smart. Sixteen-plus concepts, none announced, twenty-one-term glossary page-referenced into the story.
+One implementation note, since policy has to survive contact with an actual classroom. Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations, no teacher training required, and the same book does the family-engagement job at home with a parent or a grandparent. Elementary programs usually die on training cost. This one has none.
 The question: does NEFE's advocacy work have a position on the elementary band, or is the practical view that high school mandates are where the effort actually pays? I ask because if it's the second, I'd like to know I'm arguing with the consensus rather than filling a gap it agrees exists.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -30258,6 +30677,7 @@
 Here is my version of the argument, and I'd like to know whether it matches how you arrived at yours. Every children's money book teaches saving — I read all 25 on the ABA Foundation's list to be sure. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. We teach the second thing first and the first thing never.
 Clarence Gets a Bargain is the picture-book version. It follows a single purchase the whole distance — a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced; nobody says "budget." Twenty-one terms in a glossary at the end, each page-referenced to where it happened — which is the only point at which a kid works out he's been schooled.
 One story takes a kid from "I want it" to "Is it worth it?" — which I suspect is the same door your Challenge walks them through, thirty days at a time. Yours is a habit; mine is one transaction read in twenty minutes. Those look complementary to me rather than competing — the book could be the on-ramp to a challenge, or the thing a parent reads on day one.
+One thing your Challenge and the book share: neither one works with a kid alone in a room. It is Lexile AD 620L — Adult Directed, the trade's code for read-with rather than read-alone — and the mother explains every concept on the page, so whoever is reading gets handed the script. Parent, teacher or grandparent, the reading stops every few pages because the kid asks something.
 Worth a conversation? I'd rather compare notes with the one other person who put spending first than pitch anybody.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -30315,6 +30735,7 @@
 So I wrote the spending book. One purchase, followed the entire way: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, hands the cashier an extra ten-percent-off coupon like a tiny attorney presenting Exhibit A, discovers sales tax the way we all did — badly, and in public — and then has to live with the thing he chose. From the idea to after the receipt.
 Here is why it might fit a parenting audience rather than a classroom one. The concepts are smuggled. Sixteen-plus of them, none announced, nobody saying the word "budget." It reads as a story about a kid and a robot, and the parent doing the read-aloud gets handed the money conversation without having to deliver a lesson. And the kid does not know he's been schooled until he gets to the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. A parent can turn straight back to the exact page.
 The argument I'd bring to a podcast is the delayed one. It clicks later, in a real store. Months out, a kid says "there's a coupon in my pocket, just like Clarence" or "the sticker price isn't what you pay, there's tax" — recognition first, then the habit, and the parent isn't even in the room when it happens.
+For a parenting audience the format may matter more than the content. Lexile AD 620L — the AD is Adult Directed, the industry's own label for a book meant to be read *with* a child rather than left in their room. Mom explains every concept on the page, so the parent gets handed the script instead of being expected to know it. "Do we have a 529?" is a question a seven-year-old asks in the middle of page six, not after. Grandparents get the same deal, and they tend to enjoy it more.
 Would it work for your audience — podcast, newsletter, or neither? A no is a fine answer and faster than a maybe.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -30371,6 +30792,7 @@
 Mine is a money book, which I appreciate is the least promising sentence in children's publishing. So here is the part that makes it not that.
 Every book in this category teaches saving. Saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it — in a store, holding money, deciding whether the thing is worth what it costs. So mine follows one purchase from the idea to after the receipt: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose.
 The craft problem I'd most like another author's view on: I smuggled sixteen-plus concepts in without announcing any of them. Nobody says "budget." The glossary in the back — twenty-one terms, each page-referenced to the scene it came from — is the only place the book admits it was teaching. Getting that balance right, so it stays a story, was the whole job.
+The other half of the craft problem: it is written for an adult voice. Lexile AD 620L — Adult Directed — with the mother carrying every explanation, so whoever reads aloud gets handed the script. A series lives or dies on whether the grown-up still enjoys the fourth reading. You would know inside a page whether mine does.
 Would you read it and tell me where it stops being a story? I'll trade — send me a Noah and I'll read it properly.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -30429,6 +30851,7 @@
 The design choice that matters for your work: nothing is announced. Sixteen-plus concepts and nobody in the book says "budget." The kid does the math because the robot depends on it. The parent reading aloud is handed the conversation without having to give a lecture, which I gather is most of what you coach people out of. The child does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. The reveal is the last thing that happens, not the first.
 The shape of it, if it helps: one funny story about a boy and his dream robot takes a kid from "I want it" to "Is it worth it?" She opens it an impulsive little spender and closes it an aware, educated consumer.
 The part I'd most want your professional read on is the delayed return. The book is not really working in the twenty minutes it takes to read. It works in month eighteen, in an actual store, when the kid hits a real money moment and the book fires back — "wait, is the newer one really better? Clarence checked." Recognition first, then the habit. That is the book doing its job when the parent isn't even in the room.
+And the handoff you teach is the mechanism itself. The book is Lexile AD 620L — Adult Directed, the trade's own label for a book meant to be read *with* a child, not left in a bedroom — and Mom explains everything on the page, so the adult reading aloud is handed the script rather than asked to know the material. A parent who feels unqualified to teach money can still run it. Classroom, kitchen table, grandparent's couch: the reading stops every few pages because somebody asks.
 Two questions, either useful. Does the spending-before-saving sequence hold up against what you see in families? And is there a version of this that belongs in front of the parents you train?
 clarencegetsabargain.com/book-facts.html · https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -31158,7 +31581,8 @@
           <t>Sandy — FCCLA members are a decade older than my readers, so this is not a curriculum pitch. It is a service-project one, and I think it's a good one.
 Your chapters run community service. A high schooler reading a money book to a second-grade class is about the cleanest version of that I can think of — it needs no budget, no training, and one afternoon.
 The book is Clarence Gets a Bargain, 36 pages, ages 6-10. It follows one purchase the whole way, which is the thing that makes it work as a read-aloud rather than a lecture: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in it says "budget" — the twenty-one-term glossary in the back is page-referenced to the story, so the reader can field questions without preparing.
-It reads aloud in about twenty minutes, which is a class visit with time left for questions. And there is a free browser-based pretend register the younger kids can run afterward — a markdown, a coupon, sales tax, and a total that changes in front of them.
+The read-aloud is the entire project, so the spec matters. Lexile AD 620L — the AD is Adult Directed, the trade's own code for a book built to be read *with* a child rather than handed to one. About twenty minutes out loud, which is a class visit with time left for questions, and the mother explains every concept inside the text. A high schooler can read it cold to a second-grade class and field the questions straight off the page. Nothing to memorize, nothing to prepare, no training call beforehand.
+There is also a free browser-based pretend register the younger kids can run afterward — a markdown, a coupon, sales tax, and a total that changes in front of them.
 Does that fit how chapters choose service projects, or am I inventing a use case? Everything is free and ungated either way.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -31828,8 +32252,78 @@
       <c r="M81" s="5" t="inlineStr"/>
       <c r="N81" s="5" t="inlineStr"/>
     </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>🐋</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Grandparents</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Ron Lieber</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>New York Times</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>Read-along / grandparent lane. Lexile AD 620L = Adult Directed is the load-bearing claim.</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>lieber@nytimes.com</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>The kids' money category skipped the cash register</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>2794</v>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>Ron,
+The Opposite of Spoiled is the reason I knew what I was looking for and couldn't find it. This is a column idea, and it works whether or not my book is in it.
+Every children's book about money teaches earning or saving. I read all 25 titles on the ABA Foundation's list to be sure. Piggy banks, lemonade stands, three jars labeled spend-save-give where "spend" gets one page and a guilty look.
+But saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate and no income. What she has done is stand at a register holding a birthday five and decide. Spending is the first financial act a person performs, and the entire category skipped it for forty years.
+The timing gap sharpens it. Thirty states now guarantee a personal finance course — in high school. Money habits are largely set by seven. We're preparing children for 65 and sending them to the register unarmed today, into a store that spent millions working out how to get the five dollars in their hand.
+I wrote the book I couldn't find. Clarence Gets a Bargain, ages 6–10, one kid and one complete purchase: earning it, the sale ads at the kitchen table, two models compared on a shelf, the cheaper one taken deliberately, a coupon at the register, sales tax, and living with the thing afterward. Idea to post-receipt. Sixteen-plus concepts, none of them announced — nobody in the book says the word "budget." The reader doesn't work out he's been schooled until he reaches the glossary in the back, twenty-one terms, each one page-referenced to the scene where it happened.
+I'm an attorney, which shows: the mother photographs the receipt before the car leaves the parking lot, every time, because a receipt is what makes a return or a warranty claim winnable. Kids are consumers years before anyone tells them they have rights as one. That's a second column and possibly a better one.
+The format is worth a line too. It's catalogued Lexile AD 620L — AD for Adult Directed, the trade's own code for a book meant to be read with a child rather than handed to one. The money conversation you've spent a decade telling parents to have is structurally forced: an adult reads, a kid interrupts, and somebody has to answer "do we have one of those?" out loud. Works the same when the adult is a grandparent, which is often who's actually sitting there.
+The story I'd pitch isn't mine. It's the forty-year hole — why a whole publishing category taught children to save and skipped the only place a child has ever actually handled money.
+Wrong about that? You'd know better than anyone. clarencegetsabargain.com/book-facts.html has the specs, and I'll send a copy if it's useful.
+Jonathan Bach
+Attorney and children's book author, Baltimore
+questions@clarencegetsabargain.com</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr"/>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>National Grandparents Day is Sun 13 Sep 2026 — the September peg for this lane.</t>
+        </is>
+      </c>
+      <c r="M82" s="5" t="inlineStr"/>
+      <c r="N82" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N81"/>
+  <autoFilter ref="A1:N82"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -26507,12 +26507,12 @@
         </is>
       </c>
       <c r="I646" s="5" t="n">
-        <v>1949</v>
+        <v>2063</v>
       </c>
       <c r="J646" s="5" t="inlineStr">
         <is>
           <t>Mr. Keen — congratulations on the building. You took over a school in a town where I spend a good part of my year, so this is a local letter, and I'll keep it short because it's your first fall.
-I have had a shirt printed that reads PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW, so you may yet see me in it. Half your families were on that boardwalk in July, mid-negotiation with a seven-year-old over a claw machine. That is the moment this book is about.
+I have had a shirt printed that reads PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW, so you may yet see me in it. Half your families were on that boardwalk in July, mid-negotiation with a seven-year-old over a claw machine. That machine takes $25 to hand back a basketball Walmart sells for $9.99, and the kid has no way of knowing that. That is the moment this book is about.
 I wrote and illustrated a children's book about money. Clarence Gets a Bargain — 36 pages, grades 1-5, and it does the one thing the rest of the category skips. Every other kids' money book teaches saving. Mine teaches a purchase: a boy earns a robot, reads the sale ads at his kitchen table, compares two on a shelf, walks past the newer one deliberately, redeems a coupon at the register, and gets ambushed by sales tax. He is not thrilled about the sales tax. Neither was I at that age.
 Delaware has had K-12 financial literacy standards since 2018, and HB 203 last October sent the whole rollout to high school. Your grade band has the standard and none of the shopping list.
 The teacher side is free — four 45-minute lessons, a discussion guide, assessments with the answer keys already done, and a crosswalk to Jump$tart, CEE, Common Core, and FDIC Money Smart. It prints straight from a browser. No account, no email gate, no cost to the building.
@@ -27043,12 +27043,12 @@
         </is>
       </c>
       <c r="I655" s="5" t="n">
-        <v>1718</v>
+        <v>1888</v>
       </c>
       <c r="J655" s="5" t="inlineStr">
         <is>
           <t>Attn: Leslie Glenn, Youth Services
-Ms. Glenn — I have had a shirt printed that reads PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW. It is either marketing or a cry for help, and I intend to find out on the boardwalk this summer. In the meantime I am asking you.
+Ms. Glenn — I have had a shirt printed that reads PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW. It is either marketing or a cry for help, and I intend to find out on the boardwalk this summer. If anyone does ask, the answer is short: the claw machine takes $25 to hand back a basketball Walmart sells for $9.99, and a kid who has seen the $9.99 stops feeding it. In the meantime I am asking you.
 I wrote and illustrated a children's book and I would like to read it in your building.
 Clarence Gets a Bargain is 36 pages, ages 6-10. A boy earns a robot for good grades and chores, learns to read the sale ads, compares two models in a store, picks the discounted one over the newest one, hands a coupon to a cashier, and discovers sales tax the way we all did — badly, and in public. It reads aloud in about twenty minutes.
 What makes it work for a summer program is that the kids do something afterward. I bring printable mock price tags and ten-percent-off coupons, and there's an online pretend register they can run on a library computer where they ring up the same purchase and watch a markdown and a coupon change the total. It's a book event that turns into an activity without a worksheet in it.
@@ -27103,12 +27103,12 @@
         </is>
       </c>
       <c r="I656" s="5" t="n">
-        <v>1766</v>
+        <v>1831</v>
       </c>
       <c r="J656" s="5" t="inlineStr">
         <is>
           <t>Ms. Noonan — you coordinate the children's programming at Lewes, so you already know the difference between a book event that fills a room and one where six kids show up because it was raining. I'll tell you which one I think this is and you can decide.
-For calibration, I have had a shirt printed that says PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW. Whether anyone stops me is still an open question. But the arcade is where the money conversation happens whether a parent planned it or not, and that is the whole subject of the book.
+For calibration, I have had a shirt printed that says PREVENT BOARDWALK MELTDOWNS &amp; ARCADE HISSY-FITS, ASK ME HOW. Whether anyone stops me is still an open question. But the arcade is where the money conversation happens whether a parent planned it or not — $25 into a glass box for a basketball Walmart sells for $9.99 — and that is the whole subject of the book.
 I wrote and illustrated Clarence Gets a Bargain — 36 pages, ages 6-10. A boy earns a robot, does his "shopping homework" in the newspaper sale inserts, compares two models in a store, chooses the cheaper of the two on purpose, redeems a coupon at the checkout, and then meets sales tax and takes it as a personal betrayal. Twenty minutes read aloud.
 The reason it works as programming rather than just a reading: afterward the kids run the purchase themselves. There's a pretend register that runs in any browser, plus printable price tags and coupons, and they figure out the markdown and the discount with their own hands. Seven-year-olds get competitive about it. Loudly.
 No fee. I'm nearby a good part of the year, and I illustrated the book myself, so a drawing session is on the table if that suits the room better.

--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -1864,8 +1864,23 @@
           <t>Bill — Tennessee's commission decides what reaches classrooms statewide, and elementary is usually where state mandates run thin. Mine is a K-5 picture book with a free zero-prep classroom pack against Jump$tart, CEE, Common Core, and FDIC Money Smart. Route to get it in front of the commission? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr"/>
-      <c r="L20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Bill — a question about grade band from someone who has read what states actually fund.
+Tennessee's requirement, like all thirty of them, lands in high school. That is where the money, the training and the reporting go. The elementary standards sit underneath it with almost nothing built against them, because nothing requires a district to report on that band.
+The sequencing assumption is the part I keep circling. Financial education starts children with saving. Saving is the second thing a person does with money; the first is spending, and a first grader has done it — at a register, with a parent standing right there. The behaviors a high school course tries to correct were installed a decade earlier.
+So I built the K–5 piece. A 36-page picture book that follows one purchase from the idea to after the receipt — sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken on purpose, a coupon at the register, sales tax, and living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story.
+What matters for a commission is the rest of it, and it is free: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart. Ungated, no account, prints from a browser. A district adopting it spends nothing. Catalogued Lexile AD 620L — Adult Directed — so it is a one-period read-aloud that needs no teacher training.
+Does elementary sit inside what the Commission convenes or funds, or is high school the whole remit?
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M20" s="5" t="inlineStr"/>
       <c r="N20" s="5" t="inlineStr"/>
     </row>
@@ -1910,8 +1925,22 @@
           <t>Dave — Wisconsin has been at this longer than most states. My K-5 book and free lesson set map to five frameworks. Elementary tends to be the underserved band everywhere I look. Is there a submission route, or a person who reviews outside materials? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. For teachers: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr"/>
-      <c r="L21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Dave — Wisconsin has run a state financial-literacy office longer than most states have had a requirement, so you have seen more of these come and go than almost anyone. I would like a read on one assumption.
+Every mandate in the country lands in high school. Thirty of them now. Money habits are largely set by seven, which puts the policy about a decade behind the behaviour. Underneath that sits the belief that children should learn saving first. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent right there.
+I built the K–5 piece rather than an argument about it. A 36-page picture book that follows one complete purchase: the sale ads at the kitchen table, comparison on a shelf, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced — nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
+The classroom set behind it is free and ungated: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, and a 23-row crosswalk to the 2021 National Standards, Common Core Math and ELA, CEE and FDIC Money Smart. No account, no email capture, prints from a browser. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud that a teacher without a finance background can run cold, and the same book works at a kitchen table.
+The question: in your experience, does elementary material get adopted when it is free and aligned, or does it need a mandate behind it to move at all? I would rather know now than find out slowly.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M21" s="5" t="inlineStr"/>
       <c r="N21" s="5" t="inlineStr"/>
     </row>
@@ -2017,8 +2046,22 @@
           <t>Tom — your "Everything Your Child Should Know About Money" post did 22 comments on a 3,000-follower account. In this category that's a stadium. I studied it. Mine is the picture-book version for six-year-olds: one purchase, ad to register, tax at the end. Would you tell me whether it holds, or whether I've written a very long receipt? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Tom — you got more genuine engagement out of one post about kids and money than anyone else in this category has managed, which tells me you know exactly which part of this parents actually care about. I would like to check my premise against that.
+My premise: the whole field has the sequence backwards. Financial education starts children with saving. Saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, standing in a store holding a birthday five, working out whether the thing is worth what it costs. We teach the second thing first and the first thing never.
+So I wrote and illustrated the spending book. Clarence Gets a Bargain follows one purchase the whole way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax and objects to it, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." The reader works out he has been schooled only at the glossary — twenty-one terms in the back, page-referenced to the scene each came from.
+The instruction underneath the whole book is four words long: stop bringing kids to the store as cargo, bring them as staff. Catalogued Lexile AD 620L — Adult Directed — so the parent gets handed the script rather than an assignment, which I suspect is why your posts land: parents want the conversation and do not feel qualified to start it.
+The thing I would actually value: you know what makes a parent stop scrolling on this subject and what makes them scroll past. If "spending before saving" is the wrong hook, I would rather hear it from you than keep testing it slowly.
+Would you look and tell me? https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M23" s="5" t="inlineStr"/>
       <c r="N23" s="5" t="inlineStr"/>
     </row>
@@ -2063,8 +2106,23 @@
           <t>Andrew — 20 million downloads means you've heard every money pitch ever assembled. Here's mine: I wrote the only picture book where the kid pays sales tax. Everything else stops at the piggy bank. Do I know that for certain? I checked all 25 titles on the ABA Foundation's list, so reasonably certain. Episode, or is the gap imaginary? The format is part of the story: Lexile AD 620L — AD is Adult Directed, the industry's own code for read-WITH. An adult reads, a kid interrupts, and somebody has to answer "do we have one of those?" out loud. Same whether the adult is a teacher, a parent, or a grandparent. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>Andrew — your audience is adults fixing money habits. I wrote the book that tries to stop the habits forming, and there is an episode in the argument whether or not the book is in it.
+Every children's money book teaches saving. Piggy banks, lemonade stands, three jars. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding a birthday five, working out whether the thing is worth what it costs.
+Nobody put that in a story. So I did. Clarence Gets a Bargain follows a single purchase the whole way — a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax and regards it as a personal insult, then lives with the thing he chose. Idea to post-receipt.
+Sixteen-plus concepts and none of them announced. Nobody in the book says "budget," which for a book largely about budgeting took some doing. Kids smell a worksheet one page in; they never smell this one, because they are laughing too hard to notice. The reveal is the glossary — twenty-one terms in the back, page-referenced to the scene each came from.
+Catalogued Lexile AD 620L — Adult Directed, so it is a read-with, which means the parent listening to your show gets handed the script rather than a homework assignment.
+The episode I would pitch is not the book. It is the forty-year hole: an entire publishing category taught children to save and skipped the cash register, the only place a child has ever actually handled money.
+Worth twenty minutes of your show? https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M24" s="5" t="inlineStr"/>
       <c r="N24" s="5" t="inlineStr"/>
     </row>
@@ -2109,8 +2167,22 @@
           <t>Amy — every money book on your shelf ends at the piggy bank. Mine starts at the register: sale ads, comparison, a markdown sticker, a coupon, and the sales tax nobody warns a six-year-old about. 36 pages, 21-term glossary with page refs. Would it circulate at Boston Public, or would it sit? Spec for the shelf: Lexile AD 620L — AD is Adult Directed, the trade's code for a book meant to be read WITH a child rather than handed over. Twenty minutes out loud, which makes it a storytime and a family take-home at the same time. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr"/>
-      <c r="L25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Amy — two requests come to your desk all week. A kid wants a robot book. A parent wants something that teaches money. I wrote the one that answers both in a single checkout.
+Clarence Gets a Bargain is a 36-page picture book, ages 6–10, that follows one kid through one complete purchase: he earns a robot reward with chores and grades, does his shopping homework in the newspaper sale ads, comparison-shops the aisle, finds the markdown, hands a coupon to the cashier, meets sales tax, and watches his mother photograph the receipt before the car leaves the lot. Kids read it as a robot story. Sixteen-plus money concepts come along without announcing themselves, and the back matter carries a twenty-one-term glossary where each definition points to the page where the term happens in the plot — a decoder rather than an appendix.
+The collection case, with the qualifier a librarian will appreciate: most money picture books cover earning or saving. To my knowledge this is the first narrative picture book for this age band that traces the whole consumer arc, wish through receipt. It fills a hole rather than adding a fourth piggy-bank book to the shelf.
+Cataloguing: ISBN 979-8-234-07638-0 · LCCN 2026906164 · hardbound, case bound, full colour, 11×8.5′′ · Est. Lexile AD 620L, Guided Reading L–N · $19.99. The AD is Adult Directed, which makes it a storytime title and a family take-home at the same time. Every fact is on one page: clarencegetsabargain.com/book-facts.html
+Programming is already built and free — printable price tags and clearance stickers for a pretend store, a browser-based register kids run themselves, a five-question quiz with a printable certificate. A storytime plus the pretend store is a complete Money Smart Week event with no prep budget.
+Kids re-read it without being asked, which is the only metric that matters at your desk. Review copy on request?
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M25" s="5" t="inlineStr"/>
       <c r="N25" s="5" t="inlineStr"/>
     </row>
@@ -2155,8 +2227,23 @@
           <t>Sarah — a children's librarian at NYPL sees more money books than almost anyone alive. Mine breaks the pattern by having no piggy bank in it. It teaches spending, and there's a 21-term glossary with page references in the back so it doubles as a reference title. Would it circulate? Happy to send a copy. Spec for the shelf: Lexile AD 620L — AD is Adult Directed, the trade's code for a book meant to be read WITH a child rather than handed over. Twenty minutes out loud, which makes it a storytime and a family take-home at the same time. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>Sarah — a collection-development pitch, kept to the facts because I know what August looks like at your desk.
+Clarence Gets a Bargain is a 36-page picture book, ages 6–10, following one kid through one complete purchase: earning the robot reward, doing shopping homework in the newspaper sale ads, comparison shopping the aisle, finding the markdown, handing a coupon to the cashier, paying the sales tax, and watching his mother photograph the receipt before the car leaves the parking lot. Sixteen-plus money concepts ride inside the plot. Nobody in the book says the word "budget."
+The case for the shelf: nearly every money picture book teaches earning or saving. To my knowledge this is the first narrative picture book for this band that follows the whole consumer arc, wish through receipt. The back matter carries a twenty-one-term glossary in which every definition cites the page where the term happens in the story, so a child looking something up lands in a scene rather than a definition list.
+Cataloguing: ISBN 979-8-234-07638-0 · LCCN 2026906164 · hardbound, case bound, full colour, 11×8.5′′ · Est. Lexile AD 620L, Guided Reading L–N · $19.99. Full record at clarencegetsabargain.com/book-facts.html. The AD in that Lexile stands for Adult Directed, so it does double duty as a read-aloud title and a take-home.
+Programming, already built and free: printable price tags and clearance stickers for a pretend store, a browser-based Sea-Mart register children operate themselves with a markdown, a coupon and sales tax, and a quiz with a printable certificate. No prep budget required for a Financial Literacy Month or Money Smart Week event.
+Endorsed by a K–5 educator with 30+ years in the classroom and by the 2026 EIFLE Educator of the Year.
+Shelve it under picture books; file it under secret weapons. Happy to send a review copy — reply with an address?
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M26" s="5" t="inlineStr"/>
       <c r="N26" s="5" t="inlineStr"/>
     </row>
@@ -2201,8 +2288,23 @@
           <t>Gretchen — nowhere near your beat, so this is short. I read all 25 titles on the ABA Foundation's children's financial literacy list. Every one teaches earning, saving, or investing. None teaches spending, which is the only transaction a six-year-old actually performs. That gap struck me as a matter of first impression, so I wrote the book. If someone at the Times covers this, I'd take the name. One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr"/>
-      <c r="L27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Gretchen — you have spent a career on how financial products get sold to people who don't fully understand them. Here is the entry-level version of that, and nobody covers it.
+A child becomes a consumer the first time money leaves their hand. Six years old, a birthday five, a store. From that moment they are a party to transactions, and the entire financial education apparatus treats them as a saver in training instead. We teach them to hold money. Nobody teaches them what happens when they use it.
+The scale is small and the mechanics are identical to the ones you write about. A claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the child has no way of knowing that. Not a game of skill — a slot machine wearing a carnival hat, aimed at someone with no price memory and no comparison to make.
+I wrote the picture book for it. One kid, one purchase, followed the whole way: he wants a robot, earns it, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget." The child works out he has been schooled only when he reaches the glossary — twenty-one terms in the back, each page-referenced to where it happened.
+The format matters: Lexile AD 620L. The AD is Adult Directed, the trade's own code for a book meant to be read with a child rather than handed over.
+The story is not the book. It is that an entire publishing category taught children to save for forty years and skipped the register, which is the only place a child has ever handled money — while the arcade, the app store and the checkout lane did not skip it at all.
+Is there anything there? clarencegetsabargain.com/press-kit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M27" s="5" t="inlineStr"/>
       <c r="N27" s="5" t="inlineStr"/>
     </row>
@@ -2247,8 +2349,23 @@
           <t>Kim — you cover retail. Mine is a six-year-old's first walk through one. Circular at the kitchen table, find the aisle, compare two models, hand a coupon to a cashier, then discover sales tax the hard way. Retail from four feet up, with a robot. Story, or a colleague who'd want it? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr"/>
-      <c r="L28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>Kim — you cover retail, so you already know the boardwalk arcade is a pricing strategy rather than a game. I wrote the children's book that explains it before a kid loses to it.
+The number I keep coming back to: a claw machine takes $25 to hand back a basketball that Walmart sells for $9.99. That is the entire business model in one glass box — charge $25 for the $9.99 thing and make it feel like winning. Once a kid has seen the $9.99, the claw loses its grip. Nobody shows them the $9.99.
+Every children's money book teaches saving. Piggy banks, jars, three little tins labeled spend-save-give where "spend" gets one page and a guilty look. But saving is the second thing a child does with money. The first is spending, and a six-year-old has done it already, standing in a store, deciding.
+So mine follows a single purchase the entire distance. A boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one deliberately, hands a coupon to the cashier, meets sales tax, and then lives with the thing. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
+It is catalogued Lexile AD 620L — Adult Directed, meaning read-with rather than read-alone, so the parent gets handed the script instead of being expected to know it.
+The retail angle, if you want one: every trick your beat covers — the fake markdown, the anchor price, the "newest is better" framing — gets run on children first, in arcades and toy aisles, where there is no consumer press at all.
+Worth a look? clarencegetsabargain.com/book-facts.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M28" s="5" t="inlineStr"/>
       <c r="N28" s="5" t="inlineStr"/>
     </row>
@@ -2293,8 +2410,23 @@
           <t>Terry — syndicated for decades means you've seen every kids' money book twice. Mine leaves saving out entirely. Reckless? Possibly. But spending is the transaction a six-year-old performs first, and forty years of piggy banks haven't fixed that. 36 pages, ages 6-10. Column, or am I overselling the gap? The format is part of the story: Lexile AD 620L — AD is Adult Directed, the industry's own code for read-WITH. An adult reads, a kid interrupts, and somebody has to answer "do we have one of those?" out loud. Same whether the adult is a teacher, a parent, or a grandparent. Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Terry — you have been telling adults the truth about money for decades, usually after the damage is done. I wrote the book for about twenty years earlier than you usually get them.
+The argument in one line: mistakes at eleven cost $14, and the same mistake at twenty-seven has a credit card attached. Everything you write about compounding cuts both ways, and the habits doing the compounding were installed in a store, at six, with a parent saying no.
+Which is where the whole category gets the order wrong. Children's money books teach saving — piggy banks, jars, patience. But saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate. She has stood at a register holding money and had to decide.
+Clarence Gets a Bargain follows one purchase the entire way: a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax and takes it personally, then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none announced — nobody in the book says "budget." The reader finds out he has been schooled at the glossary, twenty-one terms in the back, each page-referenced to the scene it came from.
+It reads aloud in twenty minutes. Lexile AD 620L — Adult Directed, the industry's own code for read-with rather than read-alone, so a parent who feels unqualified on money still gets handed the script.
+The column question rather than the book question: has anyone made the case that spending competence has to come first? I have not been able to find it, and you would know if it exists.
+clarencegetsabargain.com/press-kit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M29" s="5" t="inlineStr"/>
       <c r="N29" s="5" t="inlineStr"/>
     </row>
@@ -2339,8 +2471,22 @@
           <t>Amanda — Planet Money is good at the moment someone realizes the economy just did something to them. Mine is that moment at four feet tall. Kid reaches the register, total's higher than the sticker, and sales tax enters his life uninvited. He takes it personally. 36 pages. Is that a segment or just a strange thing to have made? The format is part of the story: Lexile AD 620L — AD is Adult Directed, the industry's own code for read-WITH. An adult reads, a kid interrupts, and somebody has to answer "do we have one of those?" out loud. Same whether the adult is a teacher, a parent, or a grandparent. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr"/>
-      <c r="L30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>Amanda — Planet Money's whole trick is that people will sit still for an economics lesson if it is hidden inside a story about a person and a thing. I did that at a first-grade reading level, and I am writing about the story rather than the book.
+Every children's money book teaches earning or saving. All 25 on the ABA Foundation's list — I read them to be sure. A piggy bank, a lemonade stand, a lesson. Not one covers the cash register, which is the only place a child has ever actually handled money.
+Mine does. A boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, gets ambushed by sales tax, and then lives with what he bought. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget." They do not realise they have been schooled until they hit the glossary in the back — twenty-one terms, each page-referenced to the moment it happened. That is where the con comes apart, on purpose.
+Format note, since you make things people take in together: Lexile AD 620L, where AD means Adult Directed — a book built to be read with a child, interrupted the whole way.
+The segment is the forty-year hole. A whole publishing category taught children to save and skipped the register, while every arcade, app store and checkout lane aimed at children did not skip it at all.
+Is that an episode whether or not my book is in it? Four-minute flip: https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M30" s="5" t="inlineStr"/>
       <c r="N30" s="5" t="inlineStr"/>
     </row>
@@ -2385,8 +2531,23 @@
           <t>Bethann — a bankers association reaches classrooms and families at once, which is the distribution a K-5 book needs and rarely gets. Mine is five frameworks, free zero-prep lessons, plus a grant packet if a member bank wanted to fund classroom sets. Fit Utah's outreach? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>Bethann — you run the education side of a bankers association, which means you are the person who decides what volunteers actually carry into a classroom. I built something for the grade band most bank programs skip.
+Most financial education a bank sponsors lands in high school or in a "teach a child to save" day about saving. Saving is the second thing a child does with money. The first is spending, and a first grader has done it, at a register, with a parent behind her. There is almost nothing to hand a banker walking into a second-grade room about that.
+Clarence Gets a Bargain is a 36-page picture book following one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget."
+Why it works for a volunteer rather than a teacher: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, and the mother explains every concept inside the text. A banker can read it cold and field the questions straight off the page. No training call, nothing to memorise. Free lesson plans, assessments and a browser-based pretend register sit behind it, all ungated.
+The sponsorship math is simple if a member bank wants it: 25 copies is $499.75, one classroom, the bank's name on every book that goes home to a family. The educator program is free, so the sponsorship is entirely books, and I have a CRA-ready memo already written in examiner-friendly language.
+Does that fit how Utah banks choose classroom programs, or am I inventing a use case?
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M31" s="5" t="inlineStr"/>
       <c r="N31" s="5" t="inlineStr"/>
     </row>
@@ -2431,8 +2592,24 @@
           <t>Lynnette — you've built both a body of work and a network around this. Mine is a K-5 picture book teaching spending rather than saving. I'd take your read on where a book like this belongs, and whether FIN is a fit at all. A blunt no is useful too. The format is part of the story: Lexile AD 620L — AD is Adult Directed, the industry's own code for read-WITH. An adult reads, a kid interrupts, and somebody has to answer "do we have one of those?" out loud. Same whether the adult is a teacher, a parent, or a grandparent. More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr"/>
-      <c r="L32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>Lynnette — you have spent a career telling people the truth about money in language they can actually use, and you built a network for people doing the same. I wrote the six-year-old version and I would like your read on whether it lands.
+Every children's money book teaches saving. Piggy banks, jars, three tins labeled spend-save-give where "spend" gets one page and a guilty look. But saving is the second thing a child does with money. The first is spending, and a first grader has already done it — in a store, holding money, deciding.
+And the tools have moved against them. A card is magic; a five-dollar bill is arithmetic — a kid who watches three dollars leave their hand understands something no tap-to-pay will ever teach.
+Which matters most in households where there is no margin for a bad purchase. A child taught only to save has been handed advice that assumes surplus. A child who can compare two prices and choose deliberately has a skill that works this Saturday.
+Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, meets sales tax, and then lives with what he chose. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the story.
+Catalogued Lexile AD 620L — Adult Directed — so the adult reading it is handed the script and does not have to be the one who already knows about money. That was the design constraint that mattered most: it has to work in a house where nobody feels qualified to teach it.
+Two questions. Does the spending-first argument hold up against what you hear from your audience? And is there a version of this worth putting in front of the Financial Influencer Network?
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M32" s="5" t="inlineStr"/>
       <c r="N32" s="5" t="inlineStr"/>
     </row>
@@ -2477,8 +2654,23 @@
           <t>Ruben — my book and teaching pack are aligned to the CEE standards with a full crosswalk. Is there a route for a K-5 title into CEE's resource library or EconEdLink, and what would you want to see first? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr"/>
-      <c r="L33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>Ruben — CEE's standards are one of the five frameworks I crosswalked against, so I have spent real time inside them and want to ask about the bottom of the ladder.
+The elementary benchmarks exist. What is built against them is thin, and thinner still on the spending side. The field starts children with saving, and saving is the second thing a person does with money. The first is spending: standing in front of two prices and choosing one. A first grader has done that; she has no savings rate at all.
+I built a free K–5 classroom set around a 36-page picture book and crosswalked it concept by concept — 23 rows against the 2021 National Standards for Personal Financial Education, CEE, Common Core Math and ELA, and FDIC Money Smart, with the Grade 4 benchmark codes rather than a general claim of alignment. It is published so a reviewer can check it instead of taking my word.
+The book follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with the choice. Sixteen-plus concepts and nobody in it says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened.
+Catalogued Lexile AD 620L — Adult Directed — one class period read aloud, and because the mother explains every concept inside the text a teacher with no economics background can run it cold.
+The question: is there a route for elementary material to sit alongside CEE programs, or does that run through affiliate councils? Either answer saves me guessing.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M33" s="5" t="inlineStr"/>
       <c r="N33" s="5" t="inlineStr"/>
     </row>
@@ -2523,8 +2715,24 @@
           <t>Beth — My Mother's Money is about the inheritance nobody itemizes. Mine is the earliest deposit into it: a mother teaching a six-year-old to read a sale ad, compare two prices, and understand why the register total climbed. She also photographs every receipt in the parking lot. Real habit, straight into the book. Column? It's written for an adult voice — Lexile AD 620L, Adult Directed, read-with rather than read-alone — with Mom carrying every explanation, so whoever reads aloud gets handed the script. That constraint shaped every page. Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>Beth — you write for people trying to do the right thing with money and finding the advice arrives late. This arrives about two decades earlier than most of it.
+The premise: financial education starts children with saving, and the sequence is backwards. Saving is the second thing a person does with money. The first is spending. A seven-year-old has no savings rate and no income; what she has done is stand at a register holding money and choose. We teach that last, or never.
+I wrote the picture book for it. One purchase, followed the whole way — a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, meets sales tax, and then lives with what he chose. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; not one covers the whole arc.
+Sixteen-plus concepts, none announced — nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened, so vocabulary points a kid back into the story rather than away from it.
+Catalogued Lexile AD 620L — Adult Directed, read-with rather than read-alone. The mother explains everything on the page, so the parent gets the script and can take the credit.
+One thing I would put to you as a planner: a card is magic, and a five-dollar bill is arithmetic. Children now grow up almost entirely inside the first one, which removes the only feedback loop they had.
+The claim I would defend hardest is the delayed one. The book is not really working in the twenty minutes it takes to read. It works in month eighteen, in a real store, when the kid hits a money moment and the book fires back — "wait, is the newer one actually better?" Recognition first, then the habit.
+Does that hold up against what you see in readers? clarencegetsabargain.com/book-facts.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M34" s="5" t="inlineStr"/>
       <c r="N34" s="5" t="inlineStr"/>
     </row>
@@ -2569,8 +2777,23 @@
           <t>Julie — you translate markets for a big audience daily. Mine translates one purchase for a six-year-old: compare, take the cheaper model, pay the tax, feel mildly cheated. Smallest possible economics story. Segment, or wrong desk? The format is part of the story: Lexile AD 620L — AD is Adult Directed, the industry's own code for read-WITH. An adult reads, a kid interrupts, and somebody has to answer "do we have one of those?" out loud. Same whether the adult is a teacher, a parent, or a grandparent. Press kit: https://clarencegetsabargain.com/press-kit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr"/>
-      <c r="L35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>Julie — a segment idea, and it is short enough to survive a live hit.
+Every children's money book teaches saving. Piggy banks, lemonade stands, jars. But saving is the second thing a child does with money — the first is spending, and a six-year-old has already done it, in a store, holding a birthday five, deciding whether the thing is worth what it costs.
+The category skipped that for forty years. The arcade did not. A claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the kid has no price memory to defend himself with. Once a kid has seen the $9.99, the claw loses its grip.
+So I wrote the spending book. Clarence Gets a Bargain, ages 6–10: a boy earns a robot with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and then lives with the thing he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Twenty-one terms in a glossary at the back, each page-referenced to where it happened.
+Catalogued Lexile AD 620L — Adult Directed, the trade's own code for a book read with a child rather than handed to one. Twenty minutes out loud, interrupted the whole way.
+I am an attorney and a mixed-media artist, and I have twice walked out of the same Nordstrom Rack having paid one cent — once for a $293 pair of shoes, once for a $69.50 shirt. I kept both tags. It makes for a good visual if you ever want one on screen.
+Is there a hit in "the money skill nobody teaches kids"? clarencegetsabargain.com/press-kit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M35" s="5" t="inlineStr"/>
       <c r="N35" s="5" t="inlineStr"/>
     </row>
@@ -2615,8 +2838,23 @@
           <t>Matt — Ask Questions, Save Money, Make More is a skill book. Mine is the same skill at six: ask what it costs, ask whether the older one is actually worse, ask why the total went up at the register. I'd take your read on positioning a spend-first kids' book with no shelf-mates. It's written for an adult voice — Lexile AD 620L, Adult Directed, read-with rather than read-alone — with Mom carrying every explanation, so whoever reads aloud gets handed the script. That constraint shaped every page. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr"/>
-      <c r="L36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>Matt — you spend your working life on what happens when people meet credit without the groundwork. I wrote the book about the groundwork, roughly twenty years upstream of your data.
+The sequence is the whole argument. Financial education starts children with saving. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent behind her. Mistakes at eleven cost $14. The same mistake at twenty-seven has a credit card attached and a rate on it.
+Clarence Gets a Bargain follows one purchase the entire distance: a boy wants a robot, earns it with chores and grades, works the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; they are all parked on the earning-and-saving side of the register.
+Sixteen-plus concepts and nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened — which is the only point at which a kid works out he has been schooled.
+Catalogued Lexile AD 620L — Adult Directed, so it is read-with rather than read-alone and the parent gets handed the script.
+The question, since you have the data and I only have the book: does anything in what you see suggest that price competence at seven shows up at twenty-seven? If it does not, I would rather know.
+clarencegetsabargain.com/book-facts.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M36" s="5" t="inlineStr"/>
       <c r="N36" s="5" t="inlineStr"/>
     </row>
@@ -2661,8 +2899,22 @@
           <t>Jillian — Intuit for Education is built around real financial decisions, which is my book's entire structure: one purchase, ad to register, sales tax included. Mine sits at K-5, below your usual band. Does the framing match how you think about curriculum? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr"/>
-      <c r="L37" s="5" t="inlineStr"/>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>Jillian — Intuit for Education is built for high school and does that job well, so this is a question about the floor beneath it rather than a pitch into your territory.
+Everything in the field lands late. Thirty states require personal finance to graduate, all of it in high school. Money habits are largely set by seven. And the sequencing assumption nobody questions is that children should start with saving — when saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has stood at a register and chosen.
+I built the K–5 on-ramp. A 36-page picture book that follows one purchase the whole distance — wanting the robot, earning it, working the sale inserts at the kitchen table, comparing two models on a shelf, taking the marked-down one on purpose, redeeming a coupon, meeting sales tax, and living with the choice. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced back into the story.
+The curriculum behind it is free and ungated — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart, printable classroom pieces, and a browser-based pretend register that runs a markdown, a coupon and sales tax with the total changing in front of the class. Catalogued Lexile AD 620L — Adult Directed — one class period, no teacher training.
+The honest question rather than a pitch: when teachers come to Intuit for Education, does elementary ever come up as something they want and cannot find? I am trying to work out whether I am filling a gap or inventing one, and you would see the demand signal before I would.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M37" s="5" t="inlineStr"/>
       <c r="N37" s="5" t="inlineStr"/>
     </row>
@@ -2707,8 +2959,23 @@
           <t>Saskia — Promise Academy is deliberate about what earns classroom time, which is the right instinct. Mine teaches the complete purchase, sales tax included, and the family activity was built for a kitchen table. Classrooms or family programming — or neither? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr"/>
-      <c r="L38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Saskia — HCZ built its whole model on the idea that you intervene early and you do not wait for the system to catch up. I built the elementary financial-literacy piece on the same reasoning, and I would like your read on whether it holds.
+Every state financial-literacy requirement lands in high school. The habits being corrected there were installed at six, in a store. And the field starts children with saving, which is the second thing a child does with money — the first is spending, and it is the one your students are already doing.
+That distinction matters more, not less, for families with less room for error. A child who can compare two prices and choose deliberately has a skill that pays on a Saturday. A child taught only to save has been handed advice that requires surplus.
+Clarence Gets a Bargain is a 36-page picture book that follows one complete purchase: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget." A twenty-one-term glossary in the back, page-referenced to the story.
+Catalogued Lexile AD 620L — Adult Directed — one class period out loud, and because the mother explains every concept inside the text, a teacher needs no finance background. Everything behind it is free and ungated: lesson plans, assessments with answer keys, a standards crosswalk, printable classroom pieces, a browser-based pretend register.
+Would a read-aloud plus a pretend-store activity fit anywhere in a Promise Academy week, or is the schedule too tight for anything that is not tested?
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M38" s="5" t="inlineStr"/>
       <c r="N38" s="5" t="inlineStr"/>
     </row>
@@ -2753,8 +3020,22 @@
           <t>Ben — you run personal finance coverage, so one line: every children's money book teaches saving, mine teaches spending, and the six-year-old pays sales tax on page 22. Did I verify that gap or just assert it? Verified — all 25 titles on the ABA Foundation list. Story, or someone on the desk who'd take it? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr"/>
-      <c r="L39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>Ben — a story pitch about a gap in the coverage rather than a book pitch, though the book is how I found it.
+Thirty states now guarantee a personal finance course. Every one of those mandates lands in high school. Money habits are largely set by seven — so the policy arrives roughly ten years after the cement dries, and the funding, the training and the reporting all follow the mandate rather than the evidence.
+Underneath that sits an assumption nobody argues with: that children should learn saving first. I think it is backwards. Saving is the second thing a person does with money. The first is spending, and a first grader has done that, at a register, with a parent standing behind her. The behaviors a high school course tries to correct were installed a decade earlier by an arcade, a toy aisle and a checkout lane, none of which waited for a curriculum.
+I wrote the elementary piece rather than an op-ed about it. A 36-page picture book following one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, and living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Free ungated classroom set behind it, crosswalked to five frameworks. Catalogued Lexile AD 620L — Adult Directed, so it is a read-with, and the caregiver conversation happens inside the reading.
+The story I would pitch your desk: the whole country legislated financial literacy into ninth grade, and the elementary standards that already exist in most states sit there with nothing built against them, because nobody has to report on them.
+Does that belong to anyone on your team? clarencegetsabargain.com/book-facts.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M39" s="5" t="inlineStr"/>
       <c r="N39" s="5" t="inlineStr"/>
     </row>
@@ -2799,8 +3080,23 @@
           <t>Stacy — you cover consumer finance. I wrote the origin story: a six-year-old's first transaction, including the moment sales tax appears and ruins the arithmetic he'd already done in his head. It's a picture book, which may or may not help my case. Angle here, or a better name at the Times? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K40" s="5" t="inlineStr"/>
-      <c r="L40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>Stacy — you write about what happens to ordinary people inside financial systems. There is a version of that beat with no coverage at all, and it starts at about age six.
+A child becomes a consumer the first time they hand money to a cashier. Not at eighteen, not at a first paycheck — at six, with a birthday five. From that moment they are party to a transaction and they have rights nobody mentions: the receipt is proof, the price on the shelf has to match the price at the register, a broken thing can go back. Consumer education is the missing wing of children's financial literacy. We teach them to save and never tell them they are already the buyer.
+That is why I wrote the book. Clarence Gets a Bargain follows one purchase the entire way — a boy wants a robot, earns it, reads the sale inserts at the kitchen table, compares two on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced, and a twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
+The detail people ask me about: the mother photographs the receipt the second she sits down in the car. Every time. It takes four seconds and it is what makes a return, an exchange or a warranty claim winnable. Almost nobody teaches a child that.
+Format: Lexile AD 620L — Adult Directed, the trade's code for read-with rather than read-alone.
+I am an attorney, so I will say the honest version: the full picture crosses agencies, warranties and returns sit with the FTC, product safety with the CPSC. Nobody owns "children as consumers," which may be why nobody covers it.
+Is there a story in that? clarencegetsabargain.com/press-kit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M40" s="5" t="inlineStr"/>
       <c r="N40" s="5" t="inlineStr"/>
     </row>
@@ -2845,8 +3141,24 @@
           <t>Susan — you've directed a center for economic education for years. My K-5 book argues the elementary band is underserved because everything gets built for high school. Aligned to CEE and four others. Does that match what you see? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr"/>
-      <c r="L41" s="5" t="inlineStr"/>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>Susan — you built a center from nothing and have spent years getting economics into elementary classrooms, which makes you exactly the person to tell me whether I am filling a gap or inventing one.
+The gap as I see it: elementary standards exist in most states and almost nothing is built against them, because nobody has to report on them. Every mandate lands in high school. Thirty states now.
+And underneath that, a sequencing assumption nobody argues with — that children should learn saving first. Saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has stood at a register and chosen.
+So I wrote the K–5 piece. Clarence Gets a Bargain follows one purchase from the idea to after the receipt: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, so vocabulary review points a child back into the story instead of away from it.
+The teacher side is free and ungated — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE, and FDIC Money Smart. No account, no email capture. It prints from a browser.
+Catalogued Lexile AD 620L — Adult Directed — so it runs as a one-period read-aloud and a teacher with no finance background can deliver it cold.
+Does the spending-first sequence match what you see in classrooms, or is there a reason the field starts where it starts?
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M41" s="5" t="inlineStr"/>
       <c r="N41" s="5" t="inlineStr"/>
     </row>
@@ -2891,8 +3203,23 @@
           <t>Veronica — you write about money across a whole life. This is hour one. Six-year-old runs his first purchase, ad to register. The parent hook: his mother photographs every receipt before she pulls out of the parking space. That's in the book because it's a real habit, and it's the one detail adults tell me they recognized. The format is part of the story: Lexile AD 620L — AD is Adult Directed, the industry's own code for read-WITH. An adult reads, a kid interrupts, and somebody has to answer "do we have one of those?" out loud. Same whether the adult is a teacher, a parent, or a grandparent. Press kit: https://clarencegetsabargain.com/press-kit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K42" s="5" t="inlineStr"/>
-      <c r="L42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>Veronica — you cover how families hold on to money across generations, which is why I am writing about the earliest possible end of that.
+The money conversation in most families starts far too late to be a conversation. By the time a parent sits a teenager down, the habits are set — they were set at six, in a store, with a parent saying no and no explanation attached to the no.
+Every children's book on the shelf teaches saving. Piggy banks, jars, patience. But saving is the second thing a child does with money; the first is spending, and a six-year-old has already done it.
+Clarence Gets a Bargain follows one purchase the whole way — earning the reward through chores and grades, working the sale ads at the kitchen table, comparing two models on a shelf, taking the cheaper one on purpose, handing over a coupon, meeting sales tax, and then living with what was bought. Idea to post-receipt. And on page 6 there is something I have not found in any other picture book: a 529 plan. In the plot. Explained by a mom, eye-rolled at by a kid, and defended by a dad two scenes later.
+Sixteen-plus concepts and nobody says "budget." A twenty-one-term glossary in the back, page-referenced to the story. Catalogued Lexile AD 620L — Adult Directed — so it is a read-with, and the conversation happens during the reading rather than after it.
+The angle for your beat: advisors spend fortunes trying to meet the next generation before the assets move. This is what meeting them at seven looks like, and it costs $19.99.
+Worth a column, or am I describing something you have already covered? clarencegetsabargain.com/press-kit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M42" s="5" t="inlineStr"/>
       <c r="N42" s="5" t="inlineStr"/>
     </row>
@@ -2937,8 +3264,25 @@
           <t>Dr. Taylor — Montgomery County sets what reaches a lot of classrooms. Mine is a K-5 picture book with a free zero-prep lesson set, five frameworks, nothing consumable to reorder next August. The honest question is placement rather than merit: classroom, library, or family night? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K43" s="5" t="inlineStr"/>
-      <c r="L43" s="5" t="inlineStr"/>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Taylor — I am a Maryland attorney and children's book author writing about the elementary end of financial literacy, which is the end nobody funds.
+Maryland's requirement, like every state's, lands in high school. The elementary standards sit underneath it with almost nothing built against them, because no one has to report on that band. Meanwhile the habits a high school course is trying to correct were installed at six, in a store, with a parent saying no and no reasoning attached.
+The field's answer is to teach children saving first. Saving is the second thing a person does with money. The first is spending, and a first grader has done it — at a register, with a parent standing right there.
+I wrote the K–5 piece. A 36-page picture book following one purchase from the idea through the receipt: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken on purpose, a coupon at the register, sales tax, and living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced back into the story.
+What matters for a district is that all of it is free. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, and a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart. No account, no email capture, no purchase order. It prints from a browser, so adoption costs a building nothing. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud a teacher can run with no finance background.
+I am local and would happily walk a curriculum team through it, or a single school if that is the right size to start.
+Who in MCPS owns elementary financial literacy, if anyone does?
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan Bach
+Attorney and children's book author, Baltimore</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M43" s="5" t="inlineStr"/>
       <c r="N43" s="5" t="inlineStr"/>
     </row>
@@ -2983,8 +3327,24 @@
           <t>Beth — a research question. My K-5 book argues spending competence precedes saving competence developmentally, which would mean the field teaches the wrong skill first. Does that square with your research and impact work, or am I overstating a tidy story? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K44" s="5" t="inlineStr"/>
-      <c r="L44" s="5" t="inlineStr"/>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>Beth — a research question rather than a pitch, and the book is only the reason I ran into it.
+Financial capability gets measured, sensibly, on saving, compounding and risk. Those are the right things to measure in adults. But each of them sits downstream of a decision made years earlier that nobody scores: a child standing in front of two prices, picking one. Spending is the first financial behavior a person performs, and it is taught last or not at all.
+The environment is not waiting for the curriculum. Children are transacting constantly — arcades, app stores, checkout lanes — and none of it gets counted as financial education, though it plainly is.
+I wrote the elementary piece. A 36-page picture book following one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, and living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced back into the story. Free ungated classroom set behind it, crosswalked to five frameworks.
+Design note that may matter to your work: the book is catalogued Lexile AD 620L — Adult Directed. The intervention is an adult and a child reading together, not a child reading alone, which makes it closer to a shared-reading study than a curriculum study.
+The question: does the evidence base start at adolescence the way the books do? If spending competence at seven predicts nothing at twenty-seven, that is worth knowing and I would rather hear it than keep arguing.
+clarencegetsabargain.com/book-facts.html
+Jonathan Bach
+Attorney and children's book author, Baltimore</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M44" s="5" t="inlineStr"/>
       <c r="N44" s="5" t="inlineStr"/>
     </row>
@@ -3029,8 +3389,23 @@
           <t>Sam — twenty-plus years and a quarter million kids means you've seen every approach in this space. Sammy teaches saving beautifully. I went the other way on the theory that spending is what a six-year-old does first. Real gap, or a convenient story I tell myself? You'd know. One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K45" s="5" t="inlineStr"/>
-      <c r="L45" s="5" t="inlineStr"/>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>Sam — you have been reading, singing and performing a savings habit into elementary classrooms for two decades across thirty states, which is more direct contact with this audience than anyone else in the category has. So I want to put an argument in front of you and hear where it is wrong.
+Sammy teaches saving, and teaches it better than anything else aimed at this age. My argument is not about quality; it is about order. Saving is the second thing a child does with money. The first is spending — a first grader has stood at a register holding money and chosen, years before she has anything to save. Teach that moment first, and everything Sammy preaches lands harder, because a kid who understands what money buys has a reason to keep some.
+That is the book I wrote. Clarence Gets a Bargain follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the scene each term came from.
+Catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, with every concept explained inside the text, so somebody can read it cold to a class. You will recognise why that mattered to me.
+You also solved a distribution problem the rest of us have not: banks and credit unions sponsor the visits and buy the books, and their community reports write themselves. I would genuinely rather learn that from you than reverse-engineer it.
+Trade copies and compare notes? I will read Sammy properly and tell you the truth about it, which is the only thing worth trading.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M45" s="5" t="inlineStr"/>
       <c r="N45" s="5" t="inlineStr"/>
     </row>
@@ -3075,8 +3450,23 @@
           <t>Vince — NFEC reaches thousands of instructors, and K-5 is where most of them have the least to hand anyone. Mine runs 36 pages plus free classroom materials against five frameworks, crosswalk included. Route into the NFEC resource network? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K46" s="5" t="inlineStr"/>
-      <c r="L46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>Vince — you have thousands of instructors in the field, which means you know better than almost anyone what they walk into a room without. I built the elementary thing they do not have.
+Most financial education material aimed at children starts with saving. Saving is the second thing a child does with money. The first is spending — and a first grader has done it, at a register, with a parent behind her. An instructor standing in front of a second-grade class has almost nothing to hand them about that moment.
+Clarence Gets a Bargain is a 36-page picture book that follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one deliberately, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget."
+Why it works for an instructor rather than a teacher: it is catalogued Lexile AD 620L — Adult Directed — it runs about twenty minutes out loud, and the mother explains every concept inside the text. Somebody can read it cold to a class and field questions straight off the page. Nothing to memorise, no training call beforehand. Behind it sits a free ungated set — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, and a browser-based pretend register with a markdown, a coupon and sales tax.
+The twenty-one-term glossary in the back is page-referenced to the story, so an instructor can answer a vocabulary question by turning to the scene rather than reciting a definition.
+Does your instructor network want elementary material, or is the demand really all adult and teen? Everything is free either way.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M46" s="5" t="inlineStr"/>
       <c r="N46" s="5" t="inlineStr"/>
     </row>
@@ -3121,8 +3511,23 @@
           <t>Billy — a NEFE-shaped question. The research keeps saying money attitudes form by seven, and almost every dollar of material lands at 9-12. I wrote a K-5 picture book teaching spending rather than saving. Does NEFE ever point people to elementary, or is that band still nobody's mandate? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. Teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K47" s="5" t="inlineStr"/>
-      <c r="L47" s="5" t="inlineStr"/>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>Billy — a question about where NEFE draws the line on grade band, asked by someone who has just spent a year building for the band nobody funds.
+Thirty states now require personal finance to graduate. The mandates land in high school, and the funding, the training and the reporting follow the mandate. Meanwhile the K–5 standards that already exist in most states sit there with almost nothing built against them, because nobody has to report on them.
+The assumption underneath is that children should learn saving first. I think it is backwards, and I would rather be told so by NEFE than keep saying it at conferences. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent standing behind her. The behaviors a high school course is trying to correct were installed a decade earlier.
+I wrote the elementary piece rather than an argument about it: a 36-page picture book that follows one purchase from the idea to after the receipt, plus a free ungated classroom set crosswalked to the 2021 National Standards, Common Core, CEE and FDIC Money Smart. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Catalogued Lexile AD 620L — Adult Directed — so the intervention is a shared read rather than solo reading, which also makes it easier to study than a curriculum.
+The question: does NEFE's research or advocacy work have a position on the elementary band, or is the practical view that high school is where the effort pays? If it is the second, I would like to know I am arguing with a considered consensus rather than filling a gap it agrees exists.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan Bach
+Attorney and children's book author, Baltimore</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="inlineStr"/>
     </row>
@@ -3167,8 +3572,23 @@
           <t>Laura — a Clearinghouse question rather than a pitch. My K-5 teacher pack is built against the National Standards, free, ungated, no email capture and no drip campaign. Is Suzann Knight the right first stop, or is there a step I'm skipping? Wally Luckeydoo endorsed the book, which I mention only because he's your 2026 Corey Carlisle recipient. Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. Teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K48" s="5" t="inlineStr"/>
-      <c r="L48" s="5" t="inlineStr"/>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>Laura — a question about scope rather than a pitch, and I have already read the Clearinghouse criteria closely enough to know which route applies to me.
+Jump$tart's standards cover K–12, but the material built against them thins out badly below grade six. The elementary band has standards and very little aimed at it, largely because nothing requires anyone to report on that band. Every state mandate lands in high school. Thirty of them now.
+There is also a sequencing assumption underneath the whole field that I would like your view on. Financial education starts children with saving. Saving is the second thing a person does with money; the first is spending. A first grader has no savings rate. She has stood at a register holding money and had to choose.
+I built a free, ungated K–5 classroom set around a 36-page picture book: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE and FDIC Money Smart, printable classroom pieces, and a browser-based pretend register. No account, no email capture, no purchase order. It prints from a browser.
+The book follows one complete purchase — sale ads, comparison, a markdown, a coupon, sales tax — with sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story. Catalogued Lexile AD 620L, Adult Directed, so it runs as a one-period read-aloud with no teacher training required.
+Two questions. Does Jump$tart consider elementary in scope, or is it a band the coalition has consciously left to others? And for the Clearinghouse, is the free classroom set the right thing to submit rather than the book?
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M48" s="5" t="inlineStr"/>
       <c r="N48" s="5" t="inlineStr"/>
     </row>
@@ -3213,8 +3633,24 @@
           <t>Prince — real respect for the Wesley Learns books; you got kids to investing without it feeling like homework. Mine sits one rung below. Before a kid invests, he has to survive a store. Ad, aisle, comparison, coupon, register. Complementary rather than competitive, I think. Trade copies? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K49" s="5" t="inlineStr"/>
-      <c r="L49" s="5" t="inlineStr"/>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>Prince — you took investing, which is the hardest concept in this category to make readable for children, and made it a series a kid comes back to. I went the opposite direction on the same shelf and I would like your read on it.
+Wesley learns to invest. Clarence learns to spend — and I mean the mechanics of it rather than the idea. Every other book in the category teaches saving, which is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. Nobody had written that one, so I did.
+Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Nobody says the word "budget."
+The craft problem I would most like another author's view on: the reader is not supposed to know he has been taught anything until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. Getting that balance right, so it stays a story, was the whole job, and it is the thing most likely to be off by a hair.
+I did the illustrations too, which means my opinion of them is worth nothing.
+Catalogued Lexile AD 620L — Adult Directed — written for the adult voice in the room, with the mother carrying every explanation.
+Trade? Send me a Wesley and I will read it properly rather than politely.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M49" s="5" t="inlineStr"/>
       <c r="N49" s="5" t="inlineStr"/>
     </row>
@@ -3259,8 +3695,23 @@
           <t>Kate — you cover taxes, so here's a sentence you may enjoy. My children's picture book teaches sales tax. Six-year-old hits the register, the total's higher than the sticker, and his mom explains where the difference goes. I cannot find another kids' book that does it. Story, or just a peculiar thing to have written? The format is part of the story: Lexile AD 620L — AD is Adult Directed, the industry's own code for read-WITH. An adult reads, a kid interrupts, and somebody has to answer "do we have one of those?" out loud. Same whether the adult is a teacher, a parent, or a grandparent. Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K50" s="5" t="inlineStr"/>
-      <c r="L50" s="5" t="inlineStr"/>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>Kate — a pitch about a gap rather than a book, though I wrote the book because of the gap.
+Everything in kids' financial literacy points at a horizon no child can see: compound interest, credit scores, retirement. All real, all decades out. Meanwhile the kid is eight, holding $20 of birthday money, standing in a store that spent millions working out how to get it. We are preparing children for 65 and sending them to the register unarmed today.
+So flip the order. Saving is the second thing a child does with money. The first is spending, and it is the one nobody puts in a story.
+Clarence Gets a Bargain does. One kid, one purchase, followed the whole distance — he wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget." The reader works out he has been schooled at the glossary — twenty-one terms in the back, each one page-referenced to the scene it came from.
+Catalogued Lexile AD 620L. The AD is Adult Directed, the industry's own code for a book meant to be read with a child rather than handed over, so a parent who does not feel qualified on money still gets handed the script.
+Timely hook if you need one: thirty states now guarantee a personal finance course, all of it in high school, roughly ten years after the habits form. The elementary standards already exist in most states and have almost nothing built against them.
+Any of that useful to you? clarencegetsabargain.com/book-facts.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M50" s="5" t="inlineStr"/>
       <c r="N50" s="5" t="inlineStr"/>
     </row>
@@ -9224,8 +9675,24 @@
           <t>Professor Urban — your work on financial education mandates is the best evidence we have on what actually moves outcomes, and nearly all of it sits at high school. I wrote a K-5 book on the premise that elementary is both untested and undersupplied. Is there research I should know before I keep saying that? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K204" s="5" t="inlineStr"/>
-      <c r="L204" s="5" t="inlineStr"/>
+      <c r="K204" s="5" t="inlineStr">
+        <is>
+          <t>Professor Urban — you produced the evidence base that mandates actually work, which is why I want to ask about the grade band your evidence does not reach.
+Every mandate you have evaluated lands in high school. Thirty states now. The effects are real and I am not arguing with them. My question is about what is happening a decade earlier, because money habits are largely set by seven and the policy arrives roughly ten years after the cement dries.
+Underneath the whole field sits a sequencing assumption nobody tests: that children should learn saving first. I think it is backwards. Saving is the second thing a person does with money. The first is spending — standing in front of two prices and picking one. A first grader has done that. She has no savings rate at all.
+I could not find the children's book for it, so I wrote one. Clarence Gets a Bargain follows a single purchase the entire way: earning the reward, reading the sale ads, comparing two models on a shelf, choosing the cheaper one deliberately, redeeming a coupon, meeting sales tax, and then living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story.
+One design feature that may matter for measurement: the book is catalogued Lexile AD 620L — Adult Directed — so the intervention is not a child reading alone but an adult and a child reading together, with the adult prompted by the text. If shared reading is doing the work rather than the book, that is testable, and it would be a more interesting finding than anything about my book.
+The real question: does anything in the literature speak to elementary spending competence, or is that band simply unstudied? Either answer is useful to me.
+clarencegetsabargain.com/book-facts.html
+Jonathan Bach
+Attorney and children's book author, Baltimore</t>
+        </is>
+      </c>
+      <c r="L204" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M204" s="5" t="inlineStr"/>
       <c r="N204" s="5" t="inlineStr"/>
     </row>
@@ -9270,8 +9737,23 @@
           <t>Iris — you're at UW-Madison, which is where the Center for Financial Security picked the titles for the CFPB's Money as You Grow Bookshelf. Mine is K-5 and goes at spending instead of saving. Do you know who evaluates additions to that shelf? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K205" s="5" t="inlineStr"/>
-      <c r="L205" s="5" t="inlineStr"/>
+      <c r="K205" s="5" t="inlineStr">
+        <is>
+          <t>Iris — you were part of the group that chose the titles on the Money as You Grow Bookshelf, so you have read this category more carefully than almost anyone, and you will know immediately whether my premise is wrong.
+The shelf, as it stands, leans toward saving and earning. What is thin is spending, and specifically the transaction — the part where a child stands in front of two prices and has to pick one. That is the first financial act a person performs. It gets taught last.
+Clarence Gets a Bargain covers exactly that, and covers the whole of it: a boy wants a robot, earns it through chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list looking for another one that does the whole arc. They are all parked on the earning-and-saving side of the register.
+Sixteen-plus concepts and none is announced — no character pauses to define a term, nobody says the word "budget." The proof and the reveal are both in the back matter: a reader does not know he has been schooled until he reaches the glossary. Twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than an appendix.
+Ages 6–10, inside the Bookshelf's 4–10 band. Catalogued Lexile AD 620L — Adult Directed, which is how the Bookshelf's titles are meant to be used anyway.
+Two questions. Was the saving weighting deliberate, or just what existed? And is the selection process still running?
+clarencegetsabargain.com/book-facts.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L205" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M205" s="5" t="inlineStr"/>
       <c r="N205" s="5" t="inlineStr"/>
     </row>
@@ -9324,12 +9806,21 @@
 You are welcome to tell me this is sentimental and that price comparison at seven predicts nothing. That's a real answer and I'd rather have it than silence. But if you think there's something in it, a sentence from an economist who has actually studied consumer financial markets does more for this than a hundred nice reviews from parents.
 The flipbook takes four minutes: https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan Bach
-Baltimore</t>
+Baltimore
+----- Whales long-form version -----
+Professor Mahoney — your work is about what consumers actually do when a price is put in front of them, as opposed to what a model says they should. I want to ask about the earliest version of that decision, because nobody seems to study it.
+A six-year-old with a birthday five in an aisle is running a comparison with no price history, no reference class and no idea that anchoring exists. She is the purest case your field could ask for and the least documented. Meanwhile the environment is not naive at all — a boardwalk claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the child has no way of knowing the $9.99 exists.
+Financial education answers this by teaching saving. But saving is the second thing a person does with money; the first is spending, and it is taught last or not at all.
+I wrote the picture book rather than the paper. Clarence Gets a Bargain follows one complete purchase — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with the choice afterward. Sixteen-plus concepts, none announced. Twenty-one terms in a back-matter glossary, each page-referenced to the scene it came from. Catalogued Lexile AD 620L — Adult Directed — so the reading is a joint activity by design rather than a solo one.
+The question I would genuinely like answered: is there work on when price competence forms, and whether early exposure to comparison changes anything measurable later? If the honest answer is that it is unstudied because it is unmeasurable at that age, that is worth knowing too.
+clarencegetsabargain.com/book-facts.html
+Jonathan Bach
+Attorney and children's book author, Baltimore</t>
         </is>
       </c>
       <c r="L206" s="5" t="inlineStr">
         <is>
-          <t>Subject: Applied micro, twenty years early · Long-form version from Jump$tart</t>
+          <t>Subject: Applied micro, twenty years early · Long-form version from Jump$tart | Subject: Applied micro, twenty years early · Long-form version from Whales long-form</t>
         </is>
       </c>
       <c r="M206" s="5" t="inlineStr"/>
@@ -9376,8 +9867,24 @@
           <t>Bina — community engagement at the SF Fed is where household financial capability actually gets measured. Mine teaches the spending half, on the theory the sequence is backwards. Does that square with what you see? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K207" s="5" t="inlineStr"/>
-      <c r="L207" s="5" t="inlineStr"/>
+      <c r="K207" s="5" t="inlineStr">
+        <is>
+          <t>Bina — a question about where community development work draws its lower age bound.
+Most financial capability programming aimed at low- and moderate-income families reaches adults, or reaches children through savings vehicles — child savings accounts, matched savings, college accounts. All of that is aimed at accumulation. Very little addresses the other side of the household ledger at a child's level: what happens when the money is spent, which for a child is nearly all of it.
+That gap has a sequencing problem behind it. Saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has handled money at a register, and the decision she made there was unassisted.
+I built the elementary resource. A 36-page picture book that follows one complete purchase — sale ads, comparison shopping, a markdown, a coupon, sales tax, and living with what was bought — with sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story. Behind it, a free ungated classroom and family set crosswalked to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE and FDIC Money Smart. No account, no email capture, no purchase order; it prints from a browser, which matters where budgets do not exist.
+Catalogued Lexile AD 620L — Adult Directed — so it works as a shared read with a caregiver who does not need to know the material first, which is the design constraint that mattered most to me.
+The question: does SF Fed's community engagement work touch the elementary band, or does it start at the account level with adults?
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan Bach
+Attorney and children's book author, Baltimore</t>
+        </is>
+      </c>
+      <c r="L207" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M207" s="5" t="inlineStr"/>
       <c r="N207" s="5" t="inlineStr"/>
     </row>
@@ -16806,8 +17313,23 @@
           <t>Jennifer — Harlem Children's Zone is deliberate about what earns a kid's time. Mine teaches the complete purchase, sales tax included, and the family activity was built for a kitchen table rather than a classroom. Fit your programming, or your development conversations? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K402" s="5" t="inlineStr"/>
-      <c r="L402" s="5" t="inlineStr"/>
+      <c r="K402" s="5" t="inlineStr">
+        <is>
+          <t>Jennifer — a funding-shaped question rather than an ask, and the resource itself is already free.
+I wrote and illustrated a K–5 financial-literacy picture book and built the entire classroom program behind it — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a standards crosswalk across five frameworks. All of it is ungated: no account, no email capture, no purchase order, prints from a browser. The only thing that ever costs anything is the physical books, and 25 copies run $499.75.
+The content premise: every children's money book teaches saving, and saving is the second thing a child does with money. The first is spending — a first grader has stood at a register and chosen. The book follows one complete purchase from the idea through the receipt, with sixteen-plus concepts hidden in the plot and a twenty-one-term glossary page-referenced back into the story.
+Why I am writing to development rather than to a classroom: this is unusually easy to fund. A bank or credit union sponsoring a classroom set gets its name on every book that goes home to a family in its assessment area, the curriculum costs the sponsor nothing because it is already free, and I have a CRA-ready memo written in examiner-friendly language. A funder can point at 25 books, one classroom, and a pre/post instrument.
+Catalogued Lexile AD 620L — Adult Directed — which also makes it a family-engagement asset rather than only a classroom one, since the book works at a kitchen table with a parent or a grandparent doing the reading.
+Is a sponsored classroom set something HCZ's funders would recognise, or does everything need to attach to an existing program line?
+clarencegetsabargain.com/resources/grant-in-a-box.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L402" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M402" s="5" t="inlineStr"/>
       <c r="N402" s="5" t="inlineStr"/>
     </row>
@@ -16852,8 +17374,23 @@
           <t>Flora — JA reaches more kids than almost anybody, and elementary is usually where the material thins out. Mine is a K-5 picture book with a free zero-prep classroom pack against five frameworks, teaching spending rather than saving. Fit anything JA Alaska runs? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K403" s="5" t="inlineStr"/>
-      <c r="L403" s="5" t="inlineStr"/>
+      <c r="K403" s="5" t="inlineStr">
+        <is>
+          <t>Flora — JA runs volunteers into elementary classrooms better than any organisation in the country, so this is a materials question rather than a pitch.
+JA's elementary programs are strong on earning, jobs and community. What is thin across the whole field — not just JA — is spending, and specifically the transaction itself. A first grader has no savings rate and no job. What she has done is stand at a register holding money and choose.
+Clarence Gets a Bargain is a 36-page picture book that puts the entire transaction on the page: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
+The part that matters for a volunteer model: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, with every concept explained inside the text by the mother. A volunteer who has never taught anything can read it cold and answer questions off the page. Nothing to memorise and no prep call. Behind it, free and ungated: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable price tags and clearance stickers for a classroom store, and a browser-based pretend register with a markdown, a coupon and sales tax.
+Alaska has its own complications on distance and travel, and virtual read-alouds work for this.
+Does a read-aloud fit how JA Alaska builds a volunteer session, or does everything have to run through national curriculum?
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L403" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M403" s="5" t="inlineStr"/>
       <c r="N403" s="5" t="inlineStr"/>
     </row>
@@ -16898,8 +17435,24 @@
           <t>Elizabeth — financial education at the Department of Education is the mission my book starts on, just twelve years early. Mine is K-5, teaching spending rather than saving, against five frameworks. Fit any program you touch, or a steer on who'd know? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K404" s="5" t="inlineStr"/>
-      <c r="L404" s="5" t="inlineStr"/>
+      <c r="K404" s="5" t="inlineStr">
+        <is>
+          <t>Elizabeth — a scope question rather than a pitch.
+Federal attention to financial education, like every state mandate, concentrates on high school. Thirty states now require a course to graduate. The elementary standards that exist in most states sit underneath that with very little built against them, largely because nothing requires reporting at that band.
+The assumption underneath is that children begin with saving. Saving is the second thing a person does with money. The first is spending — a first grader has handled money at a register and made a decision there with no framework at all.
+I built a free, ungated K–5 resource for that: a 36-page picture book that follows one complete purchase from the idea through the receipt — sale ads, comparison shopping, a markdown, a coupon, sales tax — and a classroom set behind it. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a browser-based pretend register, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education alongside Common Core Math and ELA, CEE and FDIC Money Smart, cited at the Grade 4 benchmark level rather than claimed generally.
+No account, no email capture, no purchase order. It prints from a browser. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud requiring no instructor training.
+The question: does any Department program or clearinghouse take elementary financial-education material, or is the practical route through the states? A steer on who would know is as useful to me as an answer.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan Bach
+Attorney and children's book author, Baltimore</t>
+        </is>
+      </c>
+      <c r="L404" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M404" s="5" t="inlineStr"/>
       <c r="N404" s="5" t="inlineStr"/>
     </row>
@@ -16944,8 +17497,24 @@
           <t>Gene — Troutwood makes the financial future tangible for young people. Mine makes the present tangible for a six-year-old: one purchase, compared and paid for, tax included. Does the approach fit what you're building, or sit below it? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K405" s="5" t="inlineStr"/>
-      <c r="L405" s="5" t="inlineStr"/>
+      <c r="K405" s="5" t="inlineStr">
+        <is>
+          <t>Gene — Troutwood is built on showing people the long arc of a decision, which is why I am writing about the very first decision on that arc.
+Everything in financial planning compounds, including the mistakes, and the compounding starts long before anyone opens an account. Mistakes at eleven cost $14. The same mistake at twenty-seven has a credit card attached. The habit doing the compounding was installed at six, in a store, with a parent saying no and no reasoning attached to the no.
+Financial education answers that by teaching children saving. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with no framework at all.
+Clarence Gets a Bargain is the picture book for that. One purchase, followed the whole way: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
+Catalogued Lexile AD 620L — Adult Directed — so it is a shared read, and the parent gets handed the script rather than a homework assignment.
+The claim I would defend hardest is the delayed one, and it is the same claim Troutwood makes about projections: the value is not in the twenty minutes. It is in month eighteen, in a real store, when the kid hits a money moment and the book fires back. Recognition first, then the habit.
+Does the elementary end fit anything Troutwood does, or is that below the floor?
+clarencegetsabargain.com/book-facts.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L405" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M405" s="5" t="inlineStr"/>
       <c r="N405" s="5" t="inlineStr"/>
     </row>
@@ -16990,8 +17559,23 @@
           <t>Rob — you create financial education resources, so you know what teachers actually use versus what they politely download once. Mine is a K-5 picture book with four zero-prep lessons, assessments, and a 23-row crosswalk, all free and ungated. Fit your catalog, or duplicate it? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K406" s="5" t="inlineStr"/>
-      <c r="L406" s="5" t="inlineStr"/>
+      <c r="K406" s="5" t="inlineStr">
+        <is>
+          <t>Rob — you build resources teachers actually use, which is a harder job than writing curriculum and a rarer one. I built the elementary thing that does not exist, and I want a practitioner's read on whether it survives a real classroom.
+The gap: every mandate lands in high school, so that is where every resource goes. The elementary standards exist and almost nothing is built against them. And the field starts children with saving, when saving is the second thing a person does with money — the first is spending, and a first grader has already done it at a register.
+Clarence Gets a Bargain is a 36-page picture book following one complete purchase: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken on purpose, a coupon at the register, sales tax, and living with what was bought. Sixteen-plus concepts, none announced. Kids smell a worksheet one page in; they never smell this one. A twenty-one-term glossary in the back, page-referenced to the story.
+The teacher side is where I would want your opinion. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row standards crosswalk, printable price tags and clearance stickers for a classroom store, and a browser-based register that runs a markdown, a coupon and sales tax with the total changing in front of the class. Ungated — no account, no email capture — and it prints from a browser. Catalogued Lexile AD 620L, Adult Directed: one class period, no teacher training, and the text carries every explanation.
+The whole thing rests on one instruction a teacher can act on the same week: stop bringing kids to the store as cargo, bring them as staff. Every activity in the set is a version of that.
+The honest question: what makes a free teacher resource actually get used rather than downloaded and forgotten? You have watched that happen more times than I have, and I would rather fix it now.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L406" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M406" s="5" t="inlineStr"/>
       <c r="N406" s="5" t="inlineStr"/>
     </row>
@@ -21406,8 +21990,24 @@
           <t>Martin — Chair-Elect of the CFP Board means a kids' picture book is a long way upstream of your day. That's rather the point. Spending is the first money skill a kid uses, nobody wrote the picture book for it, so I did. Five frameworks, K-5. Does it fit the early-education push the field keeps talking about, or is that talk? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K522" s="5" t="inlineStr"/>
-      <c r="L522" s="5" t="inlineStr"/>
+      <c r="K522" s="5" t="inlineStr">
+        <is>
+          <t>Martin — you sit where the profession decides what it is responsible for, so this is a question about the far upstream end of that responsibility.
+Planners meet clients' children late, usually at the worst possible moment, and by then the habits are twenty years old. They were formed at six, in a store, with a parent saying no and no reasoning attached to the no.
+The field's answer to that is to teach children saving. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, holding a birthday five, deciding whether the thing is worth what it costs.
+I wrote the picture book for that moment. Clarence Gets a Bargain follows one purchase the whole way — earning the reward through chores and grades, working the sale ads at the kitchen table, comparing two models on a shelf, taking the cheaper one on purpose, redeeming a coupon, meeting sales tax, and then living with what was bought. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in a back-matter glossary, page-referenced to the story.
+And on page 6 there is something I have not found in any other picture book: a 529 plan. In the plot. Explained by a mother, eye-rolled at by a kid, defended by a father two scenes later.
+Catalogued Lexile AD 620L — Adult Directed, so a planner handing it to a client family is handing over a script rather than an assignment. Twenty-five copies run $499.75, and the educator program behind it is free.
+The question: does CFP Board's pro bono and public-education work reach below high school at all, or is that considered somebody else's ground?
+clarencegetsabargain.com/book-facts.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L522" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M522" s="5" t="inlineStr"/>
       <c r="N522" s="5" t="inlineStr"/>
     </row>
@@ -21452,8 +22052,23 @@
           <t>Ed — a director at the Department of Education is exactly who I want on this. Mine is K-5, teaching spending rather than saving, with free standards-aligned lessons and nothing to reorder. Fit any program you touch, or a steer on who'd know? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K523" s="5" t="inlineStr"/>
-      <c r="L523" s="5" t="inlineStr"/>
+      <c r="K523" s="5" t="inlineStr">
+        <is>
+          <t>Ed — a narrow question about evidence standards, asked before I go further with something.
+I have built a free K–5 financial-education resource — a 36-page picture book plus a complete classroom set — and crosswalked it to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE and FDIC Money Smart, at the Grade 4 benchmark level. Everything is ungated: no account, no email capture, no purchase order, and it prints from a browser.
+The content premise is that the field has the sequence backwards. Financial education starts children with saving; saving is the second thing a person does with money. The first is spending, and a first grader has already done it at a register. The book follows one complete purchase from the idea through the receipt — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with what was bought.
+One structural detail relevant to evaluation: the book is catalogued Lexile AD 620L — Adult Directed — so it is delivered as a shared read between an adult and a child rather than independent reading. That makes it closer to a shared-reading intervention than a curriculum, which may change what kind of evidence would be appropriate.
+The question: what would a resource like this need in order to be taken seriously on evidence — a pre/post instrument administered at scale, a quasi-experimental design, something else? I would rather build the right study once than assemble the wrong one. And if the honest answer is that no federal pathway exists for elementary material of this kind, that is worth knowing too.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan Bach
+Attorney and children's book author, Baltimore</t>
+        </is>
+      </c>
+      <c r="L523" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M523" s="5" t="inlineStr"/>
       <c r="N523" s="5" t="inlineStr"/>
     </row>
@@ -21498,8 +22113,24 @@
           <t>Jeff — you lead consumer and community research at the Fed, so you study exactly the gaps my book tries to prevent. Mine argues spending competence precedes saving competence and is taught almost nowhere. Does that square with your research? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K524" s="5" t="inlineStr"/>
-      <c r="L524" s="5" t="inlineStr"/>
+      <c r="K524" s="5" t="inlineStr">
+        <is>
+          <t>Jeff — a question about scope, from someone who has read the SHED closely enough to know what it does and does not ask.
+The survey measures financial outcomes in adults — emergency savings, credit access, unexpected expenses. Those outcomes have long histories. What I have not been able to find, in the SHED or elsewhere, is any measure of when spending competence forms: the ability to stand in front of two prices and choose deliberately rather than by impulse or brand.
+That matters because financial education for children is built almost entirely around saving, and saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has handled money at a register.
+I wrote the elementary resource rather than a paper about it. A 36-page picture book that follows one complete purchase — sale ads, comparison shopping, a markdown, a coupon, sales tax, and living with what was bought — plus a free ungated classroom set crosswalked to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE, and FDIC Money Smart. Sixteen-plus concepts, none announced in the text. A twenty-one-term glossary page-referenced into the story.
+For the record on format: Lexile AD 620L, Adult Directed — an adult reads it with the child rather than handing it over.
+The question is narrow. Is there any Federal Reserve work, published or internal, on childhood price competence and later financial outcomes? If it does not exist, that is an answer too, and it tells me whether I am arguing with a consensus or filling a hole.
+clarencegetsabargain.com/book-facts.html
+Jonathan Bach
+Attorney and children's book author, Baltimore</t>
+        </is>
+      </c>
+      <c r="L524" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M524" s="5" t="inlineStr"/>
       <c r="N524" s="5" t="inlineStr"/>
     </row>
@@ -21544,8 +22175,23 @@
           <t>Annie — My First Nest Egg and Clarence chase the same kid. Yours is the account; mine is the trip to the store. Spending rather than saving, one purchase, ad to register. Complementary, I think. Worth comparing notes, or trading copies? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K525" s="5" t="inlineStr"/>
-      <c r="L525" s="5" t="inlineStr"/>
+      <c r="K525" s="5" t="inlineStr">
+        <is>
+          <t>Annie — you built a product for the exact age band everyone else in this category skips, so you already believe the thing I have been arguing. I want to compare notes rather than pitch you.
+My First Nest Egg puts save, spend, give and invest in front of a young child in physical form. My argument is about which of those a child actually performs first. It is spending — a six-year-old has stood in a store holding money and chosen, years before she has anything to save or invest. The category teaches saving first anyway, and I could not find the book that teaches the other one.
+So I wrote and illustrated it. Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
+Catalogued Lexile AD 620L — Adult Directed — read-with rather than read-alone, so the parent gets handed the script. And there is a free browser-based pretend register behind it that runs a markdown, a coupon and sales tax, which is the closest thing I have to your physical product.
+Those look complementary rather than competing to me: yours gives a kid the categories in their hands, mine walks them through the mechanics of one transaction in twenty minutes.
+Worth a conversation about whether they belong near each other? And separately — if you think spending-before-saving is wrong, you are one of very few people whose disagreement would actually change my mind.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L525" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M525" s="5" t="inlineStr"/>
       <c r="N525" s="5" t="inlineStr"/>
     </row>
@@ -29263,8 +29909,23 @@
           <t>Bill — Tennessee's commission decides what reaches classrooms statewide, and elementary is usually where state mandates run thin. Mine is a K-5 picture book with a free zero-prep classroom pack against Jump$tart, CEE, Common Core, and FDIC Money Smart. Route to get it in front of the commission? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr"/>
-      <c r="L20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Bill — a question about grade band from someone who has read what states actually fund.
+Tennessee's requirement, like all thirty of them, lands in high school. That is where the money, the training and the reporting go. The elementary standards sit underneath it with almost nothing built against them, because nothing requires a district to report on that band.
+The sequencing assumption is the part I keep circling. Financial education starts children with saving. Saving is the second thing a person does with money; the first is spending, and a first grader has done it — at a register, with a parent standing right there. The behaviors a high school course tries to correct were installed a decade earlier.
+So I built the K–5 piece. A 36-page picture book that follows one purchase from the idea to after the receipt — sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken on purpose, a coupon at the register, sales tax, and living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story.
+What matters for a commission is the rest of it, and it is free: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart. Ungated, no account, prints from a browser. A district adopting it spends nothing. Catalogued Lexile AD 620L — Adult Directed — so it is a one-period read-aloud that needs no teacher training.
+Does elementary sit inside what the Commission convenes or funds, or is high school the whole remit?
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M20" s="5" t="inlineStr"/>
       <c r="N20" s="5" t="inlineStr"/>
     </row>
@@ -29309,8 +29970,22 @@
           <t>Dave — Wisconsin has been at this longer than most states. My K-5 book and free lesson set map to five frameworks. Elementary tends to be the underserved band everywhere I look. Is there a submission route, or a person who reviews outside materials? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. For teachers: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr"/>
-      <c r="L21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Dave — Wisconsin has run a state financial-literacy office longer than most states have had a requirement, so you have seen more of these come and go than almost anyone. I would like a read on one assumption.
+Every mandate in the country lands in high school. Thirty of them now. Money habits are largely set by seven, which puts the policy about a decade behind the behaviour. Underneath that sits the belief that children should learn saving first. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent right there.
+I built the K–5 piece rather than an argument about it. A 36-page picture book that follows one complete purchase: the sale ads at the kitchen table, comparison on a shelf, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced — nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
+The classroom set behind it is free and ungated: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, and a 23-row crosswalk to the 2021 National Standards, Common Core Math and ELA, CEE and FDIC Money Smart. No account, no email capture, prints from a browser. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud that a teacher without a finance background can run cold, and the same book works at a kitchen table.
+The question: in your experience, does elementary material get adopted when it is free and aligned, or does it need a mandate behind it to move at all? I would rather know now than find out slowly.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M21" s="5" t="inlineStr"/>
       <c r="N21" s="5" t="inlineStr"/>
     </row>
@@ -29416,8 +30091,22 @@
           <t>Tom — your "Everything Your Child Should Know About Money" post did 22 comments on a 3,000-follower account. In this category that's a stadium. I studied it. Mine is the picture-book version for six-year-olds: one purchase, ad to register, tax at the end. Would you tell me whether it holds, or whether I've written a very long receipt? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Tom — you got more genuine engagement out of one post about kids and money than anyone else in this category has managed, which tells me you know exactly which part of this parents actually care about. I would like to check my premise against that.
+My premise: the whole field has the sequence backwards. Financial education starts children with saving. Saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, standing in a store holding a birthday five, working out whether the thing is worth what it costs. We teach the second thing first and the first thing never.
+So I wrote and illustrated the spending book. Clarence Gets a Bargain follows one purchase the whole way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax and objects to it, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." The reader works out he has been schooled only at the glossary — twenty-one terms in the back, page-referenced to the scene each came from.
+The instruction underneath the whole book is four words long: stop bringing kids to the store as cargo, bring them as staff. Catalogued Lexile AD 620L — Adult Directed — so the parent gets handed the script rather than an assignment, which I suspect is why your posts land: parents want the conversation and do not feel qualified to start it.
+The thing I would actually value: you know what makes a parent stop scrolling on this subject and what makes them scroll past. If "spending before saving" is the wrong hook, I would rather hear it from you than keep testing it slowly.
+Would you look and tell me? https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M23" s="5" t="inlineStr"/>
       <c r="N23" s="5" t="inlineStr"/>
     </row>
@@ -29462,8 +30151,23 @@
           <t>Andrew — 20 million downloads means you've heard every money pitch ever assembled. Here's mine: I wrote the only picture book where the kid pays sales tax. Everything else stops at the piggy bank. Do I know that for certain? I checked all 25 titles on the ABA Foundation's list, so reasonably certain. Episode, or is the gap imaginary? The format is part of the story: Lexile AD 620L — AD is Adult Directed, the industry's own code for read-WITH. An adult reads, a kid interrupts, and somebody has to answer "do we have one of those?" out loud. Same whether the adult is a teacher, a parent, or a grandparent. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>Andrew — your audience is adults fixing money habits. I wrote the book that tries to stop the habits forming, and there is an episode in the argument whether or not the book is in it.
+Every children's money book teaches saving. Piggy banks, lemonade stands, three jars. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding a birthday five, working out whether the thing is worth what it costs.
+Nobody put that in a story. So I did. Clarence Gets a Bargain follows a single purchase the whole way — a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax and regards it as a personal insult, then lives with the thing he chose. Idea to post-receipt.
+Sixteen-plus concepts and none of them announced. Nobody in the book says "budget," which for a book largely about budgeting took some doing. Kids smell a worksheet one page in; they never smell this one, because they are laughing too hard to notice. The reveal is the glossary — twenty-one terms in the back, page-referenced to the scene each came from.
+Catalogued Lexile AD 620L — Adult Directed, so it is a read-with, which means the parent listening to your show gets handed the script rather than a homework assignment.
+The episode I would pitch is not the book. It is the forty-year hole: an entire publishing category taught children to save and skipped the cash register, the only place a child has ever actually handled money.
+Worth twenty minutes of your show? https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M24" s="5" t="inlineStr"/>
       <c r="N24" s="5" t="inlineStr"/>
     </row>
@@ -29508,8 +30212,22 @@
           <t>Amy — every money book on your shelf ends at the piggy bank. Mine starts at the register: sale ads, comparison, a markdown sticker, a coupon, and the sales tax nobody warns a six-year-old about. 36 pages, 21-term glossary with page refs. Would it circulate at Boston Public, or would it sit? Spec for the shelf: Lexile AD 620L — AD is Adult Directed, the trade's code for a book meant to be read WITH a child rather than handed over. Twenty minutes out loud, which makes it a storytime and a family take-home at the same time. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr"/>
-      <c r="L25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Amy — two requests come to your desk all week. A kid wants a robot book. A parent wants something that teaches money. I wrote the one that answers both in a single checkout.
+Clarence Gets a Bargain is a 36-page picture book, ages 6–10, that follows one kid through one complete purchase: he earns a robot reward with chores and grades, does his shopping homework in the newspaper sale ads, comparison-shops the aisle, finds the markdown, hands a coupon to the cashier, meets sales tax, and watches his mother photograph the receipt before the car leaves the lot. Kids read it as a robot story. Sixteen-plus money concepts come along without announcing themselves, and the back matter carries a twenty-one-term glossary where each definition points to the page where the term happens in the plot — a decoder rather than an appendix.
+The collection case, with the qualifier a librarian will appreciate: most money picture books cover earning or saving. To my knowledge this is the first narrative picture book for this age band that traces the whole consumer arc, wish through receipt. It fills a hole rather than adding a fourth piggy-bank book to the shelf.
+Cataloguing: ISBN 979-8-234-07638-0 · LCCN 2026906164 · hardbound, case bound, full colour, 11×8.5′′ · Est. Lexile AD 620L, Guided Reading L–N · $19.99. The AD is Adult Directed, which makes it a storytime title and a family take-home at the same time. Every fact is on one page: clarencegetsabargain.com/book-facts.html
+Programming is already built and free — printable price tags and clearance stickers for a pretend store, a browser-based register kids run themselves, a five-question quiz with a printable certificate. A storytime plus the pretend store is a complete Money Smart Week event with no prep budget.
+Kids re-read it without being asked, which is the only metric that matters at your desk. Review copy on request?
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M25" s="5" t="inlineStr"/>
       <c r="N25" s="5" t="inlineStr"/>
     </row>
@@ -29554,8 +30272,23 @@
           <t>Sarah — a children's librarian at NYPL sees more money books than almost anyone alive. Mine breaks the pattern by having no piggy bank in it. It teaches spending, and there's a 21-term glossary with page references in the back so it doubles as a reference title. Would it circulate? Happy to send a copy. Spec for the shelf: Lexile AD 620L — AD is Adult Directed, the trade's code for a book meant to be read WITH a child rather than handed over. Twenty minutes out loud, which makes it a storytime and a family take-home at the same time. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>Sarah — a collection-development pitch, kept to the facts because I know what August looks like at your desk.
+Clarence Gets a Bargain is a 36-page picture book, ages 6–10, following one kid through one complete purchase: earning the robot reward, doing shopping homework in the newspaper sale ads, comparison shopping the aisle, finding the markdown, handing a coupon to the cashier, paying the sales tax, and watching his mother photograph the receipt before the car leaves the parking lot. Sixteen-plus money concepts ride inside the plot. Nobody in the book says the word "budget."
+The case for the shelf: nearly every money picture book teaches earning or saving. To my knowledge this is the first narrative picture book for this band that follows the whole consumer arc, wish through receipt. The back matter carries a twenty-one-term glossary in which every definition cites the page where the term happens in the story, so a child looking something up lands in a scene rather than a definition list.
+Cataloguing: ISBN 979-8-234-07638-0 · LCCN 2026906164 · hardbound, case bound, full colour, 11×8.5′′ · Est. Lexile AD 620L, Guided Reading L–N · $19.99. Full record at clarencegetsabargain.com/book-facts.html. The AD in that Lexile stands for Adult Directed, so it does double duty as a read-aloud title and a take-home.
+Programming, already built and free: printable price tags and clearance stickers for a pretend store, a browser-based Sea-Mart register children operate themselves with a markdown, a coupon and sales tax, and a quiz with a printable certificate. No prep budget required for a Financial Literacy Month or Money Smart Week event.
+Endorsed by a K–5 educator with 30+ years in the classroom and by the 2026 EIFLE Educator of the Year.
+Shelve it under picture books; file it under secret weapons. Happy to send a review copy — reply with an address?
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M26" s="5" t="inlineStr"/>
       <c r="N26" s="5" t="inlineStr"/>
     </row>
@@ -29600,8 +30333,23 @@
           <t>Gretchen — nowhere near your beat, so this is short. I read all 25 titles on the ABA Foundation's children's financial literacy list. Every one teaches earning, saving, or investing. None teaches spending, which is the only transaction a six-year-old actually performs. That gap struck me as a matter of first impression, so I wrote the book. If someone at the Times covers this, I'd take the name. One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr"/>
-      <c r="L27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Gretchen — you have spent a career on how financial products get sold to people who don't fully understand them. Here is the entry-level version of that, and nobody covers it.
+A child becomes a consumer the first time money leaves their hand. Six years old, a birthday five, a store. From that moment they are a party to transactions, and the entire financial education apparatus treats them as a saver in training instead. We teach them to hold money. Nobody teaches them what happens when they use it.
+The scale is small and the mechanics are identical to the ones you write about. A claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the child has no way of knowing that. Not a game of skill — a slot machine wearing a carnival hat, aimed at someone with no price memory and no comparison to make.
+I wrote the picture book for it. One kid, one purchase, followed the whole way: he wants a robot, earns it, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget." The child works out he has been schooled only when he reaches the glossary — twenty-one terms in the back, each page-referenced to where it happened.
+The format matters: Lexile AD 620L. The AD is Adult Directed, the trade's own code for a book meant to be read with a child rather than handed over.
+The story is not the book. It is that an entire publishing category taught children to save for forty years and skipped the register, which is the only place a child has ever handled money — while the arcade, the app store and the checkout lane did not skip it at all.
+Is there anything there? clarencegetsabargain.com/press-kit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M27" s="5" t="inlineStr"/>
       <c r="N27" s="5" t="inlineStr"/>
     </row>
@@ -29646,8 +30394,23 @@
           <t>Kim — you cover retail. Mine is a six-year-old's first walk through one. Circular at the kitchen table, find the aisle, compare two models, hand a coupon to a cashier, then discover sales tax the hard way. Retail from four feet up, with a robot. Story, or a colleague who'd want it? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr"/>
-      <c r="L28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>Kim — you cover retail, so you already know the boardwalk arcade is a pricing strategy rather than a game. I wrote the children's book that explains it before a kid loses to it.
+The number I keep coming back to: a claw machine takes $25 to hand back a basketball that Walmart sells for $9.99. That is the entire business model in one glass box — charge $25 for the $9.99 thing and make it feel like winning. Once a kid has seen the $9.99, the claw loses its grip. Nobody shows them the $9.99.
+Every children's money book teaches saving. Piggy banks, jars, three little tins labeled spend-save-give where "spend" gets one page and a guilty look. But saving is the second thing a child does with money. The first is spending, and a six-year-old has done it already, standing in a store, deciding.
+So mine follows a single purchase the entire distance. A boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one deliberately, hands a coupon to the cashier, meets sales tax, and then lives with the thing. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
+It is catalogued Lexile AD 620L — Adult Directed, meaning read-with rather than read-alone, so the parent gets handed the script instead of being expected to know it.
+The retail angle, if you want one: every trick your beat covers — the fake markdown, the anchor price, the "newest is better" framing — gets run on children first, in arcades and toy aisles, where there is no consumer press at all.
+Worth a look? clarencegetsabargain.com/book-facts.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M28" s="5" t="inlineStr"/>
       <c r="N28" s="5" t="inlineStr"/>
     </row>
@@ -29692,8 +30455,23 @@
           <t>Terry — syndicated for decades means you've seen every kids' money book twice. Mine leaves saving out entirely. Reckless? Possibly. But spending is the transaction a six-year-old performs first, and forty years of piggy banks haven't fixed that. 36 pages, ages 6-10. Column, or am I overselling the gap? The format is part of the story: Lexile AD 620L — AD is Adult Directed, the industry's own code for read-WITH. An adult reads, a kid interrupts, and somebody has to answer "do we have one of those?" out loud. Same whether the adult is a teacher, a parent, or a grandparent. Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Terry — you have been telling adults the truth about money for decades, usually after the damage is done. I wrote the book for about twenty years earlier than you usually get them.
+The argument in one line: mistakes at eleven cost $14, and the same mistake at twenty-seven has a credit card attached. Everything you write about compounding cuts both ways, and the habits doing the compounding were installed in a store, at six, with a parent saying no.
+Which is where the whole category gets the order wrong. Children's money books teach saving — piggy banks, jars, patience. But saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate. She has stood at a register holding money and had to decide.
+Clarence Gets a Bargain follows one purchase the entire way: a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax and takes it personally, then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none announced — nobody in the book says "budget." The reader finds out he has been schooled at the glossary, twenty-one terms in the back, each page-referenced to the scene it came from.
+It reads aloud in twenty minutes. Lexile AD 620L — Adult Directed, the industry's own code for read-with rather than read-alone, so a parent who feels unqualified on money still gets handed the script.
+The column question rather than the book question: has anyone made the case that spending competence has to come first? I have not been able to find it, and you would know if it exists.
+clarencegetsabargain.com/press-kit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M29" s="5" t="inlineStr"/>
       <c r="N29" s="5" t="inlineStr"/>
     </row>
@@ -29738,8 +30516,22 @@
           <t>Amanda — Planet Money is good at the moment someone realizes the economy just did something to them. Mine is that moment at four feet tall. Kid reaches the register, total's higher than the sticker, and sales tax enters his life uninvited. He takes it personally. 36 pages. Is that a segment or just a strange thing to have made? The format is part of the story: Lexile AD 620L — AD is Adult Directed, the industry's own code for read-WITH. An adult reads, a kid interrupts, and somebody has to answer "do we have one of those?" out loud. Same whether the adult is a teacher, a parent, or a grandparent. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr"/>
-      <c r="L30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>Amanda — Planet Money's whole trick is that people will sit still for an economics lesson if it is hidden inside a story about a person and a thing. I did that at a first-grade reading level, and I am writing about the story rather than the book.
+Every children's money book teaches earning or saving. All 25 on the ABA Foundation's list — I read them to be sure. A piggy bank, a lemonade stand, a lesson. Not one covers the cash register, which is the only place a child has ever actually handled money.
+Mine does. A boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, gets ambushed by sales tax, and then lives with what he bought. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget." They do not realise they have been schooled until they hit the glossary in the back — twenty-one terms, each page-referenced to the moment it happened. That is where the con comes apart, on purpose.
+Format note, since you make things people take in together: Lexile AD 620L, where AD means Adult Directed — a book built to be read with a child, interrupted the whole way.
+The segment is the forty-year hole. A whole publishing category taught children to save and skipped the register, while every arcade, app store and checkout lane aimed at children did not skip it at all.
+Is that an episode whether or not my book is in it? Four-minute flip: https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M30" s="5" t="inlineStr"/>
       <c r="N30" s="5" t="inlineStr"/>
     </row>
@@ -29784,8 +30576,23 @@
           <t>Bethann — a bankers association reaches classrooms and families at once, which is the distribution a K-5 book needs and rarely gets. Mine is five frameworks, free zero-prep lessons, plus a grant packet if a member bank wanted to fund classroom sets. Fit Utah's outreach? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>Bethann — you run the education side of a bankers association, which means you are the person who decides what volunteers actually carry into a classroom. I built something for the grade band most bank programs skip.
+Most financial education a bank sponsors lands in high school or in a "teach a child to save" day about saving. Saving is the second thing a child does with money. The first is spending, and a first grader has done it, at a register, with a parent behind her. There is almost nothing to hand a banker walking into a second-grade room about that.
+Clarence Gets a Bargain is a 36-page picture book following one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget."
+Why it works for a volunteer rather than a teacher: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, and the mother explains every concept inside the text. A banker can read it cold and field the questions straight off the page. No training call, nothing to memorise. Free lesson plans, assessments and a browser-based pretend register sit behind it, all ungated.
+The sponsorship math is simple if a member bank wants it: 25 copies is $499.75, one classroom, the bank's name on every book that goes home to a family. The educator program is free, so the sponsorship is entirely books, and I have a CRA-ready memo already written in examiner-friendly language.
+Does that fit how Utah banks choose classroom programs, or am I inventing a use case?
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M31" s="5" t="inlineStr"/>
       <c r="N31" s="5" t="inlineStr"/>
     </row>
@@ -29830,8 +30637,24 @@
           <t>Lynnette — you've built both a body of work and a network around this. Mine is a K-5 picture book teaching spending rather than saving. I'd take your read on where a book like this belongs, and whether FIN is a fit at all. A blunt no is useful too. The format is part of the story: Lexile AD 620L — AD is Adult Directed, the industry's own code for read-WITH. An adult reads, a kid interrupts, and somebody has to answer "do we have one of those?" out loud. Same whether the adult is a teacher, a parent, or a grandparent. More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr"/>
-      <c r="L32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>Lynnette — you have spent a career telling people the truth about money in language they can actually use, and you built a network for people doing the same. I wrote the six-year-old version and I would like your read on whether it lands.
+Every children's money book teaches saving. Piggy banks, jars, three tins labeled spend-save-give where "spend" gets one page and a guilty look. But saving is the second thing a child does with money. The first is spending, and a first grader has already done it — in a store, holding money, deciding.
+And the tools have moved against them. A card is magic; a five-dollar bill is arithmetic — a kid who watches three dollars leave their hand understands something no tap-to-pay will ever teach.
+Which matters most in households where there is no margin for a bad purchase. A child taught only to save has been handed advice that assumes surplus. A child who can compare two prices and choose deliberately has a skill that works this Saturday.
+Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, meets sales tax, and then lives with what he chose. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the story.
+Catalogued Lexile AD 620L — Adult Directed — so the adult reading it is handed the script and does not have to be the one who already knows about money. That was the design constraint that mattered most: it has to work in a house where nobody feels qualified to teach it.
+Two questions. Does the spending-first argument hold up against what you hear from your audience? And is there a version of this worth putting in front of the Financial Influencer Network?
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M32" s="5" t="inlineStr"/>
       <c r="N32" s="5" t="inlineStr"/>
     </row>
@@ -29876,8 +30699,23 @@
           <t>Ruben — my book and teaching pack are aligned to the CEE standards with a full crosswalk. Is there a route for a K-5 title into CEE's resource library or EconEdLink, and what would you want to see first? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr"/>
-      <c r="L33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>Ruben — CEE's standards are one of the five frameworks I crosswalked against, so I have spent real time inside them and want to ask about the bottom of the ladder.
+The elementary benchmarks exist. What is built against them is thin, and thinner still on the spending side. The field starts children with saving, and saving is the second thing a person does with money. The first is spending: standing in front of two prices and choosing one. A first grader has done that; she has no savings rate at all.
+I built a free K–5 classroom set around a 36-page picture book and crosswalked it concept by concept — 23 rows against the 2021 National Standards for Personal Financial Education, CEE, Common Core Math and ELA, and FDIC Money Smart, with the Grade 4 benchmark codes rather than a general claim of alignment. It is published so a reviewer can check it instead of taking my word.
+The book follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with the choice. Sixteen-plus concepts and nobody in it says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened.
+Catalogued Lexile AD 620L — Adult Directed — one class period read aloud, and because the mother explains every concept inside the text a teacher with no economics background can run it cold.
+The question: is there a route for elementary material to sit alongside CEE programs, or does that run through affiliate councils? Either answer saves me guessing.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M33" s="5" t="inlineStr"/>
       <c r="N33" s="5" t="inlineStr"/>
     </row>
@@ -29922,8 +30760,24 @@
           <t>Beth — My Mother's Money is about the inheritance nobody itemizes. Mine is the earliest deposit into it: a mother teaching a six-year-old to read a sale ad, compare two prices, and understand why the register total climbed. She also photographs every receipt in the parking lot. Real habit, straight into the book. Column? It's written for an adult voice — Lexile AD 620L, Adult Directed, read-with rather than read-alone — with Mom carrying every explanation, so whoever reads aloud gets handed the script. That constraint shaped every page. Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>Beth — you write for people trying to do the right thing with money and finding the advice arrives late. This arrives about two decades earlier than most of it.
+The premise: financial education starts children with saving, and the sequence is backwards. Saving is the second thing a person does with money. The first is spending. A seven-year-old has no savings rate and no income; what she has done is stand at a register holding money and choose. We teach that last, or never.
+I wrote the picture book for it. One purchase, followed the whole way — a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, meets sales tax, and then lives with what he chose. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; not one covers the whole arc.
+Sixteen-plus concepts, none announced — nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened, so vocabulary points a kid back into the story rather than away from it.
+Catalogued Lexile AD 620L — Adult Directed, read-with rather than read-alone. The mother explains everything on the page, so the parent gets the script and can take the credit.
+One thing I would put to you as a planner: a card is magic, and a five-dollar bill is arithmetic. Children now grow up almost entirely inside the first one, which removes the only feedback loop they had.
+The claim I would defend hardest is the delayed one. The book is not really working in the twenty minutes it takes to read. It works in month eighteen, in a real store, when the kid hits a money moment and the book fires back — "wait, is the newer one actually better?" Recognition first, then the habit.
+Does that hold up against what you see in readers? clarencegetsabargain.com/book-facts.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M34" s="5" t="inlineStr"/>
       <c r="N34" s="5" t="inlineStr"/>
     </row>
@@ -29968,8 +30822,23 @@
           <t>Julie — you translate markets for a big audience daily. Mine translates one purchase for a six-year-old: compare, take the cheaper model, pay the tax, feel mildly cheated. Smallest possible economics story. Segment, or wrong desk? The format is part of the story: Lexile AD 620L — AD is Adult Directed, the industry's own code for read-WITH. An adult reads, a kid interrupts, and somebody has to answer "do we have one of those?" out loud. Same whether the adult is a teacher, a parent, or a grandparent. Press kit: https://clarencegetsabargain.com/press-kit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr"/>
-      <c r="L35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>Julie — a segment idea, and it is short enough to survive a live hit.
+Every children's money book teaches saving. Piggy banks, lemonade stands, jars. But saving is the second thing a child does with money — the first is spending, and a six-year-old has already done it, in a store, holding a birthday five, deciding whether the thing is worth what it costs.
+The category skipped that for forty years. The arcade did not. A claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the kid has no price memory to defend himself with. Once a kid has seen the $9.99, the claw loses its grip.
+So I wrote the spending book. Clarence Gets a Bargain, ages 6–10: a boy earns a robot with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and then lives with the thing he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Twenty-one terms in a glossary at the back, each page-referenced to where it happened.
+Catalogued Lexile AD 620L — Adult Directed, the trade's own code for a book read with a child rather than handed to one. Twenty minutes out loud, interrupted the whole way.
+I am an attorney and a mixed-media artist, and I have twice walked out of the same Nordstrom Rack having paid one cent — once for a $293 pair of shoes, once for a $69.50 shirt. I kept both tags. It makes for a good visual if you ever want one on screen.
+Is there a hit in "the money skill nobody teaches kids"? clarencegetsabargain.com/press-kit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M35" s="5" t="inlineStr"/>
       <c r="N35" s="5" t="inlineStr"/>
     </row>
@@ -30014,8 +30883,23 @@
           <t>Matt — Ask Questions, Save Money, Make More is a skill book. Mine is the same skill at six: ask what it costs, ask whether the older one is actually worse, ask why the total went up at the register. I'd take your read on positioning a spend-first kids' book with no shelf-mates. It's written for an adult voice — Lexile AD 620L, Adult Directed, read-with rather than read-alone — with Mom carrying every explanation, so whoever reads aloud gets handed the script. That constraint shaped every page. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr"/>
-      <c r="L36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>Matt — you spend your working life on what happens when people meet credit without the groundwork. I wrote the book about the groundwork, roughly twenty years upstream of your data.
+The sequence is the whole argument. Financial education starts children with saving. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent behind her. Mistakes at eleven cost $14. The same mistake at twenty-seven has a credit card attached and a rate on it.
+Clarence Gets a Bargain follows one purchase the entire distance: a boy wants a robot, earns it with chores and grades, works the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; they are all parked on the earning-and-saving side of the register.
+Sixteen-plus concepts and nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened — which is the only point at which a kid works out he has been schooled.
+Catalogued Lexile AD 620L — Adult Directed, so it is read-with rather than read-alone and the parent gets handed the script.
+The question, since you have the data and I only have the book: does anything in what you see suggest that price competence at seven shows up at twenty-seven? If it does not, I would rather know.
+clarencegetsabargain.com/book-facts.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M36" s="5" t="inlineStr"/>
       <c r="N36" s="5" t="inlineStr"/>
     </row>
@@ -30060,8 +30944,22 @@
           <t>Jillian — Intuit for Education is built around real financial decisions, which is my book's entire structure: one purchase, ad to register, sales tax included. Mine sits at K-5, below your usual band. Does the framing match how you think about curriculum? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr"/>
-      <c r="L37" s="5" t="inlineStr"/>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>Jillian — Intuit for Education is built for high school and does that job well, so this is a question about the floor beneath it rather than a pitch into your territory.
+Everything in the field lands late. Thirty states require personal finance to graduate, all of it in high school. Money habits are largely set by seven. And the sequencing assumption nobody questions is that children should start with saving — when saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has stood at a register and chosen.
+I built the K–5 on-ramp. A 36-page picture book that follows one purchase the whole distance — wanting the robot, earning it, working the sale inserts at the kitchen table, comparing two models on a shelf, taking the marked-down one on purpose, redeeming a coupon, meeting sales tax, and living with the choice. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced back into the story.
+The curriculum behind it is free and ungated — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart, printable classroom pieces, and a browser-based pretend register that runs a markdown, a coupon and sales tax with the total changing in front of the class. Catalogued Lexile AD 620L — Adult Directed — one class period, no teacher training.
+The honest question rather than a pitch: when teachers come to Intuit for Education, does elementary ever come up as something they want and cannot find? I am trying to work out whether I am filling a gap or inventing one, and you would see the demand signal before I would.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M37" s="5" t="inlineStr"/>
       <c r="N37" s="5" t="inlineStr"/>
     </row>
@@ -30106,8 +31004,23 @@
           <t>Saskia — Promise Academy is deliberate about what earns classroom time, which is the right instinct. Mine teaches the complete purchase, sales tax included, and the family activity was built for a kitchen table. Classrooms or family programming — or neither? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr"/>
-      <c r="L38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Saskia — HCZ built its whole model on the idea that you intervene early and you do not wait for the system to catch up. I built the elementary financial-literacy piece on the same reasoning, and I would like your read on whether it holds.
+Every state financial-literacy requirement lands in high school. The habits being corrected there were installed at six, in a store. And the field starts children with saving, which is the second thing a child does with money — the first is spending, and it is the one your students are already doing.
+That distinction matters more, not less, for families with less room for error. A child who can compare two prices and choose deliberately has a skill that pays on a Saturday. A child taught only to save has been handed advice that requires surplus.
+Clarence Gets a Bargain is a 36-page picture book that follows one complete purchase: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget." A twenty-one-term glossary in the back, page-referenced to the story.
+Catalogued Lexile AD 620L — Adult Directed — one class period out loud, and because the mother explains every concept inside the text, a teacher needs no finance background. Everything behind it is free and ungated: lesson plans, assessments with answer keys, a standards crosswalk, printable classroom pieces, a browser-based pretend register.
+Would a read-aloud plus a pretend-store activity fit anywhere in a Promise Academy week, or is the schedule too tight for anything that is not tested?
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M38" s="5" t="inlineStr"/>
       <c r="N38" s="5" t="inlineStr"/>
     </row>
@@ -30152,8 +31065,22 @@
           <t>Ben — you run personal finance coverage, so one line: every children's money book teaches saving, mine teaches spending, and the six-year-old pays sales tax on page 22. Did I verify that gap or just assert it? Verified — all 25 titles on the ABA Foundation list. Story, or someone on the desk who'd take it? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr"/>
-      <c r="L39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>Ben — a story pitch about a gap in the coverage rather than a book pitch, though the book is how I found it.
+Thirty states now guarantee a personal finance course. Every one of those mandates lands in high school. Money habits are largely set by seven — so the policy arrives roughly ten years after the cement dries, and the funding, the training and the reporting all follow the mandate rather than the evidence.
+Underneath that sits an assumption nobody argues with: that children should learn saving first. I think it is backwards. Saving is the second thing a person does with money. The first is spending, and a first grader has done that, at a register, with a parent standing behind her. The behaviors a high school course tries to correct were installed a decade earlier by an arcade, a toy aisle and a checkout lane, none of which waited for a curriculum.
+I wrote the elementary piece rather than an op-ed about it. A 36-page picture book following one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, and living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Free ungated classroom set behind it, crosswalked to five frameworks. Catalogued Lexile AD 620L — Adult Directed, so it is a read-with, and the caregiver conversation happens inside the reading.
+The story I would pitch your desk: the whole country legislated financial literacy into ninth grade, and the elementary standards that already exist in most states sit there with nothing built against them, because nobody has to report on them.
+Does that belong to anyone on your team? clarencegetsabargain.com/book-facts.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M39" s="5" t="inlineStr"/>
       <c r="N39" s="5" t="inlineStr"/>
     </row>
@@ -30198,8 +31125,23 @@
           <t>Stacy — you cover consumer finance. I wrote the origin story: a six-year-old's first transaction, including the moment sales tax appears and ruins the arithmetic he'd already done in his head. It's a picture book, which may or may not help my case. Angle here, or a better name at the Times? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K40" s="5" t="inlineStr"/>
-      <c r="L40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>Stacy — you write about what happens to ordinary people inside financial systems. There is a version of that beat with no coverage at all, and it starts at about age six.
+A child becomes a consumer the first time they hand money to a cashier. Not at eighteen, not at a first paycheck — at six, with a birthday five. From that moment they are party to a transaction and they have rights nobody mentions: the receipt is proof, the price on the shelf has to match the price at the register, a broken thing can go back. Consumer education is the missing wing of children's financial literacy. We teach them to save and never tell them they are already the buyer.
+That is why I wrote the book. Clarence Gets a Bargain follows one purchase the entire way — a boy wants a robot, earns it, reads the sale inserts at the kitchen table, compares two on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced, and a twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
+The detail people ask me about: the mother photographs the receipt the second she sits down in the car. Every time. It takes four seconds and it is what makes a return, an exchange or a warranty claim winnable. Almost nobody teaches a child that.
+Format: Lexile AD 620L — Adult Directed, the trade's code for read-with rather than read-alone.
+I am an attorney, so I will say the honest version: the full picture crosses agencies, warranties and returns sit with the FTC, product safety with the CPSC. Nobody owns "children as consumers," which may be why nobody covers it.
+Is there a story in that? clarencegetsabargain.com/press-kit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M40" s="5" t="inlineStr"/>
       <c r="N40" s="5" t="inlineStr"/>
     </row>
@@ -30244,8 +31186,24 @@
           <t>Susan — you've directed a center for economic education for years. My K-5 book argues the elementary band is underserved because everything gets built for high school. Aligned to CEE and four others. Does that match what you see? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr"/>
-      <c r="L41" s="5" t="inlineStr"/>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>Susan — you built a center from nothing and have spent years getting economics into elementary classrooms, which makes you exactly the person to tell me whether I am filling a gap or inventing one.
+The gap as I see it: elementary standards exist in most states and almost nothing is built against them, because nobody has to report on them. Every mandate lands in high school. Thirty states now.
+And underneath that, a sequencing assumption nobody argues with — that children should learn saving first. Saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has stood at a register and chosen.
+So I wrote the K–5 piece. Clarence Gets a Bargain follows one purchase from the idea to after the receipt: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, so vocabulary review points a child back into the story instead of away from it.
+The teacher side is free and ungated — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE, and FDIC Money Smart. No account, no email capture. It prints from a browser.
+Catalogued Lexile AD 620L — Adult Directed — so it runs as a one-period read-aloud and a teacher with no finance background can deliver it cold.
+Does the spending-first sequence match what you see in classrooms, or is there a reason the field starts where it starts?
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M41" s="5" t="inlineStr"/>
       <c r="N41" s="5" t="inlineStr"/>
     </row>
@@ -30290,8 +31248,23 @@
           <t>Veronica — you write about money across a whole life. This is hour one. Six-year-old runs his first purchase, ad to register. The parent hook: his mother photographs every receipt before she pulls out of the parking space. That's in the book because it's a real habit, and it's the one detail adults tell me they recognized. The format is part of the story: Lexile AD 620L — AD is Adult Directed, the industry's own code for read-WITH. An adult reads, a kid interrupts, and somebody has to answer "do we have one of those?" out loud. Same whether the adult is a teacher, a parent, or a grandparent. Press kit: https://clarencegetsabargain.com/press-kit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K42" s="5" t="inlineStr"/>
-      <c r="L42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>Veronica — you cover how families hold on to money across generations, which is why I am writing about the earliest possible end of that.
+The money conversation in most families starts far too late to be a conversation. By the time a parent sits a teenager down, the habits are set — they were set at six, in a store, with a parent saying no and no explanation attached to the no.
+Every children's book on the shelf teaches saving. Piggy banks, jars, patience. But saving is the second thing a child does with money; the first is spending, and a six-year-old has already done it.
+Clarence Gets a Bargain follows one purchase the whole way — earning the reward through chores and grades, working the sale ads at the kitchen table, comparing two models on a shelf, taking the cheaper one on purpose, handing over a coupon, meeting sales tax, and then living with what was bought. Idea to post-receipt. And on page 6 there is something I have not found in any other picture book: a 529 plan. In the plot. Explained by a mom, eye-rolled at by a kid, and defended by a dad two scenes later.
+Sixteen-plus concepts and nobody says "budget." A twenty-one-term glossary in the back, page-referenced to the story. Catalogued Lexile AD 620L — Adult Directed — so it is a read-with, and the conversation happens during the reading rather than after it.
+The angle for your beat: advisors spend fortunes trying to meet the next generation before the assets move. This is what meeting them at seven looks like, and it costs $19.99.
+Worth a column, or am I describing something you have already covered? clarencegetsabargain.com/press-kit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M42" s="5" t="inlineStr"/>
       <c r="N42" s="5" t="inlineStr"/>
     </row>
@@ -30336,8 +31309,25 @@
           <t>Dr. Taylor — Montgomery County sets what reaches a lot of classrooms. Mine is a K-5 picture book with a free zero-prep lesson set, five frameworks, nothing consumable to reorder next August. The honest question is placement rather than merit: classroom, library, or family night? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K43" s="5" t="inlineStr"/>
-      <c r="L43" s="5" t="inlineStr"/>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>Dr. Taylor — I am a Maryland attorney and children's book author writing about the elementary end of financial literacy, which is the end nobody funds.
+Maryland's requirement, like every state's, lands in high school. The elementary standards sit underneath it with almost nothing built against them, because no one has to report on that band. Meanwhile the habits a high school course is trying to correct were installed at six, in a store, with a parent saying no and no reasoning attached.
+The field's answer is to teach children saving first. Saving is the second thing a person does with money. The first is spending, and a first grader has done it — at a register, with a parent standing right there.
+I wrote the K–5 piece. A 36-page picture book following one purchase from the idea through the receipt: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken on purpose, a coupon at the register, sales tax, and living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced back into the story.
+What matters for a district is that all of it is free. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, and a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart. No account, no email capture, no purchase order. It prints from a browser, so adoption costs a building nothing. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud a teacher can run with no finance background.
+I am local and would happily walk a curriculum team through it, or a single school if that is the right size to start.
+Who in MCPS owns elementary financial literacy, if anyone does?
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan Bach
+Attorney and children's book author, Baltimore</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M43" s="5" t="inlineStr"/>
       <c r="N43" s="5" t="inlineStr"/>
     </row>
@@ -30382,8 +31372,24 @@
           <t>Beth — a research question. My K-5 book argues spending competence precedes saving competence developmentally, which would mean the field teaches the wrong skill first. Does that square with your research and impact work, or am I overstating a tidy story? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K44" s="5" t="inlineStr"/>
-      <c r="L44" s="5" t="inlineStr"/>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>Beth — a research question rather than a pitch, and the book is only the reason I ran into it.
+Financial capability gets measured, sensibly, on saving, compounding and risk. Those are the right things to measure in adults. But each of them sits downstream of a decision made years earlier that nobody scores: a child standing in front of two prices, picking one. Spending is the first financial behavior a person performs, and it is taught last or not at all.
+The environment is not waiting for the curriculum. Children are transacting constantly — arcades, app stores, checkout lanes — and none of it gets counted as financial education, though it plainly is.
+I wrote the elementary piece. A 36-page picture book following one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, and living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced back into the story. Free ungated classroom set behind it, crosswalked to five frameworks.
+Design note that may matter to your work: the book is catalogued Lexile AD 620L — Adult Directed. The intervention is an adult and a child reading together, not a child reading alone, which makes it closer to a shared-reading study than a curriculum study.
+The question: does the evidence base start at adolescence the way the books do? If spending competence at seven predicts nothing at twenty-seven, that is worth knowing and I would rather hear it than keep arguing.
+clarencegetsabargain.com/book-facts.html
+Jonathan Bach
+Attorney and children's book author, Baltimore</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M44" s="5" t="inlineStr"/>
       <c r="N44" s="5" t="inlineStr"/>
     </row>
@@ -30428,8 +31434,23 @@
           <t>Sam — twenty-plus years and a quarter million kids means you've seen every approach in this space. Sammy teaches saving beautifully. I went the other way on the theory that spending is what a six-year-old does first. Real gap, or a convenient story I tell myself? You'd know. One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K45" s="5" t="inlineStr"/>
-      <c r="L45" s="5" t="inlineStr"/>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>Sam — you have been reading, singing and performing a savings habit into elementary classrooms for two decades across thirty states, which is more direct contact with this audience than anyone else in the category has. So I want to put an argument in front of you and hear where it is wrong.
+Sammy teaches saving, and teaches it better than anything else aimed at this age. My argument is not about quality; it is about order. Saving is the second thing a child does with money. The first is spending — a first grader has stood at a register holding money and chosen, years before she has anything to save. Teach that moment first, and everything Sammy preaches lands harder, because a kid who understands what money buys has a reason to keep some.
+That is the book I wrote. Clarence Gets a Bargain follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the scene each term came from.
+Catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, with every concept explained inside the text, so somebody can read it cold to a class. You will recognise why that mattered to me.
+You also solved a distribution problem the rest of us have not: banks and credit unions sponsor the visits and buy the books, and their community reports write themselves. I would genuinely rather learn that from you than reverse-engineer it.
+Trade copies and compare notes? I will read Sammy properly and tell you the truth about it, which is the only thing worth trading.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M45" s="5" t="inlineStr"/>
       <c r="N45" s="5" t="inlineStr"/>
     </row>
@@ -30474,8 +31495,23 @@
           <t>Vince — NFEC reaches thousands of instructors, and K-5 is where most of them have the least to hand anyone. Mine runs 36 pages plus free classroom materials against five frameworks, crosswalk included. Route into the NFEC resource network? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K46" s="5" t="inlineStr"/>
-      <c r="L46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>Vince — you have thousands of instructors in the field, which means you know better than almost anyone what they walk into a room without. I built the elementary thing they do not have.
+Most financial education material aimed at children starts with saving. Saving is the second thing a child does with money. The first is spending — and a first grader has done it, at a register, with a parent behind her. An instructor standing in front of a second-grade class has almost nothing to hand them about that moment.
+Clarence Gets a Bargain is a 36-page picture book that follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one deliberately, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget."
+Why it works for an instructor rather than a teacher: it is catalogued Lexile AD 620L — Adult Directed — it runs about twenty minutes out loud, and the mother explains every concept inside the text. Somebody can read it cold to a class and field questions straight off the page. Nothing to memorise, no training call beforehand. Behind it sits a free ungated set — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, and a browser-based pretend register with a markdown, a coupon and sales tax.
+The twenty-one-term glossary in the back is page-referenced to the story, so an instructor can answer a vocabulary question by turning to the scene rather than reciting a definition.
+Does your instructor network want elementary material, or is the demand really all adult and teen? Everything is free either way.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M46" s="5" t="inlineStr"/>
       <c r="N46" s="5" t="inlineStr"/>
     </row>
@@ -30520,8 +31556,23 @@
           <t>Billy — a NEFE-shaped question. The research keeps saying money attitudes form by seven, and almost every dollar of material lands at 9-12. I wrote a K-5 picture book teaching spending rather than saving. Does NEFE ever point people to elementary, or is that band still nobody's mandate? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. Teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K47" s="5" t="inlineStr"/>
-      <c r="L47" s="5" t="inlineStr"/>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>Billy — a question about where NEFE draws the line on grade band, asked by someone who has just spent a year building for the band nobody funds.
+Thirty states now require personal finance to graduate. The mandates land in high school, and the funding, the training and the reporting follow the mandate. Meanwhile the K–5 standards that already exist in most states sit there with almost nothing built against them, because nobody has to report on them.
+The assumption underneath is that children should learn saving first. I think it is backwards, and I would rather be told so by NEFE than keep saying it at conferences. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent standing behind her. The behaviors a high school course is trying to correct were installed a decade earlier.
+I wrote the elementary piece rather than an argument about it: a 36-page picture book that follows one purchase from the idea to after the receipt, plus a free ungated classroom set crosswalked to the 2021 National Standards, Common Core, CEE and FDIC Money Smart. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Catalogued Lexile AD 620L — Adult Directed — so the intervention is a shared read rather than solo reading, which also makes it easier to study than a curriculum.
+The question: does NEFE's research or advocacy work have a position on the elementary band, or is the practical view that high school is where the effort pays? If it is the second, I would like to know I am arguing with a considered consensus rather than filling a gap it agrees exists.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan Bach
+Attorney and children's book author, Baltimore</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="inlineStr"/>
     </row>
@@ -30566,8 +31617,23 @@
           <t>Laura — a Clearinghouse question rather than a pitch. My K-5 teacher pack is built against the National Standards, free, ungated, no email capture and no drip campaign. Is Suzann Knight the right first stop, or is there a step I'm skipping? Wally Luckeydoo endorsed the book, which I mention only because he's your 2026 Corey Carlisle recipient. Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. Teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K48" s="5" t="inlineStr"/>
-      <c r="L48" s="5" t="inlineStr"/>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>Laura — a question about scope rather than a pitch, and I have already read the Clearinghouse criteria closely enough to know which route applies to me.
+Jump$tart's standards cover K–12, but the material built against them thins out badly below grade six. The elementary band has standards and very little aimed at it, largely because nothing requires anyone to report on that band. Every state mandate lands in high school. Thirty of them now.
+There is also a sequencing assumption underneath the whole field that I would like your view on. Financial education starts children with saving. Saving is the second thing a person does with money; the first is spending. A first grader has no savings rate. She has stood at a register holding money and had to choose.
+I built a free, ungated K–5 classroom set around a 36-page picture book: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE and FDIC Money Smart, printable classroom pieces, and a browser-based pretend register. No account, no email capture, no purchase order. It prints from a browser.
+The book follows one complete purchase — sale ads, comparison, a markdown, a coupon, sales tax — with sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story. Catalogued Lexile AD 620L, Adult Directed, so it runs as a one-period read-aloud with no teacher training required.
+Two questions. Does Jump$tart consider elementary in scope, or is it a band the coalition has consciously left to others? And for the Clearinghouse, is the free classroom set the right thing to submit rather than the book?
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M48" s="5" t="inlineStr"/>
       <c r="N48" s="5" t="inlineStr"/>
     </row>
@@ -30612,8 +31678,24 @@
           <t>Prince — real respect for the Wesley Learns books; you got kids to investing without it feeling like homework. Mine sits one rung below. Before a kid invests, he has to survive a store. Ad, aisle, comparison, coupon, register. Complementary rather than competitive, I think. Trade copies? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K49" s="5" t="inlineStr"/>
-      <c r="L49" s="5" t="inlineStr"/>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>Prince — you took investing, which is the hardest concept in this category to make readable for children, and made it a series a kid comes back to. I went the opposite direction on the same shelf and I would like your read on it.
+Wesley learns to invest. Clarence learns to spend — and I mean the mechanics of it rather than the idea. Every other book in the category teaches saving, which is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. Nobody had written that one, so I did.
+Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Nobody says the word "budget."
+The craft problem I would most like another author's view on: the reader is not supposed to know he has been taught anything until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. Getting that balance right, so it stays a story, was the whole job, and it is the thing most likely to be off by a hair.
+I did the illustrations too, which means my opinion of them is worth nothing.
+Catalogued Lexile AD 620L — Adult Directed — written for the adult voice in the room, with the mother carrying every explanation.
+Trade? Send me a Wesley and I will read it properly rather than politely.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M49" s="5" t="inlineStr"/>
       <c r="N49" s="5" t="inlineStr"/>
     </row>
@@ -30658,8 +31740,23 @@
           <t>Kate — you cover taxes, so here's a sentence you may enjoy. My children's picture book teaches sales tax. Six-year-old hits the register, the total's higher than the sticker, and his mom explains where the difference goes. I cannot find another kids' book that does it. Story, or just a peculiar thing to have written? The format is part of the story: Lexile AD 620L — AD is Adult Directed, the industry's own code for read-WITH. An adult reads, a kid interrupts, and somebody has to answer "do we have one of those?" out loud. Same whether the adult is a teacher, a parent, or a grandparent. Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K50" s="5" t="inlineStr"/>
-      <c r="L50" s="5" t="inlineStr"/>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>Kate — a pitch about a gap rather than a book, though I wrote the book because of the gap.
+Everything in kids' financial literacy points at a horizon no child can see: compound interest, credit scores, retirement. All real, all decades out. Meanwhile the kid is eight, holding $20 of birthday money, standing in a store that spent millions working out how to get it. We are preparing children for 65 and sending them to the register unarmed today.
+So flip the order. Saving is the second thing a child does with money. The first is spending, and it is the one nobody puts in a story.
+Clarence Gets a Bargain does. One kid, one purchase, followed the whole distance — he wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget." The reader works out he has been schooled at the glossary — twenty-one terms in the back, each one page-referenced to the scene it came from.
+Catalogued Lexile AD 620L. The AD is Adult Directed, the industry's own code for a book meant to be read with a child rather than handed over, so a parent who does not feel qualified on money still gets handed the script.
+Timely hook if you need one: thirty states now guarantee a personal finance course, all of it in high school, roughly ten years after the habits form. The elementary standards already exist in most states and have almost nothing built against them.
+Any of that useful to you? clarencegetsabargain.com/book-facts.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M50" s="5" t="inlineStr"/>
       <c r="N50" s="5" t="inlineStr"/>
     </row>
@@ -30935,8 +32032,24 @@
           <t>Professor Urban — your work on financial education mandates is the best evidence we have on what actually moves outcomes, and nearly all of it sits at high school. I wrote a K-5 book on the premise that elementary is both untested and undersupplied. Is there research I should know before I keep saying that? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K55" s="5" t="inlineStr"/>
-      <c r="L55" s="5" t="inlineStr"/>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>Professor Urban — you produced the evidence base that mandates actually work, which is why I want to ask about the grade band your evidence does not reach.
+Every mandate you have evaluated lands in high school. Thirty states now. The effects are real and I am not arguing with them. My question is about what is happening a decade earlier, because money habits are largely set by seven and the policy arrives roughly ten years after the cement dries.
+Underneath the whole field sits a sequencing assumption nobody tests: that children should learn saving first. I think it is backwards. Saving is the second thing a person does with money. The first is spending — standing in front of two prices and picking one. A first grader has done that. She has no savings rate at all.
+I could not find the children's book for it, so I wrote one. Clarence Gets a Bargain follows a single purchase the entire way: earning the reward, reading the sale ads, comparing two models on a shelf, choosing the cheaper one deliberately, redeeming a coupon, meeting sales tax, and then living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story.
+One design feature that may matter for measurement: the book is catalogued Lexile AD 620L — Adult Directed — so the intervention is not a child reading alone but an adult and a child reading together, with the adult prompted by the text. If shared reading is doing the work rather than the book, that is testable, and it would be a more interesting finding than anything about my book.
+The real question: does anything in the literature speak to elementary spending competence, or is that band simply unstudied? Either answer is useful to me.
+clarencegetsabargain.com/book-facts.html
+Jonathan Bach
+Attorney and children's book author, Baltimore</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M55" s="5" t="inlineStr"/>
       <c r="N55" s="5" t="inlineStr"/>
     </row>
@@ -30981,8 +32094,23 @@
           <t>Iris — you're at UW-Madison, which is where the Center for Financial Security picked the titles for the CFPB's Money as You Grow Bookshelf. Mine is K-5 and goes at spending instead of saving. Do you know who evaluates additions to that shelf? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K56" s="5" t="inlineStr"/>
-      <c r="L56" s="5" t="inlineStr"/>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>Iris — you were part of the group that chose the titles on the Money as You Grow Bookshelf, so you have read this category more carefully than almost anyone, and you will know immediately whether my premise is wrong.
+The shelf, as it stands, leans toward saving and earning. What is thin is spending, and specifically the transaction — the part where a child stands in front of two prices and has to pick one. That is the first financial act a person performs. It gets taught last.
+Clarence Gets a Bargain covers exactly that, and covers the whole of it: a boy wants a robot, earns it through chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list looking for another one that does the whole arc. They are all parked on the earning-and-saving side of the register.
+Sixteen-plus concepts and none is announced — no character pauses to define a term, nobody says the word "budget." The proof and the reveal are both in the back matter: a reader does not know he has been schooled until he reaches the glossary. Twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than an appendix.
+Ages 6–10, inside the Bookshelf's 4–10 band. Catalogued Lexile AD 620L — Adult Directed, which is how the Bookshelf's titles are meant to be used anyway.
+Two questions. Was the saving weighting deliberate, or just what existed? And is the selection process still running?
+clarencegetsabargain.com/book-facts.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M56" s="5" t="inlineStr"/>
       <c r="N56" s="5" t="inlineStr"/>
     </row>
@@ -31035,12 +32163,21 @@
 You are welcome to tell me this is sentimental and that price comparison at seven predicts nothing. That's a real answer and I'd rather have it than silence. But if you think there's something in it, a sentence from an economist who has actually studied consumer financial markets does more for this than a hundred nice reviews from parents.
 The flipbook takes four minutes: https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan Bach
-Baltimore</t>
+Baltimore
+----- Whales long-form version -----
+Professor Mahoney — your work is about what consumers actually do when a price is put in front of them, as opposed to what a model says they should. I want to ask about the earliest version of that decision, because nobody seems to study it.
+A six-year-old with a birthday five in an aisle is running a comparison with no price history, no reference class and no idea that anchoring exists. She is the purest case your field could ask for and the least documented. Meanwhile the environment is not naive at all — a boardwalk claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the child has no way of knowing the $9.99 exists.
+Financial education answers this by teaching saving. But saving is the second thing a person does with money; the first is spending, and it is taught last or not at all.
+I wrote the picture book rather than the paper. Clarence Gets a Bargain follows one complete purchase — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with the choice afterward. Sixteen-plus concepts, none announced. Twenty-one terms in a back-matter glossary, each page-referenced to the scene it came from. Catalogued Lexile AD 620L — Adult Directed — so the reading is a joint activity by design rather than a solo one.
+The question I would genuinely like answered: is there work on when price competence forms, and whether early exposure to comparison changes anything measurable later? If the honest answer is that it is unstudied because it is unmeasurable at that age, that is worth knowing too.
+clarencegetsabargain.com/book-facts.html
+Jonathan Bach
+Attorney and children's book author, Baltimore</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>Subject: Applied micro, twenty years early · Long-form version from Jump$tart</t>
+          <t>Subject: Applied micro, twenty years early · Long-form version from Jump$tart | Subject: Applied micro, twenty years early · Long-form version from Whales long-form</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr"/>
@@ -31087,8 +32224,24 @@
           <t>Bina — community engagement at the SF Fed is where household financial capability actually gets measured. Mine teaches the spending half, on the theory the sequence is backwards. Does that square with what you see? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K58" s="5" t="inlineStr"/>
-      <c r="L58" s="5" t="inlineStr"/>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>Bina — a question about where community development work draws its lower age bound.
+Most financial capability programming aimed at low- and moderate-income families reaches adults, or reaches children through savings vehicles — child savings accounts, matched savings, college accounts. All of that is aimed at accumulation. Very little addresses the other side of the household ledger at a child's level: what happens when the money is spent, which for a child is nearly all of it.
+That gap has a sequencing problem behind it. Saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has handled money at a register, and the decision she made there was unassisted.
+I built the elementary resource. A 36-page picture book that follows one complete purchase — sale ads, comparison shopping, a markdown, a coupon, sales tax, and living with what was bought — with sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story. Behind it, a free ungated classroom and family set crosswalked to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE and FDIC Money Smart. No account, no email capture, no purchase order; it prints from a browser, which matters where budgets do not exist.
+Catalogued Lexile AD 620L — Adult Directed — so it works as a shared read with a caregiver who does not need to know the material first, which is the design constraint that mattered most to me.
+The question: does SF Fed's community engagement work touch the elementary band, or does it start at the account level with adults?
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan Bach
+Attorney and children's book author, Baltimore</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M58" s="5" t="inlineStr"/>
       <c r="N58" s="5" t="inlineStr"/>
     </row>
@@ -31191,8 +32344,23 @@
           <t>Jennifer — Harlem Children's Zone is deliberate about what earns a kid's time. Mine teaches the complete purchase, sales tax included, and the family activity was built for a kitchen table rather than a classroom. Fit your programming, or your development conversations? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K60" s="5" t="inlineStr"/>
-      <c r="L60" s="5" t="inlineStr"/>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>Jennifer — a funding-shaped question rather than an ask, and the resource itself is already free.
+I wrote and illustrated a K–5 financial-literacy picture book and built the entire classroom program behind it — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a standards crosswalk across five frameworks. All of it is ungated: no account, no email capture, no purchase order, prints from a browser. The only thing that ever costs anything is the physical books, and 25 copies run $499.75.
+The content premise: every children's money book teaches saving, and saving is the second thing a child does with money. The first is spending — a first grader has stood at a register and chosen. The book follows one complete purchase from the idea through the receipt, with sixteen-plus concepts hidden in the plot and a twenty-one-term glossary page-referenced back into the story.
+Why I am writing to development rather than to a classroom: this is unusually easy to fund. A bank or credit union sponsoring a classroom set gets its name on every book that goes home to a family in its assessment area, the curriculum costs the sponsor nothing because it is already free, and I have a CRA-ready memo written in examiner-friendly language. A funder can point at 25 books, one classroom, and a pre/post instrument.
+Catalogued Lexile AD 620L — Adult Directed — which also makes it a family-engagement asset rather than only a classroom one, since the book works at a kitchen table with a parent or a grandparent doing the reading.
+Is a sponsored classroom set something HCZ's funders would recognise, or does everything need to attach to an existing program line?
+clarencegetsabargain.com/resources/grant-in-a-box.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M60" s="5" t="inlineStr"/>
       <c r="N60" s="5" t="inlineStr"/>
     </row>
@@ -31237,8 +32405,23 @@
           <t>Flora — JA reaches more kids than almost anybody, and elementary is usually where the material thins out. Mine is a K-5 picture book with a free zero-prep classroom pack against five frameworks, teaching spending rather than saving. Fit anything JA Alaska runs? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K61" s="5" t="inlineStr"/>
-      <c r="L61" s="5" t="inlineStr"/>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>Flora — JA runs volunteers into elementary classrooms better than any organisation in the country, so this is a materials question rather than a pitch.
+JA's elementary programs are strong on earning, jobs and community. What is thin across the whole field — not just JA — is spending, and specifically the transaction itself. A first grader has no savings rate and no job. What she has done is stand at a register holding money and choose.
+Clarence Gets a Bargain is a 36-page picture book that puts the entire transaction on the page: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
+The part that matters for a volunteer model: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, with every concept explained inside the text by the mother. A volunteer who has never taught anything can read it cold and answer questions off the page. Nothing to memorise and no prep call. Behind it, free and ungated: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable price tags and clearance stickers for a classroom store, and a browser-based pretend register with a markdown, a coupon and sales tax.
+Alaska has its own complications on distance and travel, and virtual read-alouds work for this.
+Does a read-aloud fit how JA Alaska builds a volunteer session, or does everything have to run through national curriculum?
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M61" s="5" t="inlineStr"/>
       <c r="N61" s="5" t="inlineStr"/>
     </row>
@@ -31283,8 +32466,24 @@
           <t>Elizabeth — financial education at the Department of Education is the mission my book starts on, just twelve years early. Mine is K-5, teaching spending rather than saving, against five frameworks. Fit any program you touch, or a steer on who'd know? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K62" s="5" t="inlineStr"/>
-      <c r="L62" s="5" t="inlineStr"/>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>Elizabeth — a scope question rather than a pitch.
+Federal attention to financial education, like every state mandate, concentrates on high school. Thirty states now require a course to graduate. The elementary standards that exist in most states sit underneath that with very little built against them, largely because nothing requires reporting at that band.
+The assumption underneath is that children begin with saving. Saving is the second thing a person does with money. The first is spending — a first grader has handled money at a register and made a decision there with no framework at all.
+I built a free, ungated K–5 resource for that: a 36-page picture book that follows one complete purchase from the idea through the receipt — sale ads, comparison shopping, a markdown, a coupon, sales tax — and a classroom set behind it. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a browser-based pretend register, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education alongside Common Core Math and ELA, CEE and FDIC Money Smart, cited at the Grade 4 benchmark level rather than claimed generally.
+No account, no email capture, no purchase order. It prints from a browser. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud requiring no instructor training.
+The question: does any Department program or clearinghouse take elementary financial-education material, or is the practical route through the states? A steer on who would know is as useful to me as an answer.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan Bach
+Attorney and children's book author, Baltimore</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M62" s="5" t="inlineStr"/>
       <c r="N62" s="5" t="inlineStr"/>
     </row>
@@ -31329,8 +32528,24 @@
           <t>Gene — Troutwood makes the financial future tangible for young people. Mine makes the present tangible for a six-year-old: one purchase, compared and paid for, tax included. Does the approach fit what you're building, or sit below it? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K63" s="5" t="inlineStr"/>
-      <c r="L63" s="5" t="inlineStr"/>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>Gene — Troutwood is built on showing people the long arc of a decision, which is why I am writing about the very first decision on that arc.
+Everything in financial planning compounds, including the mistakes, and the compounding starts long before anyone opens an account. Mistakes at eleven cost $14. The same mistake at twenty-seven has a credit card attached. The habit doing the compounding was installed at six, in a store, with a parent saying no and no reasoning attached to the no.
+Financial education answers that by teaching children saving. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with no framework at all.
+Clarence Gets a Bargain is the picture book for that. One purchase, followed the whole way: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
+Catalogued Lexile AD 620L — Adult Directed — so it is a shared read, and the parent gets handed the script rather than a homework assignment.
+The claim I would defend hardest is the delayed one, and it is the same claim Troutwood makes about projections: the value is not in the twenty minutes. It is in month eighteen, in a real store, when the kid hits a money moment and the book fires back. Recognition first, then the habit.
+Does the elementary end fit anything Troutwood does, or is that below the floor?
+clarencegetsabargain.com/book-facts.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M63" s="5" t="inlineStr"/>
       <c r="N63" s="5" t="inlineStr"/>
     </row>
@@ -31375,8 +32590,23 @@
           <t>Rob — you create financial education resources, so you know what teachers actually use versus what they politely download once. Mine is a K-5 picture book with four zero-prep lessons, assessments, and a 23-row crosswalk, all free and ungated. Fit your catalog, or duplicate it? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K64" s="5" t="inlineStr"/>
-      <c r="L64" s="5" t="inlineStr"/>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>Rob — you build resources teachers actually use, which is a harder job than writing curriculum and a rarer one. I built the elementary thing that does not exist, and I want a practitioner's read on whether it survives a real classroom.
+The gap: every mandate lands in high school, so that is where every resource goes. The elementary standards exist and almost nothing is built against them. And the field starts children with saving, when saving is the second thing a person does with money — the first is spending, and a first grader has already done it at a register.
+Clarence Gets a Bargain is a 36-page picture book following one complete purchase: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken on purpose, a coupon at the register, sales tax, and living with what was bought. Sixteen-plus concepts, none announced. Kids smell a worksheet one page in; they never smell this one. A twenty-one-term glossary in the back, page-referenced to the story.
+The teacher side is where I would want your opinion. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row standards crosswalk, printable price tags and clearance stickers for a classroom store, and a browser-based register that runs a markdown, a coupon and sales tax with the total changing in front of the class. Ungated — no account, no email capture — and it prints from a browser. Catalogued Lexile AD 620L, Adult Directed: one class period, no teacher training, and the text carries every explanation.
+The whole thing rests on one instruction a teacher can act on the same week: stop bringing kids to the store as cargo, bring them as staff. Every activity in the set is a version of that.
+The honest question: what makes a free teacher resource actually get used rather than downloaded and forgotten? You have watched that happen more times than I have, and I would rather fix it now.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M64" s="5" t="inlineStr"/>
       <c r="N64" s="5" t="inlineStr"/>
     </row>
@@ -31421,8 +32651,24 @@
           <t>Martin — Chair-Elect of the CFP Board means a kids' picture book is a long way upstream of your day. That's rather the point. Spending is the first money skill a kid uses, nobody wrote the picture book for it, so I did. Five frameworks, K-5. Does it fit the early-education push the field keeps talking about, or is that talk? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K65" s="5" t="inlineStr"/>
-      <c r="L65" s="5" t="inlineStr"/>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>Martin — you sit where the profession decides what it is responsible for, so this is a question about the far upstream end of that responsibility.
+Planners meet clients' children late, usually at the worst possible moment, and by then the habits are twenty years old. They were formed at six, in a store, with a parent saying no and no reasoning attached to the no.
+The field's answer to that is to teach children saving. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, holding a birthday five, deciding whether the thing is worth what it costs.
+I wrote the picture book for that moment. Clarence Gets a Bargain follows one purchase the whole way — earning the reward through chores and grades, working the sale ads at the kitchen table, comparing two models on a shelf, taking the cheaper one on purpose, redeeming a coupon, meeting sales tax, and then living with what was bought. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in a back-matter glossary, page-referenced to the story.
+And on page 6 there is something I have not found in any other picture book: a 529 plan. In the plot. Explained by a mother, eye-rolled at by a kid, defended by a father two scenes later.
+Catalogued Lexile AD 620L — Adult Directed, so a planner handing it to a client family is handing over a script rather than an assignment. Twenty-five copies run $499.75, and the educator program behind it is free.
+The question: does CFP Board's pro bono and public-education work reach below high school at all, or is that considered somebody else's ground?
+clarencegetsabargain.com/book-facts.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M65" s="5" t="inlineStr"/>
       <c r="N65" s="5" t="inlineStr"/>
     </row>
@@ -31467,8 +32713,23 @@
           <t>Ed — a director at the Department of Education is exactly who I want on this. Mine is K-5, teaching spending rather than saving, with free standards-aligned lessons and nothing to reorder. Fit any program you touch, or a steer on who'd know? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K66" s="5" t="inlineStr"/>
-      <c r="L66" s="5" t="inlineStr"/>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>Ed — a narrow question about evidence standards, asked before I go further with something.
+I have built a free K–5 financial-education resource — a 36-page picture book plus a complete classroom set — and crosswalked it to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE and FDIC Money Smart, at the Grade 4 benchmark level. Everything is ungated: no account, no email capture, no purchase order, and it prints from a browser.
+The content premise is that the field has the sequence backwards. Financial education starts children with saving; saving is the second thing a person does with money. The first is spending, and a first grader has already done it at a register. The book follows one complete purchase from the idea through the receipt — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with what was bought.
+One structural detail relevant to evaluation: the book is catalogued Lexile AD 620L — Adult Directed — so it is delivered as a shared read between an adult and a child rather than independent reading. That makes it closer to a shared-reading intervention than a curriculum, which may change what kind of evidence would be appropriate.
+The question: what would a resource like this need in order to be taken seriously on evidence — a pre/post instrument administered at scale, a quasi-experimental design, something else? I would rather build the right study once than assemble the wrong one. And if the honest answer is that no federal pathway exists for elementary material of this kind, that is worth knowing too.
+clarencegetsabargain.com/educator-toolkit.html
+Jonathan Bach
+Attorney and children's book author, Baltimore</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M66" s="5" t="inlineStr"/>
       <c r="N66" s="5" t="inlineStr"/>
     </row>
@@ -31513,8 +32774,24 @@
           <t>Jeff — you lead consumer and community research at the Fed, so you study exactly the gaps my book tries to prevent. Mine argues spending competence precedes saving competence and is taught almost nowhere. Does that square with your research? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K67" s="5" t="inlineStr"/>
-      <c r="L67" s="5" t="inlineStr"/>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>Jeff — a question about scope, from someone who has read the SHED closely enough to know what it does and does not ask.
+The survey measures financial outcomes in adults — emergency savings, credit access, unexpected expenses. Those outcomes have long histories. What I have not been able to find, in the SHED or elsewhere, is any measure of when spending competence forms: the ability to stand in front of two prices and choose deliberately rather than by impulse or brand.
+That matters because financial education for children is built almost entirely around saving, and saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has handled money at a register.
+I wrote the elementary resource rather than a paper about it. A 36-page picture book that follows one complete purchase — sale ads, comparison shopping, a markdown, a coupon, sales tax, and living with what was bought — plus a free ungated classroom set crosswalked to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE, and FDIC Money Smart. Sixteen-plus concepts, none announced in the text. A twenty-one-term glossary page-referenced into the story.
+For the record on format: Lexile AD 620L, Adult Directed — an adult reads it with the child rather than handing it over.
+The question is narrow. Is there any Federal Reserve work, published or internal, on childhood price competence and later financial outcomes? If it does not exist, that is an answer too, and it tells me whether I am arguing with a consensus or filling a hole.
+clarencegetsabargain.com/book-facts.html
+Jonathan Bach
+Attorney and children's book author, Baltimore</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M67" s="5" t="inlineStr"/>
       <c r="N67" s="5" t="inlineStr"/>
     </row>
@@ -31559,8 +32836,23 @@
           <t>Annie — My First Nest Egg and Clarence chase the same kid. Yours is the account; mine is the trip to the store. Spending rather than saving, one purchase, ad to register. Complementary, I think. Worth comparing notes, or trading copies? One spec worth knowing: Lexile AD 620L — AD is Adult Directed, the industry's code for a book meant to be read WITH a kid rather than handed over. Mom explains everything inside the text, so the adult reading gets handed the script. Teacher, parent or grandparent, same result. More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
-      <c r="K68" s="5" t="inlineStr"/>
-      <c r="L68" s="5" t="inlineStr"/>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>Annie — you built a product for the exact age band everyone else in this category skips, so you already believe the thing I have been arguing. I want to compare notes rather than pitch you.
+My First Nest Egg puts save, spend, give and invest in front of a young child in physical form. My argument is about which of those a child actually performs first. It is spending — a six-year-old has stood in a store holding money and chosen, years before she has anything to save or invest. The category teaches saving first anyway, and I could not find the book that teaches the other one.
+So I wrote and illustrated it. Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
+Catalogued Lexile AD 620L — Adult Directed — read-with rather than read-alone, so the parent gets handed the script. And there is a free browser-based pretend register behind it that runs a markdown, a coupon and sales tax, which is the closest thing I have to your physical product.
+Those look complementary rather than competing to me: yours gives a kid the categories in their hands, mine walks them through the mechanics of one transaction in twenty minutes.
+Worth a conversation about whether they belong near each other? And separately — if you think spending-before-saving is wrong, you are one of very few people whose disagreement would actually change my mind.
+https://heyzine.com/flip-book/eeb1ef6cff.html
+Jonathan</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>Long-form version from Whales long-form</t>
+        </is>
+      </c>
       <c r="M68" s="5" t="inlineStr"/>
       <c r="N68" s="5" t="inlineStr"/>
     </row>

--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -3395,7 +3395,7 @@
 Sammy teaches saving, and teaches it better than anything else aimed at this age. My argument is not about quality; it is about order. Saving is the second thing a child does with money. The first is spending — a first grader has stood at a register holding money and chosen, years before she has anything to save. Teach that moment first, and everything Sammy preaches lands harder, because a kid who understands what money buys has a reason to keep some.
 That is the book I wrote. Clarence Gets a Bargain follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the scene each term came from.
 Catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, with every concept explained inside the text, so somebody can read it cold to a class. You will recognise why that mattered to me.
-You also solved a distribution problem the rest of us have not: banks and credit unions sponsor the visits and buy the books, and their community reports write themselves. I would genuinely rather learn that from you than reverse-engineer it.
+You also solved a distribution problem the rest of us have not: banks and credit unions sponsor the visits and buy the books, and their community reports write themselves. I would rather learn that from you than reverse-engineer it.
 Trade copies and compare notes? I will read Sammy properly and tell you the truth about it, which is the only thing worth trading.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -9812,7 +9812,7 @@
 A six-year-old with a birthday five in an aisle is running a comparison with no price history, no reference class and no idea that anchoring exists. She is the purest case your field could ask for and the least documented. Meanwhile the environment is not naive at all — a boardwalk claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the child has no way of knowing the $9.99 exists.
 Financial education answers this by teaching saving. But saving is the second thing a person does with money; the first is spending, and it is taught last or not at all.
 I wrote the picture book rather than the paper. Clarence Gets a Bargain follows one complete purchase — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with the choice afterward. Sixteen-plus concepts, none announced. Twenty-one terms in a back-matter glossary, each page-referenced to the scene it came from. Catalogued Lexile AD 620L — Adult Directed — so the reading is a joint activity by design rather than a solo one.
-The question I would genuinely like answered: is there work on when price competence forms, and whether early exposure to comparison changes anything measurable later? If the honest answer is that it is unstudied because it is unmeasurable at that age, that is worth knowing too.
+The question I would actually like answered: is there work on when price competence forms, and whether early exposure to comparison changes anything measurable later? If the honest answer is that it is unstudied because it is unmeasurable at that age, that is worth knowing too.
 clarencegetsabargain.com/book-facts.html
 Jonathan Bach
 Attorney and children's book author, Baltimore</t>
@@ -28308,18 +28308,18 @@
         </is>
       </c>
       <c r="I666" s="5" t="n">
-        <v>2819</v>
+        <v>2933</v>
       </c>
       <c r="J666" s="5" t="inlineStr">
         <is>
           <t>Christine,
-You're closing September, Grandparents Day lands on the 13th, and I have a piece for it that isn't about a gift. It's about an afternoon.
+You're closing September, Grandparents Day is the 13th, and every other pitch on your desk this week is a gift guide. Mine is an afternoon.
 I'm an attorney, a mixed-media artist, and a dad, and I wrote and illustrated a children's picture book called Clarence Gets a Bargain. Ages 6–10. A boy earns a robot with chores and grades, then has to figure out how to buy it — sale ads at the kitchen table, two models compared on a shelf, the cheaper one taken on purpose, a coupon handed to the cashier, and sales tax showing up uninvited at the end.
-Here's the part your readers own. Every children's money book teaches saving. Piggy banks, jars, three little tins labeled spend-save-give where "spend" gets one page and a guilty look. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding a birthday five, deciding whether the thing is worth what it costs. We teach the second thing first and the first thing never.
+Your readers own the next part. Every children's money book teaches saving. Piggy banks, jars, three little tins labeled spend-save-give where "spend" gets one page and a guilty look. But saving is the second thing a child does with money; the first is spending, and a six-year-old has already done it, in a store, holding a birthday five, deciding whether the thing is worth what it costs. We teach the second thing first and the first thing never.
 Grandparents are the only people left who can teach the first one from experience. You clipped coupons back when it was a survival skill rather than a hobby. You remember layaway. You know what your first paycheck was and exactly what it wouldn't cover. Those stories are the best money curriculum a child will ever get and they have nowhere to land — until a book puts a kid in a store and every page comes with a "that reminds me of the time" already sitting in it.
-The format is the argument. The book is catalogued Lexile AD 620L, and the AD means Adult Directed — the industry's own code for a book meant to be read WITH a child, not handed to one. You're not optional equipment. You're cast. Mom explains everything inside the story, so the grandparent reading aloud gets handed the script and can take the credit for knowing it. Twenty minutes out loud, interrupted the whole way, and the interruptions are the point: "Do we have a 529?" "Why do you take pictures of receipts?" "Can I hand the cashier the coupon next time?"
-And two of the games in it can't be played alone. Page 27: whoever spots the biggest savings at the grocery store wins, loser carries the bags in from the car. Page 28: after dinner somebody shares a deal they got that day and everyone guesses the price. Three players minimum. Grandma counts.
-I'd write it for you as 800–1,200 words — "What Grandparents Can Teach About Money That Nobody Else Can" — with the games as a sidebar readers can tear out and use. Or if you'd rather run it as a product review, the book is $19.99, 36 pages, hardbound, and I'll send a copy today either way.
+The book is catalogued Lexile AD 620L, and the AD means Adult Directed — the industry's own code for a book meant to be read WITH a child rather than handed to one. It needs a grown-up in the room. You're cast. Mom explains everything inside the story, so the grandparent reading aloud gets handed the script and can take the credit for knowing it. Twenty minutes out loud, interrupted the whole way, and the interruptions are the point: "Do we have a 529?" "Why do you take pictures of receipts?" "Can I hand the cashier the coupon next time?"
+And two of the games in it can't be played alone. Page 27: whoever spots the biggest savings at the grocery store wins, loser carries the bags in from the car. Page 28: after dinner somebody shares a deal they got that day and everyone guesses the price. Kids' guesses are unhinged. A gallon of milk goes for $45; a car for $100. The reveal face is the whole entertainment. Three players minimum. Grandma counts.
+I'd write it for you as 800–1,200 words, under the title "What Grandparents Can Teach About Money That Nobody Else Can," with the games as a sidebar readers can tear out and use. Or if you'd rather run it as a product review, the book is $19.99, 36 pages, hardbound, and I'll send a copy today either way.
 Which is more useful to you?
 Jonathan Bach
 Author &amp; illustrator, Clarence Gets a Bargain
@@ -28370,7 +28370,7 @@
       </c>
       <c r="H667" s="5" t="inlineStr"/>
       <c r="I667" s="5" t="n">
-        <v>2724</v>
+        <v>2749</v>
       </c>
       <c r="J667" s="5" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
 I'm writing to you rather than to a gift guide, and here's the difference. Your whole editorial line is that a good grandparent supports the parents instead of running past them. This book does that structurally. Mom is the one who teaches Clarence in the story — the sale ads, the markdown, the coupon, the sales tax. A grandparent reading it aloud is reading the parent's lines, not competing with them.
 The format backs that up. It's catalogued Lexile AD 620L, and AD stands for Adult Directed — the trade's own code for a book meant to be read WITH a child rather than handed over. It doesn't work in the corner. It works on a couch, with somebody's grandkid interrupting every third page. And because Mom explains every concept inside the text, the grandparent doesn't have to be confident about money to run it. The script is on the page. Take the credit.
 Two of the games in the back half need other people, which I did on purpose. Page 27: everyone hunts for the biggest savings on the next grocery run, loser carries the bags in from the car. Page 28: after dinner someone shares a deal they got that day and everybody guesses the price. Three players minimum. Grandma counts.
-And if you're the grandparent who quietly opened the 529 — page 6 is your victory lap. Read it twice.
+And if you're the grandparent who opened the 529 and never mentioned it to anyone — page 6 is your victory lap. Read it twice.
 You run two pages that this could belong on: Best Books on Grandparenting, and Gifts for Grandchildren. I'd rather be on the first one than the second, because the pitch isn't "buy this for them," it's "here's something to do with them." But you know your readers and I don't.
 Would you take a look? I'll mail you a hardback this week, no strings and no expectation. $19.99, 36 pages, and I did the art, so all the blame is in one place.
 Jonathan Bach
@@ -31440,7 +31440,7 @@
 Sammy teaches saving, and teaches it better than anything else aimed at this age. My argument is not about quality; it is about order. Saving is the second thing a child does with money. The first is spending — a first grader has stood at a register holding money and chosen, years before she has anything to save. Teach that moment first, and everything Sammy preaches lands harder, because a kid who understands what money buys has a reason to keep some.
 That is the book I wrote. Clarence Gets a Bargain follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the scene each term came from.
 Catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, with every concept explained inside the text, so somebody can read it cold to a class. You will recognise why that mattered to me.
-You also solved a distribution problem the rest of us have not: banks and credit unions sponsor the visits and buy the books, and their community reports write themselves. I would genuinely rather learn that from you than reverse-engineer it.
+You also solved a distribution problem the rest of us have not: banks and credit unions sponsor the visits and buy the books, and their community reports write themselves. I would rather learn that from you than reverse-engineer it.
 Trade copies and compare notes? I will read Sammy properly and tell you the truth about it, which is the only thing worth trading.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -32169,7 +32169,7 @@
 A six-year-old with a birthday five in an aisle is running a comparison with no price history, no reference class and no idea that anchoring exists. She is the purest case your field could ask for and the least documented. Meanwhile the environment is not naive at all — a boardwalk claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the child has no way of knowing the $9.99 exists.
 Financial education answers this by teaching saving. But saving is the second thing a person does with money; the first is spending, and it is taught last or not at all.
 I wrote the picture book rather than the paper. Clarence Gets a Bargain follows one complete purchase — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with the choice afterward. Sixteen-plus concepts, none announced. Twenty-one terms in a back-matter glossary, each page-referenced to the scene it came from. Catalogued Lexile AD 620L — Adult Directed — so the reading is a joint activity by design rather than a solo one.
-The question I would genuinely like answered: is there work on when price competence forms, and whether early exposure to comparison changes anything measurable later? If the honest answer is that it is unstudied because it is unmeasurable at that age, that is worth knowing too.
+The question I would actually like answered: is there work on when price competence forms, and whether early exposure to comparison changes anything measurable later? If the honest answer is that it is unstudied because it is unmeasurable at that age, that is worth knowing too.
 clarencegetsabargain.com/book-facts.html
 Jonathan Bach
 Attorney and children's book author, Baltimore</t>

--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -2111,8 +2111,8 @@
           <t>Andrew — your audience is adults fixing money habits. I wrote the book that tries to stop the habits forming, and there is an episode in the argument whether or not the book is in it.
 Every children's money book teaches saving. Piggy banks, lemonade stands, three jars. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding a birthday five, working out whether the thing is worth what it costs.
 Nobody put that in a story. So I did. Clarence Gets a Bargain follows a single purchase the whole way — a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax and regards it as a personal insult, then lives with the thing he chose. Idea to post-receipt.
-Sixteen-plus concepts and none of them announced. Nobody in the book says "budget," which for a book largely about budgeting took some doing. Kids smell a worksheet one page in; they never smell this one, because they are laughing too hard to notice. The reveal is the glossary — twenty-one terms in the back, page-referenced to the scene each came from.
-Catalogued Lexile AD 620L — Adult Directed, so it is a read-with, which means the parent listening to your show gets handed the script rather than a homework assignment.
+Sixteen-plus concepts and none of them announced. Nobody in the book says "budget," which for a book largely about budgeting took some doing. Kids smell a worksheet one page in; they never smell this one, because they are laughing too hard to notice. The reveal is the glossary — twenty-one terms in the back, page-referenced to the scene each came from. It is catalogued AD 620L, Adult Directed, so the parent listening to your show gets handed the script rather than a homework assignment.
+Their books are about earning and saving, which is fine, but there is no game in a piggy bank and kids know it.
 The episode I would pitch is not the book. It is the forty-year hole: an entire publishing category taught children to save and skipped the cash register, the only place a child has ever actually handled money.
 Worth twenty minutes of your show? https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -2170,7 +2170,7 @@
       <c r="K25" s="5" t="inlineStr">
         <is>
           <t>Amy — two requests come to your desk all week. A kid wants a robot book. A parent wants something that teaches money. I wrote the one that answers both in a single checkout.
-Clarence Gets a Bargain is a 36-page picture book, ages 6–10, that follows one kid through one complete purchase: he earns a robot reward with chores and grades, does his shopping homework in the newspaper sale ads, comparison-shops the aisle, finds the markdown, hands a coupon to the cashier, meets sales tax, and watches his mother photograph the receipt before the car leaves the lot. Kids read it as a robot story. Sixteen-plus money concepts come along without announcing themselves, and the back matter carries a twenty-one-term glossary where each definition points to the page where the term happens in the plot — a decoder rather than an appendix.
+Clarence Gets a Bargain is a 36-page picture book, ages 6–10, that follows one kid through one complete purchase: he earns a robot reward with chores and grades, does his shopping homework in the newspaper sale ads, comparison-shops the aisle, finds the markdown, hands a coupon to the cashier, meets sales tax, and watches his mother photograph the receipt before the car leaves the lot. Kids read it as a robot story. Saving is the second thing a child does with money; the first is spending, and this is the book for that. Sixteen-plus money concepts come along without announcing themselves, and the back matter carries a twenty-one-term glossary where each definition points to the page where the term happens in the plot — a decoder rather than an appendix.
 The collection case, with the qualifier a librarian will appreciate: most money picture books cover earning or saving. To my knowledge this is the first narrative picture book for this age band that traces the whole consumer arc, wish through receipt. It fills a hole rather than adding a fourth piggy-bank book to the shelf.
 Cataloguing: ISBN 979-8-234-07638-0 · LCCN 2026906164 · hardbound, case bound, full colour, 11×8.5′′ · Est. Lexile AD 620L, Guided Reading L–N · $19.99. The AD is Adult Directed, which makes it a storytime title and a family take-home at the same time. Every fact is on one page: clarencegetsabargain.com/book-facts.html
 Programming is already built and free — printable price tags and clearance stickers for a pretend store, a browser-based register kids run themselves, a five-question quiz with a printable certificate. A storytime plus the pretend store is a complete Money Smart Week event with no prep budget.
@@ -2231,7 +2231,7 @@
         <is>
           <t>Sarah — a collection-development pitch, kept to the facts because I know what August looks like at your desk.
 Clarence Gets a Bargain is a 36-page picture book, ages 6–10, following one kid through one complete purchase: earning the robot reward, doing shopping homework in the newspaper sale ads, comparison shopping the aisle, finding the markdown, handing a coupon to the cashier, paying the sales tax, and watching his mother photograph the receipt before the car leaves the parking lot. Sixteen-plus money concepts ride inside the plot. Nobody in the book says the word "budget."
-The case for the shelf: nearly every money picture book teaches earning or saving. To my knowledge this is the first narrative picture book for this band that follows the whole consumer arc, wish through receipt. The back matter carries a twenty-one-term glossary in which every definition cites the page where the term happens in the story, so a child looking something up lands in a scene rather than a definition list.
+The case for the shelf: nearly every money picture book teaches earning or saving, which is the second thing a child does with money. Spending is the first. To my knowledge this is the first narrative picture book for this band that follows the whole consumer arc, wish through receipt. The back matter carries a twenty-one-term glossary in which every definition cites the page where the term happens in the story, so a child looking something up lands in a scene rather than a definition list.
 Cataloguing: ISBN 979-8-234-07638-0 · LCCN 2026906164 · hardbound, case bound, full colour, 11×8.5′′ · Est. Lexile AD 620L, Guided Reading L–N · $19.99. Full record at clarencegetsabargain.com/book-facts.html. The AD in that Lexile stands for Adult Directed, so it does double duty as a read-aloud title and a take-home.
 Programming, already built and free: printable price tags and clearance stickers for a pretend store, a browser-based Sea-Mart register children operate themselves with a markdown, a coupon and sales tax, and a quiz with a printable certificate. No prep budget required for a Financial Literacy Month or Money Smart Week event.
 Endorsed by a K–5 educator with 30+ years in the classroom and by the 2026 EIFLE Educator of the Year.
@@ -2293,8 +2293,7 @@
           <t>Gretchen — you have spent a career on how financial products get sold to people who don't fully understand them. Here is the entry-level version of that, and nobody covers it.
 A child becomes a consumer the first time money leaves their hand. Six years old, a birthday five, a store. From that moment they are a party to transactions, and the entire financial education apparatus treats them as a saver in training instead. We teach them to hold money. Nobody teaches them what happens when they use it.
 The scale is small and the mechanics are identical to the ones you write about. A claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the child has no way of knowing that. Not a game of skill — a slot machine wearing a carnival hat, aimed at someone with no price memory and no comparison to make.
-I wrote the picture book for it. One kid, one purchase, followed the whole way: he wants a robot, earns it, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget." The child works out he has been schooled only when he reaches the glossary — twenty-one terms in the back, each page-referenced to where it happened.
-The format matters: Lexile AD 620L. The AD is Adult Directed, the trade's own code for a book meant to be read with a child rather than handed over.
+I wrote the picture book for it. One kid, one purchase, followed the whole way: he wants a robot, earns it, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget." The child works out he has been schooled only when he reaches the glossary — twenty-one terms in the back, each page-referenced to where it happened. It is catalogued Lexile AD 620L, where AD stands for Adult Directed — the trade's own code for a book an adult reads with a child rather than hands over.
 The story is not the book. It is that an entire publishing category taught children to save for forty years and skipped the register, which is the only place a child has ever handled money — while the arcade, the app store and the checkout lane did not skip it at all.
 Is there anything there? clarencegetsabargain.com/press-kit.html
 Jonathan</t>
@@ -2354,9 +2353,8 @@
           <t>Kim — you cover retail, so you already know the boardwalk arcade is a pricing strategy rather than a game. I wrote the children's book that explains it before a kid loses to it.
 The number I keep coming back to: a claw machine takes $25 to hand back a basketball that Walmart sells for $9.99. That is the entire business model in one glass box — charge $25 for the $9.99 thing and make it feel like winning. Once a kid has seen the $9.99, the claw loses its grip. Nobody shows them the $9.99.
 Every children's money book teaches saving. Piggy banks, jars, three little tins labeled spend-save-give where "spend" gets one page and a guilty look. But saving is the second thing a child does with money. The first is spending, and a six-year-old has done it already, standing in a store, deciding.
-So mine follows a single purchase the entire distance. A boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one deliberately, hands a coupon to the cashier, meets sales tax, and then lives with the thing. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
-It is catalogued Lexile AD 620L — Adult Directed, meaning read-with rather than read-alone, so the parent gets handed the script instead of being expected to know it.
-The retail angle, if you want one: every trick your beat covers — the fake markdown, the anchor price, the "newest is better" framing — gets run on children first, in arcades and toy aisles, where there is no consumer press at all.
+So mine follows a single purchase the entire distance. A boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one deliberately, hands a coupon to the cashier, meets sales tax, and then lives with the thing. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed, so the parent reads it with the kid and gets handed the script instead of being expected to know it.
+The retail angle, if you want one: every trick your beat covers — the fake markdown, the anchor price, the "newest is better" framing — gets run on children first, in arcades and toy aisles, where there is no consumer press at all. The boardwalk airbrush stand charges $28 for a shirt that says BRAYDEN. Your kid's name is not Brayden.
 Worth a look? clarencegetsabargain.com/book-facts.html
 Jonathan</t>
         </is>
@@ -2474,10 +2472,10 @@
       <c r="K30" s="5" t="inlineStr">
         <is>
           <t>Amanda — Planet Money's whole trick is that people will sit still for an economics lesson if it is hidden inside a story about a person and a thing. I did that at a first-grade reading level, and I am writing about the story rather than the book.
-Every children's money book teaches earning or saving. All 25 on the ABA Foundation's list — I read them to be sure. A piggy bank, a lemonade stand, a lesson. Not one covers the cash register, which is the only place a child has ever actually handled money.
-Mine does. A boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, gets ambushed by sales tax, and then lives with what he bought. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget." They do not realise they have been schooled until they hit the glossary in the back — twenty-one terms, each page-referenced to the moment it happened. That is where the con comes apart, on purpose.
-Format note, since you make things people take in together: Lexile AD 620L, where AD means Adult Directed — a book built to be read with a child, interrupted the whole way.
-The segment is the forty-year hole. A whole publishing category taught children to save and skipped the register, while every arcade, app store and checkout lane aimed at children did not skip it at all.
+Every children's money book teaches earning or saving. All 25 on the ABA Foundation's list — I read them to be sure. A piggy bank, a lemonade stand, a lesson. Not one covers the cash register. Saving is the second thing a child does with money; spending is the first, and the register is the only place a child has ever actually handled any.
+Mine does. A boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, gets ambushed by sales tax, and then lives with what he bought. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget." They do not realise they have been schooled until they hit the glossary in the back — twenty-one terms, each page-referenced to the moment it happened. That is where the con comes apart, on purpose. It is catalogued AD 620L — Adult Directed — which is the trade's way of saying it only works out loud, with somebody interrupting.
+The numbers on the other side are absurd and nobody has ever put a microphone on them. Twelve hundred arcade tickets for a rubber slinky is an exchange rate that would embarrass a currency trader, and the kid making that trade has no idea he is trading.
+The segment is the forty-year hole. A whole publishing category taught children to save and skipped the register, while every arcade, app store and checkout lane aimed at children did not skip it at all. Nobody regulates the toy aisle and nobody covers it.
 Is that an episode whether or not my book is in it? Four-minute flip: https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
         </is>
@@ -2536,7 +2534,7 @@
           <t>Bethann — you run the education side of a bankers association, which means you are the person who decides what volunteers actually carry into a classroom. I built something for the grade band most bank programs skip.
 Most financial education a bank sponsors lands in high school or in a "teach a child to save" day about saving. Saving is the second thing a child does with money. The first is spending, and a first grader has done it, at a register, with a parent behind her. There is almost nothing to hand a banker walking into a second-grade room about that.
 Clarence Gets a Bargain is a 36-page picture book following one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget."
-Why it works for a volunteer rather than a teacher: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, and the mother explains every concept inside the text. A banker can read it cold and field the questions straight off the page. No training call, nothing to memorise. Free lesson plans, assessments and a browser-based pretend register sit behind it, all ungated.
+Why it works for a volunteer rather than a teacher: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, and the mother explains every concept inside the text. A banker can read it cold and field the questions straight off the page. No training call, nothing to memorise. The twenty-one-term glossary in the back is page-referenced to the story, so a volunteer answering a vocabulary question can turn to the scene rather than recite a definition. Free lesson plans, assessments and a browser-based pretend register sit behind it, all ungated.
 The sponsorship math is simple if a member bank wants it: 25 copies is $499.75, one classroom, the bank's name on every book that goes home to a family. The educator program is free, so the sponsorship is entirely books, and I have a CRA-ready memo already written in examiner-friendly language.
 Does that fit how Utah banks choose classroom programs, or am I inventing a use case?
 clarencegetsabargain.com/educator-toolkit.html
@@ -2598,8 +2596,7 @@
 Every children's money book teaches saving. Piggy banks, jars, three tins labeled spend-save-give where "spend" gets one page and a guilty look. But saving is the second thing a child does with money. The first is spending, and a first grader has already done it — in a store, holding money, deciding.
 And the tools have moved against them. A card is magic; a five-dollar bill is arithmetic — a kid who watches three dollars leave their hand understands something no tap-to-pay will ever teach.
 Which matters most in households where there is no margin for a bad purchase. A child taught only to save has been handed advice that assumes surplus. A child who can compare two prices and choose deliberately has a skill that works this Saturday.
-Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, meets sales tax, and then lives with what he chose. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the story.
-Catalogued Lexile AD 620L — Adult Directed — so the adult reading it is handed the script and does not have to be the one who already knows about money. That was the design constraint that mattered most: it has to work in a house where nobody feels qualified to teach it.
+Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, meets sales tax, and then lives with what he chose. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the story. It is catalogued AD 620L — Adult Directed — so the adult reading gets handed the script and does not have to be the one who already knows about money. That was the design constraint that mattered most: it has to work in a house where nobody feels qualified to teach it.
 Two questions. Does the spending-first argument hold up against what you hear from your audience? And is there a version of this worth putting in front of the Financial Influencer Network?
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -2659,8 +2656,7 @@
           <t>Ruben — CEE's standards are one of the five frameworks I crosswalked against, so I have spent real time inside them and want to ask about the bottom of the ladder.
 The elementary benchmarks exist. What is built against them is thin, and thinner still on the spending side. The field starts children with saving, and saving is the second thing a person does with money. The first is spending: standing in front of two prices and choosing one. A first grader has done that; she has no savings rate at all.
 I built a free K–5 classroom set around a 36-page picture book and crosswalked it concept by concept — 23 rows against the 2021 National Standards for Personal Financial Education, CEE, Common Core Math and ELA, and FDIC Money Smart, with the Grade 4 benchmark codes rather than a general claim of alignment. It is published so a reviewer can check it instead of taking my word.
-The book follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with the choice. Sixteen-plus concepts and nobody in it says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened.
-Catalogued Lexile AD 620L — Adult Directed — one class period read aloud, and because the mother explains every concept inside the text a teacher with no economics background can run it cold.
+The book follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with the choice. Sixteen-plus concepts and nobody in it says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened. Catalogued AD 620L — Adult Directed — one class period read aloud, and because the mother explains every concept inside the text a teacher with no economics background runs it cold.
 The question: is there a route for elementary material to sit alongside CEE programs, or does that run through affiliate councils? Either answer saves me guessing.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -2720,8 +2716,7 @@
           <t>Beth — you write for people trying to do the right thing with money and finding the advice arrives late. This arrives about two decades earlier than most of it.
 The premise: financial education starts children with saving, and the sequence is backwards. Saving is the second thing a person does with money. The first is spending. A seven-year-old has no savings rate and no income; what she has done is stand at a register holding money and choose. We teach that last, or never.
 I wrote the picture book for it. One purchase, followed the whole way — a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, meets sales tax, and then lives with what he chose. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; not one covers the whole arc.
-Sixteen-plus concepts, none announced — nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened, so vocabulary points a kid back into the story rather than away from it.
-Catalogued Lexile AD 620L — Adult Directed, read-with rather than read-alone. The mother explains everything on the page, so the parent gets the script and can take the credit.
+Sixteen-plus concepts, none announced — nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened, so vocabulary points a kid back into the story rather than away from it. It is catalogued AD 620L — Adult Directed — and the mother explains everything on the page, so the parent gets the script and can take the credit.
 One thing I would put to you as a planner: a card is magic, and a five-dollar bill is arithmetic. Children now grow up almost entirely inside the first one, which removes the only feedback loop they had.
 The claim I would defend hardest is the delayed one. The book is not really working in the twenty minutes it takes to read. It works in month eighteen, in a real store, when the kid hits a money moment and the book fires back — "wait, is the newer one actually better?" Recognition first, then the habit.
 Does that hold up against what you see in readers? clarencegetsabargain.com/book-facts.html
@@ -2782,8 +2777,7 @@
           <t>Julie — a segment idea, and it is short enough to survive a live hit.
 Every children's money book teaches saving. Piggy banks, lemonade stands, jars. But saving is the second thing a child does with money — the first is spending, and a six-year-old has already done it, in a store, holding a birthday five, deciding whether the thing is worth what it costs.
 The category skipped that for forty years. The arcade did not. A claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the kid has no price memory to defend himself with. Once a kid has seen the $9.99, the claw loses its grip.
-So I wrote the spending book. Clarence Gets a Bargain, ages 6–10: a boy earns a robot with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and then lives with the thing he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Twenty-one terms in a glossary at the back, each page-referenced to where it happened.
-Catalogued Lexile AD 620L — Adult Directed, the trade's own code for a book read with a child rather than handed to one. Twenty minutes out loud, interrupted the whole way.
+So I wrote the spending book. Clarence Gets a Bargain, ages 6–10: a boy earns a robot with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and then lives with the thing he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Twenty-one terms in a glossary at the back, each page-referenced to where it happened. Catalogued AD 620L — Adult Directed — twenty minutes out loud, interrupted the whole way.
 I am an attorney and a mixed-media artist, and I have twice walked out of the same Nordstrom Rack having paid one cent — once for a $293 pair of shoes, once for a $69.50 shirt. I kept both tags. It makes for a good visual if you ever want one on screen.
 Is there a hit in "the money skill nobody teaches kids"? clarencegetsabargain.com/press-kit.html
 Jonathan</t>
@@ -2843,8 +2837,7 @@
           <t>Matt — you spend your working life on what happens when people meet credit without the groundwork. I wrote the book about the groundwork, roughly twenty years upstream of your data.
 The sequence is the whole argument. Financial education starts children with saving. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent behind her. Mistakes at eleven cost $14. The same mistake at twenty-seven has a credit card attached and a rate on it.
 Clarence Gets a Bargain follows one purchase the entire distance: a boy wants a robot, earns it with chores and grades, works the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; they are all parked on the earning-and-saving side of the register.
-Sixteen-plus concepts and nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened — which is the only point at which a kid works out he has been schooled.
-Catalogued Lexile AD 620L — Adult Directed, so it is read-with rather than read-alone and the parent gets handed the script.
+Sixteen-plus concepts and nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened — which is the only point at which a kid works out he has been schooled. Catalogued AD 620L — Adult Directed — read with a parent, not handed to a kid alone. The single sentence I most want an eleven-year-old to own: marked down does not mean broken, it means the timing is on your side.
 The question, since you have the data and I only have the book: does anything in what you see suggest that price competence at seven shows up at twenty-seven? If it does not, I would rather know.
 clarencegetsabargain.com/book-facts.html
 Jonathan</t>
@@ -3026,6 +3019,7 @@
 Thirty states now guarantee a personal finance course. Every one of those mandates lands in high school. Money habits are largely set by seven — so the policy arrives roughly ten years after the cement dries, and the funding, the training and the reporting all follow the mandate rather than the evidence.
 Underneath that sits an assumption nobody argues with: that children should learn saving first. I think it is backwards. Saving is the second thing a person does with money. The first is spending, and a first grader has done that, at a register, with a parent standing behind her. The behaviors a high school course tries to correct were installed a decade earlier by an arcade, a toy aisle and a checkout lane, none of which waited for a curriculum.
 I wrote the elementary piece rather than an op-ed about it. A 36-page picture book following one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, and living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Free ungated classroom set behind it, crosswalked to five frameworks. Catalogued Lexile AD 620L — Adult Directed, so it is a read-with, and the caregiver conversation happens inside the reading.
+Meanwhile the arcade never waited for a standard: $25 into a glass box for a basketball Walmart sells for $9.99, and the kid has no price memory to argue with.
 The story I would pitch your desk: the whole country legislated financial literacy into ninth grade, and the elementary standards that already exist in most states sit there with nothing built against them, because nobody has to report on them.
 Does that belong to anyone on your team? clarencegetsabargain.com/book-facts.html
 Jonathan</t>
@@ -3085,9 +3079,9 @@
           <t>Stacy — you write about what happens to ordinary people inside financial systems. There is a version of that beat with no coverage at all, and it starts at about age six.
 A child becomes a consumer the first time they hand money to a cashier. Not at eighteen, not at a first paycheck — at six, with a birthday five. From that moment they are party to a transaction and they have rights nobody mentions: the receipt is proof, the price on the shelf has to match the price at the register, a broken thing can go back. Consumer education is the missing wing of children's financial literacy. We teach them to save and never tell them they are already the buyer.
 That is why I wrote the book. Clarence Gets a Bargain follows one purchase the entire way — a boy wants a robot, earns it, reads the sale inserts at the kitchen table, compares two on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced, and a twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
-The detail people ask me about: the mother photographs the receipt the second she sits down in the car. Every time. It takes four seconds and it is what makes a return, an exchange or a warranty claim winnable. Almost nobody teaches a child that.
-Format: Lexile AD 620L — Adult Directed, the trade's code for read-with rather than read-alone.
-I am an attorney, so I will say the honest version: the full picture crosses agencies, warranties and returns sit with the FTC, product safety with the CPSC. Nobody owns "children as consumers," which may be why nobody covers it.
+The detail people ask me about: the mother photographs the receipt the second she sits down in the car. Every time. It takes four seconds and it is what makes a return, an exchange or a warranty claim winnable. Almost nobody teaches a child that, which is why the book is catalogued AD 620L — Adult Directed — and gets read with an adult rather than handed to a kid alone.
+I am an attorney, and on vacation that mostly means the souvenirs get cross-examined. The hermit crab: who feeds it over the holidays, and in two weeks when it dies — and buddy, it will — is it worth the tears? My kids find this insufferable. It is also the entire skill.
+The honest version of the beat problem: the full picture crosses agencies. Warranties and returns sit with the FTC, product safety with the CPSC. Nobody owns "children as consumers," which may be exactly why nobody covers it.
 Is there a story in that? clarencegetsabargain.com/press-kit.html
 Jonathan</t>
         </is>
@@ -3147,8 +3141,7 @@
 The gap as I see it: elementary standards exist in most states and almost nothing is built against them, because nobody has to report on them. Every mandate lands in high school. Thirty states now.
 And underneath that, a sequencing assumption nobody argues with — that children should learn saving first. Saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has stood at a register and chosen.
 So I wrote the K–5 piece. Clarence Gets a Bargain follows one purchase from the idea to after the receipt: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, so vocabulary review points a child back into the story instead of away from it.
-The teacher side is free and ungated — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE, and FDIC Money Smart. No account, no email capture. It prints from a browser.
-Catalogued Lexile AD 620L — Adult Directed — so it runs as a one-period read-aloud and a teacher with no finance background can deliver it cold.
+The teacher side is free and ungated — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE, and FDIC Money Smart. No account, no email capture, and it prints from a browser. Catalogued AD 620L — Adult Directed — a one-period read-aloud a teacher with no finance background can deliver cold.
 Does the spending-first sequence match what you see in classrooms, or is there a reason the field starts where it starts?
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -3210,6 +3203,7 @@
 Every children's book on the shelf teaches saving. Piggy banks, jars, patience. But saving is the second thing a child does with money; the first is spending, and a six-year-old has already done it.
 Clarence Gets a Bargain follows one purchase the whole way — earning the reward through chores and grades, working the sale ads at the kitchen table, comparing two models on a shelf, taking the cheaper one on purpose, handing over a coupon, meeting sales tax, and then living with what was bought. Idea to post-receipt. And on page 6 there is something I have not found in any other picture book: a 529 plan. In the plot. Explained by a mom, eye-rolled at by a kid, and defended by a dad two scenes later.
 Sixteen-plus concepts and nobody says "budget." A twenty-one-term glossary in the back, page-referenced to the story. Catalogued Lexile AD 620L — Adult Directed — so it is a read-with, and the conversation happens during the reading rather than after it.
+A card is magic; a five-dollar bill is arithmetic. Children now grow up almost entirely inside the first one, which removed the only feedback loop they had.
 The angle for your beat: advisors spend fortunes trying to meet the next generation before the assets move. This is what meeting them at seven looks like, and it costs $19.99.
 Worth a column, or am I describing something you have already covered? clarencegetsabargain.com/press-kit.html
 Jonathan</t>
@@ -3393,8 +3387,7 @@
         <is>
           <t>Sam — you have been reading, singing and performing a savings habit into elementary classrooms for two decades across thirty states, which is more direct contact with this audience than anyone else in the category has. So I want to put an argument in front of you and hear where it is wrong.
 Sammy teaches saving, and teaches it better than anything else aimed at this age. My argument is not about quality; it is about order. Saving is the second thing a child does with money. The first is spending — a first grader has stood at a register holding money and chosen, years before she has anything to save. Teach that moment first, and everything Sammy preaches lands harder, because a kid who understands what money buys has a reason to keep some.
-That is the book I wrote. Clarence Gets a Bargain follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the scene each term came from.
-Catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, with every concept explained inside the text, so somebody can read it cold to a class. You will recognise why that mattered to me.
+That is the book I wrote. Clarence Gets a Bargain follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the scene each term came from. Catalogued AD 620L — Adult Directed — about twenty minutes out loud, every concept explained inside the text, so somebody can read it cold to a class. You of all people will know why that mattered to me.
 You also solved a distribution problem the rest of us have not: banks and credit unions sponsor the visits and buy the books, and their community reports write themselves. I would rather learn that from you than reverse-engineer it.
 Trade copies and compare notes? I will read Sammy properly and tell you the truth about it, which is the only thing worth trading.
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -3517,6 +3510,7 @@
 Thirty states now require personal finance to graduate. The mandates land in high school, and the funding, the training and the reporting follow the mandate. Meanwhile the K–5 standards that already exist in most states sit there with almost nothing built against them, because nobody has to report on them.
 The assumption underneath is that children should learn saving first. I think it is backwards, and I would rather be told so by NEFE than keep saying it at conferences. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent standing behind her. The behaviors a high school course is trying to correct were installed a decade earlier.
 I wrote the elementary piece rather than an argument about it: a 36-page picture book that follows one purchase from the idea to after the receipt, plus a free ungated classroom set crosswalked to the 2021 National Standards, Common Core, CEE and FDIC Money Smart. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Catalogued Lexile AD 620L — Adult Directed — so the intervention is a shared read rather than solo reading, which also makes it easier to study than a curriculum.
+The line I would put on a poster if I could: mistakes at eleven cost $14, and the same mistake at twenty-seven has a credit card attached.
 The question: does NEFE's research or advocacy work have a position on the elementary band, or is the practical view that high school is where the effort pays? If it is the second, I would like to know I am arguing with a considered consensus rather than filling a gap it agrees exists.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan Bach
@@ -3579,6 +3573,7 @@
 There is also a sequencing assumption underneath the whole field that I would like your view on. Financial education starts children with saving. Saving is the second thing a person does with money; the first is spending. A first grader has no savings rate. She has stood at a register holding money and had to choose.
 I built a free, ungated K–5 classroom set around a 36-page picture book: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE and FDIC Money Smart, printable classroom pieces, and a browser-based pretend register. No account, no email capture, no purchase order. It prints from a browser.
 The book follows one complete purchase — sale ads, comparison, a markdown, a coupon, sales tax — with sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story. Catalogued Lexile AD 620L, Adult Directed, so it runs as a one-period read-aloud with no teacher training required.
+One line from the book does the work of a standards document, and it is the one I would defend hardest: marked down does not mean broken, it means the timing is on your side.
 Two questions. Does Jump$tart consider elementary in scope, or is it a band the coalition has consciously left to others? And for the Clearinghouse, is the free classroom set the right thing to submit rather than the book?
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -3639,8 +3634,7 @@
 Wesley learns to invest. Clarence learns to spend — and I mean the mechanics of it rather than the idea. Every other book in the category teaches saving, which is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. Nobody had written that one, so I did.
 Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Nobody says the word "budget."
 The craft problem I would most like another author's view on: the reader is not supposed to know he has been taught anything until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. Getting that balance right, so it stays a story, was the whole job, and it is the thing most likely to be off by a hair.
-I did the illustrations too, which means my opinion of them is worth nothing.
-Catalogued Lexile AD 620L — Adult Directed — written for the adult voice in the room, with the mother carrying every explanation.
+I did the illustrations too, which means my opinion of them is worth nothing. It is written for the adult voice in the room — catalogued AD 620L, Adult Directed — with the mother carrying every explanation.
 Trade? Send me a Wesley and I will read it properly rather than politely.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -3700,9 +3694,9 @@
           <t>Kate — a pitch about a gap rather than a book, though I wrote the book because of the gap.
 Everything in kids' financial literacy points at a horizon no child can see: compound interest, credit scores, retirement. All real, all decades out. Meanwhile the kid is eight, holding $20 of birthday money, standing in a store that spent millions working out how to get it. We are preparing children for 65 and sending them to the register unarmed today.
 So flip the order. Saving is the second thing a child does with money. The first is spending, and it is the one nobody puts in a story.
-Clarence Gets a Bargain does. One kid, one purchase, followed the whole distance — he wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget." The reader works out he has been schooled at the glossary — twenty-one terms in the back, each one page-referenced to the scene it came from.
-Catalogued Lexile AD 620L. The AD is Adult Directed, the industry's own code for a book meant to be read with a child rather than handed over, so a parent who does not feel qualified on money still gets handed the script.
-Timely hook if you need one: thirty states now guarantee a personal finance course, all of it in high school, roughly ten years after the habits form. The elementary standards already exist in most states and have almost nothing built against them.
+Clarence Gets a Bargain does. One kid, one purchase, followed the whole distance — he wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget." The reader works out he has been schooled at the glossary — twenty-one terms in the back, each one page-referenced to the scene it came from. Catalogued AD 620L — Adult Directed — so a parent who does not feel qualified on money still gets handed the script and can take the credit.
+The boardwalk is a pop quiz your kid has not studied for, and it runs all summer with real money.
+Timely hook if you need one: thirty states now guarantee a personal finance course, all of it in high school, long after the habits form. The elementary standards already exist in most states and have almost nothing built against them.
 Any of that useful to you? clarencegetsabargain.com/book-facts.html
 Jonathan</t>
         </is>
@@ -9740,7 +9734,7 @@
       <c r="K205" s="5" t="inlineStr">
         <is>
           <t>Iris — you were part of the group that chose the titles on the Money as You Grow Bookshelf, so you have read this category more carefully than almost anyone, and you will know immediately whether my premise is wrong.
-The shelf, as it stands, leans toward saving and earning. What is thin is spending, and specifically the transaction — the part where a child stands in front of two prices and has to pick one. That is the first financial act a person performs. It gets taught last.
+The shelf, as it stands, leans toward saving and earning. Spending is thin, and the transaction itself is thinner — the part where a child stands in front of two prices and picks one. Saving is the second thing a person does with money; spending is the first, and it gets taught last or not at all.
 Clarence Gets a Bargain covers exactly that, and covers the whole of it: a boy wants a robot, earns it through chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list looking for another one that does the whole arc. They are all parked on the earning-and-saving side of the register.
 Sixteen-plus concepts and none is announced — no character pauses to define a term, nobody says the word "budget." The proof and the reveal are both in the back matter: a reader does not know he has been schooled until he reaches the glossary. Twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than an appendix.
 Ages 6–10, inside the Bookshelf's 4–10 band. Catalogued Lexile AD 620L — Adult Directed, which is how the Bookshelf's titles are meant to be used anyway.
@@ -9812,6 +9806,7 @@
 A six-year-old with a birthday five in an aisle is running a comparison with no price history, no reference class and no idea that anchoring exists. She is the purest case your field could ask for and the least documented. Meanwhile the environment is not naive at all — a boardwalk claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the child has no way of knowing the $9.99 exists.
 Financial education answers this by teaching saving. But saving is the second thing a person does with money; the first is spending, and it is taught last or not at all.
 I wrote the picture book rather than the paper. Clarence Gets a Bargain follows one complete purchase — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with the choice afterward. Sixteen-plus concepts, none announced. Twenty-one terms in a back-matter glossary, each page-referenced to the scene it came from. Catalogued Lexile AD 620L — Adult Directed — so the reading is a joint activity by design rather than a solo one.
+For what it is worth, the field's own blind spot has a price tag on it: a boardwalk claw machine takes $25 to hand back a basketball Walmart sells for $9.99, and no curriculum anywhere treats that as a financial event.
 The question I would actually like answered: is there work on when price competence forms, and whether early exposure to comparison changes anything measurable later? If the honest answer is that it is unstudied because it is unmeasurable at that age, that is worth knowing too.
 clarencegetsabargain.com/book-facts.html
 Jonathan Bach
@@ -9872,8 +9867,7 @@
           <t>Bina — a question about where community development work draws its lower age bound.
 Most financial capability programming aimed at low- and moderate-income families reaches adults, or reaches children through savings vehicles — child savings accounts, matched savings, college accounts. All of that is aimed at accumulation. Very little addresses the other side of the household ledger at a child's level: what happens when the money is spent, which for a child is nearly all of it.
 That gap has a sequencing problem behind it. Saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has handled money at a register, and the decision she made there was unassisted.
-I built the elementary resource. A 36-page picture book that follows one complete purchase — sale ads, comparison shopping, a markdown, a coupon, sales tax, and living with what was bought — with sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story. Behind it, a free ungated classroom and family set crosswalked to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE and FDIC Money Smart. No account, no email capture, no purchase order; it prints from a browser, which matters where budgets do not exist.
-Catalogued Lexile AD 620L — Adult Directed — so it works as a shared read with a caregiver who does not need to know the material first, which is the design constraint that mattered most to me.
+I built the elementary resource. A 36-page picture book that follows one complete purchase — sale ads, comparison shopping, a markdown, a coupon, sales tax, and living with what was bought — with sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story. Behind it, a free ungated classroom and family set crosswalked to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE and FDIC Money Smart. No account, no email capture, no purchase order; it prints from a browser, which matters where budgets do not exist. It is catalogued AD 620L — Adult Directed — so it works as a shared read with a caregiver who does not need to know the material first. That was the design constraint that mattered most to me.
 The question: does SF Fed's community engagement work touch the elementary band, or does it start at the account level with adults?
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan Bach
@@ -17318,8 +17312,7 @@
           <t>Jennifer — a funding-shaped question rather than an ask, and the resource itself is already free.
 I wrote and illustrated a K–5 financial-literacy picture book and built the entire classroom program behind it — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a standards crosswalk across five frameworks. All of it is ungated: no account, no email capture, no purchase order, prints from a browser. The only thing that ever costs anything is the physical books, and 25 copies run $499.75.
 The content premise: every children's money book teaches saving, and saving is the second thing a child does with money. The first is spending — a first grader has stood at a register and chosen. The book follows one complete purchase from the idea through the receipt, with sixteen-plus concepts hidden in the plot and a twenty-one-term glossary page-referenced back into the story.
-Why I am writing to development rather than to a classroom: this is unusually easy to fund. A bank or credit union sponsoring a classroom set gets its name on every book that goes home to a family in its assessment area, the curriculum costs the sponsor nothing because it is already free, and I have a CRA-ready memo written in examiner-friendly language. A funder can point at 25 books, one classroom, and a pre/post instrument.
-Catalogued Lexile AD 620L — Adult Directed — which also makes it a family-engagement asset rather than only a classroom one, since the book works at a kitchen table with a parent or a grandparent doing the reading.
+Why I am writing to development rather than to a classroom: this is unusually easy to fund. A bank or credit union sponsoring a classroom set gets its name on every book that goes home to a family in its assessment area, the curriculum costs the sponsor nothing because it is already free, and I have a CRA-ready memo written in examiner-friendly language. A funder can point at 25 books, one classroom, and a pre/post instrument. And because it is catalogued AD 620L — Adult Directed — it doubles as family engagement: the same book works at a kitchen table with a parent or a grandparent reading.
 Is a sponsored classroom set something HCZ's funders would recognise, or does everything need to attach to an existing program line?
 clarencegetsabargain.com/resources/grant-in-a-box.html
 Jonathan</t>
@@ -17377,7 +17370,7 @@
       <c r="K403" s="5" t="inlineStr">
         <is>
           <t>Flora — JA runs volunteers into elementary classrooms better than any organisation in the country, so this is a materials question rather than a pitch.
-JA's elementary programs are strong on earning, jobs and community. What is thin across the whole field — not just JA — is spending, and specifically the transaction itself. A first grader has no savings rate and no job. What she has done is stand at a register holding money and choose.
+JA's elementary programs are strong on earning, jobs and community. What is thin across the whole field, JA included, is spending — the second thing everybody teaches and the first thing a child actually does. A first grader has no savings rate and no job. What she has done is stand at a register holding money and choose.
 Clarence Gets a Bargain is a 36-page picture book that puts the entire transaction on the page: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
 The part that matters for a volunteer model: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, with every concept explained inside the text by the mother. A volunteer who has never taught anything can read it cold and answer questions off the page. Nothing to memorise and no prep call. Behind it, free and ungated: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable price tags and clearance stickers for a classroom store, and a browser-based pretend register with a markdown, a coupon and sales tax.
 Alaska has its own complications on distance and travel, and virtual read-alouds work for this.
@@ -17440,8 +17433,8 @@
           <t>Elizabeth — a scope question rather than a pitch.
 Federal attention to financial education, like every state mandate, concentrates on high school. Thirty states now require a course to graduate. The elementary standards that exist in most states sit underneath that with very little built against them, largely because nothing requires reporting at that band.
 The assumption underneath is that children begin with saving. Saving is the second thing a person does with money. The first is spending — a first grader has handled money at a register and made a decision there with no framework at all.
-I built a free, ungated K–5 resource for that: a 36-page picture book that follows one complete purchase from the idea through the receipt — sale ads, comparison shopping, a markdown, a coupon, sales tax — and a classroom set behind it. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a browser-based pretend register, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education alongside Common Core Math and ELA, CEE and FDIC Money Smart, cited at the Grade 4 benchmark level rather than claimed generally.
-No account, no email capture, no purchase order. It prints from a browser. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud requiring no instructor training.
+I built a free, ungated K–5 resource for that: a 36-page picture book that follows one complete purchase from the idea through the receipt — sale ads, comparison shopping, a markdown, a coupon, sales tax — and a classroom set behind it. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a browser-based pretend register, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education alongside Common Core Math and ELA, CEE and FDIC Money Smart, cited at the Grade 4 benchmark level rather than claimed generally. Sixteen-plus concepts appear in the story without being announced, and a twenty-one-term glossary in the back matter page-references each one to the scene where it occurs.
+No concept is announced in the text; the twenty-one-term glossary in the back matter carries the definitions, each page-referenced to where the term occurs. No account, no email capture, no purchase order. It prints from a browser. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud requiring no instructor training.
 The question: does any Department program or clearinghouse take elementary financial-education material, or is the practical route through the states? A steer on who would know is as useful to me as an answer.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan Bach
@@ -17502,8 +17495,7 @@
           <t>Gene — Troutwood is built on showing people the long arc of a decision, which is why I am writing about the very first decision on that arc.
 Everything in financial planning compounds, including the mistakes, and the compounding starts long before anyone opens an account. Mistakes at eleven cost $14. The same mistake at twenty-seven has a credit card attached. The habit doing the compounding was installed at six, in a store, with a parent saying no and no reasoning attached to the no.
 Financial education answers that by teaching children saving. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with no framework at all.
-Clarence Gets a Bargain is the picture book for that. One purchase, followed the whole way: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
-Catalogued Lexile AD 620L — Adult Directed — so it is a shared read, and the parent gets handed the script rather than a homework assignment.
+Clarence Gets a Bargain is the picture book for that. One purchase, followed the whole way: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed — so it is a shared read and the parent gets the script rather than a homework assignment.
 The claim I would defend hardest is the delayed one, and it is the same claim Troutwood makes about projections: the value is not in the twenty minutes. It is in month eighteen, in a real store, when the kid hits a money moment and the book fires back. Recognition first, then the habit.
 Does the elementary end fit anything Troutwood does, or is that below the floor?
 clarencegetsabargain.com/book-facts.html
@@ -21996,8 +21988,7 @@
 Planners meet clients' children late, usually at the worst possible moment, and by then the habits are twenty years old. They were formed at six, in a store, with a parent saying no and no reasoning attached to the no.
 The field's answer to that is to teach children saving. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, holding a birthday five, deciding whether the thing is worth what it costs.
 I wrote the picture book for that moment. Clarence Gets a Bargain follows one purchase the whole way — earning the reward through chores and grades, working the sale ads at the kitchen table, comparing two models on a shelf, taking the cheaper one on purpose, redeeming a coupon, meeting sales tax, and then living with what was bought. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in a back-matter glossary, page-referenced to the story.
-And on page 6 there is something I have not found in any other picture book: a 529 plan. In the plot. Explained by a mother, eye-rolled at by a kid, defended by a father two scenes later.
-Catalogued Lexile AD 620L — Adult Directed, so a planner handing it to a client family is handing over a script rather than an assignment. Twenty-five copies run $499.75, and the educator program behind it is free.
+And on page 6 there is something I have not found in any other picture book: a 529 plan. In the plot. Explained by a mother, eye-rolled at by a kid, defended by a father two scenes later. It is catalogued AD 620L — Adult Directed — so a planner handing it to a client family is handing over a script rather than an assignment. Twenty-five copies run $499.75, and the educator program behind it is free.
 The question: does CFP Board's pro bono and public-education work reach below high school at all, or is that considered somebody else's ground?
 clarencegetsabargain.com/book-facts.html
 Jonathan</t>
@@ -22056,7 +22047,7 @@
         <is>
           <t>Ed — a narrow question about evidence standards, asked before I go further with something.
 I have built a free K–5 financial-education resource — a 36-page picture book plus a complete classroom set — and crosswalked it to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE and FDIC Money Smart, at the Grade 4 benchmark level. Everything is ungated: no account, no email capture, no purchase order, and it prints from a browser.
-The content premise is that the field has the sequence backwards. Financial education starts children with saving; saving is the second thing a person does with money. The first is spending, and a first grader has already done it at a register. The book follows one complete purchase from the idea through the receipt — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with what was bought.
+The content premise is that the field has the sequence backwards. Financial education starts children with saving; saving is the second thing a person does with money. The first is spending, and a first grader has already done it at a register. The book follows one complete purchase from the idea through the receipt — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with what was bought. No concept is announced in the text; a twenty-one-term glossary in the back matter carries the definitions, each page-referenced to where the term occurs.
 One structural detail relevant to evaluation: the book is catalogued Lexile AD 620L — Adult Directed — so it is delivered as a shared read between an adult and a child rather than independent reading. That makes it closer to a shared-reading intervention than a curriculum, which may change what kind of evidence would be appropriate.
 The question: what would a resource like this need in order to be taken seriously on evidence — a pre/post instrument administered at scale, a quasi-experimental design, something else? I would rather build the right study once than assemble the wrong one. And if the honest answer is that no federal pathway exists for elementary material of this kind, that is worth knowing too.
 clarencegetsabargain.com/educator-toolkit.html
@@ -22179,8 +22170,7 @@
         <is>
           <t>Annie — you built a product for the exact age band everyone else in this category skips, so you already believe the thing I have been arguing. I want to compare notes rather than pitch you.
 My First Nest Egg puts save, spend, give and invest in front of a young child in physical form. My argument is about which of those a child actually performs first. It is spending — a six-year-old has stood in a store holding money and chosen, years before she has anything to save or invest. The category teaches saving first anyway, and I could not find the book that teaches the other one.
-So I wrote and illustrated it. Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
-Catalogued Lexile AD 620L — Adult Directed — read-with rather than read-alone, so the parent gets handed the script. And there is a free browser-based pretend register behind it that runs a markdown, a coupon and sales tax, which is the closest thing I have to your physical product.
+So I wrote and illustrated it. Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed — read with a grown-up rather than handed over. There is also a free browser-based pretend register behind it that runs a markdown, a coupon and sales tax, which is the closest thing I have to your physical product.
 Those look complementary rather than competing to me: yours gives a kid the categories in their hands, mine walks them through the mechanics of one transaction in twenty minutes.
 Worth a conversation about whether they belong near each other? And separately — if you think spending-before-saving is wrong, you are one of very few people whose disagreement would actually change my mind.
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -28308,19 +28298,19 @@
         </is>
       </c>
       <c r="I666" s="5" t="n">
-        <v>2933</v>
+        <v>3349</v>
       </c>
       <c r="J666" s="5" t="inlineStr">
         <is>
           <t>Christine,
 You're closing September, Grandparents Day is the 13th, and every other pitch on your desk this week is a gift guide. Mine is an afternoon.
-I'm an attorney, a mixed-media artist, and a dad, and I wrote and illustrated a children's picture book called Clarence Gets a Bargain. Ages 6–10. A boy earns a robot with chores and grades, then has to figure out how to buy it — sale ads at the kitchen table, two models compared on a shelf, the cheaper one taken on purpose, a coupon handed to the cashier, and sales tax showing up uninvited at the end.
+I'm an attorney, a mixed-media artist, and a dad, and I wrote and illustrated a children's picture book called Clarence Gets a Bargain. Ages 6–10. A boy earns a robot with chores and grades, then has to figure out how to buy it — sale ads at the kitchen table, two models compared on a shelf, the cheaper one taken on purpose, a coupon handed to the cashier, and sales tax showing up uninvited at the end. Sixteen-plus money concepts are in there and not one of them is announced; nobody in the book ever says the word "budget." A kid doesn't work out he's been taught anything until he reaches the glossary at the back — twenty-one terms, each one pointing back to the page where it happened.
 Your readers own the next part. Every children's money book teaches saving. Piggy banks, jars, three little tins labeled spend-save-give where "spend" gets one page and a guilty look. But saving is the second thing a child does with money; the first is spending, and a six-year-old has already done it, in a store, holding a birthday five, deciding whether the thing is worth what it costs. We teach the second thing first and the first thing never.
-Grandparents are the only people left who can teach the first one from experience. You clipped coupons back when it was a survival skill rather than a hobby. You remember layaway. You know what your first paycheck was and exactly what it wouldn't cover. Those stories are the best money curriculum a child will ever get and they have nowhere to land — until a book puts a kid in a store and every page comes with a "that reminds me of the time" already sitting in it.
+Your readers clipped coupons back when it was a survival skill rather than a hobby. They remember layaway. They know what their first paycheck was and exactly what it wouldn't cover. That is better money curriculum than anything a school hands out, and it has nowhere to land, because nobody asks. A book that puts a kid in a store gives it somewhere to land: every page has a "that reminds me of the time" already sitting in it, waiting for somebody to say it out loud.
 The book is catalogued Lexile AD 620L, and the AD means Adult Directed — the industry's own code for a book meant to be read WITH a child rather than handed to one. It needs a grown-up in the room. You're cast. Mom explains everything inside the story, so the grandparent reading aloud gets handed the script and can take the credit for knowing it. Twenty minutes out loud, interrupted the whole way, and the interruptions are the point: "Do we have a 529?" "Why do you take pictures of receipts?" "Can I hand the cashier the coupon next time?"
 And two of the games in it can't be played alone. Page 27: whoever spots the biggest savings at the grocery store wins, loser carries the bags in from the car. Page 28: after dinner somebody shares a deal they got that day and everyone guesses the price. Kids' guesses are unhinged. A gallon of milk goes for $45; a car for $100. The reveal face is the whole entertainment. Three players minimum. Grandma counts.
-I'd write it for you as 800–1,200 words, under the title "What Grandparents Can Teach About Money That Nobody Else Can," with the games as a sidebar readers can tear out and use. Or if you'd rather run it as a product review, the book is $19.99, 36 pages, hardbound, and I'll send a copy today either way.
-Which is more useful to you?
+The piece I want to write for you is 800 to 1,200 words: "What Grandparents Can Teach About Money That Nobody Else Can," with the two games as a tear-out sidebar. If you'd rather have a product review instead, I'll take that too; the book is $19.99, 36 pages, hardbound. But the article is the better use of your page, and I'd rather argue for it than hedge.
+Copy goes in the mail today either way. Say the word on the piece and you'll have a draft this week.
 Jonathan Bach
 Author &amp; illustrator, Clarence Gets a Bargain
 Attorney. Dad. Keeper of receipts.
@@ -28370,13 +28360,13 @@
       </c>
       <c r="H667" s="5" t="inlineStr"/>
       <c r="I667" s="5" t="n">
-        <v>2749</v>
+        <v>2975</v>
       </c>
       <c r="J667" s="5" t="inlineStr">
         <is>
           <t>DeeDee,
 You started More Than Grand in 2019 because you couldn't find the grandparent resource you wanted, so you built it. I did the same thing on a different shelf, which is the only reason I'm comfortable writing to you cold.
-I went looking for the children's book that teaches a kid how to spend money — not save it, spend it — and there wasn't one. Every book in that category is about a piggy bank or a lemonade stand. All of them teach saving, which is the second thing a child does with money. The first is spending, and a six-year-old has already done it, standing in a store holding a birthday five, working out whether the thing is worth what it costs. So I wrote and illustrated it: Clarence Gets a Bargain, ages 6–10, one kid following one purchase the whole way, from wanting the robot to living with the one he chose.
+I went looking for the children's book that teaches a kid how to spend money — not save it, spend it — and there wasn't one. Every book in that category is about a piggy bank or a lemonade stand. All of them teach saving, which is the second thing a child does with money. The first is spending, and a six-year-old has already done it, standing in a store holding a birthday five, working out whether the thing is worth what it costs. So I wrote and illustrated it: Clarence Gets a Bargain, ages 6–10, one kid following one purchase the whole way, from wanting the robot to living with the one he chose. Sixteen-plus concepts, none of them announced — nobody says "budget" — and a twenty-one-term glossary in the back where every entry points to the page it came from. The kid doesn't know he's been schooled until he gets there.
 I'm writing to you rather than to a gift guide, and here's the difference. Your whole editorial line is that a good grandparent supports the parents instead of running past them. This book does that structurally. Mom is the one who teaches Clarence in the story — the sale ads, the markdown, the coupon, the sales tax. A grandparent reading it aloud is reading the parent's lines, not competing with them.
 The format backs that up. It's catalogued Lexile AD 620L, and AD stands for Adult Directed — the trade's own code for a book meant to be read WITH a child rather than handed over. It doesn't work in the corner. It works on a couch, with somebody's grandkid interrupting every third page. And because Mom explains every concept inside the text, the grandparent doesn't have to be confident about money to run it. The script is on the page. Take the credit.
 Two of the games in the back half need other people, which I did on purpose. Page 27: everyone hunts for the biggest savings on the next grocery run, loser carries the bags in from the car. Page 28: after dinner someone shares a deal they got that day and everybody guesses the price. Three players minimum. Grandma counts.
@@ -28432,16 +28422,18 @@
       </c>
       <c r="H668" s="5" t="inlineStr"/>
       <c r="I668" s="5" t="n">
-        <v>1903</v>
+        <v>2327</v>
       </c>
       <c r="J668" s="5" t="inlineStr">
         <is>
           <t>Hello,
 A contribution to Do Something Grand rather than a request, and it's free.
 Grandparents Day falls on September 13 this year, and your activity-ideas page is built around things a grandparent and a grandchild can actually do together. I have two that cost nothing and take one afternoon, and I'd like to hand them over.
+The premise behind both: saving is the second thing a child does with money, and spending is the first. The games teach the first one, which is the half nobody covers.
 I wrote and illustrated a children's picture book, Clarence Gets a Bargain, about a kid learning how to spend money rather than save it — one purchase followed all the way, from reading the sale ads at the kitchen table to the sales tax at the register. Two of the games in it were written to require more than one person:
 The Grocery Savings Hunt — on the next shopping trip, everyone looks for the biggest markdown. Best find wins. The loser carries the bags in from the car.
 Guess the Price — after dinner, one person shares something they bought that day and everybody guesses what it cost. Closest guess wins. Kids' guesses are unhinged, which is the entire entertainment value.
+The book itself is catalogued Lexile AD 620L — Adult Directed — which is the trade's way of saying it only works with a grown-up in the room, so the games and the book are built on the same idea: a grandparent and a grandchild, doing something together.
 I'll build both as a free one-page printable in your Do Something Grand look, with no book cover on it and no purchase link — a grandparent can use it having never heard of me. Everything else on my site for teachers and families is already free and ungated, no email capture and no account, and this would be the same.
 Two questions. Is a submitted activity something the campaign takes from outside, and if so who should I send the draft to? And separately, is there interest in a short piece on why grandparents are the right people to teach the spending half of money — they're the last group who remember layaway and clipping coupons as a survival skill rather than a hobby.
 Happy to be told no. The printable will exist either way and you're welcome to it.
@@ -28559,12 +28551,13 @@
       <c r="G670" s="5" t="inlineStr"/>
       <c r="H670" s="5" t="inlineStr"/>
       <c r="I670" s="5" t="n">
-        <v>1145</v>
+        <v>1450</v>
       </c>
       <c r="J670" s="5" t="inlineStr">
         <is>
           <t>Greg — a grandfather-adjacent pitch, though I'm a dad rather than a grandpa yet, so tell me if that disqualifies me and I'll take it well.
-I wrote and illustrated a kids' picture book about the money skill nobody teaches: spending. Every children's money book is about a piggy bank. But saving is the second thing a kid does with money — the first is spending, usually on a Saturday, at a register, with a grown-up standing right there sweating the total.
+I wrote and illustrated a kids' picture book about the money skill nobody teaches: spending — one kid, one purchase, followed the whole way from the sale ads at the kitchen table to the sales tax on the receipt. Every children's money book is about a piggy bank. But saving is the second thing a kid does with money — the first is spending, usually on a Saturday, at a register, with a grown-up standing right there sweating the total.
+Sixteen-plus money concepts are hidden in it and none are announced — the glossary in the back is the only place the book admits what it was doing, and it's the last thing a kid reads.
 The reason I think it's a grandpa episode: the book is built to be read out loud with a kid, not handed to one. It's catalogued Lexile AD 620L — Adult Directed, the industry's own code for read-WITH. And the grandparents are the last people alive who remember layaway and clipping coupons as a survival skill. Every page has a "that reminds me of the time" sitting in it.
 Two of the games in it need more than one player on purpose. One is a grocery-store savings hunt where the loser carries the bags in from the car.
 Worth twenty minutes of your show? I'll send a copy either way.
@@ -28611,7 +28604,7 @@
       <c r="G671" s="5" t="inlineStr"/>
       <c r="H671" s="5" t="inlineStr"/>
       <c r="I671" s="5" t="n">
-        <v>3463</v>
+        <v>3977</v>
       </c>
       <c r="J671" s="5" t="inlineStr">
         <is>
@@ -28620,6 +28613,7 @@
 Clarence Gets a Bargain carries a reading level of Lexile AD 620L. The AD stands for "Adult Directed" — the book industry's own label for a title meant to be read WITH a child rather than handed to one. That code isn't an accident. I built the book for the couch, not the corner.
 Here's why. In the story, Clarence doesn't learn about money from a worksheet. He learns it from his mom — at the kitchen table with the sale ads, in the car, in the middle of the store. Read the book to your kid and you aren't describing that scene. You're in it.
 And the interruptions will come. "Do we have a 529?" "Why do you take pictures of receipts?" "Can I hand the cashier the coupon next time?" "Is the internet a need or a want?" A kid alone in the corner reads a robot story and moves on. A kid pressed against your shoulder reads the same story and starts an argument about whether Wi-Fi counts as shelter. You want that argument. The argument is the product; the robot is the delivery vehicle.
+Every other money book for kids teaches saving, which is the second thing a child does with money. Spending is the first, and this one follows a single purchase the whole way — the sale ads, the aisle, the markdown, the coupon, the sales tax, and living with what got bought. Sixteen or more money concepts are in there and not one of them is announced. Nobody says the word "budget." Your kid won't know she's been taught anything until she reaches the glossary at the back — which is the last page, on purpose.
 You don't need to know anything about finance to do this well. Mom explains everything to Clarence inside the story — sale ads, clearance, markdowns, sales tax — so your only job is to read her lines like you knew it all along. I wrote you the script. Take the credit.
 Two parts of the book flat-out require company:
 The grocery game, page 27. Whoever spots the biggest savings wins; the loser carries the bags in from the car. A kid cannot play this alone. That's the point.
@@ -30156,8 +30150,8 @@
           <t>Andrew — your audience is adults fixing money habits. I wrote the book that tries to stop the habits forming, and there is an episode in the argument whether or not the book is in it.
 Every children's money book teaches saving. Piggy banks, lemonade stands, three jars. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding a birthday five, working out whether the thing is worth what it costs.
 Nobody put that in a story. So I did. Clarence Gets a Bargain follows a single purchase the whole way — a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax and regards it as a personal insult, then lives with the thing he chose. Idea to post-receipt.
-Sixteen-plus concepts and none of them announced. Nobody in the book says "budget," which for a book largely about budgeting took some doing. Kids smell a worksheet one page in; they never smell this one, because they are laughing too hard to notice. The reveal is the glossary — twenty-one terms in the back, page-referenced to the scene each came from.
-Catalogued Lexile AD 620L — Adult Directed, so it is a read-with, which means the parent listening to your show gets handed the script rather than a homework assignment.
+Sixteen-plus concepts and none of them announced. Nobody in the book says "budget," which for a book largely about budgeting took some doing. Kids smell a worksheet one page in; they never smell this one, because they are laughing too hard to notice. The reveal is the glossary — twenty-one terms in the back, page-referenced to the scene each came from. It is catalogued AD 620L, Adult Directed, so the parent listening to your show gets handed the script rather than a homework assignment.
+Their books are about earning and saving, which is fine, but there is no game in a piggy bank and kids know it.
 The episode I would pitch is not the book. It is the forty-year hole: an entire publishing category taught children to save and skipped the cash register, the only place a child has ever actually handled money.
 Worth twenty minutes of your show? https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -30215,7 +30209,7 @@
       <c r="K25" s="5" t="inlineStr">
         <is>
           <t>Amy — two requests come to your desk all week. A kid wants a robot book. A parent wants something that teaches money. I wrote the one that answers both in a single checkout.
-Clarence Gets a Bargain is a 36-page picture book, ages 6–10, that follows one kid through one complete purchase: he earns a robot reward with chores and grades, does his shopping homework in the newspaper sale ads, comparison-shops the aisle, finds the markdown, hands a coupon to the cashier, meets sales tax, and watches his mother photograph the receipt before the car leaves the lot. Kids read it as a robot story. Sixteen-plus money concepts come along without announcing themselves, and the back matter carries a twenty-one-term glossary where each definition points to the page where the term happens in the plot — a decoder rather than an appendix.
+Clarence Gets a Bargain is a 36-page picture book, ages 6–10, that follows one kid through one complete purchase: he earns a robot reward with chores and grades, does his shopping homework in the newspaper sale ads, comparison-shops the aisle, finds the markdown, hands a coupon to the cashier, meets sales tax, and watches his mother photograph the receipt before the car leaves the lot. Kids read it as a robot story. Saving is the second thing a child does with money; the first is spending, and this is the book for that. Sixteen-plus money concepts come along without announcing themselves, and the back matter carries a twenty-one-term glossary where each definition points to the page where the term happens in the plot — a decoder rather than an appendix.
 The collection case, with the qualifier a librarian will appreciate: most money picture books cover earning or saving. To my knowledge this is the first narrative picture book for this age band that traces the whole consumer arc, wish through receipt. It fills a hole rather than adding a fourth piggy-bank book to the shelf.
 Cataloguing: ISBN 979-8-234-07638-0 · LCCN 2026906164 · hardbound, case bound, full colour, 11×8.5′′ · Est. Lexile AD 620L, Guided Reading L–N · $19.99. The AD is Adult Directed, which makes it a storytime title and a family take-home at the same time. Every fact is on one page: clarencegetsabargain.com/book-facts.html
 Programming is already built and free — printable price tags and clearance stickers for a pretend store, a browser-based register kids run themselves, a five-question quiz with a printable certificate. A storytime plus the pretend store is a complete Money Smart Week event with no prep budget.
@@ -30276,7 +30270,7 @@
         <is>
           <t>Sarah — a collection-development pitch, kept to the facts because I know what August looks like at your desk.
 Clarence Gets a Bargain is a 36-page picture book, ages 6–10, following one kid through one complete purchase: earning the robot reward, doing shopping homework in the newspaper sale ads, comparison shopping the aisle, finding the markdown, handing a coupon to the cashier, paying the sales tax, and watching his mother photograph the receipt before the car leaves the parking lot. Sixteen-plus money concepts ride inside the plot. Nobody in the book says the word "budget."
-The case for the shelf: nearly every money picture book teaches earning or saving. To my knowledge this is the first narrative picture book for this band that follows the whole consumer arc, wish through receipt. The back matter carries a twenty-one-term glossary in which every definition cites the page where the term happens in the story, so a child looking something up lands in a scene rather than a definition list.
+The case for the shelf: nearly every money picture book teaches earning or saving, which is the second thing a child does with money. Spending is the first. To my knowledge this is the first narrative picture book for this band that follows the whole consumer arc, wish through receipt. The back matter carries a twenty-one-term glossary in which every definition cites the page where the term happens in the story, so a child looking something up lands in a scene rather than a definition list.
 Cataloguing: ISBN 979-8-234-07638-0 · LCCN 2026906164 · hardbound, case bound, full colour, 11×8.5′′ · Est. Lexile AD 620L, Guided Reading L–N · $19.99. Full record at clarencegetsabargain.com/book-facts.html. The AD in that Lexile stands for Adult Directed, so it does double duty as a read-aloud title and a take-home.
 Programming, already built and free: printable price tags and clearance stickers for a pretend store, a browser-based Sea-Mart register children operate themselves with a markdown, a coupon and sales tax, and a quiz with a printable certificate. No prep budget required for a Financial Literacy Month or Money Smart Week event.
 Endorsed by a K–5 educator with 30+ years in the classroom and by the 2026 EIFLE Educator of the Year.
@@ -30338,8 +30332,7 @@
           <t>Gretchen — you have spent a career on how financial products get sold to people who don't fully understand them. Here is the entry-level version of that, and nobody covers it.
 A child becomes a consumer the first time money leaves their hand. Six years old, a birthday five, a store. From that moment they are a party to transactions, and the entire financial education apparatus treats them as a saver in training instead. We teach them to hold money. Nobody teaches them what happens when they use it.
 The scale is small and the mechanics are identical to the ones you write about. A claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the child has no way of knowing that. Not a game of skill — a slot machine wearing a carnival hat, aimed at someone with no price memory and no comparison to make.
-I wrote the picture book for it. One kid, one purchase, followed the whole way: he wants a robot, earns it, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget." The child works out he has been schooled only when he reaches the glossary — twenty-one terms in the back, each page-referenced to where it happened.
-The format matters: Lexile AD 620L. The AD is Adult Directed, the trade's own code for a book meant to be read with a child rather than handed over.
+I wrote the picture book for it. One kid, one purchase, followed the whole way: he wants a robot, earns it, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget." The child works out he has been schooled only when he reaches the glossary — twenty-one terms in the back, each page-referenced to where it happened. It is catalogued Lexile AD 620L, where AD stands for Adult Directed — the trade's own code for a book an adult reads with a child rather than hands over.
 The story is not the book. It is that an entire publishing category taught children to save for forty years and skipped the register, which is the only place a child has ever handled money — while the arcade, the app store and the checkout lane did not skip it at all.
 Is there anything there? clarencegetsabargain.com/press-kit.html
 Jonathan</t>
@@ -30399,9 +30392,8 @@
           <t>Kim — you cover retail, so you already know the boardwalk arcade is a pricing strategy rather than a game. I wrote the children's book that explains it before a kid loses to it.
 The number I keep coming back to: a claw machine takes $25 to hand back a basketball that Walmart sells for $9.99. That is the entire business model in one glass box — charge $25 for the $9.99 thing and make it feel like winning. Once a kid has seen the $9.99, the claw loses its grip. Nobody shows them the $9.99.
 Every children's money book teaches saving. Piggy banks, jars, three little tins labeled spend-save-give where "spend" gets one page and a guilty look. But saving is the second thing a child does with money. The first is spending, and a six-year-old has done it already, standing in a store, deciding.
-So mine follows a single purchase the entire distance. A boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one deliberately, hands a coupon to the cashier, meets sales tax, and then lives with the thing. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
-It is catalogued Lexile AD 620L — Adult Directed, meaning read-with rather than read-alone, so the parent gets handed the script instead of being expected to know it.
-The retail angle, if you want one: every trick your beat covers — the fake markdown, the anchor price, the "newest is better" framing — gets run on children first, in arcades and toy aisles, where there is no consumer press at all.
+So mine follows a single purchase the entire distance. A boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one deliberately, hands a coupon to the cashier, meets sales tax, and then lives with the thing. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed, so the parent reads it with the kid and gets handed the script instead of being expected to know it.
+The retail angle, if you want one: every trick your beat covers — the fake markdown, the anchor price, the "newest is better" framing — gets run on children first, in arcades and toy aisles, where there is no consumer press at all. The boardwalk airbrush stand charges $28 for a shirt that says BRAYDEN. Your kid's name is not Brayden.
 Worth a look? clarencegetsabargain.com/book-facts.html
 Jonathan</t>
         </is>
@@ -30519,10 +30511,10 @@
       <c r="K30" s="5" t="inlineStr">
         <is>
           <t>Amanda — Planet Money's whole trick is that people will sit still for an economics lesson if it is hidden inside a story about a person and a thing. I did that at a first-grade reading level, and I am writing about the story rather than the book.
-Every children's money book teaches earning or saving. All 25 on the ABA Foundation's list — I read them to be sure. A piggy bank, a lemonade stand, a lesson. Not one covers the cash register, which is the only place a child has ever actually handled money.
-Mine does. A boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, gets ambushed by sales tax, and then lives with what he bought. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget." They do not realise they have been schooled until they hit the glossary in the back — twenty-one terms, each page-referenced to the moment it happened. That is where the con comes apart, on purpose.
-Format note, since you make things people take in together: Lexile AD 620L, where AD means Adult Directed — a book built to be read with a child, interrupted the whole way.
-The segment is the forty-year hole. A whole publishing category taught children to save and skipped the register, while every arcade, app store and checkout lane aimed at children did not skip it at all.
+Every children's money book teaches earning or saving. All 25 on the ABA Foundation's list — I read them to be sure. A piggy bank, a lemonade stand, a lesson. Not one covers the cash register. Saving is the second thing a child does with money; spending is the first, and the register is the only place a child has ever actually handled any.
+Mine does. A boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, gets ambushed by sales tax, and then lives with what he bought. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget." They do not realise they have been schooled until they hit the glossary in the back — twenty-one terms, each page-referenced to the moment it happened. That is where the con comes apart, on purpose. It is catalogued AD 620L — Adult Directed — which is the trade's way of saying it only works out loud, with somebody interrupting.
+The numbers on the other side are absurd and nobody has ever put a microphone on them. Twelve hundred arcade tickets for a rubber slinky is an exchange rate that would embarrass a currency trader, and the kid making that trade has no idea he is trading.
+The segment is the forty-year hole. A whole publishing category taught children to save and skipped the register, while every arcade, app store and checkout lane aimed at children did not skip it at all. Nobody regulates the toy aisle and nobody covers it.
 Is that an episode whether or not my book is in it? Four-minute flip: https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
         </is>
@@ -30581,7 +30573,7 @@
           <t>Bethann — you run the education side of a bankers association, which means you are the person who decides what volunteers actually carry into a classroom. I built something for the grade band most bank programs skip.
 Most financial education a bank sponsors lands in high school or in a "teach a child to save" day about saving. Saving is the second thing a child does with money. The first is spending, and a first grader has done it, at a register, with a parent behind her. There is almost nothing to hand a banker walking into a second-grade room about that.
 Clarence Gets a Bargain is a 36-page picture book following one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget."
-Why it works for a volunteer rather than a teacher: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, and the mother explains every concept inside the text. A banker can read it cold and field the questions straight off the page. No training call, nothing to memorise. Free lesson plans, assessments and a browser-based pretend register sit behind it, all ungated.
+Why it works for a volunteer rather than a teacher: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, and the mother explains every concept inside the text. A banker can read it cold and field the questions straight off the page. No training call, nothing to memorise. The twenty-one-term glossary in the back is page-referenced to the story, so a volunteer answering a vocabulary question can turn to the scene rather than recite a definition. Free lesson plans, assessments and a browser-based pretend register sit behind it, all ungated.
 The sponsorship math is simple if a member bank wants it: 25 copies is $499.75, one classroom, the bank's name on every book that goes home to a family. The educator program is free, so the sponsorship is entirely books, and I have a CRA-ready memo already written in examiner-friendly language.
 Does that fit how Utah banks choose classroom programs, or am I inventing a use case?
 clarencegetsabargain.com/educator-toolkit.html
@@ -30643,8 +30635,7 @@
 Every children's money book teaches saving. Piggy banks, jars, three tins labeled spend-save-give where "spend" gets one page and a guilty look. But saving is the second thing a child does with money. The first is spending, and a first grader has already done it — in a store, holding money, deciding.
 And the tools have moved against them. A card is magic; a five-dollar bill is arithmetic — a kid who watches three dollars leave their hand understands something no tap-to-pay will ever teach.
 Which matters most in households where there is no margin for a bad purchase. A child taught only to save has been handed advice that assumes surplus. A child who can compare two prices and choose deliberately has a skill that works this Saturday.
-Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, meets sales tax, and then lives with what he chose. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the story.
-Catalogued Lexile AD 620L — Adult Directed — so the adult reading it is handed the script and does not have to be the one who already knows about money. That was the design constraint that mattered most: it has to work in a house where nobody feels qualified to teach it.
+Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, meets sales tax, and then lives with what he chose. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the story. It is catalogued AD 620L — Adult Directed — so the adult reading gets handed the script and does not have to be the one who already knows about money. That was the design constraint that mattered most: it has to work in a house where nobody feels qualified to teach it.
 Two questions. Does the spending-first argument hold up against what you hear from your audience? And is there a version of this worth putting in front of the Financial Influencer Network?
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -30704,8 +30695,7 @@
           <t>Ruben — CEE's standards are one of the five frameworks I crosswalked against, so I have spent real time inside them and want to ask about the bottom of the ladder.
 The elementary benchmarks exist. What is built against them is thin, and thinner still on the spending side. The field starts children with saving, and saving is the second thing a person does with money. The first is spending: standing in front of two prices and choosing one. A first grader has done that; she has no savings rate at all.
 I built a free K–5 classroom set around a 36-page picture book and crosswalked it concept by concept — 23 rows against the 2021 National Standards for Personal Financial Education, CEE, Common Core Math and ELA, and FDIC Money Smart, with the Grade 4 benchmark codes rather than a general claim of alignment. It is published so a reviewer can check it instead of taking my word.
-The book follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with the choice. Sixteen-plus concepts and nobody in it says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened.
-Catalogued Lexile AD 620L — Adult Directed — one class period read aloud, and because the mother explains every concept inside the text a teacher with no economics background can run it cold.
+The book follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with the choice. Sixteen-plus concepts and nobody in it says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened. Catalogued AD 620L — Adult Directed — one class period read aloud, and because the mother explains every concept inside the text a teacher with no economics background runs it cold.
 The question: is there a route for elementary material to sit alongside CEE programs, or does that run through affiliate councils? Either answer saves me guessing.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -30765,8 +30755,7 @@
           <t>Beth — you write for people trying to do the right thing with money and finding the advice arrives late. This arrives about two decades earlier than most of it.
 The premise: financial education starts children with saving, and the sequence is backwards. Saving is the second thing a person does with money. The first is spending. A seven-year-old has no savings rate and no income; what she has done is stand at a register holding money and choose. We teach that last, or never.
 I wrote the picture book for it. One purchase, followed the whole way — a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, meets sales tax, and then lives with what he chose. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; not one covers the whole arc.
-Sixteen-plus concepts, none announced — nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened, so vocabulary points a kid back into the story rather than away from it.
-Catalogued Lexile AD 620L — Adult Directed, read-with rather than read-alone. The mother explains everything on the page, so the parent gets the script and can take the credit.
+Sixteen-plus concepts, none announced — nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened, so vocabulary points a kid back into the story rather than away from it. It is catalogued AD 620L — Adult Directed — and the mother explains everything on the page, so the parent gets the script and can take the credit.
 One thing I would put to you as a planner: a card is magic, and a five-dollar bill is arithmetic. Children now grow up almost entirely inside the first one, which removes the only feedback loop they had.
 The claim I would defend hardest is the delayed one. The book is not really working in the twenty minutes it takes to read. It works in month eighteen, in a real store, when the kid hits a money moment and the book fires back — "wait, is the newer one actually better?" Recognition first, then the habit.
 Does that hold up against what you see in readers? clarencegetsabargain.com/book-facts.html
@@ -30827,8 +30816,7 @@
           <t>Julie — a segment idea, and it is short enough to survive a live hit.
 Every children's money book teaches saving. Piggy banks, lemonade stands, jars. But saving is the second thing a child does with money — the first is spending, and a six-year-old has already done it, in a store, holding a birthday five, deciding whether the thing is worth what it costs.
 The category skipped that for forty years. The arcade did not. A claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the kid has no price memory to defend himself with. Once a kid has seen the $9.99, the claw loses its grip.
-So I wrote the spending book. Clarence Gets a Bargain, ages 6–10: a boy earns a robot with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and then lives with the thing he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Twenty-one terms in a glossary at the back, each page-referenced to where it happened.
-Catalogued Lexile AD 620L — Adult Directed, the trade's own code for a book read with a child rather than handed to one. Twenty minutes out loud, interrupted the whole way.
+So I wrote the spending book. Clarence Gets a Bargain, ages 6–10: a boy earns a robot with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and then lives with the thing he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Twenty-one terms in a glossary at the back, each page-referenced to where it happened. Catalogued AD 620L — Adult Directed — twenty minutes out loud, interrupted the whole way.
 I am an attorney and a mixed-media artist, and I have twice walked out of the same Nordstrom Rack having paid one cent — once for a $293 pair of shoes, once for a $69.50 shirt. I kept both tags. It makes for a good visual if you ever want one on screen.
 Is there a hit in "the money skill nobody teaches kids"? clarencegetsabargain.com/press-kit.html
 Jonathan</t>
@@ -30888,8 +30876,7 @@
           <t>Matt — you spend your working life on what happens when people meet credit without the groundwork. I wrote the book about the groundwork, roughly twenty years upstream of your data.
 The sequence is the whole argument. Financial education starts children with saving. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent behind her. Mistakes at eleven cost $14. The same mistake at twenty-seven has a credit card attached and a rate on it.
 Clarence Gets a Bargain follows one purchase the entire distance: a boy wants a robot, earns it with chores and grades, works the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; they are all parked on the earning-and-saving side of the register.
-Sixteen-plus concepts and nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened — which is the only point at which a kid works out he has been schooled.
-Catalogued Lexile AD 620L — Adult Directed, so it is read-with rather than read-alone and the parent gets handed the script.
+Sixteen-plus concepts and nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened — which is the only point at which a kid works out he has been schooled. Catalogued AD 620L — Adult Directed — read with a parent, not handed to a kid alone. The single sentence I most want an eleven-year-old to own: marked down does not mean broken, it means the timing is on your side.
 The question, since you have the data and I only have the book: does anything in what you see suggest that price competence at seven shows up at twenty-seven? If it does not, I would rather know.
 clarencegetsabargain.com/book-facts.html
 Jonathan</t>
@@ -31071,6 +31058,7 @@
 Thirty states now guarantee a personal finance course. Every one of those mandates lands in high school. Money habits are largely set by seven — so the policy arrives roughly ten years after the cement dries, and the funding, the training and the reporting all follow the mandate rather than the evidence.
 Underneath that sits an assumption nobody argues with: that children should learn saving first. I think it is backwards. Saving is the second thing a person does with money. The first is spending, and a first grader has done that, at a register, with a parent standing behind her. The behaviors a high school course tries to correct were installed a decade earlier by an arcade, a toy aisle and a checkout lane, none of which waited for a curriculum.
 I wrote the elementary piece rather than an op-ed about it. A 36-page picture book following one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, and living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Free ungated classroom set behind it, crosswalked to five frameworks. Catalogued Lexile AD 620L — Adult Directed, so it is a read-with, and the caregiver conversation happens inside the reading.
+Meanwhile the arcade never waited for a standard: $25 into a glass box for a basketball Walmart sells for $9.99, and the kid has no price memory to argue with.
 The story I would pitch your desk: the whole country legislated financial literacy into ninth grade, and the elementary standards that already exist in most states sit there with nothing built against them, because nobody has to report on them.
 Does that belong to anyone on your team? clarencegetsabargain.com/book-facts.html
 Jonathan</t>
@@ -31130,9 +31118,9 @@
           <t>Stacy — you write about what happens to ordinary people inside financial systems. There is a version of that beat with no coverage at all, and it starts at about age six.
 A child becomes a consumer the first time they hand money to a cashier. Not at eighteen, not at a first paycheck — at six, with a birthday five. From that moment they are party to a transaction and they have rights nobody mentions: the receipt is proof, the price on the shelf has to match the price at the register, a broken thing can go back. Consumer education is the missing wing of children's financial literacy. We teach them to save and never tell them they are already the buyer.
 That is why I wrote the book. Clarence Gets a Bargain follows one purchase the entire way — a boy wants a robot, earns it, reads the sale inserts at the kitchen table, compares two on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced, and a twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
-The detail people ask me about: the mother photographs the receipt the second she sits down in the car. Every time. It takes four seconds and it is what makes a return, an exchange or a warranty claim winnable. Almost nobody teaches a child that.
-Format: Lexile AD 620L — Adult Directed, the trade's code for read-with rather than read-alone.
-I am an attorney, so I will say the honest version: the full picture crosses agencies, warranties and returns sit with the FTC, product safety with the CPSC. Nobody owns "children as consumers," which may be why nobody covers it.
+The detail people ask me about: the mother photographs the receipt the second she sits down in the car. Every time. It takes four seconds and it is what makes a return, an exchange or a warranty claim winnable. Almost nobody teaches a child that, which is why the book is catalogued AD 620L — Adult Directed — and gets read with an adult rather than handed to a kid alone.
+I am an attorney, and on vacation that mostly means the souvenirs get cross-examined. The hermit crab: who feeds it over the holidays, and in two weeks when it dies — and buddy, it will — is it worth the tears? My kids find this insufferable. It is also the entire skill.
+The honest version of the beat problem: the full picture crosses agencies. Warranties and returns sit with the FTC, product safety with the CPSC. Nobody owns "children as consumers," which may be exactly why nobody covers it.
 Is there a story in that? clarencegetsabargain.com/press-kit.html
 Jonathan</t>
         </is>
@@ -31192,8 +31180,7 @@
 The gap as I see it: elementary standards exist in most states and almost nothing is built against them, because nobody has to report on them. Every mandate lands in high school. Thirty states now.
 And underneath that, a sequencing assumption nobody argues with — that children should learn saving first. Saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has stood at a register and chosen.
 So I wrote the K–5 piece. Clarence Gets a Bargain follows one purchase from the idea to after the receipt: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, so vocabulary review points a child back into the story instead of away from it.
-The teacher side is free and ungated — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE, and FDIC Money Smart. No account, no email capture. It prints from a browser.
-Catalogued Lexile AD 620L — Adult Directed — so it runs as a one-period read-aloud and a teacher with no finance background can deliver it cold.
+The teacher side is free and ungated — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE, and FDIC Money Smart. No account, no email capture, and it prints from a browser. Catalogued AD 620L — Adult Directed — a one-period read-aloud a teacher with no finance background can deliver cold.
 Does the spending-first sequence match what you see in classrooms, or is there a reason the field starts where it starts?
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -31255,6 +31242,7 @@
 Every children's book on the shelf teaches saving. Piggy banks, jars, patience. But saving is the second thing a child does with money; the first is spending, and a six-year-old has already done it.
 Clarence Gets a Bargain follows one purchase the whole way — earning the reward through chores and grades, working the sale ads at the kitchen table, comparing two models on a shelf, taking the cheaper one on purpose, handing over a coupon, meeting sales tax, and then living with what was bought. Idea to post-receipt. And on page 6 there is something I have not found in any other picture book: a 529 plan. In the plot. Explained by a mom, eye-rolled at by a kid, and defended by a dad two scenes later.
 Sixteen-plus concepts and nobody says "budget." A twenty-one-term glossary in the back, page-referenced to the story. Catalogued Lexile AD 620L — Adult Directed — so it is a read-with, and the conversation happens during the reading rather than after it.
+A card is magic; a five-dollar bill is arithmetic. Children now grow up almost entirely inside the first one, which removed the only feedback loop they had.
 The angle for your beat: advisors spend fortunes trying to meet the next generation before the assets move. This is what meeting them at seven looks like, and it costs $19.99.
 Worth a column, or am I describing something you have already covered? clarencegetsabargain.com/press-kit.html
 Jonathan</t>
@@ -31438,8 +31426,7 @@
         <is>
           <t>Sam — you have been reading, singing and performing a savings habit into elementary classrooms for two decades across thirty states, which is more direct contact with this audience than anyone else in the category has. So I want to put an argument in front of you and hear where it is wrong.
 Sammy teaches saving, and teaches it better than anything else aimed at this age. My argument is not about quality; it is about order. Saving is the second thing a child does with money. The first is spending — a first grader has stood at a register holding money and chosen, years before she has anything to save. Teach that moment first, and everything Sammy preaches lands harder, because a kid who understands what money buys has a reason to keep some.
-That is the book I wrote. Clarence Gets a Bargain follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the scene each term came from.
-Catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, with every concept explained inside the text, so somebody can read it cold to a class. You will recognise why that mattered to me.
+That is the book I wrote. Clarence Gets a Bargain follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the scene each term came from. Catalogued AD 620L — Adult Directed — about twenty minutes out loud, every concept explained inside the text, so somebody can read it cold to a class. You of all people will know why that mattered to me.
 You also solved a distribution problem the rest of us have not: banks and credit unions sponsor the visits and buy the books, and their community reports write themselves. I would rather learn that from you than reverse-engineer it.
 Trade copies and compare notes? I will read Sammy properly and tell you the truth about it, which is the only thing worth trading.
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -31562,6 +31549,7 @@
 Thirty states now require personal finance to graduate. The mandates land in high school, and the funding, the training and the reporting follow the mandate. Meanwhile the K–5 standards that already exist in most states sit there with almost nothing built against them, because nobody has to report on them.
 The assumption underneath is that children should learn saving first. I think it is backwards, and I would rather be told so by NEFE than keep saying it at conferences. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent standing behind her. The behaviors a high school course is trying to correct were installed a decade earlier.
 I wrote the elementary piece rather than an argument about it: a 36-page picture book that follows one purchase from the idea to after the receipt, plus a free ungated classroom set crosswalked to the 2021 National Standards, Common Core, CEE and FDIC Money Smart. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Catalogued Lexile AD 620L — Adult Directed — so the intervention is a shared read rather than solo reading, which also makes it easier to study than a curriculum.
+The line I would put on a poster if I could: mistakes at eleven cost $14, and the same mistake at twenty-seven has a credit card attached.
 The question: does NEFE's research or advocacy work have a position on the elementary band, or is the practical view that high school is where the effort pays? If it is the second, I would like to know I am arguing with a considered consensus rather than filling a gap it agrees exists.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan Bach
@@ -31624,6 +31612,7 @@
 There is also a sequencing assumption underneath the whole field that I would like your view on. Financial education starts children with saving. Saving is the second thing a person does with money; the first is spending. A first grader has no savings rate. She has stood at a register holding money and had to choose.
 I built a free, ungated K–5 classroom set around a 36-page picture book: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE and FDIC Money Smart, printable classroom pieces, and a browser-based pretend register. No account, no email capture, no purchase order. It prints from a browser.
 The book follows one complete purchase — sale ads, comparison, a markdown, a coupon, sales tax — with sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story. Catalogued Lexile AD 620L, Adult Directed, so it runs as a one-period read-aloud with no teacher training required.
+One line from the book does the work of a standards document, and it is the one I would defend hardest: marked down does not mean broken, it means the timing is on your side.
 Two questions. Does Jump$tart consider elementary in scope, or is it a band the coalition has consciously left to others? And for the Clearinghouse, is the free classroom set the right thing to submit rather than the book?
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -31684,8 +31673,7 @@
 Wesley learns to invest. Clarence learns to spend — and I mean the mechanics of it rather than the idea. Every other book in the category teaches saving, which is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. Nobody had written that one, so I did.
 Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Nobody says the word "budget."
 The craft problem I would most like another author's view on: the reader is not supposed to know he has been taught anything until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. Getting that balance right, so it stays a story, was the whole job, and it is the thing most likely to be off by a hair.
-I did the illustrations too, which means my opinion of them is worth nothing.
-Catalogued Lexile AD 620L — Adult Directed — written for the adult voice in the room, with the mother carrying every explanation.
+I did the illustrations too, which means my opinion of them is worth nothing. It is written for the adult voice in the room — catalogued AD 620L, Adult Directed — with the mother carrying every explanation.
 Trade? Send me a Wesley and I will read it properly rather than politely.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -31745,9 +31733,9 @@
           <t>Kate — a pitch about a gap rather than a book, though I wrote the book because of the gap.
 Everything in kids' financial literacy points at a horizon no child can see: compound interest, credit scores, retirement. All real, all decades out. Meanwhile the kid is eight, holding $20 of birthday money, standing in a store that spent millions working out how to get it. We are preparing children for 65 and sending them to the register unarmed today.
 So flip the order. Saving is the second thing a child does with money. The first is spending, and it is the one nobody puts in a story.
-Clarence Gets a Bargain does. One kid, one purchase, followed the whole distance — he wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget." The reader works out he has been schooled at the glossary — twenty-one terms in the back, each one page-referenced to the scene it came from.
-Catalogued Lexile AD 620L. The AD is Adult Directed, the industry's own code for a book meant to be read with a child rather than handed over, so a parent who does not feel qualified on money still gets handed the script.
-Timely hook if you need one: thirty states now guarantee a personal finance course, all of it in high school, roughly ten years after the habits form. The elementary standards already exist in most states and have almost nothing built against them.
+Clarence Gets a Bargain does. One kid, one purchase, followed the whole distance — he wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget." The reader works out he has been schooled at the glossary — twenty-one terms in the back, each one page-referenced to the scene it came from. Catalogued AD 620L — Adult Directed — so a parent who does not feel qualified on money still gets handed the script and can take the credit.
+The boardwalk is a pop quiz your kid has not studied for, and it runs all summer with real money.
+Timely hook if you need one: thirty states now guarantee a personal finance course, all of it in high school, long after the habits form. The elementary standards already exist in most states and have almost nothing built against them.
 Any of that useful to you? clarencegetsabargain.com/book-facts.html
 Jonathan</t>
         </is>
@@ -32097,7 +32085,7 @@
       <c r="K56" s="5" t="inlineStr">
         <is>
           <t>Iris — you were part of the group that chose the titles on the Money as You Grow Bookshelf, so you have read this category more carefully than almost anyone, and you will know immediately whether my premise is wrong.
-The shelf, as it stands, leans toward saving and earning. What is thin is spending, and specifically the transaction — the part where a child stands in front of two prices and has to pick one. That is the first financial act a person performs. It gets taught last.
+The shelf, as it stands, leans toward saving and earning. Spending is thin, and the transaction itself is thinner — the part where a child stands in front of two prices and picks one. Saving is the second thing a person does with money; spending is the first, and it gets taught last or not at all.
 Clarence Gets a Bargain covers exactly that, and covers the whole of it: a boy wants a robot, earns it through chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list looking for another one that does the whole arc. They are all parked on the earning-and-saving side of the register.
 Sixteen-plus concepts and none is announced — no character pauses to define a term, nobody says the word "budget." The proof and the reveal are both in the back matter: a reader does not know he has been schooled until he reaches the glossary. Twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than an appendix.
 Ages 6–10, inside the Bookshelf's 4–10 band. Catalogued Lexile AD 620L — Adult Directed, which is how the Bookshelf's titles are meant to be used anyway.
@@ -32169,6 +32157,7 @@
 A six-year-old with a birthday five in an aisle is running a comparison with no price history, no reference class and no idea that anchoring exists. She is the purest case your field could ask for and the least documented. Meanwhile the environment is not naive at all — a boardwalk claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the child has no way of knowing the $9.99 exists.
 Financial education answers this by teaching saving. But saving is the second thing a person does with money; the first is spending, and it is taught last or not at all.
 I wrote the picture book rather than the paper. Clarence Gets a Bargain follows one complete purchase — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with the choice afterward. Sixteen-plus concepts, none announced. Twenty-one terms in a back-matter glossary, each page-referenced to the scene it came from. Catalogued Lexile AD 620L — Adult Directed — so the reading is a joint activity by design rather than a solo one.
+For what it is worth, the field's own blind spot has a price tag on it: a boardwalk claw machine takes $25 to hand back a basketball Walmart sells for $9.99, and no curriculum anywhere treats that as a financial event.
 The question I would actually like answered: is there work on when price competence forms, and whether early exposure to comparison changes anything measurable later? If the honest answer is that it is unstudied because it is unmeasurable at that age, that is worth knowing too.
 clarencegetsabargain.com/book-facts.html
 Jonathan Bach
@@ -32229,8 +32218,7 @@
           <t>Bina — a question about where community development work draws its lower age bound.
 Most financial capability programming aimed at low- and moderate-income families reaches adults, or reaches children through savings vehicles — child savings accounts, matched savings, college accounts. All of that is aimed at accumulation. Very little addresses the other side of the household ledger at a child's level: what happens when the money is spent, which for a child is nearly all of it.
 That gap has a sequencing problem behind it. Saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has handled money at a register, and the decision she made there was unassisted.
-I built the elementary resource. A 36-page picture book that follows one complete purchase — sale ads, comparison shopping, a markdown, a coupon, sales tax, and living with what was bought — with sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story. Behind it, a free ungated classroom and family set crosswalked to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE and FDIC Money Smart. No account, no email capture, no purchase order; it prints from a browser, which matters where budgets do not exist.
-Catalogued Lexile AD 620L — Adult Directed — so it works as a shared read with a caregiver who does not need to know the material first, which is the design constraint that mattered most to me.
+I built the elementary resource. A 36-page picture book that follows one complete purchase — sale ads, comparison shopping, a markdown, a coupon, sales tax, and living with what was bought — with sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story. Behind it, a free ungated classroom and family set crosswalked to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE and FDIC Money Smart. No account, no email capture, no purchase order; it prints from a browser, which matters where budgets do not exist. It is catalogued AD 620L — Adult Directed — so it works as a shared read with a caregiver who does not need to know the material first. That was the design constraint that mattered most to me.
 The question: does SF Fed's community engagement work touch the elementary band, or does it start at the account level with adults?
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan Bach
@@ -32349,8 +32337,7 @@
           <t>Jennifer — a funding-shaped question rather than an ask, and the resource itself is already free.
 I wrote and illustrated a K–5 financial-literacy picture book and built the entire classroom program behind it — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a standards crosswalk across five frameworks. All of it is ungated: no account, no email capture, no purchase order, prints from a browser. The only thing that ever costs anything is the physical books, and 25 copies run $499.75.
 The content premise: every children's money book teaches saving, and saving is the second thing a child does with money. The first is spending — a first grader has stood at a register and chosen. The book follows one complete purchase from the idea through the receipt, with sixteen-plus concepts hidden in the plot and a twenty-one-term glossary page-referenced back into the story.
-Why I am writing to development rather than to a classroom: this is unusually easy to fund. A bank or credit union sponsoring a classroom set gets its name on every book that goes home to a family in its assessment area, the curriculum costs the sponsor nothing because it is already free, and I have a CRA-ready memo written in examiner-friendly language. A funder can point at 25 books, one classroom, and a pre/post instrument.
-Catalogued Lexile AD 620L — Adult Directed — which also makes it a family-engagement asset rather than only a classroom one, since the book works at a kitchen table with a parent or a grandparent doing the reading.
+Why I am writing to development rather than to a classroom: this is unusually easy to fund. A bank or credit union sponsoring a classroom set gets its name on every book that goes home to a family in its assessment area, the curriculum costs the sponsor nothing because it is already free, and I have a CRA-ready memo written in examiner-friendly language. A funder can point at 25 books, one classroom, and a pre/post instrument. And because it is catalogued AD 620L — Adult Directed — it doubles as family engagement: the same book works at a kitchen table with a parent or a grandparent reading.
 Is a sponsored classroom set something HCZ's funders would recognise, or does everything need to attach to an existing program line?
 clarencegetsabargain.com/resources/grant-in-a-box.html
 Jonathan</t>
@@ -32408,7 +32395,7 @@
       <c r="K61" s="5" t="inlineStr">
         <is>
           <t>Flora — JA runs volunteers into elementary classrooms better than any organisation in the country, so this is a materials question rather than a pitch.
-JA's elementary programs are strong on earning, jobs and community. What is thin across the whole field — not just JA — is spending, and specifically the transaction itself. A first grader has no savings rate and no job. What she has done is stand at a register holding money and choose.
+JA's elementary programs are strong on earning, jobs and community. What is thin across the whole field, JA included, is spending — the second thing everybody teaches and the first thing a child actually does. A first grader has no savings rate and no job. What she has done is stand at a register holding money and choose.
 Clarence Gets a Bargain is a 36-page picture book that puts the entire transaction on the page: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
 The part that matters for a volunteer model: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, with every concept explained inside the text by the mother. A volunteer who has never taught anything can read it cold and answer questions off the page. Nothing to memorise and no prep call. Behind it, free and ungated: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable price tags and clearance stickers for a classroom store, and a browser-based pretend register with a markdown, a coupon and sales tax.
 Alaska has its own complications on distance and travel, and virtual read-alouds work for this.
@@ -32471,8 +32458,8 @@
           <t>Elizabeth — a scope question rather than a pitch.
 Federal attention to financial education, like every state mandate, concentrates on high school. Thirty states now require a course to graduate. The elementary standards that exist in most states sit underneath that with very little built against them, largely because nothing requires reporting at that band.
 The assumption underneath is that children begin with saving. Saving is the second thing a person does with money. The first is spending — a first grader has handled money at a register and made a decision there with no framework at all.
-I built a free, ungated K–5 resource for that: a 36-page picture book that follows one complete purchase from the idea through the receipt — sale ads, comparison shopping, a markdown, a coupon, sales tax — and a classroom set behind it. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a browser-based pretend register, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education alongside Common Core Math and ELA, CEE and FDIC Money Smart, cited at the Grade 4 benchmark level rather than claimed generally.
-No account, no email capture, no purchase order. It prints from a browser. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud requiring no instructor training.
+I built a free, ungated K–5 resource for that: a 36-page picture book that follows one complete purchase from the idea through the receipt — sale ads, comparison shopping, a markdown, a coupon, sales tax — and a classroom set behind it. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a browser-based pretend register, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education alongside Common Core Math and ELA, CEE and FDIC Money Smart, cited at the Grade 4 benchmark level rather than claimed generally. Sixteen-plus concepts appear in the story without being announced, and a twenty-one-term glossary in the back matter page-references each one to the scene where it occurs.
+No concept is announced in the text; the twenty-one-term glossary in the back matter carries the definitions, each page-referenced to where the term occurs. No account, no email capture, no purchase order. It prints from a browser. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud requiring no instructor training.
 The question: does any Department program or clearinghouse take elementary financial-education material, or is the practical route through the states? A steer on who would know is as useful to me as an answer.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan Bach
@@ -32533,8 +32520,7 @@
           <t>Gene — Troutwood is built on showing people the long arc of a decision, which is why I am writing about the very first decision on that arc.
 Everything in financial planning compounds, including the mistakes, and the compounding starts long before anyone opens an account. Mistakes at eleven cost $14. The same mistake at twenty-seven has a credit card attached. The habit doing the compounding was installed at six, in a store, with a parent saying no and no reasoning attached to the no.
 Financial education answers that by teaching children saving. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with no framework at all.
-Clarence Gets a Bargain is the picture book for that. One purchase, followed the whole way: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
-Catalogued Lexile AD 620L — Adult Directed — so it is a shared read, and the parent gets handed the script rather than a homework assignment.
+Clarence Gets a Bargain is the picture book for that. One purchase, followed the whole way: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed — so it is a shared read and the parent gets the script rather than a homework assignment.
 The claim I would defend hardest is the delayed one, and it is the same claim Troutwood makes about projections: the value is not in the twenty minutes. It is in month eighteen, in a real store, when the kid hits a money moment and the book fires back. Recognition first, then the habit.
 Does the elementary end fit anything Troutwood does, or is that below the floor?
 clarencegetsabargain.com/book-facts.html
@@ -32657,8 +32643,7 @@
 Planners meet clients' children late, usually at the worst possible moment, and by then the habits are twenty years old. They were formed at six, in a store, with a parent saying no and no reasoning attached to the no.
 The field's answer to that is to teach children saving. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, holding a birthday five, deciding whether the thing is worth what it costs.
 I wrote the picture book for that moment. Clarence Gets a Bargain follows one purchase the whole way — earning the reward through chores and grades, working the sale ads at the kitchen table, comparing two models on a shelf, taking the cheaper one on purpose, redeeming a coupon, meeting sales tax, and then living with what was bought. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in a back-matter glossary, page-referenced to the story.
-And on page 6 there is something I have not found in any other picture book: a 529 plan. In the plot. Explained by a mother, eye-rolled at by a kid, defended by a father two scenes later.
-Catalogued Lexile AD 620L — Adult Directed, so a planner handing it to a client family is handing over a script rather than an assignment. Twenty-five copies run $499.75, and the educator program behind it is free.
+And on page 6 there is something I have not found in any other picture book: a 529 plan. In the plot. Explained by a mother, eye-rolled at by a kid, defended by a father two scenes later. It is catalogued AD 620L — Adult Directed — so a planner handing it to a client family is handing over a script rather than an assignment. Twenty-five copies run $499.75, and the educator program behind it is free.
 The question: does CFP Board's pro bono and public-education work reach below high school at all, or is that considered somebody else's ground?
 clarencegetsabargain.com/book-facts.html
 Jonathan</t>
@@ -32717,7 +32702,7 @@
         <is>
           <t>Ed — a narrow question about evidence standards, asked before I go further with something.
 I have built a free K–5 financial-education resource — a 36-page picture book plus a complete classroom set — and crosswalked it to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE and FDIC Money Smart, at the Grade 4 benchmark level. Everything is ungated: no account, no email capture, no purchase order, and it prints from a browser.
-The content premise is that the field has the sequence backwards. Financial education starts children with saving; saving is the second thing a person does with money. The first is spending, and a first grader has already done it at a register. The book follows one complete purchase from the idea through the receipt — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with what was bought.
+The content premise is that the field has the sequence backwards. Financial education starts children with saving; saving is the second thing a person does with money. The first is spending, and a first grader has already done it at a register. The book follows one complete purchase from the idea through the receipt — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with what was bought. No concept is announced in the text; a twenty-one-term glossary in the back matter carries the definitions, each page-referenced to where the term occurs.
 One structural detail relevant to evaluation: the book is catalogued Lexile AD 620L — Adult Directed — so it is delivered as a shared read between an adult and a child rather than independent reading. That makes it closer to a shared-reading intervention than a curriculum, which may change what kind of evidence would be appropriate.
 The question: what would a resource like this need in order to be taken seriously on evidence — a pre/post instrument administered at scale, a quasi-experimental design, something else? I would rather build the right study once than assemble the wrong one. And if the honest answer is that no federal pathway exists for elementary material of this kind, that is worth knowing too.
 clarencegetsabargain.com/educator-toolkit.html
@@ -32840,8 +32825,7 @@
         <is>
           <t>Annie — you built a product for the exact age band everyone else in this category skips, so you already believe the thing I have been arguing. I want to compare notes rather than pitch you.
 My First Nest Egg puts save, spend, give and invest in front of a young child in physical form. My argument is about which of those a child actually performs first. It is spending — a six-year-old has stood in a store holding money and chosen, years before she has anything to save or invest. The category teaches saving first anyway, and I could not find the book that teaches the other one.
-So I wrote and illustrated it. Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
-Catalogued Lexile AD 620L — Adult Directed — read-with rather than read-alone, so the parent gets handed the script. And there is a free browser-based pretend register behind it that runs a markdown, a coupon and sales tax, which is the closest thing I have to your physical product.
+So I wrote and illustrated it. Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed — read with a grown-up rather than handed over. There is also a free browser-based pretend register behind it that runs a markdown, a coupon and sales tax, which is the closest thing I have to your physical product.
 Those look complementary rather than competing to me: yours gives a kid the categories in their hands, mine walks them through the mechanics of one transaction in twenty minutes.
 Worth a conversation about whether they belong near each other? And separately — if you think spending-before-saving is wrong, you are one of very few people whose disagreement would actually change my mind.
 https://heyzine.com/flip-book/eeb1ef6cff.html

--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -1869,7 +1869,7 @@
           <t>Bill — a question about grade band from someone who has read what states actually fund.
 Tennessee's requirement, like all thirty of them, lands in high school. That is where the money, the training and the reporting go. The elementary standards sit underneath it with almost nothing built against them, because nothing requires a district to report on that band.
 The sequencing assumption is the part I keep circling. Financial education starts children with saving. Saving is the second thing a person does with money; the first is spending, and a first grader has done it — at a register, with a parent standing right there. The behaviors a high school course tries to correct were installed a decade earlier.
-So I built the K–5 piece. A 36-page picture book that follows one purchase from the idea to after the receipt — sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken on purpose, a coupon at the register, sales tax, and living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story.
+So I built the K–5 piece. A 36-page picture book that follows one purchase from the idea to after the receipt — sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken on purpose, a coupon at the register, sales tax, and living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. There is a whole industry aimed at teenagers who already have the habit, and almost nobody upstream of it.
 What matters for a commission is the rest of it, and it is free: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart. Ungated, no account, prints from a browser. A district adopting it spends nothing. Catalogued Lexile AD 620L — Adult Directed — so it is a one-period read-aloud that needs no teacher training.
 Does elementary sit inside what the Commission convenes or funds, or is high school the whole remit?
 clarencegetsabargain.com/educator-toolkit.html
@@ -1929,7 +1929,7 @@
         <is>
           <t>Dave — Wisconsin has run a state financial-literacy office longer than most states have had a requirement, so you have seen more of these come and go than almost anyone. I would like a read on one assumption.
 Every mandate in the country lands in high school. Thirty of them now. Money habits are largely set by seven, which puts the policy about a decade behind the behaviour. Underneath that sits the belief that children should learn saving first. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent right there.
-I built the K–5 piece rather than an argument about it. A 36-page picture book that follows one complete purchase: the sale ads at the kitchen table, comparison on a shelf, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced — nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
+I built the K–5 piece rather than an argument about it. A 36-page picture book that follows one complete purchase: the sale ads at the kitchen table, comparison on a shelf, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced — nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from. We are very good at teaching this to people who have already made the mistake.
 The classroom set behind it is free and ungated: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, and a 23-row crosswalk to the 2021 National Standards, Common Core Math and ELA, CEE and FDIC Money Smart. No account, no email capture, prints from a browser. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud that a teacher without a finance background can run cold, and the same book works at a kitchen table.
 The question: in your experience, does elementary material get adopted when it is free and aligned, or does it need a mandate behind it to move at all? I would rather know now than find out slowly.
 clarencegetsabargain.com/educator-toolkit.html
@@ -2050,7 +2050,7 @@
         <is>
           <t>Tom — you got more genuine engagement out of one post about kids and money than anyone else in this category has managed, which tells me you know exactly which part of this parents actually care about. I would like to check my premise against that.
 My premise: the whole field has the sequence backwards. Financial education starts children with saving. Saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, standing in a store holding a birthday five, working out whether the thing is worth what it costs. We teach the second thing first and the first thing never.
-So I wrote and illustrated the spending book. Clarence Gets a Bargain follows one purchase the whole way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax and objects to it, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." The reader works out he has been schooled only at the glossary — twenty-one terms in the back, page-referenced to the scene each came from.
+So I wrote and illustrated the spending book. Clarence Gets a Bargain follows one purchase the whole way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax and objects to it, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." The reader works out he has been schooled only at the glossary — twenty-one terms in the back, page-referenced to the scene each came from. A jar is a storage container. It has never once talked a kid out of anything.
 The instruction underneath the whole book is four words long: stop bringing kids to the store as cargo, bring them as staff. Catalogued Lexile AD 620L — Adult Directed — so the parent gets handed the script rather than an assignment, which I suspect is why your posts land: parents want the conversation and do not feel qualified to start it.
 The thing I would actually value: you know what makes a parent stop scrolling on this subject and what makes them scroll past. If "spending before saving" is the wrong hook, I would rather hear it from you than keep testing it slowly.
 Would you look and tell me? https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -2109,10 +2109,10 @@
       <c r="K24" s="5" t="inlineStr">
         <is>
           <t>Andrew — your audience is adults fixing money habits. I wrote the book that tries to stop the habits forming, and there is an episode in the argument whether or not the book is in it.
-Every children's money book teaches saving. Piggy banks, lemonade stands, three jars. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding a birthday five, working out whether the thing is worth what it costs.
+Every children's money book teaches saving. Piggy banks, lemonade stands, three jars. A piggy bank, a lemonade stand, a lesson — that is the whole category, and it has never once been to a register. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding a birthday five, working out whether the thing is worth what it costs.
 Nobody put that in a story. So I did. Clarence Gets a Bargain follows a single purchase the whole way — a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax and regards it as a personal insult, then lives with the thing he chose. Idea to post-receipt.
 Sixteen-plus concepts and none of them announced. Nobody in the book says "budget," which for a book largely about budgeting took some doing. Kids smell a worksheet one page in; they never smell this one, because they are laughing too hard to notice. The reveal is the glossary — twenty-one terms in the back, page-referenced to the scene each came from. It is catalogued AD 620L, Adult Directed, so the parent listening to your show gets handed the script rather than a homework assignment.
-Their books are about earning and saving, which is fine, but there is no game in a piggy bank and kids know it.
+Their books are about earning and saving, which is fine, but there is no game in a piggy bank and kids work that out faster than we do. They smell a worksheet through a backpack.
 The episode I would pitch is not the book. It is the forty-year hole: an entire publishing category taught children to save and skipped the cash register, the only place a child has ever actually handled money.
 Worth twenty minutes of your show? https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -2170,7 +2170,7 @@
       <c r="K25" s="5" t="inlineStr">
         <is>
           <t>Amy — two requests come to your desk all week. A kid wants a robot book. A parent wants something that teaches money. I wrote the one that answers both in a single checkout.
-Clarence Gets a Bargain is a 36-page picture book, ages 6–10, that follows one kid through one complete purchase: he earns a robot reward with chores and grades, does his shopping homework in the newspaper sale ads, comparison-shops the aisle, finds the markdown, hands a coupon to the cashier, meets sales tax, and watches his mother photograph the receipt before the car leaves the lot. Kids read it as a robot story. Saving is the second thing a child does with money; the first is spending, and this is the book for that. Sixteen-plus money concepts come along without announcing themselves, and the back matter carries a twenty-one-term glossary where each definition points to the page where the term happens in the plot — a decoder rather than an appendix.
+Clarence Gets a Bargain is a 36-page picture book, ages 6–10, that follows one kid through one complete purchase: he earns a robot reward with chores and grades, does his shopping homework in the newspaper sale ads, comparison-shops the aisle, finds the markdown, hands a coupon to the cashier, meets sales tax, and watches his mother photograph the receipt before the car leaves the lot. Kids read it as a robot story. Saving is the second thing a child does with money; the first is spending, and this is the book for that. Sixteen-plus money concepts come along without announcing themselves, and the back matter carries a twenty-one-term glossary where each definition points to the page where the term happens in the plot — a decoder rather than an appendix. A worksheet announces itself from three hallways away. Kids file it under school and stop reading, which is a design problem rather than a discipline one.
 The collection case, with the qualifier a librarian will appreciate: most money picture books cover earning or saving. To my knowledge this is the first narrative picture book for this age band that traces the whole consumer arc, wish through receipt. It fills a hole rather than adding a fourth piggy-bank book to the shelf.
 Cataloguing: ISBN 979-8-234-07638-0 · LCCN 2026906164 · hardbound, case bound, full colour, 11×8.5′′ · Est. Lexile AD 620L, Guided Reading L–N · $19.99. The AD is Adult Directed, which makes it a storytime title and a family take-home at the same time. Every fact is on one page: clarencegetsabargain.com/book-facts.html
 Programming is already built and free — printable price tags and clearance stickers for a pretend store, a browser-based register kids run themselves, a five-question quiz with a printable certificate. A storytime plus the pretend store is a complete Money Smart Week event with no prep budget.
@@ -2231,7 +2231,7 @@
         <is>
           <t>Sarah — a collection-development pitch, kept to the facts because I know what August looks like at your desk.
 Clarence Gets a Bargain is a 36-page picture book, ages 6–10, following one kid through one complete purchase: earning the robot reward, doing shopping homework in the newspaper sale ads, comparison shopping the aisle, finding the markdown, handing a coupon to the cashier, paying the sales tax, and watching his mother photograph the receipt before the car leaves the parking lot. Sixteen-plus money concepts ride inside the plot. Nobody in the book says the word "budget."
-The case for the shelf: nearly every money picture book teaches earning or saving, which is the second thing a child does with money. Spending is the first. To my knowledge this is the first narrative picture book for this band that follows the whole consumer arc, wish through receipt. The back matter carries a twenty-one-term glossary in which every definition cites the page where the term happens in the story, so a child looking something up lands in a scene rather than a definition list.
+The case for the shelf: nearly every money picture book teaches earning or saving, which is the second thing a child does with money. Spending is the first. To my knowledge this is the first narrative picture book for this band that follows the whole consumer arc, wish through receipt. The back matter carries a twenty-one-term glossary in which every definition cites the page where the term happens in the story, so a child looking something up lands in a scene rather than a definition list. If a money lesson looks like school, it gets filed under school and read at school speed.
 Cataloguing: ISBN 979-8-234-07638-0 · LCCN 2026906164 · hardbound, case bound, full colour, 11×8.5′′ · Est. Lexile AD 620L, Guided Reading L–N · $19.99. Full record at clarencegetsabargain.com/book-facts.html. The AD in that Lexile stands for Adult Directed, so it does double duty as a read-aloud title and a take-home.
 Programming, already built and free: printable price tags and clearance stickers for a pretend store, a browser-based Sea-Mart register children operate themselves with a markdown, a coupon and sales tax, and a quiz with a printable certificate. No prep budget required for a Financial Literacy Month or Money Smart Week event.
 Endorsed by a K–5 educator with 30+ years in the classroom and by the 2026 EIFLE Educator of the Year.
@@ -2291,7 +2291,7 @@
       <c r="K27" s="5" t="inlineStr">
         <is>
           <t>Gretchen — you have spent a career on how financial products get sold to people who don't fully understand them. Here is the entry-level version of that, and nobody covers it.
-A child becomes a consumer the first time money leaves their hand. Six years old, a birthday five, a store. From that moment they are a party to transactions, and the entire financial education apparatus treats them as a saver in training instead. We teach them to hold money. Nobody teaches them what happens when they use it.
+A child becomes a consumer the first time money leaves their hand. Six years old, a birthday five, a store. From that moment they are a party to transactions, and the entire financial education apparatus treats them as a saver in training instead. We teach them to hold money. Nobody teaches them what happens when they use it, which is the only thing they were ever going to do with it.
 The scale is small and the mechanics are identical to the ones you write about. A claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the child has no way of knowing that. Not a game of skill — a slot machine wearing a carnival hat, aimed at someone with no price memory and no comparison to make.
 I wrote the picture book for it. One kid, one purchase, followed the whole way: he wants a robot, earns it, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget." The child works out he has been schooled only when he reaches the glossary — twenty-one terms in the back, each page-referenced to where it happened. It is catalogued Lexile AD 620L, where AD stands for Adult Directed — the trade's own code for a book an adult reads with a child rather than hands over.
 The story is not the book. It is that an entire publishing category taught children to save for forty years and skipped the register, which is the only place a child has ever handled money — while the arcade, the app store and the checkout lane did not skip it at all.
@@ -2352,9 +2352,9 @@
         <is>
           <t>Kim — you cover retail, so you already know the boardwalk arcade is a pricing strategy rather than a game. I wrote the children's book that explains it before a kid loses to it.
 The number I keep coming back to: a claw machine takes $25 to hand back a basketball that Walmart sells for $9.99. That is the entire business model in one glass box — charge $25 for the $9.99 thing and make it feel like winning. Once a kid has seen the $9.99, the claw loses its grip. Nobody shows them the $9.99.
-Every children's money book teaches saving. Piggy banks, jars, three little tins labeled spend-save-give where "spend" gets one page and a guilty look. But saving is the second thing a child does with money. The first is spending, and a six-year-old has done it already, standing in a store, deciding.
+Every children's money book teaches saving. Piggy banks, jars, three little tins labeled spend-save-give where "spend" gets one page and a guilty look. The genre's idea of a plot twist is a bigger jar. Meanwhile saving is the second thing a child does with money; the first is spending, and a six-year-old has done it already, standing in a store, deciding.
 So mine follows a single purchase the entire distance. A boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one deliberately, hands a coupon to the cashier, meets sales tax, and then lives with the thing. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed, so the parent reads it with the kid and gets handed the script instead of being expected to know it.
-The retail angle, if you want one: every trick your beat covers — the fake markdown, the anchor price, the "newest is better" framing — gets run on children first, in arcades and toy aisles, where there is no consumer press at all. The boardwalk airbrush stand charges $28 for a shirt that says BRAYDEN. Your kid's name is not Brayden.
+The retail angle, if you want one: every trick your beat covers — the fake markdown, the anchor price, the "newest is better" framing — gets run on children first, in arcades and toy aisles, where there is no consumer press and no one filing complaints because the mark is seven. The boardwalk airbrush stand charges $28 for a shirt that says BRAYDEN. Your kid's name is not Brayden.
 Worth a look? clarencegetsabargain.com/book-facts.html
 Jonathan</t>
         </is>
@@ -2412,7 +2412,7 @@
         <is>
           <t>Terry — you have been telling adults the truth about money for decades, usually after the damage is done. I wrote the book for about twenty years earlier than you usually get them.
 The argument in one line: mistakes at eleven cost $14, and the same mistake at twenty-seven has a credit card attached. Everything you write about compounding cuts both ways, and the habits doing the compounding were installed in a store, at six, with a parent saying no.
-Which is where the whole category gets the order wrong. Children's money books teach saving — piggy banks, jars, patience. But saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate. She has stood at a register holding money and had to decide.
+Which is where the whole category gets the order wrong. Children's money books teach saving — piggy banks, jars, patience, and a strong implication that wanting things is a character flaw. But saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate. She has stood at a register holding money and had to decide.
 Clarence Gets a Bargain follows one purchase the entire way: a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax and takes it personally, then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none announced — nobody in the book says "budget." The reader finds out he has been schooled at the glossary, twenty-one terms in the back, each page-referenced to the scene it came from.
 It reads aloud in twenty minutes. Lexile AD 620L — Adult Directed, the industry's own code for read-with rather than read-alone, so a parent who feels unqualified on money still gets handed the script.
 The column question rather than the book question: has anyone made the case that spending competence has to come first? I have not been able to find it, and you would know if it exists.
@@ -2472,7 +2472,7 @@
       <c r="K30" s="5" t="inlineStr">
         <is>
           <t>Amanda — Planet Money's whole trick is that people will sit still for an economics lesson if it is hidden inside a story about a person and a thing. I did that at a first-grade reading level, and I am writing about the story rather than the book.
-Every children's money book teaches earning or saving. All 25 on the ABA Foundation's list — I read them to be sure. A piggy bank, a lemonade stand, a lesson. Not one covers the cash register. Saving is the second thing a child does with money; spending is the first, and the register is the only place a child has ever actually handled any.
+Every children's money book teaches earning or saving. All 25 on the ABA Foundation's list — I read them to be sure. A piggy bank, a lemonade stand, a lesson. Not one covers the cash register. Forty years of piggy banks and not one of them has ever been to a store. Saving is the second thing a child does with money; spending is the first, and the register is the only place a child has ever actually handled any.
 Mine does. A boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, gets ambushed by sales tax, and then lives with what he bought. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget." They do not realise they have been schooled until they hit the glossary in the back — twenty-one terms, each page-referenced to the moment it happened. That is where the con comes apart, on purpose. It is catalogued AD 620L — Adult Directed — which is the trade's way of saying it only works out loud, with somebody interrupting.
 The numbers on the other side are absurd and nobody has ever put a microphone on them. Twelve hundred arcade tickets for a rubber slinky is an exchange rate that would embarrass a currency trader, and the kid making that trade has no idea he is trading.
 The segment is the forty-year hole. A whole publishing category taught children to save and skipped the register, while every arcade, app store and checkout lane aimed at children did not skip it at all. Nobody regulates the toy aisle and nobody covers it.
@@ -2534,7 +2534,7 @@
           <t>Bethann — you run the education side of a bankers association, which means you are the person who decides what volunteers actually carry into a classroom. I built something for the grade band most bank programs skip.
 Most financial education a bank sponsors lands in high school or in a "teach a child to save" day about saving. Saving is the second thing a child does with money. The first is spending, and a first grader has done it, at a register, with a parent behind her. There is almost nothing to hand a banker walking into a second-grade room about that.
 Clarence Gets a Bargain is a 36-page picture book following one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget."
-Why it works for a volunteer rather than a teacher: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, and the mother explains every concept inside the text. A banker can read it cold and field the questions straight off the page. No training call, nothing to memorise. The twenty-one-term glossary in the back is page-referenced to the story, so a volunteer answering a vocabulary question can turn to the scene rather than recite a definition. Free lesson plans, assessments and a browser-based pretend register sit behind it, all ungated.
+Why it works for a volunteer rather than a teacher: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, and the mother explains every concept inside the text. A banker can read it cold and field the questions straight off the page. No training call, nothing to memorise. The twenty-one-term glossary in the back is page-referenced to the story, so a volunteer answering a vocabulary question can turn to the scene rather than recite a definition. Free lesson plans, assessments and a browser-based pretend register sit behind it, all ungated. Every year the field builds another high-school course for a habit that set in first grade, and every year it works about as well as you would expect.
 The sponsorship math is simple if a member bank wants it: 25 copies is $499.75, one classroom, the bank's name on every book that goes home to a family. The educator program is free, so the sponsorship is entirely books, and I have a CRA-ready memo already written in examiner-friendly language.
 Does that fit how Utah banks choose classroom programs, or am I inventing a use case?
 clarencegetsabargain.com/educator-toolkit.html
@@ -2593,10 +2593,10 @@
       <c r="K32" s="5" t="inlineStr">
         <is>
           <t>Lynnette — you have spent a career telling people the truth about money in language they can actually use, and you built a network for people doing the same. I wrote the six-year-old version and I would like your read on whether it lands.
-Every children's money book teaches saving. Piggy banks, jars, three tins labeled spend-save-give where "spend" gets one page and a guilty look. But saving is the second thing a child does with money. The first is spending, and a first grader has already done it — in a store, holding money, deciding.
+Every children's money book teaches saving. Piggy banks, jars, three tins labeled spend-save-give where "spend" gets one page and a guilty look. Saving is the second thing a child does with money; the first is spending, and a first grader has already done it — in a store, holding money, deciding, with nobody having told her a single useful thing about it.
 And the tools have moved against them. A card is magic; a five-dollar bill is arithmetic — a kid who watches three dollars leave their hand understands something no tap-to-pay will ever teach.
 Which matters most in households where there is no margin for a bad purchase. A child taught only to save has been handed advice that assumes surplus. A child who can compare two prices and choose deliberately has a skill that works this Saturday.
-Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, meets sales tax, and then lives with what he chose. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the story. It is catalogued AD 620L — Adult Directed — so the adult reading gets handed the script and does not have to be the one who already knows about money. That was the design constraint that mattered most: it has to work in a house where nobody feels qualified to teach it.
+Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, meets sales tax, and then lives with what he chose. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the story. It is catalogued AD 620L — Adult Directed — so the adult reading gets handed the script and does not have to be the one who already knows about money. That was the design constraint that mattered most: it has to work in a house where nobody feels qualified to teach it. The piggy bank has had four hundred years and has yet to file a price comparison.
 Two questions. Does the spending-first argument hold up against what you hear from your audience? And is there a version of this worth putting in front of the Financial Influencer Network?
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -2656,7 +2656,7 @@
           <t>Ruben — CEE's standards are one of the five frameworks I crosswalked against, so I have spent real time inside them and want to ask about the bottom of the ladder.
 The elementary benchmarks exist. What is built against them is thin, and thinner still on the spending side. The field starts children with saving, and saving is the second thing a person does with money. The first is spending: standing in front of two prices and choosing one. A first grader has done that; she has no savings rate at all.
 I built a free K–5 classroom set around a 36-page picture book and crosswalked it concept by concept — 23 rows against the 2021 National Standards for Personal Financial Education, CEE, Common Core Math and ELA, and FDIC Money Smart, with the Grade 4 benchmark codes rather than a general claim of alignment. It is published so a reviewer can check it instead of taking my word.
-The book follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with the choice. Sixteen-plus concepts and nobody in it says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened. Catalogued AD 620L — Adult Directed — one class period read aloud, and because the mother explains every concept inside the text a teacher with no economics background runs it cold.
+The book follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with the choice. Sixteen-plus concepts and nobody in it says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened. Catalogued AD 620L — Adult Directed — one class period read aloud, and because the mother explains every concept inside the text a teacher with no economics background runs it cold. We are very good at teaching this to people who have already made the mistake.
 The question: is there a route for elementary material to sit alongside CEE programs, or does that run through affiliate councils? Either answer saves me guessing.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -2716,7 +2716,7 @@
           <t>Beth — you write for people trying to do the right thing with money and finding the advice arrives late. This arrives about two decades earlier than most of it.
 The premise: financial education starts children with saving, and the sequence is backwards. Saving is the second thing a person does with money. The first is spending. A seven-year-old has no savings rate and no income; what she has done is stand at a register holding money and choose. We teach that last, or never.
 I wrote the picture book for it. One purchase, followed the whole way — a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, meets sales tax, and then lives with what he chose. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; not one covers the whole arc.
-Sixteen-plus concepts, none announced — nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened, so vocabulary points a kid back into the story rather than away from it. It is catalogued AD 620L — Adult Directed — and the mother explains everything on the page, so the parent gets the script and can take the credit.
+Sixteen-plus concepts, none announced — nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened, so vocabulary points a kid back into the story rather than away from it. It is catalogued AD 620L — Adult Directed — and the mother explains everything on the page, so the parent gets the script and can take the credit. The subject is treated as serious and taught as though nobody ever spends any.
 One thing I would put to you as a planner: a card is magic, and a five-dollar bill is arithmetic. Children now grow up almost entirely inside the first one, which removes the only feedback loop they had.
 The claim I would defend hardest is the delayed one. The book is not really working in the twenty minutes it takes to read. It works in month eighteen, in a real store, when the kid hits a money moment and the book fires back — "wait, is the newer one actually better?" Recognition first, then the habit.
 Does that hold up against what you see in readers? clarencegetsabargain.com/book-facts.html
@@ -2777,7 +2777,7 @@
           <t>Julie — a segment idea, and it is short enough to survive a live hit.
 Every children's money book teaches saving. Piggy banks, lemonade stands, jars. But saving is the second thing a child does with money — the first is spending, and a six-year-old has already done it, in a store, holding a birthday five, deciding whether the thing is worth what it costs.
 The category skipped that for forty years. The arcade did not. A claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the kid has no price memory to defend himself with. Once a kid has seen the $9.99, the claw loses its grip.
-So I wrote the spending book. Clarence Gets a Bargain, ages 6–10: a boy earns a robot with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and then lives with the thing he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Twenty-one terms in a glossary at the back, each page-referenced to where it happened. Catalogued AD 620L — Adult Directed — twenty minutes out loud, interrupted the whole way.
+So I wrote the spending book. Clarence Gets a Bargain, ages 6–10: a boy earns a robot with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and then lives with the thing he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Twenty-one terms in a glossary at the back, each page-referenced to where it happened. Catalogued AD 620L — Adult Directed — twenty minutes out loud, interrupted the whole way. The category's own defence is that money is a serious subject. It is. So is getting fleeced in an aisle at the age of seven.
 I am an attorney and a mixed-media artist, and I have twice walked out of the same Nordstrom Rack having paid one cent — once for a $293 pair of shoes, once for a $69.50 shirt. I kept both tags. It makes for a good visual if you ever want one on screen.
 Is there a hit in "the money skill nobody teaches kids"? clarencegetsabargain.com/press-kit.html
 Jonathan</t>
@@ -2837,7 +2837,7 @@
           <t>Matt — you spend your working life on what happens when people meet credit without the groundwork. I wrote the book about the groundwork, roughly twenty years upstream of your data.
 The sequence is the whole argument. Financial education starts children with saving. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent behind her. Mistakes at eleven cost $14. The same mistake at twenty-seven has a credit card attached and a rate on it.
 Clarence Gets a Bargain follows one purchase the entire distance: a boy wants a robot, earns it with chores and grades, works the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; they are all parked on the earning-and-saving side of the register.
-Sixteen-plus concepts and nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened — which is the only point at which a kid works out he has been schooled. Catalogued AD 620L — Adult Directed — read with a parent, not handed to a kid alone. The single sentence I most want an eleven-year-old to own: marked down does not mean broken, it means the timing is on your side.
+Sixteen-plus concepts and nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened — which is the only point at which a kid works out he has been schooled. Catalogued AD 620L — Adult Directed — read with a parent, not handed to a kid alone. The single sentence I most want an eleven-year-old to own: marked down does not mean broken, it means the timing is on your side. The subject is treated as serious and taught as though nobody ever spends any.
 The question, since you have the data and I only have the book: does anything in what you see suggest that price competence at seven shows up at twenty-seven? If it does not, I would rather know.
 clarencegetsabargain.com/book-facts.html
 Jonathan</t>
@@ -2896,7 +2896,7 @@
         <is>
           <t>Jillian — Intuit for Education is built for high school and does that job well, so this is a question about the floor beneath it rather than a pitch into your territory.
 Everything in the field lands late. Thirty states require personal finance to graduate, all of it in high school. Money habits are largely set by seven. And the sequencing assumption nobody questions is that children should start with saving — when saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has stood at a register and chosen.
-I built the K–5 on-ramp. A 36-page picture book that follows one purchase the whole distance — wanting the robot, earning it, working the sale inserts at the kitchen table, comparing two models on a shelf, taking the marked-down one on purpose, redeeming a coupon, meeting sales tax, and living with the choice. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced back into the story.
+I built the K–5 on-ramp. A 36-page picture book that follows one purchase the whole distance — wanting the robot, earning it, working the sale inserts at the kitchen table, comparing two models on a shelf, taking the marked-down one on purpose, redeeming a coupon, meeting sales tax, and living with the choice. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced back into the story. Children can identify a worksheet through a closed backpack. That is the constraint everything else has to survive.
 The curriculum behind it is free and ungated — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart, printable classroom pieces, and a browser-based pretend register that runs a markdown, a coupon and sales tax with the total changing in front of the class. Catalogued Lexile AD 620L — Adult Directed — one class period, no teacher training.
 The honest question rather than a pitch: when teachers come to Intuit for Education, does elementary ever come up as something they want and cannot find? I am trying to work out whether I am filling a gap or inventing one, and you would see the demand signal before I would.
 clarencegetsabargain.com/educator-toolkit.html
@@ -2957,7 +2957,7 @@
           <t>Saskia — HCZ built its whole model on the idea that you intervene early and you do not wait for the system to catch up. I built the elementary financial-literacy piece on the same reasoning, and I would like your read on whether it holds.
 Every state financial-literacy requirement lands in high school. The habits being corrected there were installed at six, in a store. And the field starts children with saving, which is the second thing a child does with money — the first is spending, and it is the one your students are already doing.
 That distinction matters more, not less, for families with less room for error. A child who can compare two prices and choose deliberately has a skill that pays on a Saturday. A child taught only to save has been handed advice that requires surplus.
-Clarence Gets a Bargain is a 36-page picture book that follows one complete purchase: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget." A twenty-one-term glossary in the back, page-referenced to the story.
+Clarence Gets a Bargain is a 36-page picture book that follows one complete purchase: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget." A twenty-one-term glossary in the back, page-referenced to the story. A worksheet announces itself from three hallways away. Kids file it under school and stop reading, which is a design problem rather than a discipline one.
 Catalogued Lexile AD 620L — Adult Directed — one class period out loud, and because the mother explains every concept inside the text, a teacher needs no finance background. Everything behind it is free and ungated: lesson plans, assessments with answer keys, a standards crosswalk, printable classroom pieces, a browser-based pretend register.
 Would a read-aloud plus a pretend-store activity fit anywhere in a Promise Academy week, or is the schedule too tight for anything that is not tested?
 clarencegetsabargain.com/educator-toolkit.html
@@ -3016,7 +3016,7 @@
       <c r="K39" s="5" t="inlineStr">
         <is>
           <t>Ben — a story pitch about a gap in the coverage rather than a book pitch, though the book is how I found it.
-Thirty states now guarantee a personal finance course. Every one of those mandates lands in high school. Money habits are largely set by seven — so the policy arrives roughly ten years after the cement dries, and the funding, the training and the reporting all follow the mandate rather than the evidence.
+Thirty states now guarantee a personal finance course. Every one of those mandates lands in high school. Money habits are largely set by seven, so the policy arrives roughly ten years after the cement dries — a fifteen-year-old handed a course for a habit he formed at six, and everyone acting surprised, and the funding, the training and the reporting all follow the mandate rather than the evidence.
 Underneath that sits an assumption nobody argues with: that children should learn saving first. I think it is backwards. Saving is the second thing a person does with money. The first is spending, and a first grader has done that, at a register, with a parent standing behind her. The behaviors a high school course tries to correct were installed a decade earlier by an arcade, a toy aisle and a checkout lane, none of which waited for a curriculum.
 I wrote the elementary piece rather than an op-ed about it. A 36-page picture book following one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, and living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Free ungated classroom set behind it, crosswalked to five frameworks. Catalogued Lexile AD 620L — Adult Directed, so it is a read-with, and the caregiver conversation happens inside the reading.
 Meanwhile the arcade never waited for a standard: $25 into a glass box for a basketball Walmart sells for $9.99, and the kid has no price memory to argue with.
@@ -3140,7 +3140,7 @@
           <t>Susan — you built a center from nothing and have spent years getting economics into elementary classrooms, which makes you exactly the person to tell me whether I am filling a gap or inventing one.
 The gap as I see it: elementary standards exist in most states and almost nothing is built against them, because nobody has to report on them. Every mandate lands in high school. Thirty states now.
 And underneath that, a sequencing assumption nobody argues with — that children should learn saving first. Saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has stood at a register and chosen.
-So I wrote the K–5 piece. Clarence Gets a Bargain follows one purchase from the idea to after the receipt: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, so vocabulary review points a child back into the story instead of away from it.
+So I wrote the K–5 piece. Clarence Gets a Bargain follows one purchase from the idea to after the receipt: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, so vocabulary review points a child back into the story instead of away from it. The polite version is that the elementary band is understudied. The blunt version is that nobody has to report on it, so nobody looks.
 The teacher side is free and ungated — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE, and FDIC Money Smart. No account, no email capture, and it prints from a browser. Catalogued AD 620L — Adult Directed — a one-period read-aloud a teacher with no finance background can deliver cold.
 Does the spending-first sequence match what you see in classrooms, or is there a reason the field starts where it starts?
 clarencegetsabargain.com/educator-toolkit.html
@@ -3202,7 +3202,7 @@
 The money conversation in most families starts far too late to be a conversation. By the time a parent sits a teenager down, the habits are set — they were set at six, in a store, with a parent saying no and no explanation attached to the no.
 Every children's book on the shelf teaches saving. Piggy banks, jars, patience. But saving is the second thing a child does with money; the first is spending, and a six-year-old has already done it.
 Clarence Gets a Bargain follows one purchase the whole way — earning the reward through chores and grades, working the sale ads at the kitchen table, comparing two models on a shelf, taking the cheaper one on purpose, handing over a coupon, meeting sales tax, and then living with what was bought. Idea to post-receipt. And on page 6 there is something I have not found in any other picture book: a 529 plan. In the plot. Explained by a mom, eye-rolled at by a kid, and defended by a dad two scenes later.
-Sixteen-plus concepts and nobody says "budget." A twenty-one-term glossary in the back, page-referenced to the story. Catalogued Lexile AD 620L — Adult Directed — so it is a read-with, and the conversation happens during the reading rather than after it.
+Sixteen-plus concepts and nobody says "budget." A twenty-one-term glossary in the back, page-referenced to the story. Catalogued Lexile AD 620L — Adult Directed — so it is a read-with, and the conversation happens during the reading rather than after it. The category's own defence is that money is a serious subject. It is. So is getting fleeced in an aisle at the age of seven.
 A card is magic; a five-dollar bill is arithmetic. Children now grow up almost entirely inside the first one, which removed the only feedback loop they had.
 The angle for your beat: advisors spend fortunes trying to meet the next generation before the assets move. This is what meeting them at seven looks like, and it costs $19.99.
 Worth a column, or am I describing something you have already covered? clarencegetsabargain.com/press-kit.html
@@ -3261,7 +3261,7 @@
       <c r="K43" s="5" t="inlineStr">
         <is>
           <t>Dr. Taylor — I am a Maryland attorney and children's book author writing about the elementary end of financial literacy, which is the end nobody funds.
-Maryland's requirement, like every state's, lands in high school. The elementary standards sit underneath it with almost nothing built against them, because no one has to report on that band. Meanwhile the habits a high school course is trying to correct were installed at six, in a store, with a parent saying no and no reasoning attached.
+Maryland's requirement, like every state's, lands in high school. The elementary standards sit underneath it with almost nothing built against them, for the least respectable reason available: nobody has to report on that band. Meanwhile the habits a high school course is trying to correct were installed at six, in a store, with a parent saying no and no reasoning attached.
 The field's answer is to teach children saving first. Saving is the second thing a person does with money. The first is spending, and a first grader has done it — at a register, with a parent standing right there.
 I wrote the K–5 piece. A 36-page picture book following one purchase from the idea through the receipt: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken on purpose, a coupon at the register, sales tax, and living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced back into the story.
 What matters for a district is that all of it is free. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, and a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart. No account, no email capture, no purchase order. It prints from a browser, so adoption costs a building nothing. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud a teacher can run with no finance background.
@@ -3326,7 +3326,7 @@
           <t>Beth — a research question rather than a pitch, and the book is only the reason I ran into it.
 Financial capability gets measured, sensibly, on saving, compounding and risk. Those are the right things to measure in adults. But each of them sits downstream of a decision made years earlier that nobody scores: a child standing in front of two prices, picking one. Spending is the first financial behavior a person performs, and it is taught last or not at all.
 The environment is not waiting for the curriculum. Children are transacting constantly — arcades, app stores, checkout lanes — and none of it gets counted as financial education, though it plainly is.
-I wrote the elementary piece. A 36-page picture book following one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, and living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced back into the story. Free ungated classroom set behind it, crosswalked to five frameworks.
+I wrote the elementary piece. A 36-page picture book following one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, and living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced back into the story. Free ungated classroom set behind it, crosswalked to five frameworks. The polite version is that the elementary band is understudied. The blunt version is that nobody has to report on it, so nobody looks.
 Design note that may matter to your work: the book is catalogued Lexile AD 620L — Adult Directed. The intervention is an adult and a child reading together, not a child reading alone, which makes it closer to a shared-reading study than a curriculum study.
 The question: does the evidence base start at adolescence the way the books do? If spending competence at seven predicts nothing at twenty-seven, that is worth knowing and I would rather hear it than keep arguing.
 clarencegetsabargain.com/book-facts.html
@@ -3387,7 +3387,7 @@
         <is>
           <t>Sam — you have been reading, singing and performing a savings habit into elementary classrooms for two decades across thirty states, which is more direct contact with this audience than anyone else in the category has. So I want to put an argument in front of you and hear where it is wrong.
 Sammy teaches saving, and teaches it better than anything else aimed at this age. My argument is not about quality; it is about order. Saving is the second thing a child does with money. The first is spending — a first grader has stood at a register holding money and chosen, years before she has anything to save. Teach that moment first, and everything Sammy preaches lands harder, because a kid who understands what money buys has a reason to keep some.
-That is the book I wrote. Clarence Gets a Bargain follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the scene each term came from. Catalogued AD 620L — Adult Directed — about twenty minutes out loud, every concept explained inside the text, so somebody can read it cold to a class. You of all people will know why that mattered to me.
+That is the book I wrote. Clarence Gets a Bargain follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the scene each term came from. Catalogued AD 620L — Adult Directed — about twenty minutes out loud, every concept explained inside the text, so somebody can read it cold to a class. You of all people will know why that mattered to me. The rest of the shelf is piggy banks with plots. Good ones, some of them — but none of them has ever been to a register.
 You also solved a distribution problem the rest of us have not: banks and credit unions sponsor the visits and buy the books, and their community reports write themselves. I would rather learn that from you than reverse-engineer it.
 Trade copies and compare notes? I will read Sammy properly and tell you the truth about it, which is the only thing worth trading.
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -3449,7 +3449,7 @@
 Most financial education material aimed at children starts with saving. Saving is the second thing a child does with money. The first is spending — and a first grader has done it, at a register, with a parent behind her. An instructor standing in front of a second-grade class has almost nothing to hand them about that moment.
 Clarence Gets a Bargain is a 36-page picture book that follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one deliberately, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget."
 Why it works for an instructor rather than a teacher: it is catalogued Lexile AD 620L — Adult Directed — it runs about twenty minutes out loud, and the mother explains every concept inside the text. Somebody can read it cold to a class and field questions straight off the page. Nothing to memorise, no training call beforehand. Behind it sits a free ungated set — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, and a browser-based pretend register with a markdown, a coupon and sales tax.
-The twenty-one-term glossary in the back is page-referenced to the story, so an instructor can answer a vocabulary question by turning to the scene rather than reciting a definition.
+The twenty-one-term glossary in the back is page-referenced to the story, so an instructor can answer a vocabulary question by turning to the scene rather than reciting a definition. The field keeps building the ninth-grade course and keeps skipping the second-grade one, which is a strange place to draw a line.
 Does your instructor network want elementary material, or is the demand really all adult and teen? Everything is free either way.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -3507,9 +3507,9 @@
       <c r="K47" s="5" t="inlineStr">
         <is>
           <t>Billy — a question about where NEFE draws the line on grade band, asked by someone who has just spent a year building for the band nobody funds.
-Thirty states now require personal finance to graduate. The mandates land in high school, and the funding, the training and the reporting follow the mandate. Meanwhile the K–5 standards that already exist in most states sit there with almost nothing built against them, because nobody has to report on them.
+Thirty states now require personal finance to graduate. The mandates land in high school, and the funding, the training and the reporting follow the mandate — which is a tidy way of arriving about nine years late and calling it early intervention. Meanwhile the K–5 standards that already exist in most states sit there with almost nothing built against them, because nobody has to report on them.
 The assumption underneath is that children should learn saving first. I think it is backwards, and I would rather be told so by NEFE than keep saying it at conferences. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent standing behind her. The behaviors a high school course is trying to correct were installed a decade earlier.
-I wrote the elementary piece rather than an argument about it: a 36-page picture book that follows one purchase from the idea to after the receipt, plus a free ungated classroom set crosswalked to the 2021 National Standards, Common Core, CEE and FDIC Money Smart. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Catalogued Lexile AD 620L — Adult Directed — so the intervention is a shared read rather than solo reading, which also makes it easier to study than a curriculum.
+I wrote the elementary piece rather than an argument about it: a 36-page picture book that follows one purchase from the idea to after the receipt, plus a free ungated classroom set crosswalked to the 2021 National Standards, Common Core, CEE and FDIC Money Smart. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Catalogued Lexile AD 620L — Adult Directed — so the intervention is a shared read rather than solo reading, which also makes it easier to study than a curriculum. There is a whole industry aimed at teenagers who already have the habit, and almost nobody upstream of it.
 The line I would put on a poster if I could: mistakes at eleven cost $14, and the same mistake at twenty-seven has a credit card attached.
 The question: does NEFE's research or advocacy work have a position on the elementary band, or is the practical view that high school is where the effort pays? If it is the second, I would like to know I am arguing with a considered consensus rather than filling a gap it agrees exists.
 clarencegetsabargain.com/educator-toolkit.html
@@ -3572,7 +3572,7 @@
 Jump$tart's standards cover K–12, but the material built against them thins out badly below grade six. The elementary band has standards and very little aimed at it, largely because nothing requires anyone to report on that band. Every state mandate lands in high school. Thirty of them now.
 There is also a sequencing assumption underneath the whole field that I would like your view on. Financial education starts children with saving. Saving is the second thing a person does with money; the first is spending. A first grader has no savings rate. She has stood at a register holding money and had to choose.
 I built a free, ungated K–5 classroom set around a 36-page picture book: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE and FDIC Money Smart, printable classroom pieces, and a browser-based pretend register. No account, no email capture, no purchase order. It prints from a browser.
-The book follows one complete purchase — sale ads, comparison, a markdown, a coupon, sales tax — with sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story. Catalogued Lexile AD 620L, Adult Directed, so it runs as a one-period read-aloud with no teacher training required.
+The book follows one complete purchase — sale ads, comparison, a markdown, a coupon, sales tax — with sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story. Catalogued Lexile AD 620L, Adult Directed, so it runs as a one-period read-aloud with no teacher training required. The field keeps building the ninth-grade course and keeps skipping the second-grade one, which is a strange place to draw a line.
 One line from the book does the work of a standards document, and it is the one I would defend hardest: marked down does not mean broken, it means the timing is on your side.
 Two questions. Does Jump$tart consider elementary in scope, or is it a band the coalition has consciously left to others? And for the Clearinghouse, is the free classroom set the right thing to submit rather than the book?
 clarencegetsabargain.com/educator-toolkit.html
@@ -3633,7 +3633,7 @@
           <t>Prince — you took investing, which is the hardest concept in this category to make readable for children, and made it a series a kid comes back to. I went the opposite direction on the same shelf and I would like your read on it.
 Wesley learns to invest. Clarence learns to spend — and I mean the mechanics of it rather than the idea. Every other book in the category teaches saving, which is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. Nobody had written that one, so I did.
 Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Nobody says the word "budget."
-The craft problem I would most like another author's view on: the reader is not supposed to know he has been taught anything until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. Getting that balance right, so it stays a story, was the whole job, and it is the thing most likely to be off by a hair.
+The craft problem I would most like another author's view on: the reader is not supposed to know he has been taught anything until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. Getting that balance right, so it stays a story, was the whole job, and it is the thing most likely to be off by a hair. The rest of the shelf is piggy banks with plots. Good ones, some of them — but none of them has ever been to a register.
 I did the illustrations too, which means my opinion of them is worth nothing. It is written for the adult voice in the room — catalogued AD 620L, Adult Directed — with the mother carrying every explanation.
 Trade? Send me a Wesley and I will read it properly rather than politely.
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -3692,7 +3692,7 @@
       <c r="K50" s="5" t="inlineStr">
         <is>
           <t>Kate — a pitch about a gap rather than a book, though I wrote the book because of the gap.
-Everything in kids' financial literacy points at a horizon no child can see: compound interest, credit scores, retirement. All real, all decades out. Meanwhile the kid is eight, holding $20 of birthday money, standing in a store that spent millions working out how to get it. We are preparing children for 65 and sending them to the register unarmed today.
+Everything in kids' financial literacy points at a horizon no child can see: compound interest, credit scores, retirement. All real, all decades out, and all completely useless to somebody who is eight. Meanwhile the kid is eight, holding $20 of birthday money, standing in a store that spent millions working out how to get it. We are preparing children for 65 and sending them to the register unarmed today.
 So flip the order. Saving is the second thing a child does with money. The first is spending, and it is the one nobody puts in a story.
 Clarence Gets a Bargain does. One kid, one purchase, followed the whole distance — he wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget." The reader works out he has been schooled at the glossary — twenty-one terms in the back, each one page-referenced to the scene it came from. Catalogued AD 620L — Adult Directed — so a parent who does not feel qualified on money still gets handed the script and can take the credit.
 The boardwalk is a pop quiz your kid has not studied for, and it runs all summer with real money.
@@ -9674,7 +9674,7 @@
           <t>Professor Urban — you produced the evidence base that mandates actually work, which is why I want to ask about the grade band your evidence does not reach.
 Every mandate you have evaluated lands in high school. Thirty states now. The effects are real and I am not arguing with them. My question is about what is happening a decade earlier, because money habits are largely set by seven and the policy arrives roughly ten years after the cement dries.
 Underneath the whole field sits a sequencing assumption nobody tests: that children should learn saving first. I think it is backwards. Saving is the second thing a person does with money. The first is spending — standing in front of two prices and picking one. A first grader has done that. She has no savings rate at all.
-I could not find the children's book for it, so I wrote one. Clarence Gets a Bargain follows a single purchase the entire way: earning the reward, reading the sale ads, comparing two models on a shelf, choosing the cheaper one deliberately, redeeming a coupon, meeting sales tax, and then living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story.
+I could not find the children's book for it, so I wrote one. Clarence Gets a Bargain follows a single purchase the entire way: earning the reward, reading the sale ads, comparing two models on a shelf, choosing the cheaper one deliberately, redeeming a coupon, meeting sales tax, and then living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Elementary is not so much contested ground as unvisited ground.
 One design feature that may matter for measurement: the book is catalogued Lexile AD 620L — Adult Directed — so the intervention is not a child reading alone but an adult and a child reading together, with the adult prompted by the text. If shared reading is doing the work rather than the book, that is testable, and it would be a more interesting finding than anything about my book.
 The real question: does anything in the literature speak to elementary spending competence, or is that band simply unstudied? Either answer is useful to me.
 clarencegetsabargain.com/book-facts.html
@@ -9736,7 +9736,7 @@
           <t>Iris — you were part of the group that chose the titles on the Money as You Grow Bookshelf, so you have read this category more carefully than almost anyone, and you will know immediately whether my premise is wrong.
 The shelf, as it stands, leans toward saving and earning. Spending is thin, and the transaction itself is thinner — the part where a child stands in front of two prices and picks one. Saving is the second thing a person does with money; spending is the first, and it gets taught last or not at all.
 Clarence Gets a Bargain covers exactly that, and covers the whole of it: a boy wants a robot, earns it through chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list looking for another one that does the whole arc. They are all parked on the earning-and-saving side of the register.
-Sixteen-plus concepts and none is announced — no character pauses to define a term, nobody says the word "budget." The proof and the reveal are both in the back matter: a reader does not know he has been schooled until he reaches the glossary. Twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than an appendix.
+Sixteen-plus concepts and none is announced — no character pauses to define a term, nobody says the word "budget." The proof and the reveal are both in the back matter: a reader does not know he has been schooled until he reaches the glossary. Twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than an appendix. Elementary is not so much contested ground as unvisited ground.
 Ages 6–10, inside the Bookshelf's 4–10 band. Catalogued Lexile AD 620L — Adult Directed, which is how the Bookshelf's titles are meant to be used anyway.
 Two questions. Was the saving weighting deliberate, or just what existed? And is the selection process still running?
 clarencegetsabargain.com/book-facts.html
@@ -9805,7 +9805,7 @@
 Professor Mahoney — your work is about what consumers actually do when a price is put in front of them, as opposed to what a model says they should. I want to ask about the earliest version of that decision, because nobody seems to study it.
 A six-year-old with a birthday five in an aisle is running a comparison with no price history, no reference class and no idea that anchoring exists. She is the purest case your field could ask for and the least documented. Meanwhile the environment is not naive at all — a boardwalk claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the child has no way of knowing the $9.99 exists.
 Financial education answers this by teaching saving. But saving is the second thing a person does with money; the first is spending, and it is taught last or not at all.
-I wrote the picture book rather than the paper. Clarence Gets a Bargain follows one complete purchase — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with the choice afterward. Sixteen-plus concepts, none announced. Twenty-one terms in a back-matter glossary, each page-referenced to the scene it came from. Catalogued Lexile AD 620L — Adult Directed — so the reading is a joint activity by design rather than a solo one.
+I wrote the picture book rather than the paper. Clarence Gets a Bargain follows one complete purchase — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with the choice afterward. Sixteen-plus concepts, none announced. Twenty-one terms in a back-matter glossary, each page-referenced to the scene it came from. Catalogued Lexile AD 620L — Adult Directed — so the reading is a joint activity by design rather than a solo one. The band is not understudied because it is uninteresting. It is understudied because nothing forces anyone to count it.
 For what it is worth, the field's own blind spot has a price tag on it: a boardwalk claw machine takes $25 to hand back a basketball Walmart sells for $9.99, and no curriculum anywhere treats that as a financial event.
 The question I would actually like answered: is there work on when price competence forms, and whether early exposure to comparison changes anything measurable later? If the honest answer is that it is unstudied because it is unmeasurable at that age, that is worth knowing too.
 clarencegetsabargain.com/book-facts.html
@@ -17311,7 +17311,7 @@
         <is>
           <t>Jennifer — a funding-shaped question rather than an ask, and the resource itself is already free.
 I wrote and illustrated a K–5 financial-literacy picture book and built the entire classroom program behind it — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a standards crosswalk across five frameworks. All of it is ungated: no account, no email capture, no purchase order, prints from a browser. The only thing that ever costs anything is the physical books, and 25 copies run $499.75.
-The content premise: every children's money book teaches saving, and saving is the second thing a child does with money. The first is spending — a first grader has stood at a register and chosen. The book follows one complete purchase from the idea through the receipt, with sixteen-plus concepts hidden in the plot and a twenty-one-term glossary page-referenced back into the story.
+The content premise: every children's money book teaches saving, and saving is the second thing a child does with money. The first is spending — a first grader has stood at a register and chosen. The book follows one complete purchase from the idea through the receipt, with sixteen-plus concepts hidden in the plot and a twenty-one-term glossary page-referenced back into the story. If a money lesson looks like school, it gets filed under school and read at school speed.
 Why I am writing to development rather than to a classroom: this is unusually easy to fund. A bank or credit union sponsoring a classroom set gets its name on every book that goes home to a family in its assessment area, the curriculum costs the sponsor nothing because it is already free, and I have a CRA-ready memo written in examiner-friendly language. A funder can point at 25 books, one classroom, and a pre/post instrument. And because it is catalogued AD 620L — Adult Directed — it doubles as family engagement: the same book works at a kitchen table with a parent or a grandparent reading.
 Is a sponsored classroom set something HCZ's funders would recognise, or does everything need to attach to an existing program line?
 clarencegetsabargain.com/resources/grant-in-a-box.html
@@ -17371,7 +17371,7 @@
         <is>
           <t>Flora — JA runs volunteers into elementary classrooms better than any organisation in the country, so this is a materials question rather than a pitch.
 JA's elementary programs are strong on earning, jobs and community. What is thin across the whole field, JA included, is spending — the second thing everybody teaches and the first thing a child actually does. A first grader has no savings rate and no job. What she has done is stand at a register holding money and choose.
-Clarence Gets a Bargain is a 36-page picture book that puts the entire transaction on the page: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
+Clarence Gets a Bargain is a 36-page picture book that puts the entire transaction on the page: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from. Every year the field builds another high-school course for a habit that set in first grade, and every year it works about as well as you would expect.
 The part that matters for a volunteer model: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, with every concept explained inside the text by the mother. A volunteer who has never taught anything can read it cold and answer questions off the page. Nothing to memorise and no prep call. Behind it, free and ungated: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable price tags and clearance stickers for a classroom store, and a browser-based pretend register with a markdown, a coupon and sales tax.
 Alaska has its own complications on distance and travel, and virtual read-alouds work for this.
 Does a read-aloud fit how JA Alaska builds a volunteer session, or does everything have to run through national curriculum?
@@ -17495,7 +17495,7 @@
           <t>Gene — Troutwood is built on showing people the long arc of a decision, which is why I am writing about the very first decision on that arc.
 Everything in financial planning compounds, including the mistakes, and the compounding starts long before anyone opens an account. Mistakes at eleven cost $14. The same mistake at twenty-seven has a credit card attached. The habit doing the compounding was installed at six, in a store, with a parent saying no and no reasoning attached to the no.
 Financial education answers that by teaching children saving. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with no framework at all.
-Clarence Gets a Bargain is the picture book for that. One purchase, followed the whole way: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed — so it is a shared read and the parent gets the script rather than a homework assignment.
+Clarence Gets a Bargain is the picture book for that. One purchase, followed the whole way: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed — so it is a shared read and the parent gets the script rather than a homework assignment. A jar is a storage container. It has never once talked a kid out of anything.
 The claim I would defend hardest is the delayed one, and it is the same claim Troutwood makes about projections: the value is not in the twenty minutes. It is in month eighteen, in a real store, when the kid hits a money moment and the book fires back. Recognition first, then the habit.
 Does the elementary end fit anything Troutwood does, or is that below the floor?
 clarencegetsabargain.com/book-facts.html
@@ -17555,7 +17555,7 @@
         <is>
           <t>Rob — you build resources teachers actually use, which is a harder job than writing curriculum and a rarer one. I built the elementary thing that does not exist, and I want a practitioner's read on whether it survives a real classroom.
 The gap: every mandate lands in high school, so that is where every resource goes. The elementary standards exist and almost nothing is built against them. And the field starts children with saving, when saving is the second thing a person does with money — the first is spending, and a first grader has already done it at a register.
-Clarence Gets a Bargain is a 36-page picture book following one complete purchase: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken on purpose, a coupon at the register, sales tax, and living with what was bought. Sixteen-plus concepts, none announced. Kids smell a worksheet one page in; they never smell this one. A twenty-one-term glossary in the back, page-referenced to the story.
+Clarence Gets a Bargain is a 36-page picture book following one complete purchase: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken on purpose, a coupon at the register, sales tax, and living with what was bought. Sixteen-plus concepts, none announced. Kids smell a worksheet one page in; they never smell this one. A twenty-one-term glossary in the back, page-referenced to the story. Nobody has ever formed a money habit by looking at a jar.
 The teacher side is where I would want your opinion. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row standards crosswalk, printable price tags and clearance stickers for a classroom store, and a browser-based register that runs a markdown, a coupon and sales tax with the total changing in front of the class. Ungated — no account, no email capture — and it prints from a browser. Catalogued Lexile AD 620L, Adult Directed: one class period, no teacher training, and the text carries every explanation.
 The whole thing rests on one instruction a teacher can act on the same week: stop bringing kids to the store as cargo, bring them as staff. Every activity in the set is a version of that.
 The honest question: what makes a free teacher resource actually get used rather than downloaded and forgotten? You have watched that happen more times than I have, and I would rather fix it now.
@@ -21987,7 +21987,7 @@
           <t>Martin — you sit where the profession decides what it is responsible for, so this is a question about the far upstream end of that responsibility.
 Planners meet clients' children late, usually at the worst possible moment, and by then the habits are twenty years old. They were formed at six, in a store, with a parent saying no and no reasoning attached to the no.
 The field's answer to that is to teach children saving. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, holding a birthday five, deciding whether the thing is worth what it costs.
-I wrote the picture book for that moment. Clarence Gets a Bargain follows one purchase the whole way — earning the reward through chores and grades, working the sale ads at the kitchen table, comparing two models on a shelf, taking the cheaper one on purpose, redeeming a coupon, meeting sales tax, and then living with what was bought. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in a back-matter glossary, page-referenced to the story.
+I wrote the picture book for that moment. Clarence Gets a Bargain follows one purchase the whole way — earning the reward through chores and grades, working the sale ads at the kitchen table, comparing two models on a shelf, taking the cheaper one on purpose, redeeming a coupon, meeting sales tax, and then living with what was bought. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in a back-matter glossary, page-referenced to the story. A course at fifteen for a habit set at six is not early intervention; it is a receipt.
 And on page 6 there is something I have not found in any other picture book: a 529 plan. In the plot. Explained by a mother, eye-rolled at by a kid, defended by a father two scenes later. It is catalogued AD 620L — Adult Directed — so a planner handing it to a client family is handing over a script rather than an assignment. Twenty-five copies run $499.75, and the educator program behind it is free.
 The question: does CFP Board's pro bono and public-education work reach below high school at all, or is that considered somebody else's ground?
 clarencegetsabargain.com/book-facts.html
@@ -22170,7 +22170,7 @@
         <is>
           <t>Annie — you built a product for the exact age band everyone else in this category skips, so you already believe the thing I have been arguing. I want to compare notes rather than pitch you.
 My First Nest Egg puts save, spend, give and invest in front of a young child in physical form. My argument is about which of those a child actually performs first. It is spending — a six-year-old has stood in a store holding money and chosen, years before she has anything to save or invest. The category teaches saving first anyway, and I could not find the book that teaches the other one.
-So I wrote and illustrated it. Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed — read with a grown-up rather than handed over. There is also a free browser-based pretend register behind it that runs a markdown, a coupon and sales tax, which is the closest thing I have to your physical product.
+So I wrote and illustrated it. Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed — read with a grown-up rather than handed over. There is also a free browser-based pretend register behind it that runs a markdown, a coupon and sales tax, which is the closest thing I have to your physical product. Nobody has ever formed a money habit by looking at a jar.
 Those look complementary rather than competing to me: yours gives a kid the categories in their hands, mine walks them through the mechanics of one transaction in twenty minutes.
 Worth a conversation about whether they belong near each other? And separately — if you think spending-before-saving is wrong, you are one of very few people whose disagreement would actually change my mind.
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -28298,17 +28298,17 @@
         </is>
       </c>
       <c r="I666" s="5" t="n">
-        <v>3349</v>
+        <v>3450</v>
       </c>
       <c r="J666" s="5" t="inlineStr">
         <is>
           <t>Christine,
 You're closing September, Grandparents Day is the 13th, and every other pitch on your desk this week is a gift guide. Mine is an afternoon.
 I'm an attorney, a mixed-media artist, and a dad, and I wrote and illustrated a children's picture book called Clarence Gets a Bargain. Ages 6–10. A boy earns a robot with chores and grades, then has to figure out how to buy it — sale ads at the kitchen table, two models compared on a shelf, the cheaper one taken on purpose, a coupon handed to the cashier, and sales tax showing up uninvited at the end. Sixteen-plus money concepts are in there and not one of them is announced; nobody in the book ever says the word "budget." A kid doesn't work out he's been taught anything until he reaches the glossary at the back — twenty-one terms, each one pointing back to the page where it happened.
-Your readers own the next part. Every children's money book teaches saving. Piggy banks, jars, three little tins labeled spend-save-give where "spend" gets one page and a guilty look. But saving is the second thing a child does with money; the first is spending, and a six-year-old has already done it, in a store, holding a birthday five, deciding whether the thing is worth what it costs. We teach the second thing first and the first thing never.
+Your readers own the next part. Every children's money book teaches saving. Piggy banks, jars, three little tins labeled spend-save-give where "spend" gets one page and a guilty look, as though wanting something were a character defect. But saving is the second thing a child does with money; the first is spending, and a six-year-old has already done it, in a store, holding a birthday five, deciding whether the thing is worth what it costs. We teach the second thing first and the first thing never.
 Your readers clipped coupons back when it was a survival skill rather than a hobby. They remember layaway. They know what their first paycheck was and exactly what it wouldn't cover. That is better money curriculum than anything a school hands out, and it has nowhere to land, because nobody asks. A book that puts a kid in a store gives it somewhere to land: every page has a "that reminds me of the time" already sitting in it, waiting for somebody to say it out loud.
 The book is catalogued Lexile AD 620L, and the AD means Adult Directed — the industry's own code for a book meant to be read WITH a child rather than handed to one. It needs a grown-up in the room. You're cast. Mom explains everything inside the story, so the grandparent reading aloud gets handed the script and can take the credit for knowing it. Twenty minutes out loud, interrupted the whole way, and the interruptions are the point: "Do we have a 529?" "Why do you take pictures of receipts?" "Can I hand the cashier the coupon next time?"
-And two of the games in it can't be played alone. Page 27: whoever spots the biggest savings at the grocery store wins, loser carries the bags in from the car. Page 28: after dinner somebody shares a deal they got that day and everyone guesses the price. Kids' guesses are unhinged. A gallon of milk goes for $45; a car for $100. The reveal face is the whole entertainment. Three players minimum. Grandma counts.
+And two of the games in it can't be played alone. Page 27: whoever spots the biggest savings at the grocery store wins, loser carries the bags in from the car. Page 28: after dinner somebody shares a deal they got that day and everyone guesses the price. Kids' guesses are unhinged. A gallon of milk goes for $45; a car for $100; a Nintendo Switch, apparently, for six dollars. The reveal face is the whole entertainment. Three players minimum. Grandma counts.
 The piece I want to write for you is 800 to 1,200 words: "What Grandparents Can Teach About Money That Nobody Else Can," with the two games as a tear-out sidebar. If you'd rather have a product review instead, I'll take that too; the book is $19.99, 36 pages, hardbound. But the article is the better use of your page, and I'd rather argue for it than hedge.
 Copy goes in the mail today either way. Say the word on the piece and you'll have a draft this week.
 Jonathan Bach
@@ -28360,13 +28360,13 @@
       </c>
       <c r="H667" s="5" t="inlineStr"/>
       <c r="I667" s="5" t="n">
-        <v>2975</v>
+        <v>3034</v>
       </c>
       <c r="J667" s="5" t="inlineStr">
         <is>
           <t>DeeDee,
 You started More Than Grand in 2019 because you couldn't find the grandparent resource you wanted, so you built it. I did the same thing on a different shelf, which is the only reason I'm comfortable writing to you cold.
-I went looking for the children's book that teaches a kid how to spend money — not save it, spend it — and there wasn't one. Every book in that category is about a piggy bank or a lemonade stand. All of them teach saving, which is the second thing a child does with money. The first is spending, and a six-year-old has already done it, standing in a store holding a birthday five, working out whether the thing is worth what it costs. So I wrote and illustrated it: Clarence Gets a Bargain, ages 6–10, one kid following one purchase the whole way, from wanting the robot to living with the one he chose. Sixteen-plus concepts, none of them announced — nobody says "budget" — and a twenty-one-term glossary in the back where every entry points to the page it came from. The kid doesn't know he's been schooled until he gets there.
+I went looking for the children's book that teaches a kid how to spend money — not save it, spend it — and there wasn't one. Every book in that category is about a piggy bank or a lemonade stand. Forty years of them, and not one has ever been to a store. All of them teach saving, which is the second thing a child does with money. The first is spending, and a six-year-old has already done it, standing in a store holding a birthday five, working out whether the thing is worth what it costs. So I wrote and illustrated it: Clarence Gets a Bargain, ages 6–10, one kid following one purchase the whole way, from wanting the robot to living with the one he chose. Sixteen-plus concepts, none of them announced — nobody says "budget" — and a twenty-one-term glossary in the back where every entry points to the page it came from. The kid doesn't know he's been schooled until he gets there.
 I'm writing to you rather than to a gift guide, and here's the difference. Your whole editorial line is that a good grandparent supports the parents instead of running past them. This book does that structurally. Mom is the one who teaches Clarence in the story — the sale ads, the markdown, the coupon, the sales tax. A grandparent reading it aloud is reading the parent's lines, not competing with them.
 The format backs that up. It's catalogued Lexile AD 620L, and AD stands for Adult Directed — the trade's own code for a book meant to be read WITH a child rather than handed over. It doesn't work in the corner. It works on a couch, with somebody's grandkid interrupting every third page. And because Mom explains every concept inside the text, the grandparent doesn't have to be confident about money to run it. The script is on the page. Take the credit.
 Two of the games in the back half need other people, which I did on purpose. Page 27: everyone hunts for the biggest savings on the next grocery run, loser carries the bags in from the car. Page 28: after dinner someone shares a deal they got that day and everybody guesses the price. Three players minimum. Grandma counts.
@@ -28551,12 +28551,12 @@
       <c r="G670" s="5" t="inlineStr"/>
       <c r="H670" s="5" t="inlineStr"/>
       <c r="I670" s="5" t="n">
-        <v>1450</v>
+        <v>1509</v>
       </c>
       <c r="J670" s="5" t="inlineStr">
         <is>
           <t>Greg — a grandfather-adjacent pitch, though I'm a dad rather than a grandpa yet, so tell me if that disqualifies me and I'll take it well.
-I wrote and illustrated a kids' picture book about the money skill nobody teaches: spending — one kid, one purchase, followed the whole way from the sale ads at the kitchen table to the sales tax on the receipt. Every children's money book is about a piggy bank. But saving is the second thing a kid does with money — the first is spending, usually on a Saturday, at a register, with a grown-up standing right there sweating the total.
+I wrote and illustrated a kids' picture book about the money skill nobody teaches: spending — one kid, one purchase, followed the whole way from the sale ads at the kitchen table to the sales tax on the receipt. Every other book in the aisle is a piggy bank with a plot. Every children's money book is about a piggy bank. But saving is the second thing a kid does with money — the first is spending, usually on a Saturday, at a register, with a grown-up standing right there sweating the total.
 Sixteen-plus money concepts are hidden in it and none are announced — the glossary in the back is the only place the book admits what it was doing, and it's the last thing a kid reads.
 The reason I think it's a grandpa episode: the book is built to be read out loud with a kid, not handed to one. It's catalogued Lexile AD 620L — Adult Directed, the industry's own code for read-WITH. And the grandparents are the last people alive who remember layaway and clipping coupons as a survival skill. Every page has a "that reminds me of the time" sitting in it.
 Two of the games in it need more than one player on purpose. One is a grocery-store savings hunt where the loser carries the bags in from the car.
@@ -29908,7 +29908,7 @@
           <t>Bill — a question about grade band from someone who has read what states actually fund.
 Tennessee's requirement, like all thirty of them, lands in high school. That is where the money, the training and the reporting go. The elementary standards sit underneath it with almost nothing built against them, because nothing requires a district to report on that band.
 The sequencing assumption is the part I keep circling. Financial education starts children with saving. Saving is the second thing a person does with money; the first is spending, and a first grader has done it — at a register, with a parent standing right there. The behaviors a high school course tries to correct were installed a decade earlier.
-So I built the K–5 piece. A 36-page picture book that follows one purchase from the idea to after the receipt — sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken on purpose, a coupon at the register, sales tax, and living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story.
+So I built the K–5 piece. A 36-page picture book that follows one purchase from the idea to after the receipt — sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken on purpose, a coupon at the register, sales tax, and living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. There is a whole industry aimed at teenagers who already have the habit, and almost nobody upstream of it.
 What matters for a commission is the rest of it, and it is free: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart. Ungated, no account, prints from a browser. A district adopting it spends nothing. Catalogued Lexile AD 620L — Adult Directed — so it is a one-period read-aloud that needs no teacher training.
 Does elementary sit inside what the Commission convenes or funds, or is high school the whole remit?
 clarencegetsabargain.com/educator-toolkit.html
@@ -29968,7 +29968,7 @@
         <is>
           <t>Dave — Wisconsin has run a state financial-literacy office longer than most states have had a requirement, so you have seen more of these come and go than almost anyone. I would like a read on one assumption.
 Every mandate in the country lands in high school. Thirty of them now. Money habits are largely set by seven, which puts the policy about a decade behind the behaviour. Underneath that sits the belief that children should learn saving first. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent right there.
-I built the K–5 piece rather than an argument about it. A 36-page picture book that follows one complete purchase: the sale ads at the kitchen table, comparison on a shelf, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced — nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
+I built the K–5 piece rather than an argument about it. A 36-page picture book that follows one complete purchase: the sale ads at the kitchen table, comparison on a shelf, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced — nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from. We are very good at teaching this to people who have already made the mistake.
 The classroom set behind it is free and ungated: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, and a 23-row crosswalk to the 2021 National Standards, Common Core Math and ELA, CEE and FDIC Money Smart. No account, no email capture, prints from a browser. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud that a teacher without a finance background can run cold, and the same book works at a kitchen table.
 The question: in your experience, does elementary material get adopted when it is free and aligned, or does it need a mandate behind it to move at all? I would rather know now than find out slowly.
 clarencegetsabargain.com/educator-toolkit.html
@@ -30089,7 +30089,7 @@
         <is>
           <t>Tom — you got more genuine engagement out of one post about kids and money than anyone else in this category has managed, which tells me you know exactly which part of this parents actually care about. I would like to check my premise against that.
 My premise: the whole field has the sequence backwards. Financial education starts children with saving. Saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, standing in a store holding a birthday five, working out whether the thing is worth what it costs. We teach the second thing first and the first thing never.
-So I wrote and illustrated the spending book. Clarence Gets a Bargain follows one purchase the whole way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax and objects to it, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." The reader works out he has been schooled only at the glossary — twenty-one terms in the back, page-referenced to the scene each came from.
+So I wrote and illustrated the spending book. Clarence Gets a Bargain follows one purchase the whole way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax and objects to it, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." The reader works out he has been schooled only at the glossary — twenty-one terms in the back, page-referenced to the scene each came from. A jar is a storage container. It has never once talked a kid out of anything.
 The instruction underneath the whole book is four words long: stop bringing kids to the store as cargo, bring them as staff. Catalogued Lexile AD 620L — Adult Directed — so the parent gets handed the script rather than an assignment, which I suspect is why your posts land: parents want the conversation and do not feel qualified to start it.
 The thing I would actually value: you know what makes a parent stop scrolling on this subject and what makes them scroll past. If "spending before saving" is the wrong hook, I would rather hear it from you than keep testing it slowly.
 Would you look and tell me? https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -30148,10 +30148,10 @@
       <c r="K24" s="5" t="inlineStr">
         <is>
           <t>Andrew — your audience is adults fixing money habits. I wrote the book that tries to stop the habits forming, and there is an episode in the argument whether or not the book is in it.
-Every children's money book teaches saving. Piggy banks, lemonade stands, three jars. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding a birthday five, working out whether the thing is worth what it costs.
+Every children's money book teaches saving. Piggy banks, lemonade stands, three jars. A piggy bank, a lemonade stand, a lesson — that is the whole category, and it has never once been to a register. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding a birthday five, working out whether the thing is worth what it costs.
 Nobody put that in a story. So I did. Clarence Gets a Bargain follows a single purchase the whole way — a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax and regards it as a personal insult, then lives with the thing he chose. Idea to post-receipt.
 Sixteen-plus concepts and none of them announced. Nobody in the book says "budget," which for a book largely about budgeting took some doing. Kids smell a worksheet one page in; they never smell this one, because they are laughing too hard to notice. The reveal is the glossary — twenty-one terms in the back, page-referenced to the scene each came from. It is catalogued AD 620L, Adult Directed, so the parent listening to your show gets handed the script rather than a homework assignment.
-Their books are about earning and saving, which is fine, but there is no game in a piggy bank and kids know it.
+Their books are about earning and saving, which is fine, but there is no game in a piggy bank and kids work that out faster than we do. They smell a worksheet through a backpack.
 The episode I would pitch is not the book. It is the forty-year hole: an entire publishing category taught children to save and skipped the cash register, the only place a child has ever actually handled money.
 Worth twenty minutes of your show? https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -30209,7 +30209,7 @@
       <c r="K25" s="5" t="inlineStr">
         <is>
           <t>Amy — two requests come to your desk all week. A kid wants a robot book. A parent wants something that teaches money. I wrote the one that answers both in a single checkout.
-Clarence Gets a Bargain is a 36-page picture book, ages 6–10, that follows one kid through one complete purchase: he earns a robot reward with chores and grades, does his shopping homework in the newspaper sale ads, comparison-shops the aisle, finds the markdown, hands a coupon to the cashier, meets sales tax, and watches his mother photograph the receipt before the car leaves the lot. Kids read it as a robot story. Saving is the second thing a child does with money; the first is spending, and this is the book for that. Sixteen-plus money concepts come along without announcing themselves, and the back matter carries a twenty-one-term glossary where each definition points to the page where the term happens in the plot — a decoder rather than an appendix.
+Clarence Gets a Bargain is a 36-page picture book, ages 6–10, that follows one kid through one complete purchase: he earns a robot reward with chores and grades, does his shopping homework in the newspaper sale ads, comparison-shops the aisle, finds the markdown, hands a coupon to the cashier, meets sales tax, and watches his mother photograph the receipt before the car leaves the lot. Kids read it as a robot story. Saving is the second thing a child does with money; the first is spending, and this is the book for that. Sixteen-plus money concepts come along without announcing themselves, and the back matter carries a twenty-one-term glossary where each definition points to the page where the term happens in the plot — a decoder rather than an appendix. A worksheet announces itself from three hallways away. Kids file it under school and stop reading, which is a design problem rather than a discipline one.
 The collection case, with the qualifier a librarian will appreciate: most money picture books cover earning or saving. To my knowledge this is the first narrative picture book for this age band that traces the whole consumer arc, wish through receipt. It fills a hole rather than adding a fourth piggy-bank book to the shelf.
 Cataloguing: ISBN 979-8-234-07638-0 · LCCN 2026906164 · hardbound, case bound, full colour, 11×8.5′′ · Est. Lexile AD 620L, Guided Reading L–N · $19.99. The AD is Adult Directed, which makes it a storytime title and a family take-home at the same time. Every fact is on one page: clarencegetsabargain.com/book-facts.html
 Programming is already built and free — printable price tags and clearance stickers for a pretend store, a browser-based register kids run themselves, a five-question quiz with a printable certificate. A storytime plus the pretend store is a complete Money Smart Week event with no prep budget.
@@ -30270,7 +30270,7 @@
         <is>
           <t>Sarah — a collection-development pitch, kept to the facts because I know what August looks like at your desk.
 Clarence Gets a Bargain is a 36-page picture book, ages 6–10, following one kid through one complete purchase: earning the robot reward, doing shopping homework in the newspaper sale ads, comparison shopping the aisle, finding the markdown, handing a coupon to the cashier, paying the sales tax, and watching his mother photograph the receipt before the car leaves the parking lot. Sixteen-plus money concepts ride inside the plot. Nobody in the book says the word "budget."
-The case for the shelf: nearly every money picture book teaches earning or saving, which is the second thing a child does with money. Spending is the first. To my knowledge this is the first narrative picture book for this band that follows the whole consumer arc, wish through receipt. The back matter carries a twenty-one-term glossary in which every definition cites the page where the term happens in the story, so a child looking something up lands in a scene rather than a definition list.
+The case for the shelf: nearly every money picture book teaches earning or saving, which is the second thing a child does with money. Spending is the first. To my knowledge this is the first narrative picture book for this band that follows the whole consumer arc, wish through receipt. The back matter carries a twenty-one-term glossary in which every definition cites the page where the term happens in the story, so a child looking something up lands in a scene rather than a definition list. If a money lesson looks like school, it gets filed under school and read at school speed.
 Cataloguing: ISBN 979-8-234-07638-0 · LCCN 2026906164 · hardbound, case bound, full colour, 11×8.5′′ · Est. Lexile AD 620L, Guided Reading L–N · $19.99. Full record at clarencegetsabargain.com/book-facts.html. The AD in that Lexile stands for Adult Directed, so it does double duty as a read-aloud title and a take-home.
 Programming, already built and free: printable price tags and clearance stickers for a pretend store, a browser-based Sea-Mart register children operate themselves with a markdown, a coupon and sales tax, and a quiz with a printable certificate. No prep budget required for a Financial Literacy Month or Money Smart Week event.
 Endorsed by a K–5 educator with 30+ years in the classroom and by the 2026 EIFLE Educator of the Year.
@@ -30330,7 +30330,7 @@
       <c r="K27" s="5" t="inlineStr">
         <is>
           <t>Gretchen — you have spent a career on how financial products get sold to people who don't fully understand them. Here is the entry-level version of that, and nobody covers it.
-A child becomes a consumer the first time money leaves their hand. Six years old, a birthday five, a store. From that moment they are a party to transactions, and the entire financial education apparatus treats them as a saver in training instead. We teach them to hold money. Nobody teaches them what happens when they use it.
+A child becomes a consumer the first time money leaves their hand. Six years old, a birthday five, a store. From that moment they are a party to transactions, and the entire financial education apparatus treats them as a saver in training instead. We teach them to hold money. Nobody teaches them what happens when they use it, which is the only thing they were ever going to do with it.
 The scale is small and the mechanics are identical to the ones you write about. A claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the child has no way of knowing that. Not a game of skill — a slot machine wearing a carnival hat, aimed at someone with no price memory and no comparison to make.
 I wrote the picture book for it. One kid, one purchase, followed the whole way: he wants a robot, earns it, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget." The child works out he has been schooled only when he reaches the glossary — twenty-one terms in the back, each page-referenced to where it happened. It is catalogued Lexile AD 620L, where AD stands for Adult Directed — the trade's own code for a book an adult reads with a child rather than hands over.
 The story is not the book. It is that an entire publishing category taught children to save for forty years and skipped the register, which is the only place a child has ever handled money — while the arcade, the app store and the checkout lane did not skip it at all.
@@ -30391,9 +30391,9 @@
         <is>
           <t>Kim — you cover retail, so you already know the boardwalk arcade is a pricing strategy rather than a game. I wrote the children's book that explains it before a kid loses to it.
 The number I keep coming back to: a claw machine takes $25 to hand back a basketball that Walmart sells for $9.99. That is the entire business model in one glass box — charge $25 for the $9.99 thing and make it feel like winning. Once a kid has seen the $9.99, the claw loses its grip. Nobody shows them the $9.99.
-Every children's money book teaches saving. Piggy banks, jars, three little tins labeled spend-save-give where "spend" gets one page and a guilty look. But saving is the second thing a child does with money. The first is spending, and a six-year-old has done it already, standing in a store, deciding.
+Every children's money book teaches saving. Piggy banks, jars, three little tins labeled spend-save-give where "spend" gets one page and a guilty look. The genre's idea of a plot twist is a bigger jar. Meanwhile saving is the second thing a child does with money; the first is spending, and a six-year-old has done it already, standing in a store, deciding.
 So mine follows a single purchase the entire distance. A boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one deliberately, hands a coupon to the cashier, meets sales tax, and then lives with the thing. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed, so the parent reads it with the kid and gets handed the script instead of being expected to know it.
-The retail angle, if you want one: every trick your beat covers — the fake markdown, the anchor price, the "newest is better" framing — gets run on children first, in arcades and toy aisles, where there is no consumer press at all. The boardwalk airbrush stand charges $28 for a shirt that says BRAYDEN. Your kid's name is not Brayden.
+The retail angle, if you want one: every trick your beat covers — the fake markdown, the anchor price, the "newest is better" framing — gets run on children first, in arcades and toy aisles, where there is no consumer press and no one filing complaints because the mark is seven. The boardwalk airbrush stand charges $28 for a shirt that says BRAYDEN. Your kid's name is not Brayden.
 Worth a look? clarencegetsabargain.com/book-facts.html
 Jonathan</t>
         </is>
@@ -30451,7 +30451,7 @@
         <is>
           <t>Terry — you have been telling adults the truth about money for decades, usually after the damage is done. I wrote the book for about twenty years earlier than you usually get them.
 The argument in one line: mistakes at eleven cost $14, and the same mistake at twenty-seven has a credit card attached. Everything you write about compounding cuts both ways, and the habits doing the compounding were installed in a store, at six, with a parent saying no.
-Which is where the whole category gets the order wrong. Children's money books teach saving — piggy banks, jars, patience. But saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate. She has stood at a register holding money and had to decide.
+Which is where the whole category gets the order wrong. Children's money books teach saving — piggy banks, jars, patience, and a strong implication that wanting things is a character flaw. But saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate. She has stood at a register holding money and had to decide.
 Clarence Gets a Bargain follows one purchase the entire way: a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax and takes it personally, then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none announced — nobody in the book says "budget." The reader finds out he has been schooled at the glossary, twenty-one terms in the back, each page-referenced to the scene it came from.
 It reads aloud in twenty minutes. Lexile AD 620L — Adult Directed, the industry's own code for read-with rather than read-alone, so a parent who feels unqualified on money still gets handed the script.
 The column question rather than the book question: has anyone made the case that spending competence has to come first? I have not been able to find it, and you would know if it exists.
@@ -30511,7 +30511,7 @@
       <c r="K30" s="5" t="inlineStr">
         <is>
           <t>Amanda — Planet Money's whole trick is that people will sit still for an economics lesson if it is hidden inside a story about a person and a thing. I did that at a first-grade reading level, and I am writing about the story rather than the book.
-Every children's money book teaches earning or saving. All 25 on the ABA Foundation's list — I read them to be sure. A piggy bank, a lemonade stand, a lesson. Not one covers the cash register. Saving is the second thing a child does with money; spending is the first, and the register is the only place a child has ever actually handled any.
+Every children's money book teaches earning or saving. All 25 on the ABA Foundation's list — I read them to be sure. A piggy bank, a lemonade stand, a lesson. Not one covers the cash register. Forty years of piggy banks and not one of them has ever been to a store. Saving is the second thing a child does with money; spending is the first, and the register is the only place a child has ever actually handled any.
 Mine does. A boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, gets ambushed by sales tax, and then lives with what he bought. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget." They do not realise they have been schooled until they hit the glossary in the back — twenty-one terms, each page-referenced to the moment it happened. That is where the con comes apart, on purpose. It is catalogued AD 620L — Adult Directed — which is the trade's way of saying it only works out loud, with somebody interrupting.
 The numbers on the other side are absurd and nobody has ever put a microphone on them. Twelve hundred arcade tickets for a rubber slinky is an exchange rate that would embarrass a currency trader, and the kid making that trade has no idea he is trading.
 The segment is the forty-year hole. A whole publishing category taught children to save and skipped the register, while every arcade, app store and checkout lane aimed at children did not skip it at all. Nobody regulates the toy aisle and nobody covers it.
@@ -30573,7 +30573,7 @@
           <t>Bethann — you run the education side of a bankers association, which means you are the person who decides what volunteers actually carry into a classroom. I built something for the grade band most bank programs skip.
 Most financial education a bank sponsors lands in high school or in a "teach a child to save" day about saving. Saving is the second thing a child does with money. The first is spending, and a first grader has done it, at a register, with a parent behind her. There is almost nothing to hand a banker walking into a second-grade room about that.
 Clarence Gets a Bargain is a 36-page picture book following one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget."
-Why it works for a volunteer rather than a teacher: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, and the mother explains every concept inside the text. A banker can read it cold and field the questions straight off the page. No training call, nothing to memorise. The twenty-one-term glossary in the back is page-referenced to the story, so a volunteer answering a vocabulary question can turn to the scene rather than recite a definition. Free lesson plans, assessments and a browser-based pretend register sit behind it, all ungated.
+Why it works for a volunteer rather than a teacher: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, and the mother explains every concept inside the text. A banker can read it cold and field the questions straight off the page. No training call, nothing to memorise. The twenty-one-term glossary in the back is page-referenced to the story, so a volunteer answering a vocabulary question can turn to the scene rather than recite a definition. Free lesson plans, assessments and a browser-based pretend register sit behind it, all ungated. Every year the field builds another high-school course for a habit that set in first grade, and every year it works about as well as you would expect.
 The sponsorship math is simple if a member bank wants it: 25 copies is $499.75, one classroom, the bank's name on every book that goes home to a family. The educator program is free, so the sponsorship is entirely books, and I have a CRA-ready memo already written in examiner-friendly language.
 Does that fit how Utah banks choose classroom programs, or am I inventing a use case?
 clarencegetsabargain.com/educator-toolkit.html
@@ -30632,10 +30632,10 @@
       <c r="K32" s="5" t="inlineStr">
         <is>
           <t>Lynnette — you have spent a career telling people the truth about money in language they can actually use, and you built a network for people doing the same. I wrote the six-year-old version and I would like your read on whether it lands.
-Every children's money book teaches saving. Piggy banks, jars, three tins labeled spend-save-give where "spend" gets one page and a guilty look. But saving is the second thing a child does with money. The first is spending, and a first grader has already done it — in a store, holding money, deciding.
+Every children's money book teaches saving. Piggy banks, jars, three tins labeled spend-save-give where "spend" gets one page and a guilty look. Saving is the second thing a child does with money; the first is spending, and a first grader has already done it — in a store, holding money, deciding, with nobody having told her a single useful thing about it.
 And the tools have moved against them. A card is magic; a five-dollar bill is arithmetic — a kid who watches three dollars leave their hand understands something no tap-to-pay will ever teach.
 Which matters most in households where there is no margin for a bad purchase. A child taught only to save has been handed advice that assumes surplus. A child who can compare two prices and choose deliberately has a skill that works this Saturday.
-Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, meets sales tax, and then lives with what he chose. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the story. It is catalogued AD 620L — Adult Directed — so the adult reading gets handed the script and does not have to be the one who already knows about money. That was the design constraint that mattered most: it has to work in a house where nobody feels qualified to teach it.
+Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, meets sales tax, and then lives with what he chose. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the story. It is catalogued AD 620L — Adult Directed — so the adult reading gets handed the script and does not have to be the one who already knows about money. That was the design constraint that mattered most: it has to work in a house where nobody feels qualified to teach it. The piggy bank has had four hundred years and has yet to file a price comparison.
 Two questions. Does the spending-first argument hold up against what you hear from your audience? And is there a version of this worth putting in front of the Financial Influencer Network?
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -30695,7 +30695,7 @@
           <t>Ruben — CEE's standards are one of the five frameworks I crosswalked against, so I have spent real time inside them and want to ask about the bottom of the ladder.
 The elementary benchmarks exist. What is built against them is thin, and thinner still on the spending side. The field starts children with saving, and saving is the second thing a person does with money. The first is spending: standing in front of two prices and choosing one. A first grader has done that; she has no savings rate at all.
 I built a free K–5 classroom set around a 36-page picture book and crosswalked it concept by concept — 23 rows against the 2021 National Standards for Personal Financial Education, CEE, Common Core Math and ELA, and FDIC Money Smart, with the Grade 4 benchmark codes rather than a general claim of alignment. It is published so a reviewer can check it instead of taking my word.
-The book follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with the choice. Sixteen-plus concepts and nobody in it says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened. Catalogued AD 620L — Adult Directed — one class period read aloud, and because the mother explains every concept inside the text a teacher with no economics background runs it cold.
+The book follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with the choice. Sixteen-plus concepts and nobody in it says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened. Catalogued AD 620L — Adult Directed — one class period read aloud, and because the mother explains every concept inside the text a teacher with no economics background runs it cold. We are very good at teaching this to people who have already made the mistake.
 The question: is there a route for elementary material to sit alongside CEE programs, or does that run through affiliate councils? Either answer saves me guessing.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -30755,7 +30755,7 @@
           <t>Beth — you write for people trying to do the right thing with money and finding the advice arrives late. This arrives about two decades earlier than most of it.
 The premise: financial education starts children with saving, and the sequence is backwards. Saving is the second thing a person does with money. The first is spending. A seven-year-old has no savings rate and no income; what she has done is stand at a register holding money and choose. We teach that last, or never.
 I wrote the picture book for it. One purchase, followed the whole way — a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, meets sales tax, and then lives with what he chose. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; not one covers the whole arc.
-Sixteen-plus concepts, none announced — nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened, so vocabulary points a kid back into the story rather than away from it. It is catalogued AD 620L — Adult Directed — and the mother explains everything on the page, so the parent gets the script and can take the credit.
+Sixteen-plus concepts, none announced — nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened, so vocabulary points a kid back into the story rather than away from it. It is catalogued AD 620L — Adult Directed — and the mother explains everything on the page, so the parent gets the script and can take the credit. The subject is treated as serious and taught as though nobody ever spends any.
 One thing I would put to you as a planner: a card is magic, and a five-dollar bill is arithmetic. Children now grow up almost entirely inside the first one, which removes the only feedback loop they had.
 The claim I would defend hardest is the delayed one. The book is not really working in the twenty minutes it takes to read. It works in month eighteen, in a real store, when the kid hits a money moment and the book fires back — "wait, is the newer one actually better?" Recognition first, then the habit.
 Does that hold up against what you see in readers? clarencegetsabargain.com/book-facts.html
@@ -30816,7 +30816,7 @@
           <t>Julie — a segment idea, and it is short enough to survive a live hit.
 Every children's money book teaches saving. Piggy banks, lemonade stands, jars. But saving is the second thing a child does with money — the first is spending, and a six-year-old has already done it, in a store, holding a birthday five, deciding whether the thing is worth what it costs.
 The category skipped that for forty years. The arcade did not. A claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the kid has no price memory to defend himself with. Once a kid has seen the $9.99, the claw loses its grip.
-So I wrote the spending book. Clarence Gets a Bargain, ages 6–10: a boy earns a robot with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and then lives with the thing he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Twenty-one terms in a glossary at the back, each page-referenced to where it happened. Catalogued AD 620L — Adult Directed — twenty minutes out loud, interrupted the whole way.
+So I wrote the spending book. Clarence Gets a Bargain, ages 6–10: a boy earns a robot with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and then lives with the thing he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Twenty-one terms in a glossary at the back, each page-referenced to where it happened. Catalogued AD 620L — Adult Directed — twenty minutes out loud, interrupted the whole way. The category's own defence is that money is a serious subject. It is. So is getting fleeced in an aisle at the age of seven.
 I am an attorney and a mixed-media artist, and I have twice walked out of the same Nordstrom Rack having paid one cent — once for a $293 pair of shoes, once for a $69.50 shirt. I kept both tags. It makes for a good visual if you ever want one on screen.
 Is there a hit in "the money skill nobody teaches kids"? clarencegetsabargain.com/press-kit.html
 Jonathan</t>
@@ -30876,7 +30876,7 @@
           <t>Matt — you spend your working life on what happens when people meet credit without the groundwork. I wrote the book about the groundwork, roughly twenty years upstream of your data.
 The sequence is the whole argument. Financial education starts children with saving. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent behind her. Mistakes at eleven cost $14. The same mistake at twenty-seven has a credit card attached and a rate on it.
 Clarence Gets a Bargain follows one purchase the entire distance: a boy wants a robot, earns it with chores and grades, works the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; they are all parked on the earning-and-saving side of the register.
-Sixteen-plus concepts and nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened — which is the only point at which a kid works out he has been schooled. Catalogued AD 620L — Adult Directed — read with a parent, not handed to a kid alone. The single sentence I most want an eleven-year-old to own: marked down does not mean broken, it means the timing is on your side.
+Sixteen-plus concepts and nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened — which is the only point at which a kid works out he has been schooled. Catalogued AD 620L — Adult Directed — read with a parent, not handed to a kid alone. The single sentence I most want an eleven-year-old to own: marked down does not mean broken, it means the timing is on your side. The subject is treated as serious and taught as though nobody ever spends any.
 The question, since you have the data and I only have the book: does anything in what you see suggest that price competence at seven shows up at twenty-seven? If it does not, I would rather know.
 clarencegetsabargain.com/book-facts.html
 Jonathan</t>
@@ -30935,7 +30935,7 @@
         <is>
           <t>Jillian — Intuit for Education is built for high school and does that job well, so this is a question about the floor beneath it rather than a pitch into your territory.
 Everything in the field lands late. Thirty states require personal finance to graduate, all of it in high school. Money habits are largely set by seven. And the sequencing assumption nobody questions is that children should start with saving — when saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has stood at a register and chosen.
-I built the K–5 on-ramp. A 36-page picture book that follows one purchase the whole distance — wanting the robot, earning it, working the sale inserts at the kitchen table, comparing two models on a shelf, taking the marked-down one on purpose, redeeming a coupon, meeting sales tax, and living with the choice. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced back into the story.
+I built the K–5 on-ramp. A 36-page picture book that follows one purchase the whole distance — wanting the robot, earning it, working the sale inserts at the kitchen table, comparing two models on a shelf, taking the marked-down one on purpose, redeeming a coupon, meeting sales tax, and living with the choice. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced back into the story. Children can identify a worksheet through a closed backpack. That is the constraint everything else has to survive.
 The curriculum behind it is free and ungated — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart, printable classroom pieces, and a browser-based pretend register that runs a markdown, a coupon and sales tax with the total changing in front of the class. Catalogued Lexile AD 620L — Adult Directed — one class period, no teacher training.
 The honest question rather than a pitch: when teachers come to Intuit for Education, does elementary ever come up as something they want and cannot find? I am trying to work out whether I am filling a gap or inventing one, and you would see the demand signal before I would.
 clarencegetsabargain.com/educator-toolkit.html
@@ -30996,7 +30996,7 @@
           <t>Saskia — HCZ built its whole model on the idea that you intervene early and you do not wait for the system to catch up. I built the elementary financial-literacy piece on the same reasoning, and I would like your read on whether it holds.
 Every state financial-literacy requirement lands in high school. The habits being corrected there were installed at six, in a store. And the field starts children with saving, which is the second thing a child does with money — the first is spending, and it is the one your students are already doing.
 That distinction matters more, not less, for families with less room for error. A child who can compare two prices and choose deliberately has a skill that pays on a Saturday. A child taught only to save has been handed advice that requires surplus.
-Clarence Gets a Bargain is a 36-page picture book that follows one complete purchase: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget." A twenty-one-term glossary in the back, page-referenced to the story.
+Clarence Gets a Bargain is a 36-page picture book that follows one complete purchase: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget." A twenty-one-term glossary in the back, page-referenced to the story. A worksheet announces itself from three hallways away. Kids file it under school and stop reading, which is a design problem rather than a discipline one.
 Catalogued Lexile AD 620L — Adult Directed — one class period out loud, and because the mother explains every concept inside the text, a teacher needs no finance background. Everything behind it is free and ungated: lesson plans, assessments with answer keys, a standards crosswalk, printable classroom pieces, a browser-based pretend register.
 Would a read-aloud plus a pretend-store activity fit anywhere in a Promise Academy week, or is the schedule too tight for anything that is not tested?
 clarencegetsabargain.com/educator-toolkit.html
@@ -31055,7 +31055,7 @@
       <c r="K39" s="5" t="inlineStr">
         <is>
           <t>Ben — a story pitch about a gap in the coverage rather than a book pitch, though the book is how I found it.
-Thirty states now guarantee a personal finance course. Every one of those mandates lands in high school. Money habits are largely set by seven — so the policy arrives roughly ten years after the cement dries, and the funding, the training and the reporting all follow the mandate rather than the evidence.
+Thirty states now guarantee a personal finance course. Every one of those mandates lands in high school. Money habits are largely set by seven, so the policy arrives roughly ten years after the cement dries — a fifteen-year-old handed a course for a habit he formed at six, and everyone acting surprised, and the funding, the training and the reporting all follow the mandate rather than the evidence.
 Underneath that sits an assumption nobody argues with: that children should learn saving first. I think it is backwards. Saving is the second thing a person does with money. The first is spending, and a first grader has done that, at a register, with a parent standing behind her. The behaviors a high school course tries to correct were installed a decade earlier by an arcade, a toy aisle and a checkout lane, none of which waited for a curriculum.
 I wrote the elementary piece rather than an op-ed about it. A 36-page picture book following one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, and living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Free ungated classroom set behind it, crosswalked to five frameworks. Catalogued Lexile AD 620L — Adult Directed, so it is a read-with, and the caregiver conversation happens inside the reading.
 Meanwhile the arcade never waited for a standard: $25 into a glass box for a basketball Walmart sells for $9.99, and the kid has no price memory to argue with.
@@ -31179,7 +31179,7 @@
           <t>Susan — you built a center from nothing and have spent years getting economics into elementary classrooms, which makes you exactly the person to tell me whether I am filling a gap or inventing one.
 The gap as I see it: elementary standards exist in most states and almost nothing is built against them, because nobody has to report on them. Every mandate lands in high school. Thirty states now.
 And underneath that, a sequencing assumption nobody argues with — that children should learn saving first. Saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has stood at a register and chosen.
-So I wrote the K–5 piece. Clarence Gets a Bargain follows one purchase from the idea to after the receipt: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, so vocabulary review points a child back into the story instead of away from it.
+So I wrote the K–5 piece. Clarence Gets a Bargain follows one purchase from the idea to after the receipt: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, so vocabulary review points a child back into the story instead of away from it. The polite version is that the elementary band is understudied. The blunt version is that nobody has to report on it, so nobody looks.
 The teacher side is free and ungated — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE, and FDIC Money Smart. No account, no email capture, and it prints from a browser. Catalogued AD 620L — Adult Directed — a one-period read-aloud a teacher with no finance background can deliver cold.
 Does the spending-first sequence match what you see in classrooms, or is there a reason the field starts where it starts?
 clarencegetsabargain.com/educator-toolkit.html
@@ -31241,7 +31241,7 @@
 The money conversation in most families starts far too late to be a conversation. By the time a parent sits a teenager down, the habits are set — they were set at six, in a store, with a parent saying no and no explanation attached to the no.
 Every children's book on the shelf teaches saving. Piggy banks, jars, patience. But saving is the second thing a child does with money; the first is spending, and a six-year-old has already done it.
 Clarence Gets a Bargain follows one purchase the whole way — earning the reward through chores and grades, working the sale ads at the kitchen table, comparing two models on a shelf, taking the cheaper one on purpose, handing over a coupon, meeting sales tax, and then living with what was bought. Idea to post-receipt. And on page 6 there is something I have not found in any other picture book: a 529 plan. In the plot. Explained by a mom, eye-rolled at by a kid, and defended by a dad two scenes later.
-Sixteen-plus concepts and nobody says "budget." A twenty-one-term glossary in the back, page-referenced to the story. Catalogued Lexile AD 620L — Adult Directed — so it is a read-with, and the conversation happens during the reading rather than after it.
+Sixteen-plus concepts and nobody says "budget." A twenty-one-term glossary in the back, page-referenced to the story. Catalogued Lexile AD 620L — Adult Directed — so it is a read-with, and the conversation happens during the reading rather than after it. The category's own defence is that money is a serious subject. It is. So is getting fleeced in an aisle at the age of seven.
 A card is magic; a five-dollar bill is arithmetic. Children now grow up almost entirely inside the first one, which removed the only feedback loop they had.
 The angle for your beat: advisors spend fortunes trying to meet the next generation before the assets move. This is what meeting them at seven looks like, and it costs $19.99.
 Worth a column, or am I describing something you have already covered? clarencegetsabargain.com/press-kit.html
@@ -31300,7 +31300,7 @@
       <c r="K43" s="5" t="inlineStr">
         <is>
           <t>Dr. Taylor — I am a Maryland attorney and children's book author writing about the elementary end of financial literacy, which is the end nobody funds.
-Maryland's requirement, like every state's, lands in high school. The elementary standards sit underneath it with almost nothing built against them, because no one has to report on that band. Meanwhile the habits a high school course is trying to correct were installed at six, in a store, with a parent saying no and no reasoning attached.
+Maryland's requirement, like every state's, lands in high school. The elementary standards sit underneath it with almost nothing built against them, for the least respectable reason available: nobody has to report on that band. Meanwhile the habits a high school course is trying to correct were installed at six, in a store, with a parent saying no and no reasoning attached.
 The field's answer is to teach children saving first. Saving is the second thing a person does with money. The first is spending, and a first grader has done it — at a register, with a parent standing right there.
 I wrote the K–5 piece. A 36-page picture book following one purchase from the idea through the receipt: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken on purpose, a coupon at the register, sales tax, and living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced back into the story.
 What matters for a district is that all of it is free. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, and a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart. No account, no email capture, no purchase order. It prints from a browser, so adoption costs a building nothing. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud a teacher can run with no finance background.
@@ -31365,7 +31365,7 @@
           <t>Beth — a research question rather than a pitch, and the book is only the reason I ran into it.
 Financial capability gets measured, sensibly, on saving, compounding and risk. Those are the right things to measure in adults. But each of them sits downstream of a decision made years earlier that nobody scores: a child standing in front of two prices, picking one. Spending is the first financial behavior a person performs, and it is taught last or not at all.
 The environment is not waiting for the curriculum. Children are transacting constantly — arcades, app stores, checkout lanes — and none of it gets counted as financial education, though it plainly is.
-I wrote the elementary piece. A 36-page picture book following one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, and living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced back into the story. Free ungated classroom set behind it, crosswalked to five frameworks.
+I wrote the elementary piece. A 36-page picture book following one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, and living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced back into the story. Free ungated classroom set behind it, crosswalked to five frameworks. The polite version is that the elementary band is understudied. The blunt version is that nobody has to report on it, so nobody looks.
 Design note that may matter to your work: the book is catalogued Lexile AD 620L — Adult Directed. The intervention is an adult and a child reading together, not a child reading alone, which makes it closer to a shared-reading study than a curriculum study.
 The question: does the evidence base start at adolescence the way the books do? If spending competence at seven predicts nothing at twenty-seven, that is worth knowing and I would rather hear it than keep arguing.
 clarencegetsabargain.com/book-facts.html
@@ -31426,7 +31426,7 @@
         <is>
           <t>Sam — you have been reading, singing and performing a savings habit into elementary classrooms for two decades across thirty states, which is more direct contact with this audience than anyone else in the category has. So I want to put an argument in front of you and hear where it is wrong.
 Sammy teaches saving, and teaches it better than anything else aimed at this age. My argument is not about quality; it is about order. Saving is the second thing a child does with money. The first is spending — a first grader has stood at a register holding money and chosen, years before she has anything to save. Teach that moment first, and everything Sammy preaches lands harder, because a kid who understands what money buys has a reason to keep some.
-That is the book I wrote. Clarence Gets a Bargain follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the scene each term came from. Catalogued AD 620L — Adult Directed — about twenty minutes out loud, every concept explained inside the text, so somebody can read it cold to a class. You of all people will know why that mattered to me.
+That is the book I wrote. Clarence Gets a Bargain follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the scene each term came from. Catalogued AD 620L — Adult Directed — about twenty minutes out loud, every concept explained inside the text, so somebody can read it cold to a class. You of all people will know why that mattered to me. The rest of the shelf is piggy banks with plots. Good ones, some of them — but none of them has ever been to a register.
 You also solved a distribution problem the rest of us have not: banks and credit unions sponsor the visits and buy the books, and their community reports write themselves. I would rather learn that from you than reverse-engineer it.
 Trade copies and compare notes? I will read Sammy properly and tell you the truth about it, which is the only thing worth trading.
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -31488,7 +31488,7 @@
 Most financial education material aimed at children starts with saving. Saving is the second thing a child does with money. The first is spending — and a first grader has done it, at a register, with a parent behind her. An instructor standing in front of a second-grade class has almost nothing to hand them about that moment.
 Clarence Gets a Bargain is a 36-page picture book that follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one deliberately, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget."
 Why it works for an instructor rather than a teacher: it is catalogued Lexile AD 620L — Adult Directed — it runs about twenty minutes out loud, and the mother explains every concept inside the text. Somebody can read it cold to a class and field questions straight off the page. Nothing to memorise, no training call beforehand. Behind it sits a free ungated set — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, and a browser-based pretend register with a markdown, a coupon and sales tax.
-The twenty-one-term glossary in the back is page-referenced to the story, so an instructor can answer a vocabulary question by turning to the scene rather than reciting a definition.
+The twenty-one-term glossary in the back is page-referenced to the story, so an instructor can answer a vocabulary question by turning to the scene rather than reciting a definition. The field keeps building the ninth-grade course and keeps skipping the second-grade one, which is a strange place to draw a line.
 Does your instructor network want elementary material, or is the demand really all adult and teen? Everything is free either way.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan</t>
@@ -31546,9 +31546,9 @@
       <c r="K47" s="5" t="inlineStr">
         <is>
           <t>Billy — a question about where NEFE draws the line on grade band, asked by someone who has just spent a year building for the band nobody funds.
-Thirty states now require personal finance to graduate. The mandates land in high school, and the funding, the training and the reporting follow the mandate. Meanwhile the K–5 standards that already exist in most states sit there with almost nothing built against them, because nobody has to report on them.
+Thirty states now require personal finance to graduate. The mandates land in high school, and the funding, the training and the reporting follow the mandate — which is a tidy way of arriving about nine years late and calling it early intervention. Meanwhile the K–5 standards that already exist in most states sit there with almost nothing built against them, because nobody has to report on them.
 The assumption underneath is that children should learn saving first. I think it is backwards, and I would rather be told so by NEFE than keep saying it at conferences. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent standing behind her. The behaviors a high school course is trying to correct were installed a decade earlier.
-I wrote the elementary piece rather than an argument about it: a 36-page picture book that follows one purchase from the idea to after the receipt, plus a free ungated classroom set crosswalked to the 2021 National Standards, Common Core, CEE and FDIC Money Smart. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Catalogued Lexile AD 620L — Adult Directed — so the intervention is a shared read rather than solo reading, which also makes it easier to study than a curriculum.
+I wrote the elementary piece rather than an argument about it: a 36-page picture book that follows one purchase from the idea to after the receipt, plus a free ungated classroom set crosswalked to the 2021 National Standards, Common Core, CEE and FDIC Money Smart. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Catalogued Lexile AD 620L — Adult Directed — so the intervention is a shared read rather than solo reading, which also makes it easier to study than a curriculum. There is a whole industry aimed at teenagers who already have the habit, and almost nobody upstream of it.
 The line I would put on a poster if I could: mistakes at eleven cost $14, and the same mistake at twenty-seven has a credit card attached.
 The question: does NEFE's research or advocacy work have a position on the elementary band, or is the practical view that high school is where the effort pays? If it is the second, I would like to know I am arguing with a considered consensus rather than filling a gap it agrees exists.
 clarencegetsabargain.com/educator-toolkit.html
@@ -31611,7 +31611,7 @@
 Jump$tart's standards cover K–12, but the material built against them thins out badly below grade six. The elementary band has standards and very little aimed at it, largely because nothing requires anyone to report on that band. Every state mandate lands in high school. Thirty of them now.
 There is also a sequencing assumption underneath the whole field that I would like your view on. Financial education starts children with saving. Saving is the second thing a person does with money; the first is spending. A first grader has no savings rate. She has stood at a register holding money and had to choose.
 I built a free, ungated K–5 classroom set around a 36-page picture book: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE and FDIC Money Smart, printable classroom pieces, and a browser-based pretend register. No account, no email capture, no purchase order. It prints from a browser.
-The book follows one complete purchase — sale ads, comparison, a markdown, a coupon, sales tax — with sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story. Catalogued Lexile AD 620L, Adult Directed, so it runs as a one-period read-aloud with no teacher training required.
+The book follows one complete purchase — sale ads, comparison, a markdown, a coupon, sales tax — with sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story. Catalogued Lexile AD 620L, Adult Directed, so it runs as a one-period read-aloud with no teacher training required. The field keeps building the ninth-grade course and keeps skipping the second-grade one, which is a strange place to draw a line.
 One line from the book does the work of a standards document, and it is the one I would defend hardest: marked down does not mean broken, it means the timing is on your side.
 Two questions. Does Jump$tart consider elementary in scope, or is it a band the coalition has consciously left to others? And for the Clearinghouse, is the free classroom set the right thing to submit rather than the book?
 clarencegetsabargain.com/educator-toolkit.html
@@ -31672,7 +31672,7 @@
           <t>Prince — you took investing, which is the hardest concept in this category to make readable for children, and made it a series a kid comes back to. I went the opposite direction on the same shelf and I would like your read on it.
 Wesley learns to invest. Clarence learns to spend — and I mean the mechanics of it rather than the idea. Every other book in the category teaches saving, which is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. Nobody had written that one, so I did.
 Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Nobody says the word "budget."
-The craft problem I would most like another author's view on: the reader is not supposed to know he has been taught anything until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. Getting that balance right, so it stays a story, was the whole job, and it is the thing most likely to be off by a hair.
+The craft problem I would most like another author's view on: the reader is not supposed to know he has been taught anything until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. Getting that balance right, so it stays a story, was the whole job, and it is the thing most likely to be off by a hair. The rest of the shelf is piggy banks with plots. Good ones, some of them — but none of them has ever been to a register.
 I did the illustrations too, which means my opinion of them is worth nothing. It is written for the adult voice in the room — catalogued AD 620L, Adult Directed — with the mother carrying every explanation.
 Trade? Send me a Wesley and I will read it properly rather than politely.
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -31731,7 +31731,7 @@
       <c r="K50" s="5" t="inlineStr">
         <is>
           <t>Kate — a pitch about a gap rather than a book, though I wrote the book because of the gap.
-Everything in kids' financial literacy points at a horizon no child can see: compound interest, credit scores, retirement. All real, all decades out. Meanwhile the kid is eight, holding $20 of birthday money, standing in a store that spent millions working out how to get it. We are preparing children for 65 and sending them to the register unarmed today.
+Everything in kids' financial literacy points at a horizon no child can see: compound interest, credit scores, retirement. All real, all decades out, and all completely useless to somebody who is eight. Meanwhile the kid is eight, holding $20 of birthday money, standing in a store that spent millions working out how to get it. We are preparing children for 65 and sending them to the register unarmed today.
 So flip the order. Saving is the second thing a child does with money. The first is spending, and it is the one nobody puts in a story.
 Clarence Gets a Bargain does. One kid, one purchase, followed the whole distance — he wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget." The reader works out he has been schooled at the glossary — twenty-one terms in the back, each one page-referenced to the scene it came from. Catalogued AD 620L — Adult Directed — so a parent who does not feel qualified on money still gets handed the script and can take the credit.
 The boardwalk is a pop quiz your kid has not studied for, and it runs all summer with real money.
@@ -32025,7 +32025,7 @@
           <t>Professor Urban — you produced the evidence base that mandates actually work, which is why I want to ask about the grade band your evidence does not reach.
 Every mandate you have evaluated lands in high school. Thirty states now. The effects are real and I am not arguing with them. My question is about what is happening a decade earlier, because money habits are largely set by seven and the policy arrives roughly ten years after the cement dries.
 Underneath the whole field sits a sequencing assumption nobody tests: that children should learn saving first. I think it is backwards. Saving is the second thing a person does with money. The first is spending — standing in front of two prices and picking one. A first grader has done that. She has no savings rate at all.
-I could not find the children's book for it, so I wrote one. Clarence Gets a Bargain follows a single purchase the entire way: earning the reward, reading the sale ads, comparing two models on a shelf, choosing the cheaper one deliberately, redeeming a coupon, meeting sales tax, and then living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story.
+I could not find the children's book for it, so I wrote one. Clarence Gets a Bargain follows a single purchase the entire way: earning the reward, reading the sale ads, comparing two models on a shelf, choosing the cheaper one deliberately, redeeming a coupon, meeting sales tax, and then living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Elementary is not so much contested ground as unvisited ground.
 One design feature that may matter for measurement: the book is catalogued Lexile AD 620L — Adult Directed — so the intervention is not a child reading alone but an adult and a child reading together, with the adult prompted by the text. If shared reading is doing the work rather than the book, that is testable, and it would be a more interesting finding than anything about my book.
 The real question: does anything in the literature speak to elementary spending competence, or is that band simply unstudied? Either answer is useful to me.
 clarencegetsabargain.com/book-facts.html
@@ -32087,7 +32087,7 @@
           <t>Iris — you were part of the group that chose the titles on the Money as You Grow Bookshelf, so you have read this category more carefully than almost anyone, and you will know immediately whether my premise is wrong.
 The shelf, as it stands, leans toward saving and earning. Spending is thin, and the transaction itself is thinner — the part where a child stands in front of two prices and picks one. Saving is the second thing a person does with money; spending is the first, and it gets taught last or not at all.
 Clarence Gets a Bargain covers exactly that, and covers the whole of it: a boy wants a robot, earns it through chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list looking for another one that does the whole arc. They are all parked on the earning-and-saving side of the register.
-Sixteen-plus concepts and none is announced — no character pauses to define a term, nobody says the word "budget." The proof and the reveal are both in the back matter: a reader does not know he has been schooled until he reaches the glossary. Twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than an appendix.
+Sixteen-plus concepts and none is announced — no character pauses to define a term, nobody says the word "budget." The proof and the reveal are both in the back matter: a reader does not know he has been schooled until he reaches the glossary. Twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than an appendix. Elementary is not so much contested ground as unvisited ground.
 Ages 6–10, inside the Bookshelf's 4–10 band. Catalogued Lexile AD 620L — Adult Directed, which is how the Bookshelf's titles are meant to be used anyway.
 Two questions. Was the saving weighting deliberate, or just what existed? And is the selection process still running?
 clarencegetsabargain.com/book-facts.html
@@ -32156,7 +32156,7 @@
 Professor Mahoney — your work is about what consumers actually do when a price is put in front of them, as opposed to what a model says they should. I want to ask about the earliest version of that decision, because nobody seems to study it.
 A six-year-old with a birthday five in an aisle is running a comparison with no price history, no reference class and no idea that anchoring exists. She is the purest case your field could ask for and the least documented. Meanwhile the environment is not naive at all — a boardwalk claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the child has no way of knowing the $9.99 exists.
 Financial education answers this by teaching saving. But saving is the second thing a person does with money; the first is spending, and it is taught last or not at all.
-I wrote the picture book rather than the paper. Clarence Gets a Bargain follows one complete purchase — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with the choice afterward. Sixteen-plus concepts, none announced. Twenty-one terms in a back-matter glossary, each page-referenced to the scene it came from. Catalogued Lexile AD 620L — Adult Directed — so the reading is a joint activity by design rather than a solo one.
+I wrote the picture book rather than the paper. Clarence Gets a Bargain follows one complete purchase — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with the choice afterward. Sixteen-plus concepts, none announced. Twenty-one terms in a back-matter glossary, each page-referenced to the scene it came from. Catalogued Lexile AD 620L — Adult Directed — so the reading is a joint activity by design rather than a solo one. The band is not understudied because it is uninteresting. It is understudied because nothing forces anyone to count it.
 For what it is worth, the field's own blind spot has a price tag on it: a boardwalk claw machine takes $25 to hand back a basketball Walmart sells for $9.99, and no curriculum anywhere treats that as a financial event.
 The question I would actually like answered: is there work on when price competence forms, and whether early exposure to comparison changes anything measurable later? If the honest answer is that it is unstudied because it is unmeasurable at that age, that is worth knowing too.
 clarencegetsabargain.com/book-facts.html
@@ -32336,7 +32336,7 @@
         <is>
           <t>Jennifer — a funding-shaped question rather than an ask, and the resource itself is already free.
 I wrote and illustrated a K–5 financial-literacy picture book and built the entire classroom program behind it — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a standards crosswalk across five frameworks. All of it is ungated: no account, no email capture, no purchase order, prints from a browser. The only thing that ever costs anything is the physical books, and 25 copies run $499.75.
-The content premise: every children's money book teaches saving, and saving is the second thing a child does with money. The first is spending — a first grader has stood at a register and chosen. The book follows one complete purchase from the idea through the receipt, with sixteen-plus concepts hidden in the plot and a twenty-one-term glossary page-referenced back into the story.
+The content premise: every children's money book teaches saving, and saving is the second thing a child does with money. The first is spending — a first grader has stood at a register and chosen. The book follows one complete purchase from the idea through the receipt, with sixteen-plus concepts hidden in the plot and a twenty-one-term glossary page-referenced back into the story. If a money lesson looks like school, it gets filed under school and read at school speed.
 Why I am writing to development rather than to a classroom: this is unusually easy to fund. A bank or credit union sponsoring a classroom set gets its name on every book that goes home to a family in its assessment area, the curriculum costs the sponsor nothing because it is already free, and I have a CRA-ready memo written in examiner-friendly language. A funder can point at 25 books, one classroom, and a pre/post instrument. And because it is catalogued AD 620L — Adult Directed — it doubles as family engagement: the same book works at a kitchen table with a parent or a grandparent reading.
 Is a sponsored classroom set something HCZ's funders would recognise, or does everything need to attach to an existing program line?
 clarencegetsabargain.com/resources/grant-in-a-box.html
@@ -32396,7 +32396,7 @@
         <is>
           <t>Flora — JA runs volunteers into elementary classrooms better than any organisation in the country, so this is a materials question rather than a pitch.
 JA's elementary programs are strong on earning, jobs and community. What is thin across the whole field, JA included, is spending — the second thing everybody teaches and the first thing a child actually does. A first grader has no savings rate and no job. What she has done is stand at a register holding money and choose.
-Clarence Gets a Bargain is a 36-page picture book that puts the entire transaction on the page: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
+Clarence Gets a Bargain is a 36-page picture book that puts the entire transaction on the page: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from. Every year the field builds another high-school course for a habit that set in first grade, and every year it works about as well as you would expect.
 The part that matters for a volunteer model: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, with every concept explained inside the text by the mother. A volunteer who has never taught anything can read it cold and answer questions off the page. Nothing to memorise and no prep call. Behind it, free and ungated: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable price tags and clearance stickers for a classroom store, and a browser-based pretend register with a markdown, a coupon and sales tax.
 Alaska has its own complications on distance and travel, and virtual read-alouds work for this.
 Does a read-aloud fit how JA Alaska builds a volunteer session, or does everything have to run through national curriculum?
@@ -32520,7 +32520,7 @@
           <t>Gene — Troutwood is built on showing people the long arc of a decision, which is why I am writing about the very first decision on that arc.
 Everything in financial planning compounds, including the mistakes, and the compounding starts long before anyone opens an account. Mistakes at eleven cost $14. The same mistake at twenty-seven has a credit card attached. The habit doing the compounding was installed at six, in a store, with a parent saying no and no reasoning attached to the no.
 Financial education answers that by teaching children saving. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with no framework at all.
-Clarence Gets a Bargain is the picture book for that. One purchase, followed the whole way: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed — so it is a shared read and the parent gets the script rather than a homework assignment.
+Clarence Gets a Bargain is the picture book for that. One purchase, followed the whole way: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed — so it is a shared read and the parent gets the script rather than a homework assignment. A jar is a storage container. It has never once talked a kid out of anything.
 The claim I would defend hardest is the delayed one, and it is the same claim Troutwood makes about projections: the value is not in the twenty minutes. It is in month eighteen, in a real store, when the kid hits a money moment and the book fires back. Recognition first, then the habit.
 Does the elementary end fit anything Troutwood does, or is that below the floor?
 clarencegetsabargain.com/book-facts.html
@@ -32580,7 +32580,7 @@
         <is>
           <t>Rob — you build resources teachers actually use, which is a harder job than writing curriculum and a rarer one. I built the elementary thing that does not exist, and I want a practitioner's read on whether it survives a real classroom.
 The gap: every mandate lands in high school, so that is where every resource goes. The elementary standards exist and almost nothing is built against them. And the field starts children with saving, when saving is the second thing a person does with money — the first is spending, and a first grader has already done it at a register.
-Clarence Gets a Bargain is a 36-page picture book following one complete purchase: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken on purpose, a coupon at the register, sales tax, and living with what was bought. Sixteen-plus concepts, none announced. Kids smell a worksheet one page in; they never smell this one. A twenty-one-term glossary in the back, page-referenced to the story.
+Clarence Gets a Bargain is a 36-page picture book following one complete purchase: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken on purpose, a coupon at the register, sales tax, and living with what was bought. Sixteen-plus concepts, none announced. Kids smell a worksheet one page in; they never smell this one. A twenty-one-term glossary in the back, page-referenced to the story. Nobody has ever formed a money habit by looking at a jar.
 The teacher side is where I would want your opinion. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row standards crosswalk, printable price tags and clearance stickers for a classroom store, and a browser-based register that runs a markdown, a coupon and sales tax with the total changing in front of the class. Ungated — no account, no email capture — and it prints from a browser. Catalogued Lexile AD 620L, Adult Directed: one class period, no teacher training, and the text carries every explanation.
 The whole thing rests on one instruction a teacher can act on the same week: stop bringing kids to the store as cargo, bring them as staff. Every activity in the set is a version of that.
 The honest question: what makes a free teacher resource actually get used rather than downloaded and forgotten? You have watched that happen more times than I have, and I would rather fix it now.
@@ -32642,7 +32642,7 @@
           <t>Martin — you sit where the profession decides what it is responsible for, so this is a question about the far upstream end of that responsibility.
 Planners meet clients' children late, usually at the worst possible moment, and by then the habits are twenty years old. They were formed at six, in a store, with a parent saying no and no reasoning attached to the no.
 The field's answer to that is to teach children saving. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, holding a birthday five, deciding whether the thing is worth what it costs.
-I wrote the picture book for that moment. Clarence Gets a Bargain follows one purchase the whole way — earning the reward through chores and grades, working the sale ads at the kitchen table, comparing two models on a shelf, taking the cheaper one on purpose, redeeming a coupon, meeting sales tax, and then living with what was bought. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in a back-matter glossary, page-referenced to the story.
+I wrote the picture book for that moment. Clarence Gets a Bargain follows one purchase the whole way — earning the reward through chores and grades, working the sale ads at the kitchen table, comparing two models on a shelf, taking the cheaper one on purpose, redeeming a coupon, meeting sales tax, and then living with what was bought. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in a back-matter glossary, page-referenced to the story. A course at fifteen for a habit set at six is not early intervention; it is a receipt.
 And on page 6 there is something I have not found in any other picture book: a 529 plan. In the plot. Explained by a mother, eye-rolled at by a kid, defended by a father two scenes later. It is catalogued AD 620L — Adult Directed — so a planner handing it to a client family is handing over a script rather than an assignment. Twenty-five copies run $499.75, and the educator program behind it is free.
 The question: does CFP Board's pro bono and public-education work reach below high school at all, or is that considered somebody else's ground?
 clarencegetsabargain.com/book-facts.html
@@ -32825,7 +32825,7 @@
         <is>
           <t>Annie — you built a product for the exact age band everyone else in this category skips, so you already believe the thing I have been arguing. I want to compare notes rather than pitch you.
 My First Nest Egg puts save, spend, give and invest in front of a young child in physical form. My argument is about which of those a child actually performs first. It is spending — a six-year-old has stood in a store holding money and chosen, years before she has anything to save or invest. The category teaches saving first anyway, and I could not find the book that teaches the other one.
-So I wrote and illustrated it. Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed — read with a grown-up rather than handed over. There is also a free browser-based pretend register behind it that runs a markdown, a coupon and sales tax, which is the closest thing I have to your physical product.
+So I wrote and illustrated it. Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed — read with a grown-up rather than handed over. There is also a free browser-based pretend register behind it that runs a markdown, a coupon and sales tax, which is the closest thing I have to your physical product. Nobody has ever formed a money habit by looking at a jar.
 Those look complementary rather than competing to me: yours gives a kid the categories in their hands, mine walks them through the mechanics of one transaction in twenty minutes.
 Worth a conversation about whether they belong near each other? And separately — if you think spending-before-saving is wrong, you are one of very few people whose disagreement would actually change my mind.
 https://heyzine.com/flip-book/eeb1ef6cff.html

--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -750,7 +750,7 @@
 Here is the pitch in one line: every children's money book teaches saving, and saving is the second thing a kid does with money. The first is spending. A six-year-old has no savings rate. She has stood in an aisle holding a birthday five, deciding whether the thing is worth it.
 So I wrote the spending one. Clarence Gets a Bargain follows a single purchase the entire way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, gets ambushed by sales tax, and then lives with the thing he bought. Idea to post-receipt. Name another picture book where the kid reads the sale ads before the trip, compares models in the aisle, hands over a coupon, and pays the sales tax. I read all 25 titles on the ABA Foundation's list looking for one. They are all parked on the earning-and-saving side of the register.
 Sixteen-plus concepts are in there and none of them are announced. Nobody says the word "budget." They don't realise they've been schooled until they hit the glossary — twenty-one terms in the back, each page-referenced to the moment it actually happened. That's where the con comes apart, on purpose.
-The segment I'd pitch is not the book. It's the forty-year hole: why an entire publishing category skipped the cash register. There is a Planet Money episode in that whether or not mine is the book that gets mentioned.
+The segment worth doing has nothing to do with my book. It's the forty-year hole: why an entire publishing category skipped the cash register. There is a Planet Money episode in that whether or not mine is the book that gets mentioned.
 One structural note, since you make things people take in together: the reading level is Lexile AD 620L, and the AD stands for Adult Directed — the trade's own code for a book meant to be read *with* a child rather than handed to one. That was the design, not the accident. Twenty minutes out loud, interrupted the whole way, and the interruptions are the product. Classroom, kitchen table, grandparent's couch — same pages, same arguments break out.
 Am I wrong that it's a story? clarencegetsabargain.com/book-facts.html has the specs. Four-minute flip: https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -869,7 +869,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>Tim — NGPF owns 9-12 and does it better than anyone, so this is not a pitch into your territory. It is a question about the floor beneath it.
+          <t>Tim — NGPF owns 9-12 and does it better than anyone, so take this as a question about the floor beneath your work rather than a pitch into your territory.
 Every state that mandates personal finance mandates it in high school. Delaware just became the thirtieth and put the course in front of ninth graders. Fine as far as it goes. But the money behaviors NGPF is correcting at sixteen were installed at six, in a store, with a parent saying no.
 The sequence is what I keep coming back to. Financial education starts with saving, and saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has stood at a register and chosen.
 I wrote the K-5 on-ramp. One purchase, followed the whole distance — wanting a robot, earning it, working the sale inserts at the kitchen table, comparing two on a shelf, taking the cheaper one on purpose, redeeming a coupon, meeting sales tax, and living with the choice. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; none does the full arc. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced back into the story.
@@ -992,11 +992,11 @@
       <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Kim — you review children's books for a living, so you have read more well-meaning money picture books than anyone should have to, and you already know the problem with them.
-They all teach saving. A piggy bank, a lemonade stand, a lesson. Which is fine advice in the wrong order, because saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate and has absolutely stood in a store holding money and had to decide.
+They all teach saving. A piggy bank, a lemonade stand, a lesson. Which is fine advice in the wrong order, because saving is the second thing a child does with money; the first is spending. A six-year-old has no savings rate and has absolutely stood in a store holding money and had to decide.
 Mine is the spending one, and it follows a single purchase the whole distance rather than gesturing at the idea: a boy wants a robot, earns it with chores and grades, works the sale ads at the kitchen table, compares two models in the aisle, takes the cheaper one on purpose, hands a coupon to the cashier, gets hit with sales tax, and then has to live with the thing. Idea to post-receipt. I read all 25 on the ABA Foundation's list to be sure nobody had done it. Nobody had.
-What I'd actually want your eye on is the smuggling. Sixteen-plus concepts and not one of them is announced — no character stops to explain a term, nobody says "budget." The reader does not know he's been schooled until he reaches the glossary — twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than a homework appendix. The reveal is deliberate and it is on the last page. That balance is the hardest thing in the book and the thing most likely to be off by a hair.
+What I'd actually want your eye on is the smuggling. Sixteen-plus concepts and not one of them is announced , no character stops to explain a term, nobody says "budget." The reader does not know he's been schooled until he reaches the glossary , twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than a homework appendix. The reveal is deliberate and it is on the last page. That balance is the hardest thing in the book and the thing most likely to be off by a hair.
 One thing I'd want you to test rather than take on faith: whether it clicks later. The book is built to fire back months on, in a real store — "is the newer one really better? Clarence checked." Recognition first, then the habit. If that isn't actually in the pages, I'd want to know.
-The other thing worth your reviewer's ear: it is built to be read aloud, and Lexile has it at AD 620L — Adult Directed, read-with rather than read-alone. The mother carries the exposition, which means the adult holding the book is handed the script. Whether that voice actually holds up out loud — across a classroom, a couch, and a grandparent's lap — is something you would hear in a page and I can only guess at.
+The other thing worth your reviewer's ear: it is built to be read aloud, and Lexile has it at AD 620L — Adult Directed, read-with rather than read-alone. The mother carries the exposition, which means the adult holding the book is handed the script. Whether that voice actually holds up out loud , across a classroom, a couch, and a grandparent's lap , is something you would hear in a page and I can only guess at.
 Would you read it as an editor rather than as a friend? I would rather hear where it sags than be told it's charming.
 clarencegetsabargain.com/press-kit.html · https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -1176,7 +1176,7 @@
       <c r="K9" s="5" t="inlineStr">
         <is>
           <t>Michelle — you have written for twenty years that the money conversation with children has to start early, and I wrote the book for the earliest version of it. One question at the end, and it is a column question rather than a book question.
-Every children's financial literacy book teaches saving. I read all 25 on the ABA Foundation's list to be certain. Piggy banks, jars, patience. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it — in a store, holding money, deciding whether the thing is worth what it costs.
+Every children's financial literacy book teaches saving. I read all 25 on the ABA Foundation's list to be certain. Piggy banks, jars, patience. But saving is the second thing a child does with money; the first is spending, and a six-year-old has already done it — in a store, holding money, deciding whether the thing is worth what it costs.
 Mine follows one purchase the entire way. A boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he bought. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." Twenty-one terms in the glossary, each page-referenced to the scene it came from.
 The format is part of the argument. Lexile AD 620L — Adult Directed, the industry's own code for a book meant to be read *with* a child. Which means the conversation you have been telling parents to have for twenty years happens on its own: an adult reads, a kid interrupts, and somebody in the room has to answer "do we have one of those?" out loud. It works the same when the adult is a grandparent, which is often who is actually sitting there.
 The column, if there is one: an entire publishing category has taught children to save for forty years and skipped the cash register, which is the only place a child has ever actually handled money. That is a story about the field, not about me.
@@ -1238,9 +1238,9 @@
         <is>
           <t>Cinders — Moneybunnies splits money into Earn, Save, Spend and Give, which makes you the one person in this category who already agreed with me before I showed up.
 I went deep on one of your four. Spending, and specifically the whole transaction rather than the idea of it. Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then has to live with what he picked. Idea to post-receipt.
-The reason I think it sits beside Moneybunnies rather than against it: you give a child the four categories, and mine walks them through the mechanics of one. Sixteen-plus concepts, none announced — nobody says "budget" — and twenty-one terms in a glossary in the back, each page-referenced to the scene where it happened.
+The reason I think it sits beside Moneybunnies rather than against it: you give a child the four categories, and mine walks them through the mechanics of one. Sixteen-plus concepts, none announced , nobody says "budget" , and twenty-one terms in a glossary in the back, each page-referenced to the scene where it happened.
 Author-illustrator to author-illustrator: I did the art as well, so I know exactly how much of the work nobody sees. I'd rather you saw this from me than off a shelf.
-The read-aloud is the other half of it. Lexile AD 620L — Adult Directed — written for the adult voice in the room rather than for a child alone, with the mother carrying the explanations so the grown-up gets handed the script. You will know better than most how much that changes what has to happen on the page.
+The read-aloud is the other half of it. Lexile AD 620L , Adult Directed , written for the adult voice in the room rather than for a child alone, with the mother carrying the explanations so the grown-up gets handed the script. You will know better than most how much that changes what has to happen on the page.
 Trade copies? I'll read yours properly and tell you the truth about it, which is the only thing worth trading.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -1360,7 +1360,7 @@
           <t>Leslie — a Money as You Grow question, and then an idea I'd like a CFPB read on.
 The question first. Is the Bookshelf still evaluating titles, and who owns it now? I have a K-5 picture book that teaches spending rather than saving, and the current shelf leans heavily toward saving.
 The idea. A child becomes a consumer the first time they hand money to a cashier. Not at eighteen, not at a first paycheck — at six, at a register, with a birthday five. Everything in youth financial education treats that child as a saver in training. Almost nothing treats her as what she already is: a party to a transaction.
-My book follows one purchase the entire way, which is the part I could not find anywhere else — from wanting the thing, through the sale ads, the comparison, the markdown, the coupon, and the sales tax, to living with what was bought. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in the glossary, each page-referenced to the scene where it happened.
+My book follows one purchase the entire way, which is the part I could not find anywhere else — from wanting the thing, through the sale ads, the comparison, the markdown, the coupon, and the sales tax, to living with what was bought. Idea to post-receipt; sixteen-plus concepts, none announced. Twenty-one terms in the glossary, each page-referenced to the scene where it happened.
 One format note relevant to Money as You Grow: Lexile AD 620L — Adult Directed, a read-with rather than a read-alone. The caregiver conversation the framework is built around happens inside the reading rather than after it, and it happens whether the adult is a parent, a teacher, or a grandparent.
 I know the full picture crosses agencies — warranties and returns are FTC, product safety is CPSC — and I am not asking CFPB to cover those. I am asking whether Money as You Grow has room for material that treats the child as a consumer on the financial side from the first purchase forward.
 clarencegetsabargain.com/educator-toolkit.html
@@ -1551,11 +1551,11 @@
       <c r="K15" s="5" t="inlineStr">
         <is>
           <t>Tiffany — you built a career on the thing nobody teaches: what to actually do, in order, with money that is already in your hand. That is why I'm writing about the six-year-old version.
-Every children's money book teaches saving. All 25 on the ABA Foundation's list — I checked. Piggy banks, jars, patience. But saving is the second thing a child does with money. The first is spending, and a first grader has already done it, in a store, holding a birthday five, working out whether the thing is worth what it costs.
+Every children's money book teaches saving. All 25 on the ABA Foundation's list — I checked. Piggy banks, jars, patience. But saving is the second thing a child does with money; the first is spending, and a first grader has already done it, in a store, holding a birthday five, working out whether the thing is worth what it costs.
 Mine is the spending one, and it follows a single purchase the whole way rather than talking about the idea: a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, gets hit with sales tax, and then lives with what he chose. Idea to post-receipt.
 The design choice: none of the sixteen-plus concepts is announced. Nobody in the book says "budget," which for a book that is largely about budgeting took some doing. The kid does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. There for the kid who wants it, invisible to the kid who doesn't.
 The claim I'd defend hardest is the delayed one: it clicks later, in a real store. Recognition first, then the habit — the book doing its job when nobody is standing there teaching.
-One more thing about how it gets used, because it changes who it is for. Lexile AD 620L — Adult Directed, the industry's own code for a book meant to be read *with* a child. The mother explains every concept on the page, so the adult reading aloud gets handed the script and does not have to be the one who already knows about money. That matters most in the houses where nobody feels qualified to teach it, which is most houses.
+One more thing about how it gets used, because it changes who it is for. Lexile AD 620L — Adult Directed, the industry's own code for a book meant to be read *with* a child. The mother explains every concept on the page, so the adult reading aloud gets handed the script and does not have to be the one who already knows about money. It counts most in the houses where nobody feels qualified to teach it, which is most houses.
 You know better than almost anyone whether a thing lands with the people it's for. Would you look, and tell me if the six-year-old version of your audience would sit still for it?
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -1675,7 +1675,7 @@
         <is>
           <t>Professor Lusardi — you built the instruments the field measures itself with, so you have better grounds than anyone to tell me my premise is wrong. That is the reason I'm writing rather than sending a press release.
 The premise. Financial literacy is measured, sensibly, on saving, compounding and risk. Those are the right things to measure in adults. But each of them is downstream of a decision a child makes years earlier that nobody scores: standing in front of two prices and picking one. Spending is the first financial behavior a person performs. It is taught last, or not at all.
-I could not find the children's book for it, so I wrote one. Clarence Gets a Bargain follows a single purchase the entire way — wanting the thing, earning it, reading the sale ads, comparing two models, choosing the cheaper one deliberately, redeeming a coupon, meeting sales tax, and then living with the choice. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in the glossary, each page-referenced to the scene it came from.
+I could not find the children's book for it, so I wrote one. Clarence Gets a Bargain follows a single purchase the entire way — wanting the thing, earning it, reading the sale ads, comparing two models, choosing the cheaper one deliberately, redeeming a coupon, meeting sales tax, and then living with the choice. Idea to post-receipt; sixteen-plus concepts, none announced. Twenty-one terms in the glossary, each page-referenced to the scene it came from.
 One design feature that may matter for measurement. The book is classified Lexile AD 620L — Adult Directed — so the intervention is not a child reading alone but an adult and a child reading together, with the adult prompted by the text rather than expected to supply the content. If shared reading is doing the work rather than the book, that is testable, and it would be a more interesting finding than anything about my book.
 The question I would actually like answered: does the evidence base start at adolescence the way the books do? If spending competence at seven predicts nothing at twenty-seven, that is worth knowing and you would know it. If it does predict something, then there is a gap in the literature sitting underneath a picture book, and you are far better placed to say so than I am.
 clarencegetsabargain.com/book-facts.html · https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -1745,7 +1745,7 @@
       <c r="K18" s="5" t="inlineStr">
         <is>
           <t>Tracy — a public-private partnership is how a K-5 resource actually reaches classrooms, because elementary rarely gets its own budget line. That is the whole reason I'm writing to you rather than to a district.
-The gap I'm working on: every state financial-literacy mandate lands in high school. Thirty of them now. Meanwhile the behaviors being corrected at sixteen were installed at six, in a store, and the sequence nobody questions is that children should learn saving first. Saving is the second thing a person does with money. The first is spending.
+The gap I'm working on: every state financial-literacy mandate lands in high school. Thirty of them now. Meanwhile the behaviors being corrected at sixteen were installed at six, in a store, and the sequence nobody questions is that children should learn saving first. Saving is the second thing a person does with money; the first is spending.
 I wrote the K-5 piece. One purchase followed from the idea to after the receipt — sale ads at the kitchen table, comparison shopping, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story.
 What matters for a partnership is the rest of it, and it is free. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart. Ungated, no account, prints from a browser. A district adopting it spends nothing.
 One practical spec for adoption: Lexile AD 620L — Adult Directed — one class period read aloud, with the text carrying the explanations so a teacher needs no finance training. The same book goes home and works at a kitchen table with a parent or a grandparent, which is usually where a partnership wants the family-engagement half to come from and rarely finds it.
@@ -1806,7 +1806,7 @@
       <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Nicolle — your twelve-book roundup is the one I point people to, which is slightly awkward, because every title on it teaches earning or saving.
-That's not a criticism of the list. It is an accurate reflection of what exists — the whole category is parked on the earning-and-saving side of the register. I went looking for the spending book and could not find it, so I wrote it.
+The list is accurate; that's simply what exists. The whole category is parked on the earning-and-saving side of the register. I went looking for the spending book and could not find it, so I wrote it.
 The argument in one line: saving is the second thing a child does with money, and the first is spending. A six-year-old has no savings rate and has definitely stood in a store holding a birthday five, deciding whether the thing is worth what it costs.
 Clarence Gets a Bargain follows one purchase from the idea to after the receipt. A boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Sixteen-plus concepts and nobody in the book says "budget." Twenty-one terms in the glossary, each page-referenced to the scene it came from.
 Two asks, and the second one matters more. Worth a look for the next update to the roundup? And separately — you run a company built on kids and money, so if you think spending-before-saving is wrong, I would rather hear it from you than keep saying it at conferences.
@@ -1928,7 +1928,7 @@
       <c r="K21" s="5" t="inlineStr">
         <is>
           <t>Dave — Wisconsin has run a state financial-literacy office longer than most states have had a requirement, so you have seen more of these come and go than almost anyone. I would like a read on one assumption.
-Every mandate in the country lands in high school. Thirty of them now. Money habits are largely set by seven, which puts the policy about a decade behind the behaviour. Underneath that sits the belief that children should learn saving first. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent right there.
+Every mandate in the country lands in high school. Thirty of them now. Money habits are largely set by seven, which puts the policy about a decade behind the behaviour. Underneath that sits the belief that children should learn saving first. Saving is the second thing a person does with money; the first is spending — and a first grader has done it, at a register, with a parent right there.
 I built the K–5 piece rather than an argument about it. A 36-page picture book that follows one complete purchase: the sale ads at the kitchen table, comparison on a shelf, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced — nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from. We are very good at teaching this to people who have already made the mistake.
 The classroom set behind it is free and ungated: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, and a 23-row crosswalk to the 2021 National Standards, Common Core Math and ELA, CEE and FDIC Money Smart. No account, no email capture, prints from a browser. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud that a teacher without a finance background can run cold, and the same book works at a kitchen table.
 The question: in your experience, does elementary material get adopted when it is free and aligned, or does it need a mandate behind it to move at all? I would rather know now than find out slowly.
@@ -1989,7 +1989,7 @@
         <is>
           <t>Hunter — a policy observation, and a question about whether NEFE has a view on it.
 Thirty states now require a personal finance course to graduate. Delaware became the thirtieth last October. Every one of those mandates lands in high school, and the funding and training follow the mandate. Meanwhile the K-5 standards that already exist in most states sit there with almost nothing built against them, because nobody has to report on them.
-The sequence assumption underneath all of it is that children should learn saving first. I think that is backwards. Saving is the second thing a person does with money. The first is spending — and a first grader has done that, at a register, with a parent standing behind her. The behaviors a high school course is trying to correct were installed a decade earlier.
+The sequence assumption underneath all of it is that children should learn saving first. I think that is backwards. Saving is the second thing a person does with money; the first is spending — and a first grader has done that, at a register, with a parent standing behind her. The behaviors a high school course is trying to correct were installed a decade earlier.
 I wrote the elementary piece rather than an argument about it: a 36-page picture book that follows one purchase from the idea to after the receipt, plus a free ungated classroom set crosswalked to the 2021 National Standards, Common Core, CEE and FDIC Money Smart. Sixteen-plus concepts, none announced, twenty-one-term glossary page-referenced into the story.
 One implementation note, since policy has to survive contact with an actual classroom. Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations, no teacher training required, and the same book does the family-engagement job at home with a parent or a grandparent. Elementary programs usually die on training cost. This one has none.
 The question: does NEFE's advocacy work have a position on the elementary band, or is the practical view that high school mandates are where the effort actually pays? I ask because if it's the second, I'd like to know I'm arguing with the consensus rather than filling a gap it agrees exists.
@@ -2050,8 +2050,8 @@
         <is>
           <t>Tom — you got more genuine engagement out of one post about kids and money than anyone else in this category has managed, which tells me you know exactly which part of this parents actually care about. I would like to check my premise against that.
 My premise: the whole field has the sequence backwards. Financial education starts children with saving. Saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, standing in a store holding a birthday five, working out whether the thing is worth what it costs. We teach the second thing first and the first thing never.
-So I wrote and illustrated the spending book. Clarence Gets a Bargain follows one purchase the whole way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax and objects to it, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." The reader works out he has been schooled only at the glossary — twenty-one terms in the back, page-referenced to the scene each came from. A jar is a storage container. It has never once talked a kid out of anything.
-The instruction underneath the whole book is four words long: stop bringing kids to the store as cargo, bring them as staff. Catalogued Lexile AD 620L — Adult Directed — so the parent gets handed the script rather than an assignment, which I suspect is why your posts land: parents want the conversation and do not feel qualified to start it.
+So I wrote and illustrated the spending book. Clarence Gets a Bargain follows one purchase the whole way , a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax and objects to it, and then lives with what he chose. Idea to post-receipt; sixteen-plus concepts and nobody in the book says "budget." The reader works out he has been schooled only at the glossary , twenty-one terms in the back, page-referenced to the scene each came from. A jar is a storage container. It has never once talked a kid out of anything.
+The instruction underneath the whole book is four words long: stop bringing kids to the store as cargo, bring them as staff. Catalogued Lexile AD 620L , Adult Directed , so the parent gets handed the script rather than an assignment, which I suspect is why your posts land: parents want the conversation and do not feel qualified to start it.
 The thing I would actually value: you know what makes a parent stop scrolling on this subject and what makes them scroll past. If "spending before saving" is the wrong hook, I would rather hear it from you than keep testing it slowly.
 Would you look and tell me? https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -2113,7 +2113,7 @@
 Nobody put that in a story. So I did. Clarence Gets a Bargain follows a single purchase the whole way — a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax and regards it as a personal insult, then lives with the thing he chose. Idea to post-receipt.
 Sixteen-plus concepts and none of them announced. Nobody in the book says "budget," which for a book largely about budgeting took some doing. Kids smell a worksheet one page in; they never smell this one, because they are laughing too hard to notice. The reveal is the glossary — twenty-one terms in the back, page-referenced to the scene each came from. It is catalogued AD 620L, Adult Directed, so the parent listening to your show gets handed the script rather than a homework assignment.
 Their books are about earning and saving, which is fine, but there is no game in a piggy bank and kids work that out faster than we do. They smell a worksheet through a backpack.
-The episode I would pitch is not the book. It is the forty-year hole: an entire publishing category taught children to save and skipped the cash register, the only place a child has ever actually handled money.
+The episode worth doing has nothing to do with my book. Pitch the forty-year hole: an entire publishing category taught children to save and skipped the cash register, the only place a child has ever actually handled money.
 Worth twenty minutes of your show? https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
         </is>
@@ -2293,8 +2293,8 @@
           <t>Gretchen — you have spent a career on how financial products get sold to people who don't fully understand them. Here is the entry-level version of that, and nobody covers it.
 A child becomes a consumer the first time money leaves their hand. Six years old, a birthday five, a store. From that moment they are a party to transactions, and the entire financial education apparatus treats them as a saver in training instead. We teach them to hold money. Nobody teaches them what happens when they use it, which is the only thing they were ever going to do with it.
 The scale is small and the mechanics are identical to the ones you write about. A claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the child has no way of knowing that. Not a game of skill — a slot machine wearing a carnival hat, aimed at someone with no price memory and no comparison to make.
-I wrote the picture book for it. One kid, one purchase, followed the whole way: he wants a robot, earns it, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget." The child works out he has been schooled only when he reaches the glossary — twenty-one terms in the back, each page-referenced to where it happened. It is catalogued Lexile AD 620L, where AD stands for Adult Directed — the trade's own code for a book an adult reads with a child rather than hands over.
-The story is not the book. It is that an entire publishing category taught children to save for forty years and skipped the register, which is the only place a child has ever handled money — while the arcade, the app store and the checkout lane did not skip it at all.
+I wrote the picture book for it. One kid, one purchase, followed the whole way: he wants a robot, earns it, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt; sixteen-plus concepts and nobody in the book says the word "budget." The child works out he has been schooled only when he reaches the glossary — twenty-one terms in the back, each page-referenced to where it happened. It is catalogued Lexile AD 620L, where AD stands for Adult Directed — the trade's own code for a book an adult reads with a child rather than hands over.
+The story here has nothing to do with my book. An entire publishing category taught children to save for forty years and skipped the register, which is the only place a child has ever handled money — while the arcade, the app store and the checkout lane did not skip it at all.
 Is there anything there? clarencegetsabargain.com/press-kit.html
 Jonathan</t>
         </is>
@@ -2412,7 +2412,7 @@
         <is>
           <t>Terry — you have been telling adults the truth about money for decades, usually after the damage is done. I wrote the book for about twenty years earlier than you usually get them.
 The argument in one line: mistakes at eleven cost $14, and the same mistake at twenty-seven has a credit card attached. Everything you write about compounding cuts both ways, and the habits doing the compounding were installed in a store, at six, with a parent saying no.
-Which is where the whole category gets the order wrong. Children's money books teach saving — piggy banks, jars, patience, and a strong implication that wanting things is a character flaw. But saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate. She has stood at a register holding money and had to decide.
+Which is where the whole category gets the order wrong. Children's money books teach saving — piggy banks, jars, patience, and a strong implication that wanting things is a character flaw. But saving is the second thing a child does with money; the first is spending. A six-year-old has no savings rate. She has stood at a register holding money and had to decide.
 Clarence Gets a Bargain follows one purchase the entire way: a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax and takes it personally, then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none announced — nobody in the book says "budget." The reader finds out he has been schooled at the glossary, twenty-one terms in the back, each page-referenced to the scene it came from.
 It reads aloud in twenty minutes. Lexile AD 620L — Adult Directed, the industry's own code for read-with rather than read-alone, so a parent who feels unqualified on money still gets handed the script.
 The column question rather than the book question: has anyone made the case that spending competence has to come first? I have not been able to find it, and you would know if it exists.
@@ -2777,7 +2777,7 @@
           <t>Julie — a segment idea, and it is short enough to survive a live hit.
 Every children's money book teaches saving. Piggy banks, lemonade stands, jars. But saving is the second thing a child does with money — the first is spending, and a six-year-old has already done it, in a store, holding a birthday five, deciding whether the thing is worth what it costs.
 The category skipped that for forty years. The arcade did not. A claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the kid has no price memory to defend himself with. Once a kid has seen the $9.99, the claw loses its grip.
-So I wrote the spending book. Clarence Gets a Bargain, ages 6–10: a boy earns a robot with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and then lives with the thing he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Twenty-one terms in a glossary at the back, each page-referenced to where it happened. Catalogued AD 620L — Adult Directed — twenty minutes out loud, interrupted the whole way. The category's own defence is that money is a serious subject. It is. So is getting fleeced in an aisle at the age of seven.
+So I wrote the spending book. Clarence Gets a Bargain, ages 6–10: a boy earns a robot with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and then lives with the thing he picked. Idea to post-receipt; sixteen-plus concepts, none of them announced. Twenty-one terms in a glossary at the back, each page-referenced to where it happened. Catalogued AD 620L — Adult Directed — twenty minutes out loud, interrupted the whole way. The category's own defence is that money is a serious subject. It is. So is getting fleeced in an aisle at the age of seven.
 I am an attorney and a mixed-media artist, and I have twice walked out of the same Nordstrom Rack having paid one cent — once for a $293 pair of shoes, once for a $69.50 shirt. I kept both tags. It makes for a good visual if you ever want one on screen.
 Is there a hit in "the money skill nobody teaches kids"? clarencegetsabargain.com/press-kit.html
 Jonathan</t>
@@ -3017,7 +3017,7 @@
         <is>
           <t>Ben — a story pitch about a gap in the coverage rather than a book pitch, though the book is how I found it.
 Thirty states now guarantee a personal finance course. Every one of those mandates lands in high school. Money habits are largely set by seven, so the policy arrives roughly ten years after the cement dries — a fifteen-year-old handed a course for a habit he formed at six, and everyone acting surprised, and the funding, the training and the reporting all follow the mandate rather than the evidence.
-Underneath that sits an assumption nobody argues with: that children should learn saving first. I think it is backwards. Saving is the second thing a person does with money. The first is spending, and a first grader has done that, at a register, with a parent standing behind her. The behaviors a high school course tries to correct were installed a decade earlier by an arcade, a toy aisle and a checkout lane, none of which waited for a curriculum.
+Underneath that sits an assumption nobody argues with: that children should learn saving first. I think it is backwards. Saving is the second thing a person does with money; the first is spending, and a first grader has done that, at a register, with a parent standing behind her. The behaviors a high school course tries to correct were installed a decade earlier by an arcade, a toy aisle and a checkout lane, none of which waited for a curriculum.
 I wrote the elementary piece rather than an op-ed about it. A 36-page picture book following one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, and living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Free ungated classroom set behind it, crosswalked to five frameworks. Catalogued Lexile AD 620L — Adult Directed, so it is a read-with, and the caregiver conversation happens inside the reading.
 Meanwhile the arcade never waited for a standard: $25 into a glass box for a basketball Walmart sells for $9.99, and the kid has no price memory to argue with.
 The story I would pitch your desk: the whole country legislated financial literacy into ninth grade, and the elementary standards that already exist in most states sit there with nothing built against them, because nobody has to report on them.
@@ -3078,9 +3078,9 @@
         <is>
           <t>Stacy — you write about what happens to ordinary people inside financial systems. There is a version of that beat with no coverage at all, and it starts at about age six.
 A child becomes a consumer the first time they hand money to a cashier. Not at eighteen, not at a first paycheck — at six, with a birthday five. From that moment they are party to a transaction and they have rights nobody mentions: the receipt is proof, the price on the shelf has to match the price at the register, a broken thing can go back. Consumer education is the missing wing of children's financial literacy. We teach them to save and never tell them they are already the buyer.
-That is why I wrote the book. Clarence Gets a Bargain follows one purchase the entire way — a boy wants a robot, earns it, reads the sale inserts at the kitchen table, compares two on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced, and a twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
-The detail people ask me about: the mother photographs the receipt the second she sits down in the car. Every time. It takes four seconds and it is what makes a return, an exchange or a warranty claim winnable. Almost nobody teaches a child that, which is why the book is catalogued AD 620L — Adult Directed — and gets read with an adult rather than handed to a kid alone.
-I am an attorney, and on vacation that mostly means the souvenirs get cross-examined. The hermit crab: who feeds it over the holidays, and in two weeks when it dies — and buddy, it will — is it worth the tears? My kids find this insufferable. It is also the entire skill.
+That is why I wrote the book. Clarence Gets a Bargain follows one purchase the entire way — a boy wants a robot, earns it, reads the sale inserts at the kitchen table, compares two on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt; sixteen-plus concepts, none announced, and a twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
+The detail people ask me about: the mother photographs the receipt the second she sits down in the car. Every time. It takes four seconds and it is what makes a return, an exchange or a warranty claim winnable. Almost nobody teaches a child that, which is why the book is catalogued AD 620L , Adult Directed , and gets read with an adult rather than handed to a kid alone.
+I am an attorney, and on vacation that mostly means the souvenirs get cross-examined. The hermit crab: who feeds it over the holidays, and in two weeks when it dies , and buddy, it will , is it worth the tears? My kids find this insufferable. It is also the entire skill.
 The honest version of the beat problem: the full picture crosses agencies. Warranties and returns sit with the FTC, product safety with the CPSC. Nobody owns "children as consumers," which may be exactly why nobody covers it.
 Is there a story in that? clarencegetsabargain.com/press-kit.html
 Jonathan</t>
@@ -3262,7 +3262,7 @@
         <is>
           <t>Dr. Taylor — I am a Maryland attorney and children's book author writing about the elementary end of financial literacy, which is the end nobody funds.
 Maryland's requirement, like every state's, lands in high school. The elementary standards sit underneath it with almost nothing built against them, for the least respectable reason available: nobody has to report on that band. Meanwhile the habits a high school course is trying to correct were installed at six, in a store, with a parent saying no and no reasoning attached.
-The field's answer is to teach children saving first. Saving is the second thing a person does with money. The first is spending, and a first grader has done it — at a register, with a parent standing right there.
+The field's answer is to teach children saving first. Saving is the second thing a person does with money; the first is spending, and a first grader has done it — at a register, with a parent standing right there.
 I wrote the K–5 piece. A 36-page picture book following one purchase from the idea through the receipt: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken on purpose, a coupon at the register, sales tax, and living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced back into the story.
 What matters for a district is that all of it is free. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, and a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart. No account, no email capture, no purchase order. It prints from a browser, so adoption costs a building nothing. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud a teacher can run with no finance background.
 I am local and would happily walk a curriculum team through it, or a single school if that is the right size to start.
@@ -3326,7 +3326,7 @@
           <t>Beth — a research question rather than a pitch, and the book is only the reason I ran into it.
 Financial capability gets measured, sensibly, on saving, compounding and risk. Those are the right things to measure in adults. But each of them sits downstream of a decision made years earlier that nobody scores: a child standing in front of two prices, picking one. Spending is the first financial behavior a person performs, and it is taught last or not at all.
 The environment is not waiting for the curriculum. Children are transacting constantly — arcades, app stores, checkout lanes — and none of it gets counted as financial education, though it plainly is.
-I wrote the elementary piece. A 36-page picture book following one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, and living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced back into the story. Free ungated classroom set behind it, crosswalked to five frameworks. The polite version is that the elementary band is understudied. The blunt version is that nobody has to report on it, so nobody looks.
+I wrote the elementary piece. A 36-page picture book following one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, and living with the choice. Sixteen-plus concepts, none announced; a twenty-one-term glossary page-referenced back into the story. Free ungated classroom set behind it, crosswalked to five frameworks. The polite version is that the elementary band is understudied. The blunt version is that nobody has to report on it, so nobody looks.
 Design note that may matter to your work: the book is catalogued Lexile AD 620L — Adult Directed. The intervention is an adult and a child reading together, not a child reading alone, which makes it closer to a shared-reading study than a curriculum study.
 The question: does the evidence base start at adolescence the way the books do? If spending competence at seven predicts nothing at twenty-seven, that is worth knowing and I would rather hear it than keep arguing.
 clarencegetsabargain.com/book-facts.html
@@ -3447,7 +3447,7 @@
         <is>
           <t>Vince — you have thousands of instructors in the field, which means you know better than almost anyone what they walk into a room without. I built the elementary thing they do not have.
 Most financial education material aimed at children starts with saving. Saving is the second thing a child does with money. The first is spending — and a first grader has done it, at a register, with a parent behind her. An instructor standing in front of a second-grade class has almost nothing to hand them about that moment.
-Clarence Gets a Bargain is a 36-page picture book that follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one deliberately, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget."
+Clarence Gets a Bargain is a 36-page picture book that follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one deliberately, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt; sixteen-plus concepts and nobody in the book says the word "budget."
 Why it works for an instructor rather than a teacher: it is catalogued Lexile AD 620L — Adult Directed — it runs about twenty minutes out loud, and the mother explains every concept inside the text. Somebody can read it cold to a class and field questions straight off the page. Nothing to memorise, no training call beforehand. Behind it sits a free ungated set — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, and a browser-based pretend register with a markdown, a coupon and sales tax.
 The twenty-one-term glossary in the back is page-referenced to the story, so an instructor can answer a vocabulary question by turning to the scene rather than reciting a definition. The field keeps building the ninth-grade course and keeps skipping the second-grade one, which is a strange place to draw a line.
 Does your instructor network want elementary material, or is the demand really all adult and teen? Everything is free either way.
@@ -3508,7 +3508,7 @@
         <is>
           <t>Billy — a question about where NEFE draws the line on grade band, asked by someone who has just spent a year building for the band nobody funds.
 Thirty states now require personal finance to graduate. The mandates land in high school, and the funding, the training and the reporting follow the mandate — which is a tidy way of arriving about nine years late and calling it early intervention. Meanwhile the K–5 standards that already exist in most states sit there with almost nothing built against them, because nobody has to report on them.
-The assumption underneath is that children should learn saving first. I think it is backwards, and I would rather be told so by NEFE than keep saying it at conferences. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent standing behind her. The behaviors a high school course is trying to correct were installed a decade earlier.
+The assumption underneath is that children should learn saving first. I think it is backwards, and I would rather be told so by NEFE than keep saying it at conferences. Saving is the second thing a person does with money; the first is spending — and a first grader has done it, at a register, with a parent standing behind her. The behaviors a high school course is trying to correct were installed a decade earlier.
 I wrote the elementary piece rather than an argument about it: a 36-page picture book that follows one purchase from the idea to after the receipt, plus a free ungated classroom set crosswalked to the 2021 National Standards, Common Core, CEE and FDIC Money Smart. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Catalogued Lexile AD 620L — Adult Directed — so the intervention is a shared read rather than solo reading, which also makes it easier to study than a curriculum. There is a whole industry aimed at teenagers who already have the habit, and almost nobody upstream of it.
 The line I would put on a poster if I could: mistakes at eleven cost $14, and the same mistake at twenty-seven has a credit card attached.
 The question: does NEFE's research or advocacy work have a position on the elementary band, or is the practical view that high school is where the effort pays? If it is the second, I would like to know I am arguing with a considered consensus rather than filling a gap it agrees exists.
@@ -3632,9 +3632,9 @@
         <is>
           <t>Prince — you took investing, which is the hardest concept in this category to make readable for children, and made it a series a kid comes back to. I went the opposite direction on the same shelf and I would like your read on it.
 Wesley learns to invest. Clarence learns to spend — and I mean the mechanics of it rather than the idea. Every other book in the category teaches saving, which is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. Nobody had written that one, so I did.
-Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Nobody says the word "budget."
-The craft problem I would most like another author's view on: the reader is not supposed to know he has been taught anything until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. Getting that balance right, so it stays a story, was the whole job, and it is the thing most likely to be off by a hair. The rest of the shelf is piggy banks with plots. Good ones, some of them — but none of them has ever been to a register.
-I did the illustrations too, which means my opinion of them is worth nothing. It is written for the adult voice in the room — catalogued AD 620L, Adult Directed — with the mother carrying every explanation.
+Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt; sixteen-plus concepts, none of them announced. Nobody says the word "budget."
+The craft problem I would most like another author's view on: the reader is not supposed to know he has been taught anything until he reaches the glossary , twenty-one terms in the back, each page-referenced to the scene it came from. Getting that balance right, so it stays a story, was the whole job, and it is the thing most likely to be off by a hair. The rest of the shelf is piggy banks with plots. Good ones, some of them , but none of them has ever been to a register.
+I did the illustrations too, which means my opinion of them is worth nothing. It is written for the adult voice in the room , catalogued AD 620L, Adult Directed , with the mother carrying every explanation.
 Trade? Send me a Wesley and I will read it properly rather than politely.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -3692,7 +3692,7 @@
       <c r="K50" s="5" t="inlineStr">
         <is>
           <t>Kate — a pitch about a gap rather than a book, though I wrote the book because of the gap.
-Everything in kids' financial literacy points at a horizon no child can see: compound interest, credit scores, retirement. All real, all decades out, and all completely useless to somebody who is eight. Meanwhile the kid is eight, holding $20 of birthday money, standing in a store that spent millions working out how to get it. We are preparing children for 65 and sending them to the register unarmed today.
+Everything in kids' financial literacy points at a horizon no child can see: compound interest, credit scores, retirement. All real; all decades out, and all completely useless to somebody who is eight. Meanwhile the kid is eight, holding $20 of birthday money, standing in a store that spent millions working out how to get it. We are preparing children for 65 and sending them to the register unarmed today.
 So flip the order. Saving is the second thing a child does with money. The first is spending, and it is the one nobody puts in a story.
 Clarence Gets a Bargain does. One kid, one purchase, followed the whole distance — he wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget." The reader works out he has been schooled at the glossary — twenty-one terms in the back, each one page-referenced to the scene it came from. Catalogued AD 620L — Adult Directed — so a parent who does not feel qualified on money still gets handed the script and can take the credit.
 The boardwalk is a pop quiz your kid has not studied for, and it runs all summer with real money.
@@ -5776,9 +5776,9 @@
         <is>
           <t>Roda — you built a 30-Day Smart Spending Challenge. Not a saving challenge. Spending. As far as I can tell that makes two of us in this entire category who think the sequence is backwards.
 Here is my version of the argument, and I'd like to know whether it matches how you arrived at yours. Every children's money book teaches saving — I read all 25 on the ABA Foundation's list to be sure. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. We teach the second thing first and the first thing never.
-Clarence Gets a Bargain is the picture-book version. It follows a single purchase the whole distance — a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced; nobody says "budget." Twenty-one terms in a glossary at the end, each page-referenced to where it happened — which is the only point at which a kid works out he's been schooled.
-One story takes a kid from "I want it" to "Is it worth it?" — which I suspect is the same door your Challenge walks them through, thirty days at a time. Yours is a habit; mine is one transaction read in twenty minutes. Those look complementary to me rather than competing — the book could be the on-ramp to a challenge, or the thing a parent reads on day one.
-One thing your Challenge and the book share: neither one works with a kid alone in a room. It is Lexile AD 620L — Adult Directed, the trade's code for read-with rather than read-alone — and the mother explains every concept on the page, so whoever is reading gets handed the script. Parent, teacher or grandparent, the reading stops every few pages because the kid asks something.
+Clarence Gets a Bargain is the picture-book version. It follows a single purchase the whole distance , a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced; nobody says "budget." Twenty-one terms in a glossary at the end, each page-referenced to where it happened , which is the only point at which a kid works out he's been schooled.
+One story takes a kid from "I want it" to "Is it worth it?" , which I suspect is the same door your Challenge walks them through, thirty days at a time. Yours is a habit; mine is one transaction read in twenty minutes. Those look complementary to me rather than competing , the book could be the on-ramp to a challenge, or the thing a parent reads on day one.
+One thing your Challenge and the book share: neither one works with a kid alone in a room. It is Lexile AD 620L , Adult Directed, the trade's code for read-with rather than read-alone , and the mother explains every concept on the page, so whoever is reading gets handed the script. Parent, teacher or grandparent, the reading stops every few pages because the kid asks something.
 Worth a conversation? I'd rather compare notes with the one other person who put spending first than pitch anybody.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -7048,7 +7048,7 @@
       <c r="K137" s="5" t="inlineStr">
         <is>
           <t>Daniel — you built 360 Parenting around the whole child rather than one slice of them, so this is a slice you may be missing, and I say that as someone who only noticed it because I went looking for a book and could not find one.
-Money education for kids begins with saving. Every time. But saving is the second thing a child does with money. The first is spending — and a six-year-old has done that, repeatedly, usually in a store, usually while a parent quietly loses the will to live.
+Money education for kids begins with saving. Every time. But saving is the second thing a child does with money; the first is spending — and a six-year-old has done that, repeatedly, usually in a store, usually while a parent loses the will to live in the background.
 So I wrote the spending book. One purchase, followed the entire way: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, hands the cashier an extra ten-percent-off coupon like a tiny attorney presenting Exhibit A, discovers sales tax the way we all did — badly, and in public — and then has to live with the thing he chose. From the idea to after the receipt.
 Here is why it might fit a parenting audience rather than a classroom one. The concepts are smuggled. Sixteen-plus of them, none announced, nobody saying the word "budget." It reads as a story about a kid and a robot, and the parent doing the read-aloud gets handed the money conversation without having to deliver a lesson. And the kid does not know he's been schooled until he gets to the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. A parent can turn straight back to the exact page.
 The argument I'd bring to a podcast is the delayed one. It clicks later, in a real store. Months out, a kid says "there's a coupon in my pocket, just like Clarence" or "the sticker price isn't what you pay, there's tax" — recognition first, then the habit, and the parent isn't even in the room when it happens.
@@ -7108,8 +7108,8 @@
           <t>ML — you built a series a child comes back to, which is harder than writing one good book, and it's the reason I'm writing to a peer rather than a gatekeeper.
 Mine is a money book, which I appreciate is the least promising sentence in children's publishing. So here is the part that makes it not that.
 Every book in this category teaches saving. Saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it — in a store, holding money, deciding whether the thing is worth what it costs. So mine follows one purchase from the idea to after the receipt: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose.
-The craft problem I'd most like another author's view on: I smuggled sixteen-plus concepts in without announcing any of them. Nobody says "budget." The glossary in the back — twenty-one terms, each page-referenced to the scene it came from — is the only place the book admits it was teaching. Getting that balance right, so it stays a story, was the whole job.
-The other half of the craft problem: it is written for an adult voice. Lexile AD 620L — Adult Directed — with the mother carrying every explanation, so whoever reads aloud gets handed the script. A series lives or dies on whether the grown-up still enjoys the fourth reading. You would know inside a page whether mine does.
+The craft problem I'd most like another author's view on: I smuggled sixteen-plus concepts in without announcing any of them. Nobody says "budget." The glossary in the back , twenty-one terms, each page-referenced to the scene it came from , is the only place the book admits it was teaching. Getting that balance right, so it stays a story, was the whole job.
+The other half of the craft problem: it is written for an adult voice. Lexile AD 620L , Adult Directed , with the mother carrying every explanation, so whoever reads aloud gets handed the script. A series lives or dies on whether the grown-up still enjoys the fourth reading. You would know inside a page whether mine does.
 Would you read it and tell me where it stops being a story? I'll trade — send me a Noah and I'll read it properly.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -8305,7 +8305,7 @@
           <t>Linda — you teach financial parenting, which means you spend your working life on the exact handoff I wrote a book about: the moment a parent has to explain money to a child who is standing right there wanting something.
 My argument, and you are better placed than almost anyone to tell me it's wrong. Financial education for children starts with saving, and it has the sequence backwards. A seven-year-old has no savings rate and no income. What she has done is stand at a register holding money and decide. Spending is the first money behavior a person performs. We teach it last, or not at all.
 Clarence Gets a Bargain is the spending book. It follows one purchase the whole distance — wanting the thing, earning it through chores and grades, reading the sale inserts at the kitchen table with a parent, comparing two models on a shelf, choosing the cheaper one on purpose, handing over a coupon, meeting sales tax, and then living with what he bought. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; not one covers the whole arc.
-The design choice that matters for your work: nothing is announced. Sixteen-plus concepts and nobody in the book says "budget." The kid does the math because the robot depends on it. The parent reading aloud is handed the conversation without having to give a lecture, which I gather is most of what you coach people out of. The child does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. The reveal is the last thing that happens, not the first.
+The design choice bearing on your work: nothing is announced. Sixteen-plus concepts and nobody in the book says "budget." The kid does the math because the robot depends on it. The parent reading aloud is handed the conversation without having to give a lecture, which I gather is most of what you coach people out of. The child does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. The reveal is the last thing that happens, not the first.
 The shape of it, if it helps: one funny story about a boy and his dream robot takes a kid from "I want it" to "Is it worth it?" She opens it an impulsive little spender and closes it an aware, educated consumer.
 The part I'd most want your professional read on is the delayed return. The book is not really working in the twenty minutes it takes to read. It works in month eighteen, in an actual store, when the kid hits a real money moment and the book fires back — "wait, is the newer one really better? Clarence checked." Recognition first, then the habit. That is the book doing its job when the parent isn't even in the room.
 And the handoff you teach is the mechanism itself. The book is Lexile AD 620L — Adult Directed, the trade's own label for a book meant to be read *with* a child, not left in a bedroom — and Mom explains everything on the page, so the adult reading aloud is handed the script rather than asked to know the material. A parent who feels unqualified to teach money can still run it. Classroom, kitchen table, grandparent's couch: the reading stops every few pages because somebody asks.
@@ -8357,9 +8357,9 @@
       </c>
       <c r="K170" s="5" t="inlineStr">
         <is>
-          <t>Stacey — you design and produce books for other authors, which makes you one of very few people I could ask this of honestly: does mine look like it was made by someone who knew what he was doing?
+          <t>Stacey — you design and produce books for other authors, which makes you one of very few people I can ask this without getting a polite answer: does mine look like it was made by someone who knew what he was doing?
 I wrote and illustrated a 36-page hardbound picture book, full colour, 11 by 8.5. I am a mixed-media artist and a real estate attorney, which is a combination that gets me neither the benefit of the doubt on the art nor on the commercial sense. I did the interior, the cover, the whole object.
-The content, briefly, because you'll want to know whether it's worth the production critique. Every children's money book teaches saving. Mine teaches spending, on the argument that saving is the second thing a child does with money and spending is the first. It follows one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, then living with what was bought. Sixteen-plus concepts, none announced. Twenty-one terms in a glossary in the back, each page-referenced to the scene it came from.
+The content, briefly, because you'll want to know whether it's worth the production critique. Every children's money book teaches saving. Mine teaches spending, on the argument that saving is the second thing a child does with money and spending is the first. It follows one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, then living with what was bought. Sixteen-plus concepts, none announced; twenty-one terms in a glossary in the back, each page-referenced to the scene it came from.
 What I'd actually value from you is the unglamorous part: trim size, the cover, whether the interior typography holds at read-aloud distance, whether the object reads as professionally published or as a very determined amateur. I would rather hear it from you now than infer it from a bookseller later.
 And the read-aloud is why I asked about typography at distance rather than at arm's length. It is Lexile AD 620L — Adult Directed — so the object gets held up by an adult with a kid beside them, or a class in front of them, looking at it from three or four feet. If the interior does not hold at that distance the whole use case fails, and that is a production question rather than a content one.
 Paid engagement or a favour returned, whichever you prefer. https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -9673,7 +9673,7 @@
         <is>
           <t>Professor Urban — you produced the evidence base that mandates actually work, which is why I want to ask about the grade band your evidence does not reach.
 Every mandate you have evaluated lands in high school. Thirty states now. The effects are real and I am not arguing with them. My question is about what is happening a decade earlier, because money habits are largely set by seven and the policy arrives roughly ten years after the cement dries.
-Underneath the whole field sits a sequencing assumption nobody tests: that children should learn saving first. I think it is backwards. Saving is the second thing a person does with money. The first is spending — standing in front of two prices and picking one. A first grader has done that. She has no savings rate at all.
+Underneath the whole field sits a sequencing assumption nobody tests: that children should learn saving first. I think it is backwards. Saving is the second thing a person does with money; the first is spending — standing in front of two prices and picking one. A first grader has done that. She has no savings rate at all.
 I could not find the children's book for it, so I wrote one. Clarence Gets a Bargain follows a single purchase the entire way: earning the reward, reading the sale ads, comparing two models on a shelf, choosing the cheaper one deliberately, redeeming a coupon, meeting sales tax, and then living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Elementary is not so much contested ground as unvisited ground.
 One design feature that may matter for measurement: the book is catalogued Lexile AD 620L — Adult Directed — so the intervention is not a child reading alone but an adult and a child reading together, with the adult prompted by the text. If shared reading is doing the work rather than the book, that is testable, and it would be a more interesting finding than anything about my book.
 The real question: does anything in the literature speak to elementary spending competence, or is that band simply unstudied? Either answer is useful to me.
@@ -17311,7 +17311,7 @@
         <is>
           <t>Jennifer — a funding-shaped question rather than an ask, and the resource itself is already free.
 I wrote and illustrated a K–5 financial-literacy picture book and built the entire classroom program behind it — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a standards crosswalk across five frameworks. All of it is ungated: no account, no email capture, no purchase order, prints from a browser. The only thing that ever costs anything is the physical books, and 25 copies run $499.75.
-The content premise: every children's money book teaches saving, and saving is the second thing a child does with money. The first is spending — a first grader has stood at a register and chosen. The book follows one complete purchase from the idea through the receipt, with sixteen-plus concepts hidden in the plot and a twenty-one-term glossary page-referenced back into the story. If a money lesson looks like school, it gets filed under school and read at school speed.
+The content premise: every children's money book teaches saving, and saving is the second thing a child does with money; the first is spending — a first grader has stood at a register and chosen. The book follows one complete purchase from the idea through the receipt, with sixteen-plus concepts hidden in the plot and a twenty-one-term glossary page-referenced back into the story. If a money lesson looks like school, it gets filed under school and read at school speed.
 Why I am writing to development rather than to a classroom: this is unusually easy to fund. A bank or credit union sponsoring a classroom set gets its name on every book that goes home to a family in its assessment area, the curriculum costs the sponsor nothing because it is already free, and I have a CRA-ready memo written in examiner-friendly language. A funder can point at 25 books, one classroom, and a pre/post instrument. And because it is catalogued AD 620L — Adult Directed — it doubles as family engagement: the same book works at a kitchen table with a parent or a grandparent reading.
 Is a sponsored classroom set something HCZ's funders would recognise, or does everything need to attach to an existing program line?
 clarencegetsabargain.com/resources/grant-in-a-box.html
@@ -17371,8 +17371,8 @@
         <is>
           <t>Flora — JA runs volunteers into elementary classrooms better than any organisation in the country, so this is a materials question rather than a pitch.
 JA's elementary programs are strong on earning, jobs and community. What is thin across the whole field, JA included, is spending — the second thing everybody teaches and the first thing a child actually does. A first grader has no savings rate and no job. What she has done is stand at a register holding money and choose.
-Clarence Gets a Bargain is a 36-page picture book that puts the entire transaction on the page: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from. Every year the field builds another high-school course for a habit that set in first grade, and every year it works about as well as you would expect.
-The part that matters for a volunteer model: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, with every concept explained inside the text by the mother. A volunteer who has never taught anything can read it cold and answer questions off the page. Nothing to memorise and no prep call. Behind it, free and ungated: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable price tags and clearance stickers for a classroom store, and a browser-based pretend register with a markdown, a coupon and sales tax.
+Clarence Gets a Bargain is a 36-page picture book that puts the entire transaction on the page: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced; a twenty-one-term glossary in the back, each entry page-referenced to the scene it came from. Every year the field builds another high-school course for a habit that set in first grade, and every year it works about as well as you would expect.
+The part a volunteer model turns on: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, with every concept explained inside the text by the mother. A volunteer who has never taught anything can read it cold and answer questions off the page. Nothing to memorise and no prep call. Behind it, free and ungated: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable price tags and clearance stickers for a classroom store, and a browser-based pretend register with a markdown, a coupon and sales tax.
 Alaska has its own complications on distance and travel, and virtual read-alouds work for this.
 Does a read-aloud fit how JA Alaska builds a volunteer session, or does everything have to run through national curriculum?
 clarencegetsabargain.com/educator-toolkit.html
@@ -17433,8 +17433,8 @@
           <t>Elizabeth — a scope question rather than a pitch.
 Federal attention to financial education, like every state mandate, concentrates on high school. Thirty states now require a course to graduate. The elementary standards that exist in most states sit underneath that with very little built against them, largely because nothing requires reporting at that band.
 The assumption underneath is that children begin with saving. Saving is the second thing a person does with money. The first is spending — a first grader has handled money at a register and made a decision there with no framework at all.
-I built a free, ungated K–5 resource for that: a 36-page picture book that follows one complete purchase from the idea through the receipt — sale ads, comparison shopping, a markdown, a coupon, sales tax — and a classroom set behind it. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a browser-based pretend register, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education alongside Common Core Math and ELA, CEE and FDIC Money Smart, cited at the Grade 4 benchmark level rather than claimed generally. Sixteen-plus concepts appear in the story without being announced, and a twenty-one-term glossary in the back matter page-references each one to the scene where it occurs.
-No concept is announced in the text; the twenty-one-term glossary in the back matter carries the definitions, each page-referenced to where the term occurs. No account, no email capture, no purchase order. It prints from a browser. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud requiring no instructor training.
+I built a free, ungated K–5 resource for that: a 36-page picture book that follows one complete purchase from the idea through the receipt , sale ads, comparison shopping, a markdown, a coupon, sales tax , and a classroom set behind it. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a browser-based pretend register, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education alongside Common Core Math and ELA, CEE and FDIC Money Smart, cited at the Grade 4 benchmark level rather than claimed generally. Sixteen-plus concepts appear in the story without being announced, and a twenty-one-term glossary in the back matter page-references each one to the scene where it occurs.
+No concept is announced in the text; the twenty-one-term glossary in the back matter carries the definitions, each page-referenced to where the term occurs. No account, no email capture, no purchase order. It prints from a browser. Catalogued Lexile AD 620L , Adult Directed , a one-period read-aloud requiring no instructor training.
 The question: does any Department program or clearinghouse take elementary financial-education material, or is the practical route through the states? A steer on who would know is as useful to me as an answer.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan Bach
@@ -17494,7 +17494,7 @@
         <is>
           <t>Gene — Troutwood is built on showing people the long arc of a decision, which is why I am writing about the very first decision on that arc.
 Everything in financial planning compounds, including the mistakes, and the compounding starts long before anyone opens an account. Mistakes at eleven cost $14. The same mistake at twenty-seven has a credit card attached. The habit doing the compounding was installed at six, in a store, with a parent saying no and no reasoning attached to the no.
-Financial education answers that by teaching children saving. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with no framework at all.
+Financial education answers that by teaching children saving. Saving is the second thing a person does with money; the first is spending — and a first grader has done it, at a register, with no framework at all.
 Clarence Gets a Bargain is the picture book for that. One purchase, followed the whole way: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed — so it is a shared read and the parent gets the script rather than a homework assignment. A jar is a storage container. It has never once talked a kid out of anything.
 The claim I would defend hardest is the delayed one, and it is the same claim Troutwood makes about projections: the value is not in the twenty minutes. It is in month eighteen, in a real store, when the kid hits a money moment and the book fires back. Recognition first, then the habit.
 Does the elementary end fit anything Troutwood does, or is that below the floor?
@@ -22046,9 +22046,9 @@
       <c r="K523" s="5" t="inlineStr">
         <is>
           <t>Ed — a narrow question about evidence standards, asked before I go further with something.
-I have built a free K–5 financial-education resource — a 36-page picture book plus a complete classroom set — and crosswalked it to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE and FDIC Money Smart, at the Grade 4 benchmark level. Everything is ungated: no account, no email capture, no purchase order, and it prints from a browser.
+I have built a free K–5 financial-education resource , a 36-page picture book plus a complete classroom set , and crosswalked it to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE and FDIC Money Smart, at the Grade 4 benchmark level. Everything is ungated: no account, no email capture, no purchase order, and it prints from a browser.
 The content premise is that the field has the sequence backwards. Financial education starts children with saving; saving is the second thing a person does with money. The first is spending, and a first grader has already done it at a register. The book follows one complete purchase from the idea through the receipt — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with what was bought. No concept is announced in the text; a twenty-one-term glossary in the back matter carries the definitions, each page-referenced to where the term occurs.
-One structural detail relevant to evaluation: the book is catalogued Lexile AD 620L — Adult Directed — so it is delivered as a shared read between an adult and a child rather than independent reading. That makes it closer to a shared-reading intervention than a curriculum, which may change what kind of evidence would be appropriate.
+One structural detail relevant to evaluation: the book is catalogued Lexile AD 620L , Adult Directed , so it is delivered as a shared read between an adult and a child rather than independent reading. That makes it closer to a shared-reading intervention than a curriculum, which may change what kind of evidence would be appropriate.
 The question: what would a resource like this need in order to be taken seriously on evidence — a pre/post instrument administered at scale, a quasi-experimental design, something else? I would rather build the right study once than assemble the wrong one. And if the honest answer is that no federal pathway exists for elementary material of this kind, that is worth knowing too.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan Bach
@@ -22108,7 +22108,7 @@
         <is>
           <t>Jeff — a question about scope, from someone who has read the SHED closely enough to know what it does and does not ask.
 The survey measures financial outcomes in adults — emergency savings, credit access, unexpected expenses. Those outcomes have long histories. What I have not been able to find, in the SHED or elsewhere, is any measure of when spending competence forms: the ability to stand in front of two prices and choose deliberately rather than by impulse or brand.
-That matters because financial education for children is built almost entirely around saving, and saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has handled money at a register.
+It bears on the whole design, because financial education for children is built almost entirely around saving, and saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has handled money at a register.
 I wrote the elementary resource rather than a paper about it. A 36-page picture book that follows one complete purchase — sale ads, comparison shopping, a markdown, a coupon, sales tax, and living with what was bought — plus a free ungated classroom set crosswalked to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE, and FDIC Money Smart. Sixteen-plus concepts, none announced in the text. A twenty-one-term glossary page-referenced into the story.
 For the record on format: Lexile AD 620L, Adult Directed — an adult reads it with the child rather than handing it over.
 The question is narrow. Is there any Federal Reserve work, published or internal, on childhood price competence and later financial outcomes? If it does not exist, that is an answer too, and it tells me whether I am arguing with a consensus or filling a hole.
@@ -22170,7 +22170,7 @@
         <is>
           <t>Annie — you built a product for the exact age band everyone else in this category skips, so you already believe the thing I have been arguing. I want to compare notes rather than pitch you.
 My First Nest Egg puts save, spend, give and invest in front of a young child in physical form. My argument is about which of those a child actually performs first. It is spending — a six-year-old has stood in a store holding money and chosen, years before she has anything to save or invest. The category teaches saving first anyway, and I could not find the book that teaches the other one.
-So I wrote and illustrated it. Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed — read with a grown-up rather than handed over. There is also a free browser-based pretend register behind it that runs a markdown, a coupon and sales tax, which is the closest thing I have to your physical product. Nobody has ever formed a money habit by looking at a jar.
+So I wrote and illustrated it. Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced; a twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed — read with a grown-up rather than handed over. There is also a free browser-based pretend register behind it that runs a markdown, a coupon and sales tax, which is the closest thing I have to your physical product. Nobody has ever formed a money habit by looking at a jar.
 Those look complementary rather than competing to me: yours gives a kid the categories in their hands, mine walks them through the mechanics of one transaction in twenty minutes.
 Worth a conversation about whether they belong near each other? And separately — if you think spending-before-saving is wrong, you are one of very few people whose disagreement would actually change my mind.
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -25876,9 +25876,9 @@
       </c>
       <c r="K622" s="5" t="inlineStr">
         <is>
-          <t>Sandy — FCCLA members are a decade older than my readers, so this is not a curriculum pitch. It is a service-project one, and I think it's a good one.
+          <t>Sandy — FCCLA members are a decade older than my readers, so take this as a service-project idea rather than a curriculum pitch. I think it's a good one.
 Your chapters run community service. A high schooler reading a money book to a second-grade class is about the cleanest version of that I can think of — it needs no budget, no training, and one afternoon.
-The book is Clarence Gets a Bargain, 36 pages, ages 6-10. It follows one purchase the whole way, which is the thing that makes it work as a read-aloud rather than a lecture: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in it says "budget" — the twenty-one-term glossary in the back is page-referenced to the story, so the reader can field questions without preparing.
+The book is Clarence Gets a Bargain, 36 pages, ages 6-10. It follows one purchase the whole way, which is the thing that makes it work as a read-aloud rather than a lecture: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt; sixteen-plus concepts and nobody in it says "budget" — the twenty-one-term glossary in the back is page-referenced to the story, so the reader can field questions without preparing.
 The read-aloud is the entire project, so the spec matters. Lexile AD 620L — the AD is Adult Directed, the trade's own code for a book built to be read *with* a child rather than handed to one. About twenty minutes out loud, which is a class visit with time left for questions, and the mother explains every concept inside the text. A high schooler can read it cold to a second-grade class and field the questions straight off the page. Nothing to memorize, nothing to prepare, no training call beforehand.
 There is also a free browser-based pretend register the younger kids can run afterward — a markdown, a coupon, sales tax, and a total that changes in front of them.
 Does that fit how chapters choose service projects, or am I inventing a use case? Everything is free and ungated either way.
@@ -28500,7 +28500,7 @@
           <t>Ron,
 The Opposite of Spoiled is the reason I knew what I was looking for and couldn't find it. This is a column idea, and it works whether or not my book is in it.
 Every children's book about money teaches earning or saving. I read all 25 titles on the ABA Foundation's list to be sure. Piggy banks, lemonade stands, three jars labeled spend-save-give where "spend" gets one page and a guilty look.
-But saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate and no income. What she has done is stand at a register holding a birthday five and decide. Spending is the first financial act a person performs, and the entire category skipped it for forty years.
+But saving is the second thing a child does with money; the first is spending. A six-year-old has no savings rate and no income. What she has done is stand at a register holding a birthday five and decide. Spending is the first financial act a person performs, and the entire category skipped it for forty years.
 The timing gap sharpens it. Thirty states now guarantee a personal finance course — in high school. Money habits are largely set by seven. We're preparing children for 65 and sending them to the register unarmed today, into a store that spent millions working out how to get the five dollars in their hand.
 I wrote the book I couldn't find. Clarence Gets a Bargain, ages 6–10, one kid and one complete purchase: earning it, the sale ads at the kitchen table, two models compared on a shelf, the cheaper one taken deliberately, a coupon at the register, sales tax, and living with the thing afterward. Idea to post-receipt. Sixteen-plus concepts, none of them announced — nobody in the book says the word "budget." The reader doesn't work out he's been schooled until he reaches the glossary in the back, twenty-one terms, each one page-referenced to the scene where it happened.
 I'm an attorney, which shows: the mother photographs the receipt before the car leaves the parking lot, every time, because a receipt is what makes a return or a warranty claim winnable. Kids are consumers years before anyone tells them they have rights as one. That's a second column and possibly a better one.
@@ -28613,8 +28613,8 @@
 Clarence Gets a Bargain carries a reading level of Lexile AD 620L. The AD stands for "Adult Directed" — the book industry's own label for a title meant to be read WITH a child rather than handed to one. That code isn't an accident. I built the book for the couch, not the corner.
 Here's why. In the story, Clarence doesn't learn about money from a worksheet. He learns it from his mom — at the kitchen table with the sale ads, in the car, in the middle of the store. Read the book to your kid and you aren't describing that scene. You're in it.
 And the interruptions will come. "Do we have a 529?" "Why do you take pictures of receipts?" "Can I hand the cashier the coupon next time?" "Is the internet a need or a want?" A kid alone in the corner reads a robot story and moves on. A kid pressed against your shoulder reads the same story and starts an argument about whether Wi-Fi counts as shelter. You want that argument. The argument is the product; the robot is the delivery vehicle.
-Every other money book for kids teaches saving, which is the second thing a child does with money. Spending is the first, and this one follows a single purchase the whole way — the sale ads, the aisle, the markdown, the coupon, the sales tax, and living with what got bought. Sixteen or more money concepts are in there and not one of them is announced. Nobody says the word "budget." Your kid won't know she's been taught anything until she reaches the glossary at the back — which is the last page, on purpose.
-You don't need to know anything about finance to do this well. Mom explains everything to Clarence inside the story — sale ads, clearance, markdowns, sales tax — so your only job is to read her lines like you knew it all along. I wrote you the script. Take the credit.
+Every other money book for kids teaches saving, which is the second thing a child does with money. Spending is the first, and this one follows a single purchase the whole way , the sale ads, the aisle, the markdown, the coupon, the sales tax, and living with what got bought. Sixteen or more money concepts are in there and not one of them is announced. Nobody says the word "budget." Your kid won't know she's been taught anything until she reaches the glossary at the back , which is the last page, on purpose.
+You don't need to know anything about finance to do this well. Mom explains everything to Clarence inside the story , sale ads, clearance, markdowns, sales tax , so your only job is to read her lines like you knew it all along. I wrote you the script. Take the credit.
 Two parts of the book flat-out require company:
 The grocery game, page 27. Whoever spots the biggest savings wins; the loser carries the bags in from the car. A kid cannot play this alone. That's the point.
 "Guess the Price," page 28. After dinner, somebody shares a deal they got that day and everyone guesses what it cost. Clarence guesses last and lowest, every time — his logic being that if a price is low enough to brag about at dinner, it has to be really low. Three players minimum. Grandma counts.
@@ -28789,7 +28789,7 @@
 Here is the pitch in one line: every children's money book teaches saving, and saving is the second thing a kid does with money. The first is spending. A six-year-old has no savings rate. She has stood in an aisle holding a birthday five, deciding whether the thing is worth it.
 So I wrote the spending one. Clarence Gets a Bargain follows a single purchase the entire way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, gets ambushed by sales tax, and then lives with the thing he bought. Idea to post-receipt. Name another picture book where the kid reads the sale ads before the trip, compares models in the aisle, hands over a coupon, and pays the sales tax. I read all 25 titles on the ABA Foundation's list looking for one. They are all parked on the earning-and-saving side of the register.
 Sixteen-plus concepts are in there and none of them are announced. Nobody says the word "budget." They don't realise they've been schooled until they hit the glossary — twenty-one terms in the back, each page-referenced to the moment it actually happened. That's where the con comes apart, on purpose.
-The segment I'd pitch is not the book. It's the forty-year hole: why an entire publishing category skipped the cash register. There is a Planet Money episode in that whether or not mine is the book that gets mentioned.
+The segment worth doing has nothing to do with my book. It's the forty-year hole: why an entire publishing category skipped the cash register. There is a Planet Money episode in that whether or not mine is the book that gets mentioned.
 One structural note, since you make things people take in together: the reading level is Lexile AD 620L, and the AD stands for Adult Directed — the trade's own code for a book meant to be read *with* a child rather than handed to one. That was the design, not the accident. Twenty minutes out loud, interrupted the whole way, and the interruptions are the product. Classroom, kitchen table, grandparent's couch — same pages, same arguments break out.
 Am I wrong that it's a story? clarencegetsabargain.com/book-facts.html has the specs. Four-minute flip: https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -28908,7 +28908,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>Tim — NGPF owns 9-12 and does it better than anyone, so this is not a pitch into your territory. It is a question about the floor beneath it.
+          <t>Tim — NGPF owns 9-12 and does it better than anyone, so take this as a question about the floor beneath your work rather than a pitch into your territory.
 Every state that mandates personal finance mandates it in high school. Delaware just became the thirtieth and put the course in front of ninth graders. Fine as far as it goes. But the money behaviors NGPF is correcting at sixteen were installed at six, in a store, with a parent saying no.
 The sequence is what I keep coming back to. Financial education starts with saving, and saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has stood at a register and chosen.
 I wrote the K-5 on-ramp. One purchase, followed the whole distance — wanting a robot, earning it, working the sale inserts at the kitchen table, comparing two on a shelf, taking the cheaper one on purpose, redeeming a coupon, meeting sales tax, and living with the choice. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; none does the full arc. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced back into the story.
@@ -29031,11 +29031,11 @@
       <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Kim — you review children's books for a living, so you have read more well-meaning money picture books than anyone should have to, and you already know the problem with them.
-They all teach saving. A piggy bank, a lemonade stand, a lesson. Which is fine advice in the wrong order, because saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate and has absolutely stood in a store holding money and had to decide.
+They all teach saving. A piggy bank, a lemonade stand, a lesson. Which is fine advice in the wrong order, because saving is the second thing a child does with money; the first is spending. A six-year-old has no savings rate and has absolutely stood in a store holding money and had to decide.
 Mine is the spending one, and it follows a single purchase the whole distance rather than gesturing at the idea: a boy wants a robot, earns it with chores and grades, works the sale ads at the kitchen table, compares two models in the aisle, takes the cheaper one on purpose, hands a coupon to the cashier, gets hit with sales tax, and then has to live with the thing. Idea to post-receipt. I read all 25 on the ABA Foundation's list to be sure nobody had done it. Nobody had.
-What I'd actually want your eye on is the smuggling. Sixteen-plus concepts and not one of them is announced — no character stops to explain a term, nobody says "budget." The reader does not know he's been schooled until he reaches the glossary — twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than a homework appendix. The reveal is deliberate and it is on the last page. That balance is the hardest thing in the book and the thing most likely to be off by a hair.
+What I'd actually want your eye on is the smuggling. Sixteen-plus concepts and not one of them is announced , no character stops to explain a term, nobody says "budget." The reader does not know he's been schooled until he reaches the glossary , twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than a homework appendix. The reveal is deliberate and it is on the last page. That balance is the hardest thing in the book and the thing most likely to be off by a hair.
 One thing I'd want you to test rather than take on faith: whether it clicks later. The book is built to fire back months on, in a real store — "is the newer one really better? Clarence checked." Recognition first, then the habit. If that isn't actually in the pages, I'd want to know.
-The other thing worth your reviewer's ear: it is built to be read aloud, and Lexile has it at AD 620L — Adult Directed, read-with rather than read-alone. The mother carries the exposition, which means the adult holding the book is handed the script. Whether that voice actually holds up out loud — across a classroom, a couch, and a grandparent's lap — is something you would hear in a page and I can only guess at.
+The other thing worth your reviewer's ear: it is built to be read aloud, and Lexile has it at AD 620L — Adult Directed, read-with rather than read-alone. The mother carries the exposition, which means the adult holding the book is handed the script. Whether that voice actually holds up out loud , across a classroom, a couch, and a grandparent's lap , is something you would hear in a page and I can only guess at.
 Would you read it as an editor rather than as a friend? I would rather hear where it sags than be told it's charming.
 clarencegetsabargain.com/press-kit.html · https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -29215,7 +29215,7 @@
       <c r="K9" s="5" t="inlineStr">
         <is>
           <t>Michelle — you have written for twenty years that the money conversation with children has to start early, and I wrote the book for the earliest version of it. One question at the end, and it is a column question rather than a book question.
-Every children's financial literacy book teaches saving. I read all 25 on the ABA Foundation's list to be certain. Piggy banks, jars, patience. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it — in a store, holding money, deciding whether the thing is worth what it costs.
+Every children's financial literacy book teaches saving. I read all 25 on the ABA Foundation's list to be certain. Piggy banks, jars, patience. But saving is the second thing a child does with money; the first is spending, and a six-year-old has already done it — in a store, holding money, deciding whether the thing is worth what it costs.
 Mine follows one purchase the entire way. A boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he bought. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." Twenty-one terms in the glossary, each page-referenced to the scene it came from.
 The format is part of the argument. Lexile AD 620L — Adult Directed, the industry's own code for a book meant to be read *with* a child. Which means the conversation you have been telling parents to have for twenty years happens on its own: an adult reads, a kid interrupts, and somebody in the room has to answer "do we have one of those?" out loud. It works the same when the adult is a grandparent, which is often who is actually sitting there.
 The column, if there is one: an entire publishing category has taught children to save for forty years and skipped the cash register, which is the only place a child has ever actually handled money. That is a story about the field, not about me.
@@ -29277,9 +29277,9 @@
         <is>
           <t>Cinders — Moneybunnies splits money into Earn, Save, Spend and Give, which makes you the one person in this category who already agreed with me before I showed up.
 I went deep on one of your four. Spending, and specifically the whole transaction rather than the idea of it. Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then has to live with what he picked. Idea to post-receipt.
-The reason I think it sits beside Moneybunnies rather than against it: you give a child the four categories, and mine walks them through the mechanics of one. Sixteen-plus concepts, none announced — nobody says "budget" — and twenty-one terms in a glossary in the back, each page-referenced to the scene where it happened.
+The reason I think it sits beside Moneybunnies rather than against it: you give a child the four categories, and mine walks them through the mechanics of one. Sixteen-plus concepts, none announced , nobody says "budget" , and twenty-one terms in a glossary in the back, each page-referenced to the scene where it happened.
 Author-illustrator to author-illustrator: I did the art as well, so I know exactly how much of the work nobody sees. I'd rather you saw this from me than off a shelf.
-The read-aloud is the other half of it. Lexile AD 620L — Adult Directed — written for the adult voice in the room rather than for a child alone, with the mother carrying the explanations so the grown-up gets handed the script. You will know better than most how much that changes what has to happen on the page.
+The read-aloud is the other half of it. Lexile AD 620L , Adult Directed , written for the adult voice in the room rather than for a child alone, with the mother carrying the explanations so the grown-up gets handed the script. You will know better than most how much that changes what has to happen on the page.
 Trade copies? I'll read yours properly and tell you the truth about it, which is the only thing worth trading.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -29399,7 +29399,7 @@
           <t>Leslie — a Money as You Grow question, and then an idea I'd like a CFPB read on.
 The question first. Is the Bookshelf still evaluating titles, and who owns it now? I have a K-5 picture book that teaches spending rather than saving, and the current shelf leans heavily toward saving.
 The idea. A child becomes a consumer the first time they hand money to a cashier. Not at eighteen, not at a first paycheck — at six, at a register, with a birthday five. Everything in youth financial education treats that child as a saver in training. Almost nothing treats her as what she already is: a party to a transaction.
-My book follows one purchase the entire way, which is the part I could not find anywhere else — from wanting the thing, through the sale ads, the comparison, the markdown, the coupon, and the sales tax, to living with what was bought. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in the glossary, each page-referenced to the scene where it happened.
+My book follows one purchase the entire way, which is the part I could not find anywhere else — from wanting the thing, through the sale ads, the comparison, the markdown, the coupon, and the sales tax, to living with what was bought. Idea to post-receipt; sixteen-plus concepts, none announced. Twenty-one terms in the glossary, each page-referenced to the scene where it happened.
 One format note relevant to Money as You Grow: Lexile AD 620L — Adult Directed, a read-with rather than a read-alone. The caregiver conversation the framework is built around happens inside the reading rather than after it, and it happens whether the adult is a parent, a teacher, or a grandparent.
 I know the full picture crosses agencies — warranties and returns are FTC, product safety is CPSC — and I am not asking CFPB to cover those. I am asking whether Money as You Grow has room for material that treats the child as a consumer on the financial side from the first purchase forward.
 clarencegetsabargain.com/educator-toolkit.html
@@ -29590,11 +29590,11 @@
       <c r="K15" s="5" t="inlineStr">
         <is>
           <t>Tiffany — you built a career on the thing nobody teaches: what to actually do, in order, with money that is already in your hand. That is why I'm writing about the six-year-old version.
-Every children's money book teaches saving. All 25 on the ABA Foundation's list — I checked. Piggy banks, jars, patience. But saving is the second thing a child does with money. The first is spending, and a first grader has already done it, in a store, holding a birthday five, working out whether the thing is worth what it costs.
+Every children's money book teaches saving. All 25 on the ABA Foundation's list — I checked. Piggy banks, jars, patience. But saving is the second thing a child does with money; the first is spending, and a first grader has already done it, in a store, holding a birthday five, working out whether the thing is worth what it costs.
 Mine is the spending one, and it follows a single purchase the whole way rather than talking about the idea: a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, gets hit with sales tax, and then lives with what he chose. Idea to post-receipt.
 The design choice: none of the sixteen-plus concepts is announced. Nobody in the book says "budget," which for a book that is largely about budgeting took some doing. The kid does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. There for the kid who wants it, invisible to the kid who doesn't.
 The claim I'd defend hardest is the delayed one: it clicks later, in a real store. Recognition first, then the habit — the book doing its job when nobody is standing there teaching.
-One more thing about how it gets used, because it changes who it is for. Lexile AD 620L — Adult Directed, the industry's own code for a book meant to be read *with* a child. The mother explains every concept on the page, so the adult reading aloud gets handed the script and does not have to be the one who already knows about money. That matters most in the houses where nobody feels qualified to teach it, which is most houses.
+One more thing about how it gets used, because it changes who it is for. Lexile AD 620L — Adult Directed, the industry's own code for a book meant to be read *with* a child. The mother explains every concept on the page, so the adult reading aloud gets handed the script and does not have to be the one who already knows about money. It counts most in the houses where nobody feels qualified to teach it, which is most houses.
 You know better than almost anyone whether a thing lands with the people it's for. Would you look, and tell me if the six-year-old version of your audience would sit still for it?
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -29714,7 +29714,7 @@
         <is>
           <t>Professor Lusardi — you built the instruments the field measures itself with, so you have better grounds than anyone to tell me my premise is wrong. That is the reason I'm writing rather than sending a press release.
 The premise. Financial literacy is measured, sensibly, on saving, compounding and risk. Those are the right things to measure in adults. But each of them is downstream of a decision a child makes years earlier that nobody scores: standing in front of two prices and picking one. Spending is the first financial behavior a person performs. It is taught last, or not at all.
-I could not find the children's book for it, so I wrote one. Clarence Gets a Bargain follows a single purchase the entire way — wanting the thing, earning it, reading the sale ads, comparing two models, choosing the cheaper one deliberately, redeeming a coupon, meeting sales tax, and then living with the choice. Idea to post-receipt. Sixteen-plus concepts, none announced. Twenty-one terms in the glossary, each page-referenced to the scene it came from.
+I could not find the children's book for it, so I wrote one. Clarence Gets a Bargain follows a single purchase the entire way — wanting the thing, earning it, reading the sale ads, comparing two models, choosing the cheaper one deliberately, redeeming a coupon, meeting sales tax, and then living with the choice. Idea to post-receipt; sixteen-plus concepts, none announced. Twenty-one terms in the glossary, each page-referenced to the scene it came from.
 One design feature that may matter for measurement. The book is classified Lexile AD 620L — Adult Directed — so the intervention is not a child reading alone but an adult and a child reading together, with the adult prompted by the text rather than expected to supply the content. If shared reading is doing the work rather than the book, that is testable, and it would be a more interesting finding than anything about my book.
 The question I would actually like answered: does the evidence base start at adolescence the way the books do? If spending competence at seven predicts nothing at twenty-seven, that is worth knowing and you would know it. If it does predict something, then there is a gap in the literature sitting underneath a picture book, and you are far better placed to say so than I am.
 clarencegetsabargain.com/book-facts.html · https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -29784,7 +29784,7 @@
       <c r="K18" s="5" t="inlineStr">
         <is>
           <t>Tracy — a public-private partnership is how a K-5 resource actually reaches classrooms, because elementary rarely gets its own budget line. That is the whole reason I'm writing to you rather than to a district.
-The gap I'm working on: every state financial-literacy mandate lands in high school. Thirty of them now. Meanwhile the behaviors being corrected at sixteen were installed at six, in a store, and the sequence nobody questions is that children should learn saving first. Saving is the second thing a person does with money. The first is spending.
+The gap I'm working on: every state financial-literacy mandate lands in high school. Thirty of them now. Meanwhile the behaviors being corrected at sixteen were installed at six, in a store, and the sequence nobody questions is that children should learn saving first. Saving is the second thing a person does with money; the first is spending.
 I wrote the K-5 piece. One purchase followed from the idea to after the receipt — sale ads at the kitchen table, comparison shopping, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced, and a twenty-one-term glossary page-referenced into the story.
 What matters for a partnership is the rest of it, and it is free. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart. Ungated, no account, prints from a browser. A district adopting it spends nothing.
 One practical spec for adoption: Lexile AD 620L — Adult Directed — one class period read aloud, with the text carrying the explanations so a teacher needs no finance training. The same book goes home and works at a kitchen table with a parent or a grandparent, which is usually where a partnership wants the family-engagement half to come from and rarely finds it.
@@ -29845,7 +29845,7 @@
       <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Nicolle — your twelve-book roundup is the one I point people to, which is slightly awkward, because every title on it teaches earning or saving.
-That's not a criticism of the list. It is an accurate reflection of what exists — the whole category is parked on the earning-and-saving side of the register. I went looking for the spending book and could not find it, so I wrote it.
+The list is accurate; that's simply what exists. The whole category is parked on the earning-and-saving side of the register. I went looking for the spending book and could not find it, so I wrote it.
 The argument in one line: saving is the second thing a child does with money, and the first is spending. A six-year-old has no savings rate and has definitely stood in a store holding a birthday five, deciding whether the thing is worth what it costs.
 Clarence Gets a Bargain follows one purchase from the idea to after the receipt. A boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Sixteen-plus concepts and nobody in the book says "budget." Twenty-one terms in the glossary, each page-referenced to the scene it came from.
 Two asks, and the second one matters more. Worth a look for the next update to the roundup? And separately — you run a company built on kids and money, so if you think spending-before-saving is wrong, I would rather hear it from you than keep saying it at conferences.
@@ -29967,7 +29967,7 @@
       <c r="K21" s="5" t="inlineStr">
         <is>
           <t>Dave — Wisconsin has run a state financial-literacy office longer than most states have had a requirement, so you have seen more of these come and go than almost anyone. I would like a read on one assumption.
-Every mandate in the country lands in high school. Thirty of them now. Money habits are largely set by seven, which puts the policy about a decade behind the behaviour. Underneath that sits the belief that children should learn saving first. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent right there.
+Every mandate in the country lands in high school. Thirty of them now. Money habits are largely set by seven, which puts the policy about a decade behind the behaviour. Underneath that sits the belief that children should learn saving first. Saving is the second thing a person does with money; the first is spending — and a first grader has done it, at a register, with a parent right there.
 I built the K–5 piece rather than an argument about it. A 36-page picture book that follows one complete purchase: the sale ads at the kitchen table, comparison on a shelf, a markdown taken deliberately, a coupon at the register, sales tax, and then living with what was bought. Sixteen-plus concepts, none announced — nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from. We are very good at teaching this to people who have already made the mistake.
 The classroom set behind it is free and ungated: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, and a 23-row crosswalk to the 2021 National Standards, Common Core Math and ELA, CEE and FDIC Money Smart. No account, no email capture, prints from a browser. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud that a teacher without a finance background can run cold, and the same book works at a kitchen table.
 The question: in your experience, does elementary material get adopted when it is free and aligned, or does it need a mandate behind it to move at all? I would rather know now than find out slowly.
@@ -30028,7 +30028,7 @@
         <is>
           <t>Hunter — a policy observation, and a question about whether NEFE has a view on it.
 Thirty states now require a personal finance course to graduate. Delaware became the thirtieth last October. Every one of those mandates lands in high school, and the funding and training follow the mandate. Meanwhile the K-5 standards that already exist in most states sit there with almost nothing built against them, because nobody has to report on them.
-The sequence assumption underneath all of it is that children should learn saving first. I think that is backwards. Saving is the second thing a person does with money. The first is spending — and a first grader has done that, at a register, with a parent standing behind her. The behaviors a high school course is trying to correct were installed a decade earlier.
+The sequence assumption underneath all of it is that children should learn saving first. I think that is backwards. Saving is the second thing a person does with money; the first is spending — and a first grader has done that, at a register, with a parent standing behind her. The behaviors a high school course is trying to correct were installed a decade earlier.
 I wrote the elementary piece rather than an argument about it: a 36-page picture book that follows one purchase from the idea to after the receipt, plus a free ungated classroom set crosswalked to the 2021 National Standards, Common Core, CEE and FDIC Money Smart. Sixteen-plus concepts, none announced, twenty-one-term glossary page-referenced into the story.
 One implementation note, since policy has to survive contact with an actual classroom. Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations, no teacher training required, and the same book does the family-engagement job at home with a parent or a grandparent. Elementary programs usually die on training cost. This one has none.
 The question: does NEFE's advocacy work have a position on the elementary band, or is the practical view that high school mandates are where the effort actually pays? I ask because if it's the second, I'd like to know I'm arguing with the consensus rather than filling a gap it agrees exists.
@@ -30089,8 +30089,8 @@
         <is>
           <t>Tom — you got more genuine engagement out of one post about kids and money than anyone else in this category has managed, which tells me you know exactly which part of this parents actually care about. I would like to check my premise against that.
 My premise: the whole field has the sequence backwards. Financial education starts children with saving. Saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, standing in a store holding a birthday five, working out whether the thing is worth what it costs. We teach the second thing first and the first thing never.
-So I wrote and illustrated the spending book. Clarence Gets a Bargain follows one purchase the whole way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax and objects to it, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." The reader works out he has been schooled only at the glossary — twenty-one terms in the back, page-referenced to the scene each came from. A jar is a storage container. It has never once talked a kid out of anything.
-The instruction underneath the whole book is four words long: stop bringing kids to the store as cargo, bring them as staff. Catalogued Lexile AD 620L — Adult Directed — so the parent gets handed the script rather than an assignment, which I suspect is why your posts land: parents want the conversation and do not feel qualified to start it.
+So I wrote and illustrated the spending book. Clarence Gets a Bargain follows one purchase the whole way , a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax and objects to it, and then lives with what he chose. Idea to post-receipt; sixteen-plus concepts and nobody in the book says "budget." The reader works out he has been schooled only at the glossary , twenty-one terms in the back, page-referenced to the scene each came from. A jar is a storage container. It has never once talked a kid out of anything.
+The instruction underneath the whole book is four words long: stop bringing kids to the store as cargo, bring them as staff. Catalogued Lexile AD 620L , Adult Directed , so the parent gets handed the script rather than an assignment, which I suspect is why your posts land: parents want the conversation and do not feel qualified to start it.
 The thing I would actually value: you know what makes a parent stop scrolling on this subject and what makes them scroll past. If "spending before saving" is the wrong hook, I would rather hear it from you than keep testing it slowly.
 Would you look and tell me? https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -30152,7 +30152,7 @@
 Nobody put that in a story. So I did. Clarence Gets a Bargain follows a single purchase the whole way — a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax and regards it as a personal insult, then lives with the thing he chose. Idea to post-receipt.
 Sixteen-plus concepts and none of them announced. Nobody in the book says "budget," which for a book largely about budgeting took some doing. Kids smell a worksheet one page in; they never smell this one, because they are laughing too hard to notice. The reveal is the glossary — twenty-one terms in the back, page-referenced to the scene each came from. It is catalogued AD 620L, Adult Directed, so the parent listening to your show gets handed the script rather than a homework assignment.
 Their books are about earning and saving, which is fine, but there is no game in a piggy bank and kids work that out faster than we do. They smell a worksheet through a backpack.
-The episode I would pitch is not the book. It is the forty-year hole: an entire publishing category taught children to save and skipped the cash register, the only place a child has ever actually handled money.
+The episode worth doing has nothing to do with my book. Pitch the forty-year hole: an entire publishing category taught children to save and skipped the cash register, the only place a child has ever actually handled money.
 Worth twenty minutes of your show? https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
         </is>
@@ -30332,8 +30332,8 @@
           <t>Gretchen — you have spent a career on how financial products get sold to people who don't fully understand them. Here is the entry-level version of that, and nobody covers it.
 A child becomes a consumer the first time money leaves their hand. Six years old, a birthday five, a store. From that moment they are a party to transactions, and the entire financial education apparatus treats them as a saver in training instead. We teach them to hold money. Nobody teaches them what happens when they use it, which is the only thing they were ever going to do with it.
 The scale is small and the mechanics are identical to the ones you write about. A claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the child has no way of knowing that. Not a game of skill — a slot machine wearing a carnival hat, aimed at someone with no price memory and no comparison to make.
-I wrote the picture book for it. One kid, one purchase, followed the whole way: he wants a robot, earns it, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget." The child works out he has been schooled only when he reaches the glossary — twenty-one terms in the back, each page-referenced to where it happened. It is catalogued Lexile AD 620L, where AD stands for Adult Directed — the trade's own code for a book an adult reads with a child rather than hands over.
-The story is not the book. It is that an entire publishing category taught children to save for forty years and skipped the register, which is the only place a child has ever handled money — while the arcade, the app store and the checkout lane did not skip it at all.
+I wrote the picture book for it. One kid, one purchase, followed the whole way: he wants a robot, earns it, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt; sixteen-plus concepts and nobody in the book says the word "budget." The child works out he has been schooled only when he reaches the glossary — twenty-one terms in the back, each page-referenced to where it happened. It is catalogued Lexile AD 620L, where AD stands for Adult Directed — the trade's own code for a book an adult reads with a child rather than hands over.
+The story here has nothing to do with my book. An entire publishing category taught children to save for forty years and skipped the register, which is the only place a child has ever handled money — while the arcade, the app store and the checkout lane did not skip it at all.
 Is there anything there? clarencegetsabargain.com/press-kit.html
 Jonathan</t>
         </is>
@@ -30451,7 +30451,7 @@
         <is>
           <t>Terry — you have been telling adults the truth about money for decades, usually after the damage is done. I wrote the book for about twenty years earlier than you usually get them.
 The argument in one line: mistakes at eleven cost $14, and the same mistake at twenty-seven has a credit card attached. Everything you write about compounding cuts both ways, and the habits doing the compounding were installed in a store, at six, with a parent saying no.
-Which is where the whole category gets the order wrong. Children's money books teach saving — piggy banks, jars, patience, and a strong implication that wanting things is a character flaw. But saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate. She has stood at a register holding money and had to decide.
+Which is where the whole category gets the order wrong. Children's money books teach saving — piggy banks, jars, patience, and a strong implication that wanting things is a character flaw. But saving is the second thing a child does with money; the first is spending. A six-year-old has no savings rate. She has stood at a register holding money and had to decide.
 Clarence Gets a Bargain follows one purchase the entire way: a boy wants a robot, earns it through chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax and takes it personally, then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none announced — nobody in the book says "budget." The reader finds out he has been schooled at the glossary, twenty-one terms in the back, each page-referenced to the scene it came from.
 It reads aloud in twenty minutes. Lexile AD 620L — Adult Directed, the industry's own code for read-with rather than read-alone, so a parent who feels unqualified on money still gets handed the script.
 The column question rather than the book question: has anyone made the case that spending competence has to come first? I have not been able to find it, and you would know if it exists.
@@ -30816,7 +30816,7 @@
           <t>Julie — a segment idea, and it is short enough to survive a live hit.
 Every children's money book teaches saving. Piggy banks, lemonade stands, jars. But saving is the second thing a child does with money — the first is spending, and a six-year-old has already done it, in a store, holding a birthday five, deciding whether the thing is worth what it costs.
 The category skipped that for forty years. The arcade did not. A claw machine takes $25 to hand back a basketball that Walmart sells for $9.99, and the kid has no price memory to defend himself with. Once a kid has seen the $9.99, the claw loses its grip.
-So I wrote the spending book. Clarence Gets a Bargain, ages 6–10: a boy earns a robot with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and then lives with the thing he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Twenty-one terms in a glossary at the back, each page-referenced to where it happened. Catalogued AD 620L — Adult Directed — twenty minutes out loud, interrupted the whole way. The category's own defence is that money is a serious subject. It is. So is getting fleeced in an aisle at the age of seven.
+So I wrote the spending book. Clarence Gets a Bargain, ages 6–10: a boy earns a robot with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and then lives with the thing he picked. Idea to post-receipt; sixteen-plus concepts, none of them announced. Twenty-one terms in a glossary at the back, each page-referenced to where it happened. Catalogued AD 620L — Adult Directed — twenty minutes out loud, interrupted the whole way. The category's own defence is that money is a serious subject. It is. So is getting fleeced in an aisle at the age of seven.
 I am an attorney and a mixed-media artist, and I have twice walked out of the same Nordstrom Rack having paid one cent — once for a $293 pair of shoes, once for a $69.50 shirt. I kept both tags. It makes for a good visual if you ever want one on screen.
 Is there a hit in "the money skill nobody teaches kids"? clarencegetsabargain.com/press-kit.html
 Jonathan</t>
@@ -31056,7 +31056,7 @@
         <is>
           <t>Ben — a story pitch about a gap in the coverage rather than a book pitch, though the book is how I found it.
 Thirty states now guarantee a personal finance course. Every one of those mandates lands in high school. Money habits are largely set by seven, so the policy arrives roughly ten years after the cement dries — a fifteen-year-old handed a course for a habit he formed at six, and everyone acting surprised, and the funding, the training and the reporting all follow the mandate rather than the evidence.
-Underneath that sits an assumption nobody argues with: that children should learn saving first. I think it is backwards. Saving is the second thing a person does with money. The first is spending, and a first grader has done that, at a register, with a parent standing behind her. The behaviors a high school course tries to correct were installed a decade earlier by an arcade, a toy aisle and a checkout lane, none of which waited for a curriculum.
+Underneath that sits an assumption nobody argues with: that children should learn saving first. I think it is backwards. Saving is the second thing a person does with money; the first is spending, and a first grader has done that, at a register, with a parent standing behind her. The behaviors a high school course tries to correct were installed a decade earlier by an arcade, a toy aisle and a checkout lane, none of which waited for a curriculum.
 I wrote the elementary piece rather than an op-ed about it. A 36-page picture book following one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, and living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Free ungated classroom set behind it, crosswalked to five frameworks. Catalogued Lexile AD 620L — Adult Directed, so it is a read-with, and the caregiver conversation happens inside the reading.
 Meanwhile the arcade never waited for a standard: $25 into a glass box for a basketball Walmart sells for $9.99, and the kid has no price memory to argue with.
 The story I would pitch your desk: the whole country legislated financial literacy into ninth grade, and the elementary standards that already exist in most states sit there with nothing built against them, because nobody has to report on them.
@@ -31117,9 +31117,9 @@
         <is>
           <t>Stacy — you write about what happens to ordinary people inside financial systems. There is a version of that beat with no coverage at all, and it starts at about age six.
 A child becomes a consumer the first time they hand money to a cashier. Not at eighteen, not at a first paycheck — at six, with a birthday five. From that moment they are party to a transaction and they have rights nobody mentions: the receipt is proof, the price on the shelf has to match the price at the register, a broken thing can go back. Consumer education is the missing wing of children's financial literacy. We teach them to save and never tell them they are already the buyer.
-That is why I wrote the book. Clarence Gets a Bargain follows one purchase the entire way — a boy wants a robot, earns it, reads the sale inserts at the kitchen table, compares two on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced, and a twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
-The detail people ask me about: the mother photographs the receipt the second she sits down in the car. Every time. It takes four seconds and it is what makes a return, an exchange or a warranty claim winnable. Almost nobody teaches a child that, which is why the book is catalogued AD 620L — Adult Directed — and gets read with an adult rather than handed to a kid alone.
-I am an attorney, and on vacation that mostly means the souvenirs get cross-examined. The hermit crab: who feeds it over the holidays, and in two weeks when it dies — and buddy, it will — is it worth the tears? My kids find this insufferable. It is also the entire skill.
+That is why I wrote the book. Clarence Gets a Bargain follows one purchase the entire way — a boy wants a robot, earns it, reads the sale inserts at the kitchen table, compares two on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt; sixteen-plus concepts, none announced, and a twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
+The detail people ask me about: the mother photographs the receipt the second she sits down in the car. Every time. It takes four seconds and it is what makes a return, an exchange or a warranty claim winnable. Almost nobody teaches a child that, which is why the book is catalogued AD 620L , Adult Directed , and gets read with an adult rather than handed to a kid alone.
+I am an attorney, and on vacation that mostly means the souvenirs get cross-examined. The hermit crab: who feeds it over the holidays, and in two weeks when it dies , and buddy, it will , is it worth the tears? My kids find this insufferable. It is also the entire skill.
 The honest version of the beat problem: the full picture crosses agencies. Warranties and returns sit with the FTC, product safety with the CPSC. Nobody owns "children as consumers," which may be exactly why nobody covers it.
 Is there a story in that? clarencegetsabargain.com/press-kit.html
 Jonathan</t>
@@ -31301,7 +31301,7 @@
         <is>
           <t>Dr. Taylor — I am a Maryland attorney and children's book author writing about the elementary end of financial literacy, which is the end nobody funds.
 Maryland's requirement, like every state's, lands in high school. The elementary standards sit underneath it with almost nothing built against them, for the least respectable reason available: nobody has to report on that band. Meanwhile the habits a high school course is trying to correct were installed at six, in a store, with a parent saying no and no reasoning attached.
-The field's answer is to teach children saving first. Saving is the second thing a person does with money. The first is spending, and a first grader has done it — at a register, with a parent standing right there.
+The field's answer is to teach children saving first. Saving is the second thing a person does with money; the first is spending, and a first grader has done it — at a register, with a parent standing right there.
 I wrote the K–5 piece. A 36-page picture book following one purchase from the idea through the receipt: sale ads at the kitchen table, comparison shopping on a shelf, a markdown taken on purpose, a coupon at the register, sales tax, and living with what was bought. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced back into the story.
 What matters for a district is that all of it is free. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, and a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart. No account, no email capture, no purchase order. It prints from a browser, so adoption costs a building nothing. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud a teacher can run with no finance background.
 I am local and would happily walk a curriculum team through it, or a single school if that is the right size to start.
@@ -31365,7 +31365,7 @@
           <t>Beth — a research question rather than a pitch, and the book is only the reason I ran into it.
 Financial capability gets measured, sensibly, on saving, compounding and risk. Those are the right things to measure in adults. But each of them sits downstream of a decision made years earlier that nobody scores: a child standing in front of two prices, picking one. Spending is the first financial behavior a person performs, and it is taught last or not at all.
 The environment is not waiting for the curriculum. Children are transacting constantly — arcades, app stores, checkout lanes — and none of it gets counted as financial education, though it plainly is.
-I wrote the elementary piece. A 36-page picture book following one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, and living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced back into the story. Free ungated classroom set behind it, crosswalked to five frameworks. The polite version is that the elementary band is understudied. The blunt version is that nobody has to report on it, so nobody looks.
+I wrote the elementary piece. A 36-page picture book following one purchase from the idea to after the receipt — sale ads, comparison, a markdown, a coupon, sales tax, and living with the choice. Sixteen-plus concepts, none announced; a twenty-one-term glossary page-referenced back into the story. Free ungated classroom set behind it, crosswalked to five frameworks. The polite version is that the elementary band is understudied. The blunt version is that nobody has to report on it, so nobody looks.
 Design note that may matter to your work: the book is catalogued Lexile AD 620L — Adult Directed. The intervention is an adult and a child reading together, not a child reading alone, which makes it closer to a shared-reading study than a curriculum study.
 The question: does the evidence base start at adolescence the way the books do? If spending competence at seven predicts nothing at twenty-seven, that is worth knowing and I would rather hear it than keep arguing.
 clarencegetsabargain.com/book-facts.html
@@ -31486,7 +31486,7 @@
         <is>
           <t>Vince — you have thousands of instructors in the field, which means you know better than almost anyone what they walk into a room without. I built the elementary thing they do not have.
 Most financial education material aimed at children starts with saving. Saving is the second thing a child does with money. The first is spending — and a first grader has done it, at a register, with a parent behind her. An instructor standing in front of a second-grade class has almost nothing to hand them about that moment.
-Clarence Gets a Bargain is a 36-page picture book that follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one deliberately, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says the word "budget."
+Clarence Gets a Bargain is a 36-page picture book that follows one purchase the whole way: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one deliberately, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt; sixteen-plus concepts and nobody in the book says the word "budget."
 Why it works for an instructor rather than a teacher: it is catalogued Lexile AD 620L — Adult Directed — it runs about twenty minutes out loud, and the mother explains every concept inside the text. Somebody can read it cold to a class and field questions straight off the page. Nothing to memorise, no training call beforehand. Behind it sits a free ungated set — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, and a browser-based pretend register with a markdown, a coupon and sales tax.
 The twenty-one-term glossary in the back is page-referenced to the story, so an instructor can answer a vocabulary question by turning to the scene rather than reciting a definition. The field keeps building the ninth-grade course and keeps skipping the second-grade one, which is a strange place to draw a line.
 Does your instructor network want elementary material, or is the demand really all adult and teen? Everything is free either way.
@@ -31547,7 +31547,7 @@
         <is>
           <t>Billy — a question about where NEFE draws the line on grade band, asked by someone who has just spent a year building for the band nobody funds.
 Thirty states now require personal finance to graduate. The mandates land in high school, and the funding, the training and the reporting follow the mandate — which is a tidy way of arriving about nine years late and calling it early intervention. Meanwhile the K–5 standards that already exist in most states sit there with almost nothing built against them, because nobody has to report on them.
-The assumption underneath is that children should learn saving first. I think it is backwards, and I would rather be told so by NEFE than keep saying it at conferences. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with a parent standing behind her. The behaviors a high school course is trying to correct were installed a decade earlier.
+The assumption underneath is that children should learn saving first. I think it is backwards, and I would rather be told so by NEFE than keep saying it at conferences. Saving is the second thing a person does with money; the first is spending — and a first grader has done it, at a register, with a parent standing behind her. The behaviors a high school course is trying to correct were installed a decade earlier.
 I wrote the elementary piece rather than an argument about it: a 36-page picture book that follows one purchase from the idea to after the receipt, plus a free ungated classroom set crosswalked to the 2021 National Standards, Common Core, CEE and FDIC Money Smart. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Catalogued Lexile AD 620L — Adult Directed — so the intervention is a shared read rather than solo reading, which also makes it easier to study than a curriculum. There is a whole industry aimed at teenagers who already have the habit, and almost nobody upstream of it.
 The line I would put on a poster if I could: mistakes at eleven cost $14, and the same mistake at twenty-seven has a credit card attached.
 The question: does NEFE's research or advocacy work have a position on the elementary band, or is the practical view that high school is where the effort pays? If it is the second, I would like to know I am arguing with a considered consensus rather than filling a gap it agrees exists.
@@ -31671,9 +31671,9 @@
         <is>
           <t>Prince — you took investing, which is the hardest concept in this category to make readable for children, and made it a series a kid comes back to. I went the opposite direction on the same shelf and I would like your read on it.
 Wesley learns to invest. Clarence learns to spend — and I mean the mechanics of it rather than the idea. Every other book in the category teaches saving, which is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. Nobody had written that one, so I did.
-Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt. Sixteen-plus concepts, none of them announced. Nobody says the word "budget."
-The craft problem I would most like another author's view on: the reader is not supposed to know he has been taught anything until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. Getting that balance right, so it stays a story, was the whole job, and it is the thing most likely to be off by a hair. The rest of the shelf is piggy banks with plots. Good ones, some of them — but none of them has ever been to a register.
-I did the illustrations too, which means my opinion of them is worth nothing. It is written for the adult voice in the room — catalogued AD 620L, Adult Directed — with the mother carrying every explanation.
+Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt; sixteen-plus concepts, none of them announced. Nobody says the word "budget."
+The craft problem I would most like another author's view on: the reader is not supposed to know he has been taught anything until he reaches the glossary , twenty-one terms in the back, each page-referenced to the scene it came from. Getting that balance right, so it stays a story, was the whole job, and it is the thing most likely to be off by a hair. The rest of the shelf is piggy banks with plots. Good ones, some of them , but none of them has ever been to a register.
+I did the illustrations too, which means my opinion of them is worth nothing. It is written for the adult voice in the room , catalogued AD 620L, Adult Directed , with the mother carrying every explanation.
 Trade? Send me a Wesley and I will read it properly rather than politely.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -31731,7 +31731,7 @@
       <c r="K50" s="5" t="inlineStr">
         <is>
           <t>Kate — a pitch about a gap rather than a book, though I wrote the book because of the gap.
-Everything in kids' financial literacy points at a horizon no child can see: compound interest, credit scores, retirement. All real, all decades out, and all completely useless to somebody who is eight. Meanwhile the kid is eight, holding $20 of birthday money, standing in a store that spent millions working out how to get it. We are preparing children for 65 and sending them to the register unarmed today.
+Everything in kids' financial literacy points at a horizon no child can see: compound interest, credit scores, retirement. All real; all decades out, and all completely useless to somebody who is eight. Meanwhile the kid is eight, holding $20 of birthday money, standing in a store that spent millions working out how to get it. We are preparing children for 65 and sending them to the register unarmed today.
 So flip the order. Saving is the second thing a child does with money. The first is spending, and it is the one nobody puts in a story.
 Clarence Gets a Bargain does. One kid, one purchase, followed the whole distance — he wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and lives with what he chose. Sixteen-plus concepts and nobody in the book says the word "budget." The reader works out he has been schooled at the glossary — twenty-one terms in the back, each one page-referenced to the scene it came from. Catalogued AD 620L — Adult Directed — so a parent who does not feel qualified on money still gets handed the script and can take the credit.
 The boardwalk is a pop quiz your kid has not studied for, and it runs all summer with real money.
@@ -31789,9 +31789,9 @@
         <is>
           <t>Roda — you built a 30-Day Smart Spending Challenge. Not a saving challenge. Spending. As far as I can tell that makes two of us in this entire category who think the sequence is backwards.
 Here is my version of the argument, and I'd like to know whether it matches how you arrived at yours. Every children's money book teaches saving — I read all 25 on the ABA Foundation's list to be sure. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. We teach the second thing first and the first thing never.
-Clarence Gets a Bargain is the picture-book version. It follows a single purchase the whole distance — a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced; nobody says "budget." Twenty-one terms in a glossary at the end, each page-referenced to where it happened — which is the only point at which a kid works out he's been schooled.
-One story takes a kid from "I want it" to "Is it worth it?" — which I suspect is the same door your Challenge walks them through, thirty days at a time. Yours is a habit; mine is one transaction read in twenty minutes. Those look complementary to me rather than competing — the book could be the on-ramp to a challenge, or the thing a parent reads on day one.
-One thing your Challenge and the book share: neither one works with a kid alone in a room. It is Lexile AD 620L — Adult Directed, the trade's code for read-with rather than read-alone — and the mother explains every concept on the page, so whoever is reading gets handed the script. Parent, teacher or grandparent, the reading stops every few pages because the kid asks something.
+Clarence Gets a Bargain is the picture-book version. It follows a single purchase the whole distance , a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced; nobody says "budget." Twenty-one terms in a glossary at the end, each page-referenced to where it happened , which is the only point at which a kid works out he's been schooled.
+One story takes a kid from "I want it" to "Is it worth it?" , which I suspect is the same door your Challenge walks them through, thirty days at a time. Yours is a habit; mine is one transaction read in twenty minutes. Those look complementary to me rather than competing , the book could be the on-ramp to a challenge, or the thing a parent reads on day one.
+One thing your Challenge and the book share: neither one works with a kid alone in a room. It is Lexile AD 620L , Adult Directed, the trade's code for read-with rather than read-alone , and the mother explains every concept on the page, so whoever is reading gets handed the script. Parent, teacher or grandparent, the reading stops every few pages because the kid asks something.
 Worth a conversation? I'd rather compare notes with the one other person who put spending first than pitch anybody.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -31845,7 +31845,7 @@
       <c r="K52" s="5" t="inlineStr">
         <is>
           <t>Daniel — you built 360 Parenting around the whole child rather than one slice of them, so this is a slice you may be missing, and I say that as someone who only noticed it because I went looking for a book and could not find one.
-Money education for kids begins with saving. Every time. But saving is the second thing a child does with money. The first is spending — and a six-year-old has done that, repeatedly, usually in a store, usually while a parent quietly loses the will to live.
+Money education for kids begins with saving. Every time. But saving is the second thing a child does with money; the first is spending — and a six-year-old has done that, repeatedly, usually in a store, usually while a parent loses the will to live in the background.
 So I wrote the spending book. One purchase, followed the entire way: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, hands the cashier an extra ten-percent-off coupon like a tiny attorney presenting Exhibit A, discovers sales tax the way we all did — badly, and in public — and then has to live with the thing he chose. From the idea to after the receipt.
 Here is why it might fit a parenting audience rather than a classroom one. The concepts are smuggled. Sixteen-plus of them, none announced, nobody saying the word "budget." It reads as a story about a kid and a robot, and the parent doing the read-aloud gets handed the money conversation without having to deliver a lesson. And the kid does not know he's been schooled until he gets to the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. A parent can turn straight back to the exact page.
 The argument I'd bring to a podcast is the delayed one. It clicks later, in a real store. Months out, a kid says "there's a coupon in my pocket, just like Clarence" or "the sticker price isn't what you pay, there's tax" — recognition first, then the habit, and the parent isn't even in the room when it happens.
@@ -31905,8 +31905,8 @@
           <t>ML — you built a series a child comes back to, which is harder than writing one good book, and it's the reason I'm writing to a peer rather than a gatekeeper.
 Mine is a money book, which I appreciate is the least promising sentence in children's publishing. So here is the part that makes it not that.
 Every book in this category teaches saving. Saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it — in a store, holding money, deciding whether the thing is worth what it costs. So mine follows one purchase from the idea to after the receipt: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose.
-The craft problem I'd most like another author's view on: I smuggled sixteen-plus concepts in without announcing any of them. Nobody says "budget." The glossary in the back — twenty-one terms, each page-referenced to the scene it came from — is the only place the book admits it was teaching. Getting that balance right, so it stays a story, was the whole job.
-The other half of the craft problem: it is written for an adult voice. Lexile AD 620L — Adult Directed — with the mother carrying every explanation, so whoever reads aloud gets handed the script. A series lives or dies on whether the grown-up still enjoys the fourth reading. You would know inside a page whether mine does.
+The craft problem I'd most like another author's view on: I smuggled sixteen-plus concepts in without announcing any of them. Nobody says "budget." The glossary in the back , twenty-one terms, each page-referenced to the scene it came from , is the only place the book admits it was teaching. Getting that balance right, so it stays a story, was the whole job.
+The other half of the craft problem: it is written for an adult voice. Lexile AD 620L , Adult Directed , with the mother carrying every explanation, so whoever reads aloud gets handed the script. A series lives or dies on whether the grown-up still enjoys the fourth reading. You would know inside a page whether mine does.
 Would you read it and tell me where it stops being a story? I'll trade — send me a Noah and I'll read it properly.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -31962,7 +31962,7 @@
           <t>Linda — you teach financial parenting, which means you spend your working life on the exact handoff I wrote a book about: the moment a parent has to explain money to a child who is standing right there wanting something.
 My argument, and you are better placed than almost anyone to tell me it's wrong. Financial education for children starts with saving, and it has the sequence backwards. A seven-year-old has no savings rate and no income. What she has done is stand at a register holding money and decide. Spending is the first money behavior a person performs. We teach it last, or not at all.
 Clarence Gets a Bargain is the spending book. It follows one purchase the whole distance — wanting the thing, earning it through chores and grades, reading the sale inserts at the kitchen table with a parent, comparing two models on a shelf, choosing the cheaper one on purpose, handing over a coupon, meeting sales tax, and then living with what he bought. Idea to post-receipt. I read all 25 titles on the ABA Foundation's list; not one covers the whole arc.
-The design choice that matters for your work: nothing is announced. Sixteen-plus concepts and nobody in the book says "budget." The kid does the math because the robot depends on it. The parent reading aloud is handed the conversation without having to give a lecture, which I gather is most of what you coach people out of. The child does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. The reveal is the last thing that happens, not the first.
+The design choice bearing on your work: nothing is announced. Sixteen-plus concepts and nobody in the book says "budget." The kid does the math because the robot depends on it. The parent reading aloud is handed the conversation without having to give a lecture, which I gather is most of what you coach people out of. The child does not know she's been schooled until the glossary — twenty-one terms at the end, each page-referenced to the scene it came from. The reveal is the last thing that happens, not the first.
 The shape of it, if it helps: one funny story about a boy and his dream robot takes a kid from "I want it" to "Is it worth it?" She opens it an impulsive little spender and closes it an aware, educated consumer.
 The part I'd most want your professional read on is the delayed return. The book is not really working in the twenty minutes it takes to read. It works in month eighteen, in an actual store, when the kid hits a real money moment and the book fires back — "wait, is the newer one really better? Clarence checked." Recognition first, then the habit. That is the book doing its job when the parent isn't even in the room.
 And the handoff you teach is the mechanism itself. The book is Lexile AD 620L — Adult Directed, the trade's own label for a book meant to be read *with* a child, not left in a bedroom — and Mom explains everything on the page, so the adult reading aloud is handed the script rather than asked to know the material. A parent who feels unqualified to teach money can still run it. Classroom, kitchen table, grandparent's couch: the reading stops every few pages because somebody asks.
@@ -32024,7 +32024,7 @@
         <is>
           <t>Professor Urban — you produced the evidence base that mandates actually work, which is why I want to ask about the grade band your evidence does not reach.
 Every mandate you have evaluated lands in high school. Thirty states now. The effects are real and I am not arguing with them. My question is about what is happening a decade earlier, because money habits are largely set by seven and the policy arrives roughly ten years after the cement dries.
-Underneath the whole field sits a sequencing assumption nobody tests: that children should learn saving first. I think it is backwards. Saving is the second thing a person does with money. The first is spending — standing in front of two prices and picking one. A first grader has done that. She has no savings rate at all.
+Underneath the whole field sits a sequencing assumption nobody tests: that children should learn saving first. I think it is backwards. Saving is the second thing a person does with money; the first is spending — standing in front of two prices and picking one. A first grader has done that. She has no savings rate at all.
 I could not find the children's book for it, so I wrote one. Clarence Gets a Bargain follows a single purchase the entire way: earning the reward, reading the sale ads, comparing two models on a shelf, choosing the cheaper one deliberately, redeeming a coupon, meeting sales tax, and then living with the choice. Sixteen-plus concepts, none announced. A twenty-one-term glossary page-referenced into the story. Elementary is not so much contested ground as unvisited ground.
 One design feature that may matter for measurement: the book is catalogued Lexile AD 620L — Adult Directed — so the intervention is not a child reading alone but an adult and a child reading together, with the adult prompted by the text. If shared reading is doing the work rather than the book, that is testable, and it would be a more interesting finding than anything about my book.
 The real question: does anything in the literature speak to elementary spending competence, or is that band simply unstudied? Either answer is useful to me.
@@ -32336,7 +32336,7 @@
         <is>
           <t>Jennifer — a funding-shaped question rather than an ask, and the resource itself is already free.
 I wrote and illustrated a K–5 financial-literacy picture book and built the entire classroom program behind it — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a standards crosswalk across five frameworks. All of it is ungated: no account, no email capture, no purchase order, prints from a browser. The only thing that ever costs anything is the physical books, and 25 copies run $499.75.
-The content premise: every children's money book teaches saving, and saving is the second thing a child does with money. The first is spending — a first grader has stood at a register and chosen. The book follows one complete purchase from the idea through the receipt, with sixteen-plus concepts hidden in the plot and a twenty-one-term glossary page-referenced back into the story. If a money lesson looks like school, it gets filed under school and read at school speed.
+The content premise: every children's money book teaches saving, and saving is the second thing a child does with money; the first is spending — a first grader has stood at a register and chosen. The book follows one complete purchase from the idea through the receipt, with sixteen-plus concepts hidden in the plot and a twenty-one-term glossary page-referenced back into the story. If a money lesson looks like school, it gets filed under school and read at school speed.
 Why I am writing to development rather than to a classroom: this is unusually easy to fund. A bank or credit union sponsoring a classroom set gets its name on every book that goes home to a family in its assessment area, the curriculum costs the sponsor nothing because it is already free, and I have a CRA-ready memo written in examiner-friendly language. A funder can point at 25 books, one classroom, and a pre/post instrument. And because it is catalogued AD 620L — Adult Directed — it doubles as family engagement: the same book works at a kitchen table with a parent or a grandparent reading.
 Is a sponsored classroom set something HCZ's funders would recognise, or does everything need to attach to an existing program line?
 clarencegetsabargain.com/resources/grant-in-a-box.html
@@ -32396,8 +32396,8 @@
         <is>
           <t>Flora — JA runs volunteers into elementary classrooms better than any organisation in the country, so this is a materials question rather than a pitch.
 JA's elementary programs are strong on earning, jobs and community. What is thin across the whole field, JA included, is spending — the second thing everybody teaches and the first thing a child actually does. A first grader has no savings rate and no job. What she has done is stand at a register holding money and choose.
-Clarence Gets a Bargain is a 36-page picture book that puts the entire transaction on the page: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from. Every year the field builds another high-school course for a habit that set in first grade, and every year it works about as well as you would expect.
-The part that matters for a volunteer model: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, with every concept explained inside the text by the mother. A volunteer who has never taught anything can read it cold and answer questions off the page. Nothing to memorise and no prep call. Behind it, free and ungated: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable price tags and clearance stickers for a classroom store, and a browser-based pretend register with a markdown, a coupon and sales tax.
+Clarence Gets a Bargain is a 36-page picture book that puts the entire transaction on the page: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced; a twenty-one-term glossary in the back, each entry page-referenced to the scene it came from. Every year the field builds another high-school course for a habit that set in first grade, and every year it works about as well as you would expect.
+The part a volunteer model turns on: it is catalogued Lexile AD 620L — Adult Directed — about twenty minutes out loud, with every concept explained inside the text by the mother. A volunteer who has never taught anything can read it cold and answer questions off the page. Nothing to memorise and no prep call. Behind it, free and ungated: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable price tags and clearance stickers for a classroom store, and a browser-based pretend register with a markdown, a coupon and sales tax.
 Alaska has its own complications on distance and travel, and virtual read-alouds work for this.
 Does a read-aloud fit how JA Alaska builds a volunteer session, or does everything have to run through national curriculum?
 clarencegetsabargain.com/educator-toolkit.html
@@ -32458,8 +32458,8 @@
           <t>Elizabeth — a scope question rather than a pitch.
 Federal attention to financial education, like every state mandate, concentrates on high school. Thirty states now require a course to graduate. The elementary standards that exist in most states sit underneath that with very little built against them, largely because nothing requires reporting at that band.
 The assumption underneath is that children begin with saving. Saving is the second thing a person does with money. The first is spending — a first grader has handled money at a register and made a decision there with no framework at all.
-I built a free, ungated K–5 resource for that: a 36-page picture book that follows one complete purchase from the idea through the receipt — sale ads, comparison shopping, a markdown, a coupon, sales tax — and a classroom set behind it. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a browser-based pretend register, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education alongside Common Core Math and ELA, CEE and FDIC Money Smart, cited at the Grade 4 benchmark level rather than claimed generally. Sixteen-plus concepts appear in the story without being announced, and a twenty-one-term glossary in the back matter page-references each one to the scene where it occurs.
-No concept is announced in the text; the twenty-one-term glossary in the back matter carries the definitions, each page-referenced to where the term occurs. No account, no email capture, no purchase order. It prints from a browser. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud requiring no instructor training.
+I built a free, ungated K–5 resource for that: a 36-page picture book that follows one complete purchase from the idea through the receipt , sale ads, comparison shopping, a markdown, a coupon, sales tax , and a classroom set behind it. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a browser-based pretend register, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education alongside Common Core Math and ELA, CEE and FDIC Money Smart, cited at the Grade 4 benchmark level rather than claimed generally. Sixteen-plus concepts appear in the story without being announced, and a twenty-one-term glossary in the back matter page-references each one to the scene where it occurs.
+No concept is announced in the text; the twenty-one-term glossary in the back matter carries the definitions, each page-referenced to where the term occurs. No account, no email capture, no purchase order. It prints from a browser. Catalogued Lexile AD 620L , Adult Directed , a one-period read-aloud requiring no instructor training.
 The question: does any Department program or clearinghouse take elementary financial-education material, or is the practical route through the states? A steer on who would know is as useful to me as an answer.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan Bach
@@ -32519,7 +32519,7 @@
         <is>
           <t>Gene — Troutwood is built on showing people the long arc of a decision, which is why I am writing about the very first decision on that arc.
 Everything in financial planning compounds, including the mistakes, and the compounding starts long before anyone opens an account. Mistakes at eleven cost $14. The same mistake at twenty-seven has a credit card attached. The habit doing the compounding was installed at six, in a store, with a parent saying no and no reasoning attached to the no.
-Financial education answers that by teaching children saving. Saving is the second thing a person does with money. The first is spending — and a first grader has done it, at a register, with no framework at all.
+Financial education answers that by teaching children saving. Saving is the second thing a person does with money; the first is spending — and a first grader has done it, at a register, with no framework at all.
 Clarence Gets a Bargain is the picture book for that. One purchase, followed the whole way: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in the book says "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed — so it is a shared read and the parent gets the script rather than a homework assignment. A jar is a storage container. It has never once talked a kid out of anything.
 The claim I would defend hardest is the delayed one, and it is the same claim Troutwood makes about projections: the value is not in the twenty minutes. It is in month eighteen, in a real store, when the kid hits a money moment and the book fires back. Recognition first, then the habit.
 Does the elementary end fit anything Troutwood does, or is that below the floor?
@@ -32701,9 +32701,9 @@
       <c r="K66" s="5" t="inlineStr">
         <is>
           <t>Ed — a narrow question about evidence standards, asked before I go further with something.
-I have built a free K–5 financial-education resource — a 36-page picture book plus a complete classroom set — and crosswalked it to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE and FDIC Money Smart, at the Grade 4 benchmark level. Everything is ungated: no account, no email capture, no purchase order, and it prints from a browser.
+I have built a free K–5 financial-education resource , a 36-page picture book plus a complete classroom set , and crosswalked it to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE and FDIC Money Smart, at the Grade 4 benchmark level. Everything is ungated: no account, no email capture, no purchase order, and it prints from a browser.
 The content premise is that the field has the sequence backwards. Financial education starts children with saving; saving is the second thing a person does with money. The first is spending, and a first grader has already done it at a register. The book follows one complete purchase from the idea through the receipt — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with what was bought. No concept is announced in the text; a twenty-one-term glossary in the back matter carries the definitions, each page-referenced to where the term occurs.
-One structural detail relevant to evaluation: the book is catalogued Lexile AD 620L — Adult Directed — so it is delivered as a shared read between an adult and a child rather than independent reading. That makes it closer to a shared-reading intervention than a curriculum, which may change what kind of evidence would be appropriate.
+One structural detail relevant to evaluation: the book is catalogued Lexile AD 620L , Adult Directed , so it is delivered as a shared read between an adult and a child rather than independent reading. That makes it closer to a shared-reading intervention than a curriculum, which may change what kind of evidence would be appropriate.
 The question: what would a resource like this need in order to be taken seriously on evidence — a pre/post instrument administered at scale, a quasi-experimental design, something else? I would rather build the right study once than assemble the wrong one. And if the honest answer is that no federal pathway exists for elementary material of this kind, that is worth knowing too.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan Bach
@@ -32763,7 +32763,7 @@
         <is>
           <t>Jeff — a question about scope, from someone who has read the SHED closely enough to know what it does and does not ask.
 The survey measures financial outcomes in adults — emergency savings, credit access, unexpected expenses. Those outcomes have long histories. What I have not been able to find, in the SHED or elsewhere, is any measure of when spending competence forms: the ability to stand in front of two prices and choose deliberately rather than by impulse or brand.
-That matters because financial education for children is built almost entirely around saving, and saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has handled money at a register.
+It bears on the whole design, because financial education for children is built almost entirely around saving, and saving is the second thing a person does with money. The first is spending. A first grader has no savings rate; she has handled money at a register.
 I wrote the elementary resource rather than a paper about it. A 36-page picture book that follows one complete purchase — sale ads, comparison shopping, a markdown, a coupon, sales tax, and living with what was bought — plus a free ungated classroom set crosswalked to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE, and FDIC Money Smart. Sixteen-plus concepts, none announced in the text. A twenty-one-term glossary page-referenced into the story.
 For the record on format: Lexile AD 620L, Adult Directed — an adult reads it with the child rather than handing it over.
 The question is narrow. Is there any Federal Reserve work, published or internal, on childhood price competence and later financial outcomes? If it does not exist, that is an answer too, and it tells me whether I am arguing with a consensus or filling a hole.
@@ -32825,7 +32825,7 @@
         <is>
           <t>Annie — you built a product for the exact age band everyone else in this category skips, so you already believe the thing I have been arguing. I want to compare notes rather than pitch you.
 My First Nest Egg puts save, spend, give and invest in front of a young child in physical form. My argument is about which of those a child actually performs first. It is spending — a six-year-old has stood in a store holding money and chosen, years before she has anything to save or invest. The category teaches saving first anyway, and I could not find the book that teaches the other one.
-So I wrote and illustrated it. Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed — read with a grown-up rather than handed over. There is also a free browser-based pretend register behind it that runs a markdown, a coupon and sales tax, which is the closest thing I have to your physical product. Nobody has ever formed a money habit by looking at a jar.
+So I wrote and illustrated it. Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose. Idea to post-receipt. Sixteen-plus concepts, none announced; a twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed — read with a grown-up rather than handed over. There is also a free browser-based pretend register behind it that runs a markdown, a coupon and sales tax, which is the closest thing I have to your physical product. Nobody has ever formed a money habit by looking at a jar.
 Those look complementary rather than competing to me: yours gives a kid the categories in their hands, mine walks them through the mechanics of one transaction in twenty minutes.
 Worth a conversation about whether they belong near each other? And separately — if you think spending-before-saving is wrong, you are one of very few people whose disagreement would actually change my mind.
 https://heyzine.com/flip-book/eeb1ef6cff.html
@@ -32883,9 +32883,9 @@
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>Sandy — FCCLA members are a decade older than my readers, so this is not a curriculum pitch. It is a service-project one, and I think it's a good one.
+          <t>Sandy — FCCLA members are a decade older than my readers, so take this as a service-project idea rather than a curriculum pitch. I think it's a good one.
 Your chapters run community service. A high schooler reading a money book to a second-grade class is about the cleanest version of that I can think of — it needs no budget, no training, and one afternoon.
-The book is Clarence Gets a Bargain, 36 pages, ages 6-10. It follows one purchase the whole way, which is the thing that makes it work as a read-aloud rather than a lecture: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt. Sixteen-plus concepts and nobody in it says "budget" — the twenty-one-term glossary in the back is page-referenced to the story, so the reader can field questions without preparing.
+The book is Clarence Gets a Bargain, 36 pages, ages 6-10. It follows one purchase the whole way, which is the thing that makes it work as a read-aloud rather than a lecture: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt; sixteen-plus concepts and nobody in it says "budget" — the twenty-one-term glossary in the back is page-referenced to the story, so the reader can field questions without preparing.
 The read-aloud is the entire project, so the spec matters. Lexile AD 620L — the AD is Adult Directed, the trade's own code for a book built to be read *with* a child rather than handed to one. About twenty minutes out loud, which is a class visit with time left for questions, and the mother explains every concept inside the text. A high schooler can read it cold to a second-grade class and field the questions straight off the page. Nothing to memorize, nothing to prepare, no training call beforehand.
 There is also a free browser-based pretend register the younger kids can run afterward — a markdown, a coupon, sales tax, and a total that changes in front of them.
 Does that fit how chapters choose service projects, or am I inventing a use case? Everything is free and ungated either way.
@@ -33609,7 +33609,7 @@
           <t>Ron,
 The Opposite of Spoiled is the reason I knew what I was looking for and couldn't find it. This is a column idea, and it works whether or not my book is in it.
 Every children's book about money teaches earning or saving. I read all 25 titles on the ABA Foundation's list to be sure. Piggy banks, lemonade stands, three jars labeled spend-save-give where "spend" gets one page and a guilty look.
-But saving is the second thing a child does with money. The first is spending. A six-year-old has no savings rate and no income. What she has done is stand at a register holding a birthday five and decide. Spending is the first financial act a person performs, and the entire category skipped it for forty years.
+But saving is the second thing a child does with money; the first is spending. A six-year-old has no savings rate and no income. What she has done is stand at a register holding a birthday five and decide. Spending is the first financial act a person performs, and the entire category skipped it for forty years.
 The timing gap sharpens it. Thirty states now guarantee a personal finance course — in high school. Money habits are largely set by seven. We're preparing children for 65 and sending them to the register unarmed today, into a store that spent millions working out how to get the five dollars in their hand.
 I wrote the book I couldn't find. Clarence Gets a Bargain, ages 6–10, one kid and one complete purchase: earning it, the sale ads at the kitchen table, two models compared on a shelf, the cheaper one taken deliberately, a coupon at the register, sales tax, and living with the thing afterward. Idea to post-receipt. Sixteen-plus concepts, none of them announced — nobody in the book says the word "budget." The reader doesn't work out he's been schooled until he reaches the glossary in the back, twenty-one terms, each one page-referenced to the scene where it happened.
 I'm an attorney, which shows: the mother photographs the receipt before the car leaves the parking lot, every time, because a receipt is what makes a return or a warranty claim winnable. Kids are consumers years before anyone tells them they have rights as one. That's a second column and possibly a better one.

--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -994,9 +994,9 @@
           <t>Kim — you review children's books for a living, so you have read more well-meaning money picture books than anyone should have to, and you already know the problem with them.
 They all teach saving. A piggy bank, a lemonade stand, a lesson. Which is fine advice in the wrong order, because saving is the second thing a child does with money; the first is spending. A six-year-old has no savings rate and has absolutely stood in a store holding money and had to decide.
 Mine is the spending one, and it follows a single purchase the whole distance rather than gesturing at the idea: a boy wants a robot, earns it with chores and grades, works the sale ads at the kitchen table, compares two models in the aisle, takes the cheaper one on purpose, hands a coupon to the cashier, gets hit with sales tax, and then has to live with the thing. Idea to post-receipt. I read all 25 on the ABA Foundation's list to be sure nobody had done it. Nobody had.
-What I'd actually want your eye on is the smuggling. Sixteen-plus concepts and not one of them is announced , no character stops to explain a term, nobody says "budget." The reader does not know he's been schooled until he reaches the glossary , twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than a homework appendix. The reveal is deliberate and it is on the last page. That balance is the hardest thing in the book and the thing most likely to be off by a hair.
+What I'd actually want your eye on is the smuggling. Sixteen-plus concepts and not one of them is announced — no character stops to explain a term, nobody says "budget." The reader does not know he's been schooled until he reaches the glossary — twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than a homework appendix. The reveal is deliberate and it is on the last page. That balance is the hardest thing in the book and the thing most likely to be off by a hair.
 One thing I'd want you to test rather than take on faith: whether it clicks later. The book is built to fire back months on, in a real store — "is the newer one really better? Clarence checked." Recognition first, then the habit. If that isn't actually in the pages, I'd want to know.
-The other thing worth your reviewer's ear: it is built to be read aloud, and Lexile has it at AD 620L — Adult Directed, read-with rather than read-alone. The mother carries the exposition, which means the adult holding the book is handed the script. Whether that voice actually holds up out loud , across a classroom, a couch, and a grandparent's lap , is something you would hear in a page and I can only guess at.
+The other thing worth your reviewer's ear: it is built to be read aloud, and Lexile has it at AD 620L — Adult Directed, read-with rather than read-alone. The mother carries the exposition, which means the adult holding the book is handed the script. Whether that voice actually holds up out loud — across a classroom, a couch, and a grandparent's lap — is something you would hear in a page and I can only guess at.
 Would you read it as an editor rather than as a friend? I would rather hear where it sags than be told it's charming.
 clarencegetsabargain.com/press-kit.html · https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -1238,9 +1238,9 @@
         <is>
           <t>Cinders — Moneybunnies splits money into Earn, Save, Spend and Give, which makes you the one person in this category who already agreed with me before I showed up.
 I went deep on one of your four. Spending, and specifically the whole transaction rather than the idea of it. Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then has to live with what he picked. Idea to post-receipt.
-The reason I think it sits beside Moneybunnies rather than against it: you give a child the four categories, and mine walks them through the mechanics of one. Sixteen-plus concepts, none announced , nobody says "budget" , and twenty-one terms in a glossary in the back, each page-referenced to the scene where it happened.
+The reason I think it sits beside Moneybunnies rather than against it: you give a child the four categories, and mine walks them through the mechanics of one. Sixteen-plus concepts, none announced — nobody says "budget" — and twenty-one terms in a glossary in the back, each page-referenced to the scene where it happened.
 Author-illustrator to author-illustrator: I did the art as well, so I know exactly how much of the work nobody sees. I'd rather you saw this from me than off a shelf.
-The read-aloud is the other half of it. Lexile AD 620L , Adult Directed , written for the adult voice in the room rather than for a child alone, with the mother carrying the explanations so the grown-up gets handed the script. You will know better than most how much that changes what has to happen on the page.
+The read-aloud is the other half of it. Lexile AD 620L — Adult Directed — written for the adult voice in the room rather than for a child alone, with the mother carrying the explanations so the grown-up gets handed the script. You will know better than most how much that changes what has to happen on the page.
 Trade copies? I'll read yours properly and tell you the truth about it, which is the only thing worth trading.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -2050,8 +2050,8 @@
         <is>
           <t>Tom — you got more genuine engagement out of one post about kids and money than anyone else in this category has managed, which tells me you know exactly which part of this parents actually care about. I would like to check my premise against that.
 My premise: the whole field has the sequence backwards. Financial education starts children with saving. Saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, standing in a store holding a birthday five, working out whether the thing is worth what it costs. We teach the second thing first and the first thing never.
-So I wrote and illustrated the spending book. Clarence Gets a Bargain follows one purchase the whole way , a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax and objects to it, and then lives with what he chose. Idea to post-receipt; sixteen-plus concepts and nobody in the book says "budget." The reader works out he has been schooled only at the glossary , twenty-one terms in the back, page-referenced to the scene each came from. A jar is a storage container. It has never once talked a kid out of anything.
-The instruction underneath the whole book is four words long: stop bringing kids to the store as cargo, bring them as staff. Catalogued Lexile AD 620L , Adult Directed , so the parent gets handed the script rather than an assignment, which I suspect is why your posts land: parents want the conversation and do not feel qualified to start it.
+So I wrote and illustrated the spending book. Clarence Gets a Bargain follows one purchase the whole way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax and objects to it, and then lives with what he chose. Idea to post-receipt; sixteen-plus concepts and nobody in the book says "budget." The reader works out he has been schooled only at the glossary — twenty-one terms in the back, page-referenced to the scene each came from. A jar is a storage container. It has never once talked a kid out of anything.
+The instruction underneath the whole book is four words long: stop bringing kids to the store as cargo, bring them as staff. Catalogued Lexile AD 620L — Adult Directed — so the parent gets handed the script rather than an assignment, which I suspect is why your posts land: parents want the conversation and do not feel qualified to start it.
 The thing I would actually value: you know what makes a parent stop scrolling on this subject and what makes them scroll past. If "spending before saving" is the wrong hook, I would rather hear it from you than keep testing it slowly.
 Would you look and tell me? https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -3079,8 +3079,8 @@
           <t>Stacy — you write about what happens to ordinary people inside financial systems. There is a version of that beat with no coverage at all, and it starts at about age six.
 A child becomes a consumer the first time they hand money to a cashier. Not at eighteen, not at a first paycheck — at six, with a birthday five. From that moment they are party to a transaction and they have rights nobody mentions: the receipt is proof, the price on the shelf has to match the price at the register, a broken thing can go back. Consumer education is the missing wing of children's financial literacy. We teach them to save and never tell them they are already the buyer.
 That is why I wrote the book. Clarence Gets a Bargain follows one purchase the entire way — a boy wants a robot, earns it, reads the sale inserts at the kitchen table, compares two on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt; sixteen-plus concepts, none announced, and a twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
-The detail people ask me about: the mother photographs the receipt the second she sits down in the car. Every time. It takes four seconds and it is what makes a return, an exchange or a warranty claim winnable. Almost nobody teaches a child that, which is why the book is catalogued AD 620L , Adult Directed , and gets read with an adult rather than handed to a kid alone.
-I am an attorney, and on vacation that mostly means the souvenirs get cross-examined. The hermit crab: who feeds it over the holidays, and in two weeks when it dies , and buddy, it will , is it worth the tears? My kids find this insufferable. It is also the entire skill.
+The detail people ask me about: the mother photographs the receipt the second she sits down in the car. Every time. It takes four seconds and it is what makes a return, an exchange or a warranty claim winnable. Almost nobody teaches a child that, which is why the book is catalogued AD 620L — Adult Directed — and gets read with an adult rather than handed to a kid alone.
+I am an attorney, and on vacation that mostly means the souvenirs get cross-examined. The hermit crab: who feeds it over the holidays, and in two weeks when it dies — and buddy, it will — is it worth the tears? My kids find this insufferable. It is also the entire skill.
 The honest version of the beat problem: the full picture crosses agencies. Warranties and returns sit with the FTC, product safety with the CPSC. Nobody owns "children as consumers," which may be exactly why nobody covers it.
 Is there a story in that? clarencegetsabargain.com/press-kit.html
 Jonathan</t>
@@ -3633,8 +3633,8 @@
           <t>Prince — you took investing, which is the hardest concept in this category to make readable for children, and made it a series a kid comes back to. I went the opposite direction on the same shelf and I would like your read on it.
 Wesley learns to invest. Clarence learns to spend — and I mean the mechanics of it rather than the idea. Every other book in the category teaches saving, which is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. Nobody had written that one, so I did.
 Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt; sixteen-plus concepts, none of them announced. Nobody says the word "budget."
-The craft problem I would most like another author's view on: the reader is not supposed to know he has been taught anything until he reaches the glossary , twenty-one terms in the back, each page-referenced to the scene it came from. Getting that balance right, so it stays a story, was the whole job, and it is the thing most likely to be off by a hair. The rest of the shelf is piggy banks with plots. Good ones, some of them , but none of them has ever been to a register.
-I did the illustrations too, which means my opinion of them is worth nothing. It is written for the adult voice in the room , catalogued AD 620L, Adult Directed , with the mother carrying every explanation.
+The craft problem I would most like another author's view on: the reader is not supposed to know he has been taught anything until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. Getting that balance right, so it stays a story, was the whole job, and it is the thing most likely to be off by a hair. The rest of the shelf is piggy banks with plots. Good ones, some of them — but none of them has ever been to a register.
+I did the illustrations too, which means my opinion of them is worth nothing. It is written for the adult voice in the room — catalogued AD 620L, Adult Directed — with the mother carrying every explanation.
 Trade? Send me a Wesley and I will read it properly rather than politely.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -5776,9 +5776,9 @@
         <is>
           <t>Roda — you built a 30-Day Smart Spending Challenge. Not a saving challenge. Spending. As far as I can tell that makes two of us in this entire category who think the sequence is backwards.
 Here is my version of the argument, and I'd like to know whether it matches how you arrived at yours. Every children's money book teaches saving — I read all 25 on the ABA Foundation's list to be sure. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. We teach the second thing first and the first thing never.
-Clarence Gets a Bargain is the picture-book version. It follows a single purchase the whole distance , a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced; nobody says "budget." Twenty-one terms in a glossary at the end, each page-referenced to where it happened , which is the only point at which a kid works out he's been schooled.
-One story takes a kid from "I want it" to "Is it worth it?" , which I suspect is the same door your Challenge walks them through, thirty days at a time. Yours is a habit; mine is one transaction read in twenty minutes. Those look complementary to me rather than competing , the book could be the on-ramp to a challenge, or the thing a parent reads on day one.
-One thing your Challenge and the book share: neither one works with a kid alone in a room. It is Lexile AD 620L , Adult Directed, the trade's code for read-with rather than read-alone , and the mother explains every concept on the page, so whoever is reading gets handed the script. Parent, teacher or grandparent, the reading stops every few pages because the kid asks something.
+Clarence Gets a Bargain is the picture-book version. It follows a single purchase the whole distance — a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced; nobody says "budget." Twenty-one terms in a glossary at the end, each page-referenced to where it happened — which is the only point at which a kid works out he's been schooled.
+One story takes a kid from "I want it" to "Is it worth it?" — which I suspect is the same door your Challenge walks them through, thirty days at a time. Yours is a habit; mine is one transaction read in twenty minutes. Those look complementary to me rather than competing — the book could be the on-ramp to a challenge, or the thing a parent reads on day one.
+One thing your Challenge and the book share: neither one works with a kid alone in a room. It is Lexile AD 620L — Adult Directed, the trade's code for read-with rather than read-alone — and the mother explains every concept on the page, so whoever is reading gets handed the script. Parent, teacher or grandparent, the reading stops every few pages because the kid asks something.
 Worth a conversation? I'd rather compare notes with the one other person who put spending first than pitch anybody.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -7108,8 +7108,8 @@
           <t>ML — you built a series a child comes back to, which is harder than writing one good book, and it's the reason I'm writing to a peer rather than a gatekeeper.
 Mine is a money book, which I appreciate is the least promising sentence in children's publishing. So here is the part that makes it not that.
 Every book in this category teaches saving. Saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it — in a store, holding money, deciding whether the thing is worth what it costs. So mine follows one purchase from the idea to after the receipt: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose.
-The craft problem I'd most like another author's view on: I smuggled sixteen-plus concepts in without announcing any of them. Nobody says "budget." The glossary in the back , twenty-one terms, each page-referenced to the scene it came from , is the only place the book admits it was teaching. Getting that balance right, so it stays a story, was the whole job.
-The other half of the craft problem: it is written for an adult voice. Lexile AD 620L , Adult Directed , with the mother carrying every explanation, so whoever reads aloud gets handed the script. A series lives or dies on whether the grown-up still enjoys the fourth reading. You would know inside a page whether mine does.
+The craft problem I'd most like another author's view on: I smuggled sixteen-plus concepts in without announcing any of them. Nobody says "budget." The glossary in the back — twenty-one terms, each page-referenced to the scene it came from — is the only place the book admits it was teaching. Getting that balance right, so it stays a story, was the whole job.
+The other half of the craft problem: it is written for an adult voice. Lexile AD 620L — Adult Directed — with the mother carrying every explanation, so whoever reads aloud gets handed the script. A series lives or dies on whether the grown-up still enjoys the fourth reading. You would know inside a page whether mine does.
 Would you read it and tell me where it stops being a story? I'll trade — send me a Noah and I'll read it properly.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -17433,8 +17433,8 @@
           <t>Elizabeth — a scope question rather than a pitch.
 Federal attention to financial education, like every state mandate, concentrates on high school. Thirty states now require a course to graduate. The elementary standards that exist in most states sit underneath that with very little built against them, largely because nothing requires reporting at that band.
 The assumption underneath is that children begin with saving. Saving is the second thing a person does with money. The first is spending — a first grader has handled money at a register and made a decision there with no framework at all.
-I built a free, ungated K–5 resource for that: a 36-page picture book that follows one complete purchase from the idea through the receipt , sale ads, comparison shopping, a markdown, a coupon, sales tax , and a classroom set behind it. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a browser-based pretend register, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education alongside Common Core Math and ELA, CEE and FDIC Money Smart, cited at the Grade 4 benchmark level rather than claimed generally. Sixteen-plus concepts appear in the story without being announced, and a twenty-one-term glossary in the back matter page-references each one to the scene where it occurs.
-No concept is announced in the text; the twenty-one-term glossary in the back matter carries the definitions, each page-referenced to where the term occurs. No account, no email capture, no purchase order. It prints from a browser. Catalogued Lexile AD 620L , Adult Directed , a one-period read-aloud requiring no instructor training.
+I built a free, ungated K–5 resource for that: a 36-page picture book that follows one complete purchase from the idea through the receipt — sale ads, comparison shopping, a markdown, a coupon, sales tax — and a classroom set behind it. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a browser-based pretend register, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education alongside Common Core Math and ELA, CEE and FDIC Money Smart, cited at the Grade 4 benchmark level rather than claimed generally. Sixteen-plus concepts appear in the story without being announced, and a twenty-one-term glossary in the back matter page-references each one to the scene where it occurs.
+No concept is announced in the text; the twenty-one-term glossary in the back matter carries the definitions, each page-referenced to where the term occurs. No account, no email capture, no purchase order. It prints from a browser. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud requiring no instructor training.
 The question: does any Department program or clearinghouse take elementary financial-education material, or is the practical route through the states? A steer on who would know is as useful to me as an answer.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan Bach
@@ -22046,9 +22046,9 @@
       <c r="K523" s="5" t="inlineStr">
         <is>
           <t>Ed — a narrow question about evidence standards, asked before I go further with something.
-I have built a free K–5 financial-education resource , a 36-page picture book plus a complete classroom set , and crosswalked it to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE and FDIC Money Smart, at the Grade 4 benchmark level. Everything is ungated: no account, no email capture, no purchase order, and it prints from a browser.
+I have built a free K–5 financial-education resource — a 36-page picture book plus a complete classroom set — and crosswalked it to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE and FDIC Money Smart, at the Grade 4 benchmark level. Everything is ungated: no account, no email capture, no purchase order, and it prints from a browser.
 The content premise is that the field has the sequence backwards. Financial education starts children with saving; saving is the second thing a person does with money. The first is spending, and a first grader has already done it at a register. The book follows one complete purchase from the idea through the receipt — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with what was bought. No concept is announced in the text; a twenty-one-term glossary in the back matter carries the definitions, each page-referenced to where the term occurs.
-One structural detail relevant to evaluation: the book is catalogued Lexile AD 620L , Adult Directed , so it is delivered as a shared read between an adult and a child rather than independent reading. That makes it closer to a shared-reading intervention than a curriculum, which may change what kind of evidence would be appropriate.
+One structural detail relevant to evaluation: the book is catalogued Lexile AD 620L — Adult Directed — so it is delivered as a shared read between an adult and a child rather than independent reading. That makes it closer to a shared-reading intervention than a curriculum, which may change what kind of evidence would be appropriate.
 The question: what would a resource like this need in order to be taken seriously on evidence — a pre/post instrument administered at scale, a quasi-experimental design, something else? I would rather build the right study once than assemble the wrong one. And if the honest answer is that no federal pathway exists for elementary material of this kind, that is worth knowing too.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan Bach
@@ -28613,8 +28613,8 @@
 Clarence Gets a Bargain carries a reading level of Lexile AD 620L. The AD stands for "Adult Directed" — the book industry's own label for a title meant to be read WITH a child rather than handed to one. That code isn't an accident. I built the book for the couch, not the corner.
 Here's why. In the story, Clarence doesn't learn about money from a worksheet. He learns it from his mom — at the kitchen table with the sale ads, in the car, in the middle of the store. Read the book to your kid and you aren't describing that scene. You're in it.
 And the interruptions will come. "Do we have a 529?" "Why do you take pictures of receipts?" "Can I hand the cashier the coupon next time?" "Is the internet a need or a want?" A kid alone in the corner reads a robot story and moves on. A kid pressed against your shoulder reads the same story and starts an argument about whether Wi-Fi counts as shelter. You want that argument. The argument is the product; the robot is the delivery vehicle.
-Every other money book for kids teaches saving, which is the second thing a child does with money. Spending is the first, and this one follows a single purchase the whole way , the sale ads, the aisle, the markdown, the coupon, the sales tax, and living with what got bought. Sixteen or more money concepts are in there and not one of them is announced. Nobody says the word "budget." Your kid won't know she's been taught anything until she reaches the glossary at the back , which is the last page, on purpose.
-You don't need to know anything about finance to do this well. Mom explains everything to Clarence inside the story , sale ads, clearance, markdowns, sales tax , so your only job is to read her lines like you knew it all along. I wrote you the script. Take the credit.
+Every other money book for kids teaches saving, which is the second thing a child does with money. Spending is the first, and this one follows a single purchase the whole way — the sale ads, the aisle, the markdown, the coupon, the sales tax, and living with what got bought. Sixteen or more money concepts are in there and not one of them is announced. Nobody says the word "budget." Your kid won't know she's been taught anything until she reaches the glossary at the back — which is the last page, on purpose.
+You don't need to know anything about finance to do this well. Mom explains everything to Clarence inside the story — sale ads, clearance, markdowns, sales tax — so your only job is to read her lines like you knew it all along. I wrote you the script. Take the credit.
 Two parts of the book flat-out require company:
 The grocery game, page 27. Whoever spots the biggest savings wins; the loser carries the bags in from the car. A kid cannot play this alone. That's the point.
 "Guess the Price," page 28. After dinner, somebody shares a deal they got that day and everyone guesses what it cost. Clarence guesses last and lowest, every time — his logic being that if a price is low enough to brag about at dinner, it has to be really low. Three players minimum. Grandma counts.
@@ -29033,9 +29033,9 @@
           <t>Kim — you review children's books for a living, so you have read more well-meaning money picture books than anyone should have to, and you already know the problem with them.
 They all teach saving. A piggy bank, a lemonade stand, a lesson. Which is fine advice in the wrong order, because saving is the second thing a child does with money; the first is spending. A six-year-old has no savings rate and has absolutely stood in a store holding money and had to decide.
 Mine is the spending one, and it follows a single purchase the whole distance rather than gesturing at the idea: a boy wants a robot, earns it with chores and grades, works the sale ads at the kitchen table, compares two models in the aisle, takes the cheaper one on purpose, hands a coupon to the cashier, gets hit with sales tax, and then has to live with the thing. Idea to post-receipt. I read all 25 on the ABA Foundation's list to be sure nobody had done it. Nobody had.
-What I'd actually want your eye on is the smuggling. Sixteen-plus concepts and not one of them is announced , no character stops to explain a term, nobody says "budget." The reader does not know he's been schooled until he reaches the glossary , twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than a homework appendix. The reveal is deliberate and it is on the last page. That balance is the hardest thing in the book and the thing most likely to be off by a hair.
+What I'd actually want your eye on is the smuggling. Sixteen-plus concepts and not one of them is announced — no character stops to explain a term, nobody says "budget." The reader does not know he's been schooled until he reaches the glossary — twenty-one terms, each page-referenced to the scene it came from, working as a decoder rather than a homework appendix. The reveal is deliberate and it is on the last page. That balance is the hardest thing in the book and the thing most likely to be off by a hair.
 One thing I'd want you to test rather than take on faith: whether it clicks later. The book is built to fire back months on, in a real store — "is the newer one really better? Clarence checked." Recognition first, then the habit. If that isn't actually in the pages, I'd want to know.
-The other thing worth your reviewer's ear: it is built to be read aloud, and Lexile has it at AD 620L — Adult Directed, read-with rather than read-alone. The mother carries the exposition, which means the adult holding the book is handed the script. Whether that voice actually holds up out loud , across a classroom, a couch, and a grandparent's lap , is something you would hear in a page and I can only guess at.
+The other thing worth your reviewer's ear: it is built to be read aloud, and Lexile has it at AD 620L — Adult Directed, read-with rather than read-alone. The mother carries the exposition, which means the adult holding the book is handed the script. Whether that voice actually holds up out loud — across a classroom, a couch, and a grandparent's lap — is something you would hear in a page and I can only guess at.
 Would you read it as an editor rather than as a friend? I would rather hear where it sags than be told it's charming.
 clarencegetsabargain.com/press-kit.html · https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -29277,9 +29277,9 @@
         <is>
           <t>Cinders — Moneybunnies splits money into Earn, Save, Spend and Give, which makes you the one person in this category who already agreed with me before I showed up.
 I went deep on one of your four. Spending, and specifically the whole transaction rather than the idea of it. Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then has to live with what he picked. Idea to post-receipt.
-The reason I think it sits beside Moneybunnies rather than against it: you give a child the four categories, and mine walks them through the mechanics of one. Sixteen-plus concepts, none announced , nobody says "budget" , and twenty-one terms in a glossary in the back, each page-referenced to the scene where it happened.
+The reason I think it sits beside Moneybunnies rather than against it: you give a child the four categories, and mine walks them through the mechanics of one. Sixteen-plus concepts, none announced — nobody says "budget" — and twenty-one terms in a glossary in the back, each page-referenced to the scene where it happened.
 Author-illustrator to author-illustrator: I did the art as well, so I know exactly how much of the work nobody sees. I'd rather you saw this from me than off a shelf.
-The read-aloud is the other half of it. Lexile AD 620L , Adult Directed , written for the adult voice in the room rather than for a child alone, with the mother carrying the explanations so the grown-up gets handed the script. You will know better than most how much that changes what has to happen on the page.
+The read-aloud is the other half of it. Lexile AD 620L — Adult Directed — written for the adult voice in the room rather than for a child alone, with the mother carrying the explanations so the grown-up gets handed the script. You will know better than most how much that changes what has to happen on the page.
 Trade copies? I'll read yours properly and tell you the truth about it, which is the only thing worth trading.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -30089,8 +30089,8 @@
         <is>
           <t>Tom — you got more genuine engagement out of one post about kids and money than anyone else in this category has managed, which tells me you know exactly which part of this parents actually care about. I would like to check my premise against that.
 My premise: the whole field has the sequence backwards. Financial education starts children with saving. Saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, standing in a store holding a birthday five, working out whether the thing is worth what it costs. We teach the second thing first and the first thing never.
-So I wrote and illustrated the spending book. Clarence Gets a Bargain follows one purchase the whole way , a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax and objects to it, and then lives with what he chose. Idea to post-receipt; sixteen-plus concepts and nobody in the book says "budget." The reader works out he has been schooled only at the glossary , twenty-one terms in the back, page-referenced to the scene each came from. A jar is a storage container. It has never once talked a kid out of anything.
-The instruction underneath the whole book is four words long: stop bringing kids to the store as cargo, bring them as staff. Catalogued Lexile AD 620L , Adult Directed , so the parent gets handed the script rather than an assignment, which I suspect is why your posts land: parents want the conversation and do not feel qualified to start it.
+So I wrote and illustrated the spending book. Clarence Gets a Bargain follows one purchase the whole way — a boy wants a robot, earns it with chores and grades, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands a coupon to the cashier, meets sales tax and objects to it, and then lives with what he chose. Idea to post-receipt; sixteen-plus concepts and nobody in the book says "budget." The reader works out he has been schooled only at the glossary — twenty-one terms in the back, page-referenced to the scene each came from. A jar is a storage container. It has never once talked a kid out of anything.
+The instruction underneath the whole book is four words long: stop bringing kids to the store as cargo, bring them as staff. Catalogued Lexile AD 620L — Adult Directed — so the parent gets handed the script rather than an assignment, which I suspect is why your posts land: parents want the conversation and do not feel qualified to start it.
 The thing I would actually value: you know what makes a parent stop scrolling on this subject and what makes them scroll past. If "spending before saving" is the wrong hook, I would rather hear it from you than keep testing it slowly.
 Would you look and tell me? https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -31118,8 +31118,8 @@
           <t>Stacy — you write about what happens to ordinary people inside financial systems. There is a version of that beat with no coverage at all, and it starts at about age six.
 A child becomes a consumer the first time they hand money to a cashier. Not at eighteen, not at a first paycheck — at six, with a birthday five. From that moment they are party to a transaction and they have rights nobody mentions: the receipt is proof, the price on the shelf has to match the price at the register, a broken thing can go back. Consumer education is the missing wing of children's financial literacy. We teach them to save and never tell them they are already the buyer.
 That is why I wrote the book. Clarence Gets a Bargain follows one purchase the entire way — a boy wants a robot, earns it, reads the sale inserts at the kitchen table, compares two on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt; sixteen-plus concepts, none announced, and a twenty-one-term glossary in the back, each entry page-referenced to the scene it came from.
-The detail people ask me about: the mother photographs the receipt the second she sits down in the car. Every time. It takes four seconds and it is what makes a return, an exchange or a warranty claim winnable. Almost nobody teaches a child that, which is why the book is catalogued AD 620L , Adult Directed , and gets read with an adult rather than handed to a kid alone.
-I am an attorney, and on vacation that mostly means the souvenirs get cross-examined. The hermit crab: who feeds it over the holidays, and in two weeks when it dies , and buddy, it will , is it worth the tears? My kids find this insufferable. It is also the entire skill.
+The detail people ask me about: the mother photographs the receipt the second she sits down in the car. Every time. It takes four seconds and it is what makes a return, an exchange or a warranty claim winnable. Almost nobody teaches a child that, which is why the book is catalogued AD 620L — Adult Directed — and gets read with an adult rather than handed to a kid alone.
+I am an attorney, and on vacation that mostly means the souvenirs get cross-examined. The hermit crab: who feeds it over the holidays, and in two weeks when it dies — and buddy, it will — is it worth the tears? My kids find this insufferable. It is also the entire skill.
 The honest version of the beat problem: the full picture crosses agencies. Warranties and returns sit with the FTC, product safety with the CPSC. Nobody owns "children as consumers," which may be exactly why nobody covers it.
 Is there a story in that? clarencegetsabargain.com/press-kit.html
 Jonathan</t>
@@ -31672,8 +31672,8 @@
           <t>Prince — you took investing, which is the hardest concept in this category to make readable for children, and made it a series a kid comes back to. I went the opposite direction on the same shelf and I would like your read on it.
 Wesley learns to invest. Clarence learns to spend — and I mean the mechanics of it rather than the idea. Every other book in the category teaches saving, which is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. Nobody had written that one, so I did.
 Clarence Gets a Bargain follows a single purchase from beginning to end: a boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one deliberately, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt; sixteen-plus concepts, none of them announced. Nobody says the word "budget."
-The craft problem I would most like another author's view on: the reader is not supposed to know he has been taught anything until he reaches the glossary , twenty-one terms in the back, each page-referenced to the scene it came from. Getting that balance right, so it stays a story, was the whole job, and it is the thing most likely to be off by a hair. The rest of the shelf is piggy banks with plots. Good ones, some of them , but none of them has ever been to a register.
-I did the illustrations too, which means my opinion of them is worth nothing. It is written for the adult voice in the room , catalogued AD 620L, Adult Directed , with the mother carrying every explanation.
+The craft problem I would most like another author's view on: the reader is not supposed to know he has been taught anything until he reaches the glossary — twenty-one terms in the back, each page-referenced to the scene it came from. Getting that balance right, so it stays a story, was the whole job, and it is the thing most likely to be off by a hair. The rest of the shelf is piggy banks with plots. Good ones, some of them — but none of them has ever been to a register.
+I did the illustrations too, which means my opinion of them is worth nothing. It is written for the adult voice in the room — catalogued AD 620L, Adult Directed — with the mother carrying every explanation.
 Trade? Send me a Wesley and I will read it properly rather than politely.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -31789,9 +31789,9 @@
         <is>
           <t>Roda — you built a 30-Day Smart Spending Challenge. Not a saving challenge. Spending. As far as I can tell that makes two of us in this entire category who think the sequence is backwards.
 Here is my version of the argument, and I'd like to know whether it matches how you arrived at yours. Every children's money book teaches saving — I read all 25 on the ABA Foundation's list to be sure. But saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it, in a store, holding money, deciding whether the thing is worth what it costs. We teach the second thing first and the first thing never.
-Clarence Gets a Bargain is the picture-book version. It follows a single purchase the whole distance , a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced; nobody says "budget." Twenty-one terms in a glossary at the end, each page-referenced to where it happened , which is the only point at which a kid works out he's been schooled.
-One story takes a kid from "I want it" to "Is it worth it?" , which I suspect is the same door your Challenge walks them through, thirty days at a time. Yours is a habit; mine is one transaction read in twenty minutes. Those look complementary to me rather than competing , the book could be the on-ramp to a challenge, or the thing a parent reads on day one.
-One thing your Challenge and the book share: neither one works with a kid alone in a room. It is Lexile AD 620L , Adult Directed, the trade's code for read-with rather than read-alone , and the mother explains every concept on the page, so whoever is reading gets handed the script. Parent, teacher or grandparent, the reading stops every few pages because the kid asks something.
+Clarence Gets a Bargain is the picture-book version. It follows a single purchase the whole distance — a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he picked. Idea to post-receipt. Sixteen-plus concepts, none of them announced; nobody says "budget." Twenty-one terms in a glossary at the end, each page-referenced to where it happened — which is the only point at which a kid works out he's been schooled.
+One story takes a kid from "I want it" to "Is it worth it?" — which I suspect is the same door your Challenge walks them through, thirty days at a time. Yours is a habit; mine is one transaction read in twenty minutes. Those look complementary to me rather than competing — the book could be the on-ramp to a challenge, or the thing a parent reads on day one.
+One thing your Challenge and the book share: neither one works with a kid alone in a room. It is Lexile AD 620L — Adult Directed, the trade's code for read-with rather than read-alone — and the mother explains every concept on the page, so whoever is reading gets handed the script. Parent, teacher or grandparent, the reading stops every few pages because the kid asks something.
 Worth a conversation? I'd rather compare notes with the one other person who put spending first than pitch anybody.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -31905,8 +31905,8 @@
           <t>ML — you built a series a child comes back to, which is harder than writing one good book, and it's the reason I'm writing to a peer rather than a gatekeeper.
 Mine is a money book, which I appreciate is the least promising sentence in children's publishing. So here is the part that makes it not that.
 Every book in this category teaches saving. Saving is the second thing a child does with money. The first is spending, and a six-year-old has already done it — in a store, holding money, deciding whether the thing is worth what it costs. So mine follows one purchase from the idea to after the receipt: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then lives with what he chose.
-The craft problem I'd most like another author's view on: I smuggled sixteen-plus concepts in without announcing any of them. Nobody says "budget." The glossary in the back , twenty-one terms, each page-referenced to the scene it came from , is the only place the book admits it was teaching. Getting that balance right, so it stays a story, was the whole job.
-The other half of the craft problem: it is written for an adult voice. Lexile AD 620L , Adult Directed , with the mother carrying every explanation, so whoever reads aloud gets handed the script. A series lives or dies on whether the grown-up still enjoys the fourth reading. You would know inside a page whether mine does.
+The craft problem I'd most like another author's view on: I smuggled sixteen-plus concepts in without announcing any of them. Nobody says "budget." The glossary in the back — twenty-one terms, each page-referenced to the scene it came from — is the only place the book admits it was teaching. Getting that balance right, so it stays a story, was the whole job.
+The other half of the craft problem: it is written for an adult voice. Lexile AD 620L — Adult Directed — with the mother carrying every explanation, so whoever reads aloud gets handed the script. A series lives or dies on whether the grown-up still enjoys the fourth reading. You would know inside a page whether mine does.
 Would you read it and tell me where it stops being a story? I'll trade — send me a Noah and I'll read it properly.
 https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -32458,8 +32458,8 @@
           <t>Elizabeth — a scope question rather than a pitch.
 Federal attention to financial education, like every state mandate, concentrates on high school. Thirty states now require a course to graduate. The elementary standards that exist in most states sit underneath that with very little built against them, largely because nothing requires reporting at that band.
 The assumption underneath is that children begin with saving. Saving is the second thing a person does with money. The first is spending — a first grader has handled money at a register and made a decision there with no framework at all.
-I built a free, ungated K–5 resource for that: a 36-page picture book that follows one complete purchase from the idea through the receipt , sale ads, comparison shopping, a markdown, a coupon, sales tax , and a classroom set behind it. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a browser-based pretend register, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education alongside Common Core Math and ELA, CEE and FDIC Money Smart, cited at the Grade 4 benchmark level rather than claimed generally. Sixteen-plus concepts appear in the story without being announced, and a twenty-one-term glossary in the back matter page-references each one to the scene where it occurs.
-No concept is announced in the text; the twenty-one-term glossary in the back matter carries the definitions, each page-referenced to where the term occurs. No account, no email capture, no purchase order. It prints from a browser. Catalogued Lexile AD 620L , Adult Directed , a one-period read-aloud requiring no instructor training.
+I built a free, ungated K–5 resource for that: a 36-page picture book that follows one complete purchase from the idea through the receipt — sale ads, comparison shopping, a markdown, a coupon, sales tax — and a classroom set behind it. Four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, printable classroom pieces, a browser-based pretend register, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education alongside Common Core Math and ELA, CEE and FDIC Money Smart, cited at the Grade 4 benchmark level rather than claimed generally. Sixteen-plus concepts appear in the story without being announced, and a twenty-one-term glossary in the back matter page-references each one to the scene where it occurs.
+No concept is announced in the text; the twenty-one-term glossary in the back matter carries the definitions, each page-referenced to where the term occurs. No account, no email capture, no purchase order. It prints from a browser. Catalogued Lexile AD 620L — Adult Directed — a one-period read-aloud requiring no instructor training.
 The question: does any Department program or clearinghouse take elementary financial-education material, or is the practical route through the states? A steer on who would know is as useful to me as an answer.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan Bach
@@ -32701,9 +32701,9 @@
       <c r="K66" s="5" t="inlineStr">
         <is>
           <t>Ed — a narrow question about evidence standards, asked before I go further with something.
-I have built a free K–5 financial-education resource , a 36-page picture book plus a complete classroom set , and crosswalked it to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE and FDIC Money Smart, at the Grade 4 benchmark level. Everything is ungated: no account, no email capture, no purchase order, and it prints from a browser.
+I have built a free K–5 financial-education resource — a 36-page picture book plus a complete classroom set — and crosswalked it to the 2021 National Standards for Personal Financial Education, Common Core Math and ELA, CEE and FDIC Money Smart, at the Grade 4 benchmark level. Everything is ungated: no account, no email capture, no purchase order, and it prints from a browser.
 The content premise is that the field has the sequence backwards. Financial education starts children with saving; saving is the second thing a person does with money. The first is spending, and a first grader has already done it at a register. The book follows one complete purchase from the idea through the receipt — the sale ads, the comparison, the markdown, the coupon, the sales tax, and living with what was bought. No concept is announced in the text; a twenty-one-term glossary in the back matter carries the definitions, each page-referenced to where the term occurs.
-One structural detail relevant to evaluation: the book is catalogued Lexile AD 620L , Adult Directed , so it is delivered as a shared read between an adult and a child rather than independent reading. That makes it closer to a shared-reading intervention than a curriculum, which may change what kind of evidence would be appropriate.
+One structural detail relevant to evaluation: the book is catalogued Lexile AD 620L — Adult Directed — so it is delivered as a shared read between an adult and a child rather than independent reading. That makes it closer to a shared-reading intervention than a curriculum, which may change what kind of evidence would be appropriate.
 The question: what would a resource like this need in order to be taken seriously on evidence — a pre/post instrument administered at scale, a quasi-experimental design, something else? I would rather build the right study once than assemble the wrong one. And if the honest answer is that no federal pathway exists for elementary material of this kind, that is worth knowing too.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan Bach

--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -753,7 +753,8 @@
 The segment worth doing has nothing to do with my book. It's the forty-year hole: why an entire publishing category skipped the cash register. There is a Planet Money episode in that whether or not mine is the book that gets mentioned.
 One structural note, since you make things people take in together: the reading level is Lexile AD 620L, and the AD stands for Adult Directed — the trade's own code for a book meant to be read *with* a child rather than handed to one. That was the design, not the accident. Twenty minutes out loud, interrupted the whole way, and the interruptions are the product. Classroom, kitchen table, grandparent's couch — same pages, same arguments break out.
 Am I wrong that it's a story? clarencegetsabargain.com/book-facts.html has the specs. Four-minute flip: https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
@@ -815,7 +816,8 @@
 The other craft problem, which you will have solved in your own books: it is written to be read aloud by an adult who does not know the material either. Lexile has it at AD 620L — Adult Directed, read-with rather than read-alone — and the mother explains every concept on the page, so whoever is holding the book gets handed the script. Teacher, parent, grandparent, same outcome: the reading stops every few pages because somebody in the room asks a question.
 Would you look at it and tell me where the seams show? I'd trade — send me yours and I'll read it properly, not politely.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
@@ -937,7 +939,8 @@
 Format note, since your audience is adults deciding what to hand a kid: Lexile AD 620L, where AD means Adult Directed — the trade's code for a book meant to be read *with* a child. Not a book you leave in a bedroom. Twenty minutes out loud, and the kid interrupts constantly, which is the whole point. The argument about whether Wi-Fi is a need or a want is the product; the robot is the delivery vehicle.
 Is there an episode in the fact that the entire children's money category skipped the cash register for forty years? I'd rather you took the argument than the book.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
@@ -999,7 +1002,8 @@
 The other thing worth your reviewer's ear: it is built to be read aloud, and Lexile has it at AD 620L — Adult Directed, read-with rather than read-alone. The mother carries the exposition, which means the adult holding the book is handed the script. Whether that voice actually holds up out loud — across a classroom, a couch, and a grandparent's lap — is something you would hear in a page and I can only guess at.
 Would you read it as an editor rather than as a friend? I would rather hear where it sags than be told it's charming.
 clarencegetsabargain.com/press-kit.html · https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
@@ -1060,7 +1064,8 @@
 One design decision I would want your view on. It is written for an adult to read aloud, not for a child alone: Lexile AD 620L, Adult Directed. The mother carries every explanation on the page, so the grown-up gets the script rather than the homework. You spent a career telling parents to have the conversation. This one hands them the conversation and lets them take the credit for it.
 Author to author, I'd like to trade. Send me one of yours and I'll read it properly. And if you think the spending-first premise is wrong, that is worth more to me than a kind word about the illustrations.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
@@ -1117,7 +1122,7 @@
           <t>Joel — a specific question rather than a pitch, and it should take you a minute.
 I have a K-5 resource I would like to list in the Jump$tart Clearinghouse, and I have read the listing criteria closely enough to know which route applies to me. I am not a National Partner and have never listed before, so I would be applying under the letter-of-reference route.
 The resource is a free, ungated classroom set built around a 36-page picture book: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE, and FDIC Money Smart, printable classroom pieces, and a browser-based pretend register. No account, no email capture, no purchase order. It prints from a browser.
-What the book does that the category does not: it teaches spending rather than saving, and it follows one complete purchase from the idea through the receipt — sale ads, comparison, markdown, coupon, sales tax. Sixteen-plus concepts, a twenty-one-term glossary page-referenced to the story. The elementary grade band has standards and very little built against them.
+What the book does that the category does not: it teaches spending rather than saving, and it follows one complete purchase from the idea through the receipt — sale ads, comparison, markdown, coupon, sales tax. Sixteen-plus concepts, none of them announced in the text, and a twenty-one-term glossary page-referenced to the story. The elementary grade band has standards and very little built against them.
 One spec relevant to classroom use: Lexile AD 620L. The AD is Adult Directed — read-aloud with an adult rather than independent reading. It runs one class period, and the mother explains each concept inside the text, so a teacher with no finance background can run it without preparation. The same design makes it work as a family take-home.
 Two questions. Is the free classroom set the right thing to submit, rather than the book? And for the reference letter, would Wally Luckeydoo carry weight — he received your 2026 Corey Carlisle Award and endorsed the book before any of this came up.
 clarencegetsabargain.com/educator-toolkit.html
@@ -1182,7 +1187,8 @@
 The column, if there is one: an entire publishing category has taught children to save for forty years and skipped the cash register, which is the only place a child has ever actually handled money. That is a story about the field, not about me.
 clarencegetsabargain.com/press-kit.html
 Jonathan Bach
-Baltimore</t>
+Baltimore
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
@@ -1243,7 +1249,8 @@
 The read-aloud is the other half of it. Lexile AD 620L — Adult Directed — written for the adult voice in the room rather than for a child alone, with the mother carrying the explanations so the grown-up gets handed the script. You will know better than most how much that changes what has to happen on the page.
 Trade copies? I'll read yours properly and tell you the truth about it, which is the only thing worth trading.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
@@ -1303,7 +1310,8 @@
 For the teacher side: AD 620L — Adult Directed — one class period out loud, with the mother explaining every concept in the text so a teacher without a finance background can run it cold. The same book does the job at a kitchen table with a parent or a grandparent, which is the part elementary teachers actually ask for and rarely get.
 Honest question rather than a pitch: when you talk to teachers, does elementary ever come up as something they want and cannot find? I am trying to work out whether I am filling a gap or inventing one.
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
@@ -1496,7 +1504,8 @@
 And on the read-along specifically, since I raised it: the book is Lexile AD 620L — AD for Adult Directed, the trade's code for read-with rather than read-alone. It is built for somebody to perform. You explain to camera; this hands the explaining to whoever is holding the book — teacher, parent, grandparent — and then the kid interrupts them. Different mechanism, same job.
 Is there a version of this worth putting in front of your audience — a read-along, a segment, a mention? And separately: at sixteen, would this book have been too young for you, or exactly right for the you at six?
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -1558,7 +1567,8 @@
 One more thing about how it gets used, because it changes who it is for. Lexile AD 620L — Adult Directed, the industry's own code for a book meant to be read *with* a child. The mother explains every concept on the page, so the adult reading aloud gets handed the script and does not have to be the one who already knows about money. It counts most in the houses where nobody feels qualified to teach it, which is most houses.
 You know better than almost anyone whether a thing lands with the people it's for. Would you look, and tell me if the six-year-old version of your audience would sit still for it?
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -1812,7 +1822,8 @@
 Two asks, and the second one matters more. Worth a look for the next update to the roundup? And separately — you run a company built on kids and money, so if you think spending-before-saving is wrong, I would rather hear it from you than keep saying it at conferences.
 One line worth having in a roundup, because parents ask it: Lexile AD 620L — Adult Directed, the industry's own code for a book meant to be read *with* a child rather than handed over. Twenty minutes out loud, interrupted the whole way. Grandparents take to it fastest — it gives them something to do with the grandkid instead of something to hand them, and every page has a "that reminds me of the time" sitting in it.
 I'll send a copy either way. https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
@@ -2054,7 +2065,8 @@
 The instruction underneath the whole book is four words long: stop bringing kids to the store as cargo, bring them as staff. Catalogued Lexile AD 620L — Adult Directed — so the parent gets handed the script rather than an assignment, which I suspect is why your posts land: parents want the conversation and do not feel qualified to start it.
 The thing I would actually value: you know what makes a parent stop scrolling on this subject and what makes them scroll past. If "spending before saving" is the wrong hook, I would rather hear it from you than keep testing it slowly.
 Would you look and tell me? https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -2115,7 +2127,8 @@
 Their books are about earning and saving, which is fine, but there is no game in a piggy bank and kids work that out faster than we do. They smell a worksheet through a backpack.
 The episode worth doing has nothing to do with my book. Pitch the forty-year hole: an entire publishing category taught children to save and skipped the cash register, the only place a child has ever actually handled money.
 Worth twenty minutes of your show? https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
@@ -2175,7 +2188,8 @@
 Cataloguing: ISBN 979-8-234-07638-0 · LCCN 2026906164 · hardbound, case bound, full colour, 11×8.5′′ · Est. Lexile AD 620L, Guided Reading L–N · $19.99. The AD is Adult Directed, which makes it a storytime title and a family take-home at the same time. Every fact is on one page: clarencegetsabargain.com/book-facts.html
 Programming is already built and free — printable price tags and clearance stickers for a pretend store, a browser-based register kids run themselves, a five-question quiz with a printable certificate. A storytime plus the pretend store is a complete Money Smart Week event with no prep budget.
 Kids re-read it without being asked, which is the only metric that matters at your desk. Review copy on request?
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -2236,7 +2250,8 @@
 Programming, already built and free: printable price tags and clearance stickers for a pretend store, a browser-based Sea-Mart register children operate themselves with a markdown, a coupon and sales tax, and a quiz with a printable certificate. No prep budget required for a Financial Literacy Month or Money Smart Week event.
 Endorsed by a K–5 educator with 30+ years in the classroom and by the 2026 EIFLE Educator of the Year.
 Shelve it under picture books; file it under secret weapons. Happy to send a review copy — reply with an address?
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
@@ -2296,7 +2311,8 @@
 I wrote the picture book for it. One kid, one purchase, followed the whole way: he wants a robot, earns it, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt; sixteen-plus concepts and nobody in the book says the word "budget." The child works out he has been schooled only when he reaches the glossary — twenty-one terms in the back, each page-referenced to where it happened. It is catalogued Lexile AD 620L, where AD stands for Adult Directed — the trade's own code for a book an adult reads with a child rather than hands over.
 The story here has nothing to do with my book. An entire publishing category taught children to save for forty years and skipped the register, which is the only place a child has ever handled money — while the arcade, the app store and the checkout lane did not skip it at all.
 Is there anything there? clarencegetsabargain.com/press-kit.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -2356,7 +2372,8 @@
 So mine follows a single purchase the entire distance. A boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one deliberately, hands a coupon to the cashier, meets sales tax, and then lives with the thing. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed, so the parent reads it with the kid and gets handed the script instead of being expected to know it.
 The retail angle, if you want one: every trick your beat covers — the fake markdown, the anchor price, the "newest is better" framing — gets run on children first, in arcades and toy aisles, where there is no consumer press and no one filing complaints because the mark is seven. The boardwalk airbrush stand charges $28 for a shirt that says BRAYDEN. Your kid's name is not Brayden.
 Worth a look? clarencegetsabargain.com/book-facts.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
@@ -2417,7 +2434,8 @@
 It reads aloud in twenty minutes. Lexile AD 620L — Adult Directed, the industry's own code for read-with rather than read-alone, so a parent who feels unqualified on money still gets handed the script.
 The column question rather than the book question: has anyone made the case that spending competence has to come first? I have not been able to find it, and you would know if it exists.
 clarencegetsabargain.com/press-kit.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -2477,7 +2495,8 @@
 The numbers on the other side are absurd and nobody has ever put a microphone on them. Twelve hundred arcade tickets for a rubber slinky is an exchange rate that would embarrass a currency trader, and the kid making that trade has no idea he is trading.
 The segment is the forty-year hole. A whole publishing category taught children to save and skipped the register, while every arcade, app store and checkout lane aimed at children did not skip it at all. Nobody regulates the toy aisle and nobody covers it.
 Is that an episode whether or not my book is in it? Four-minute flip: https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
@@ -2538,7 +2557,8 @@
 The sponsorship math is simple if a member bank wants it: 25 copies is $499.75, one classroom, the bank's name on every book that goes home to a family. The educator program is free, so the sponsorship is entirely books, and I have a CRA-ready memo already written in examiner-friendly language.
 Does that fit how Utah banks choose classroom programs, or am I inventing a use case?
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -2599,7 +2619,8 @@
 Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, meets sales tax, and then lives with what he chose. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the story. It is catalogued AD 620L — Adult Directed — so the adult reading gets handed the script and does not have to be the one who already knows about money. That was the design constraint that mattered most: it has to work in a house where nobody feels qualified to teach it. The piggy bank has had four hundred years and has yet to file a price comparison.
 Two questions. Does the spending-first argument hold up against what you hear from your audience? And is there a version of this worth putting in front of the Financial Influencer Network?
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
@@ -2720,7 +2741,8 @@
 One thing I would put to you as a planner: a card is magic, and a five-dollar bill is arithmetic. Children now grow up almost entirely inside the first one, which removes the only feedback loop they had.
 The claim I would defend hardest is the delayed one. The book is not really working in the twenty minutes it takes to read. It works in month eighteen, in a real store, when the kid hits a money moment and the book fires back — "wait, is the newer one actually better?" Recognition first, then the habit.
 Does that hold up against what you see in readers? clarencegetsabargain.com/book-facts.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
@@ -2780,7 +2802,8 @@
 So I wrote the spending book. Clarence Gets a Bargain, ages 6–10: a boy earns a robot with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and then lives with the thing he picked. Idea to post-receipt; sixteen-plus concepts, none of them announced. Twenty-one terms in a glossary at the back, each page-referenced to where it happened. Catalogued AD 620L — Adult Directed — twenty minutes out loud, interrupted the whole way. The category's own defence is that money is a serious subject. It is. So is getting fleeced in an aisle at the age of seven.
 I am an attorney and a mixed-media artist, and I have twice walked out of the same Nordstrom Rack having paid one cent — once for a $293 pair of shoes, once for a $69.50 shirt. I kept both tags. It makes for a good visual if you ever want one on screen.
 Is there a hit in "the money skill nobody teaches kids"? clarencegetsabargain.com/press-kit.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -2840,7 +2863,8 @@
 Sixteen-plus concepts and nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened — which is the only point at which a kid works out he has been schooled. Catalogued AD 620L — Adult Directed — read with a parent, not handed to a kid alone. The single sentence I most want an eleven-year-old to own: marked down does not mean broken, it means the timing is on your side. The subject is treated as serious and taught as though nobody ever spends any.
 The question, since you have the data and I only have the book: does anything in what you see suggest that price competence at seven shows up at twenty-seven? If it does not, I would rather know.
 clarencegetsabargain.com/book-facts.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
@@ -2900,7 +2924,8 @@
 The curriculum behind it is free and ungated — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart, printable classroom pieces, and a browser-based pretend register that runs a markdown, a coupon and sales tax with the total changing in front of the class. Catalogued Lexile AD 620L — Adult Directed — one class period, no teacher training.
 The honest question rather than a pitch: when teachers come to Intuit for Education, does elementary ever come up as something they want and cannot find? I am trying to work out whether I am filling a gap or inventing one, and you would see the demand signal before I would.
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -2961,7 +2986,8 @@
 Catalogued Lexile AD 620L — Adult Directed — one class period out loud, and because the mother explains every concept inside the text, a teacher needs no finance background. Everything behind it is free and ungated: lesson plans, assessments with answer keys, a standards crosswalk, printable classroom pieces, a browser-based pretend register.
 Would a read-aloud plus a pretend-store activity fit anywhere in a Promise Academy week, or is the schedule too tight for anything that is not tested?
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -3022,7 +3048,8 @@
 Meanwhile the arcade never waited for a standard: $25 into a glass box for a basketball Walmart sells for $9.99, and the kid has no price memory to argue with.
 The story I would pitch your desk: the whole country legislated financial literacy into ninth grade, and the elementary standards that already exist in most states sit there with nothing built against them, because nobody has to report on them.
 Does that belong to anyone on your team? clarencegetsabargain.com/book-facts.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -3083,7 +3110,8 @@
 I am an attorney, and on vacation that mostly means the souvenirs get cross-examined. The hermit crab: who feeds it over the holidays, and in two weeks when it dies — and buddy, it will — is it worth the tears? My kids find this insufferable. It is also the entire skill.
 The honest version of the beat problem: the full picture crosses agencies. Warranties and returns sit with the FTC, product safety with the CPSC. Nobody owns "children as consumers," which may be exactly why nobody covers it.
 Is there a story in that? clarencegetsabargain.com/press-kit.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
@@ -3144,7 +3172,8 @@
 The teacher side is free and ungated — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE, and FDIC Money Smart. No account, no email capture, and it prints from a browser. Catalogued AD 620L — Adult Directed — a one-period read-aloud a teacher with no finance background can deliver cold.
 Does the spending-first sequence match what you see in classrooms, or is there a reason the field starts where it starts?
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -3206,7 +3235,8 @@
 A card is magic; a five-dollar bill is arithmetic. Children now grow up almost entirely inside the first one, which removed the only feedback loop they had.
 The angle for your beat: advisors spend fortunes trying to meet the next generation before the assets move. This is what meeting them at seven looks like, and it costs $19.99.
 Worth a column, or am I describing something you have already covered? clarencegetsabargain.com/press-kit.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
@@ -3269,7 +3299,8 @@
 Who in MCPS owns elementary financial literacy, if anyone does?
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan Bach
-Attorney and children's book author, Baltimore</t>
+Attorney and children's book author, Baltimore
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -3331,7 +3362,8 @@
 The question: does the evidence base start at adolescence the way the books do? If spending competence at seven predicts nothing at twenty-seven, that is worth knowing and I would rather hear it than keep arguing.
 clarencegetsabargain.com/book-facts.html
 Jonathan Bach
-Attorney and children's book author, Baltimore</t>
+Attorney and children's book author, Baltimore
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
@@ -3391,7 +3423,8 @@
 You also solved a distribution problem the rest of us have not: banks and credit unions sponsor the visits and buy the books, and their community reports write themselves. I would rather learn that from you than reverse-engineer it.
 Trade copies and compare notes? I will read Sammy properly and tell you the truth about it, which is the only thing worth trading.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -3452,7 +3485,8 @@
 The twenty-one-term glossary in the back is page-referenced to the story, so an instructor can answer a vocabulary question by turning to the scene rather than reciting a definition. The field keeps building the ninth-grade course and keeps skipping the second-grade one, which is a strange place to draw a line.
 Does your instructor network want elementary material, or is the demand really all adult and teen? Everything is free either way.
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
@@ -3514,7 +3548,8 @@
 The question: does NEFE's research or advocacy work have a position on the elementary band, or is the practical view that high school is where the effort pays? If it is the second, I would like to know I am arguing with a considered consensus rather than filling a gap it agrees exists.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan Bach
-Attorney and children's book author, Baltimore</t>
+Attorney and children's book author, Baltimore
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -3576,7 +3611,8 @@
 One line from the book does the work of a standards document, and it is the one I would defend hardest: marked down does not mean broken, it means the timing is on your side.
 Two questions. Does Jump$tart consider elementary in scope, or is it a band the coalition has consciously left to others? And for the Clearinghouse, is the free classroom set the right thing to submit rather than the book?
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
@@ -3637,7 +3673,8 @@
 I did the illustrations too, which means my opinion of them is worth nothing. It is written for the adult voice in the room — catalogued AD 620L, Adult Directed — with the mother carrying every explanation.
 Trade? Send me a Wesley and I will read it properly rather than politely.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -3698,7 +3735,8 @@
 The boardwalk is a pop quiz your kid has not studied for, and it runs all summer with real money.
 Timely hook if you need one: thirty states now guarantee a personal finance course, all of it in high school, long after the habits form. The elementary standards already exist in most states and have almost nothing built against them.
 Any of that useful to you? clarencegetsabargain.com/book-facts.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
@@ -5781,7 +5819,8 @@
 One thing your Challenge and the book share: neither one works with a kid alone in a room. It is Lexile AD 620L — Adult Directed, the trade's code for read-with rather than read-alone — and the mother explains every concept on the page, so whoever is reading gets handed the script. Parent, teacher or grandparent, the reading stops every few pages because the kid asks something.
 Worth a conversation? I'd rather compare notes with the one other person who put spending first than pitch anybody.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L104" s="5" t="inlineStr">
@@ -7055,7 +7094,8 @@
 For a parenting audience the format may matter more than the content. Lexile AD 620L — the AD is Adult Directed, the industry's own label for a book meant to be read *with* a child rather than left in their room. Mom explains every concept on the page, so the parent gets handed the script instead of being expected to know it. "Do we have a 529?" is a question a seven-year-old asks in the middle of page six, not after. Grandparents get the same deal, and they tend to enjoy it more.
 Would it work for your audience — podcast, newsletter, or neither? A no is a fine answer and faster than a maybe.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L137" s="5" t="inlineStr">
@@ -7112,7 +7152,8 @@
 The other half of the craft problem: it is written for an adult voice. Lexile AD 620L — Adult Directed — with the mother carrying every explanation, so whoever reads aloud gets handed the script. A series lives or dies on whether the grown-up still enjoys the fourth reading. You would know inside a page whether mine does.
 Would you read it and tell me where it stops being a story? I'll trade — send me a Noah and I'll read it properly.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L138" s="5" t="inlineStr">
@@ -8311,7 +8352,8 @@
 And the handoff you teach is the mechanism itself. The book is Lexile AD 620L — Adult Directed, the trade's own label for a book meant to be read *with* a child, not left in a bedroom — and Mom explains everything on the page, so the adult reading aloud is handed the script rather than asked to know the material. A parent who feels unqualified to teach money can still run it. Classroom, kitchen table, grandparent's couch: the reading stops every few pages because somebody asks.
 Two questions, either useful. Does the spending-before-saving sequence hold up against what you see in families? And is there a version of this that belongs in front of the parents you train?
 clarencegetsabargain.com/book-facts.html · https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L169" s="5" t="inlineStr">
@@ -8363,7 +8405,8 @@
 What I'd actually value from you is the unglamorous part: trim size, the cover, whether the interior typography holds at read-aloud distance, whether the object reads as professionally published or as a very determined amateur. I would rather hear it from you now than infer it from a bookseller later.
 And the read-aloud is why I asked about typography at distance rather than at arm's length. It is Lexile AD 620L — Adult Directed — so the object gets held up by an adult with a kid beside them, or a class in front of them, looking at it from three or four feet. If the interior does not hold at that distance the whole use case fails, and that is a production question rather than a content one.
 Paid engagement or a favour returned, whichever you prefer. https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L170" s="5" t="inlineStr">
@@ -9679,7 +9722,8 @@
 The real question: does anything in the literature speak to elementary spending competence, or is that band simply unstudied? Either answer is useful to me.
 clarencegetsabargain.com/book-facts.html
 Jonathan Bach
-Attorney and children's book author, Baltimore</t>
+Attorney and children's book author, Baltimore
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L204" s="5" t="inlineStr">
@@ -9740,7 +9784,8 @@
 Ages 6–10, inside the Bookshelf's 4–10 band. Catalogued Lexile AD 620L — Adult Directed, which is how the Bookshelf's titles are meant to be used anyway.
 Two questions. Was the saving weighting deliberate, or just what existed? And is the selection process still running?
 clarencegetsabargain.com/book-facts.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L205" s="5" t="inlineStr">
@@ -9810,7 +9855,8 @@
 The question I would actually like answered: is there work on when price competence forms, and whether early exposure to comparison changes anything measurable later? If the honest answer is that it is unstudied because it is unmeasurable at that age, that is worth knowing too.
 clarencegetsabargain.com/book-facts.html
 Jonathan Bach
-Attorney and children's book author, Baltimore</t>
+Attorney and children's book author, Baltimore
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L206" s="5" t="inlineStr">
@@ -17315,7 +17361,8 @@
 Why I am writing to development rather than to a classroom: this is unusually easy to fund. A bank or credit union sponsoring a classroom set gets its name on every book that goes home to a family in its assessment area, the curriculum costs the sponsor nothing because it is already free, and I have a CRA-ready memo written in examiner-friendly language. A funder can point at 25 books, one classroom, and a pre/post instrument. And because it is catalogued AD 620L — Adult Directed — it doubles as family engagement: the same book works at a kitchen table with a parent or a grandparent reading.
 Is a sponsored classroom set something HCZ's funders would recognise, or does everything need to attach to an existing program line?
 clarencegetsabargain.com/resources/grant-in-a-box.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L402" s="5" t="inlineStr">
@@ -17376,7 +17423,8 @@
 Alaska has its own complications on distance and travel, and virtual read-alouds work for this.
 Does a read-aloud fit how JA Alaska builds a volunteer session, or does everything have to run through national curriculum?
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L403" s="5" t="inlineStr">
@@ -17499,7 +17547,8 @@
 The claim I would defend hardest is the delayed one, and it is the same claim Troutwood makes about projections: the value is not in the twenty minutes. It is in month eighteen, in a real store, when the kid hits a money moment and the book fires back. Recognition first, then the habit.
 Does the elementary end fit anything Troutwood does, or is that below the floor?
 clarencegetsabargain.com/book-facts.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L405" s="5" t="inlineStr">
@@ -17560,7 +17609,8 @@
 The whole thing rests on one instruction a teacher can act on the same week: stop bringing kids to the store as cargo, bring them as staff. Every activity in the set is a version of that.
 The honest question: what makes a free teacher resource actually get used rather than downloaded and forgotten? You have watched that happen more times than I have, and I would rather fix it now.
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L406" s="5" t="inlineStr">
@@ -22174,7 +22224,8 @@
 Those look complementary rather than competing to me: yours gives a kid the categories in their hands, mine walks them through the mechanics of one transaction in twenty minutes.
 Worth a conversation about whether they belong near each other? And separately — if you think spending-before-saving is wrong, you are one of very few people whose disagreement would actually change my mind.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L525" s="5" t="inlineStr">
@@ -25877,13 +25928,14 @@
       <c r="K622" s="5" t="inlineStr">
         <is>
           <t>Sandy — FCCLA members are a decade older than my readers, so take this as a service-project idea rather than a curriculum pitch. I think it's a good one.
-Your chapters run community service. A high schooler reading a money book to a second-grade class is about the cleanest version of that I can think of — it needs no budget, no training, and one afternoon.
+Your chapters run community service. A high schooler reading a money book to a second-grade class is about the cleanest version of that I can think of — it needs no budget, no training, and one afternoon. The book teaches spending rather than saving, on the argument that saving is the second thing a child does with money and spending is the first.
 The book is Clarence Gets a Bargain, 36 pages, ages 6-10. It follows one purchase the whole way, which is the thing that makes it work as a read-aloud rather than a lecture: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt; sixteen-plus concepts and nobody in it says "budget" — the twenty-one-term glossary in the back is page-referenced to the story, so the reader can field questions without preparing.
 The read-aloud is the entire project, so the spec matters. Lexile AD 620L — the AD is Adult Directed, the trade's own code for a book built to be read *with* a child rather than handed to one. About twenty minutes out loud, which is a class visit with time left for questions, and the mother explains every concept inside the text. A high schooler can read it cold to a second-grade class and field the questions straight off the page. Nothing to memorize, nothing to prepare, no training call beforehand.
 There is also a free browser-based pretend register the younger kids can run afterward — a markdown, a coupon, sales tax, and a total that changes in front of them.
 Does that fit how chapters choose service projects, or am I inventing a use case? Everything is free and ungated either way.
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L622" s="5" t="inlineStr">
@@ -28298,7 +28350,7 @@
         </is>
       </c>
       <c r="I666" s="5" t="n">
-        <v>3450</v>
+        <v>3585</v>
       </c>
       <c r="J666" s="5" t="inlineStr">
         <is>
@@ -28314,7 +28366,8 @@
 Jonathan Bach
 Author &amp; illustrator, Clarence Gets a Bargain
 Attorney. Dad. Keeper of receipts.
-questions@clarencegetsabargain.com · clarencegetsabargain.com</t>
+questions@clarencegetsabargain.com · clarencegetsabargain.com
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="K666" s="5" t="inlineStr"/>
@@ -28360,7 +28413,7 @@
       </c>
       <c r="H667" s="5" t="inlineStr"/>
       <c r="I667" s="5" t="n">
-        <v>3034</v>
+        <v>3162</v>
       </c>
       <c r="J667" s="5" t="inlineStr">
         <is>
@@ -28376,7 +28429,8 @@
 Jonathan Bach
 Author &amp; illustrator, Clarence Gets a Bargain
 Attorney. Dad. Keeper of receipts.
-questions@clarencegetsabargain.com · clarencegetsabargain.com</t>
+questions@clarencegetsabargain.com · clarencegetsabargain.com
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="K667" s="5" t="inlineStr"/>
@@ -28493,7 +28547,7 @@
         </is>
       </c>
       <c r="I669" s="5" t="n">
-        <v>2794</v>
+        <v>2932</v>
       </c>
       <c r="J669" s="5" t="inlineStr">
         <is>
@@ -28509,7 +28563,8 @@
 Wrong about that? You'd know better than anyone. clarencegetsabargain.com/book-facts.html has the specs, and I'll send a copy if it's useful.
 Jonathan Bach
 Attorney and children's book author, Baltimore
-questions@clarencegetsabargain.com</t>
+questions@clarencegetsabargain.com
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="K669" s="5" t="inlineStr"/>
@@ -28551,7 +28606,7 @@
       <c r="G670" s="5" t="inlineStr"/>
       <c r="H670" s="5" t="inlineStr"/>
       <c r="I670" s="5" t="n">
-        <v>1509</v>
+        <v>1644</v>
       </c>
       <c r="J670" s="5" t="inlineStr">
         <is>
@@ -28562,7 +28617,8 @@
 Two of the games in it need more than one player on purpose. One is a grocery-store savings hunt where the loser carries the bags in from the car.
 Worth twenty minutes of your show? I'll send a copy either way.
 Jonathan Bach — Clarence Gets a Bargain
-questions@clarencegetsabargain.com · clarencegetsabargain.com</t>
+questions@clarencegetsabargain.com · clarencegetsabargain.com
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="K670" s="5" t="inlineStr"/>
@@ -28792,7 +28848,8 @@
 The segment worth doing has nothing to do with my book. It's the forty-year hole: why an entire publishing category skipped the cash register. There is a Planet Money episode in that whether or not mine is the book that gets mentioned.
 One structural note, since you make things people take in together: the reading level is Lexile AD 620L, and the AD stands for Adult Directed — the trade's own code for a book meant to be read *with* a child rather than handed to one. That was the design, not the accident. Twenty minutes out loud, interrupted the whole way, and the interruptions are the product. Classroom, kitchen table, grandparent's couch — same pages, same arguments break out.
 Am I wrong that it's a story? clarencegetsabargain.com/book-facts.html has the specs. Four-minute flip: https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
@@ -28854,7 +28911,8 @@
 The other craft problem, which you will have solved in your own books: it is written to be read aloud by an adult who does not know the material either. Lexile has it at AD 620L — Adult Directed, read-with rather than read-alone — and the mother explains every concept on the page, so whoever is holding the book gets handed the script. Teacher, parent, grandparent, same outcome: the reading stops every few pages because somebody in the room asks a question.
 Would you look at it and tell me where the seams show? I'd trade — send me yours and I'll read it properly, not politely.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
@@ -28976,7 +29034,8 @@
 Format note, since your audience is adults deciding what to hand a kid: Lexile AD 620L, where AD means Adult Directed — the trade's code for a book meant to be read *with* a child. Not a book you leave in a bedroom. Twenty minutes out loud, and the kid interrupts constantly, which is the whole point. The argument about whether Wi-Fi is a need or a want is the product; the robot is the delivery vehicle.
 Is there an episode in the fact that the entire children's money category skipped the cash register for forty years? I'd rather you took the argument than the book.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
@@ -29038,7 +29097,8 @@
 The other thing worth your reviewer's ear: it is built to be read aloud, and Lexile has it at AD 620L — Adult Directed, read-with rather than read-alone. The mother carries the exposition, which means the adult holding the book is handed the script. Whether that voice actually holds up out loud — across a classroom, a couch, and a grandparent's lap — is something you would hear in a page and I can only guess at.
 Would you read it as an editor rather than as a friend? I would rather hear where it sags than be told it's charming.
 clarencegetsabargain.com/press-kit.html · https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
@@ -29099,7 +29159,8 @@
 One design decision I would want your view on. It is written for an adult to read aloud, not for a child alone: Lexile AD 620L, Adult Directed. The mother carries every explanation on the page, so the grown-up gets the script rather than the homework. You spent a career telling parents to have the conversation. This one hands them the conversation and lets them take the credit for it.
 Author to author, I'd like to trade. Send me one of yours and I'll read it properly. And if you think the spending-first premise is wrong, that is worth more to me than a kind word about the illustrations.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
@@ -29156,7 +29217,7 @@
           <t>Joel — a specific question rather than a pitch, and it should take you a minute.
 I have a K-5 resource I would like to list in the Jump$tart Clearinghouse, and I have read the listing criteria closely enough to know which route applies to me. I am not a National Partner and have never listed before, so I would be applying under the letter-of-reference route.
 The resource is a free, ungated classroom set built around a 36-page picture book: four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE, and FDIC Money Smart, printable classroom pieces, and a browser-based pretend register. No account, no email capture, no purchase order. It prints from a browser.
-What the book does that the category does not: it teaches spending rather than saving, and it follows one complete purchase from the idea through the receipt — sale ads, comparison, markdown, coupon, sales tax. Sixteen-plus concepts, a twenty-one-term glossary page-referenced to the story. The elementary grade band has standards and very little built against them.
+What the book does that the category does not: it teaches spending rather than saving, and it follows one complete purchase from the idea through the receipt — sale ads, comparison, markdown, coupon, sales tax. Sixteen-plus concepts, none of them announced in the text, and a twenty-one-term glossary page-referenced to the story. The elementary grade band has standards and very little built against them.
 One spec relevant to classroom use: Lexile AD 620L. The AD is Adult Directed — read-aloud with an adult rather than independent reading. It runs one class period, and the mother explains each concept inside the text, so a teacher with no finance background can run it without preparation. The same design makes it work as a family take-home.
 Two questions. Is the free classroom set the right thing to submit, rather than the book? And for the reference letter, would Wally Luckeydoo carry weight — he received your 2026 Corey Carlisle Award and endorsed the book before any of this came up.
 clarencegetsabargain.com/educator-toolkit.html
@@ -29221,7 +29282,8 @@
 The column, if there is one: an entire publishing category has taught children to save for forty years and skipped the cash register, which is the only place a child has ever actually handled money. That is a story about the field, not about me.
 clarencegetsabargain.com/press-kit.html
 Jonathan Bach
-Baltimore</t>
+Baltimore
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
@@ -29282,7 +29344,8 @@
 The read-aloud is the other half of it. Lexile AD 620L — Adult Directed — written for the adult voice in the room rather than for a child alone, with the mother carrying the explanations so the grown-up gets handed the script. You will know better than most how much that changes what has to happen on the page.
 Trade copies? I'll read yours properly and tell you the truth about it, which is the only thing worth trading.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
@@ -29342,7 +29405,8 @@
 For the teacher side: AD 620L — Adult Directed — one class period out loud, with the mother explaining every concept in the text so a teacher without a finance background can run it cold. The same book does the job at a kitchen table with a parent or a grandparent, which is the part elementary teachers actually ask for and rarely get.
 Honest question rather than a pitch: when you talk to teachers, does elementary ever come up as something they want and cannot find? I am trying to work out whether I am filling a gap or inventing one.
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
@@ -29535,7 +29599,8 @@
 And on the read-along specifically, since I raised it: the book is Lexile AD 620L — AD for Adult Directed, the trade's code for read-with rather than read-alone. It is built for somebody to perform. You explain to camera; this hands the explaining to whoever is holding the book — teacher, parent, grandparent — and then the kid interrupts them. Different mechanism, same job.
 Is there a version of this worth putting in front of your audience — a read-along, a segment, a mention? And separately: at sixteen, would this book have been too young for you, or exactly right for the you at six?
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -29597,7 +29662,8 @@
 One more thing about how it gets used, because it changes who it is for. Lexile AD 620L — Adult Directed, the industry's own code for a book meant to be read *with* a child. The mother explains every concept on the page, so the adult reading aloud gets handed the script and does not have to be the one who already knows about money. It counts most in the houses where nobody feels qualified to teach it, which is most houses.
 You know better than almost anyone whether a thing lands with the people it's for. Would you look, and tell me if the six-year-old version of your audience would sit still for it?
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -29851,7 +29917,8 @@
 Two asks, and the second one matters more. Worth a look for the next update to the roundup? And separately — you run a company built on kids and money, so if you think spending-before-saving is wrong, I would rather hear it from you than keep saying it at conferences.
 One line worth having in a roundup, because parents ask it: Lexile AD 620L — Adult Directed, the industry's own code for a book meant to be read *with* a child rather than handed over. Twenty minutes out loud, interrupted the whole way. Grandparents take to it fastest — it gives them something to do with the grandkid instead of something to hand them, and every page has a "that reminds me of the time" sitting in it.
 I'll send a copy either way. https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
@@ -30093,7 +30160,8 @@
 The instruction underneath the whole book is four words long: stop bringing kids to the store as cargo, bring them as staff. Catalogued Lexile AD 620L — Adult Directed — so the parent gets handed the script rather than an assignment, which I suspect is why your posts land: parents want the conversation and do not feel qualified to start it.
 The thing I would actually value: you know what makes a parent stop scrolling on this subject and what makes them scroll past. If "spending before saving" is the wrong hook, I would rather hear it from you than keep testing it slowly.
 Would you look and tell me? https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -30154,7 +30222,8 @@
 Their books are about earning and saving, which is fine, but there is no game in a piggy bank and kids work that out faster than we do. They smell a worksheet through a backpack.
 The episode worth doing has nothing to do with my book. Pitch the forty-year hole: an entire publishing category taught children to save and skipped the cash register, the only place a child has ever actually handled money.
 Worth twenty minutes of your show? https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
@@ -30214,7 +30283,8 @@
 Cataloguing: ISBN 979-8-234-07638-0 · LCCN 2026906164 · hardbound, case bound, full colour, 11×8.5′′ · Est. Lexile AD 620L, Guided Reading L–N · $19.99. The AD is Adult Directed, which makes it a storytime title and a family take-home at the same time. Every fact is on one page: clarencegetsabargain.com/book-facts.html
 Programming is already built and free — printable price tags and clearance stickers for a pretend store, a browser-based register kids run themselves, a five-question quiz with a printable certificate. A storytime plus the pretend store is a complete Money Smart Week event with no prep budget.
 Kids re-read it without being asked, which is the only metric that matters at your desk. Review copy on request?
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -30275,7 +30345,8 @@
 Programming, already built and free: printable price tags and clearance stickers for a pretend store, a browser-based Sea-Mart register children operate themselves with a markdown, a coupon and sales tax, and a quiz with a printable certificate. No prep budget required for a Financial Literacy Month or Money Smart Week event.
 Endorsed by a K–5 educator with 30+ years in the classroom and by the 2026 EIFLE Educator of the Year.
 Shelve it under picture books; file it under secret weapons. Happy to send a review copy — reply with an address?
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
@@ -30335,7 +30406,8 @@
 I wrote the picture book for it. One kid, one purchase, followed the whole way: he wants a robot, earns it, reads the newspaper sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and lives with what he chose. Idea to post-receipt; sixteen-plus concepts and nobody in the book says the word "budget." The child works out he has been schooled only when he reaches the glossary — twenty-one terms in the back, each page-referenced to where it happened. It is catalogued Lexile AD 620L, where AD stands for Adult Directed — the trade's own code for a book an adult reads with a child rather than hands over.
 The story here has nothing to do with my book. An entire publishing category taught children to save for forty years and skipped the register, which is the only place a child has ever handled money — while the arcade, the app store and the checkout lane did not skip it at all.
 Is there anything there? clarencegetsabargain.com/press-kit.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -30395,7 +30467,8 @@
 So mine follows a single purchase the entire distance. A boy wants a robot, earns it with chores and grades, works the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one deliberately, hands a coupon to the cashier, meets sales tax, and then lives with the thing. Idea to post-receipt. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, each entry page-referenced to the scene it came from, and a Lexile of AD 620L — Adult Directed, so the parent reads it with the kid and gets handed the script instead of being expected to know it.
 The retail angle, if you want one: every trick your beat covers — the fake markdown, the anchor price, the "newest is better" framing — gets run on children first, in arcades and toy aisles, where there is no consumer press and no one filing complaints because the mark is seven. The boardwalk airbrush stand charges $28 for a shirt that says BRAYDEN. Your kid's name is not Brayden.
 Worth a look? clarencegetsabargain.com/book-facts.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
@@ -30456,7 +30529,8 @@
 It reads aloud in twenty minutes. Lexile AD 620L — Adult Directed, the industry's own code for read-with rather than read-alone, so a parent who feels unqualified on money still gets handed the script.
 The column question rather than the book question: has anyone made the case that spending competence has to come first? I have not been able to find it, and you would know if it exists.
 clarencegetsabargain.com/press-kit.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -30516,7 +30590,8 @@
 The numbers on the other side are absurd and nobody has ever put a microphone on them. Twelve hundred arcade tickets for a rubber slinky is an exchange rate that would embarrass a currency trader, and the kid making that trade has no idea he is trading.
 The segment is the forty-year hole. A whole publishing category taught children to save and skipped the register, while every arcade, app store and checkout lane aimed at children did not skip it at all. Nobody regulates the toy aisle and nobody covers it.
 Is that an episode whether or not my book is in it? Four-minute flip: https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
@@ -30577,7 +30652,8 @@
 The sponsorship math is simple if a member bank wants it: 25 copies is $499.75, one classroom, the bank's name on every book that goes home to a family. The educator program is free, so the sponsorship is entirely books, and I have a CRA-ready memo already written in examiner-friendly language.
 Does that fit how Utah banks choose classroom programs, or am I inventing a use case?
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -30638,7 +30714,8 @@
 Clarence Gets a Bargain follows one purchase the whole distance: a boy wants a robot, earns it with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the marked-down one on purpose, hands the cashier a coupon he has been clutching like a winning lottery ticket, meets sales tax, and then lives with what he chose. Sixteen-plus concepts, none announced. A twenty-one-term glossary in the back, page-referenced to the story. It is catalogued AD 620L — Adult Directed — so the adult reading gets handed the script and does not have to be the one who already knows about money. That was the design constraint that mattered most: it has to work in a house where nobody feels qualified to teach it. The piggy bank has had four hundred years and has yet to file a price comparison.
 Two questions. Does the spending-first argument hold up against what you hear from your audience? And is there a version of this worth putting in front of the Financial Influencer Network?
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
@@ -30759,7 +30836,8 @@
 One thing I would put to you as a planner: a card is magic, and a five-dollar bill is arithmetic. Children now grow up almost entirely inside the first one, which removes the only feedback loop they had.
 The claim I would defend hardest is the delayed one. The book is not really working in the twenty minutes it takes to read. It works in month eighteen, in a real store, when the kid hits a money moment and the book fires back — "wait, is the newer one actually better?" Recognition first, then the habit.
 Does that hold up against what you see in readers? clarencegetsabargain.com/book-facts.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
@@ -30819,7 +30897,8 @@
 So I wrote the spending book. Clarence Gets a Bargain, ages 6–10: a boy earns a robot with chores and grades, reads the sale inserts at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands over a coupon, meets sales tax, and then lives with the thing he picked. Idea to post-receipt; sixteen-plus concepts, none of them announced. Twenty-one terms in a glossary at the back, each page-referenced to where it happened. Catalogued AD 620L — Adult Directed — twenty minutes out loud, interrupted the whole way. The category's own defence is that money is a serious subject. It is. So is getting fleeced in an aisle at the age of seven.
 I am an attorney and a mixed-media artist, and I have twice walked out of the same Nordstrom Rack having paid one cent — once for a $293 pair of shoes, once for a $69.50 shirt. I kept both tags. It makes for a good visual if you ever want one on screen.
 Is there a hit in "the money skill nobody teaches kids"? clarencegetsabargain.com/press-kit.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -30879,7 +30958,8 @@
 Sixteen-plus concepts and nobody in the book says the word "budget." A twenty-one-term glossary in the back, each entry page-referenced to the scene where it happened — which is the only point at which a kid works out he has been schooled. Catalogued AD 620L — Adult Directed — read with a parent, not handed to a kid alone. The single sentence I most want an eleven-year-old to own: marked down does not mean broken, it means the timing is on your side. The subject is treated as serious and taught as though nobody ever spends any.
 The question, since you have the data and I only have the book: does anything in what you see suggest that price competence at seven shows up at twenty-seven? If it does not, I would rather know.
 clarencegetsabargain.com/book-facts.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
@@ -30939,7 +31019,8 @@
 The curriculum behind it is free and ungated — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, a 23-row crosswalk to the 2021 National Standards plus Common Core Math and ELA, CEE and FDIC Money Smart, printable classroom pieces, and a browser-based pretend register that runs a markdown, a coupon and sales tax with the total changing in front of the class. Catalogued Lexile AD 620L — Adult Directed — one class period, no teacher training.
 The honest question rather than a pitch: when teachers come to Intuit for Education, does elementary ever come up as something they want and cannot find? I am trying to work out whether I am filling a gap or inventing one, and you would see the demand signal before I would.
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -31000,7 +31081,8 @@
 Catalogued Lexile AD 620L — Adult Directed — one class period out loud, and because the mother explains every concept inside the text, a teacher needs no finance background. Everything behind it is free and ungated: lesson plans, assessments with answer keys, a standards crosswalk, printable classroom pieces, a browser-based pretend register.
 Would a read-aloud plus a pretend-store activity fit anywhere in a Promise Academy week, or is the schedule too tight for anything that is not tested?
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -31061,7 +31143,8 @@
 Meanwhile the arcade never waited for a standard: $25 into a glass box for a basketball Walmart sells for $9.99, and the kid has no price memory to argue with.
 The story I would pitch your desk: the whole country legislated financial literacy into ninth grade, and the elementary standards that already exist in most states sit there with nothing built against them, because nobody has to report on them.
 Does that belong to anyone on your team? clarencegetsabargain.com/book-facts.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -31122,7 +31205,8 @@
 I am an attorney, and on vacation that mostly means the souvenirs get cross-examined. The hermit crab: who feeds it over the holidays, and in two weeks when it dies — and buddy, it will — is it worth the tears? My kids find this insufferable. It is also the entire skill.
 The honest version of the beat problem: the full picture crosses agencies. Warranties and returns sit with the FTC, product safety with the CPSC. Nobody owns "children as consumers," which may be exactly why nobody covers it.
 Is there a story in that? clarencegetsabargain.com/press-kit.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
@@ -31183,7 +31267,8 @@
 The teacher side is free and ungated — four 45-minute lesson plans, a discussion guide, pre- and post-assessments with answer keys, and a 23-row crosswalk to the 2021 National Standards for Personal Financial Education plus Common Core Math and ELA, CEE, and FDIC Money Smart. No account, no email capture, and it prints from a browser. Catalogued AD 620L — Adult Directed — a one-period read-aloud a teacher with no finance background can deliver cold.
 Does the spending-first sequence match what you see in classrooms, or is there a reason the field starts where it starts?
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -31245,7 +31330,8 @@
 A card is magic; a five-dollar bill is arithmetic. Children now grow up almost entirely inside the first one, which removed the only feedback loop they had.
 The angle for your beat: advisors spend fortunes trying to meet the next generation before the assets move. This is what meeting them at seven looks like, and it costs $19.99.
 Worth a column, or am I describing something you have already covered? clarencegetsabargain.com/press-kit.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
@@ -31308,7 +31394,8 @@
 Who in MCPS owns elementary financial literacy, if anyone does?
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan Bach
-Attorney and children's book author, Baltimore</t>
+Attorney and children's book author, Baltimore
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -31370,7 +31457,8 @@
 The question: does the evidence base start at adolescence the way the books do? If spending competence at seven predicts nothing at twenty-seven, that is worth knowing and I would rather hear it than keep arguing.
 clarencegetsabargain.com/book-facts.html
 Jonathan Bach
-Attorney and children's book author, Baltimore</t>
+Attorney and children's book author, Baltimore
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
@@ -31430,7 +31518,8 @@
 You also solved a distribution problem the rest of us have not: banks and credit unions sponsor the visits and buy the books, and their community reports write themselves. I would rather learn that from you than reverse-engineer it.
 Trade copies and compare notes? I will read Sammy properly and tell you the truth about it, which is the only thing worth trading.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -31491,7 +31580,8 @@
 The twenty-one-term glossary in the back is page-referenced to the story, so an instructor can answer a vocabulary question by turning to the scene rather than reciting a definition. The field keeps building the ninth-grade course and keeps skipping the second-grade one, which is a strange place to draw a line.
 Does your instructor network want elementary material, or is the demand really all adult and teen? Everything is free either way.
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
@@ -31553,7 +31643,8 @@
 The question: does NEFE's research or advocacy work have a position on the elementary band, or is the practical view that high school is where the effort pays? If it is the second, I would like to know I am arguing with a considered consensus rather than filling a gap it agrees exists.
 clarencegetsabargain.com/educator-toolkit.html
 Jonathan Bach
-Attorney and children's book author, Baltimore</t>
+Attorney and children's book author, Baltimore
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -31615,7 +31706,8 @@
 One line from the book does the work of a standards document, and it is the one I would defend hardest: marked down does not mean broken, it means the timing is on your side.
 Two questions. Does Jump$tart consider elementary in scope, or is it a band the coalition has consciously left to others? And for the Clearinghouse, is the free classroom set the right thing to submit rather than the book?
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
@@ -31676,7 +31768,8 @@
 I did the illustrations too, which means my opinion of them is worth nothing. It is written for the adult voice in the room — catalogued AD 620L, Adult Directed — with the mother carrying every explanation.
 Trade? Send me a Wesley and I will read it properly rather than politely.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -31737,7 +31830,8 @@
 The boardwalk is a pop quiz your kid has not studied for, and it runs all summer with real money.
 Timely hook if you need one: thirty states now guarantee a personal finance course, all of it in high school, long after the habits form. The elementary standards already exist in most states and have almost nothing built against them.
 Any of that useful to you? clarencegetsabargain.com/book-facts.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
@@ -31794,7 +31888,8 @@
 One thing your Challenge and the book share: neither one works with a kid alone in a room. It is Lexile AD 620L — Adult Directed, the trade's code for read-with rather than read-alone — and the mother explains every concept on the page, so whoever is reading gets handed the script. Parent, teacher or grandparent, the reading stops every few pages because the kid asks something.
 Worth a conversation? I'd rather compare notes with the one other person who put spending first than pitch anybody.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -31852,7 +31947,8 @@
 For a parenting audience the format may matter more than the content. Lexile AD 620L — the AD is Adult Directed, the industry's own label for a book meant to be read *with* a child rather than left in their room. Mom explains every concept on the page, so the parent gets handed the script instead of being expected to know it. "Do we have a 529?" is a question a seven-year-old asks in the middle of page six, not after. Grandparents get the same deal, and they tend to enjoy it more.
 Would it work for your audience — podcast, newsletter, or neither? A no is a fine answer and faster than a maybe.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
@@ -31909,7 +32005,8 @@
 The other half of the craft problem: it is written for an adult voice. Lexile AD 620L — Adult Directed — with the mother carrying every explanation, so whoever reads aloud gets handed the script. A series lives or dies on whether the grown-up still enjoys the fourth reading. You would know inside a page whether mine does.
 Would you read it and tell me where it stops being a story? I'll trade — send me a Noah and I'll read it properly.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -31968,7 +32065,8 @@
 And the handoff you teach is the mechanism itself. The book is Lexile AD 620L — Adult Directed, the trade's own label for a book meant to be read *with* a child, not left in a bedroom — and Mom explains everything on the page, so the adult reading aloud is handed the script rather than asked to know the material. A parent who feels unqualified to teach money can still run it. Classroom, kitchen table, grandparent's couch: the reading stops every few pages because somebody asks.
 Two questions, either useful. Does the spending-before-saving sequence hold up against what you see in families? And is there a version of this that belongs in front of the parents you train?
 clarencegetsabargain.com/book-facts.html · https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
@@ -32030,7 +32128,8 @@
 The real question: does anything in the literature speak to elementary spending competence, or is that band simply unstudied? Either answer is useful to me.
 clarencegetsabargain.com/book-facts.html
 Jonathan Bach
-Attorney and children's book author, Baltimore</t>
+Attorney and children's book author, Baltimore
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -32091,7 +32190,8 @@
 Ages 6–10, inside the Bookshelf's 4–10 band. Catalogued Lexile AD 620L — Adult Directed, which is how the Bookshelf's titles are meant to be used anyway.
 Two questions. Was the saving weighting deliberate, or just what existed? And is the selection process still running?
 clarencegetsabargain.com/book-facts.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr">
@@ -32161,7 +32261,8 @@
 The question I would actually like answered: is there work on when price competence forms, and whether early exposure to comparison changes anything measurable later? If the honest answer is that it is unstudied because it is unmeasurable at that age, that is worth knowing too.
 clarencegetsabargain.com/book-facts.html
 Jonathan Bach
-Attorney and children's book author, Baltimore</t>
+Attorney and children's book author, Baltimore
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
@@ -32340,7 +32441,8 @@
 Why I am writing to development rather than to a classroom: this is unusually easy to fund. A bank or credit union sponsoring a classroom set gets its name on every book that goes home to a family in its assessment area, the curriculum costs the sponsor nothing because it is already free, and I have a CRA-ready memo written in examiner-friendly language. A funder can point at 25 books, one classroom, and a pre/post instrument. And because it is catalogued AD 620L — Adult Directed — it doubles as family engagement: the same book works at a kitchen table with a parent or a grandparent reading.
 Is a sponsored classroom set something HCZ's funders would recognise, or does everything need to attach to an existing program line?
 clarencegetsabargain.com/resources/grant-in-a-box.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr">
@@ -32401,7 +32503,8 @@
 Alaska has its own complications on distance and travel, and virtual read-alouds work for this.
 Does a read-aloud fit how JA Alaska builds a volunteer session, or does everything have to run through national curriculum?
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
@@ -32524,7 +32627,8 @@
 The claim I would defend hardest is the delayed one, and it is the same claim Troutwood makes about projections: the value is not in the twenty minutes. It is in month eighteen, in a real store, when the kid hits a money moment and the book fires back. Recognition first, then the habit.
 Does the elementary end fit anything Troutwood does, or is that below the floor?
 clarencegetsabargain.com/book-facts.html
-Jonathan</t>
+Jonathan
+P.S. Yes, the em dashes are load-bearing. I've used them as long as I can remember and I'm not quitting now on account of the robots.</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
@@ -32585,7 +32689,8 @@
 The whole thing rests on one instruction a teacher can act on the same week: stop bringing kids to the store as cargo, bring them as staff. Every activity in the set is a version of that.
 The honest question: what makes a free teacher resource actually get used rather than downloaded and forgotten? You have watched that happen more times than I have, and I would rather fix it now.
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. I've used em dashes as long as I can remember and I'm not about to stop now because somebody might accuse me of being AI.</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
@@ -32829,7 +32934,8 @@
 Those look complementary rather than competing to me: yours gives a kid the categories in their hands, mine walks them through the mechanics of one transaction in twenty minutes.
 Worth a conversation about whether they belong near each other? And separately — if you think spending-before-saving is wrong, you are one of very few people whose disagreement would actually change my mind.
 https://heyzine.com/flip-book/eeb1ef6cff.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr">
@@ -32884,13 +32990,14 @@
       <c r="K69" s="5" t="inlineStr">
         <is>
           <t>Sandy — FCCLA members are a decade older than my readers, so take this as a service-project idea rather than a curriculum pitch. I think it's a good one.
-Your chapters run community service. A high schooler reading a money book to a second-grade class is about the cleanest version of that I can think of — it needs no budget, no training, and one afternoon.
+Your chapters run community service. A high schooler reading a money book to a second-grade class is about the cleanest version of that I can think of — it needs no budget, no training, and one afternoon. The book teaches spending rather than saving, on the argument that saving is the second thing a child does with money and spending is the first.
 The book is Clarence Gets a Bargain, 36 pages, ages 6-10. It follows one purchase the whole way, which is the thing that makes it work as a read-aloud rather than a lecture: a boy wants a robot, earns it with chores and grades, reads the sale ads at the kitchen table, compares two models on a shelf, takes the cheaper one on purpose, hands a coupon to the cashier, meets sales tax, and then has to live with what he chose. Idea to post-receipt; sixteen-plus concepts and nobody in it says "budget" — the twenty-one-term glossary in the back is page-referenced to the story, so the reader can field questions without preparing.
 The read-aloud is the entire project, so the spec matters. Lexile AD 620L — the AD is Adult Directed, the trade's own code for a book built to be read *with* a child rather than handed to one. About twenty minutes out loud, which is a class visit with time left for questions, and the mother explains every concept inside the text. A high schooler can read it cold to a second-grade class and field the questions straight off the page. Nothing to memorize, nothing to prepare, no training call beforehand.
 There is also a free browser-based pretend register the younger kids can run afterward — a markdown, a coupon, sales tax, and a total that changes in front of them.
 Does that fit how chapters choose service projects, or am I inventing a use case? Everything is free and ungated either way.
 clarencegetsabargain.com/educator-toolkit.html
-Jonathan</t>
+Jonathan
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
@@ -33602,7 +33709,7 @@
         </is>
       </c>
       <c r="I82" s="5" t="n">
-        <v>2794</v>
+        <v>2932</v>
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
@@ -33618,7 +33725,8 @@
 Wrong about that? You'd know better than anyone. clarencegetsabargain.com/book-facts.html has the specs, and I'll send a copy if it's useful.
 Jonathan Bach
 Attorney and children's book author, Baltimore
-questions@clarencegetsabargain.com</t>
+questions@clarencegetsabargain.com
+P.S. The em dashes are mine. I've used them as long as I can remember and I'm not giving them up now because a machine got hold of them.</t>
         </is>
       </c>
       <c r="K82" s="5" t="inlineStr"/>

--- a/CGB_MASTER_outreach.xlsx
+++ b/CGB_MASTER_outreach.xlsx
@@ -1110,11 +1110,11 @@
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="n">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Joel — no login, no email capture, no funnel. Four 45-minute lesson plans, a pre/post assessment with the answer key, and a 23-row crosswalk, all built against the National Standards and all free. I'd like it in the Clearinghouse. Does it clear the bar as you read the criteria? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Joel — no login, no email capture, no funnel. Four 45-minute lesson plans, a pre/post assessment with the answer key, and a 23-row crosswalk, all built against the National Standards and all free. I'd like it in the Clearinghouse. Does it clear the bar as you read the criteria? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -1295,11 +1295,11 @@
       <c r="G11" s="5" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="n">
-        <v>652</v>
+        <v>667</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Yanely — you've said the gaps show up long before high school. I wrote the K-5 version, and it teaches spending because that's the transaction a six-year-old actually performs. Does NGPF ever point teachers below ninth grade, or is that outside the remit? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. For teachers: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Yanely — you've said the gaps show up long before high school. I wrote the K-5 version, and it teaches spending because that's the transaction a six-year-old actually performs. Does NGPF ever point teachers below ninth grade, or is that outside the remit? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. For teachers: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -1356,11 +1356,11 @@
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="n">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Leslie — a Bookshelf question, not a pitch. The Money as You Grow selections skew toward saving and earning. Mine teaches the transaction itself, right through the register. Is the shelf still open, and who does the evaluating? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Leslie — a Bookshelf question, not a pitch. The Money as You Grow selections skew toward saving and earning. Mine teaches the transaction itself, right through the register. Is the shelf still open, and who does the evaluating? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -1379,7 +1379,7 @@
 Here is the piece I keep circling. The moment a kid makes that first purchase, they have entered a relationship that comes with rights, and nobody teaches a seven-year-old they have any. An adult knows to keep the receipt and that a broken thing can go back. A child thinks the deal ends when the bag is handed over.
 I know the full rights picture crosses agencies — warranties and returns are FTC, product safety is CPSC. I'm not asking CFPB to cover those. I'm asking whether there's appetite within Money as You Grow for material that treats the child as a consumer with standing on the financial side, the day they first spend, rather than only as a saver in training.
 Realistic version of the ask: is the Bookshelf still evaluating titles, and who owns it now? And if the framing above is interesting, I'd trade ten minutes for your read on it.
-One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it.
+The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it.
 The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html
 The book in four minutes: https://heyzine.com/flip-book/eeb1ef6cff.html
 Jonathan</t>
@@ -1427,11 +1427,11 @@
       <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Ken — my book and its free K-5 classroom materials are aligned to Money Smart for Young People, with a crosswalk mapping every concept to the specific standard rather than asking you to take my word. Is there a process for a title to sit alongside Money Smart materials, or is that not how it works? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Print it here: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ken — my book and its free K-5 classroom materials are aligned to Money Smart for Young People, with a crosswalk mapping every concept to the specific standard rather than asking you to take my word. Is there a process for a title to sit alongside Money Smart materials, or is that not how it works? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Print it here: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -1745,11 +1745,11 @@
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="n">
-        <v>630</v>
+        <v>645</v>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Tracy — a public-private partnership is how a K-5 resource actually scales, since elementary rarely gets its own budget line. It's a 36-page picture book plus free ungated teacher pack against five frameworks. Fit inside the partnership? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tracy — a public-private partnership is how a K-5 resource actually scales, since elementary rarely gets its own budget line. It's a 36-page picture book plus free ungated teacher pack against five frameworks. Fit inside the partnership? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -2541,11 +2541,11 @@
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="n">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Bethann — a bankers association reaches classrooms and families at once, which is the distribution a K-5 book needs and rarely gets. Mine is five frameworks, free zero-prep lessons, plus a grant packet if a member bank wanted to fund classroom sets. Fit Utah's outreach? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Bethann — a bankers association reaches classrooms and families at once, which is the distribution a K-5 book needs and rarely gets. Mine is five frameworks, free zero-prep lessons, plus a grant packet if a member bank wanted to fund classroom sets. Fit Utah's outreach? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -2909,11 +2909,11 @@
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="n">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Jillian — Intuit for Education is built around real financial decisions, which is my book's entire structure: one purchase, ad to register, sales tax included. Mine sits at K-5, below your usual band. Does the framing match how you think about curriculum? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jillian — Intuit for Education is built around real financial decisions, which is my book's entire structure: one purchase, ad to register, sales tax included. Mine sits at K-5, below your usual band. Does the framing match how you think about curriculum? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -2970,11 +2970,11 @@
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="n">
-        <v>651</v>
+        <v>666</v>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Saskia — Promise Academy is deliberate about what earns classroom time, which is the right instinct. Mine teaches the complete purchase, sales tax included, and the family activity was built for a kitchen table. Classrooms or family programming — or neither? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Saskia — Promise Academy is deliberate about what earns classroom time, which is the right instinct. Mine teaches the complete purchase, sales tax included, and the family activity was built for a kitchen table. Classrooms or family programming — or neither? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -3156,11 +3156,11 @@
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="n">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Susan — you've directed a center for economic education for years. My K-5 book argues the elementary band is underserved because everything gets built for high school. Aligned to CEE and four others. Does that match what you see? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Susan — you've directed a center for economic education for years. My K-5 book argues the elementary band is underserved because everything gets built for high school. Aligned to CEE and four others. Does that match what you see? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -3281,11 +3281,11 @@
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr"/>
       <c r="I43" s="5" t="n">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Dr. Taylor — Montgomery County sets what reaches a lot of classrooms. Mine is a K-5 picture book with a free zero-prep lesson set, five frameworks, nothing consumable to reorder next August. The honest question is placement rather than merit: classroom, library, or family night? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Taylor — Montgomery County sets what reaches a lot of classrooms. Mine is a K-5 picture book with a free zero-prep lesson set, five frameworks, nothing consumable to reorder next August. The honest question is placement rather than merit: classroom, library, or family night? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
@@ -3657,11 +3657,11 @@
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="n">
-        <v>652</v>
+        <v>667</v>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Prince — real respect for the Wesley Learns books; you got kids to investing without it feeling like homework. Mine sits one rung below. Before a kid invests, he has to survive a store. Ad, aisle, comparison, coupon, register. Complementary rather than competitive, I think. Trade copies? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Prince — real respect for the Wesley Learns books; you got kids to investing without it feeling like homework. Mine sits one rung below. Before a kid invests, he has to survive a store. Ad, aisle, comparison, coupon, register. Complementary rather than competitive, I think. Trade copies? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
@@ -3811,11 +3811,11 @@
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="n">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Scott — as a researcher you'll want the claim tested. Mine: consumer transaction competence is taught almost nowhere in K-5, despite being the money behavior kids perform first. Is there literature contradicting me? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Scott — as a researcher you'll want the claim tested. Mine: consumer transaction competence is taught almost nowhere in K-5, despite being the money behavior kids perform first. Is there literature contradicting me? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr"/>
@@ -3849,11 +3849,11 @@
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Alison — early elementary curriculum plus research is the combination most likely to catch a flaw in my premise. I argue spending is developmentally the first money skill and the field teaches saving instead. Does that hold at early-elementary level? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Alison — early elementary curriculum plus research is the combination most likely to catch a flaw in my premise. I argue spending is developmentally the first money skill and the field teaches saving instead. Does that hold at early-elementary level? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr"/>
@@ -3955,11 +3955,11 @@
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="n">
-        <v>617</v>
+        <v>632</v>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Purnendu — you work in youth financial literacy and you're close to the age group. Mine teaches six-year-olds to spend well rather than to save. Does it read like something a real kid finishes, or does the teaching poke through? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Purnendu — you work in youth financial literacy and you're close to the age group. Mine teaches six-year-olds to spend well rather than to save. Does it read like something a real kid finishes, or does the teaching poke through? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr"/>
@@ -4069,11 +4069,11 @@
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="n">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>Sandhya — Literary Safari builds media that respects kids, which was the bar I aimed at. Mine gives a six-year-old a real financial decision with a real tradeoff and lets him make it himself. I'd take your read on positioning. One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sandhya — Literary Safari builds media that respects kids, which was the bar I aimed at. Mine gives a six-year-old a real financial decision with a real tradeoff and lets him make it himself. I'd take your read on positioning. The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr"/>
@@ -4107,11 +4107,11 @@
       <c r="G60" s="5" t="inlineStr"/>
       <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>Dr. Martin-Knox — a superintendent who's a lifelong learner is the read I hoped for. Mine is K-5 with free standards-aligned lessons, and elementary is where financial literacy gets politely skipped. Where would it fit in your district? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Martin-Knox — a superintendent who's a lifelong learner is the read I hoped for. Mine is K-5 with free standards-aligned lessons, and elementary is where financial literacy gets politely skipped. Where would it fit in your district? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr"/>
@@ -4145,11 +4145,11 @@
       <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="n">
-        <v>651</v>
+        <v>666</v>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Dr. McCoy — you've stabilized whole systems, so you know which resources survive contact with an actual building. I wrote a picture book with zero-prep lessons and nothing to reorder. Does it hold up at K-12 scale, or is it too small to matter? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. McCoy — you've stabilized whole systems, so you know which resources survive contact with an actual building. I wrote a picture book with zero-prep lessons and nothing to reorder. Does it hold up at K-12 scale, or is it too small to matter? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr"/>
@@ -4183,11 +4183,11 @@
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Denise — financial literacy politely skips K-5 and turns up in ninth grade acting surprised. Mine doesn't. 36 pages, four zero-prep lessons, a 23-row crosswalk you can check rather than take on faith, and a K-5 teacher with 30+ years who told me what to cut. Clear your bar? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Denise — financial literacy politely skips K-5 and turns up in ninth grade acting surprised. Mine doesn't. 36 pages, four zero-prep lessons, a 23-row crosswalk you can check rather than take on faith, and a K-5 teacher with 30+ years who told me what to cut. Clear your bar? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr"/>
@@ -4221,11 +4221,11 @@
       <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr"/>
       <c r="I63" s="5" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Sarai — a Spanish immersion magnet raises a question I should ask outright: the book is English-only, though the free companion activities have a Spanish toggle. Does that limit it too much for your classrooms, or does it still work? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sarai — a Spanish immersion magnet raises a question I should ask outright: the book is English-only, though the free companion activities have a Spanish toggle. Does that limit it too much for your classrooms, or does it still work? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr"/>
@@ -4297,11 +4297,11 @@
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="n">
-        <v>677</v>
+        <v>692</v>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>David — a senior curriculum designer can tell in five minutes whether something was built to teach or built to look like it was. Mine has four zero-prep lessons, assessments, and a 23-row crosswalk, all written alongside the book rather than bolted on afterward. Does the design hold? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>David — a senior curriculum designer can tell in five minutes whether something was built to teach or built to look like it was. Mine has four zero-prep lessons, assessments, and a 23-row crosswalk, all written alongside the book rather than bolted on afterward. Does the design hold? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr"/>
@@ -4335,11 +4335,11 @@
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Kevin — a CEE Master Teacher running LifeFinanceEd is the read I want most. My K-5 book aligns to CEE, Jump$tart, Common Core, and FDIC Money Smart, and it is a spending book, not a saving one. Does that framing hold up against how you actually teach it? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. For teachers: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kevin — a CEE Master Teacher running LifeFinanceEd is the read I want most. My K-5 book aligns to CEE, Jump$tart, Common Core, and FDIC Money Smart, and it is a spending book, not a saving one. Does that framing hold up against how you actually teach it? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. For teachers: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr"/>
@@ -4563,11 +4563,11 @@
       <c r="G72" s="5" t="inlineStr"/>
       <c r="H72" s="5" t="inlineStr"/>
       <c r="I72" s="5" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>Ruth — a self-described cheerleader for personal finance education is exactly who I want reading this. My K-5 book comes with free ungated content: four lessons, assessments, a 23-row crosswalk. Any of it fit your educational content? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. For teachers: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ruth — a self-described cheerleader for personal finance education is exactly who I want reading this. My K-5 book comes with free ungated content: four lessons, assessments, a 23-row crosswalk. Any of it fit your educational content? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. For teachers: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr"/>
@@ -4601,11 +4601,11 @@
       <c r="G73" s="5" t="inlineStr"/>
       <c r="H73" s="5" t="inlineStr"/>
       <c r="I73" s="5" t="n">
-        <v>605</v>
+        <v>620</v>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>Samantha — as Maine Jump$tart VP you know exactly how thin the elementary shelf is. Mine is K-5 against the National Standards with a free teacher materials. Route into what Maine Jump$tart shares with teachers? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Samantha — as Maine Jump$tart VP you know exactly how thin the elementary shelf is. Mine is K-5 against the National Standards with a free teacher materials. Route into what Maine Jump$tart shares with teachers? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. The classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr"/>
@@ -4753,11 +4753,11 @@
       <c r="G77" s="5" t="inlineStr"/>
       <c r="H77" s="5" t="inlineStr"/>
       <c r="I77" s="5" t="n">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>Sandra — my K-5 book and free classroom pack are aligned to Money Smart for Young People, crosswalk included. Is there a route for outside materials to sit alongside Money Smart, or is that closed by policy? Either answer is useful. One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sandra — my K-5 book and free classroom pack are aligned to Money Smart for Young People, crosswalk included. Is there a route for outside materials to sit alongside Money Smart, or is that closed by policy? Either answer is useful. The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Lesson plans: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr"/>
@@ -4791,11 +4791,11 @@
       <c r="G78" s="5" t="inlineStr"/>
       <c r="H78" s="5" t="inlineStr"/>
       <c r="I78" s="5" t="n">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>Christian — teacher success is the whole ballgame, and elementary teachers have close to nothing for financial literacy. I built a free K-5 lesson set around a picture book: four lessons, assessments, a crosswalk, zero prep. Would NGPF ever surface something below ninth grade? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. For teachers: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Christian — teacher success is the whole ballgame, and elementary teachers have close to nothing for financial literacy. I built a free K-5 lesson set around a picture book: four lessons, assessments, a crosswalk, zero prep. Would NGPF ever surface something below ninth grade? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. For teachers: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K78" s="5" t="inlineStr"/>
@@ -5153,11 +5153,11 @@
       <c r="G87" s="5" t="inlineStr"/>
       <c r="H87" s="5" t="inlineStr"/>
       <c r="I87" s="5" t="n">
-        <v>598</v>
+        <v>613</v>
       </c>
       <c r="J87" s="5" t="inlineStr">
         <is>
-          <t>John — as a financial education administrator you decide what actually gets used. Mine is K-5 plus a free zero-prep teaching pack against five frameworks. Elementary is usually the gap. Fit your programs? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>John — as a financial education administrator you decide what actually gets used. Mine is K-5 plus a free zero-prep teaching pack against five frameworks. Elementary is usually the gap. Fit your programs? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K87" s="5" t="inlineStr"/>
@@ -5533,11 +5533,11 @@
       <c r="G97" s="5" t="inlineStr"/>
       <c r="H97" s="5" t="inlineStr"/>
       <c r="I97" s="5" t="n">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="J97" s="5" t="inlineStr">
         <is>
-          <t>Elissa — a STEAM innovator and storytime advocate is the right test for a read-aloud. Mine has a genuine comic turn in the middle that kids react to out loud, and it teaches the complete purchase, sales tax included. Storytime material, or too transactional? Happy to send a copy. One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Elissa — a STEAM innovator and storytime advocate is the right test for a read-aloud. Mine has a genuine comic turn in the middle that kids react to out loud, and it teaches the complete purchase, sales tax included. Storytime material, or too transactional? Happy to send a copy. The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K97" s="5" t="inlineStr"/>
@@ -5647,11 +5647,11 @@
       <c r="G100" s="5" t="inlineStr"/>
       <c r="H100" s="5" t="inlineStr"/>
       <c r="I100" s="5" t="n">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>Jane — an elementary school librarian sees exactly which books get reshelved and which get hidden under a desk. Mine is a money book built as a read-aloud, with free zero-prep lessons behind it for your teachers. Would it work at Rockford? Glad to send a copy. One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jane — an elementary school librarian sees exactly which books get reshelved and which get hidden under a desk. Mine is a money book built as a read-aloud, with free zero-prep lessons behind it for your teachers. Would it work at Rockford? Glad to send a copy. The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K100" s="5" t="inlineStr"/>
@@ -5723,11 +5723,11 @@
       <c r="G102" s="5" t="inlineStr"/>
       <c r="H102" s="5" t="inlineStr"/>
       <c r="I102" s="5" t="n">
-        <v>657</v>
+        <v>672</v>
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>Olivia — a branch manager knows what actually leaves the building. Mine is a money book kids finish, because it's a story first: a boy, a robot, and one real trip to a store that goes sideways in the middle. Would it circulate at Northampton? Glad to send a copy. One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Olivia — a branch manager knows what actually leaves the building. Mine is a money book kids finish, because it's a story first: a boy, a robot, and one real trip to a store that goes sideways in the middle. Would it circulate at Northampton? Glad to send a copy. One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K102" s="5" t="inlineStr"/>
@@ -5857,11 +5857,11 @@
       <c r="G105" s="5" t="inlineStr"/>
       <c r="H105" s="5" t="inlineStr"/>
       <c r="I105" s="5" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>Stephanie — Money Monsters and Clarence are chasing the same five-to-ten-year-old. You came at it teacher-first, I came at it story-first. Mine is a spending book, not a saving one. As a teacher turned author: does the pedagogy survive underneath the story, or does the story eat it? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Stephanie — Money Monsters and Clarence are chasing the same five-to-ten-year-old. You came at it teacher-first, I came at it story-first. Mine is a spending book, not a saving one. As a teacher turned author: does the pedagogy survive underneath the story, or does the story eat it? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K105" s="5" t="inlineStr"/>
@@ -6009,11 +6009,11 @@
       <c r="G109" s="5" t="inlineStr"/>
       <c r="H109" s="5" t="inlineStr"/>
       <c r="I109" s="5" t="n">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>Jake — Face Your Financial Fears is about the block that already formed. Mine tries to stop one forming: six-year-old makes a real money decision, gets it right, feels competent. That's the whole design. Author to author, does it work? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jake — Face Your Financial Fears is about the block that already formed. Mine tries to stop one forming: six-year-old makes a real money decision, gets it right, feels competent. That's the whole design. Author to author, does it work? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K109" s="5" t="inlineStr"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t>Talaya — accountant, professor, author: three angles on one question. Mine is whether a picture book can teach sales tax honestly without boring a six-year-old. I think it can. Would you tell me if I'm wrong? It's written for an adult voice — Lexile AD 620L, Adult Directed, read-with rather than read-alone — with Mom carrying every explanation, so whoever reads aloud gets handed the script. That constraint shaped every page. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Talaya — accountant, professor, author: three angles on one question. Mine is whether a picture book can teach sales tax straight without boring a six-year-old. I think it can. Would you tell me if I'm wrong? It's written for an adult voice — Lexile AD 620L, Adult Directed, read-with rather than read-alone — with Mom carrying every explanation, so whoever reads aloud gets handed the script. That constraint shaped every page. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr"/>
@@ -6123,11 +6123,11 @@
       <c r="G112" s="5" t="inlineStr"/>
       <c r="H112" s="5" t="inlineStr"/>
       <c r="I112" s="5" t="n">
-        <v>682</v>
+        <v>697</v>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>Ronald — you built a financial literacy curriculum, so you know what teachers actually pick up versus what they politely accept. It's a 36-page picture book with four zero-prep lessons, aimed at K-5 where most curricula don't reach. Complement Responsible Money, or compete with it? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ronald — you built a financial literacy curriculum, so you know what teachers actually pick up versus what they politely accept. It's a 36-page picture book with four zero-prep lessons, aimed at K-5 where most curricula don't reach. Complement Responsible Money, or compete with it? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr"/>
@@ -6161,11 +6161,11 @@
       <c r="G113" s="5" t="inlineStr"/>
       <c r="H113" s="5" t="inlineStr"/>
       <c r="I113" s="5" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>Dr. Branch — principal, author, and coach means you see the whole building at once. Mine teaches spending through a story, with free standards-aligned lessons behind it. Would it work at Robert F. Smith STEAM Academy, and where would you slot it? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Branch — principal, author, and coach means you see the whole building at once. Mine teaches spending through a story, with free standards-aligned lessons behind it. Would it work at Robert F. Smith STEAM Academy, and where would you slot it? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K113" s="5" t="inlineStr"/>
@@ -6237,11 +6237,11 @@
       <c r="G115" s="5" t="inlineStr"/>
       <c r="H115" s="5" t="inlineStr"/>
       <c r="I115" s="5" t="n">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>Tiffany — a CFEI who writes for kids and coaches youth is a triple read. Mine teaches the complete purchase to ages 6-10, sales tax included. Does it hold as instruction, or is the story doing all the work? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tiffany — a CFEI who writes for kids and coaches youth is a triple read. Mine teaches the complete purchase to ages 6-10, sales tax included. Does it hold as instruction, or is the story doing all the work? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr"/>
@@ -6275,11 +6275,11 @@
       <c r="G116" s="5" t="inlineStr"/>
       <c r="H116" s="5" t="inlineStr"/>
       <c r="I116" s="5" t="n">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>Pamela — The Money Lady and a fellow author; you make money approachable for a living. Mine does it for six-year-olds by teaching spending rather than saving. Does the story carry the lesson, or is it doing too much? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Pamela — The Money Lady and a fellow author; you make money approachable for a living. Mine does it for six-year-olds by teaching spending rather than saving. Does the story carry the lesson, or is it doing too much? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr"/>
@@ -6351,11 +6351,11 @@
       <c r="G118" s="5" t="inlineStr"/>
       <c r="H118" s="5" t="inlineStr"/>
       <c r="I118" s="5" t="n">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>Tonia — an author and financial wellness partner meets families where money gets real. Mine teaches a six-year-old the complete purchase, and the free family activity was built for a kitchen table. Fit the families you work with? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tonia — an author and financial wellness partner meets families where money gets real. Mine teaches a six-year-old the complete purchase, and the free family activity was built for a kitchen table. Fit the families you work with? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K118" s="5" t="inlineStr"/>
@@ -6427,11 +6427,11 @@
       <c r="G120" s="5" t="inlineStr"/>
       <c r="H120" s="5" t="inlineStr"/>
       <c r="I120" s="5" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>Kathy — as a parent educator you know money is the topic parents dodge because they feel unqualified to teach it. My read-along removes that entirely. Put it in front of the parents you coach? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kathy — as a parent educator you know money is the topic parents dodge because they feel unqualified to teach it. My read-along removes that entirely. Put it in front of the parents you coach? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K120" s="5" t="inlineStr"/>
@@ -6465,11 +6465,11 @@
       <c r="G121" s="5" t="inlineStr"/>
       <c r="H121" s="5" t="inlineStr"/>
       <c r="I121" s="5" t="n">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>Jessie — as an author-illustrator running your own imprint you'll judge both halves. Mine is written and illustrated by me, which is either an advantage or a problem, and I genuinely can't tell which. Would you say? It's written for an adult voice — Lexile AD 620L, Adult Directed, read-with rather than read-alone — with Mom carrying every explanation, so whoever reads aloud gets handed the script. That constraint shaped every page. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jessie — as an author-illustrator running your own imprint you'll judge both halves. Mine is written and illustrated by me, which is either an advantage or a problem, and I cannot tell which. Would you say? It's written for an adult voice — Lexile AD 620L, Adult Directed, read-with rather than read-alone — with Mom carrying every explanation, so whoever reads aloud gets handed the script. That constraint shaped every page. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K121" s="5" t="inlineStr"/>
@@ -6617,11 +6617,11 @@
       <c r="G125" s="5" t="inlineStr"/>
       <c r="H125" s="5" t="inlineStr"/>
       <c r="I125" s="5" t="n">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>Bertram — From Piggy Banks to Portfolios runs K-12 programs, so we're literally in the same aisle. Mine is the bottom rung: before the piggy bank, a kid has to survive a store. Fit your school programs? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Bertram — From Piggy Banks to Portfolios runs K-12 programs, so we're literally in the same aisle. Mine is the bottom rung: before the piggy bank, a kid has to survive a store. Fit your school programs? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K125" s="5" t="inlineStr"/>
@@ -6693,11 +6693,11 @@
       <c r="G127" s="5" t="inlineStr"/>
       <c r="H127" s="5" t="inlineStr"/>
       <c r="I127" s="5" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>Anna — Money Mentor and a CFEI; you'll judge fast. Mine teaches K-5 spending rather than saving, against five frameworks. Fit the people Mentora reaches? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Anna — Money Mentor and a CFEI; you'll judge fast. Mine teaches K-5 spending rather than saving, against five frameworks. Fit the people Mentora reaches? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K127" s="5" t="inlineStr"/>
@@ -6769,11 +6769,11 @@
       <c r="G129" s="5" t="inlineStr"/>
       <c r="H129" s="5" t="inlineStr"/>
       <c r="I129" s="5" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>Mapalo — a bestselling personal finance author knows what makes money land. Mine goes for the youngest possible audience and teaches the spending half. Author to author: does the premise carry? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Mapalo — a bestselling personal finance author knows what makes money land. Mine goes for the youngest possible audience and teaches the spending half. Author to author: does the premise carry? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K129" s="5" t="inlineStr"/>
@@ -6845,11 +6845,11 @@
       <c r="G131" s="5" t="inlineStr"/>
       <c r="H131" s="5" t="inlineStr"/>
       <c r="I131" s="5" t="n">
-        <v>565</v>
+        <v>580</v>
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>Jeahne — educator, author, speaker; you know how to make money click. Mine does it for six-year-olds through one shopping trip rather than a set of lessons. Fellow author: does the story carry the teaching? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jeahne — educator, author, speaker; you know how to make money click. Mine does it for six-year-olds through one shopping trip rather than a set of lessons. Fellow author: does the story carry the teaching? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K131" s="5" t="inlineStr"/>
@@ -7035,11 +7035,11 @@
       <c r="G136" s="5" t="inlineStr"/>
       <c r="H136" s="5" t="inlineStr"/>
       <c r="I136" s="5" t="n">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>John — you build learning that scales globally. Mine is K-5 with a free zero-prep classroom materials against five frameworks. Does the approach fit what Electus builds, or duplicate it? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>John — you build learning that scales globally. Mine is K-5 with a free zero-prep classroom materials against five frameworks. Does the approach fit what Electus builds, or duplicate it? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K136" s="5" t="inlineStr"/>
@@ -7136,11 +7136,11 @@
       <c r="G138" s="5" t="inlineStr"/>
       <c r="H138" s="5" t="inlineStr"/>
       <c r="I138" s="5" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>ML — the Noah series shows you can carry a lesson without smothering the story, which is my whole anxiety about my own book. Would you read it as an author and tell me if the lesson shows too much? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>ML — the Noah series shows you can carry a lesson without smothering the story, which is my whole anxiety about my own book. Would you read it as an author and tell me if the lesson shows too much? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K138" s="5" t="inlineStr">
@@ -7646,11 +7646,11 @@
       <c r="G151" s="5" t="inlineStr"/>
       <c r="H151" s="5" t="inlineStr"/>
       <c r="I151" s="5" t="n">
-        <v>608</v>
+        <v>623</v>
       </c>
       <c r="J151" s="5" t="inlineStr">
         <is>
-          <t>Hassan — you take money talks into schools, which is where mine belongs. Picture book teaching spending: comparison, markdowns, coupons, sales tax, all inside a story. Five frameworks, free zero-prep lessons, no login. Fit for your school work? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hassan — you take money talks into schools, which is where mine belongs. Picture book teaching spending: comparison, markdowns, coupons, sales tax, all inside a story. Five frameworks, free zero-prep lessons, no login. Fit for your school work? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K151" s="5" t="inlineStr"/>
@@ -7836,11 +7836,11 @@
       <c r="G156" s="5" t="inlineStr"/>
       <c r="H156" s="5" t="inlineStr"/>
       <c r="I156" s="5" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="J156" s="5" t="inlineStr">
         <is>
-          <t>Leonard — Kids Real Estate and Financial Literacy is after the same kid. Mine starts one rung earlier: before a kid invests in anything, he has to survive a store. Complement what you teach? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Leonard — Kids Real Estate and Financial Literacy is after the same kid. Mine starts one rung earlier: before a kid invests in anything, he has to survive a store. Complement what you teach? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K156" s="5" t="inlineStr"/>
@@ -7874,11 +7874,11 @@
       <c r="G157" s="5" t="inlineStr"/>
       <c r="H157" s="5" t="inlineStr"/>
       <c r="I157" s="5" t="n">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="J157" s="5" t="inlineStr">
         <is>
-          <t>Dr. Robyn — as a clinical psychologist you'll spot whether a kids' book actually respects the kid. Mine gives a six-year-old a real decision with a real tradeoff and lets him make it. No moral bolted on. Land with your audience? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Robyn — as a clinical psychologist you'll spot whether a kids' book actually respects the kid. Mine gives a six-year-old a real decision with a real tradeoff and lets him make it. No moral bolted on. Land with your audience? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K157" s="5" t="inlineStr"/>
@@ -8064,11 +8064,11 @@
       <c r="G162" s="5" t="inlineStr"/>
       <c r="H162" s="5" t="inlineStr"/>
       <c r="I162" s="5" t="n">
-        <v>534</v>
+        <v>549</v>
       </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>Lawrence — you take financial literacy on the road. Mine goes into a store: a kid runs one purchase from the sale ad to the register, tax and all. Fit the audiences you reach? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Lawrence — you take financial literacy on the road. Mine goes into a store: a kid runs one purchase from the sale ad to the register, tax and all. Fit the audiences you reach? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K162" s="5" t="inlineStr"/>
@@ -8140,11 +8140,11 @@
       <c r="G164" s="5" t="inlineStr"/>
       <c r="H164" s="5" t="inlineStr"/>
       <c r="I164" s="5" t="n">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="J164" s="5" t="inlineStr">
         <is>
-          <t>Linda — you translate money for real audiences on stage. Mine is the six-year-old translation: one purchase, ad to register, sales tax included, told as a boy and a robot. Fit your talks? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Linda — you translate money for real audiences on stage. Mine is the six-year-old translation: one purchase, ad to register, sales tax included, told as a boy and a robot. Fit your talks? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K164" s="5" t="inlineStr"/>
@@ -8254,11 +8254,11 @@
       <c r="G167" s="5" t="inlineStr"/>
       <c r="H167" s="5" t="inlineStr"/>
       <c r="I167" s="5" t="n">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="J167" s="5" t="inlineStr">
         <is>
-          <t>Becky — 28 years helping people out of debt means you've traced a lot of it back to habits set at eight. Mine tries to set the good one at six: compare before you buy, know what tax adds, take the cheaper thing on purpose. Fit the families you coach? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Becky — 28 years helping people out of debt means you've traced a lot of it back to habits set at eight. Mine tries to set the good one at six: compare before you buy, know what tax adds, take the cheaper thing on purpose. Fit the families you coach? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K167" s="5" t="inlineStr"/>
@@ -8334,11 +8334,11 @@
       <c r="G169" s="5" t="inlineStr"/>
       <c r="H169" s="5" t="inlineStr"/>
       <c r="I169" s="5" t="n">
-        <v>753</v>
+        <v>768</v>
       </c>
       <c r="J169" s="5" t="inlineStr">
         <is>
-          <t>Linda — financial parenting is your field, and spending is where parents and kids collide first, usually in an aisle, usually loudly. Mine is that scene resolved well: a six-year-old compares two robots and talks himself into the cheaper one. Built with a K-5 teacher of 30+ years, 21-term glossary, free lessons. Would you put it in front of the parents you teach? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Linda — financial parenting is your field, and spending is where parents and kids collide first, usually in an aisle, usually loudly. Mine is that scene resolved well: a six-year-old compares two robots and talks himself into the cheaper one. Built with a K-5 teacher of 30+ years, 21-term glossary, free lessons. Would you put it in front of the parents you teach? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K169" s="5" t="inlineStr">
@@ -8481,11 +8481,11 @@
       <c r="G172" s="5" t="inlineStr"/>
       <c r="H172" s="5" t="inlineStr"/>
       <c r="I172" s="5" t="n">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="J172" s="5" t="inlineStr">
         <is>
-          <t>Sue — you wrote the handbook. Mine is a 36-page full-color picture book with a free teaching pack and no Amazon listing, by choice. Brave or dumb? I'd genuinely rather have the straight answer than the polite one. It's written for an adult voice — Lexile AD 620L, Adult Directed, read-with rather than read-alone — with Mom carrying every explanation, so whoever reads aloud gets handed the script. That constraint shaped every page. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sue — you wrote the handbook. Mine is a 36-page full-color picture book with a free teaching pack and no Amazon listing, by choice. Brave or dumb? I would rather have the straight answer than the polite one. It's written for an adult voice — Lexile AD 620L, Adult Directed, read-with rather than read-alone — with Mom carrying every explanation, so whoever reads aloud gets handed the script. That constraint shaped every page. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K172" s="5" t="inlineStr"/>
@@ -8747,11 +8747,11 @@
       <c r="G179" s="5" t="inlineStr"/>
       <c r="H179" s="5" t="inlineStr"/>
       <c r="I179" s="5" t="n">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="J179" s="5" t="inlineStr">
         <is>
-          <t>Kelli — an editor with a CFP spots a thin premise in about four seconds, so here's mine, checkable: spending is the first money skill a kid uses and no picture book is built around it. Does that hold, or have I missed a title? I'd genuinely rather be corrected than published on a false premise. It's written for an adult voice — Lexile AD 620L, Adult Directed, read-with rather than read-alone — with Mom carrying every explanation, so whoever reads aloud gets handed the script. That constraint shaped every page. Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kelli — an editor with a CFP spots a thin premise in about four seconds, so here's mine, checkable: spending is the first money skill a kid uses and no picture book is built around it. Does that hold, or have I missed a title? I would rather be corrected than published on a false premise. It's written for an adult voice — Lexile AD 620L, Adult Directed, read-with rather than read-alone — with Mom carrying every explanation, so whoever reads aloud gets handed the script. That constraint shaped every page. Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K179" s="5" t="inlineStr"/>
@@ -9241,11 +9241,11 @@
       <c r="G192" s="5" t="inlineStr"/>
       <c r="H192" s="5" t="inlineStr"/>
       <c r="I192" s="5" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="J192" s="5" t="inlineStr">
         <is>
-          <t>Hillary — as a curriculum developer and editor you'll see whether the lessons were written alongside the book or bolted on afterward. Mine were written alongside. Four lessons, assessments, a 23-row crosswalk. Would you test that claim? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hillary — as a curriculum developer and editor you'll see whether the lessons were written alongside the book or bolted on afterward. Mine were written alongside. Four lessons, assessments, a 23-row crosswalk. Would you test that claim? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K192" s="5" t="inlineStr"/>
@@ -9954,11 +9954,11 @@
       <c r="G208" s="5" t="inlineStr"/>
       <c r="H208" s="5" t="inlineStr"/>
       <c r="I208" s="5" t="n">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="J208" s="5" t="inlineStr">
         <is>
-          <t>Hanna — you study financial literacy and wellbeing, so you'll spot the seams. My premise: spending is the first money skill a kid uses and no picture book is built around it. I'd value a researcher's read on whether that holds for ages 6-10. One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hanna — you study financial literacy and wellbeing, so you'll spot the seams. My premise: spending is the first money skill a kid uses and no picture book is built around it. I'd value a researcher's read on whether that holds for ages 6-10. The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K208" s="5" t="inlineStr"/>
@@ -9992,11 +9992,11 @@
       <c r="G209" s="5" t="inlineStr"/>
       <c r="H209" s="5" t="inlineStr"/>
       <c r="I209" s="5" t="n">
-        <v>577</v>
+        <v>592</v>
       </c>
       <c r="J209" s="5" t="inlineStr">
         <is>
-          <t>Casey — an award-winning financial literacy educator and founder of The Orchard Method is a tough, useful read. Mine leaves saving to everybody else. Does the approach hold up for you? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Casey — an award-winning financial literacy educator and founder of The Orchard Method is a tough, useful read. Mine leaves saving to everybody else. Does the approach hold up for you? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K209" s="5" t="inlineStr"/>
@@ -10334,11 +10334,11 @@
       <c r="G218" s="5" t="inlineStr"/>
       <c r="H218" s="5" t="inlineStr"/>
       <c r="I218" s="5" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="J218" s="5" t="inlineStr">
         <is>
-          <t>Dr. Dowell — as an economics lecturer you'll want the premise tested. Mine: we teach children saving first, but spending is the transaction they perform first, so the sequence is backwards. Does it survive scrutiny? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Dowell — as an economics lecturer you'll want the premise tested. Mine: we teach children saving first, but spending is the transaction they perform first, so the sequence is backwards. Does it survive scrutiny? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K218" s="5" t="inlineStr"/>
@@ -10372,11 +10372,11 @@
       <c r="G219" s="5" t="inlineStr"/>
       <c r="H219" s="5" t="inlineStr"/>
       <c r="I219" s="5" t="n">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="J219" s="5" t="inlineStr">
         <is>
-          <t>Dr. Nahidi — you teach finance at graduate level, where the gaps students carry up from childhood are plainly visible. Mine tries to close one at six. I'd value an academic's read on whether the premise is sound or merely convenient. Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Nahidi — you teach finance at graduate level, where the gaps students carry up from childhood are plainly visible. Mine tries to close one at six. I'd value an academic's read on whether the premise is sound or just convenient. Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K219" s="5" t="inlineStr"/>
@@ -10506,11 +10506,11 @@
       <c r="G222" s="5" t="inlineStr"/>
       <c r="H222" s="5" t="inlineStr"/>
       <c r="I222" s="5" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="J222" s="5" t="inlineStr">
         <is>
-          <t>William — teaching finance at Delta Charter means you see students arrive with gaps set a decade earlier. Mine tries to close one at six. Does the premise hold from where you sit? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>William — teaching finance at Delta Charter means you see students arrive with gaps set a decade earlier. Mine tries to close one at six. Does the premise hold from where you sit? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K222" s="5" t="inlineStr"/>
@@ -10544,11 +10544,11 @@
       <c r="G223" s="5" t="inlineStr"/>
       <c r="H223" s="5" t="inlineStr"/>
       <c r="I223" s="5" t="n">
-        <v>596</v>
+        <v>611</v>
       </c>
       <c r="J223" s="5" t="inlineStr">
         <is>
-          <t>Sloane — you're studying English and education, which makes you a better test than most people I'm asking. Does my book read like something a real first grader would sit through, or does the lesson show? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sloane — you're studying English and education, which makes you a better test than most people I'm asking. Does my book read like something a real first grader would sit through, or does the lesson show? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K223" s="5" t="inlineStr"/>
@@ -10810,11 +10810,11 @@
       <c r="G230" s="5" t="inlineStr"/>
       <c r="H230" s="5" t="inlineStr"/>
       <c r="I230" s="5" t="n">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="J230" s="5" t="inlineStr">
         <is>
-          <t>Kim — a center for economic education knows what teachers actually adopt versus politely accept. Mine is aligned to CEE and four others with a full crosswalk, and elementary is usually the thinnest shelf. Fit your teacher work? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kim — a center for economic education knows what teachers actually adopt versus politely accept. Mine is aligned to CEE and four others with a full crosswalk, and elementary is usually the thinnest shelf. Fit your teacher work? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K230" s="5" t="inlineStr"/>
@@ -10848,11 +10848,11 @@
       <c r="G231" s="5" t="inlineStr"/>
       <c r="H231" s="5" t="inlineStr"/>
       <c r="I231" s="5" t="n">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="J231" s="5" t="inlineStr">
         <is>
-          <t>Maria — Tennessee's council decides what reaches classrooms. Mine is K-5 plus a free zero-prep classroom pack against five frameworks. Elementary is where most states have the least. Route in? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Maria — Tennessee's council decides what reaches classrooms. Mine is K-5 plus a free zero-prep classroom pack against five frameworks. Elementary is where most states have the least. Route in? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K231" s="5" t="inlineStr"/>
@@ -11076,11 +11076,11 @@
       <c r="G237" s="5" t="inlineStr"/>
       <c r="H237" s="5" t="inlineStr"/>
       <c r="I237" s="5" t="n">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="J237" s="5" t="inlineStr">
         <is>
-          <t>Dr. Niranjan — a finance academic's read on a children's book premise: spending competence precedes saving competence and is taught almost nowhere. Does that survive in your context? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Niranjan — a finance academic's read on a children's book premise: spending competence precedes saving competence and is taught almost nowhere. Does that survive in your context? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K237" s="5" t="inlineStr"/>
@@ -11228,11 +11228,11 @@
       <c r="G241" s="5" t="inlineStr"/>
       <c r="H241" s="5" t="inlineStr"/>
       <c r="I241" s="5" t="n">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="J241" s="5" t="inlineStr">
         <is>
-          <t>Carly — executive education is a long way from a picture book, so briefly: mine teaches the complete purchase to six-year-olds. If your college does community or K-12 outreach, would it fit? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Carly — executive education is a long way from a picture book, so briefly: mine teaches the complete purchase to six-year-olds. If your college does community or K-12 outreach, would it fit? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K241" s="5" t="inlineStr"/>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="J244" s="5" t="inlineStr">
         <is>
-          <t>Jaime — an ethnic studies lens raises a fair question about my book: it's a working family talking honestly about bills and tradeoffs, which is rarer in this category than it should be. Would you tell me whether it rings true? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jaime — an ethnic studies lens raises a fair question about my book: it's a working family talking straight about bills and tradeoffs, which is rarer in this category than it should be. Would you tell me whether it rings true? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K244" s="5" t="inlineStr"/>
@@ -11456,11 +11456,11 @@
       <c r="G247" s="5" t="inlineStr"/>
       <c r="H247" s="5" t="inlineStr"/>
       <c r="I247" s="5" t="n">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="J247" s="5" t="inlineStr">
         <is>
-          <t>Cherry — you run one of the few credit union financial education programs that isn't a poster and a pencil. Mine is K-5 with the whole lesson set free, plus a grant packet with the math already done: 25 copies, $499.75, sponsor logo optional. Built so somebody in your seat doesn't have to build the case from scratch. One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Cherry — you run one of the few credit union financial education programs that isn't a poster and a pencil. Mine is K-5 with the whole lesson set free, plus a grant packet with the math already done: 25 copies, $499.75, sponsor logo optional. Built so somebody in your seat doesn't have to build the case from scratch. The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K247" s="5" t="inlineStr"/>
@@ -11494,11 +11494,11 @@
       <c r="G248" s="5" t="inlineStr"/>
       <c r="H248" s="5" t="inlineStr"/>
       <c r="I248" s="5" t="n">
-        <v>653</v>
+        <v>668</v>
       </c>
       <c r="J248" s="5" t="inlineStr">
         <is>
-          <t>Monica — you run financial education for a credit union, so the useful detail is this: there's a grant-ready packet behind the book with exact cost math for classroom sets, built for precisely this kind of sponsorship. Fit a member or school program? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Monica — you run financial education for a credit union, so the useful detail is this: there's a grant-ready packet behind the book with exact cost math for classroom sets, built for precisely this kind of sponsorship. Fit a member or school program? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K248" s="5" t="inlineStr"/>
@@ -11532,11 +11532,11 @@
       <c r="G249" s="5" t="inlineStr"/>
       <c r="H249" s="5" t="inlineStr"/>
       <c r="I249" s="5" t="n">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="J249" s="5" t="inlineStr">
         <is>
-          <t>Angela — in-school financial wellness is the hardest version of this job and the most useful. Mine is a K-5 read-aloud with zero-prep lessons, which is what a visiting educator actually needs rather than what looks good in a binder. Fit your Visions work? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Angela — in-school financial wellness is the hardest version of this job and the most useful. Mine is a K-5 read-aloud with zero-prep lessons, which is what a visiting educator actually needs rather than what looks good in a binder. Fit your Visions work? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K249" s="5" t="inlineStr"/>
@@ -11570,11 +11570,11 @@
       <c r="G250" s="5" t="inlineStr"/>
       <c r="H250" s="5" t="inlineStr"/>
       <c r="I250" s="5" t="n">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="J250" s="5" t="inlineStr">
         <is>
-          <t>Jon — a financial education specialist with a psychology background will care that the book is built around one decision rather than a list of concepts. Fit a Cy-Fair member or family program? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jon — a financial education specialist with a psychology background will care that the book is built around one decision rather than a list of concepts. Fit a Cy-Fair member or family program? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K250" s="5" t="inlineStr"/>
@@ -11608,11 +11608,11 @@
       <c r="G251" s="5" t="inlineStr"/>
       <c r="H251" s="5" t="inlineStr"/>
       <c r="I251" s="5" t="n">
-        <v>613</v>
+        <v>628</v>
       </c>
       <c r="J251" s="5" t="inlineStr">
         <is>
-          <t>Brittney — SchoolsFirst puts you in front of educators constantly, which is the audience for the free teacher materials as much as the book. Four lessons, assessments, a crosswalk, all ungated. Fit a member program? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Brittney — SchoolsFirst puts you in front of educators constantly, which is the audience for the free teacher materials as much as the book. Four lessons, assessments, a crosswalk, all ungated. Fit a member program? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K251" s="5" t="inlineStr"/>
@@ -11646,11 +11646,11 @@
       <c r="G252" s="5" t="inlineStr"/>
       <c r="H252" s="5" t="inlineStr"/>
       <c r="I252" s="5" t="n">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="J252" s="5" t="inlineStr">
         <is>
-          <t>Judette — a bank financial literacy officer usually needs something CRA-reportable rather than merely nice. Mine has a grant-ready packet with cost math, designed to be funded and counted. Fit Byline's programs? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Judette — a bank financial literacy officer usually needs something CRA-reportable rather than just nice. Mine has a grant-ready packet with cost math, designed to be funded and counted. Fit Byline's programs? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K252" s="5" t="inlineStr"/>
@@ -11684,11 +11684,11 @@
       <c r="G253" s="5" t="inlineStr"/>
       <c r="H253" s="5" t="inlineStr"/>
       <c r="I253" s="5" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="J253" s="5" t="inlineStr">
         <is>
-          <t>Kayleigh — CTE banking students are older than my readers, but HRCU's community work probably isn't. Mine is a K-5 read-aloud with free lessons. Fit an elementary outreach program? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kayleigh — CTE banking students are older than my readers, but HRCU's community work probably isn't. Mine is a K-5 read-aloud with free lessons. Fit an elementary outreach program? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K253" s="5" t="inlineStr"/>
@@ -11798,11 +11798,11 @@
       <c r="G256" s="5" t="inlineStr"/>
       <c r="H256" s="5" t="inlineStr"/>
       <c r="I256" s="5" t="n">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="J256" s="5" t="inlineStr">
         <is>
-          <t>Sarah — MidFirst's education work reaches schools and families both. Mine is K-5 with free zero-prep lessons and a grant-ready packet if the bank wanted to fund classroom sets. Worth a look? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sarah — MidFirst's education work reaches schools and families both. Mine is K-5 with free zero-prep lessons and a grant-ready packet if the bank wanted to fund classroom sets. Worth a look? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K256" s="5" t="inlineStr"/>
@@ -11912,11 +11912,11 @@
       <c r="G259" s="5" t="inlineStr"/>
       <c r="H259" s="5" t="inlineStr"/>
       <c r="I259" s="5" t="n">
-        <v>584</v>
+        <v>599</v>
       </c>
       <c r="J259" s="5" t="inlineStr">
         <is>
-          <t>Corey — as a personal finance educator you know spending is where habits form and where nobody teaches. Mine is the K-5 version: one purchase, ad to register. Fit the learners you reach? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Corey — as a personal finance educator you know spending is where habits form and where nobody teaches. Mine is the K-5 version: one purchase, ad to register. Fit the learners you reach? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K259" s="5" t="inlineStr"/>
@@ -12026,11 +12026,11 @@
       <c r="G262" s="5" t="inlineStr"/>
       <c r="H262" s="5" t="inlineStr"/>
       <c r="I262" s="5" t="n">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="J262" s="5" t="inlineStr">
         <is>
-          <t>Alfredo — financial inclusion meets families where the gaps are widest, and elementary is where almost nothing exists. Mine is K-5 plus a free teacher pack. Fit a member or community program? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Alfredo — financial inclusion meets families where the gaps are widest, and elementary is where almost nothing exists. Mine is K-5 plus a free teacher pack. Fit a member or community program? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K262" s="5" t="inlineStr"/>
@@ -12292,11 +12292,11 @@
       <c r="G269" s="5" t="inlineStr"/>
       <c r="H269" s="5" t="inlineStr"/>
       <c r="I269" s="5" t="n">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="J269" s="5" t="inlineStr">
         <is>
-          <t>Brittany — a financial education manager needs material that works without you standing in the room. Mine is a read-aloud with zero-prep lessons a teacher or parent runs alone. Fit your programs? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Brittany — a financial education manager needs material that works without you standing in the room. Mine is a read-aloud with zero-prep lessons a teacher or parent runs alone. Fit your programs? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K269" s="5" t="inlineStr"/>
@@ -12330,11 +12330,11 @@
       <c r="G270" s="5" t="inlineStr"/>
       <c r="H270" s="5" t="inlineStr"/>
       <c r="I270" s="5" t="n">
-        <v>598</v>
+        <v>613</v>
       </c>
       <c r="J270" s="5" t="inlineStr">
         <is>
-          <t>Kayde — as coordinator you're the one who has to make it work on the ground, which is a different job from choosing it. Mine needs no prep, no platform, nothing consumable. Fit a program you coordinate? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kayde — as coordinator you're the one who has to make it work on the ground, which is a different job from choosing it. Mine needs no prep, no platform, nothing consumable. Fit a program you coordinate? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K270" s="5" t="inlineStr"/>
@@ -12558,11 +12558,11 @@
       <c r="G276" s="5" t="inlineStr"/>
       <c r="H276" s="5" t="inlineStr"/>
       <c r="I276" s="5" t="n">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="J276" s="5" t="inlineStr">
         <is>
-          <t>Melissa — a curriculum specialist in an elementary school is exactly the read I want. I wrote a picture book with zero-prep lessons against five frameworks. Would it work in Lanier's classrooms? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Melissa — a curriculum specialist in an elementary school is exactly the read I want. I wrote a picture book with zero-prep lessons against five frameworks. Would it work in Lanier's classrooms? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K276" s="5" t="inlineStr"/>
@@ -12596,11 +12596,11 @@
       <c r="G277" s="5" t="inlineStr"/>
       <c r="H277" s="5" t="inlineStr"/>
       <c r="I277" s="5" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="J277" s="5" t="inlineStr">
         <is>
-          <t>Samantha — reading intervention plus SEL is an unusual pairing and useful here: mine is and the money decision doubles as an impulse-control lesson. Fit either side of your work? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Samantha — reading intervention plus SEL is an unusual pairing and useful here: mine is and the money decision doubles as an impulse-control lesson. Fit either side of your work? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K277" s="5" t="inlineStr"/>
@@ -12634,11 +12634,11 @@
       <c r="G278" s="5" t="inlineStr"/>
       <c r="H278" s="5" t="inlineStr"/>
       <c r="I278" s="5" t="n">
-        <v>631</v>
+        <v>646</v>
       </c>
       <c r="J278" s="5" t="inlineStr">
         <is>
-          <t>Suzanne — early childhood and school readiness is the exact window. Mine starts where a kid actually starts with money, which is spending it. One trip, one real decision, no worksheet anywhere. Fit an early-grades classroom in Stockton? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Suzanne — early childhood and school readiness is the exact window. Mine starts where a kid actually starts with money, which is spending it. One trip, one real decision, no worksheet anywhere. Fit an early-grades classroom in Stockton? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K278" s="5" t="inlineStr"/>
@@ -12740,11 +12740,11 @@
       <c r="G281" s="5" t="inlineStr"/>
       <c r="H281" s="5" t="inlineStr"/>
       <c r="I281" s="5" t="n">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="J281" s="5" t="inlineStr">
         <is>
-          <t>Jake — DCPS classrooms tell you fast whether something works. Mine is K-5, teaching spending, with four zero-prep standards-aligned lessons. Elementary is usually where financial literacy gets skipped entirely. Where would it fit? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jake — DCPS classrooms tell you fast whether something works. Mine is K-5, teaching spending, with four zero-prep standards-aligned lessons. Elementary is usually where financial literacy gets skipped entirely. Where would it fit? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K281" s="5" t="inlineStr"/>
@@ -12778,11 +12778,11 @@
       <c r="G282" s="5" t="inlineStr"/>
       <c r="H282" s="5" t="inlineStr"/>
       <c r="I282" s="5" t="n">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="J282" s="5" t="inlineStr">
         <is>
-          <t>Shawn — congratulations on the superintendency. As you set priorities: elementary financial literacy is the gap nobody gets assigned. I made a picture book plus free classroom materials for K-5. Early grades or family programming — or not a priority this year? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Shawn — congratulations on the superintendency. As you set priorities: elementary financial literacy is the gap nobody gets assigned. I made a picture book plus free classroom materials for K-5. Early grades or family programming — or not a priority this year? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K282" s="5" t="inlineStr"/>
@@ -12816,11 +12816,11 @@
       <c r="G283" s="5" t="inlineStr"/>
       <c r="H283" s="5" t="inlineStr"/>
       <c r="I283" s="5" t="n">
-        <v>614</v>
+        <v>629</v>
       </c>
       <c r="J283" s="5" t="inlineStr">
         <is>
-          <t>Dr. Pinder — a superintendent's read matters most on placement rather than merit. Mine is K-5, teaching spending through a story, free standards-aligned lessons. Classroom, library, or family night. Where would you put it? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Pinder — a superintendent's read matters most on placement rather than merit. Mine is K-5, teaching spending through a story, free standards-aligned lessons. Classroom, library, or family night. Where would you put it? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K283" s="5" t="inlineStr"/>
@@ -12854,11 +12854,11 @@
       <c r="G284" s="5" t="inlineStr"/>
       <c r="H284" s="5" t="inlineStr"/>
       <c r="I284" s="5" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="J284" s="5" t="inlineStr">
         <is>
-          <t>Mallory — assistant principal, adjunct, and speaker means you've taught every audience there is. Mine is K-5, and a six-year-old makes one real money decision and gets it right. Does it land in an elementary classroom? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Mallory — assistant principal, adjunct, and speaker means you've taught every audience there is. Mine is K-5, and a six-year-old makes one real money decision and gets it right. Does it land in an elementary classroom? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K284" s="5" t="inlineStr"/>
@@ -12892,11 +12892,11 @@
       <c r="G285" s="5" t="inlineStr"/>
       <c r="H285" s="5" t="inlineStr"/>
       <c r="I285" s="5" t="n">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="J285" s="5" t="inlineStr">
         <is>
-          <t>Angela — as head of school you set what students read. Mine is a 36-page picture book teaching money through a story, with free standards-aligned lessons. Would it earn a place in your school? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Angela — as head of school you set what students read. Mine is a 36-page picture book teaching money through a story, with free standards-aligned lessons. Would it earn a place in your school? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K285" s="5" t="inlineStr"/>
@@ -12930,11 +12930,11 @@
       <c r="G286" s="5" t="inlineStr"/>
       <c r="H286" s="5" t="inlineStr"/>
       <c r="I286" s="5" t="n">
-        <v>592</v>
+        <v>607</v>
       </c>
       <c r="J286" s="5" t="inlineStr">
         <is>
-          <t>Kristen — as a director of education you decide what reaches learners. Mine skips saving and teaches spending, with four zero-prep lessons. Elementary is usually the thinnest shelf. Fit your programs? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kristen — as a director of education you decide what reaches learners. Mine skips saving and teaches spending, with four zero-prep lessons. Elementary is usually the thinnest shelf. Fit your programs? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K286" s="5" t="inlineStr"/>
@@ -12968,11 +12968,11 @@
       <c r="G287" s="5" t="inlineStr"/>
       <c r="H287" s="5" t="inlineStr"/>
       <c r="I287" s="5" t="n">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="J287" s="5" t="inlineStr">
         <is>
-          <t>Sarah — curriculum and instruction is where a book like this lives or dies. Mine has a 23-row crosswalk and four 45-minute lessons written alongside the book rather than added after. Would you look at whether that claim holds? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sarah — curriculum and instruction is where a book like this lives or dies. Mine has a 23-row crosswalk and four 45-minute lessons written alongside the book rather than added after. Would you look at whether that claim holds? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K287" s="5" t="inlineStr"/>
@@ -13006,11 +13006,11 @@
       <c r="G288" s="5" t="inlineStr"/>
       <c r="H288" s="5" t="inlineStr"/>
       <c r="I288" s="5" t="n">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="J288" s="5" t="inlineStr">
         <is>
-          <t>Malori — you lead financial literacy curriculum and build educational games, so engagement is your bar, not mine. Mine holds a six-year-old through 36 pages because it's a story first. Fit your curriculum? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Malori — you lead financial literacy curriculum and build educational games, so engagement is your bar, not mine. Mine holds a six-year-old through 36 pages because it's a story first. Fit your curriculum? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K288" s="5" t="inlineStr"/>
@@ -13044,11 +13044,11 @@
       <c r="G289" s="5" t="inlineStr"/>
       <c r="H289" s="5" t="inlineStr"/>
       <c r="I289" s="5" t="n">
-        <v>597</v>
+        <v>612</v>
       </c>
       <c r="J289" s="5" t="inlineStr">
         <is>
-          <t>Michael — education and outreach at Troutwood aims at making the future tangible. Mine makes the present tangible for a six-year-old: one purchase, compared and paid for, tax included. Fit your outreach? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Michael — education and outreach at Troutwood aims at making the future tangible. Mine makes the present tangible for a six-year-old: one purchase, compared and paid for, tax included. Fit your outreach? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K289" s="5" t="inlineStr"/>
@@ -13082,11 +13082,11 @@
       <c r="G290" s="5" t="inlineStr"/>
       <c r="H290" s="5" t="inlineStr"/>
       <c r="I290" s="5" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="J290" s="5" t="inlineStr">
         <is>
-          <t>Peggy — as a consultant and instructional designer you'll see whether the lessons teach or just look like they do. Mine are four 45-minute plans with assessments and a crosswalk. Would you look? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Peggy — as a consultant and instructional designer you'll see whether the lessons teach or just look like they do. Mine are four 45-minute plans with assessments and a crosswalk. Would you look? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K290" s="5" t="inlineStr"/>
@@ -13120,11 +13120,11 @@
       <c r="G291" s="5" t="inlineStr"/>
       <c r="H291" s="5" t="inlineStr"/>
       <c r="I291" s="5" t="n">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="J291" s="5" t="inlineStr">
         <is>
-          <t>Kim — you built your own financial literacy framework, so you think in systems. Mine is narrow by design: one transaction taught completely rather than a survey of concepts. Does narrow beat broad at K-5? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kim — you built your own financial literacy framework, so you think in systems. Mine is narrow by design: one transaction taught completely rather than a survey of concepts. Does narrow beat broad at K-5? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K291" s="5" t="inlineStr"/>
@@ -13158,11 +13158,11 @@
       <c r="G292" s="5" t="inlineStr"/>
       <c r="H292" s="5" t="inlineStr"/>
       <c r="I292" s="5" t="n">
-        <v>571</v>
+        <v>586</v>
       </c>
       <c r="J292" s="5" t="inlineStr">
         <is>
-          <t>Peter — on an advisory committee you weigh which resources are worth backing. Mine is K-5 plus a free ungated lesson set against five frameworks. Fit the committee's work? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Peter — on an advisory committee you weigh which resources are worth backing. Mine is K-5 plus a free ungated lesson set against five frameworks. Fit the committee's work? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K292" s="5" t="inlineStr"/>
@@ -13234,11 +13234,11 @@
       <c r="G294" s="5" t="inlineStr"/>
       <c r="H294" s="5" t="inlineStr"/>
       <c r="I294" s="5" t="n">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="J294" s="5" t="inlineStr">
         <is>
-          <t>Amy-Marie — head of early childhood is the reader I hoped for. Mine starts where kids start with money, which is spending it. One trip, one decision, no worksheet. Would it work in your setting? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Amy-Marie — head of early childhood is the reader I hoped for. Mine starts where kids start with money, which is spending it. One trip, one decision, no worksheet. Would it work in your setting? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K294" s="5" t="inlineStr"/>
@@ -13386,11 +13386,11 @@
       <c r="G298" s="5" t="inlineStr"/>
       <c r="H298" s="5" t="inlineStr"/>
       <c r="I298" s="5" t="n">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="J298" s="5" t="inlineStr">
         <is>
-          <t>Dr. Martirano — a superintendent who's also a digital education fellow sees the whole board. Mine is deliberately analog: a printed read-along with free digital lessons behind it. Does that combination still work in Allegany County, or is print a liability now? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Martirano — a superintendent who's also a digital education fellow sees the whole board. Mine is deliberately analog: a printed read-along with free digital lessons behind it. Does that combination still work in Allegany County, or is print a liability now? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K298" s="5" t="inlineStr"/>
@@ -13424,11 +13424,11 @@
       <c r="G299" s="5" t="inlineStr"/>
       <c r="H299" s="5" t="inlineStr"/>
       <c r="I299" s="5" t="n">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="J299" s="5" t="inlineStr">
         <is>
-          <t>Christopher — Norristown sets what reaches every elementary classroom. Mine teaches the complete purchase, sales tax included, with zero-prep lessons. Classroom, library, or family night? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Christopher — Norristown sets what reaches every elementary classroom. Mine teaches the complete purchase, sales tax included, with zero-prep lessons. Classroom, library, or family night? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K299" s="5" t="inlineStr"/>
@@ -13462,11 +13462,11 @@
       <c r="G300" s="5" t="inlineStr"/>
       <c r="H300" s="5" t="inlineStr"/>
       <c r="I300" s="5" t="n">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="J300" s="5" t="inlineStr">
         <is>
-          <t>Stephanie — a K-8 curriculum leader can tell whether lessons were built alongside a book or afterward. Mine were built alongside: four lessons, assessments, a 23-row crosswalk. Would you test that? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Stephanie — a K-8 curriculum leader can tell whether lessons were built alongside a book or afterward. Mine were built alongside: four lessons, assessments, a 23-row crosswalk. Would you test that? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K300" s="5" t="inlineStr"/>
@@ -13500,11 +13500,11 @@
       <c r="G301" s="5" t="inlineStr"/>
       <c r="H301" s="5" t="inlineStr"/>
       <c r="I301" s="5" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="J301" s="5" t="inlineStr">
         <is>
-          <t>Mansi — curriculum design and academic coordination is where my materials should get judged. Four zero-prep lessons, a pre/post assessment with answer key, a 23-row crosswalk. Does the design hold up? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Mansi — curriculum design and academic coordination is where my materials should get judged. Four zero-prep lessons, a pre/post assessment with answer key, a 23-row crosswalk. Does the design hold up? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K301" s="5" t="inlineStr"/>
@@ -13538,11 +13538,11 @@
       <c r="G302" s="5" t="inlineStr"/>
       <c r="H302" s="5" t="inlineStr"/>
       <c r="I302" s="5" t="n">
-        <v>636</v>
+        <v>651</v>
       </c>
       <c r="J302" s="5" t="inlineStr">
         <is>
-          <t>Nikole — Banzai builds financial literacy for real classrooms, and K-5 is the band with the least of it. It's a 36-page picture book plus free zero-prep lessons against five frameworks. Does the approach fit how you think about it? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Nikole — Banzai builds financial literacy for real classrooms, and K-5 is the band with the least of it. It's a 36-page picture book plus free zero-prep lessons against five frameworks. Does the approach fit how you think about it? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K302" s="5" t="inlineStr"/>
@@ -13576,11 +13576,11 @@
       <c r="G303" s="5" t="inlineStr"/>
       <c r="H303" s="5" t="inlineStr"/>
       <c r="I303" s="5" t="n">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="J303" s="5" t="inlineStr">
         <is>
-          <t>Hema — leading an early childhood school, you set what young kids read. Mine is a read-along that teaches money through story, free lessons behind it. Would it work in your setting? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hema — leading an early childhood school, you set what young kids read. Mine is a read-along that teaches money through story, free lessons behind it. Would it work in your setting? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K303" s="5" t="inlineStr"/>
@@ -13614,11 +13614,11 @@
       <c r="G304" s="5" t="inlineStr"/>
       <c r="H304" s="5" t="inlineStr"/>
       <c r="I304" s="5" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="J304" s="5" t="inlineStr">
         <is>
-          <t>Kevin — operations and instruction together means you see what survives implementation rather than what looks good in a pilot. Mine runs 36 pages with nothing to reorder and free lessons. Hold up in a real building? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kevin — operations and instruction together means you see what survives implementation rather than what looks good in a pilot. Mine runs 36 pages with nothing to reorder and free lessons. Hold up in a real building? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K304" s="5" t="inlineStr"/>
@@ -13652,11 +13652,11 @@
       <c r="G305" s="5" t="inlineStr"/>
       <c r="H305" s="5" t="inlineStr"/>
       <c r="I305" s="5" t="n">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="J305" s="5" t="inlineStr">
         <is>
-          <t>Ashley — an elementary educator who also does curriculum and ed tech sees both sides. Mine is a printed read-aloud with free digital lessons. Would it work in your classroom? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ashley — an elementary educator who also does curriculum and ed tech sees both sides. Mine is a printed read-aloud with free digital lessons. Would it work in your classroom? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K305" s="5" t="inlineStr"/>
@@ -13690,11 +13690,11 @@
       <c r="G306" s="5" t="inlineStr"/>
       <c r="H306" s="5" t="inlineStr"/>
       <c r="I306" s="5" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="J306" s="5" t="inlineStr">
         <is>
-          <t>Bailey — elementary curriculum development is where my materials get judged. Mine were built alongside the book: four zero-prep lessons, assessments, a 23-row crosswalk. Would you look? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Bailey — elementary curriculum development is where my materials get judged. Mine were built alongside the book: four zero-prep lessons, assessments, a 23-row crosswalk. Would you look? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K306" s="5" t="inlineStr"/>
@@ -13728,11 +13728,11 @@
       <c r="G307" s="5" t="inlineStr"/>
       <c r="H307" s="5" t="inlineStr"/>
       <c r="I307" s="5" t="n">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="J307" s="5" t="inlineStr">
         <is>
-          <t>Debra — as director of elementary curriculum you decide what reaches K-5, which is the band financial literacy skips entirely. Mine has a full standards crosswalk. Clear your bar? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Debra — as director of elementary curriculum you decide what reaches K-5, which is the band financial literacy skips entirely. Mine has a full standards crosswalk. Clear your bar? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K307" s="5" t="inlineStr"/>
@@ -13766,11 +13766,11 @@
       <c r="G308" s="5" t="inlineStr"/>
       <c r="H308" s="5" t="inlineStr"/>
       <c r="I308" s="5" t="n">
-        <v>599</v>
+        <v>614</v>
       </c>
       <c r="J308" s="5" t="inlineStr">
         <is>
-          <t>Ellen — curriculum facilitators see whether teachers actually adopt something or shelve it without telling you. Mine needs no prep and nothing consumable. Survive your elementary classrooms? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ellen — curriculum facilitators see whether teachers actually adopt something or shelve it without telling you. Mine needs no prep and nothing consumable. Survive your elementary classrooms? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K308" s="5" t="inlineStr"/>
@@ -13804,11 +13804,11 @@
       <c r="G309" s="5" t="inlineStr"/>
       <c r="H309" s="5" t="inlineStr"/>
       <c r="I309" s="5" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="J309" s="5" t="inlineStr">
         <is>
-          <t>Esabel — you'll ask about standards first. Mine maps to Jump$tart, Common Core Math and ELA, CEE, and FDIC Money Smart, with a 23-row crosswalk. Worth a review? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Esabel — you'll ask about standards first. Mine maps to Jump$tart, Common Core Math and ELA, CEE, and FDIC Money Smart, with a 23-row crosswalk. Worth a review? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K309" s="5" t="inlineStr"/>
@@ -13842,11 +13842,11 @@
       <c r="G310" s="5" t="inlineStr"/>
       <c r="H310" s="5" t="inlineStr"/>
       <c r="I310" s="5" t="n">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="J310" s="5" t="inlineStr">
         <is>
-          <t>Jessica — an elementary curriculum specialist knows what teachers abandon halfway through. Mine is a 36-page read-aloud with zero-prep lessons and nothing to reorder. Survive your classrooms? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jessica — an elementary curriculum specialist knows what teachers abandon halfway through. Mine is a 36-page read-aloud with zero-prep lessons and nothing to reorder. Survive your classrooms? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K310" s="5" t="inlineStr"/>
@@ -13880,11 +13880,11 @@
       <c r="G311" s="5" t="inlineStr"/>
       <c r="H311" s="5" t="inlineStr"/>
       <c r="I311" s="5" t="n">
-        <v>585</v>
+        <v>600</v>
       </c>
       <c r="J311" s="5" t="inlineStr">
         <is>
-          <t>Julie — as senior director of elementary curriculum you decide what reaches a lot of classrooms. Mine teaches the complete purchase, sales tax included, with a full crosswalk. Worth a look? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Julie — as senior director of elementary curriculum you decide what reaches a lot of classrooms. Mine teaches the complete purchase, sales tax included, with a full crosswalk. Worth a look? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K311" s="5" t="inlineStr"/>
@@ -13918,11 +13918,11 @@
       <c r="G312" s="5" t="inlineStr"/>
       <c r="H312" s="5" t="inlineStr"/>
       <c r="I312" s="5" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="J312" s="5" t="inlineStr">
         <is>
-          <t>Katie — elementary curriculum is exactly the band that gets skipped on financial literacy. I made a picture book plus four free zero-prep lessons. Fit your district? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Katie — elementary curriculum is exactly the band that gets skipped on financial literacy. I made a picture book plus four free zero-prep lessons. Fit your district? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K312" s="5" t="inlineStr"/>
@@ -13956,11 +13956,11 @@
       <c r="G313" s="5" t="inlineStr"/>
       <c r="H313" s="5" t="inlineStr"/>
       <c r="I313" s="5" t="n">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="J313" s="5" t="inlineStr">
         <is>
-          <t>Marcella — a curriculum and instruction specialist will test whether the lessons match the book. Mine were written alongside it, 23-row crosswalk included. Would you look at the alignment? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Marcella — a curriculum and instruction specialist will test whether the lessons match the book. Mine were written alongside it, 23-row crosswalk included. Would you look at the alignment? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K313" s="5" t="inlineStr"/>
@@ -13994,11 +13994,11 @@
       <c r="G314" s="5" t="inlineStr"/>
       <c r="H314" s="5" t="inlineStr"/>
       <c r="I314" s="5" t="n">
-        <v>619</v>
+        <v>634</v>
       </c>
       <c r="J314" s="5" t="inlineStr">
         <is>
-          <t>Dr. Berry — as director of elementary curriculum you set what K-5 actually gets. Financial literacy usually stops before fifth grade entirely. I wrote a picture book plus free standards-aligned lessons. Worth reviewing? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Berry — as director of elementary curriculum you set what K-5 actually gets. Financial literacy usually stops before fifth grade entirely. I wrote a picture book plus free standards-aligned lessons. Worth reviewing? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K314" s="5" t="inlineStr"/>
@@ -14032,11 +14032,11 @@
       <c r="G315" s="5" t="inlineStr"/>
       <c r="H315" s="5" t="inlineStr"/>
       <c r="I315" s="5" t="n">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="J315" s="5" t="inlineStr">
         <is>
-          <t>Shelly — an elementary curriculum coordinator sees what teachers actually pick up. Mine requires no prep, nothing consumable, and it's a story kids finish. Fit your schools? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Shelly — an elementary curriculum coordinator sees what teachers actually pick up. Mine requires no prep, nothing consumable, and it's a story kids finish. Fit your schools? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K315" s="5" t="inlineStr"/>
@@ -14070,11 +14070,11 @@
       <c r="G316" s="5" t="inlineStr"/>
       <c r="H316" s="5" t="inlineStr"/>
       <c r="I316" s="5" t="n">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="J316" s="5" t="inlineStr">
         <is>
-          <t>Suzan — elementary curriculum directors are the right filter for this. Mine is K-5, teaching spending, with assessments and a 23-row crosswalk behind it. Worth a review? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Suzan — elementary curriculum directors are the right filter for this. Mine is K-5, teaching spending, with assessments and a 23-row crosswalk behind it. Worth a review? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K316" s="5" t="inlineStr"/>
@@ -14108,11 +14108,11 @@
       <c r="G317" s="5" t="inlineStr"/>
       <c r="H317" s="5" t="inlineStr"/>
       <c r="I317" s="5" t="n">
-        <v>594</v>
+        <v>609</v>
       </c>
       <c r="J317" s="5" t="inlineStr">
         <is>
-          <t>Tamika — an elementary curriculum specialist knows whether something fits a real scope and sequence. Mine is one 36-page book plus four 45-minute lessons against five frameworks. Would you look? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tamika — an elementary curriculum specialist knows whether something fits a real scope and sequence. Mine is one 36-page book plus four 45-minute lessons against five frameworks. Would you look? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K317" s="5" t="inlineStr"/>
@@ -14146,11 +14146,11 @@
       <c r="G318" s="5" t="inlineStr"/>
       <c r="H318" s="5" t="inlineStr"/>
       <c r="I318" s="5" t="n">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="J318" s="5" t="inlineStr">
         <is>
-          <t>Toby — you coordinate across ELA, math, and social studies, which is unusual and useful: mine hits all three at once. Comparison math, a read-aloud narrative, and consumer economics. Fit? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Toby — you coordinate across ELA, math, and social studies, which is unusual and useful: mine hits all three at once. Comparison math, a read-aloud narrative, and consumer economics. Fit? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K318" s="5" t="inlineStr"/>
@@ -14222,11 +14222,11 @@
       <c r="G320" s="5" t="inlineStr"/>
       <c r="H320" s="5" t="inlineStr"/>
       <c r="I320" s="5" t="n">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="J320" s="5" t="inlineStr">
         <is>
-          <t>Noelani — you design adult learning, so you'll know whether my teacher materials teach. Four 45-minute plans, a pre/post assessment with answer key, a 23-row crosswalk, all free. Would you look at the instructional design? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Noelani — you design adult learning, so you'll know whether my teacher materials teach. Four 45-minute plans, a pre/post assessment with answer key, a 23-row crosswalk, all free. Would you look at the instructional design? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K320" s="5" t="inlineStr"/>
@@ -14260,11 +14260,11 @@
       <c r="G321" s="5" t="inlineStr"/>
       <c r="H321" s="5" t="inlineStr"/>
       <c r="I321" s="5" t="n">
-        <v>602</v>
+        <v>617</v>
       </c>
       <c r="J321" s="5" t="inlineStr">
         <is>
-          <t>Jennifer — as an EdTech implementation lead you know adoption dies on friction. Mine has none: a book and print-ready lessons. No login, no platform, no seats to provision. Fit any state program you run? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jennifer — as an EdTech implementation lead you know adoption dies on friction. Mine has none: a book and print-ready lessons. No login, no platform, no seats to provision. Fit any state program you run? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K321" s="5" t="inlineStr"/>
@@ -14298,11 +14298,11 @@
       <c r="G322" s="5" t="inlineStr"/>
       <c r="H322" s="5" t="inlineStr"/>
       <c r="I322" s="5" t="n">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="J322" s="5" t="inlineStr">
         <is>
-          <t>Gil — a curriculum developer working on financial literacy math will care that mine has real arithmetic in it: comparing two prices, applying a percentage off, adding sales tax. Fit what you're building? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Gil — a curriculum developer working on financial literacy math will care that mine has real arithmetic in it: comparing two prices, applying a percentage off, adding sales tax. Fit what you're building? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher pack: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K322" s="5" t="inlineStr"/>
@@ -14336,11 +14336,11 @@
       <c r="G323" s="5" t="inlineStr"/>
       <c r="H323" s="5" t="inlineStr"/>
       <c r="I323" s="5" t="n">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="J323" s="5" t="inlineStr">
         <is>
-          <t>Amanda — a practitioner gut-check. Mine teaches spending through a story about a boy and a robot, no worksheet anywhere. Does it hold early-childhood kids, or does it skew older than I think? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Amanda — a practitioner gut-check. Mine teaches spending through a story about a boy and a robot, no worksheet anywhere. Does it hold early-childhood kids, or does it skew older than I think? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom pack: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K323" s="5" t="inlineStr"/>
@@ -14374,11 +14374,11 @@
       <c r="G324" s="5" t="inlineStr"/>
       <c r="H324" s="5" t="inlineStr"/>
       <c r="I324" s="5" t="n">
-        <v>564</v>
+        <v>579</v>
       </c>
       <c r="J324" s="5" t="inlineStr">
         <is>
-          <t>Charlene — would you tell me whether this skews too old? 36-page read-aloud at one shopping trip start to finish. I aimed at 6-10 but I'd rather be corrected than confident. One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Charlene — would you tell me whether this skews too old? 36-page read-aloud at one shopping trip start to finish. I aimed at 6-10 but I'd rather be corrected than confident. One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K324" s="5" t="inlineStr"/>
@@ -14526,11 +14526,11 @@
       <c r="G328" s="5" t="inlineStr"/>
       <c r="H328" s="5" t="inlineStr"/>
       <c r="I328" s="5" t="n">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="J328" s="5" t="inlineStr">
         <is>
-          <t>Sito — you've led K-12 at system level, so you know financial literacy usually starts in ninth grade and acts like that was always the plan. Mine is the elementary on-ramp. Fit a district push? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sito — you've led K-12 at system level, so you know financial literacy usually starts in ninth grade and acts like that was always the plan. Mine is the elementary on-ramp. Fit a district push? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K328" s="5" t="inlineStr"/>
@@ -14564,11 +14564,11 @@
       <c r="G329" s="5" t="inlineStr"/>
       <c r="H329" s="5" t="inlineStr"/>
       <c r="I329" s="5" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="J329" s="5" t="inlineStr">
         <is>
-          <t>Ashley — an ECE strategist who keeps wellbeing central will get what I was after: a six-year-old making a real decision without being lectured at. Fit the early-childhood settings you advise? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ashley — an ECE strategist who keeps wellbeing central will get what I was after: a six-year-old making a real decision without being lectured at. Fit the early-childhood settings you advise? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K329" s="5" t="inlineStr"/>
@@ -14640,11 +14640,11 @@
       <c r="G331" s="5" t="inlineStr"/>
       <c r="H331" s="5" t="inlineStr"/>
       <c r="I331" s="5" t="n">
-        <v>547</v>
+        <v>562</v>
       </c>
       <c r="J331" s="5" t="inlineStr">
         <is>
-          <t>Cassandra — a financial educator running operations knows what gets used versus what gets filed. Mine needs no prep and nothing consumable. Fit a member or family program you run? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Cassandra — a financial educator running operations knows what gets used versus what gets filed. Mine needs no prep and nothing consumable. Fit a member or family program you run? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K331" s="5" t="inlineStr"/>
@@ -14678,11 +14678,11 @@
       <c r="G332" s="5" t="inlineStr"/>
       <c r="H332" s="5" t="inlineStr"/>
       <c r="I332" s="5" t="n">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="J332" s="5" t="inlineStr">
         <is>
-          <t>Chris — CoinSprout Kids and my book are after the same kid from different directions: yours digital, mine a printed read-along. Do those complement each other, or is print a liability now? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Chris — CoinSprout Kids and my book are after the same kid from different directions: yours digital, mine a printed read-along. Do those complement each other, or is print a liability now? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K332" s="5" t="inlineStr"/>
@@ -14716,11 +14716,11 @@
       <c r="G333" s="5" t="inlineStr"/>
       <c r="H333" s="5" t="inlineStr"/>
       <c r="I333" s="5" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="J333" s="5" t="inlineStr">
         <is>
-          <t>Christina — Think Pieces is building financial education for children, so we're solving the same problem. I made a picture book plus free ungated teacher pack for K-5. Worth comparing notes, or trading copies? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Christina — Think Pieces is building financial education for children, so we're solving the same problem. I made a picture book plus free ungated teacher pack for K-5. Worth comparing notes, or trading copies? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K333" s="5" t="inlineStr"/>
@@ -14754,11 +14754,11 @@
       <c r="G334" s="5" t="inlineStr"/>
       <c r="H334" s="5" t="inlineStr"/>
       <c r="I334" s="5" t="n">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="J334" s="5" t="inlineStr">
         <is>
-          <t>Claudia — community engagement at NFEC puts you in front of real families. Mine is a K-5 read-along with a free family activity built for a kitchen table rather than a classroom. Fit your outreach? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Claudia — community engagement at NFEC puts you in front of real families. Mine is a K-5 read-along with a free family activity built for a kitchen table rather than a classroom. Fit your outreach? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K334" s="5" t="inlineStr"/>
@@ -14868,11 +14868,11 @@
       <c r="G337" s="5" t="inlineStr"/>
       <c r="H337" s="5" t="inlineStr"/>
       <c r="I337" s="5" t="n">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="J337" s="5" t="inlineStr">
         <is>
-          <t>Ta'Donna — you help program leaders deliver measurable financial education, and measurement is the part most kids' books skip entirely. Mine has a pre/post assessment with answer key and a 25-row tracking table, all free. Fit your programs? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ta'Donna — you help program leaders deliver measurable financial education, and measurement is the part most kids' books skip entirely. Mine has a pre/post assessment with answer key and a 25-row tracking table, all free. Fit your programs? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K337" s="5" t="inlineStr"/>
@@ -14906,11 +14906,11 @@
       <c r="G338" s="5" t="inlineStr"/>
       <c r="H338" s="5" t="inlineStr"/>
       <c r="I338" s="5" t="n">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="J338" s="5" t="inlineStr">
         <is>
-          <t>Val — a self-described financial literacy disruptor leading early financial education is the right audience for a contrarian premise. Mine: we teach saving first and we have the sequence backwards. Does that land? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Val — a self-described financial literacy disruptor leading early financial education is the right audience for a contrarian premise. Mine: we teach saving first and we have the sequence backwards. Does that land? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K338" s="5" t="inlineStr"/>
@@ -14944,11 +14944,11 @@
       <c r="G339" s="5" t="inlineStr"/>
       <c r="H339" s="5" t="inlineStr"/>
       <c r="I339" s="5" t="n">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="J339" s="5" t="inlineStr">
         <is>
-          <t>Vanessa — Money Adventures and Clarence are after the same kid and the same confidence. Mine builds it through one successful purchase rather than a curriculum. As a fellow builder, does the approach land? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Vanessa — Money Adventures and Clarence are after the same kid and the same confidence. Mine builds it through one successful purchase rather than a curriculum. As a fellow builder, does the approach land? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K339" s="5" t="inlineStr"/>
@@ -15210,11 +15210,11 @@
       <c r="G346" s="5" t="inlineStr"/>
       <c r="H346" s="5" t="inlineStr"/>
       <c r="I346" s="5" t="n">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="J346" s="5" t="inlineStr">
         <is>
-          <t>Ramat — FLEX runs K-8 financial education in Pennsylvania schools, which is the exact band and the exact problem. Mine is K-5 plus free zero-prep lessons against five frameworks. Complement FLEX, or compete with it? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ramat — FLEX runs K-8 financial education in Pennsylvania schools, which is the exact band and the exact problem. Mine is K-5 plus free zero-prep lessons against five frameworks. Complement FLEX, or compete with it? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K346" s="5" t="inlineStr"/>
@@ -15248,11 +15248,11 @@
       <c r="G347" s="5" t="inlineStr"/>
       <c r="H347" s="5" t="inlineStr"/>
       <c r="I347" s="5" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="J347" s="5" t="inlineStr">
         <is>
-          <t>Alex — a published financial literacy author and educator is the read I want most. Mine argues spending is the first money skill and the category teaches saving instead. As someone who has published here — does that hold, or is it a marketing line? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Alex — a published financial literacy author and educator is the read I want most. Mine argues spending is the first money skill and the category teaches saving instead. As someone who has published here — does that hold, or is it a marketing line? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K347" s="5" t="inlineStr"/>
@@ -15362,11 +15362,11 @@
       <c r="G350" s="5" t="inlineStr"/>
       <c r="H350" s="5" t="inlineStr"/>
       <c r="I350" s="5" t="n">
-        <v>568</v>
+        <v>583</v>
       </c>
       <c r="J350" s="5" t="inlineStr">
         <is>
-          <t>James — a Barron's AP Economics author will judge accuracy first. Mine teaches comparison, percentage markdowns, and sales tax to six-year-olds. Does it get the economics right at that level, or oversimplify? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>James — a Barron's AP Economics author will judge accuracy first. Mine teaches comparison, percentage markdowns, and sales tax to six-year-olds. Does it get the economics right at that level, or oversimplify? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K350" s="5" t="inlineStr"/>
@@ -15552,11 +15552,11 @@
       <c r="G355" s="5" t="inlineStr"/>
       <c r="H355" s="5" t="inlineStr"/>
       <c r="I355" s="5" t="n">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="J355" s="5" t="inlineStr">
         <is>
-          <t>Corwin — you coach authors through self-publishing, so you'll see the strategic question rather than the literary one: I've deliberately skipped Amazon and sell direct. Brave or dumb? I'd genuinely value the straight answer. It's written for an adult voice — Lexile AD 620L, Adult Directed, read-with rather than read-alone — with Mom carrying every explanation, so whoever reads aloud gets handed the script. That constraint shaped every page. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Corwin — you coach authors through self-publishing, so you'll see the strategic question rather than the literary one: I've deliberately skipped Amazon and sell direct. Brave or dumb? I would value the straight answer. It's written for an adult voice — Lexile AD 620L, Adult Directed, read-with rather than read-alone — with Mom carrying every explanation, so whoever reads aloud gets handed the script. That constraint shaped every page. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K355" s="5" t="inlineStr"/>
@@ -15704,11 +15704,11 @@
       <c r="G359" s="5" t="inlineStr"/>
       <c r="H359" s="5" t="inlineStr"/>
       <c r="I359" s="5" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="J359" s="5" t="inlineStr">
         <is>
-          <t>Cara — ECE keynote speaker, author, and teacher trainer is three useful angles at once. Mine is a K-5 read-aloud teaching the first money behavior kids actually perform. Right age developmentally, or does it skew old? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Cara — ECE keynote speaker, author, and teacher trainer is three useful angles at once. Mine is a K-5 read-aloud teaching the first money behavior kids actually perform. Right age developmentally, or does it skew old? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K359" s="5" t="inlineStr"/>
@@ -15780,11 +15780,11 @@
       <c r="G361" s="5" t="inlineStr"/>
       <c r="H361" s="5" t="inlineStr"/>
       <c r="I361" s="5" t="n">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J361" s="5" t="inlineStr">
         <is>
-          <t>David — The Squeaky Wheel proved a kids' money book can be genuinely funny. Mine tries the same trick on spending rather than saving. Author to author, would you tell me if the humor lands or thuds? It's written for an adult voice — Lexile AD 620L, Adult Directed, read-with rather than read-alone — with Mom carrying every explanation, so whoever reads aloud gets handed the script. That constraint shaped every page. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>David — The Squeaky Wheel proved a kids' money book can be properly funny. Mine tries the same trick on spending rather than saving. Author to author, would you tell me if the humor lands or thuds? It's written for an adult voice — Lexile AD 620L, Adult Directed, read-with rather than read-alone — with Mom carrying every explanation, so whoever reads aloud gets handed the script. That constraint shaped every page. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K361" s="5" t="inlineStr"/>
@@ -17469,11 +17469,11 @@
       <c r="G404" s="5" t="inlineStr"/>
       <c r="H404" s="5" t="inlineStr"/>
       <c r="I404" s="5" t="n">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="J404" s="5" t="inlineStr">
         <is>
-          <t>Elizabeth — financial education at the Department of Education is the mission my book starts on, just twelve years early. Mine is K-5, teaching spending rather than saving, against five frameworks. Fit any program you touch, or a steer on who'd know? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Elizabeth — financial education at the Department of Education is the mission my book starts on, just twelve years early. Mine is K-5, teaching spending rather than saving, against five frameworks. Fit any program you touch, or a steer on who'd know? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K404" s="5" t="inlineStr">
@@ -17593,11 +17593,11 @@
       <c r="G406" s="5" t="inlineStr"/>
       <c r="H406" s="5" t="inlineStr"/>
       <c r="I406" s="5" t="n">
-        <v>637</v>
+        <v>652</v>
       </c>
       <c r="J406" s="5" t="inlineStr">
         <is>
-          <t>Rob — you create financial education resources, so you know what teachers actually use versus what they politely download once. Mine is a K-5 picture book with four zero-prep lessons, assessments, and a 23-row crosswalk, all free and ungated. Fit your catalog, or duplicate it? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Rob — you create financial education resources, so you know what teachers actually use versus what they politely download once. Mine is a K-5 picture book with four zero-prep lessons, assessments, and a 23-row crosswalk, all free and ungated. Fit your catalog, or duplicate it? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K406" s="5" t="inlineStr">
@@ -17647,11 +17647,11 @@
       <c r="G407" s="5" t="inlineStr"/>
       <c r="H407" s="5" t="inlineStr"/>
       <c r="I407" s="5" t="n">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="J407" s="5" t="inlineStr">
         <is>
-          <t>Dr. Melanie — early childhood is the exact window I wrote for. Mine starts where a kid actually starts with money, which is spending it. One trip, one real decision, no worksheet anywhere. Fit an early-grades classroom in Palmdale? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Melanie — early childhood is the exact window I wrote for. Mine starts where a kid actually starts with money, which is spending it. One trip, one real decision, no worksheet anywhere. Fit an early-grades classroom in Palmdale? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free lesson set: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K407" s="5" t="inlineStr"/>
@@ -17685,11 +17685,11 @@
       <c r="G408" s="5" t="inlineStr"/>
       <c r="H408" s="5" t="inlineStr"/>
       <c r="I408" s="5" t="n">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="J408" s="5" t="inlineStr">
         <is>
-          <t>Amanda — a national curriculum consultant sees whether something was built to teach or built to look like it was. Mine has four zero-prep lessons and a 23-row crosswalk written alongside the book, not bolted on after. Does the design hold? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Amanda — a national curriculum consultant sees whether something was built to teach or built to look like it was. Mine has four zero-prep lessons and a 23-row crosswalk written alongside the book, not bolted on after. Does the design hold? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teacher materials: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K408" s="5" t="inlineStr"/>
@@ -17723,11 +17723,11 @@
       <c r="G409" s="5" t="inlineStr"/>
       <c r="H409" s="5" t="inlineStr"/>
       <c r="I409" s="5" t="n">
-        <v>622</v>
+        <v>637</v>
       </c>
       <c r="J409" s="5" t="inlineStr">
         <is>
-          <t>Hayley — a curriculum specialist will test whether the lessons match the book. Mine were written alongside it: four 45-minute plans, a pre/post assessment with answer key, a 23-row crosswalk. Would you look at the alignment? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hayley — a curriculum specialist will test whether the lessons match the book. Mine were written alongside it: four 45-minute plans, a pre/post assessment with answer key, a 23-row crosswalk. Would you look at the alignment? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free classroom materials: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K409" s="5" t="inlineStr"/>
@@ -17761,11 +17761,11 @@
       <c r="G410" s="5" t="inlineStr"/>
       <c r="H410" s="5" t="inlineStr"/>
       <c r="I410" s="5" t="n">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="J410" s="5" t="inlineStr">
         <is>
-          <t>Holden — curriculum and instruction is where a book like this lives or dies. Mine is K-5, teaching the complete purchase, sales tax included, with free zero-prep lessons. Elementary is where financial literacy gets skipped. Fit your scope? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Holden — curriculum and instruction is where a book like this lives or dies. Mine is K-5, teaching the complete purchase, sales tax included, with free zero-prep lessons. Elementary is where financial literacy gets skipped. Fit your scope? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. Free teaching pack: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K410" s="5" t="inlineStr"/>
@@ -17837,11 +17837,11 @@
       <c r="G412" s="5" t="inlineStr"/>
       <c r="H412" s="5" t="inlineStr"/>
       <c r="I412" s="5" t="n">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="J412" s="5" t="inlineStr">
         <is>
-          <t>Luke — community affairs and banking is where a fundable K-5 resource needs a champion. Mine has a grant-ready packet with the math already done: 25 copies, $499.75. Built so somebody in your seat doesn't have to build the case. Fit a community program? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Luke — community affairs and banking is where a fundable K-5 resource needs a champion. Mine has a grant-ready packet with the math already done: 25 copies, $499.75. Built so somebody in your seat doesn't have to build the case. Fit a community program? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K412" s="5" t="inlineStr"/>
@@ -17875,11 +17875,11 @@
       <c r="G413" s="5" t="inlineStr"/>
       <c r="H413" s="5" t="inlineStr"/>
       <c r="I413" s="5" t="n">
-        <v>630</v>
+        <v>645</v>
       </c>
       <c r="J413" s="5" t="inlineStr">
         <is>
-          <t>Dante — a fellow Baltimorean, and lower school is exactly the age I wrote for. Mine teaches the money skill your students use the next time they're in a store: spending, not saving. 36 pages, story first, no worksheet. Would it work at Boys' Latin? Happy to bring one by. One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dante — a fellow Baltimorean, and lower school is exactly the age I wrote for. Mine teaches the money skill your students use the next time they're in a store: spending, not saving. 36 pages, story first, no worksheet. Would it work at Boys' Latin? Happy to bring one by. One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K413" s="5" t="inlineStr"/>
@@ -17913,11 +17913,11 @@
       <c r="G414" s="5" t="inlineStr"/>
       <c r="H414" s="5" t="inlineStr"/>
       <c r="I414" s="5" t="n">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="J414" s="5" t="inlineStr">
         <is>
-          <t>Linda — head of a lower school is the reader I hoped for, and I'm local to Baltimore. Every money book stops at the piggy bank; mine starts at the register. 36 pages, story first. Would it work with your kids at Gilman? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Linda — head of a lower school is the reader I hoped for, and I'm local to Baltimore. Every money book stops at the piggy bank; mine starts at the register. 36 pages, story first. Would it work with your kids at Gilman? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K414" s="5" t="inlineStr"/>
@@ -18065,11 +18065,11 @@
       <c r="G418" s="5" t="inlineStr"/>
       <c r="H418" s="5" t="inlineStr"/>
       <c r="I418" s="5" t="n">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="J418" s="5" t="inlineStr">
         <is>
-          <t>Braden — Kidz Economy and Clarence are after the same kid. Mine is K-5 with free zero-prep lessons against five frameworks, and it teaches spending rather than saving. Complement what you've built, or compete with it? Either answer is useful. One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Braden — Kidz Economy and Clarence are after the same kid. Mine is K-5 with free zero-prep lessons against five frameworks, and it teaches spending rather than saving. Complement what you've built, or compete with it? Either answer is useful. The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K418" s="5" t="inlineStr"/>
@@ -18179,11 +18179,11 @@
       <c r="G421" s="5" t="inlineStr"/>
       <c r="H421" s="5" t="inlineStr"/>
       <c r="I421" s="5" t="n">
-        <v>586</v>
+        <v>601</v>
       </c>
       <c r="J421" s="5" t="inlineStr">
         <is>
-          <t>Courtney — a nationally recognized financial literacy educator is exactly the read I want. Mine is K-5, which is the band almost nobody builds for, and it teaches spending rather than saving. Fit your classroom or your network? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Courtney — a nationally recognized financial literacy educator is exactly the read I want. Mine is K-5, which is the band almost nobody builds for, and it teaches spending rather than saving. Fit your classroom or your network? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K421" s="5" t="inlineStr"/>
@@ -18255,11 +18255,11 @@
       <c r="G423" s="5" t="inlineStr"/>
       <c r="H423" s="5" t="inlineStr"/>
       <c r="I423" s="5" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="J423" s="5" t="inlineStr">
         <is>
-          <t>Joel — FEE plus the NAEE PD committee means you know economics education cold. Mine is K-5 against CEE, Jump$tart, Common Core, and FDIC Money Smart. Elementary is usually the thinnest shelf in the room. Fit your PD work? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Joel — FEE plus the NAEE PD committee means you know economics education cold. Mine is K-5 against CEE, Jump$tart, Common Core, and FDIC Money Smart. Elementary is usually the thinnest shelf in the room. Fit your PD work? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K423" s="5" t="inlineStr"/>
@@ -18331,11 +18331,11 @@
       <c r="G425" s="5" t="inlineStr"/>
       <c r="H425" s="5" t="inlineStr"/>
       <c r="I425" s="5" t="n">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="J425" s="5" t="inlineStr">
         <is>
-          <t>Jarod — you know the value of an AFC, and you spend your days on saving and counseling. Mine is the step before: spending. A six-year-old runs one purchase, ad to register. As a practitioner, would you point families toward it? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jarod — you know the value of an AFC, and you spend your days on saving and counseling. Mine is the step before: spending. A six-year-old runs one purchase, ad to register. As a practitioner, would you point families toward it? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K425" s="5" t="inlineStr"/>
@@ -18407,11 +18407,11 @@
       <c r="G427" s="5" t="inlineStr"/>
       <c r="H427" s="5" t="inlineStr"/>
       <c r="I427" s="5" t="n">
-        <v>588</v>
+        <v>603</v>
       </c>
       <c r="J427" s="5" t="inlineStr">
         <is>
-          <t>Jill — teaching financial literacy and investments, you see the gaps students carry up from childhood. Mine tries to close one at six, against five frameworks, built with a K-5 teacher of 30+ years. Fit your world, or too young? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jill — teaching financial literacy and investments, you see the gaps students carry up from childhood. Mine tries to close one at six, against five frameworks, built with a K-5 teacher of 30+ years. Fit your world, or too young? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K427" s="5" t="inlineStr"/>
@@ -18445,11 +18445,11 @@
       <c r="G428" s="5" t="inlineStr"/>
       <c r="H428" s="5" t="inlineStr"/>
       <c r="I428" s="5" t="n">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="J428" s="5" t="inlineStr">
         <is>
-          <t>Cami — an Oklahoma financial education market manager needs things that are fundable and countable. Mine has a grant-ready packet with cost math and a pre/post assessment so a sponsor can report what changed. Fit a program you run? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Cami — an Oklahoma financial education market manager needs things that are fundable and countable. Mine has a grant-ready packet with cost math and a pre/post assessment so a sponsor can report what changed. Fit a program you run? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K428" s="5" t="inlineStr"/>
@@ -18483,11 +18483,11 @@
       <c r="G429" s="5" t="inlineStr"/>
       <c r="H429" s="5" t="inlineStr"/>
       <c r="I429" s="5" t="n">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="J429" s="5" t="inlineStr">
         <is>
-          <t>Ed — WizeUp runs financial education as a charity, which means every pound has to earn its place. Mine is a book plus a completely free teacher pack, so the only cost is the copies. Fit what WizeUp delivers? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ed — WizeUp runs financial education as a charity, which means every pound has to earn its place. Mine is a book plus a completely free teacher pack, so the only cost is the copies. Fit what WizeUp delivers? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K429" s="5" t="inlineStr"/>
@@ -18559,11 +18559,11 @@
       <c r="G431" s="5" t="inlineStr"/>
       <c r="H431" s="5" t="inlineStr"/>
       <c r="I431" s="5" t="n">
-        <v>600</v>
+        <v>615</v>
       </c>
       <c r="J431" s="5" t="inlineStr">
         <is>
-          <t>Julie — as an AVP of financial education you decide what actually reaches members. Mine is K-5, which is usually the band with nothing at all, plus a grant-ready packet if the institution wanted to fund classroom sets. Worth a look? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Julie — as an AVP of financial education you decide what actually reaches members. Mine is K-5, which is usually the band with nothing at all, plus a grant-ready packet if the institution wanted to fund classroom sets. Worth a look? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K431" s="5" t="inlineStr"/>
@@ -18673,11 +18673,11 @@
       <c r="G434" s="5" t="inlineStr"/>
       <c r="H434" s="5" t="inlineStr"/>
       <c r="I434" s="5" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="J434" s="5" t="inlineStr">
         <is>
-          <t>Skyler — Financial Education Instructor of the Year means you know what actually lands with students. Mine is K-5, a decade below your usual, teaching spending rather than saving. Does starting that early stick, in your experience? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Skyler — Financial Education Instructor of the Year means you know what actually lands with students. Mine is K-5, a decade below your usual, teaching spending rather than saving. Does starting that early stick, in your experience? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K434" s="5" t="inlineStr"/>
@@ -18711,11 +18711,11 @@
       <c r="G435" s="5" t="inlineStr"/>
       <c r="H435" s="5" t="inlineStr"/>
       <c r="I435" s="5" t="n">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="J435" s="5" t="inlineStr">
         <is>
-          <t>Christian — a math educator who champions financial literacy will appreciate that my book ends with real arithmetic: comparing two prices, applying a percentage off, adding sales tax. A six-year-old does all three. Fit your classroom? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Christian — a math educator who champions financial literacy will appreciate that my book ends with real arithmetic: comparing two prices, applying a percentage off, adding sales tax. A six-year-old does all three. Fit your classroom? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K435" s="5" t="inlineStr"/>
@@ -18749,11 +18749,11 @@
       <c r="G436" s="5" t="inlineStr"/>
       <c r="H436" s="5" t="inlineStr"/>
       <c r="I436" s="5" t="n">
-        <v>566</v>
+        <v>581</v>
       </c>
       <c r="J436" s="5" t="inlineStr">
         <is>
-          <t>Donna — a financial literacy educator and advisory board member has seen every curriculum twice. Mine is narrow by design: one transaction taught completely rather than a survey. Does narrow beat broad at K-5? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Donna — a financial literacy educator and advisory board member has seen every curriculum twice. Mine is narrow by design: one transaction taught completely rather than a survey. Does narrow beat broad at K-5? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K436" s="5" t="inlineStr"/>
@@ -18825,11 +18825,11 @@
       <c r="G438" s="5" t="inlineStr"/>
       <c r="H438" s="5" t="inlineStr"/>
       <c r="I438" s="5" t="n">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="J438" s="5" t="inlineStr">
         <is>
-          <t>Sydney — running operations at FinLit, you see what actually moves the needle versus what looks good in a deck. Mine is K-5 with free zero-prep lessons and nothing to reorder. Fit what FinLit does? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sydney — running operations at FinLit, you see what actually works versus what looks good in a deck. Mine is K-5 with free zero-prep lessons and nothing to reorder. Fit what FinLit does? Format, for the record: Lexile AD 620L — Adult Directed. One class period read aloud, the text carries the explanations so no instructor training is needed, and the same book does the family-engagement job at home. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K438" s="5" t="inlineStr"/>
@@ -18863,11 +18863,11 @@
       <c r="G439" s="5" t="inlineStr"/>
       <c r="H439" s="5" t="inlineStr"/>
       <c r="I439" s="5" t="n">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="J439" s="5" t="inlineStr">
         <is>
-          <t>Kelly — you build financial confidence in everyday Americans, and most of that starts with saving. I took the other fork. Before a kid ever saves a dollar, he spends one, and that's the skill mine teaches. Does the framing hold? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kelly — you build financial confidence in everyday Americans, and most of that starts with saving. I took the other fork. Before a kid ever saves a dollar, he spends one, and that's the skill mine teaches. Does the framing hold? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K439" s="5" t="inlineStr"/>
@@ -18901,11 +18901,11 @@
       <c r="G440" s="5" t="inlineStr"/>
       <c r="H440" s="5" t="inlineStr"/>
       <c r="I440" s="5" t="n">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="J440" s="5" t="inlineStr">
         <is>
-          <t>Chris — you create financial literacy content and hold the AFC, so you'll spot fluff instantly. Mine cuts against the grain: every money book teaches saving, mine teaches spending. As a fellow creator, does it land? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Chris — you create financial literacy content and hold the AFC, so you'll spot fluff instantly. Mine cuts against the grain: every money book teaches saving, mine teaches spending. As a fellow creator, does it land? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K440" s="5" t="inlineStr"/>
@@ -18939,11 +18939,11 @@
       <c r="G441" s="5" t="inlineStr"/>
       <c r="H441" s="5" t="inlineStr"/>
       <c r="I441" s="5" t="n">
-        <v>578</v>
+        <v>593</v>
       </c>
       <c r="J441" s="5" t="inlineStr">
         <is>
-          <t>Justin — you teach millennials and Gen Z in school workshops. I'm trying to reach them a decade earlier, on the skill they use first. Mine is K-5, one purchase, ad to register. Fit a workshop or a family you work with? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Justin — you teach millennials and Gen Z in school workshops. I'm trying to reach them a decade earlier, on the skill they use first. Mine is K-5, one purchase, ad to register. Fit a workshop or a family you work with? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K441" s="5" t="inlineStr"/>
@@ -19129,11 +19129,11 @@
       <c r="G446" s="5" t="inlineStr"/>
       <c r="H446" s="5" t="inlineStr"/>
       <c r="I446" s="5" t="n">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="J446" s="5" t="inlineStr">
         <is>
-          <t>Jeffery — as a chief financial educator you build programs for real audiences. Mine is K-5 with a free ungated classroom pack and a 21-term glossary in the back. Fit the learners you serve? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jeffery — as a chief financial educator you build programs for real audiences. Mine is K-5 with a free ungated classroom pack and a 21-term glossary in the back. Fit the learners you serve? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K446" s="5" t="inlineStr"/>
@@ -19167,11 +19167,11 @@
       <c r="G447" s="5" t="inlineStr"/>
       <c r="H447" s="5" t="inlineStr"/>
       <c r="I447" s="5" t="n">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="J447" s="5" t="inlineStr">
         <is>
-          <t>Kevin — you teach how money works for a living, so you know the lessons that stick start young. Mine teaches the skill they use first: spending. Built with a K-5 teacher of 30+ years, zero-prep lessons behind it. Fit your students? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kevin — you teach how money works for a living, so you know the lessons that stick start young. Mine teaches the skill they use first: spending. Built with a K-5 teacher of 30+ years, zero-prep lessons behind it. Fit your students? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K447" s="5" t="inlineStr"/>
@@ -19205,11 +19205,11 @@
       <c r="G448" s="5" t="inlineStr"/>
       <c r="H448" s="5" t="inlineStr"/>
       <c r="I448" s="5" t="n">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="J448" s="5" t="inlineStr">
         <is>
-          <t>Steven — helping educators and families plan ahead means you've seen the cost of what nobody taught at eight. Mine starts at six. Fit the families you serve? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Steven — helping educators and families plan ahead means you've seen the cost of what nobody taught at eight. Mine starts at six. Fit the families you serve? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K448" s="5" t="inlineStr"/>
@@ -19433,11 +19433,11 @@
       <c r="G454" s="5" t="inlineStr"/>
       <c r="H454" s="5" t="inlineStr"/>
       <c r="I454" s="5" t="n">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="J454" s="5" t="inlineStr">
         <is>
-          <t>Wadzi — scam awareness is downstream of exactly what my book teaches: check the price, question the deal, know what you're actually paying. Mine is the six-year-old version. Fit the audiences you reach? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Wadzi — scam awareness is downstream of exactly what my book teaches: check the price, question the deal, know what you're actually paying. Mine is the six-year-old version. Fit the audiences you reach? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K454" s="5" t="inlineStr"/>
@@ -19471,11 +19471,11 @@
       <c r="G455" s="5" t="inlineStr"/>
       <c r="H455" s="5" t="inlineStr"/>
       <c r="I455" s="5" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="J455" s="5" t="inlineStr">
         <is>
-          <t>Rick — as a financial educator you know the basics start younger than most people teach them. Mine is K-5 with free zero-prep lessons, teaching spending rather than saving. Fit the families you reach? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Rick — as a financial educator you know the basics start younger than most people teach them. Mine is K-5 with free zero-prep lessons, teaching spending rather than saving. Fit the families you reach? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K455" s="5" t="inlineStr"/>
@@ -19509,11 +19509,11 @@
       <c r="G456" s="5" t="inlineStr"/>
       <c r="H456" s="5" t="inlineStr"/>
       <c r="I456" s="5" t="n">
-        <v>543</v>
+        <v>558</v>
       </c>
       <c r="J456" s="5" t="inlineStr">
         <is>
-          <t>Amanda — running teacher PD in personal finance, you know what teachers actually use. Mine is K-5 with four zero-prep lessons and a 23-row crosswalk, all free and ungated. Fit your PD? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Amanda — running teacher PD in personal finance, you know what teachers actually use. Mine is K-5 with four zero-prep lessons and a 23-row crosswalk, all free and ungated. Fit your PD? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K456" s="5" t="inlineStr"/>
@@ -19585,11 +19585,11 @@
       <c r="G458" s="5" t="inlineStr"/>
       <c r="H458" s="5" t="inlineStr"/>
       <c r="I458" s="5" t="n">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="J458" s="5" t="inlineStr">
         <is>
-          <t>Andrea — a CFEI and legacy builder will judge the premise fast. Mine: we teach kids saving first, but spending is what they actually do. Does that hold, or is it a marketing line? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Andrea — a CFEI and legacy builder will judge the premise fast. Mine: we teach kids saving first, but spending is what they actually do. Does that hold, or is it a marketing line? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K458" s="5" t="inlineStr"/>
@@ -19661,11 +19661,11 @@
       <c r="G460" s="5" t="inlineStr"/>
       <c r="H460" s="5" t="inlineStr"/>
       <c r="I460" s="5" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="J460" s="5" t="inlineStr">
         <is>
-          <t>Angela — teaching personal finance at college level, you see the gaps students carry up from childhood in plain sight. Mine tries to close one at six. Fit anything you do? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Angela — teaching personal finance at college level, you see the gaps students carry up from childhood in plain sight. Mine tries to close one at six. Fit anything you do? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K460" s="5" t="inlineStr"/>
@@ -19699,11 +19699,11 @@
       <c r="G461" s="5" t="inlineStr"/>
       <c r="H461" s="5" t="inlineStr"/>
       <c r="I461" s="5" t="n">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="J461" s="5" t="inlineStr">
         <is>
-          <t>Ann — you help families find clarity and control, which starts younger than most people think. Mine is K-5 against five frameworks, teaching spending rather than saving. As an AFC, would you point families toward it? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ann — you help families find clarity and control, which starts younger than most people think. Mine is K-5 against five frameworks, teaching spending rather than saving. As an AFC, would you point families toward it? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K461" s="5" t="inlineStr"/>
@@ -19737,11 +19737,11 @@
       <c r="G462" s="5" t="inlineStr"/>
       <c r="H462" s="5" t="inlineStr"/>
       <c r="I462" s="5" t="n">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="J462" s="5" t="inlineStr">
         <is>
-          <t>Ashley — as a Certified Financial Educator you'll spot a thin premise instantly. Mine: spending is the first money skill a kid uses and no picture book is built around it. Point families toward it, or tell me I'm wrong? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ashley — as a Certified Financial Educator you'll spot a thin premise instantly. Mine: spending is the first money skill a kid uses and no picture book is built around it. Point families toward it, or tell me I'm wrong? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K462" s="5" t="inlineStr"/>
@@ -19775,11 +19775,11 @@
       <c r="G463" s="5" t="inlineStr"/>
       <c r="H463" s="5" t="inlineStr"/>
       <c r="I463" s="5" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="J463" s="5" t="inlineStr">
         <is>
-          <t>Audrey — The FinLit Zone teaches young people, so we're after the same kid at different ages. Mine is K-5, one purchase, ad to register. Complement what you do, or sit below it? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Audrey — The FinLit Zone teaches young people, so we're after the same kid at different ages. Mine is K-5, one purchase, ad to register. Complement what you do, or sit below it? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K463" s="5" t="inlineStr"/>
@@ -19813,11 +19813,11 @@
       <c r="G464" s="5" t="inlineStr"/>
       <c r="H464" s="5" t="inlineStr"/>
       <c r="I464" s="5" t="n">
-        <v>567</v>
+        <v>582</v>
       </c>
       <c r="J464" s="5" t="inlineStr">
         <is>
-          <t>Ayomide — a financial economist who also educates will judge the premise fast. Mine: children's financial education teaches saving almost exclusively while spending is what kids do first. Does the framing hold? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ayomide — a financial economist who also educates will judge the premise fast. Mine: children's financial education teaches saving almost exclusively while spending is what kids do first. Does the framing hold? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K464" s="5" t="inlineStr"/>
@@ -19851,11 +19851,11 @@
       <c r="G465" s="5" t="inlineStr"/>
       <c r="H465" s="5" t="inlineStr"/>
       <c r="I465" s="5" t="n">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="J465" s="5" t="inlineStr">
         <is>
-          <t>Bjorn — directing financial education with an AFC behind you, you decide what actually reaches learners. Mine is K-5, the band with the least material, plus a free ungated lesson set. Fit a program you run? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Bjorn — directing financial education with an AFC behind you, you decide what actually reaches learners. Mine is K-5, the band with the least material, plus a free ungated lesson set. Fit a program you run? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K465" s="5" t="inlineStr"/>
@@ -19927,11 +19927,11 @@
       <c r="G467" s="5" t="inlineStr"/>
       <c r="H467" s="5" t="inlineStr"/>
       <c r="I467" s="5" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="J467" s="5" t="inlineStr">
         <is>
-          <t>Brian — as a financial educator you know spending is where habits form and where nobody teaches. Mine is the K-5 version: one purchase, ad to register, tax at the end. Fit the learners you reach? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Brian — as a financial educator you know spending is where habits form and where nobody teaches. Mine is the K-5 version: one purchase, ad to register, tax at the end. Fit the learners you reach? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K467" s="5" t="inlineStr"/>
@@ -19965,11 +19965,11 @@
       <c r="G468" s="5" t="inlineStr"/>
       <c r="H468" s="5" t="inlineStr"/>
       <c r="I468" s="5" t="n">
-        <v>573</v>
+        <v>588</v>
       </c>
       <c r="J468" s="5" t="inlineStr">
         <is>
-          <t>Carey — equipping teachers is the harder half of this, and elementary teachers have close to nothing. Mine comes with four zero-prep lessons, assessments, and a crosswalk, all free. Fit what you give teachers? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Carey — equipping teachers is the harder half of this, and elementary teachers have close to nothing. Mine comes with four zero-prep lessons, assessments, and a crosswalk, all free. Fit what you give teachers? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K468" s="5" t="inlineStr"/>
@@ -20041,11 +20041,11 @@
       <c r="G470" s="5" t="inlineStr"/>
       <c r="H470" s="5" t="inlineStr"/>
       <c r="I470" s="5" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="J470" s="5" t="inlineStr">
         <is>
-          <t>Chi — as a Certified Financial Educator you'll spot a thin premise fast. Mine teaches spending rather than saving to ages 6-10, built with a K-5 teacher of 30+ years. Point families toward it? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Chi — as a Certified Financial Educator you'll spot a thin premise fast. Mine teaches spending rather than saving to ages 6-10, built with a K-5 teacher of 30+ years. Point families toward it? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K470" s="5" t="inlineStr"/>
@@ -20117,11 +20117,11 @@
       <c r="G472" s="5" t="inlineStr"/>
       <c r="H472" s="5" t="inlineStr"/>
       <c r="I472" s="5" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="J472" s="5" t="inlineStr">
         <is>
-          <t>Corey — financial education plus business strategy means you'll ask whether this scales. Mine is a book plus a completely free classroom materials, so the only line item is the copies. Does that hold up as a model? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Corey — financial education plus business strategy means you'll ask whether this scales. Mine is a book plus a completely free classroom materials, so the only line item is the copies. Does that hold up as a model? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K472" s="5" t="inlineStr"/>
@@ -20155,11 +20155,11 @@
       <c r="G473" s="5" t="inlineStr"/>
       <c r="H473" s="5" t="inlineStr"/>
       <c r="I473" s="5" t="n">
-        <v>588</v>
+        <v>603</v>
       </c>
       <c r="J473" s="5" t="inlineStr">
         <is>
-          <t>Dalia — a financial educator and community advocate meets families where money gets real. Mine teaches a six-year-old the complete purchase, and the free family activity was built for a kitchen table. Fit your community? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dalia — a financial educator and community advocate meets families where money gets real. Mine teaches a six-year-old the complete purchase, and the free family activity was built for a kitchen table. Fit your community? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K473" s="5" t="inlineStr"/>
@@ -20193,11 +20193,11 @@
       <c r="G474" s="5" t="inlineStr"/>
       <c r="H474" s="5" t="inlineStr"/>
       <c r="I474" s="5" t="n">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="J474" s="5" t="inlineStr">
         <is>
-          <t>Dan — coach and teacher both, you know money lessons stick when they're lived rather than lectured. Mine is one purchase, run properly, by a six-year-old. Fit your students? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dan — coach and teacher both, you know money lessons stick when they're lived rather than lectured. Mine is one purchase, run properly, by a six-year-old. Fit your students? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K474" s="5" t="inlineStr"/>
@@ -20231,11 +20231,11 @@
       <c r="G475" s="5" t="inlineStr"/>
       <c r="H475" s="5" t="inlineStr"/>
       <c r="I475" s="5" t="n">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="J475" s="5" t="inlineStr">
         <is>
-          <t>Debra — an AFC with an Ed.M bridges coaching and the classroom, which is exactly the two audiences for my book. K-5, five frameworks, free teaching pack. Point families toward it? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Debra — an AFC with an Ed.M bridges coaching and the classroom, which is exactly the two audiences for my book. K-5, five frameworks, free teaching pack. Point families toward it? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K475" s="5" t="inlineStr"/>
@@ -20307,11 +20307,11 @@
       <c r="G477" s="5" t="inlineStr"/>
       <c r="H477" s="5" t="inlineStr"/>
       <c r="I477" s="5" t="n">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="J477" s="5" t="inlineStr">
         <is>
-          <t>Derek — as a founder and financial educator you build programs for real people. Mine is K-5 with zero-prep, standards-aligned lessons and nothing consumable. Fit the families or clients you serve? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Derek — as a founder and financial educator you build programs for real people. Mine is K-5 with zero-prep, standards-aligned lessons and nothing consumable. Fit the families or clients you serve? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K477" s="5" t="inlineStr"/>
@@ -20383,11 +20383,11 @@
       <c r="G479" s="5" t="inlineStr"/>
       <c r="H479" s="5" t="inlineStr"/>
       <c r="I479" s="5" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="J479" s="5" t="inlineStr">
         <is>
-          <t>Hafsat — a financial education consultant with the CFEI knows what actually teaches versus what merely informs. Mine is K-5 against five frameworks with a free teacher pack. Fit the families or programs you work with? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hafsat — a financial education consultant with the CFEI knows what actually teaches versus what only informs. Mine is K-5 against five frameworks with a free teacher pack. Fit the families or programs you work with? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K479" s="5" t="inlineStr"/>
@@ -20421,11 +20421,11 @@
       <c r="G480" s="5" t="inlineStr"/>
       <c r="H480" s="5" t="inlineStr"/>
       <c r="I480" s="5" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="J480" s="5" t="inlineStr">
         <is>
-          <t>Helen — an executive who's also a Certified Financial Educator sees both the strategy and the teaching. Mine is K-5, five frameworks, free ungated classroom pack. Fit the programs you lead? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Helen — an executive who's also a Certified Financial Educator sees both the strategy and the teaching. Mine is K-5, five frameworks, free ungated classroom pack. Fit the programs you lead? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K480" s="5" t="inlineStr"/>
@@ -20497,11 +20497,11 @@
       <c r="G482" s="5" t="inlineStr"/>
       <c r="H482" s="5" t="inlineStr"/>
       <c r="I482" s="5" t="n">
-        <v>583</v>
+        <v>598</v>
       </c>
       <c r="J482" s="5" t="inlineStr">
         <is>
-          <t>Jonathan — teaching personal finance, you know a lesson dies the second kids tune out. Mine keeps them in the story: a boy, a robot, one real purchase. Built with a K-5 teacher and standards-aligned. Fit your classroom? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jonathan — teaching personal finance, you know a lesson dies the second kids tune out. Mine keeps them in the story: a boy, a robot, one real purchase. Built with a K-5 teacher and standards-aligned. Fit your classroom? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K482" s="5" t="inlineStr"/>
@@ -20535,11 +20535,11 @@
       <c r="G483" s="5" t="inlineStr"/>
       <c r="H483" s="5" t="inlineStr"/>
       <c r="I483" s="5" t="n">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="J483" s="5" t="inlineStr">
         <is>
-          <t>Jordan — you teach financial literacy, so you know a lesson dies the moment kids tune out. Mine keeps them in the story and teaches the skill they use first: spending. Zero-prep lessons behind it. Fit your classroom? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jordan — you teach financial literacy, so you know a lesson dies the moment kids tune out. Mine keeps them in the story and teaches the skill they use first: spending. Zero-prep lessons behind it. Fit your classroom? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K483" s="5" t="inlineStr"/>
@@ -20573,11 +20573,11 @@
       <c r="G484" s="5" t="inlineStr"/>
       <c r="H484" s="5" t="inlineStr"/>
       <c r="I484" s="5" t="n">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="J484" s="5" t="inlineStr">
         <is>
-          <t>Julie — driving economic mobility through financial education means you decide what's worth funding. Mine is K-5, the least-funded band, with a grant-ready packet and cost math already done. Fit your work? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Julie — driving economic mobility through financial education means you decide what's worth funding. Mine is K-5, the least-funded band, with a grant-ready packet and cost math already done. Fit your work? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K484" s="5" t="inlineStr"/>
@@ -20611,11 +20611,11 @@
       <c r="G485" s="5" t="inlineStr"/>
       <c r="H485" s="5" t="inlineStr"/>
       <c r="I485" s="5" t="n">
-        <v>523</v>
+        <v>538</v>
       </c>
       <c r="J485" s="5" t="inlineStr">
         <is>
-          <t>Keith — housing and financial literacy counseling means you meet people after the damage. Mine tries to prevent some of it at six. Fit the families East Akron serves? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Keith — housing and financial literacy counseling means you meet people after the damage. Mine tries to prevent some of it at six. Fit the families East Akron serves? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K485" s="5" t="inlineStr"/>
@@ -20687,11 +20687,11 @@
       <c r="G487" s="5" t="inlineStr"/>
       <c r="H487" s="5" t="inlineStr"/>
       <c r="I487" s="5" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="J487" s="5" t="inlineStr">
         <is>
-          <t>Kyle — financial literacy coaching at scale means you know what actually changes behavior. Mine tries to change one at six: compare before you buy. Fit your work, or too young? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kyle — financial literacy coaching at scale means you know what actually changes behavior. Mine tries to change one at six: compare before you buy. Fit your work, or too young? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K487" s="5" t="inlineStr"/>
@@ -20725,11 +20725,11 @@
       <c r="G488" s="5" t="inlineStr"/>
       <c r="H488" s="5" t="inlineStr"/>
       <c r="I488" s="5" t="n">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="J488" s="5" t="inlineStr">
         <is>
-          <t>Lakeisha — as a licensed financial educator you know the lessons that stick start young. Mine is K-5 with zero-prep lessons and a 21-term glossary. Fit the families you reach? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Lakeisha — as a licensed financial educator you know the lessons that stick start young. Mine is K-5 with zero-prep lessons and a 21-term glossary. Fit the families you reach? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K488" s="5" t="inlineStr"/>
@@ -20801,11 +20801,11 @@
       <c r="G490" s="5" t="inlineStr"/>
       <c r="H490" s="5" t="inlineStr"/>
       <c r="I490" s="5" t="n">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="J490" s="5" t="inlineStr">
         <is>
-          <t>Lara — a financial literacy advocate and educator knows the basics start young. Mine is K-5 against five frameworks, teaching spending rather than saving. Fit the people you reach? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Lara — a financial literacy advocate and educator knows the basics start young. Mine is K-5 against five frameworks, teaching spending rather than saving. Fit the people you reach? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K490" s="5" t="inlineStr"/>
@@ -20877,11 +20877,11 @@
       <c r="G492" s="5" t="inlineStr"/>
       <c r="H492" s="5" t="inlineStr"/>
       <c r="I492" s="5" t="n">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="J492" s="5" t="inlineStr">
         <is>
-          <t>Leah — a student loan expert has seen the far end of a chain that starts absurdly early. Mine starts at six with spending rather than saving. Fit the people you reach? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Leah — a student loan expert has seen the far end of a chain that starts absurdly early. Mine starts at six with spending rather than saving. Fit the people you reach? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K492" s="5" t="inlineStr"/>
@@ -20953,11 +20953,11 @@
       <c r="G494" s="5" t="inlineStr"/>
       <c r="H494" s="5" t="inlineStr"/>
       <c r="I494" s="5" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="J494" s="5" t="inlineStr">
         <is>
-          <t>Mark — as a Certified Financial Educator you'll size up the premise fast. Mine: spending is the first money skill kids use and the category ignores it. Does it hold, or have I missed a book? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Mark — as a Certified Financial Educator you'll size up the premise fast. Mine: spending is the first money skill kids use and the category ignores it. Does it hold, or have I missed a book? The one spec that counts in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K494" s="5" t="inlineStr"/>
@@ -20991,11 +20991,11 @@
       <c r="G495" s="5" t="inlineStr"/>
       <c r="H495" s="5" t="inlineStr"/>
       <c r="I495" s="5" t="n">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="J495" s="5" t="inlineStr">
         <is>
-          <t>Matt — delivering industry-leading financial education means you have a high bar for what counts as teaching. Mine is K-5 with four zero-prep lessons, assessments, and a 23-row crosswalk. Does it clear it? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Matt — delivering industry-leading financial education means you have a high bar for what counts as teaching. Mine is K-5 with four zero-prep lessons, assessments, and a 23-row crosswalk. Does it clear it? One spec worth having before it reaches a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K495" s="5" t="inlineStr"/>
@@ -21029,11 +21029,11 @@
       <c r="G496" s="5" t="inlineStr"/>
       <c r="H496" s="5" t="inlineStr"/>
       <c r="I496" s="5" t="n">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="J496" s="5" t="inlineStr">
         <is>
-          <t>Miria — as a community education officer you decide what reaches families. Mine is a K-5 read-along with a free family activity built for a kitchen table. Fit your outreach? One spec that matters in a classroom: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Miria — as a community education officer you decide what reaches families. Mine is a K-5 read-along with a free family activity built for a kitchen table. Fit your outreach? The classroom spec, for what it is worth: it's catalogued Lexile AD 620L — AD for Adult Directed, meaning read-with rather than read-alone. One class period out loud, and Mom explains every concept inside the text, so a teacher needs no finance background to run it. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="K496" s="5" t="inlineStr"/>
@@ -21067,11 +21067,11 @@
       <c r="G497" s="5" t="inlineStr"/>
       <c r="H497" s="5" t="inlineStr"/>
       <c r="I497" s="5" t="n">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="J497" s="5" t="inlineStr">
         <is>
-          <t>Monique — a coach with the CFP, ChFC, and AFC will judge this in a page. Mine teaches the complete purchase to six-year-olds, sal